--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,15 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="403">
   <si>
     <t>Denumire produs</t>
   </si>
   <si>
     <t>Stoc</t>
-  </si>
-  <si>
-    <t>Pret vanzare</t>
   </si>
   <si>
     <t>Pret fara TVA</t>
@@ -1583,14 +1580,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D476"/>
+  <dimension ref="A1:C476"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="4" width="15.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1600,1441 +1597,1132 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
       </c>
       <c r="B2">
         <v>235</v>
       </c>
       <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2">
         <v>12.4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>168.5</v>
-      </c>
-      <c r="D3">
         <v>139.26</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>213.9</v>
-      </c>
-      <c r="D4">
         <v>176.78</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>27</v>
       </c>
       <c r="C5">
-        <v>289.43</v>
-      </c>
-      <c r="D5">
         <v>239.2</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>317.75</v>
-      </c>
-      <c r="D6">
         <v>262.60000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>20</v>
       </c>
       <c r="C7">
-        <v>317.76</v>
-      </c>
-      <c r="D7">
         <v>262.61</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>11</v>
       </c>
       <c r="C8">
-        <v>493.51</v>
-      </c>
-      <c r="D8">
         <v>407.86</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>10</v>
       </c>
       <c r="C9">
-        <v>768.48</v>
-      </c>
-      <c r="D9">
         <v>635.11</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>29</v>
       </c>
       <c r="C10">
-        <v>374.52</v>
-      </c>
-      <c r="D10">
         <v>309.52</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>46</v>
       </c>
       <c r="C11">
-        <v>415.57</v>
-      </c>
-      <c r="D11">
         <v>343.45</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12">
-        <v>565.29999999999995</v>
-      </c>
-      <c r="D12">
         <v>467.19</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>647.5</v>
-      </c>
-      <c r="D13">
         <v>535.12</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
       <c r="C14">
-        <v>831.59</v>
-      </c>
-      <c r="D14">
         <v>687.26</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15">
-        <v>998.76</v>
-      </c>
-      <c r="D15">
         <v>825.42</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>998.76</v>
-      </c>
-      <c r="D16">
         <v>825.42</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
       <c r="C17">
-        <v>1092.3</v>
-      </c>
-      <c r="D17">
         <v>902.73</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18">
-        <v>845.05</v>
-      </c>
-      <c r="D18">
         <v>698.39</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>11</v>
       </c>
       <c r="C19">
-        <v>1100.7</v>
-      </c>
-      <c r="D19">
         <v>909.67</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20">
-        <v>1100.7</v>
-      </c>
-      <c r="D20">
         <v>909.67</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>1130.3</v>
-      </c>
-      <c r="D21">
         <v>934.13</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
       <c r="C22">
-        <v>1370.6</v>
-      </c>
-      <c r="D22">
         <v>1132.73</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>1370.6</v>
-      </c>
-      <c r="D23">
         <v>1132.73</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>22</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>2904</v>
-      </c>
-      <c r="D24">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>23</v>
       </c>
       <c r="B25">
         <v>27</v>
       </c>
       <c r="C25">
-        <v>647.29</v>
-      </c>
-      <c r="D25">
         <v>534.95000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26">
-        <v>854.4</v>
-      </c>
-      <c r="D26">
         <v>706.12</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>291.89999999999998</v>
-      </c>
-      <c r="D27">
         <v>241.24</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>241.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>25</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>291.89999999999998</v>
-      </c>
-      <c r="D28">
-        <v>241.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>26</v>
       </c>
       <c r="B29">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>336.4</v>
-      </c>
-      <c r="D29">
         <v>278.02</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>433.65</v>
-      </c>
-      <c r="D30">
         <v>358.39</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
       <c r="C31">
-        <v>455.71</v>
-      </c>
-      <c r="D31">
         <v>376.62</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>495.95</v>
-      </c>
-      <c r="D32">
         <v>409.88</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33">
         <v>21</v>
       </c>
       <c r="C33">
-        <v>535.79999999999995</v>
-      </c>
-      <c r="D33">
         <v>442.81</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34">
-        <v>594.55999999999995</v>
-      </c>
-      <c r="D34">
         <v>491.37</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>478.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>32</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>578.61</v>
-      </c>
-      <c r="D35">
-        <v>478.19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>33</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36">
-        <v>130.87</v>
-      </c>
-      <c r="D36">
         <v>108.16</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>40.270000000000003</v>
-      </c>
-      <c r="D37">
         <v>33.28</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38">
-        <v>25</v>
-      </c>
-      <c r="D38">
         <v>20.66</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39">
         <v>120</v>
       </c>
       <c r="C39">
-        <v>50.31</v>
-      </c>
-      <c r="D39">
         <v>41.58</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>7138.09</v>
-      </c>
-      <c r="D40">
         <v>5899.25</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41">
-        <v>7138.09</v>
-      </c>
-      <c r="D41">
         <v>5899.25</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42">
         <v>20</v>
       </c>
       <c r="C42">
-        <v>220.92</v>
-      </c>
-      <c r="D42">
         <v>182.58</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43">
         <v>43</v>
       </c>
       <c r="C43">
-        <v>50.31</v>
-      </c>
-      <c r="D43">
         <v>41.58</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>177.84</v>
-      </c>
-      <c r="D44">
         <v>146.97999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45">
         <v>78</v>
       </c>
       <c r="C45">
-        <v>41.89</v>
-      </c>
-      <c r="D45">
         <v>34.619999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
       <c r="C46">
-        <v>41.89</v>
-      </c>
-      <c r="D46">
         <v>34.619999999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47">
         <v>15</v>
       </c>
       <c r="C47">
-        <v>148.18</v>
-      </c>
-      <c r="D47">
         <v>122.46</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>156.07</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>45</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48">
-        <v>188.84</v>
-      </c>
-      <c r="D48">
-        <v>156.07</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>46</v>
       </c>
       <c r="B49">
         <v>60</v>
       </c>
       <c r="C49">
-        <v>30.99</v>
-      </c>
-      <c r="D49">
         <v>25.61</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50">
         <v>38</v>
       </c>
       <c r="C50">
-        <v>139.66</v>
-      </c>
-      <c r="D50">
         <v>115.42</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51">
         <v>124</v>
       </c>
       <c r="C51">
-        <v>30.98</v>
-      </c>
-      <c r="D51">
         <v>25.6</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>44.04</v>
-      </c>
-      <c r="D52">
         <v>36.4</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53">
         <v>3362</v>
       </c>
       <c r="C53">
-        <v>15.73</v>
-      </c>
-      <c r="D53">
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54">
-        <v>25.4</v>
-      </c>
-      <c r="D54">
         <v>20.99</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B55">
         <v>24</v>
       </c>
       <c r="C55">
-        <v>25.4</v>
-      </c>
-      <c r="D55">
         <v>20.99</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56">
         <v>60</v>
       </c>
       <c r="C56">
-        <v>28.28</v>
-      </c>
-      <c r="D56">
         <v>23.37</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57">
-        <v>437.92</v>
-      </c>
-      <c r="D57">
         <v>361.92</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>25.04</v>
-      </c>
-      <c r="D58">
         <v>20.69</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B59">
         <v>24</v>
       </c>
       <c r="C59">
-        <v>25.41</v>
-      </c>
-      <c r="D59">
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>385</v>
-      </c>
-      <c r="D60">
         <v>318.18</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>432.61</v>
-      </c>
-      <c r="D61">
         <v>357.53</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62">
         <v>27</v>
       </c>
       <c r="C62">
-        <v>21.96</v>
-      </c>
-      <c r="D62">
         <v>18.149999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B63">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>23.35</v>
-      </c>
-      <c r="D63">
         <v>19.3</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B64">
         <v>4</v>
       </c>
       <c r="C64">
-        <v>408.37</v>
-      </c>
-      <c r="D64">
         <v>337.5</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65">
         <v>36</v>
       </c>
       <c r="C65">
-        <v>40.71</v>
-      </c>
-      <c r="D65">
         <v>33.64</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66">
         <v>25</v>
       </c>
       <c r="C66">
-        <v>40.71</v>
-      </c>
-      <c r="D66">
         <v>33.64</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>360.73</v>
-      </c>
-      <c r="D67">
         <v>298.12</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>1982.77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
         <v>59</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68">
-        <v>2399.15</v>
-      </c>
-      <c r="D68">
-        <v>1982.77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>60</v>
       </c>
       <c r="B69">
         <v>20</v>
       </c>
       <c r="C69">
-        <v>338.95</v>
-      </c>
-      <c r="D69">
         <v>280.12</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B70">
         <v>90</v>
       </c>
       <c r="C70">
-        <v>29.66</v>
-      </c>
-      <c r="D70">
         <v>24.51</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B71">
         <v>24</v>
       </c>
       <c r="C71">
-        <v>31.56</v>
-      </c>
-      <c r="D71">
         <v>26.08</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B72">
         <v>36</v>
       </c>
       <c r="C72">
-        <v>31.71</v>
-      </c>
-      <c r="D72">
         <v>26.21</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73">
         <v>12</v>
       </c>
       <c r="C73">
-        <v>105.95</v>
-      </c>
-      <c r="D73">
         <v>87.56</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B74">
         <v>24</v>
       </c>
       <c r="C74">
-        <v>122.31</v>
-      </c>
-      <c r="D74">
         <v>101.08</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B75">
         <v>60</v>
       </c>
       <c r="C75">
-        <v>35.25</v>
-      </c>
-      <c r="D75">
         <v>29.13</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B76">
         <v>23</v>
       </c>
       <c r="C76">
-        <v>123.79</v>
-      </c>
-      <c r="D76">
         <v>102.31</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B77">
         <v>3</v>
       </c>
       <c r="C77">
-        <v>153.31</v>
-      </c>
-      <c r="D77">
         <v>126.7</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B78">
         <v>4</v>
       </c>
       <c r="C78">
-        <v>203.36</v>
-      </c>
-      <c r="D78">
         <v>168.07</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B79">
         <v>5</v>
       </c>
       <c r="C79">
-        <v>19.21</v>
-      </c>
-      <c r="D79">
         <v>15.88</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B80">
         <v>480</v>
       </c>
       <c r="C80">
-        <v>20.09</v>
-      </c>
-      <c r="D80">
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81">
         <v>7</v>
       </c>
       <c r="C81">
-        <v>72.7</v>
-      </c>
-      <c r="D81">
         <v>60.08</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82">
         <v>74</v>
       </c>
       <c r="C82">
-        <v>73.75</v>
-      </c>
-      <c r="D82">
         <v>60.95</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>92.65</v>
-      </c>
-      <c r="D83">
         <v>76.569999999999993</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B84">
         <v>84</v>
       </c>
       <c r="C84">
-        <v>92.65</v>
-      </c>
-      <c r="D84">
         <v>76.569999999999993</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B85">
         <v>65</v>
       </c>
       <c r="C85">
-        <v>20.32</v>
-      </c>
-      <c r="D85">
         <v>16.79</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B86">
         <v>120</v>
       </c>
       <c r="C86">
-        <v>22.94</v>
-      </c>
-      <c r="D86">
         <v>18.96</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B87">
         <v>28</v>
       </c>
       <c r="C87">
-        <v>77.959999999999994</v>
-      </c>
-      <c r="D87">
         <v>64.430000000000007</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B88">
         <v>8</v>
       </c>
       <c r="C88">
-        <v>88.49</v>
-      </c>
-      <c r="D88">
         <v>73.13</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B89">
         <v>22</v>
       </c>
       <c r="C89">
-        <v>96.2</v>
-      </c>
-      <c r="D89">
         <v>79.5</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B90">
         <v>60</v>
       </c>
       <c r="C90">
-        <v>108.15</v>
-      </c>
-      <c r="D90">
         <v>89.38</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B91">
         <v>50</v>
       </c>
       <c r="C91">
-        <v>20.55</v>
-      </c>
-      <c r="D91">
         <v>16.98</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B92">
         <v>44</v>
       </c>
       <c r="C92">
-        <v>22.94</v>
-      </c>
-      <c r="D92">
         <v>18.96</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B93">
         <v>19</v>
       </c>
       <c r="C93">
-        <v>79.37</v>
-      </c>
-      <c r="D93">
         <v>65.599999999999994</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B94">
         <v>40</v>
       </c>
       <c r="C94">
-        <v>88.49</v>
-      </c>
-      <c r="D94">
         <v>73.13</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B95">
         <v>23</v>
       </c>
       <c r="C95">
-        <v>108.16</v>
-      </c>
-      <c r="D95">
         <v>89.39</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
+        <v>75</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>3173.52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
         <v>76</v>
-      </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96">
-        <v>3839.96</v>
-      </c>
-      <c r="D96">
-        <v>3173.52</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>77</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97">
-        <v>230</v>
-      </c>
-      <c r="D97">
         <v>190.08</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
+        <v>77</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>66.12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
         <v>78</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98">
-        <v>80</v>
-      </c>
-      <c r="D98">
-        <v>66.12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>79</v>
       </c>
       <c r="B99">
         <v>21</v>
       </c>
       <c r="C99">
-        <v>30.73</v>
-      </c>
-      <c r="D99">
         <v>25.4</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B100">
         <v>15</v>
       </c>
       <c r="C100">
-        <v>49.51</v>
-      </c>
-      <c r="D100">
         <v>40.92</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B101">
         <v>9</v>
       </c>
       <c r="C101">
-        <v>30.73</v>
-      </c>
-      <c r="D101">
         <v>25.4</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B102">
         <v>17</v>
       </c>
       <c r="C102">
-        <v>33.96</v>
-      </c>
-      <c r="D102">
         <v>28.07</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B103">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>28.23</v>
-      </c>
-      <c r="D103">
         <v>23.33</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B104">
         <v>24</v>
@@ -3042,5215 +2730,4096 @@
       <c r="C104">
         <v>0</v>
       </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B105">
         <v>32</v>
       </c>
       <c r="C105">
-        <v>33.82</v>
-      </c>
-      <c r="D105">
         <v>27.95</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
+        <v>84</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>34.630000000000003</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
         <v>85</v>
-      </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106">
-        <v>41.9</v>
-      </c>
-      <c r="D106">
-        <v>34.630000000000003</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" t="s">
-        <v>86</v>
       </c>
       <c r="B107">
         <v>48</v>
       </c>
       <c r="C107">
-        <v>20.04</v>
-      </c>
-      <c r="D107">
         <v>16.559999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B108">
         <v>5</v>
       </c>
       <c r="C108">
-        <v>194.82</v>
-      </c>
-      <c r="D108">
         <v>161.01</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>54.27</v>
-      </c>
-      <c r="D109">
         <v>44.85</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B110">
         <v>9</v>
       </c>
       <c r="C110">
-        <v>79.650000000000006</v>
-      </c>
-      <c r="D110">
         <v>65.83</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B111">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>56.58</v>
-      </c>
-      <c r="D111">
         <v>46.76</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B112">
         <v>19</v>
       </c>
       <c r="C112">
-        <v>75.150000000000006</v>
-      </c>
-      <c r="D112">
         <v>62.11</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B113">
         <v>10</v>
       </c>
       <c r="C113">
-        <v>57.61</v>
-      </c>
-      <c r="D113">
         <v>47.61</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>63.76</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>93</v>
       </c>
-      <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114">
-        <v>77.150000000000006</v>
-      </c>
-      <c r="D114">
-        <v>63.76</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" t="s">
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>1159.2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
         <v>94</v>
       </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
-      <c r="C115">
-        <v>1402.63</v>
-      </c>
-      <c r="D115">
-        <v>1159.2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" t="s">
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
         <v>95</v>
-      </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116">
-        <v>308.55</v>
-      </c>
-      <c r="D116">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" t="s">
-        <v>96</v>
       </c>
       <c r="B117">
         <v>5</v>
       </c>
       <c r="C117">
-        <v>75.14</v>
-      </c>
-      <c r="D117">
         <v>62.1</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B118">
         <v>24</v>
       </c>
       <c r="C118">
-        <v>84.16</v>
-      </c>
-      <c r="D118">
         <v>69.55</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
+        <v>96</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>1391.04</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
         <v>97</v>
-      </c>
-      <c r="B119">
-        <v>1</v>
-      </c>
-      <c r="C119">
-        <v>1683.16</v>
-      </c>
-      <c r="D119">
-        <v>1391.04</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" t="s">
-        <v>98</v>
       </c>
       <c r="B120">
         <v>11</v>
       </c>
       <c r="C120">
-        <v>105.39</v>
-      </c>
-      <c r="D120">
         <v>87.1</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B121">
         <v>28</v>
       </c>
       <c r="C121">
-        <v>40.08</v>
-      </c>
-      <c r="D121">
         <v>33.119999999999997</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
+        <v>99</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>460.01</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>99</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>639.4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
         <v>100</v>
-      </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122">
-        <v>556.61</v>
-      </c>
-      <c r="D122">
-        <v>460.01</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" t="s">
-        <v>100</v>
-      </c>
-      <c r="B123">
-        <v>1</v>
-      </c>
-      <c r="C123">
-        <v>773.67</v>
-      </c>
-      <c r="D123">
-        <v>639.4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" t="s">
-        <v>101</v>
       </c>
       <c r="B124">
         <v>7</v>
       </c>
       <c r="C124">
-        <v>125.24</v>
-      </c>
-      <c r="D124">
         <v>103.5</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B125">
         <v>5</v>
       </c>
       <c r="C125">
-        <v>45.09</v>
-      </c>
-      <c r="D125">
         <v>37.26</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B126">
         <v>27</v>
       </c>
       <c r="C126">
-        <v>68.88</v>
-      </c>
-      <c r="D126">
         <v>56.93</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
+        <v>102</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>63.76</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
         <v>103</v>
-      </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127">
-        <v>77.150000000000006</v>
-      </c>
-      <c r="D127">
-        <v>63.76</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" t="s">
-        <v>104</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128">
-        <v>55.3</v>
-      </c>
-      <c r="D128">
         <v>45.7</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B129">
         <v>15</v>
       </c>
       <c r="C129">
-        <v>64.69</v>
-      </c>
-      <c r="D129">
         <v>53.46</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B130">
         <v>30</v>
       </c>
       <c r="C130">
-        <v>75.150000000000006</v>
-      </c>
-      <c r="D130">
         <v>62.11</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B131">
         <v>4</v>
       </c>
       <c r="C131">
-        <v>64.459999999999994</v>
-      </c>
-      <c r="D131">
         <v>53.27</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B132">
         <v>32</v>
       </c>
       <c r="C132">
-        <v>68.88</v>
-      </c>
-      <c r="D132">
         <v>56.93</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B133">
         <v>5</v>
       </c>
       <c r="C133">
-        <v>68.88</v>
-      </c>
-      <c r="D133">
         <v>56.93</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B134">
         <v>12</v>
       </c>
       <c r="C134">
-        <v>85.16</v>
-      </c>
-      <c r="D134">
         <v>70.38</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B135">
         <v>23</v>
       </c>
       <c r="C135">
-        <v>100.19</v>
-      </c>
-      <c r="D135">
         <v>82.8</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B136">
         <v>14</v>
       </c>
       <c r="C136">
-        <v>112.42</v>
-      </c>
-      <c r="D136">
         <v>92.91</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B137">
         <v>12</v>
       </c>
       <c r="C137">
-        <v>68.88</v>
-      </c>
-      <c r="D137">
         <v>56.93</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
+        <v>111</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>63.76</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>112</v>
-      </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138">
-        <v>77.150000000000006</v>
-      </c>
-      <c r="D138">
-        <v>63.76</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" t="s">
-        <v>113</v>
       </c>
       <c r="B139">
         <v>17</v>
       </c>
       <c r="C139">
-        <v>68.88</v>
-      </c>
-      <c r="D139">
         <v>56.93</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
+        <v>112</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>63.76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
         <v>113</v>
-      </c>
-      <c r="B140">
-        <v>1</v>
-      </c>
-      <c r="C140">
-        <v>77.150000000000006</v>
-      </c>
-      <c r="D140">
-        <v>63.76</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" t="s">
-        <v>114</v>
       </c>
       <c r="B141">
         <v>14</v>
       </c>
       <c r="C141">
-        <v>87.67</v>
-      </c>
-      <c r="D141">
         <v>72.45</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B142">
         <v>27</v>
       </c>
       <c r="C142">
-        <v>68.88</v>
-      </c>
-      <c r="D142">
         <v>56.93</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B143">
         <v>19</v>
       </c>
       <c r="C143">
-        <v>84.23</v>
-      </c>
-      <c r="D143">
         <v>69.61</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B144">
         <v>14</v>
       </c>
       <c r="C144">
-        <v>68.88</v>
-      </c>
-      <c r="D144">
         <v>56.93</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B145">
         <v>30</v>
       </c>
       <c r="C145">
-        <v>75.150000000000006</v>
-      </c>
-      <c r="D145">
         <v>62.11</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B146">
         <v>6</v>
       </c>
       <c r="C146">
-        <v>75.150000000000006</v>
-      </c>
-      <c r="D146">
         <v>62.11</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B147">
         <v>50</v>
       </c>
       <c r="C147">
-        <v>56.36</v>
-      </c>
-      <c r="D147">
         <v>46.58</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B148">
         <v>2</v>
       </c>
       <c r="C148">
-        <v>63.13</v>
-      </c>
-      <c r="D148">
         <v>52.17</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B149">
         <v>9</v>
       </c>
       <c r="C149">
-        <v>225.42</v>
-      </c>
-      <c r="D149">
         <v>186.3</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B150">
         <v>7</v>
       </c>
       <c r="C150">
-        <v>96.01</v>
-      </c>
-      <c r="D150">
         <v>79.349999999999994</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B151">
         <v>24</v>
       </c>
       <c r="C151">
-        <v>107.53</v>
-      </c>
-      <c r="D151">
         <v>88.87</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B152">
         <v>72</v>
       </c>
       <c r="C152">
-        <v>81.41</v>
-      </c>
-      <c r="D152">
         <v>67.28</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B153">
         <v>8</v>
       </c>
       <c r="C153">
-        <v>75.150000000000006</v>
-      </c>
-      <c r="D153">
         <v>62.11</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:3">
       <c r="A154" t="s">
+        <v>123</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>69.55</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
         <v>124</v>
-      </c>
-      <c r="B154">
-        <v>1</v>
-      </c>
-      <c r="C154">
-        <v>84.16</v>
-      </c>
-      <c r="D154">
-        <v>69.55</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" t="s">
-        <v>125</v>
       </c>
       <c r="B155">
         <v>10</v>
       </c>
       <c r="C155">
-        <v>69.02</v>
-      </c>
-      <c r="D155">
         <v>57.04</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B156">
         <v>6</v>
       </c>
       <c r="C156">
-        <v>102.69</v>
-      </c>
-      <c r="D156">
         <v>84.87</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B157">
         <v>5</v>
       </c>
       <c r="C157">
-        <v>34.229999999999997</v>
-      </c>
-      <c r="D157">
         <v>28.29</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B158">
         <v>7</v>
       </c>
       <c r="C158">
-        <v>223.98</v>
-      </c>
-      <c r="D158">
         <v>185.11</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B159">
         <v>24</v>
       </c>
       <c r="C159">
-        <v>70.47</v>
-      </c>
-      <c r="D159">
         <v>58.24</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:3">
       <c r="A160" t="s">
+        <v>128</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>65.23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
         <v>129</v>
-      </c>
-      <c r="B160">
-        <v>1</v>
-      </c>
-      <c r="C160">
-        <v>78.930000000000007</v>
-      </c>
-      <c r="D160">
-        <v>65.23</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" t="s">
-        <v>130</v>
       </c>
       <c r="B161">
         <v>11</v>
       </c>
       <c r="C161">
-        <v>352.05</v>
-      </c>
-      <c r="D161">
         <v>290.95</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:3">
       <c r="A162" t="s">
+        <v>130</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162">
+        <v>5744.25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
         <v>131</v>
-      </c>
-      <c r="B162">
-        <v>1</v>
-      </c>
-      <c r="C162">
-        <v>6950.54</v>
-      </c>
-      <c r="D162">
-        <v>5744.25</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" t="s">
-        <v>132</v>
       </c>
       <c r="B163">
         <v>3</v>
       </c>
       <c r="C163">
-        <v>494.54</v>
-      </c>
-      <c r="D163">
         <v>408.71</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B164">
         <v>4</v>
       </c>
       <c r="C164">
-        <v>692.97</v>
-      </c>
-      <c r="D164">
         <v>572.70000000000005</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B165">
         <v>40</v>
       </c>
       <c r="C165">
-        <v>72.36</v>
-      </c>
-      <c r="D165">
         <v>59.8</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B166">
         <v>4</v>
       </c>
       <c r="C166">
-        <v>444.58</v>
-      </c>
-      <c r="D166">
         <v>367.42</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B167">
         <v>12</v>
       </c>
       <c r="C167">
-        <v>55.67</v>
-      </c>
-      <c r="D167">
         <v>46.01</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B168">
         <v>10</v>
       </c>
       <c r="C168">
-        <v>25.05</v>
-      </c>
-      <c r="D168">
         <v>20.7</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B169">
         <v>23</v>
       </c>
       <c r="C169">
-        <v>25.05</v>
-      </c>
-      <c r="D169">
         <v>20.7</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:3">
       <c r="A170" t="s">
+        <v>137</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170">
+        <v>23.19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
         <v>138</v>
-      </c>
-      <c r="B170">
-        <v>1</v>
-      </c>
-      <c r="C170">
-        <v>28.06</v>
-      </c>
-      <c r="D170">
-        <v>23.19</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
-      <c r="A171" t="s">
-        <v>139</v>
       </c>
       <c r="B171">
         <v>28</v>
       </c>
       <c r="C171">
-        <v>75.150000000000006</v>
-      </c>
-      <c r="D171">
         <v>62.11</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B172">
         <v>2</v>
       </c>
       <c r="C172">
-        <v>3424.41</v>
-      </c>
-      <c r="D172">
         <v>2830.09</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B173">
         <v>12</v>
       </c>
       <c r="C173">
-        <v>87.67</v>
-      </c>
-      <c r="D173">
         <v>72.45</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B174">
         <v>19</v>
       </c>
       <c r="C174">
-        <v>87.67</v>
-      </c>
-      <c r="D174">
         <v>72.45</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B175">
         <v>3</v>
       </c>
       <c r="C175">
-        <v>65.13</v>
-      </c>
-      <c r="D175">
         <v>53.83</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B176">
         <v>40</v>
       </c>
       <c r="C176">
-        <v>72.95</v>
-      </c>
-      <c r="D176">
         <v>60.29</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B177">
         <v>8</v>
       </c>
       <c r="C177">
-        <v>100.01</v>
-      </c>
-      <c r="D177">
         <v>82.65</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B178">
         <v>24</v>
       </c>
       <c r="C178">
-        <v>112.95</v>
-      </c>
-      <c r="D178">
         <v>93.35</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:3">
       <c r="A179" t="s">
+        <v>144</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179">
+        <v>1217.1600000000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
         <v>145</v>
       </c>
-      <c r="B179">
-        <v>1</v>
-      </c>
-      <c r="C179">
-        <v>1472.76</v>
-      </c>
-      <c r="D179">
-        <v>1217.1600000000001</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
-      <c r="A180" t="s">
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>2749.17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
         <v>146</v>
-      </c>
-      <c r="B180">
-        <v>1</v>
-      </c>
-      <c r="C180">
-        <v>3326.5</v>
-      </c>
-      <c r="D180">
-        <v>2749.17</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
-      <c r="A181" t="s">
-        <v>147</v>
       </c>
       <c r="B181">
         <v>9</v>
       </c>
       <c r="C181">
-        <v>52.88</v>
-      </c>
-      <c r="D181">
         <v>43.7</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:3">
       <c r="A182" t="s">
+        <v>146</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182">
+        <v>48.95</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
         <v>147</v>
-      </c>
-      <c r="B182">
-        <v>1</v>
-      </c>
-      <c r="C182">
-        <v>59.23</v>
-      </c>
-      <c r="D182">
-        <v>48.95</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
-      <c r="A183" t="s">
-        <v>148</v>
       </c>
       <c r="B183">
         <v>8</v>
       </c>
       <c r="C183">
-        <v>78.150000000000006</v>
-      </c>
-      <c r="D183">
         <v>64.59</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:3">
       <c r="A184" t="s">
+        <v>147</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184">
+        <v>72.33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
         <v>148</v>
-      </c>
-      <c r="B184">
-        <v>1</v>
-      </c>
-      <c r="C184">
-        <v>87.52</v>
-      </c>
-      <c r="D184">
-        <v>72.33</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
-      <c r="A185" t="s">
-        <v>149</v>
       </c>
       <c r="B185">
         <v>7</v>
       </c>
       <c r="C185">
-        <v>265.77999999999997</v>
-      </c>
-      <c r="D185">
         <v>219.65</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B186">
         <v>15</v>
       </c>
       <c r="C186">
-        <v>78.55</v>
-      </c>
-      <c r="D186">
         <v>64.92</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B187">
         <v>62</v>
       </c>
       <c r="C187">
-        <v>34.79</v>
-      </c>
-      <c r="D187">
         <v>28.75</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B188">
         <v>9</v>
       </c>
       <c r="C188">
-        <v>34.79</v>
-      </c>
-      <c r="D188">
         <v>28.75</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:3">
       <c r="A189" t="s">
+        <v>152</v>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+      <c r="C189">
+        <v>37.43</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
         <v>153</v>
-      </c>
-      <c r="B189">
-        <v>1</v>
-      </c>
-      <c r="C189">
-        <v>45.29</v>
-      </c>
-      <c r="D189">
-        <v>37.43</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190" t="s">
-        <v>154</v>
       </c>
       <c r="B190">
         <v>47</v>
       </c>
       <c r="C190">
-        <v>34.79</v>
-      </c>
-      <c r="D190">
         <v>28.75</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B191">
         <v>9</v>
       </c>
       <c r="C191">
-        <v>139.16</v>
-      </c>
-      <c r="D191">
         <v>115.01</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B192">
         <v>16</v>
       </c>
       <c r="C192">
-        <v>32.369999999999997</v>
-      </c>
-      <c r="D192">
         <v>26.75</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:3">
       <c r="A193" t="s">
+        <v>155</v>
+      </c>
+      <c r="B193">
+        <v>1</v>
+      </c>
+      <c r="C193">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
         <v>156</v>
-      </c>
-      <c r="B193">
-        <v>1</v>
-      </c>
-      <c r="C193">
-        <v>46.45</v>
-      </c>
-      <c r="D193">
-        <v>38.39</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" t="s">
-        <v>157</v>
       </c>
       <c r="B194">
         <v>3</v>
       </c>
       <c r="C194">
-        <v>124.65</v>
-      </c>
-      <c r="D194">
         <v>103.02</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B195">
         <v>12</v>
       </c>
       <c r="C195">
-        <v>146.91</v>
-      </c>
-      <c r="D195">
         <v>121.41</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B196">
         <v>12</v>
       </c>
       <c r="C196">
-        <v>21.68</v>
-      </c>
-      <c r="D196">
         <v>17.920000000000002</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B197">
         <v>9</v>
       </c>
       <c r="C197">
-        <v>14.62</v>
-      </c>
-      <c r="D197">
         <v>12.08</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B198">
         <v>15</v>
       </c>
       <c r="C198">
-        <v>27.84</v>
-      </c>
-      <c r="D198">
         <v>23.01</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B199">
         <v>12</v>
       </c>
       <c r="C199">
-        <v>32.36</v>
-      </c>
-      <c r="D199">
         <v>26.74</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B200">
         <v>10</v>
       </c>
       <c r="C200">
-        <v>63.4</v>
-      </c>
-      <c r="D200">
         <v>52.4</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:3">
       <c r="A201" t="s">
+        <v>162</v>
+      </c>
+      <c r="B201">
+        <v>1</v>
+      </c>
+      <c r="C201">
+        <v>58.67</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
         <v>163</v>
-      </c>
-      <c r="B201">
-        <v>1</v>
-      </c>
-      <c r="C201">
-        <v>70.989999999999995</v>
-      </c>
-      <c r="D201">
-        <v>58.67</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
-      <c r="A202" t="s">
-        <v>164</v>
       </c>
       <c r="B202">
         <v>3</v>
       </c>
       <c r="C202">
-        <v>74.59</v>
-      </c>
-      <c r="D202">
         <v>61.64</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B203">
         <v>31</v>
       </c>
       <c r="C203">
-        <v>41.89</v>
-      </c>
-      <c r="D203">
         <v>34.619999999999997</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B204">
         <v>13</v>
       </c>
       <c r="C204">
-        <v>115.98</v>
-      </c>
-      <c r="D204">
         <v>95.85</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B205">
         <v>19</v>
       </c>
       <c r="C205">
-        <v>66.790000000000006</v>
-      </c>
-      <c r="D205">
         <v>55.2</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:3">
       <c r="A206" t="s">
+        <v>166</v>
+      </c>
+      <c r="B206">
+        <v>1</v>
+      </c>
+      <c r="C206">
+        <v>61.83</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
         <v>167</v>
-      </c>
-      <c r="B206">
-        <v>1</v>
-      </c>
-      <c r="C206">
-        <v>74.81</v>
-      </c>
-      <c r="D206">
-        <v>61.83</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4">
-      <c r="A207" t="s">
-        <v>168</v>
       </c>
       <c r="B207">
         <v>22</v>
       </c>
       <c r="C207">
-        <v>173.66</v>
-      </c>
-      <c r="D207">
         <v>143.52000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B208">
         <v>35</v>
       </c>
       <c r="C208">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="D208">
         <v>56.94</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B209">
         <v>16</v>
       </c>
       <c r="C209">
-        <v>82.1</v>
-      </c>
-      <c r="D209">
         <v>67.849999999999994</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:3">
       <c r="A210" t="s">
+        <v>169</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>75.989999999999995</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" t="s">
         <v>170</v>
-      </c>
-      <c r="B210">
-        <v>1</v>
-      </c>
-      <c r="C210">
-        <v>91.95</v>
-      </c>
-      <c r="D210">
-        <v>75.989999999999995</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
-      <c r="A211" t="s">
-        <v>171</v>
       </c>
       <c r="B211">
         <v>3</v>
       </c>
       <c r="C211">
-        <v>326.77999999999997</v>
-      </c>
-      <c r="D211">
         <v>270.07</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B212">
         <v>14</v>
       </c>
       <c r="C212">
-        <v>83.5</v>
-      </c>
-      <c r="D212">
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B213">
         <v>15</v>
       </c>
       <c r="C213">
-        <v>82.1</v>
-      </c>
-      <c r="D213">
         <v>67.849999999999994</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B214">
         <v>8</v>
       </c>
       <c r="C214">
-        <v>414.11</v>
-      </c>
-      <c r="D214">
         <v>342.24</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B215">
         <v>2</v>
       </c>
       <c r="C215">
-        <v>537.1</v>
-      </c>
-      <c r="D215">
         <v>443.88</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B216">
         <v>55</v>
       </c>
       <c r="C216">
-        <v>44.53</v>
-      </c>
-      <c r="D216">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B217">
         <v>23</v>
       </c>
       <c r="C217">
-        <v>61.12</v>
-      </c>
-      <c r="D217">
         <v>50.51</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B218">
         <v>2</v>
       </c>
       <c r="C218">
-        <v>704.1</v>
-      </c>
-      <c r="D218">
         <v>581.9</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B219">
         <v>2</v>
       </c>
       <c r="C219">
-        <v>700.74</v>
-      </c>
-      <c r="D219">
         <v>579.12</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B220">
         <v>11</v>
       </c>
       <c r="C220">
-        <v>132.19999999999999</v>
-      </c>
-      <c r="D220">
         <v>109.26</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:3">
       <c r="A221" t="s">
+        <v>178</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221">
+        <v>122.36</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
         <v>179</v>
-      </c>
-      <c r="B221">
-        <v>1</v>
-      </c>
-      <c r="C221">
-        <v>148.06</v>
-      </c>
-      <c r="D221">
-        <v>122.36</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
-      <c r="A222" t="s">
-        <v>180</v>
       </c>
       <c r="B222">
         <v>15</v>
       </c>
       <c r="C222">
-        <v>38.69</v>
-      </c>
-      <c r="D222">
         <v>31.98</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B223">
         <v>25</v>
       </c>
       <c r="C223">
-        <v>43.33</v>
-      </c>
-      <c r="D223">
         <v>35.81</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B224">
         <v>37</v>
       </c>
       <c r="C224">
-        <v>59.4</v>
-      </c>
-      <c r="D224">
         <v>49.09</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B225">
         <v>12</v>
       </c>
       <c r="C225">
-        <v>243.28</v>
-      </c>
-      <c r="D225">
         <v>201.06</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B226">
         <v>8</v>
       </c>
       <c r="C226">
-        <v>52.11</v>
-      </c>
-      <c r="D226">
         <v>43.07</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B227">
         <v>12</v>
       </c>
       <c r="C227">
-        <v>52.11</v>
-      </c>
-      <c r="D227">
         <v>43.07</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B228">
         <v>6</v>
       </c>
       <c r="C228">
-        <v>239.68</v>
-      </c>
-      <c r="D228">
         <v>198.08</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B229">
         <v>4</v>
       </c>
       <c r="C229">
-        <v>70.59</v>
-      </c>
-      <c r="D229">
         <v>58.34</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B230">
         <v>20</v>
       </c>
       <c r="C230">
-        <v>321.25</v>
-      </c>
-      <c r="D230">
         <v>265.5</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B231">
         <v>15</v>
       </c>
       <c r="C231">
-        <v>149.97</v>
-      </c>
-      <c r="D231">
         <v>123.94</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B232">
         <v>25</v>
       </c>
       <c r="C232">
-        <v>37.53</v>
-      </c>
-      <c r="D232">
         <v>31.02</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B233">
         <v>2</v>
       </c>
       <c r="C233">
-        <v>149.97</v>
-      </c>
-      <c r="D233">
         <v>123.94</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B234">
         <v>17</v>
       </c>
       <c r="C234">
-        <v>187.2</v>
-      </c>
-      <c r="D234">
         <v>154.71</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B235">
         <v>2</v>
       </c>
       <c r="C235">
-        <v>548.4</v>
-      </c>
-      <c r="D235">
         <v>453.22</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B236">
         <v>13</v>
       </c>
       <c r="C236">
-        <v>33.82</v>
-      </c>
-      <c r="D236">
         <v>27.95</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B237">
         <v>9</v>
       </c>
       <c r="C237">
-        <v>136.80000000000001</v>
-      </c>
-      <c r="D237">
         <v>113.06</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B238">
         <v>5</v>
       </c>
       <c r="C238">
-        <v>67.42</v>
-      </c>
-      <c r="D238">
         <v>55.72</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B239">
         <v>15</v>
       </c>
       <c r="C239">
-        <v>51.35</v>
-      </c>
-      <c r="D239">
         <v>42.44</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B240">
         <v>13</v>
       </c>
       <c r="C240">
-        <v>39.15</v>
-      </c>
-      <c r="D240">
         <v>32.36</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B241">
         <v>9</v>
       </c>
       <c r="C241">
-        <v>148.28</v>
-      </c>
-      <c r="D241">
         <v>122.55</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B242">
         <v>36</v>
       </c>
       <c r="C242">
-        <v>216.59</v>
-      </c>
-      <c r="D242">
         <v>179</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:3">
       <c r="A243" t="s">
+        <v>199</v>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243">
+        <v>2060.8000000000002</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" t="s">
         <v>200</v>
-      </c>
-      <c r="B243">
-        <v>1</v>
-      </c>
-      <c r="C243">
-        <v>2493.5700000000002</v>
-      </c>
-      <c r="D243">
-        <v>2060.8000000000002</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
-      <c r="A244" t="s">
-        <v>201</v>
       </c>
       <c r="B244">
         <v>11</v>
       </c>
       <c r="C244">
-        <v>55.1</v>
-      </c>
-      <c r="D244">
         <v>45.54</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B245">
         <v>11</v>
       </c>
       <c r="C245">
-        <v>55.1</v>
-      </c>
-      <c r="D245">
         <v>45.54</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B246">
         <v>11</v>
       </c>
       <c r="C246">
-        <v>198.15</v>
-      </c>
-      <c r="D246">
         <v>163.76</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B247">
         <v>11</v>
       </c>
       <c r="C247">
-        <v>222.91</v>
-      </c>
-      <c r="D247">
         <v>184.22</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B248">
         <v>15</v>
       </c>
       <c r="C248">
-        <v>36.17</v>
-      </c>
-      <c r="D248">
         <v>29.89</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B249">
         <v>25</v>
       </c>
       <c r="C249">
-        <v>40.51</v>
-      </c>
-      <c r="D249">
         <v>33.479999999999997</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B250">
         <v>36</v>
       </c>
       <c r="C250">
-        <v>55.73</v>
-      </c>
-      <c r="D250">
         <v>46.06</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:3">
       <c r="A251" t="s">
+        <v>205</v>
+      </c>
+      <c r="B251">
+        <v>1</v>
+      </c>
+      <c r="C251">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" t="s">
+        <v>205</v>
+      </c>
+      <c r="B252">
+        <v>1</v>
+      </c>
+      <c r="C252">
+        <v>5345.33</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" t="s">
         <v>206</v>
-      </c>
-      <c r="B251">
-        <v>1</v>
-      </c>
-      <c r="C251">
-        <v>5647.07</v>
-      </c>
-      <c r="D251">
-        <v>4667</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
-      <c r="A252" t="s">
-        <v>206</v>
-      </c>
-      <c r="B252">
-        <v>1</v>
-      </c>
-      <c r="C252">
-        <v>6467.85</v>
-      </c>
-      <c r="D252">
-        <v>5345.33</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
-      <c r="A253" t="s">
-        <v>207</v>
       </c>
       <c r="B253">
         <v>17</v>
       </c>
       <c r="C253">
-        <v>170.08</v>
-      </c>
-      <c r="D253">
         <v>140.56</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B254">
         <v>2</v>
       </c>
       <c r="C254">
-        <v>196.18</v>
-      </c>
-      <c r="D254">
         <v>162.13</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B255">
         <v>11</v>
       </c>
       <c r="C255">
-        <v>232.94</v>
-      </c>
-      <c r="D255">
         <v>192.51</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B256">
         <v>25</v>
       </c>
       <c r="C256">
-        <v>64.5</v>
-      </c>
-      <c r="D256">
         <v>53.31</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:3">
       <c r="A257" t="s">
+        <v>209</v>
+      </c>
+      <c r="B257">
+        <v>1</v>
+      </c>
+      <c r="C257">
+        <v>236.66</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
         <v>210</v>
-      </c>
-      <c r="B257">
-        <v>1</v>
-      </c>
-      <c r="C257">
-        <v>286.36</v>
-      </c>
-      <c r="D257">
-        <v>236.66</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
-      <c r="A258" t="s">
-        <v>211</v>
       </c>
       <c r="B258">
         <v>35</v>
       </c>
       <c r="C258">
-        <v>36.17</v>
-      </c>
-      <c r="D258">
         <v>29.89</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B259">
         <v>18</v>
       </c>
       <c r="C259">
-        <v>111.33</v>
-      </c>
-      <c r="D259">
         <v>92.01</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B260">
         <v>54</v>
       </c>
       <c r="C260">
-        <v>41.46</v>
-      </c>
-      <c r="D260">
         <v>34.26</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B261">
         <v>11</v>
       </c>
       <c r="C261">
-        <v>57.06</v>
-      </c>
-      <c r="D261">
         <v>47.16</v>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B262">
         <v>27</v>
       </c>
       <c r="C262">
-        <v>20.34</v>
-      </c>
-      <c r="D262">
         <v>16.809999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B263">
         <v>11</v>
       </c>
       <c r="C263">
-        <v>34.71</v>
-      </c>
-      <c r="D263">
         <v>28.69</v>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B264">
         <v>40</v>
       </c>
       <c r="C264">
-        <v>45.15</v>
-      </c>
-      <c r="D264">
         <v>37.31</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B265">
         <v>6</v>
       </c>
       <c r="C265">
-        <v>125.19</v>
-      </c>
-      <c r="D265">
         <v>103.46</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B266">
         <v>20</v>
       </c>
       <c r="C266">
-        <v>152.75</v>
-      </c>
-      <c r="D266">
         <v>126.24</v>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B267">
         <v>10</v>
       </c>
       <c r="C267">
-        <v>174.57</v>
-      </c>
-      <c r="D267">
         <v>144.27000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B268">
         <v>2</v>
       </c>
       <c r="C268">
-        <v>499.7</v>
-      </c>
-      <c r="D268">
         <v>412.98</v>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:3">
       <c r="A269" t="s">
+        <v>219</v>
+      </c>
+      <c r="B269">
+        <v>1</v>
+      </c>
+      <c r="C269">
+        <v>6302</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" t="s">
         <v>220</v>
-      </c>
-      <c r="B269">
-        <v>1</v>
-      </c>
-      <c r="C269">
-        <v>7625.42</v>
-      </c>
-      <c r="D269">
-        <v>6302</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
-      <c r="A270" t="s">
-        <v>221</v>
       </c>
       <c r="B270">
         <v>3</v>
       </c>
       <c r="C270">
-        <v>500.42</v>
-      </c>
-      <c r="D270">
         <v>413.57</v>
       </c>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:3">
       <c r="A271" t="s">
+        <v>220</v>
+      </c>
+      <c r="B271">
+        <v>1</v>
+      </c>
+      <c r="C271">
+        <v>570.28</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" t="s">
         <v>221</v>
-      </c>
-      <c r="B271">
-        <v>1</v>
-      </c>
-      <c r="C271">
-        <v>690.04</v>
-      </c>
-      <c r="D271">
-        <v>570.28</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
-      <c r="A272" t="s">
-        <v>222</v>
       </c>
       <c r="B272">
         <v>15</v>
       </c>
       <c r="C272">
-        <v>62.62</v>
-      </c>
-      <c r="D272">
         <v>51.75</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B273">
         <v>8</v>
       </c>
       <c r="C273">
-        <v>65.12</v>
-      </c>
-      <c r="D273">
         <v>53.82</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:3">
       <c r="A274" t="s">
+        <v>223</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274">
+        <v>20789.41</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" t="s">
+        <v>223</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275">
+        <v>33057.85</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" t="s">
         <v>224</v>
-      </c>
-      <c r="B274">
-        <v>1</v>
-      </c>
-      <c r="C274">
-        <v>25155.19</v>
-      </c>
-      <c r="D274">
-        <v>20789.41</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
-      <c r="A275" t="s">
-        <v>224</v>
-      </c>
-      <c r="B275">
-        <v>1</v>
-      </c>
-      <c r="C275">
-        <v>40000</v>
-      </c>
-      <c r="D275">
-        <v>33057.85</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
-      <c r="A276" t="s">
-        <v>225</v>
       </c>
       <c r="B276">
         <v>7</v>
       </c>
       <c r="C276">
-        <v>86.01</v>
-      </c>
-      <c r="D276">
         <v>71.08</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B277">
         <v>14</v>
       </c>
       <c r="C277">
-        <v>55.31</v>
-      </c>
-      <c r="D277">
         <v>45.71</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B278">
         <v>16</v>
       </c>
       <c r="C278">
-        <v>61.13</v>
-      </c>
-      <c r="D278">
         <v>50.52</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:3">
       <c r="A279" t="s">
+        <v>226</v>
+      </c>
+      <c r="B279">
+        <v>1</v>
+      </c>
+      <c r="C279">
+        <v>50.71</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
         <v>227</v>
-      </c>
-      <c r="B279">
-        <v>1</v>
-      </c>
-      <c r="C279">
-        <v>61.36</v>
-      </c>
-      <c r="D279">
-        <v>50.71</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" t="s">
-        <v>228</v>
       </c>
       <c r="B280">
         <v>10</v>
       </c>
       <c r="C280">
-        <v>62.62</v>
-      </c>
-      <c r="D280">
         <v>51.75</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B281">
         <v>13</v>
       </c>
       <c r="C281">
-        <v>44.53</v>
-      </c>
-      <c r="D281">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B282">
         <v>24</v>
       </c>
       <c r="C282">
-        <v>44.53</v>
-      </c>
-      <c r="D282">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B283">
         <v>45</v>
       </c>
       <c r="C283">
-        <v>71.010000000000005</v>
-      </c>
-      <c r="D283">
         <v>58.69</v>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B284">
         <v>35</v>
       </c>
       <c r="C284">
-        <v>70.33</v>
-      </c>
-      <c r="D284">
         <v>58.12</v>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B285">
         <v>5</v>
       </c>
       <c r="C285">
-        <v>70.8</v>
-      </c>
-      <c r="D285">
         <v>58.51</v>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B286">
         <v>42</v>
       </c>
       <c r="C286">
-        <v>79.290000000000006</v>
-      </c>
-      <c r="D286">
         <v>65.53</v>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B287">
         <v>34</v>
       </c>
       <c r="C287">
-        <v>87.67</v>
-      </c>
-      <c r="D287">
         <v>72.45</v>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B288">
         <v>26</v>
       </c>
       <c r="C288">
-        <v>36.17</v>
-      </c>
-      <c r="D288">
         <v>29.89</v>
       </c>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:3">
       <c r="A289" t="s">
+        <v>235</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+      <c r="C289">
+        <v>3806.5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" t="s">
         <v>236</v>
-      </c>
-      <c r="B289">
-        <v>1</v>
-      </c>
-      <c r="C289">
-        <v>4605.87</v>
-      </c>
-      <c r="D289">
-        <v>3806.5</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4">
-      <c r="A290" t="s">
-        <v>237</v>
       </c>
       <c r="B290">
         <v>6</v>
       </c>
       <c r="C290">
-        <v>406.32</v>
-      </c>
-      <c r="D290">
         <v>335.8</v>
       </c>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B291">
         <v>2</v>
       </c>
       <c r="C291">
-        <v>1218.95</v>
-      </c>
-      <c r="D291">
         <v>1007.4</v>
       </c>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B292">
         <v>20</v>
       </c>
       <c r="C292">
-        <v>6.97</v>
-      </c>
-      <c r="D292">
         <v>5.76</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B293">
         <v>9</v>
       </c>
       <c r="C293">
-        <v>116.89</v>
-      </c>
-      <c r="D293">
         <v>96.6</v>
       </c>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:3">
       <c r="A294" t="s">
+        <v>240</v>
+      </c>
+      <c r="B294">
+        <v>1</v>
+      </c>
+      <c r="C294">
+        <v>4456.4799999999996</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" t="s">
+        <v>240</v>
+      </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
+      <c r="C295">
+        <v>7429</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" t="s">
         <v>241</v>
-      </c>
-      <c r="B294">
-        <v>1</v>
-      </c>
-      <c r="C294">
-        <v>5392.34</v>
-      </c>
-      <c r="D294">
-        <v>4456.4799999999996</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
-      <c r="A295" t="s">
-        <v>241</v>
-      </c>
-      <c r="B295">
-        <v>1</v>
-      </c>
-      <c r="C295">
-        <v>8989.09</v>
-      </c>
-      <c r="D295">
-        <v>7429</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
-      <c r="A296" t="s">
-        <v>242</v>
       </c>
       <c r="B296">
         <v>2</v>
       </c>
       <c r="C296">
-        <v>676.26</v>
-      </c>
-      <c r="D296">
         <v>558.89</v>
       </c>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B297">
         <v>24</v>
       </c>
       <c r="C297">
-        <v>34.79</v>
-      </c>
-      <c r="D297">
         <v>28.75</v>
       </c>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B298">
         <v>13</v>
       </c>
       <c r="C298">
-        <v>34.79</v>
-      </c>
-      <c r="D298">
         <v>28.75</v>
       </c>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B299">
         <v>42</v>
       </c>
       <c r="C299">
-        <v>34.79</v>
-      </c>
-      <c r="D299">
         <v>28.75</v>
       </c>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B300">
         <v>14</v>
       </c>
       <c r="C300">
-        <v>34.79</v>
-      </c>
-      <c r="D300">
         <v>28.75</v>
       </c>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B301">
         <v>7</v>
       </c>
       <c r="C301">
-        <v>48.7</v>
-      </c>
-      <c r="D301">
         <v>40.25</v>
       </c>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B302">
         <v>81</v>
       </c>
       <c r="C302">
-        <v>38.97</v>
-      </c>
-      <c r="D302">
         <v>32.21</v>
       </c>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B303">
         <v>18</v>
       </c>
       <c r="C303">
-        <v>53.85</v>
-      </c>
-      <c r="D303">
         <v>44.5</v>
       </c>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B304">
         <v>24</v>
       </c>
       <c r="C304">
-        <v>67.77</v>
-      </c>
-      <c r="D304">
         <v>56.01</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B305">
         <v>17</v>
       </c>
       <c r="C305">
-        <v>62.26</v>
-      </c>
-      <c r="D305">
         <v>51.45</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B306">
         <v>4</v>
       </c>
       <c r="C306">
-        <v>70.260000000000005</v>
-      </c>
-      <c r="D306">
         <v>58.07</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B307">
         <v>9</v>
       </c>
       <c r="C307">
-        <v>51.22</v>
-      </c>
-      <c r="D307">
         <v>42.33</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B308">
         <v>2</v>
       </c>
       <c r="C308">
-        <v>56</v>
-      </c>
-      <c r="D308">
         <v>46.28</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B309">
         <v>17</v>
       </c>
       <c r="C309">
-        <v>71.64</v>
-      </c>
-      <c r="D309">
         <v>59.21</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:3">
       <c r="A310" t="s">
+        <v>253</v>
+      </c>
+      <c r="B310">
+        <v>1</v>
+      </c>
+      <c r="C310">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" t="s">
         <v>254</v>
-      </c>
-      <c r="B310">
-        <v>1</v>
-      </c>
-      <c r="C310">
-        <v>80.22</v>
-      </c>
-      <c r="D310">
-        <v>66.3</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
-      <c r="A311" t="s">
-        <v>255</v>
       </c>
       <c r="B311">
         <v>6</v>
       </c>
       <c r="C311">
-        <v>282.77999999999997</v>
-      </c>
-      <c r="D311">
         <v>233.7</v>
       </c>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B312">
         <v>14</v>
       </c>
       <c r="C312">
-        <v>69.19</v>
-      </c>
-      <c r="D312">
         <v>57.18</v>
       </c>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:3">
       <c r="A313" t="s">
+        <v>256</v>
+      </c>
+      <c r="B313">
+        <v>1</v>
+      </c>
+      <c r="C313">
+        <v>77.760000000000005</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" t="s">
         <v>257</v>
-      </c>
-      <c r="B313">
-        <v>1</v>
-      </c>
-      <c r="C313">
-        <v>94.09</v>
-      </c>
-      <c r="D313">
-        <v>77.760000000000005</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4">
-      <c r="A314" t="s">
-        <v>258</v>
       </c>
       <c r="B314">
         <v>17</v>
       </c>
       <c r="C314">
-        <v>59.12</v>
-      </c>
-      <c r="D314">
         <v>48.86</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B315">
         <v>13</v>
       </c>
       <c r="C315">
-        <v>56.3</v>
-      </c>
-      <c r="D315">
         <v>46.53</v>
       </c>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B316">
         <v>6</v>
       </c>
       <c r="C316">
-        <v>271.76</v>
-      </c>
-      <c r="D316">
         <v>224.6</v>
       </c>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B317">
         <v>12</v>
       </c>
       <c r="C317">
-        <v>85.22</v>
-      </c>
-      <c r="D317">
         <v>70.430000000000007</v>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B318">
         <v>1</v>
       </c>
       <c r="C318">
-        <v>74.38</v>
-      </c>
-      <c r="D318">
         <v>61.47</v>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B319">
         <v>12</v>
       </c>
       <c r="C319">
-        <v>101.45</v>
-      </c>
-      <c r="D319">
         <v>83.84</v>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B320">
         <v>3</v>
       </c>
       <c r="C320">
-        <v>294.45</v>
-      </c>
-      <c r="D320">
         <v>243.35</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B321">
         <v>19</v>
       </c>
       <c r="C321">
-        <v>86.16</v>
-      </c>
-      <c r="D321">
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B322">
         <v>16</v>
       </c>
       <c r="C322">
-        <v>78.900000000000006</v>
-      </c>
-      <c r="D322">
         <v>65.209999999999994</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B323">
         <v>12</v>
       </c>
       <c r="C323">
-        <v>101.45</v>
-      </c>
-      <c r="D323">
         <v>83.84</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B324">
         <v>8</v>
       </c>
       <c r="C324">
-        <v>306.89</v>
-      </c>
-      <c r="D324">
         <v>253.63</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B325">
         <v>12</v>
       </c>
       <c r="C325">
-        <v>26.86</v>
-      </c>
-      <c r="D325">
         <v>22.2</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B326">
         <v>2</v>
       </c>
       <c r="C326">
-        <v>52.11</v>
-      </c>
-      <c r="D326">
         <v>43.07</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B327">
         <v>9</v>
       </c>
       <c r="C327">
-        <v>55.67</v>
-      </c>
-      <c r="D327">
         <v>46.01</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B328">
         <v>5</v>
       </c>
       <c r="C328">
-        <v>43.83</v>
-      </c>
-      <c r="D328">
         <v>36.22</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B329">
         <v>39</v>
       </c>
       <c r="C329">
-        <v>43.84</v>
-      </c>
-      <c r="D329">
         <v>36.229999999999997</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B330">
         <v>24</v>
       </c>
       <c r="C330">
-        <v>58.47</v>
-      </c>
-      <c r="D330">
         <v>48.32</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B331">
         <v>12</v>
       </c>
       <c r="C331">
-        <v>70.63</v>
-      </c>
-      <c r="D331">
         <v>58.37</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B332">
         <v>10</v>
       </c>
       <c r="C332">
-        <v>276.52</v>
-      </c>
-      <c r="D332">
         <v>228.53</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B333">
         <v>7</v>
       </c>
       <c r="C333">
-        <v>58.45</v>
-      </c>
-      <c r="D333">
         <v>48.31</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B334">
         <v>10</v>
       </c>
       <c r="C334">
-        <v>94.64</v>
-      </c>
-      <c r="D334">
         <v>78.209999999999994</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B335">
         <v>200</v>
       </c>
       <c r="C335">
-        <v>54.37</v>
-      </c>
-      <c r="D335">
         <v>44.93</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:3">
       <c r="A336" t="s">
+        <v>277</v>
+      </c>
+      <c r="B336">
+        <v>1</v>
+      </c>
+      <c r="C336">
+        <v>6578.46</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" t="s">
         <v>278</v>
-      </c>
-      <c r="B336">
-        <v>1</v>
-      </c>
-      <c r="C336">
-        <v>7959.94</v>
-      </c>
-      <c r="D336">
-        <v>6578.46</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4">
-      <c r="A337" t="s">
-        <v>279</v>
       </c>
       <c r="B337">
         <v>37</v>
       </c>
       <c r="C337">
-        <v>209.44</v>
-      </c>
-      <c r="D337">
         <v>173.09</v>
       </c>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B338">
         <v>89</v>
       </c>
       <c r="C338">
-        <v>255.59</v>
-      </c>
-      <c r="D338">
         <v>211.23</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:3">
       <c r="A339" t="s">
+        <v>280</v>
+      </c>
+      <c r="B339">
+        <v>1</v>
+      </c>
+      <c r="C339">
+        <v>2066.7600000000002</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
         <v>281</v>
-      </c>
-      <c r="B339">
-        <v>1</v>
-      </c>
-      <c r="C339">
-        <v>2500.7800000000002</v>
-      </c>
-      <c r="D339">
-        <v>2066.7600000000002</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4">
-      <c r="A340" t="s">
-        <v>282</v>
       </c>
       <c r="B340">
         <v>3</v>
       </c>
       <c r="C340">
-        <v>854.87</v>
-      </c>
-      <c r="D340">
         <v>706.5</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B341">
         <v>25</v>
       </c>
       <c r="C341">
-        <v>34.15</v>
-      </c>
-      <c r="D341">
         <v>28.22</v>
       </c>
     </row>
-    <row r="342" spans="1:4">
+    <row r="342" spans="1:3">
       <c r="A342" t="s">
+        <v>282</v>
+      </c>
+      <c r="B342">
+        <v>1</v>
+      </c>
+      <c r="C342">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" t="s">
         <v>283</v>
-      </c>
-      <c r="B342">
-        <v>1</v>
-      </c>
-      <c r="C342">
-        <v>38.24</v>
-      </c>
-      <c r="D342">
-        <v>31.6</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4">
-      <c r="A343" t="s">
-        <v>284</v>
       </c>
       <c r="B343">
         <v>6</v>
       </c>
       <c r="C343">
-        <v>83.5</v>
-      </c>
-      <c r="D343">
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="344" spans="1:4">
+    <row r="344" spans="1:3">
       <c r="A344" t="s">
+        <v>283</v>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344">
+        <v>77.28</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" t="s">
         <v>284</v>
-      </c>
-      <c r="B344">
-        <v>1</v>
-      </c>
-      <c r="C344">
-        <v>93.51</v>
-      </c>
-      <c r="D344">
-        <v>77.28</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4">
-      <c r="A345" t="s">
-        <v>285</v>
       </c>
       <c r="B345">
         <v>24</v>
       </c>
       <c r="C345">
-        <v>47.32</v>
-      </c>
-      <c r="D345">
         <v>39.11</v>
       </c>
     </row>
-    <row r="346" spans="1:4">
+    <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B346">
         <v>7</v>
       </c>
       <c r="C346">
-        <v>14.15</v>
-      </c>
-      <c r="D346">
         <v>11.69</v>
       </c>
     </row>
-    <row r="347" spans="1:4">
+    <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B347">
         <v>3</v>
       </c>
       <c r="C347">
-        <v>862.8</v>
-      </c>
-      <c r="D347">
         <v>713.06</v>
       </c>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B348">
         <v>95</v>
       </c>
       <c r="C348">
-        <v>25.05</v>
-      </c>
-      <c r="D348">
         <v>20.7</v>
       </c>
     </row>
-    <row r="349" spans="1:4">
+    <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B349">
         <v>64</v>
       </c>
       <c r="C349">
-        <v>8.91</v>
-      </c>
-      <c r="D349">
         <v>7.36</v>
       </c>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B350">
         <v>9</v>
       </c>
       <c r="C350">
-        <v>13.92</v>
-      </c>
-      <c r="D350">
         <v>11.5</v>
       </c>
     </row>
-    <row r="351" spans="1:4">
+    <row r="351" spans="1:3">
       <c r="A351" t="s">
+        <v>290</v>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351">
+        <v>26.36</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
         <v>291</v>
-      </c>
-      <c r="B351">
-        <v>1</v>
-      </c>
-      <c r="C351">
-        <v>31.9</v>
-      </c>
-      <c r="D351">
-        <v>26.36</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4">
-      <c r="A352" t="s">
-        <v>292</v>
       </c>
       <c r="B352">
         <v>9</v>
       </c>
       <c r="C352">
-        <v>34.51</v>
-      </c>
-      <c r="D352">
         <v>28.52</v>
       </c>
     </row>
-    <row r="353" spans="1:4">
+    <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B353">
         <v>106</v>
       </c>
       <c r="C353">
-        <v>17.53</v>
-      </c>
-      <c r="D353">
         <v>14.49</v>
       </c>
     </row>
-    <row r="354" spans="1:4">
+    <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B354">
         <v>11</v>
       </c>
       <c r="C354">
-        <v>23.66</v>
-      </c>
-      <c r="D354">
         <v>19.55</v>
       </c>
     </row>
-    <row r="355" spans="1:4">
+    <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B355">
         <v>12</v>
       </c>
       <c r="C355">
-        <v>23.57</v>
-      </c>
-      <c r="D355">
         <v>19.48</v>
       </c>
     </row>
-    <row r="356" spans="1:4">
+    <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B356">
         <v>11</v>
       </c>
       <c r="C356">
-        <v>22.99</v>
-      </c>
-      <c r="D356">
         <v>19</v>
       </c>
     </row>
-    <row r="357" spans="1:4">
+    <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B357">
         <v>34</v>
       </c>
       <c r="C357">
-        <v>22.99</v>
-      </c>
-      <c r="D357">
         <v>19</v>
       </c>
     </row>
-    <row r="358" spans="1:4">
+    <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B358">
         <v>11</v>
       </c>
       <c r="C358">
-        <v>62.62</v>
-      </c>
-      <c r="D358">
         <v>51.75</v>
       </c>
     </row>
-    <row r="359" spans="1:4">
+    <row r="359" spans="1:3">
       <c r="A359" t="s">
+        <v>297</v>
+      </c>
+      <c r="B359">
+        <v>1</v>
+      </c>
+      <c r="C359">
+        <v>57.96</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" t="s">
         <v>298</v>
       </c>
-      <c r="B359">
-        <v>1</v>
-      </c>
-      <c r="C359">
-        <v>70.13</v>
-      </c>
-      <c r="D359">
-        <v>57.96</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4">
-      <c r="A360" t="s">
+      <c r="B360">
+        <v>1</v>
+      </c>
+      <c r="C360">
+        <v>862.7</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" t="s">
         <v>299</v>
-      </c>
-      <c r="B360">
-        <v>1</v>
-      </c>
-      <c r="C360">
-        <v>1043.8699999999999</v>
-      </c>
-      <c r="D360">
-        <v>862.7</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4">
-      <c r="A361" t="s">
-        <v>300</v>
       </c>
       <c r="B361">
         <v>11</v>
       </c>
       <c r="C361">
-        <v>68.88</v>
-      </c>
-      <c r="D361">
         <v>56.93</v>
       </c>
     </row>
-    <row r="362" spans="1:4">
+    <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B362">
         <v>2</v>
       </c>
       <c r="C362">
-        <v>1530.65</v>
-      </c>
-      <c r="D362">
         <v>1265</v>
       </c>
     </row>
-    <row r="363" spans="1:4">
+    <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B363">
         <v>30</v>
       </c>
       <c r="C363">
-        <v>67.819999999999993</v>
-      </c>
-      <c r="D363">
         <v>56.05</v>
       </c>
     </row>
-    <row r="364" spans="1:4">
+    <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B364">
         <v>6</v>
       </c>
       <c r="C364">
-        <v>285.25</v>
-      </c>
-      <c r="D364">
         <v>235.74</v>
       </c>
     </row>
-    <row r="365" spans="1:4">
+    <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B365">
         <v>17</v>
       </c>
       <c r="C365">
-        <v>75.75</v>
-      </c>
-      <c r="D365">
         <v>62.6</v>
       </c>
     </row>
-    <row r="366" spans="1:4">
+    <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B366">
         <v>15</v>
       </c>
       <c r="C366">
-        <v>319.87</v>
-      </c>
-      <c r="D366">
         <v>264.36</v>
       </c>
     </row>
-    <row r="367" spans="1:4">
+    <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B367">
         <v>10</v>
       </c>
       <c r="C367">
-        <v>77.930000000000007</v>
-      </c>
-      <c r="D367">
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="368" spans="1:4">
+    <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B368">
         <v>44</v>
       </c>
       <c r="C368">
-        <v>279.7</v>
-      </c>
-      <c r="D368">
         <v>231.16</v>
       </c>
     </row>
-    <row r="369" spans="1:4">
+    <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B369">
         <v>38</v>
       </c>
       <c r="C369">
-        <v>44.53</v>
-      </c>
-      <c r="D369">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="370" spans="1:4">
+    <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B370">
         <v>2</v>
       </c>
       <c r="C370">
-        <v>484.66</v>
-      </c>
-      <c r="D370">
         <v>400.55</v>
       </c>
     </row>
-    <row r="371" spans="1:4">
+    <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B371">
         <v>3</v>
       </c>
       <c r="C371">
-        <v>484.66</v>
-      </c>
-      <c r="D371">
         <v>400.55</v>
       </c>
     </row>
-    <row r="372" spans="1:4">
+    <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B372">
         <v>4</v>
       </c>
       <c r="C372">
-        <v>495.93</v>
-      </c>
-      <c r="D372">
         <v>409.86</v>
       </c>
     </row>
-    <row r="373" spans="1:4">
+    <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B373">
         <v>19</v>
       </c>
       <c r="C373">
-        <v>35.049999999999997</v>
-      </c>
-      <c r="D373">
         <v>28.97</v>
       </c>
     </row>
-    <row r="374" spans="1:4">
+    <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B374">
         <v>2</v>
       </c>
       <c r="C374">
-        <v>105.46</v>
-      </c>
-      <c r="D374">
         <v>87.16</v>
       </c>
     </row>
-    <row r="375" spans="1:4">
+    <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B375">
         <v>23</v>
       </c>
       <c r="C375">
-        <v>50.72</v>
-      </c>
-      <c r="D375">
         <v>41.92</v>
       </c>
     </row>
-    <row r="376" spans="1:4">
+    <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B376">
         <v>2</v>
       </c>
       <c r="C376">
-        <v>361.92</v>
-      </c>
-      <c r="D376">
         <v>299.11</v>
       </c>
     </row>
-    <row r="377" spans="1:4">
+    <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B377">
         <v>2</v>
       </c>
       <c r="C377">
-        <v>3040.42</v>
-      </c>
-      <c r="D377">
         <v>2512.7399999999998</v>
       </c>
     </row>
-    <row r="378" spans="1:4">
+    <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B378">
         <v>5</v>
       </c>
       <c r="C378">
-        <v>369.44</v>
-      </c>
-      <c r="D378">
         <v>305.32</v>
       </c>
     </row>
-    <row r="379" spans="1:4">
+    <row r="379" spans="1:3">
       <c r="A379" t="s">
+        <v>317</v>
+      </c>
+      <c r="B379">
+        <v>1</v>
+      </c>
+      <c r="C379">
+        <v>103.51</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" t="s">
         <v>318</v>
       </c>
-      <c r="B379">
-        <v>1</v>
-      </c>
-      <c r="C379">
-        <v>125.25</v>
-      </c>
-      <c r="D379">
-        <v>103.51</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4">
-      <c r="A380" t="s">
-        <v>319</v>
-      </c>
       <c r="B380">
         <v>1</v>
       </c>
       <c r="C380">
-        <v>50.71</v>
-      </c>
-      <c r="D380">
         <v>41.91</v>
       </c>
     </row>
-    <row r="381" spans="1:4">
+    <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B381">
         <v>41</v>
       </c>
       <c r="C381">
-        <v>65.58</v>
-      </c>
-      <c r="D381">
         <v>54.2</v>
       </c>
     </row>
-    <row r="382" spans="1:4">
+    <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B382">
         <v>12</v>
       </c>
       <c r="C382">
-        <v>34.04</v>
-      </c>
-      <c r="D382">
         <v>28.13</v>
       </c>
     </row>
-    <row r="383" spans="1:4">
+    <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B383">
         <v>4</v>
       </c>
       <c r="C383">
-        <v>123.26</v>
-      </c>
-      <c r="D383">
         <v>101.87</v>
       </c>
     </row>
-    <row r="384" spans="1:4">
+    <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B384">
         <v>4</v>
       </c>
       <c r="C384">
-        <v>151.25</v>
-      </c>
-      <c r="D384">
         <v>125</v>
       </c>
     </row>
-    <row r="385" spans="1:4">
+    <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B385">
         <v>10</v>
       </c>
       <c r="C385">
-        <v>33.14</v>
-      </c>
-      <c r="D385">
         <v>27.39</v>
       </c>
     </row>
-    <row r="386" spans="1:4">
+    <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B386">
         <v>8</v>
       </c>
       <c r="C386">
-        <v>117.15</v>
-      </c>
-      <c r="D386">
         <v>96.82</v>
       </c>
     </row>
-    <row r="387" spans="1:4">
+    <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B387">
         <v>2</v>
       </c>
       <c r="C387">
-        <v>359.42</v>
-      </c>
-      <c r="D387">
         <v>297.04000000000002</v>
       </c>
     </row>
-    <row r="388" spans="1:4">
+    <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B388">
         <v>8</v>
       </c>
       <c r="C388">
-        <v>33.39</v>
-      </c>
-      <c r="D388">
         <v>27.6</v>
       </c>
     </row>
-    <row r="389" spans="1:4">
+    <row r="389" spans="1:3">
       <c r="A389" t="s">
+        <v>326</v>
+      </c>
+      <c r="B389">
+        <v>1</v>
+      </c>
+      <c r="C389">
+        <v>5746.5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
         <v>327</v>
       </c>
-      <c r="B389">
-        <v>1</v>
-      </c>
-      <c r="C389">
-        <v>6953.27</v>
-      </c>
-      <c r="D389">
-        <v>5746.5</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4">
-      <c r="A390" t="s">
-        <v>328</v>
-      </c>
       <c r="B390">
         <v>1</v>
       </c>
       <c r="C390">
-        <v>454.6</v>
-      </c>
-      <c r="D390">
         <v>375.7</v>
       </c>
     </row>
-    <row r="391" spans="1:4">
+    <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B391">
         <v>2</v>
       </c>
       <c r="C391">
-        <v>624.91999999999996</v>
-      </c>
-      <c r="D391">
         <v>516.46</v>
       </c>
     </row>
-    <row r="392" spans="1:4">
+    <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B392">
         <v>4</v>
       </c>
       <c r="C392">
-        <v>150.30000000000001</v>
-      </c>
-      <c r="D392">
         <v>124.21</v>
       </c>
     </row>
-    <row r="393" spans="1:4">
+    <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B393">
         <v>31</v>
       </c>
       <c r="C393">
-        <v>13.92</v>
-      </c>
-      <c r="D393">
         <v>11.5</v>
       </c>
     </row>
-    <row r="394" spans="1:4">
+    <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B394">
         <v>4</v>
       </c>
       <c r="C394">
-        <v>688.8</v>
-      </c>
-      <c r="D394">
         <v>569.26</v>
       </c>
     </row>
-    <row r="395" spans="1:4">
+    <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B395">
         <v>4</v>
       </c>
       <c r="C395">
-        <v>461.3</v>
-      </c>
-      <c r="D395">
         <v>381.24</v>
       </c>
     </row>
-    <row r="396" spans="1:4">
+    <row r="396" spans="1:3">
       <c r="A396" t="s">
+        <v>332</v>
+      </c>
+      <c r="B396">
+        <v>1</v>
+      </c>
+      <c r="C396">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" t="s">
         <v>333</v>
       </c>
-      <c r="B396">
-        <v>1</v>
-      </c>
-      <c r="C396">
-        <v>56.63</v>
-      </c>
-      <c r="D396">
-        <v>46.8</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4">
-      <c r="A397" t="s">
+      <c r="B397">
+        <v>1</v>
+      </c>
+      <c r="C397">
+        <v>461.23</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" t="s">
+        <v>333</v>
+      </c>
+      <c r="B398">
+        <v>1</v>
+      </c>
+      <c r="C398">
+        <v>518.41999999999996</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" t="s">
         <v>334</v>
       </c>
-      <c r="B397">
-        <v>1</v>
-      </c>
-      <c r="C397">
-        <v>558.09</v>
-      </c>
-      <c r="D397">
-        <v>461.23</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4">
-      <c r="A398" t="s">
-        <v>334</v>
-      </c>
-      <c r="B398">
-        <v>1</v>
-      </c>
-      <c r="C398">
-        <v>627.29</v>
-      </c>
-      <c r="D398">
-        <v>518.41999999999996</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4">
-      <c r="A399" t="s">
+      <c r="B399">
+        <v>1</v>
+      </c>
+      <c r="C399">
+        <v>348.08</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" t="s">
         <v>335</v>
-      </c>
-      <c r="B399">
-        <v>1</v>
-      </c>
-      <c r="C399">
-        <v>421.18</v>
-      </c>
-      <c r="D399">
-        <v>348.08</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4">
-      <c r="A400" t="s">
-        <v>336</v>
       </c>
       <c r="B400">
         <v>10</v>
       </c>
       <c r="C400">
-        <v>31.45</v>
-      </c>
-      <c r="D400">
         <v>25.99</v>
       </c>
     </row>
-    <row r="401" spans="1:4">
+    <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B401">
         <v>13</v>
       </c>
       <c r="C401">
-        <v>33.619999999999997</v>
-      </c>
-      <c r="D401">
         <v>27.79</v>
       </c>
     </row>
-    <row r="402" spans="1:4">
+    <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B402">
         <v>3</v>
       </c>
       <c r="C402">
-        <v>240.39</v>
-      </c>
-      <c r="D402">
         <v>198.67</v>
       </c>
     </row>
-    <row r="403" spans="1:4">
+    <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B403">
         <v>18</v>
       </c>
       <c r="C403">
-        <v>31.2</v>
-      </c>
-      <c r="D403">
         <v>25.79</v>
       </c>
     </row>
-    <row r="404" spans="1:4">
+    <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B404">
         <v>39</v>
       </c>
       <c r="C404">
-        <v>21.1</v>
-      </c>
-      <c r="D404">
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:4">
+    <row r="405" spans="1:3">
       <c r="A405" t="s">
+        <v>340</v>
+      </c>
+      <c r="B405">
+        <v>1</v>
+      </c>
+      <c r="C405">
+        <v>361.41</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" t="s">
         <v>341</v>
-      </c>
-      <c r="B405">
-        <v>1</v>
-      </c>
-      <c r="C405">
-        <v>437.31</v>
-      </c>
-      <c r="D405">
-        <v>361.41</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4">
-      <c r="A406" t="s">
-        <v>342</v>
       </c>
       <c r="B406">
         <v>63</v>
       </c>
       <c r="C406">
-        <v>27.5</v>
-      </c>
-      <c r="D406">
         <v>22.73</v>
       </c>
     </row>
-    <row r="407" spans="1:4">
+    <row r="407" spans="1:3">
       <c r="A407" t="s">
+        <v>341</v>
+      </c>
+      <c r="B407">
+        <v>1</v>
+      </c>
+      <c r="C407">
+        <v>29.26</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
         <v>342</v>
       </c>
-      <c r="B407">
-        <v>1</v>
-      </c>
-      <c r="C407">
-        <v>35.4</v>
-      </c>
-      <c r="D407">
-        <v>29.26</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4">
-      <c r="A408" t="s">
+      <c r="B408">
+        <v>1</v>
+      </c>
+      <c r="C408">
+        <v>7257.28</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" t="s">
         <v>343</v>
       </c>
-      <c r="B408">
-        <v>1</v>
-      </c>
-      <c r="C408">
-        <v>8781.31</v>
-      </c>
-      <c r="D408">
-        <v>7257.28</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4">
-      <c r="A409" t="s">
+      <c r="B409">
+        <v>1</v>
+      </c>
+      <c r="C409">
+        <v>304.54000000000002</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410" t="s">
         <v>344</v>
-      </c>
-      <c r="B409">
-        <v>1</v>
-      </c>
-      <c r="C409">
-        <v>368.49</v>
-      </c>
-      <c r="D409">
-        <v>304.54000000000002</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4">
-      <c r="A410" t="s">
-        <v>345</v>
       </c>
       <c r="B410">
         <v>17</v>
       </c>
       <c r="C410">
-        <v>22.25</v>
-      </c>
-      <c r="D410">
         <v>18.39</v>
       </c>
     </row>
-    <row r="411" spans="1:4">
+    <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B411">
         <v>11</v>
       </c>
       <c r="C411">
-        <v>47.3</v>
-      </c>
-      <c r="D411">
         <v>39.090000000000003</v>
       </c>
     </row>
-    <row r="412" spans="1:4">
+    <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B412">
         <v>12</v>
       </c>
       <c r="C412">
-        <v>90.53</v>
-      </c>
-      <c r="D412">
         <v>74.819999999999993</v>
       </c>
     </row>
-    <row r="413" spans="1:4">
+    <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B413">
         <v>42</v>
       </c>
       <c r="C413">
-        <v>51.11</v>
-      </c>
-      <c r="D413">
         <v>42.24</v>
       </c>
     </row>
-    <row r="414" spans="1:4">
+    <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B414">
         <v>72</v>
       </c>
       <c r="C414">
-        <v>53.62</v>
-      </c>
-      <c r="D414">
         <v>44.31</v>
       </c>
     </row>
-    <row r="415" spans="1:4">
+    <row r="415" spans="1:3">
       <c r="A415" t="s">
+        <v>348</v>
+      </c>
+      <c r="B415">
+        <v>1</v>
+      </c>
+      <c r="C415">
+        <v>7173.59</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" t="s">
         <v>349</v>
       </c>
-      <c r="B415">
-        <v>1</v>
-      </c>
-      <c r="C415">
-        <v>8680.0400000000009</v>
-      </c>
-      <c r="D415">
-        <v>7173.59</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4">
-      <c r="A416" t="s">
+      <c r="B416">
+        <v>1</v>
+      </c>
+      <c r="C416">
+        <v>781.18</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" t="s">
         <v>350</v>
-      </c>
-      <c r="B416">
-        <v>1</v>
-      </c>
-      <c r="C416">
-        <v>945.23</v>
-      </c>
-      <c r="D416">
-        <v>781.18</v>
-      </c>
-    </row>
-    <row r="417" spans="1:4">
-      <c r="A417" t="s">
-        <v>351</v>
       </c>
       <c r="B417">
         <v>3</v>
       </c>
       <c r="C417">
-        <v>189.95</v>
-      </c>
-      <c r="D417">
         <v>156.97999999999999</v>
       </c>
     </row>
-    <row r="418" spans="1:4">
+    <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B418">
         <v>40</v>
       </c>
       <c r="C418">
-        <v>202.47</v>
-      </c>
-      <c r="D418">
         <v>167.33</v>
       </c>
     </row>
-    <row r="419" spans="1:4">
+    <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B419">
         <v>63</v>
       </c>
       <c r="C419">
-        <v>231.12</v>
-      </c>
-      <c r="D419">
         <v>191.01</v>
       </c>
     </row>
-    <row r="420" spans="1:4">
+    <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B420">
         <v>3</v>
       </c>
       <c r="C420">
-        <v>1998.94</v>
-      </c>
-      <c r="D420">
         <v>1652.02</v>
       </c>
     </row>
-    <row r="421" spans="1:4">
+    <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B421">
         <v>15</v>
       </c>
       <c r="C421">
-        <v>67.03</v>
-      </c>
-      <c r="D421">
         <v>55.4</v>
       </c>
     </row>
-    <row r="422" spans="1:4">
+    <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B422">
         <v>72</v>
       </c>
       <c r="C422">
-        <v>75.069999999999993</v>
-      </c>
-      <c r="D422">
         <v>62.04</v>
       </c>
     </row>
-    <row r="423" spans="1:4">
+    <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B423">
         <v>2</v>
       </c>
       <c r="C423">
-        <v>9848.92</v>
-      </c>
-      <c r="D423">
         <v>8139.6</v>
       </c>
     </row>
-    <row r="424" spans="1:4">
+    <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B424">
         <v>32</v>
       </c>
       <c r="C424">
-        <v>284.99</v>
-      </c>
-      <c r="D424">
         <v>235.53</v>
       </c>
     </row>
-    <row r="425" spans="1:4">
+    <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B425">
         <v>28</v>
       </c>
       <c r="C425">
-        <v>280.62</v>
-      </c>
-      <c r="D425">
         <v>231.92</v>
       </c>
     </row>
-    <row r="426" spans="1:4">
+    <row r="426" spans="1:3">
       <c r="A426" t="s">
+        <v>357</v>
+      </c>
+      <c r="B426">
+        <v>1</v>
+      </c>
+      <c r="C426">
+        <v>34.630000000000003</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427" t="s">
         <v>358</v>
-      </c>
-      <c r="B426">
-        <v>1</v>
-      </c>
-      <c r="C426">
-        <v>41.9</v>
-      </c>
-      <c r="D426">
-        <v>34.630000000000003</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4">
-      <c r="A427" t="s">
-        <v>359</v>
       </c>
       <c r="B427">
         <v>4</v>
       </c>
       <c r="C427">
-        <v>79.319999999999993</v>
-      </c>
-      <c r="D427">
         <v>65.55</v>
       </c>
     </row>
-    <row r="428" spans="1:4">
+    <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B428">
         <v>13</v>
       </c>
       <c r="C428">
-        <v>315.69</v>
-      </c>
-      <c r="D428">
         <v>260.89999999999998</v>
       </c>
     </row>
-    <row r="429" spans="1:4">
+    <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B429">
         <v>25</v>
       </c>
       <c r="C429">
-        <v>67.63</v>
-      </c>
-      <c r="D429">
         <v>55.89</v>
       </c>
     </row>
-    <row r="430" spans="1:4">
+    <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B430">
         <v>8</v>
       </c>
       <c r="C430">
-        <v>337.94</v>
-      </c>
-      <c r="D430">
         <v>279.29000000000002</v>
       </c>
     </row>
-    <row r="431" spans="1:4">
+    <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B431">
         <v>16</v>
       </c>
       <c r="C431">
-        <v>63.87</v>
-      </c>
-      <c r="D431">
         <v>52.79</v>
       </c>
     </row>
-    <row r="432" spans="1:4">
+    <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B432">
         <v>21</v>
       </c>
       <c r="C432">
-        <v>81.41</v>
-      </c>
-      <c r="D432">
         <v>67.28</v>
       </c>
     </row>
-    <row r="433" spans="1:4">
+    <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B433">
         <v>3</v>
       </c>
       <c r="C433">
-        <v>1239.05</v>
-      </c>
-      <c r="D433">
         <v>1024.01</v>
       </c>
     </row>
-    <row r="434" spans="1:4">
+    <row r="434" spans="1:3">
       <c r="A434" t="s">
+        <v>363</v>
+      </c>
+      <c r="B434">
+        <v>1</v>
+      </c>
+      <c r="C434">
+        <v>1138.5</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435" t="s">
         <v>364</v>
-      </c>
-      <c r="B434">
-        <v>1</v>
-      </c>
-      <c r="C434">
-        <v>1377.59</v>
-      </c>
-      <c r="D434">
-        <v>1138.5</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4">
-      <c r="A435" t="s">
-        <v>365</v>
       </c>
       <c r="B435">
         <v>2</v>
       </c>
       <c r="C435">
-        <v>48.79</v>
-      </c>
-      <c r="D435">
         <v>40.32</v>
       </c>
     </row>
-    <row r="436" spans="1:4">
+    <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B436">
         <v>3</v>
       </c>
       <c r="C436">
-        <v>261.77</v>
-      </c>
-      <c r="D436">
         <v>216.34</v>
       </c>
     </row>
-    <row r="437" spans="1:4">
+    <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B437">
         <v>5</v>
       </c>
       <c r="C437">
-        <v>57.06</v>
-      </c>
-      <c r="D437">
         <v>47.16</v>
       </c>
     </row>
-    <row r="438" spans="1:4">
+    <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B438">
         <v>30</v>
       </c>
       <c r="C438">
-        <v>65.459999999999994</v>
-      </c>
-      <c r="D438">
         <v>54.1</v>
       </c>
     </row>
-    <row r="439" spans="1:4">
+    <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B439">
         <v>20</v>
       </c>
       <c r="C439">
-        <v>308.58999999999997</v>
-      </c>
-      <c r="D439">
         <v>255.03</v>
       </c>
     </row>
-    <row r="440" spans="1:4">
+    <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B440">
         <v>18</v>
       </c>
       <c r="C440">
-        <v>267.17</v>
-      </c>
-      <c r="D440">
         <v>220.8</v>
       </c>
     </row>
-    <row r="441" spans="1:4">
+    <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B441">
         <v>22</v>
       </c>
       <c r="C441">
-        <v>308.58999999999997</v>
-      </c>
-      <c r="D441">
         <v>255.03</v>
       </c>
     </row>
-    <row r="442" spans="1:4">
+    <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B442">
         <v>12</v>
       </c>
       <c r="C442">
-        <v>74.39</v>
-      </c>
-      <c r="D442">
         <v>61.48</v>
       </c>
     </row>
-    <row r="443" spans="1:4">
+    <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B443">
         <v>4</v>
       </c>
       <c r="C443">
-        <v>371.95</v>
-      </c>
-      <c r="D443">
         <v>307.39999999999998</v>
       </c>
     </row>
-    <row r="444" spans="1:4">
+    <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B444">
         <v>10</v>
       </c>
       <c r="C444">
-        <v>65.12</v>
-      </c>
-      <c r="D444">
         <v>53.82</v>
       </c>
     </row>
-    <row r="445" spans="1:4">
+    <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B445">
         <v>3</v>
       </c>
       <c r="C445">
-        <v>282.83999999999997</v>
-      </c>
-      <c r="D445">
         <v>233.75</v>
       </c>
     </row>
-    <row r="446" spans="1:4">
+    <row r="446" spans="1:3">
       <c r="A446" t="s">
+        <v>373</v>
+      </c>
+      <c r="B446">
+        <v>1</v>
+      </c>
+      <c r="C446">
+        <v>261.8</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447" t="s">
         <v>374</v>
       </c>
-      <c r="B446">
-        <v>1</v>
-      </c>
-      <c r="C446">
-        <v>316.77999999999997</v>
-      </c>
-      <c r="D446">
-        <v>261.8</v>
-      </c>
-    </row>
-    <row r="447" spans="1:4">
-      <c r="A447" t="s">
+      <c r="B447">
+        <v>1</v>
+      </c>
+      <c r="C447">
+        <v>30.58</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" t="s">
         <v>375</v>
       </c>
-      <c r="B447">
-        <v>1</v>
-      </c>
-      <c r="C447">
-        <v>37</v>
-      </c>
-      <c r="D447">
+      <c r="B448">
+        <v>1</v>
+      </c>
+      <c r="C448">
         <v>30.58</v>
       </c>
     </row>
-    <row r="448" spans="1:4">
-      <c r="A448" t="s">
+    <row r="449" spans="1:3">
+      <c r="A449" t="s">
         <v>376</v>
-      </c>
-      <c r="B448">
-        <v>1</v>
-      </c>
-      <c r="C448">
-        <v>37</v>
-      </c>
-      <c r="D448">
-        <v>30.58</v>
-      </c>
-    </row>
-    <row r="449" spans="1:4">
-      <c r="A449" t="s">
-        <v>377</v>
       </c>
       <c r="B449">
         <v>54</v>
       </c>
       <c r="C449">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="D449">
         <v>14.79</v>
       </c>
     </row>
-    <row r="450" spans="1:4">
+    <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B450">
         <v>60</v>
       </c>
       <c r="C450">
-        <v>26.72</v>
-      </c>
-      <c r="D450">
         <v>22.08</v>
       </c>
     </row>
-    <row r="451" spans="1:4">
+    <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B451">
         <v>3</v>
       </c>
       <c r="C451">
-        <v>776.2</v>
-      </c>
-      <c r="D451">
         <v>641.49</v>
       </c>
     </row>
-    <row r="452" spans="1:4">
+    <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B452">
         <v>12</v>
       </c>
       <c r="C452">
-        <v>42.57</v>
-      </c>
-      <c r="D452">
         <v>35.18</v>
       </c>
     </row>
-    <row r="453" spans="1:4">
+    <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B453">
         <v>36</v>
       </c>
       <c r="C453">
-        <v>62.71</v>
-      </c>
-      <c r="D453">
         <v>51.83</v>
       </c>
     </row>
-    <row r="454" spans="1:4">
+    <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B454">
         <v>48</v>
       </c>
       <c r="C454">
-        <v>36.229999999999997</v>
-      </c>
-      <c r="D454">
         <v>29.94</v>
       </c>
     </row>
-    <row r="455" spans="1:4">
+    <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B455">
         <v>21</v>
       </c>
       <c r="C455">
-        <v>160.72999999999999</v>
-      </c>
-      <c r="D455">
         <v>132.83000000000001</v>
       </c>
     </row>
-    <row r="456" spans="1:4">
+    <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B456">
         <v>25</v>
       </c>
       <c r="C456">
-        <v>154.69</v>
-      </c>
-      <c r="D456">
         <v>127.84</v>
       </c>
     </row>
-    <row r="457" spans="1:4">
+    <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B457">
         <v>25</v>
       </c>
       <c r="C457">
-        <v>122.13</v>
-      </c>
-      <c r="D457">
         <v>100.93</v>
       </c>
     </row>
-    <row r="458" spans="1:4">
+    <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B458">
         <v>14</v>
       </c>
       <c r="C458">
-        <v>132.5</v>
-      </c>
-      <c r="D458">
         <v>109.5</v>
       </c>
     </row>
-    <row r="459" spans="1:4">
+    <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B459">
         <v>10</v>
       </c>
       <c r="C459">
-        <v>29.03</v>
-      </c>
-      <c r="D459">
         <v>23.99</v>
       </c>
     </row>
-    <row r="460" spans="1:4">
+    <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B460">
         <v>94</v>
       </c>
       <c r="C460">
-        <v>26.15</v>
-      </c>
-      <c r="D460">
         <v>21.61</v>
       </c>
     </row>
-    <row r="461" spans="1:4">
+    <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B461">
         <v>10</v>
       </c>
       <c r="C461">
-        <v>39.75</v>
-      </c>
-      <c r="D461">
         <v>32.85</v>
       </c>
     </row>
-    <row r="462" spans="1:4">
+    <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B462">
         <v>10</v>
       </c>
       <c r="C462">
-        <v>190.55</v>
-      </c>
-      <c r="D462">
         <v>157.47999999999999</v>
       </c>
     </row>
-    <row r="463" spans="1:4">
+    <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B463">
         <v>48</v>
       </c>
       <c r="C463">
-        <v>28.89</v>
-      </c>
-      <c r="D463">
         <v>23.88</v>
       </c>
     </row>
-    <row r="464" spans="1:4">
+    <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B464">
         <v>50</v>
       </c>
       <c r="C464">
-        <v>9.99</v>
-      </c>
-      <c r="D464">
         <v>8.26</v>
       </c>
     </row>
-    <row r="465" spans="1:4">
+    <row r="465" spans="1:3">
       <c r="A465" t="s">
+        <v>392</v>
+      </c>
+      <c r="B465">
+        <v>1</v>
+      </c>
+      <c r="C465">
+        <v>859.21</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3">
+      <c r="A466" t="s">
         <v>393</v>
       </c>
-      <c r="B465">
-        <v>1</v>
-      </c>
-      <c r="C465">
-        <v>1039.6400000000001</v>
-      </c>
-      <c r="D465">
-        <v>859.21</v>
-      </c>
-    </row>
-    <row r="466" spans="1:4">
-      <c r="A466" t="s">
+      <c r="B466">
+        <v>1</v>
+      </c>
+      <c r="C466">
+        <v>242.4</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3">
+      <c r="A467" t="s">
         <v>394</v>
-      </c>
-      <c r="B466">
-        <v>1</v>
-      </c>
-      <c r="C466">
-        <v>293.3</v>
-      </c>
-      <c r="D466">
-        <v>242.4</v>
-      </c>
-    </row>
-    <row r="467" spans="1:4">
-      <c r="A467" t="s">
-        <v>395</v>
       </c>
       <c r="B467">
         <v>3</v>
       </c>
       <c r="C467">
-        <v>6050</v>
-      </c>
-      <c r="D467">
         <v>5000</v>
       </c>
     </row>
-    <row r="468" spans="1:4">
+    <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B468">
         <v>105</v>
       </c>
       <c r="C468">
-        <v>22.15</v>
-      </c>
-      <c r="D468">
         <v>18.309999999999999</v>
       </c>
     </row>
-    <row r="469" spans="1:4">
+    <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B469">
         <v>31</v>
       </c>
       <c r="C469">
-        <v>117.91</v>
-      </c>
-      <c r="D469">
         <v>97.45</v>
       </c>
     </row>
-    <row r="470" spans="1:4">
+    <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B470">
         <v>3</v>
       </c>
       <c r="C470">
-        <v>367.88</v>
-      </c>
-      <c r="D470">
         <v>304.02999999999997</v>
       </c>
     </row>
-    <row r="471" spans="1:4">
+    <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B471">
         <v>11</v>
       </c>
       <c r="C471">
-        <v>367.88</v>
-      </c>
-      <c r="D471">
         <v>304.02999999999997</v>
       </c>
     </row>
-    <row r="472" spans="1:4">
+    <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B472">
         <v>6</v>
       </c>
       <c r="C472">
-        <v>2050.58</v>
-      </c>
-      <c r="D472">
         <v>1694.69</v>
       </c>
     </row>
-    <row r="473" spans="1:4">
+    <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B473">
         <v>6</v>
       </c>
       <c r="C473">
-        <v>214.17</v>
-      </c>
-      <c r="D473">
         <v>177</v>
       </c>
     </row>
-    <row r="474" spans="1:4">
+    <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B474">
         <v>10</v>
       </c>
       <c r="C474">
-        <v>279.5</v>
-      </c>
-      <c r="D474">
         <v>230.99</v>
       </c>
     </row>
-    <row r="475" spans="1:4">
+    <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B475">
         <v>96</v>
       </c>
       <c r="C475">
-        <v>35.75</v>
-      </c>
-      <c r="D475">
         <v>29.55</v>
       </c>
     </row>
-    <row r="476" spans="1:4">
+    <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B476">
         <v>72</v>
       </c>
       <c r="C476">
-        <v>25</v>
-      </c>
-      <c r="D476">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -5313,7 +5313,7 @@
         <v>1</v>
       </c>
       <c r="C339">
-        <v>2066.7600000000002</v>
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="C340">
-        <v>706.5</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="341" spans="1:3">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1281,10 +1281,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1583,18 +1589,18 @@
   <dimension ref="A1:C476"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1602,10 +1608,10 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>235</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>12.4</v>
       </c>
     </row>
@@ -1613,10 +1619,10 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>139.26</v>
       </c>
     </row>
@@ -1624,10 +1630,10 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>176.78</v>
       </c>
     </row>
@@ -1635,10 +1641,10 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>27</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>239.2</v>
       </c>
     </row>
@@ -1646,10 +1652,10 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>9</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>262.60000000000002</v>
       </c>
     </row>
@@ -1657,10 +1663,10 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>20</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>262.61</v>
       </c>
     </row>
@@ -1668,10 +1674,10 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>407.86</v>
       </c>
     </row>
@@ -1679,10 +1685,10 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>10</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>635.11</v>
       </c>
     </row>
@@ -1690,10 +1696,10 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>29</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>309.52</v>
       </c>
     </row>
@@ -1701,10 +1707,10 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>46</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>343.45</v>
       </c>
     </row>
@@ -1712,10 +1718,10 @@
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>467.19</v>
       </c>
     </row>
@@ -1723,10 +1729,10 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>535.12</v>
       </c>
     </row>
@@ -1734,10 +1740,10 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>687.26</v>
       </c>
     </row>
@@ -1745,10 +1751,10 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>6</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>825.42</v>
       </c>
     </row>
@@ -1756,10 +1762,10 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>2</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>825.42</v>
       </c>
     </row>
@@ -1767,10 +1773,10 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>10</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>902.73</v>
       </c>
     </row>
@@ -1778,10 +1784,10 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>4</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>698.39</v>
       </c>
     </row>
@@ -1789,10 +1795,10 @@
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="3">
         <v>909.67</v>
       </c>
     </row>
@@ -1800,10 +1806,10 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>909.67</v>
       </c>
     </row>
@@ -1811,10 +1817,10 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>2</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>934.13</v>
       </c>
     </row>
@@ -1822,10 +1828,10 @@
       <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="3">
         <v>4</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>1132.73</v>
       </c>
     </row>
@@ -1833,10 +1839,10 @@
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>1132.73</v>
       </c>
     </row>
@@ -1844,10 +1850,10 @@
       <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
         <v>2400</v>
       </c>
     </row>
@@ -1855,10 +1861,10 @@
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="3">
         <v>27</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>534.95000000000005</v>
       </c>
     </row>
@@ -1866,10 +1872,10 @@
       <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>706.12</v>
       </c>
     </row>
@@ -1877,10 +1883,10 @@
       <c r="A27" t="s">
         <v>24</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="3">
         <v>3</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>241.24</v>
       </c>
     </row>
@@ -1888,10 +1894,10 @@
       <c r="A28" t="s">
         <v>24</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3">
         <v>241.24</v>
       </c>
     </row>
@@ -1899,10 +1905,10 @@
       <c r="A29" t="s">
         <v>25</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="3">
         <v>9</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>278.02</v>
       </c>
     </row>
@@ -1910,10 +1916,10 @@
       <c r="A30" t="s">
         <v>26</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="3">
         <v>4</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>358.39</v>
       </c>
     </row>
@@ -1921,10 +1927,10 @@
       <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="3">
         <v>30</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>376.62</v>
       </c>
     </row>
@@ -1932,10 +1938,10 @@
       <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="3">
         <v>7</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>409.88</v>
       </c>
     </row>
@@ -1943,10 +1949,10 @@
       <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="3">
         <v>21</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>442.81</v>
       </c>
     </row>
@@ -1954,10 +1960,10 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="3">
         <v>3</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>491.37</v>
       </c>
     </row>
@@ -1965,10 +1971,10 @@
       <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3">
         <v>478.19</v>
       </c>
     </row>
@@ -1976,10 +1982,10 @@
       <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="3">
         <v>3</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="3">
         <v>108.16</v>
       </c>
     </row>
@@ -1987,10 +1993,10 @@
       <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="3">
         <v>6</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="3">
         <v>33.28</v>
       </c>
     </row>
@@ -1998,10 +2004,10 @@
       <c r="A38" t="s">
         <v>34</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="3">
         <v>5</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="3">
         <v>20.66</v>
       </c>
     </row>
@@ -2009,10 +2015,10 @@
       <c r="A39" t="s">
         <v>35</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="3">
         <v>120</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="3">
         <v>41.58</v>
       </c>
     </row>
@@ -2020,10 +2026,10 @@
       <c r="A40" t="s">
         <v>36</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="3">
         <v>2</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="3">
         <v>5899.25</v>
       </c>
     </row>
@@ -2031,10 +2037,10 @@
       <c r="A41" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="3">
         <v>4</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="3">
         <v>5899.25</v>
       </c>
     </row>
@@ -2042,10 +2048,10 @@
       <c r="A42" t="s">
         <v>38</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="3">
         <v>20</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="3">
         <v>182.58</v>
       </c>
     </row>
@@ -2053,10 +2059,10 @@
       <c r="A43" t="s">
         <v>39</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="3">
         <v>43</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>41.58</v>
       </c>
     </row>
@@ -2064,10 +2070,10 @@
       <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="3">
         <v>7</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
         <v>146.97999999999999</v>
       </c>
     </row>
@@ -2075,10 +2081,10 @@
       <c r="A45" t="s">
         <v>41</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="3">
         <v>78</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>34.619999999999997</v>
       </c>
     </row>
@@ -2086,10 +2092,10 @@
       <c r="A46" t="s">
         <v>42</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="3">
         <v>4</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="3">
         <v>34.619999999999997</v>
       </c>
     </row>
@@ -2097,10 +2103,10 @@
       <c r="A47" t="s">
         <v>43</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="3">
         <v>15</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>122.46</v>
       </c>
     </row>
@@ -2108,10 +2114,10 @@
       <c r="A48" t="s">
         <v>44</v>
       </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48">
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3">
         <v>156.07</v>
       </c>
     </row>
@@ -2119,10 +2125,10 @@
       <c r="A49" t="s">
         <v>45</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="3">
         <v>60</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="3">
         <v>25.61</v>
       </c>
     </row>
@@ -2130,10 +2136,10 @@
       <c r="A50" t="s">
         <v>46</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="3">
         <v>38</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>115.42</v>
       </c>
     </row>
@@ -2141,10 +2147,10 @@
       <c r="A51" t="s">
         <v>47</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="3">
         <v>124</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="3">
         <v>25.6</v>
       </c>
     </row>
@@ -2152,10 +2158,10 @@
       <c r="A52" t="s">
         <v>48</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>3</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="3">
         <v>36.4</v>
       </c>
     </row>
@@ -2163,10 +2169,10 @@
       <c r="A53" t="s">
         <v>49</v>
       </c>
-      <c r="B53">
-        <v>3362</v>
-      </c>
-      <c r="C53">
+      <c r="B53" s="3">
+        <v>3302</v>
+      </c>
+      <c r="C53" s="3">
         <v>13</v>
       </c>
     </row>
@@ -2174,10 +2180,10 @@
       <c r="A54" t="s">
         <v>50</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="3">
         <v>3</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="3">
         <v>20.99</v>
       </c>
     </row>
@@ -2185,10 +2191,10 @@
       <c r="A55" t="s">
         <v>50</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="3">
         <v>24</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="3">
         <v>20.99</v>
       </c>
     </row>
@@ -2196,10 +2202,10 @@
       <c r="A56" t="s">
         <v>50</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="3">
         <v>60</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="3">
         <v>23.37</v>
       </c>
     </row>
@@ -2207,10 +2213,10 @@
       <c r="A57" t="s">
         <v>51</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="3">
         <v>4</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="3">
         <v>361.92</v>
       </c>
     </row>
@@ -2218,10 +2224,10 @@
       <c r="A58" t="s">
         <v>52</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="3">
         <v>2</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="3">
         <v>20.69</v>
       </c>
     </row>
@@ -2229,10 +2235,10 @@
       <c r="A59" t="s">
         <v>52</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="3">
         <v>24</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>21</v>
       </c>
     </row>
@@ -2240,10 +2246,10 @@
       <c r="A60" t="s">
         <v>53</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="3">
         <v>2</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="3">
         <v>318.18</v>
       </c>
     </row>
@@ -2251,10 +2257,10 @@
       <c r="A61" t="s">
         <v>53</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="3">
         <v>2</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="3">
         <v>357.53</v>
       </c>
     </row>
@@ -2262,10 +2268,10 @@
       <c r="A62" t="s">
         <v>54</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="3">
         <v>27</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="3">
         <v>18.149999999999999</v>
       </c>
     </row>
@@ -2273,10 +2279,10 @@
       <c r="A63" t="s">
         <v>54</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>12</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="3">
         <v>19.3</v>
       </c>
     </row>
@@ -2284,10 +2290,10 @@
       <c r="A64" t="s">
         <v>55</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="3">
         <v>4</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="3">
         <v>337.5</v>
       </c>
     </row>
@@ -2295,10 +2301,10 @@
       <c r="A65" t="s">
         <v>56</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="3">
         <v>36</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="3">
         <v>33.64</v>
       </c>
     </row>
@@ -2306,10 +2312,10 @@
       <c r="A66" t="s">
         <v>56</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="3">
         <v>25</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="3">
         <v>33.64</v>
       </c>
     </row>
@@ -2317,10 +2323,10 @@
       <c r="A67" t="s">
         <v>57</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="3">
         <v>20</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="3">
         <v>298.12</v>
       </c>
     </row>
@@ -2328,10 +2334,10 @@
       <c r="A68" t="s">
         <v>58</v>
       </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68">
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3">
         <v>1982.77</v>
       </c>
     </row>
@@ -2339,10 +2345,10 @@
       <c r="A69" t="s">
         <v>59</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="3">
         <v>20</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="3">
         <v>280.12</v>
       </c>
     </row>
@@ -2350,10 +2356,10 @@
       <c r="A70" t="s">
         <v>60</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="3">
         <v>90</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="3">
         <v>24.51</v>
       </c>
     </row>
@@ -2361,10 +2367,10 @@
       <c r="A71" t="s">
         <v>61</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="3">
         <v>24</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="3">
         <v>26.08</v>
       </c>
     </row>
@@ -2372,10 +2378,10 @@
       <c r="A72" t="s">
         <v>61</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="3">
         <v>36</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="3">
         <v>26.21</v>
       </c>
     </row>
@@ -2383,10 +2389,10 @@
       <c r="A73" t="s">
         <v>62</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="3">
         <v>12</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="3">
         <v>87.56</v>
       </c>
     </row>
@@ -2394,10 +2400,10 @@
       <c r="A74" t="s">
         <v>62</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="3">
         <v>24</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="3">
         <v>101.08</v>
       </c>
     </row>
@@ -2405,10 +2411,10 @@
       <c r="A75" t="s">
         <v>63</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="3">
         <v>60</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="3">
         <v>29.13</v>
       </c>
     </row>
@@ -2416,10 +2422,10 @@
       <c r="A76" t="s">
         <v>64</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="3">
         <v>23</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="3">
         <v>102.31</v>
       </c>
     </row>
@@ -2427,10 +2433,10 @@
       <c r="A77" t="s">
         <v>65</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="3">
         <v>3</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="3">
         <v>126.7</v>
       </c>
     </row>
@@ -2438,10 +2444,10 @@
       <c r="A78" t="s">
         <v>65</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="3">
         <v>4</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="3">
         <v>168.07</v>
       </c>
     </row>
@@ -2449,10 +2455,10 @@
       <c r="A79" t="s">
         <v>66</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="3">
         <v>5</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="3">
         <v>15.88</v>
       </c>
     </row>
@@ -2460,10 +2466,10 @@
       <c r="A80" t="s">
         <v>66</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="3">
         <v>480</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="3">
         <v>16.600000000000001</v>
       </c>
     </row>
@@ -2471,10 +2477,10 @@
       <c r="A81" t="s">
         <v>67</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="3">
         <v>7</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="3">
         <v>60.08</v>
       </c>
     </row>
@@ -2482,10 +2488,10 @@
       <c r="A82" t="s">
         <v>67</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="3">
         <v>74</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="3">
         <v>60.95</v>
       </c>
     </row>
@@ -2493,10 +2499,10 @@
       <c r="A83" t="s">
         <v>68</v>
       </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
+      <c r="B83" s="3">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3">
         <v>76.569999999999993</v>
       </c>
     </row>
@@ -2504,10 +2510,10 @@
       <c r="A84" t="s">
         <v>68</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="3">
         <v>84</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="3">
         <v>76.569999999999993</v>
       </c>
     </row>
@@ -2515,10 +2521,10 @@
       <c r="A85" t="s">
         <v>69</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="3">
         <v>65</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="3">
         <v>16.79</v>
       </c>
     </row>
@@ -2526,10 +2532,10 @@
       <c r="A86" t="s">
         <v>69</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="3">
         <v>120</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="3">
         <v>18.96</v>
       </c>
     </row>
@@ -2537,10 +2543,10 @@
       <c r="A87" t="s">
         <v>70</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="3">
         <v>28</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="3">
         <v>64.430000000000007</v>
       </c>
     </row>
@@ -2548,10 +2554,10 @@
       <c r="A88" t="s">
         <v>70</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="3">
         <v>8</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="3">
         <v>73.13</v>
       </c>
     </row>
@@ -2559,10 +2565,10 @@
       <c r="A89" t="s">
         <v>71</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="3">
         <v>22</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="3">
         <v>79.5</v>
       </c>
     </row>
@@ -2570,10 +2576,10 @@
       <c r="A90" t="s">
         <v>71</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="3">
         <v>60</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="3">
         <v>89.38</v>
       </c>
     </row>
@@ -2581,10 +2587,10 @@
       <c r="A91" t="s">
         <v>72</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="3">
         <v>50</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="3">
         <v>16.98</v>
       </c>
     </row>
@@ -2592,10 +2598,10 @@
       <c r="A92" t="s">
         <v>72</v>
       </c>
-      <c r="B92">
-        <v>44</v>
-      </c>
-      <c r="C92">
+      <c r="B92" s="3">
+        <v>38</v>
+      </c>
+      <c r="C92" s="3">
         <v>18.96</v>
       </c>
     </row>
@@ -2603,10 +2609,10 @@
       <c r="A93" t="s">
         <v>73</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="3">
         <v>19</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="3">
         <v>65.599999999999994</v>
       </c>
     </row>
@@ -2614,10 +2620,10 @@
       <c r="A94" t="s">
         <v>73</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="3">
         <v>40</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="3">
         <v>73.13</v>
       </c>
     </row>
@@ -2625,10 +2631,10 @@
       <c r="A95" t="s">
         <v>74</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="3">
         <v>23</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="3">
         <v>89.39</v>
       </c>
     </row>
@@ -2636,10 +2642,10 @@
       <c r="A96" t="s">
         <v>75</v>
       </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96">
+      <c r="B96" s="3">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3">
         <v>3173.52</v>
       </c>
     </row>
@@ -2647,10 +2653,10 @@
       <c r="A97" t="s">
         <v>76</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="3">
         <v>2</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="3">
         <v>190.08</v>
       </c>
     </row>
@@ -2658,10 +2664,10 @@
       <c r="A98" t="s">
         <v>77</v>
       </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98">
+      <c r="B98" s="3">
+        <v>1</v>
+      </c>
+      <c r="C98" s="3">
         <v>66.12</v>
       </c>
     </row>
@@ -2669,10 +2675,10 @@
       <c r="A99" t="s">
         <v>78</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="3">
         <v>21</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="3">
         <v>25.4</v>
       </c>
     </row>
@@ -2680,10 +2686,10 @@
       <c r="A100" t="s">
         <v>79</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="3">
         <v>15</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="3">
         <v>40.92</v>
       </c>
     </row>
@@ -2691,10 +2697,10 @@
       <c r="A101" t="s">
         <v>80</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="3">
         <v>9</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="3">
         <v>25.4</v>
       </c>
     </row>
@@ -2702,10 +2708,10 @@
       <c r="A102" t="s">
         <v>81</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="3">
         <v>17</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="3">
         <v>28.07</v>
       </c>
     </row>
@@ -2713,10 +2719,10 @@
       <c r="A103" t="s">
         <v>82</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="3">
         <v>6</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="3">
         <v>23.33</v>
       </c>
     </row>
@@ -2724,10 +2730,10 @@
       <c r="A104" t="s">
         <v>83</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="3">
         <v>24</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2735,10 +2741,10 @@
       <c r="A105" t="s">
         <v>84</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="3">
         <v>32</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="3">
         <v>27.95</v>
       </c>
     </row>
@@ -2746,10 +2752,10 @@
       <c r="A106" t="s">
         <v>84</v>
       </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106">
+      <c r="B106" s="3">
+        <v>1</v>
+      </c>
+      <c r="C106" s="3">
         <v>34.630000000000003</v>
       </c>
     </row>
@@ -2757,10 +2763,10 @@
       <c r="A107" t="s">
         <v>85</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="3">
         <v>48</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="3">
         <v>16.559999999999999</v>
       </c>
     </row>
@@ -2768,10 +2774,10 @@
       <c r="A108" t="s">
         <v>86</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="3">
         <v>5</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="3">
         <v>161.01</v>
       </c>
     </row>
@@ -2779,10 +2785,10 @@
       <c r="A109" t="s">
         <v>87</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="3">
         <v>2</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="3">
         <v>44.85</v>
       </c>
     </row>
@@ -2790,10 +2796,10 @@
       <c r="A110" t="s">
         <v>88</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="3">
         <v>9</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="3">
         <v>65.83</v>
       </c>
     </row>
@@ -2801,10 +2807,10 @@
       <c r="A111" t="s">
         <v>89</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="3">
         <v>3</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="3">
         <v>46.76</v>
       </c>
     </row>
@@ -2812,10 +2818,10 @@
       <c r="A112" t="s">
         <v>90</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="3">
         <v>19</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -2823,10 +2829,10 @@
       <c r="A113" t="s">
         <v>91</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="3">
         <v>10</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="3">
         <v>47.61</v>
       </c>
     </row>
@@ -2834,10 +2840,10 @@
       <c r="A114" t="s">
         <v>92</v>
       </c>
-      <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114">
+      <c r="B114" s="3">
+        <v>1</v>
+      </c>
+      <c r="C114" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -2845,10 +2851,10 @@
       <c r="A115" t="s">
         <v>93</v>
       </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
-      <c r="C115">
+      <c r="B115" s="3">
+        <v>1</v>
+      </c>
+      <c r="C115" s="3">
         <v>1159.2</v>
       </c>
     </row>
@@ -2856,10 +2862,10 @@
       <c r="A116" t="s">
         <v>94</v>
       </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116">
+      <c r="B116" s="3">
+        <v>1</v>
+      </c>
+      <c r="C116" s="3">
         <v>255</v>
       </c>
     </row>
@@ -2867,10 +2873,10 @@
       <c r="A117" t="s">
         <v>95</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="3">
         <v>5</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="3">
         <v>62.1</v>
       </c>
     </row>
@@ -2878,10 +2884,10 @@
       <c r="A118" t="s">
         <v>95</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="3">
         <v>24</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="3">
         <v>69.55</v>
       </c>
     </row>
@@ -2889,10 +2895,10 @@
       <c r="A119" t="s">
         <v>96</v>
       </c>
-      <c r="B119">
-        <v>1</v>
-      </c>
-      <c r="C119">
+      <c r="B119" s="3">
+        <v>1</v>
+      </c>
+      <c r="C119" s="3">
         <v>1391.04</v>
       </c>
     </row>
@@ -2900,10 +2906,10 @@
       <c r="A120" t="s">
         <v>97</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="3">
         <v>11</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="3">
         <v>87.1</v>
       </c>
     </row>
@@ -2911,10 +2917,10 @@
       <c r="A121" t="s">
         <v>98</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="3">
         <v>28</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="3">
         <v>33.119999999999997</v>
       </c>
     </row>
@@ -2922,10 +2928,10 @@
       <c r="A122" t="s">
         <v>99</v>
       </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122">
+      <c r="B122" s="3">
+        <v>1</v>
+      </c>
+      <c r="C122" s="3">
         <v>460.01</v>
       </c>
     </row>
@@ -2933,10 +2939,10 @@
       <c r="A123" t="s">
         <v>99</v>
       </c>
-      <c r="B123">
-        <v>1</v>
-      </c>
-      <c r="C123">
+      <c r="B123" s="3">
+        <v>1</v>
+      </c>
+      <c r="C123" s="3">
         <v>639.4</v>
       </c>
     </row>
@@ -2944,10 +2950,10 @@
       <c r="A124" t="s">
         <v>100</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="3">
         <v>7</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="3">
         <v>103.5</v>
       </c>
     </row>
@@ -2955,10 +2961,10 @@
       <c r="A125" t="s">
         <v>101</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="3">
         <v>5</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="3">
         <v>37.26</v>
       </c>
     </row>
@@ -2966,10 +2972,10 @@
       <c r="A126" t="s">
         <v>102</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="3">
         <v>27</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -2977,10 +2983,10 @@
       <c r="A127" t="s">
         <v>102</v>
       </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127">
+      <c r="B127" s="3">
+        <v>1</v>
+      </c>
+      <c r="C127" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -2988,10 +2994,10 @@
       <c r="A128" t="s">
         <v>103</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="3">
         <v>3</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="3">
         <v>45.7</v>
       </c>
     </row>
@@ -2999,10 +3005,10 @@
       <c r="A129" t="s">
         <v>104</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="3">
         <v>15</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="3">
         <v>53.46</v>
       </c>
     </row>
@@ -3010,10 +3016,10 @@
       <c r="A130" t="s">
         <v>105</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="3">
         <v>30</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -3021,10 +3027,10 @@
       <c r="A131" t="s">
         <v>106</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="3">
         <v>4</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="3">
         <v>53.27</v>
       </c>
     </row>
@@ -3032,10 +3038,10 @@
       <c r="A132" t="s">
         <v>107</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="3">
         <v>32</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3043,10 +3049,10 @@
       <c r="A133" t="s">
         <v>108</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="3">
         <v>5</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3054,10 +3060,10 @@
       <c r="A134" t="s">
         <v>108</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="3">
         <v>12</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="3">
         <v>70.38</v>
       </c>
     </row>
@@ -3065,10 +3071,10 @@
       <c r="A135" t="s">
         <v>109</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="3">
         <v>23</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="3">
         <v>82.8</v>
       </c>
     </row>
@@ -3076,10 +3082,10 @@
       <c r="A136" t="s">
         <v>110</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="3">
         <v>14</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="3">
         <v>92.91</v>
       </c>
     </row>
@@ -3087,10 +3093,10 @@
       <c r="A137" t="s">
         <v>111</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="3">
         <v>12</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3098,10 +3104,10 @@
       <c r="A138" t="s">
         <v>111</v>
       </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138">
+      <c r="B138" s="3">
+        <v>1</v>
+      </c>
+      <c r="C138" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3109,10 +3115,10 @@
       <c r="A139" t="s">
         <v>112</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="3">
         <v>17</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3120,10 +3126,10 @@
       <c r="A140" t="s">
         <v>112</v>
       </c>
-      <c r="B140">
-        <v>1</v>
-      </c>
-      <c r="C140">
+      <c r="B140" s="3">
+        <v>1</v>
+      </c>
+      <c r="C140" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3131,10 +3137,10 @@
       <c r="A141" t="s">
         <v>113</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="3">
         <v>14</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="3">
         <v>72.45</v>
       </c>
     </row>
@@ -3142,10 +3148,10 @@
       <c r="A142" t="s">
         <v>114</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="3">
         <v>27</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3153,10 +3159,10 @@
       <c r="A143" t="s">
         <v>115</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="3">
         <v>19</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="3">
         <v>69.61</v>
       </c>
     </row>
@@ -3164,10 +3170,10 @@
       <c r="A144" t="s">
         <v>116</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="3">
         <v>14</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3175,10 +3181,10 @@
       <c r="A145" t="s">
         <v>117</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="3">
         <v>30</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -3186,10 +3192,10 @@
       <c r="A146" t="s">
         <v>118</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="3">
         <v>6</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -3197,10 +3203,10 @@
       <c r="A147" t="s">
         <v>119</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="3">
         <v>50</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="3">
         <v>46.58</v>
       </c>
     </row>
@@ -3208,10 +3214,10 @@
       <c r="A148" t="s">
         <v>119</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="3">
         <v>2</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="3">
         <v>52.17</v>
       </c>
     </row>
@@ -3219,10 +3225,10 @@
       <c r="A149" t="s">
         <v>120</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="3">
         <v>9</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="3">
         <v>186.3</v>
       </c>
     </row>
@@ -3230,10 +3236,10 @@
       <c r="A150" t="s">
         <v>121</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="3">
         <v>7</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="3">
         <v>79.349999999999994</v>
       </c>
     </row>
@@ -3241,10 +3247,10 @@
       <c r="A151" t="s">
         <v>121</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="3">
         <v>24</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="3">
         <v>88.87</v>
       </c>
     </row>
@@ -3252,10 +3258,10 @@
       <c r="A152" t="s">
         <v>122</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="3">
         <v>72</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="3">
         <v>67.28</v>
       </c>
     </row>
@@ -3263,10 +3269,10 @@
       <c r="A153" t="s">
         <v>123</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="3">
         <v>8</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -3274,10 +3280,10 @@
       <c r="A154" t="s">
         <v>123</v>
       </c>
-      <c r="B154">
-        <v>1</v>
-      </c>
-      <c r="C154">
+      <c r="B154" s="3">
+        <v>1</v>
+      </c>
+      <c r="C154" s="3">
         <v>69.55</v>
       </c>
     </row>
@@ -3285,10 +3291,10 @@
       <c r="A155" t="s">
         <v>124</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="3">
         <v>10</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="3">
         <v>57.04</v>
       </c>
     </row>
@@ -3296,10 +3302,10 @@
       <c r="A156" t="s">
         <v>125</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="3">
         <v>6</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="3">
         <v>84.87</v>
       </c>
     </row>
@@ -3307,10 +3313,10 @@
       <c r="A157" t="s">
         <v>126</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="3">
         <v>5</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="3">
         <v>28.29</v>
       </c>
     </row>
@@ -3318,10 +3324,10 @@
       <c r="A158" t="s">
         <v>127</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="3">
         <v>7</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="3">
         <v>185.11</v>
       </c>
     </row>
@@ -3329,10 +3335,10 @@
       <c r="A159" t="s">
         <v>128</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="3">
         <v>24</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="3">
         <v>58.24</v>
       </c>
     </row>
@@ -3340,10 +3346,10 @@
       <c r="A160" t="s">
         <v>128</v>
       </c>
-      <c r="B160">
-        <v>1</v>
-      </c>
-      <c r="C160">
+      <c r="B160" s="3">
+        <v>1</v>
+      </c>
+      <c r="C160" s="3">
         <v>65.23</v>
       </c>
     </row>
@@ -3351,10 +3357,10 @@
       <c r="A161" t="s">
         <v>129</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="3">
         <v>11</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="3">
         <v>290.95</v>
       </c>
     </row>
@@ -3362,10 +3368,10 @@
       <c r="A162" t="s">
         <v>130</v>
       </c>
-      <c r="B162">
-        <v>1</v>
-      </c>
-      <c r="C162">
+      <c r="B162" s="3">
+        <v>1</v>
+      </c>
+      <c r="C162" s="3">
         <v>5744.25</v>
       </c>
     </row>
@@ -3373,10 +3379,10 @@
       <c r="A163" t="s">
         <v>131</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="3">
         <v>3</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="3">
         <v>408.71</v>
       </c>
     </row>
@@ -3384,10 +3390,10 @@
       <c r="A164" t="s">
         <v>132</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="3">
         <v>4</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="3">
         <v>572.70000000000005</v>
       </c>
     </row>
@@ -3395,10 +3401,10 @@
       <c r="A165" t="s">
         <v>133</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="3">
         <v>40</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="3">
         <v>59.8</v>
       </c>
     </row>
@@ -3406,10 +3412,10 @@
       <c r="A166" t="s">
         <v>134</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="3">
         <v>4</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="3">
         <v>367.42</v>
       </c>
     </row>
@@ -3417,10 +3423,10 @@
       <c r="A167" t="s">
         <v>135</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="3">
         <v>12</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="3">
         <v>46.01</v>
       </c>
     </row>
@@ -3428,10 +3434,10 @@
       <c r="A168" t="s">
         <v>136</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="3">
         <v>10</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="3">
         <v>20.7</v>
       </c>
     </row>
@@ -3439,10 +3445,10 @@
       <c r="A169" t="s">
         <v>137</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="3">
         <v>23</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="3">
         <v>20.7</v>
       </c>
     </row>
@@ -3450,10 +3456,10 @@
       <c r="A170" t="s">
         <v>137</v>
       </c>
-      <c r="B170">
-        <v>1</v>
-      </c>
-      <c r="C170">
+      <c r="B170" s="3">
+        <v>1</v>
+      </c>
+      <c r="C170" s="3">
         <v>23.19</v>
       </c>
     </row>
@@ -3461,10 +3467,10 @@
       <c r="A171" t="s">
         <v>138</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="3">
         <v>28</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -3472,10 +3478,10 @@
       <c r="A172" t="s">
         <v>139</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="3">
         <v>2</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="3">
         <v>2830.09</v>
       </c>
     </row>
@@ -3483,10 +3489,10 @@
       <c r="A173" t="s">
         <v>140</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="3">
         <v>12</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="3">
         <v>72.45</v>
       </c>
     </row>
@@ -3494,10 +3500,10 @@
       <c r="A174" t="s">
         <v>141</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="3">
         <v>19</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="3">
         <v>72.45</v>
       </c>
     </row>
@@ -3505,10 +3511,10 @@
       <c r="A175" t="s">
         <v>142</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="3">
         <v>3</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="3">
         <v>53.83</v>
       </c>
     </row>
@@ -3516,10 +3522,10 @@
       <c r="A176" t="s">
         <v>142</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="3">
         <v>40</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="3">
         <v>60.29</v>
       </c>
     </row>
@@ -3527,10 +3533,10 @@
       <c r="A177" t="s">
         <v>143</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="3">
         <v>8</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="3">
         <v>82.65</v>
       </c>
     </row>
@@ -3538,10 +3544,10 @@
       <c r="A178" t="s">
         <v>143</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="3">
         <v>24</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="3">
         <v>93.35</v>
       </c>
     </row>
@@ -3549,10 +3555,10 @@
       <c r="A179" t="s">
         <v>144</v>
       </c>
-      <c r="B179">
-        <v>1</v>
-      </c>
-      <c r="C179">
+      <c r="B179" s="3">
+        <v>1</v>
+      </c>
+      <c r="C179" s="3">
         <v>1217.1600000000001</v>
       </c>
     </row>
@@ -3560,10 +3566,10 @@
       <c r="A180" t="s">
         <v>145</v>
       </c>
-      <c r="B180">
-        <v>1</v>
-      </c>
-      <c r="C180">
+      <c r="B180" s="3">
+        <v>1</v>
+      </c>
+      <c r="C180" s="3">
         <v>2749.17</v>
       </c>
     </row>
@@ -3571,10 +3577,10 @@
       <c r="A181" t="s">
         <v>146</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="3">
         <v>9</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="3">
         <v>43.7</v>
       </c>
     </row>
@@ -3582,10 +3588,10 @@
       <c r="A182" t="s">
         <v>146</v>
       </c>
-      <c r="B182">
-        <v>1</v>
-      </c>
-      <c r="C182">
+      <c r="B182" s="3">
+        <v>1</v>
+      </c>
+      <c r="C182" s="3">
         <v>48.95</v>
       </c>
     </row>
@@ -3593,10 +3599,10 @@
       <c r="A183" t="s">
         <v>147</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="3">
         <v>8</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="3">
         <v>64.59</v>
       </c>
     </row>
@@ -3604,10 +3610,10 @@
       <c r="A184" t="s">
         <v>147</v>
       </c>
-      <c r="B184">
-        <v>1</v>
-      </c>
-      <c r="C184">
+      <c r="B184" s="3">
+        <v>1</v>
+      </c>
+      <c r="C184" s="3">
         <v>72.33</v>
       </c>
     </row>
@@ -3615,10 +3621,10 @@
       <c r="A185" t="s">
         <v>148</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="3">
         <v>7</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="3">
         <v>219.65</v>
       </c>
     </row>
@@ -3626,10 +3632,10 @@
       <c r="A186" t="s">
         <v>149</v>
       </c>
-      <c r="B186">
-        <v>15</v>
-      </c>
-      <c r="C186">
+      <c r="B186" s="3">
+        <v>12</v>
+      </c>
+      <c r="C186" s="3">
         <v>64.92</v>
       </c>
     </row>
@@ -3637,10 +3643,10 @@
       <c r="A187" t="s">
         <v>150</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="3">
         <v>62</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -3648,10 +3654,10 @@
       <c r="A188" t="s">
         <v>151</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="3">
         <v>9</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -3659,10 +3665,10 @@
       <c r="A189" t="s">
         <v>152</v>
       </c>
-      <c r="B189">
-        <v>1</v>
-      </c>
-      <c r="C189">
+      <c r="B189" s="3">
+        <v>1</v>
+      </c>
+      <c r="C189" s="3">
         <v>37.43</v>
       </c>
     </row>
@@ -3670,10 +3676,10 @@
       <c r="A190" t="s">
         <v>153</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="3">
         <v>47</v>
       </c>
-      <c r="C190">
+      <c r="C190" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -3681,10 +3687,10 @@
       <c r="A191" t="s">
         <v>154</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="3">
         <v>9</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="3">
         <v>115.01</v>
       </c>
     </row>
@@ -3692,10 +3698,10 @@
       <c r="A192" t="s">
         <v>155</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="3">
         <v>16</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="3">
         <v>26.75</v>
       </c>
     </row>
@@ -3703,10 +3709,10 @@
       <c r="A193" t="s">
         <v>155</v>
       </c>
-      <c r="B193">
-        <v>1</v>
-      </c>
-      <c r="C193">
+      <c r="B193" s="3">
+        <v>1</v>
+      </c>
+      <c r="C193" s="3">
         <v>38.39</v>
       </c>
     </row>
@@ -3714,10 +3720,10 @@
       <c r="A194" t="s">
         <v>156</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="3">
         <v>3</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="3">
         <v>103.02</v>
       </c>
     </row>
@@ -3725,10 +3731,10 @@
       <c r="A195" t="s">
         <v>157</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="3">
         <v>12</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="3">
         <v>121.41</v>
       </c>
     </row>
@@ -3736,10 +3742,10 @@
       <c r="A196" t="s">
         <v>158</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="3">
         <v>12</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="3">
         <v>17.920000000000002</v>
       </c>
     </row>
@@ -3747,10 +3753,10 @@
       <c r="A197" t="s">
         <v>159</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="3">
         <v>9</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="3">
         <v>12.08</v>
       </c>
     </row>
@@ -3758,10 +3764,10 @@
       <c r="A198" t="s">
         <v>160</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="3">
         <v>15</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="3">
         <v>23.01</v>
       </c>
     </row>
@@ -3769,10 +3775,10 @@
       <c r="A199" t="s">
         <v>161</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="3">
         <v>12</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="3">
         <v>26.74</v>
       </c>
     </row>
@@ -3780,10 +3786,10 @@
       <c r="A200" t="s">
         <v>162</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="3">
         <v>10</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="3">
         <v>52.4</v>
       </c>
     </row>
@@ -3791,10 +3797,10 @@
       <c r="A201" t="s">
         <v>162</v>
       </c>
-      <c r="B201">
-        <v>1</v>
-      </c>
-      <c r="C201">
+      <c r="B201" s="3">
+        <v>1</v>
+      </c>
+      <c r="C201" s="3">
         <v>58.67</v>
       </c>
     </row>
@@ -3802,10 +3808,10 @@
       <c r="A202" t="s">
         <v>163</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="3">
         <v>3</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="3">
         <v>61.64</v>
       </c>
     </row>
@@ -3813,10 +3819,10 @@
       <c r="A203" t="s">
         <v>164</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="3">
         <v>31</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="3">
         <v>34.619999999999997</v>
       </c>
     </row>
@@ -3824,10 +3830,10 @@
       <c r="A204" t="s">
         <v>165</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="3">
         <v>13</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="3">
         <v>95.85</v>
       </c>
     </row>
@@ -3835,10 +3841,10 @@
       <c r="A205" t="s">
         <v>166</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="3">
         <v>19</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="3">
         <v>55.2</v>
       </c>
     </row>
@@ -3846,10 +3852,10 @@
       <c r="A206" t="s">
         <v>166</v>
       </c>
-      <c r="B206">
-        <v>1</v>
-      </c>
-      <c r="C206">
+      <c r="B206" s="3">
+        <v>1</v>
+      </c>
+      <c r="C206" s="3">
         <v>61.83</v>
       </c>
     </row>
@@ -3857,10 +3863,10 @@
       <c r="A207" t="s">
         <v>167</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="3">
         <v>22</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="3">
         <v>143.52000000000001</v>
       </c>
     </row>
@@ -3868,10 +3874,10 @@
       <c r="A208" t="s">
         <v>168</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="3">
         <v>35</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="3">
         <v>56.94</v>
       </c>
     </row>
@@ -3879,10 +3885,10 @@
       <c r="A209" t="s">
         <v>169</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="3">
         <v>16</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="3">
         <v>67.849999999999994</v>
       </c>
     </row>
@@ -3890,10 +3896,10 @@
       <c r="A210" t="s">
         <v>169</v>
       </c>
-      <c r="B210">
-        <v>1</v>
-      </c>
-      <c r="C210">
+      <c r="B210" s="3">
+        <v>1</v>
+      </c>
+      <c r="C210" s="3">
         <v>75.989999999999995</v>
       </c>
     </row>
@@ -3901,10 +3907,10 @@
       <c r="A211" t="s">
         <v>170</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="3">
         <v>3</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="3">
         <v>270.07</v>
       </c>
     </row>
@@ -3912,10 +3918,10 @@
       <c r="A212" t="s">
         <v>171</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="3">
         <v>14</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="3">
         <v>69.010000000000005</v>
       </c>
     </row>
@@ -3923,10 +3929,10 @@
       <c r="A213" t="s">
         <v>172</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="3">
         <v>15</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="3">
         <v>67.849999999999994</v>
       </c>
     </row>
@@ -3934,10 +3940,10 @@
       <c r="A214" t="s">
         <v>173</v>
       </c>
-      <c r="B214">
-        <v>8</v>
-      </c>
-      <c r="C214">
+      <c r="B214" s="3">
+        <v>7</v>
+      </c>
+      <c r="C214" s="3">
         <v>342.24</v>
       </c>
     </row>
@@ -3945,10 +3951,10 @@
       <c r="A215" t="s">
         <v>174</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="3">
         <v>2</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="3">
         <v>443.88</v>
       </c>
     </row>
@@ -3956,10 +3962,10 @@
       <c r="A216" t="s">
         <v>175</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="3">
         <v>55</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="3">
         <v>36.799999999999997</v>
       </c>
     </row>
@@ -3967,10 +3973,10 @@
       <c r="A217" t="s">
         <v>175</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="3">
         <v>23</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="3">
         <v>50.51</v>
       </c>
     </row>
@@ -3978,10 +3984,10 @@
       <c r="A218" t="s">
         <v>176</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="3">
         <v>2</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="3">
         <v>581.9</v>
       </c>
     </row>
@@ -3989,10 +3995,10 @@
       <c r="A219" t="s">
         <v>177</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="3">
         <v>2</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="3">
         <v>579.12</v>
       </c>
     </row>
@@ -4000,10 +4006,10 @@
       <c r="A220" t="s">
         <v>178</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="3">
         <v>11</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="3">
         <v>109.26</v>
       </c>
     </row>
@@ -4011,10 +4017,10 @@
       <c r="A221" t="s">
         <v>178</v>
       </c>
-      <c r="B221">
-        <v>1</v>
-      </c>
-      <c r="C221">
+      <c r="B221" s="3">
+        <v>1</v>
+      </c>
+      <c r="C221" s="3">
         <v>122.36</v>
       </c>
     </row>
@@ -4022,10 +4028,10 @@
       <c r="A222" t="s">
         <v>179</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="3">
         <v>15</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="3">
         <v>31.98</v>
       </c>
     </row>
@@ -4033,10 +4039,10 @@
       <c r="A223" t="s">
         <v>179</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="3">
         <v>25</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="3">
         <v>35.81</v>
       </c>
     </row>
@@ -4044,10 +4050,10 @@
       <c r="A224" t="s">
         <v>180</v>
       </c>
-      <c r="B224">
-        <v>37</v>
-      </c>
-      <c r="C224">
+      <c r="B224" s="3">
+        <v>35</v>
+      </c>
+      <c r="C224" s="3">
         <v>49.09</v>
       </c>
     </row>
@@ -4055,10 +4061,10 @@
       <c r="A225" t="s">
         <v>181</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="3">
         <v>12</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="3">
         <v>201.06</v>
       </c>
     </row>
@@ -4066,10 +4072,10 @@
       <c r="A226" t="s">
         <v>182</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="3">
         <v>8</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="3">
         <v>43.07</v>
       </c>
     </row>
@@ -4077,10 +4083,10 @@
       <c r="A227" t="s">
         <v>183</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="3">
         <v>12</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="3">
         <v>43.07</v>
       </c>
     </row>
@@ -4088,10 +4094,10 @@
       <c r="A228" t="s">
         <v>184</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="3">
         <v>6</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="3">
         <v>198.08</v>
       </c>
     </row>
@@ -4099,10 +4105,10 @@
       <c r="A229" t="s">
         <v>185</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="3">
         <v>4</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="3">
         <v>58.34</v>
       </c>
     </row>
@@ -4110,10 +4116,10 @@
       <c r="A230" t="s">
         <v>186</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="3">
         <v>20</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="3">
         <v>265.5</v>
       </c>
     </row>
@@ -4121,10 +4127,10 @@
       <c r="A231" t="s">
         <v>187</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="3">
         <v>15</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="3">
         <v>123.94</v>
       </c>
     </row>
@@ -4132,10 +4138,10 @@
       <c r="A232" t="s">
         <v>188</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="3">
         <v>25</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="3">
         <v>31.02</v>
       </c>
     </row>
@@ -4143,10 +4149,10 @@
       <c r="A233" t="s">
         <v>189</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="3">
         <v>2</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="3">
         <v>123.94</v>
       </c>
     </row>
@@ -4154,10 +4160,10 @@
       <c r="A234" t="s">
         <v>190</v>
       </c>
-      <c r="B234">
-        <v>17</v>
-      </c>
-      <c r="C234">
+      <c r="B234" s="3">
+        <v>16</v>
+      </c>
+      <c r="C234" s="3">
         <v>154.71</v>
       </c>
     </row>
@@ -4165,10 +4171,10 @@
       <c r="A235" t="s">
         <v>191</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="3">
         <v>2</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="3">
         <v>453.22</v>
       </c>
     </row>
@@ -4176,10 +4182,10 @@
       <c r="A236" t="s">
         <v>192</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="3">
         <v>13</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="3">
         <v>27.95</v>
       </c>
     </row>
@@ -4187,10 +4193,10 @@
       <c r="A237" t="s">
         <v>193</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="3">
         <v>9</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="3">
         <v>113.06</v>
       </c>
     </row>
@@ -4198,10 +4204,10 @@
       <c r="A238" t="s">
         <v>194</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="3">
         <v>5</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="3">
         <v>55.72</v>
       </c>
     </row>
@@ -4209,10 +4215,10 @@
       <c r="A239" t="s">
         <v>195</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="3">
         <v>15</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="3">
         <v>42.44</v>
       </c>
     </row>
@@ -4220,10 +4226,10 @@
       <c r="A240" t="s">
         <v>196</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="3">
         <v>13</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="3">
         <v>32.36</v>
       </c>
     </row>
@@ -4231,10 +4237,10 @@
       <c r="A241" t="s">
         <v>197</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="3">
         <v>9</v>
       </c>
-      <c r="C241">
+      <c r="C241" s="3">
         <v>122.55</v>
       </c>
     </row>
@@ -4242,10 +4248,10 @@
       <c r="A242" t="s">
         <v>198</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="3">
         <v>36</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="3">
         <v>179</v>
       </c>
     </row>
@@ -4253,10 +4259,10 @@
       <c r="A243" t="s">
         <v>199</v>
       </c>
-      <c r="B243">
-        <v>1</v>
-      </c>
-      <c r="C243">
+      <c r="B243" s="3">
+        <v>1</v>
+      </c>
+      <c r="C243" s="3">
         <v>2060.8000000000002</v>
       </c>
     </row>
@@ -4264,10 +4270,10 @@
       <c r="A244" t="s">
         <v>200</v>
       </c>
-      <c r="B244">
-        <v>11</v>
-      </c>
-      <c r="C244">
+      <c r="B244" s="3">
+        <v>8</v>
+      </c>
+      <c r="C244" s="3">
         <v>45.54</v>
       </c>
     </row>
@@ -4275,10 +4281,10 @@
       <c r="A245" t="s">
         <v>200</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="3">
         <v>11</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="3">
         <v>45.54</v>
       </c>
     </row>
@@ -4286,10 +4292,10 @@
       <c r="A246" t="s">
         <v>201</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="3">
         <v>11</v>
       </c>
-      <c r="C246">
+      <c r="C246" s="3">
         <v>163.76</v>
       </c>
     </row>
@@ -4297,10 +4303,10 @@
       <c r="A247" t="s">
         <v>202</v>
       </c>
-      <c r="B247">
-        <v>11</v>
-      </c>
-      <c r="C247">
+      <c r="B247" s="3">
+        <v>10</v>
+      </c>
+      <c r="C247" s="3">
         <v>184.22</v>
       </c>
     </row>
@@ -4308,10 +4314,10 @@
       <c r="A248" t="s">
         <v>203</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="3">
         <v>15</v>
       </c>
-      <c r="C248">
+      <c r="C248" s="3">
         <v>29.89</v>
       </c>
     </row>
@@ -4319,10 +4325,10 @@
       <c r="A249" t="s">
         <v>203</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="3">
         <v>25</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="3">
         <v>33.479999999999997</v>
       </c>
     </row>
@@ -4330,10 +4336,10 @@
       <c r="A250" t="s">
         <v>204</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="3">
         <v>36</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="3">
         <v>46.06</v>
       </c>
     </row>
@@ -4341,10 +4347,10 @@
       <c r="A251" t="s">
         <v>205</v>
       </c>
-      <c r="B251">
-        <v>1</v>
-      </c>
-      <c r="C251">
+      <c r="B251" s="3">
+        <v>1</v>
+      </c>
+      <c r="C251" s="3">
         <v>4667</v>
       </c>
     </row>
@@ -4352,10 +4358,10 @@
       <c r="A252" t="s">
         <v>205</v>
       </c>
-      <c r="B252">
-        <v>1</v>
-      </c>
-      <c r="C252">
+      <c r="B252" s="3">
+        <v>1</v>
+      </c>
+      <c r="C252" s="3">
         <v>5345.33</v>
       </c>
     </row>
@@ -4363,10 +4369,10 @@
       <c r="A253" t="s">
         <v>206</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="3">
         <v>17</v>
       </c>
-      <c r="C253">
+      <c r="C253" s="3">
         <v>140.56</v>
       </c>
     </row>
@@ -4374,10 +4380,10 @@
       <c r="A254" t="s">
         <v>207</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="3">
         <v>2</v>
       </c>
-      <c r="C254">
+      <c r="C254" s="3">
         <v>162.13</v>
       </c>
     </row>
@@ -4385,10 +4391,10 @@
       <c r="A255" t="s">
         <v>207</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="3">
         <v>11</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="3">
         <v>192.51</v>
       </c>
     </row>
@@ -4396,10 +4402,10 @@
       <c r="A256" t="s">
         <v>208</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="3">
         <v>25</v>
       </c>
-      <c r="C256">
+      <c r="C256" s="3">
         <v>53.31</v>
       </c>
     </row>
@@ -4407,10 +4413,10 @@
       <c r="A257" t="s">
         <v>209</v>
       </c>
-      <c r="B257">
-        <v>1</v>
-      </c>
-      <c r="C257">
+      <c r="B257" s="3">
+        <v>1</v>
+      </c>
+      <c r="C257" s="3">
         <v>236.66</v>
       </c>
     </row>
@@ -4418,10 +4424,10 @@
       <c r="A258" t="s">
         <v>210</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="3">
         <v>35</v>
       </c>
-      <c r="C258">
+      <c r="C258" s="3">
         <v>29.89</v>
       </c>
     </row>
@@ -4429,10 +4435,10 @@
       <c r="A259" t="s">
         <v>211</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="3">
         <v>18</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="3">
         <v>92.01</v>
       </c>
     </row>
@@ -4440,10 +4446,10 @@
       <c r="A260" t="s">
         <v>212</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="3">
         <v>54</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="3">
         <v>34.26</v>
       </c>
     </row>
@@ -4451,10 +4457,10 @@
       <c r="A261" t="s">
         <v>213</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="3">
         <v>11</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="3">
         <v>47.16</v>
       </c>
     </row>
@@ -4462,10 +4468,10 @@
       <c r="A262" t="s">
         <v>214</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="3">
         <v>27</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="3">
         <v>16.809999999999999</v>
       </c>
     </row>
@@ -4473,10 +4479,10 @@
       <c r="A263" t="s">
         <v>215</v>
       </c>
-      <c r="B263">
-        <v>11</v>
-      </c>
-      <c r="C263">
+      <c r="B263" s="3">
+        <v>10</v>
+      </c>
+      <c r="C263" s="3">
         <v>28.69</v>
       </c>
     </row>
@@ -4484,10 +4490,10 @@
       <c r="A264" t="s">
         <v>215</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="3">
         <v>40</v>
       </c>
-      <c r="C264">
+      <c r="C264" s="3">
         <v>37.31</v>
       </c>
     </row>
@@ -4495,10 +4501,10 @@
       <c r="A265" t="s">
         <v>216</v>
       </c>
-      <c r="B265">
-        <v>6</v>
-      </c>
-      <c r="C265">
+      <c r="B265" s="3">
+        <v>5</v>
+      </c>
+      <c r="C265" s="3">
         <v>103.46</v>
       </c>
     </row>
@@ -4506,10 +4512,10 @@
       <c r="A266" t="s">
         <v>216</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="3">
         <v>20</v>
       </c>
-      <c r="C266">
+      <c r="C266" s="3">
         <v>126.24</v>
       </c>
     </row>
@@ -4517,10 +4523,10 @@
       <c r="A267" t="s">
         <v>217</v>
       </c>
-      <c r="B267">
-        <v>10</v>
-      </c>
-      <c r="C267">
+      <c r="B267" s="3">
+        <v>9</v>
+      </c>
+      <c r="C267" s="3">
         <v>144.27000000000001</v>
       </c>
     </row>
@@ -4528,10 +4534,10 @@
       <c r="A268" t="s">
         <v>218</v>
       </c>
-      <c r="B268">
+      <c r="B268" s="3">
         <v>2</v>
       </c>
-      <c r="C268">
+      <c r="C268" s="3">
         <v>412.98</v>
       </c>
     </row>
@@ -4539,10 +4545,10 @@
       <c r="A269" t="s">
         <v>219</v>
       </c>
-      <c r="B269">
-        <v>1</v>
-      </c>
-      <c r="C269">
+      <c r="B269" s="3">
+        <v>1</v>
+      </c>
+      <c r="C269" s="3">
         <v>6302</v>
       </c>
     </row>
@@ -4550,10 +4556,10 @@
       <c r="A270" t="s">
         <v>220</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="3">
         <v>3</v>
       </c>
-      <c r="C270">
+      <c r="C270" s="3">
         <v>413.57</v>
       </c>
     </row>
@@ -4561,10 +4567,10 @@
       <c r="A271" t="s">
         <v>220</v>
       </c>
-      <c r="B271">
-        <v>1</v>
-      </c>
-      <c r="C271">
+      <c r="B271" s="3">
+        <v>1</v>
+      </c>
+      <c r="C271" s="3">
         <v>570.28</v>
       </c>
     </row>
@@ -4572,10 +4578,10 @@
       <c r="A272" t="s">
         <v>221</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="3">
         <v>15</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="3">
         <v>51.75</v>
       </c>
     </row>
@@ -4583,10 +4589,10 @@
       <c r="A273" t="s">
         <v>222</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="3">
         <v>8</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="3">
         <v>53.82</v>
       </c>
     </row>
@@ -4594,10 +4600,10 @@
       <c r="A274" t="s">
         <v>223</v>
       </c>
-      <c r="B274">
-        <v>1</v>
-      </c>
-      <c r="C274">
+      <c r="B274" s="3">
+        <v>1</v>
+      </c>
+      <c r="C274" s="3">
         <v>20789.41</v>
       </c>
     </row>
@@ -4605,10 +4611,10 @@
       <c r="A275" t="s">
         <v>223</v>
       </c>
-      <c r="B275">
-        <v>1</v>
-      </c>
-      <c r="C275">
+      <c r="B275" s="3">
+        <v>1</v>
+      </c>
+      <c r="C275" s="3">
         <v>33057.85</v>
       </c>
     </row>
@@ -4616,10 +4622,10 @@
       <c r="A276" t="s">
         <v>224</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="3">
         <v>7</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="3">
         <v>71.08</v>
       </c>
     </row>
@@ -4627,10 +4633,10 @@
       <c r="A277" t="s">
         <v>225</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="3">
         <v>14</v>
       </c>
-      <c r="C277">
+      <c r="C277" s="3">
         <v>45.71</v>
       </c>
     </row>
@@ -4638,10 +4644,10 @@
       <c r="A278" t="s">
         <v>226</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="3">
         <v>16</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="3">
         <v>50.52</v>
       </c>
     </row>
@@ -4649,10 +4655,10 @@
       <c r="A279" t="s">
         <v>226</v>
       </c>
-      <c r="B279">
-        <v>1</v>
-      </c>
-      <c r="C279">
+      <c r="B279" s="3">
+        <v>1</v>
+      </c>
+      <c r="C279" s="3">
         <v>50.71</v>
       </c>
     </row>
@@ -4660,10 +4666,10 @@
       <c r="A280" t="s">
         <v>227</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="3">
         <v>10</v>
       </c>
-      <c r="C280">
+      <c r="C280" s="3">
         <v>51.75</v>
       </c>
     </row>
@@ -4671,10 +4677,10 @@
       <c r="A281" t="s">
         <v>228</v>
       </c>
-      <c r="B281">
+      <c r="B281" s="3">
         <v>13</v>
       </c>
-      <c r="C281">
+      <c r="C281" s="3">
         <v>36.799999999999997</v>
       </c>
     </row>
@@ -4682,10 +4688,10 @@
       <c r="A282" t="s">
         <v>229</v>
       </c>
-      <c r="B282">
+      <c r="B282" s="3">
         <v>24</v>
       </c>
-      <c r="C282">
+      <c r="C282" s="3">
         <v>36.799999999999997</v>
       </c>
     </row>
@@ -4693,10 +4699,10 @@
       <c r="A283" t="s">
         <v>230</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="3">
         <v>45</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="3">
         <v>58.69</v>
       </c>
     </row>
@@ -4704,10 +4710,10 @@
       <c r="A284" t="s">
         <v>231</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="3">
         <v>35</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="3">
         <v>58.12</v>
       </c>
     </row>
@@ -4715,10 +4721,10 @@
       <c r="A285" t="s">
         <v>232</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="3">
         <v>5</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="3">
         <v>58.51</v>
       </c>
     </row>
@@ -4726,10 +4732,10 @@
       <c r="A286" t="s">
         <v>232</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="3">
         <v>42</v>
       </c>
-      <c r="C286">
+      <c r="C286" s="3">
         <v>65.53</v>
       </c>
     </row>
@@ -4737,10 +4743,10 @@
       <c r="A287" t="s">
         <v>233</v>
       </c>
-      <c r="B287">
-        <v>34</v>
-      </c>
-      <c r="C287">
+      <c r="B287" s="3">
+        <v>32</v>
+      </c>
+      <c r="C287" s="3">
         <v>72.45</v>
       </c>
     </row>
@@ -4748,10 +4754,10 @@
       <c r="A288" t="s">
         <v>234</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="3">
         <v>26</v>
       </c>
-      <c r="C288">
+      <c r="C288" s="3">
         <v>29.89</v>
       </c>
     </row>
@@ -4759,10 +4765,10 @@
       <c r="A289" t="s">
         <v>235</v>
       </c>
-      <c r="B289">
-        <v>1</v>
-      </c>
-      <c r="C289">
+      <c r="B289" s="3">
+        <v>0</v>
+      </c>
+      <c r="C289" s="3">
         <v>3806.5</v>
       </c>
     </row>
@@ -4770,10 +4776,10 @@
       <c r="A290" t="s">
         <v>236</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="3">
         <v>6</v>
       </c>
-      <c r="C290">
+      <c r="C290" s="3">
         <v>335.8</v>
       </c>
     </row>
@@ -4781,10 +4787,10 @@
       <c r="A291" t="s">
         <v>237</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="3">
         <v>2</v>
       </c>
-      <c r="C291">
+      <c r="C291" s="3">
         <v>1007.4</v>
       </c>
     </row>
@@ -4792,10 +4798,10 @@
       <c r="A292" t="s">
         <v>238</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="3">
         <v>20</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="3">
         <v>5.76</v>
       </c>
     </row>
@@ -4803,10 +4809,10 @@
       <c r="A293" t="s">
         <v>239</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="3">
         <v>9</v>
       </c>
-      <c r="C293">
+      <c r="C293" s="3">
         <v>96.6</v>
       </c>
     </row>
@@ -4814,10 +4820,10 @@
       <c r="A294" t="s">
         <v>240</v>
       </c>
-      <c r="B294">
-        <v>1</v>
-      </c>
-      <c r="C294">
+      <c r="B294" s="3">
+        <v>1</v>
+      </c>
+      <c r="C294" s="3">
         <v>4456.4799999999996</v>
       </c>
     </row>
@@ -4825,10 +4831,10 @@
       <c r="A295" t="s">
         <v>240</v>
       </c>
-      <c r="B295">
-        <v>1</v>
-      </c>
-      <c r="C295">
+      <c r="B295" s="3">
+        <v>1</v>
+      </c>
+      <c r="C295" s="3">
         <v>7429</v>
       </c>
     </row>
@@ -4836,10 +4842,10 @@
       <c r="A296" t="s">
         <v>241</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="3">
         <v>2</v>
       </c>
-      <c r="C296">
+      <c r="C296" s="3">
         <v>558.89</v>
       </c>
     </row>
@@ -4847,10 +4853,10 @@
       <c r="A297" t="s">
         <v>242</v>
       </c>
-      <c r="B297">
-        <v>24</v>
-      </c>
-      <c r="C297">
+      <c r="B297" s="3">
+        <v>23</v>
+      </c>
+      <c r="C297" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -4858,10 +4864,10 @@
       <c r="A298" t="s">
         <v>243</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="3">
         <v>13</v>
       </c>
-      <c r="C298">
+      <c r="C298" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -4869,10 +4875,10 @@
       <c r="A299" t="s">
         <v>244</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="3">
         <v>42</v>
       </c>
-      <c r="C299">
+      <c r="C299" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -4880,10 +4886,10 @@
       <c r="A300" t="s">
         <v>245</v>
       </c>
-      <c r="B300">
-        <v>14</v>
-      </c>
-      <c r="C300">
+      <c r="B300" s="3">
+        <v>9</v>
+      </c>
+      <c r="C300" s="3">
         <v>28.75</v>
       </c>
     </row>
@@ -4891,10 +4897,10 @@
       <c r="A301" t="s">
         <v>246</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="3">
         <v>7</v>
       </c>
-      <c r="C301">
+      <c r="C301" s="3">
         <v>40.25</v>
       </c>
     </row>
@@ -4902,10 +4908,10 @@
       <c r="A302" t="s">
         <v>247</v>
       </c>
-      <c r="B302">
-        <v>81</v>
-      </c>
-      <c r="C302">
+      <c r="B302" s="3">
+        <v>80</v>
+      </c>
+      <c r="C302" s="3">
         <v>32.21</v>
       </c>
     </row>
@@ -4913,10 +4919,10 @@
       <c r="A303" t="s">
         <v>248</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="3">
         <v>18</v>
       </c>
-      <c r="C303">
+      <c r="C303" s="3">
         <v>44.5</v>
       </c>
     </row>
@@ -4924,10 +4930,10 @@
       <c r="A304" t="s">
         <v>248</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="3">
         <v>24</v>
       </c>
-      <c r="C304">
+      <c r="C304" s="3">
         <v>56.01</v>
       </c>
     </row>
@@ -4935,10 +4941,10 @@
       <c r="A305" t="s">
         <v>249</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="3">
         <v>17</v>
       </c>
-      <c r="C305">
+      <c r="C305" s="3">
         <v>51.45</v>
       </c>
     </row>
@@ -4946,10 +4952,10 @@
       <c r="A306" t="s">
         <v>250</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="3">
         <v>4</v>
       </c>
-      <c r="C306">
+      <c r="C306" s="3">
         <v>58.07</v>
       </c>
     </row>
@@ -4957,10 +4963,10 @@
       <c r="A307" t="s">
         <v>251</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="3">
         <v>9</v>
       </c>
-      <c r="C307">
+      <c r="C307" s="3">
         <v>42.33</v>
       </c>
     </row>
@@ -4968,10 +4974,10 @@
       <c r="A308" t="s">
         <v>252</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="3">
         <v>2</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="3">
         <v>46.28</v>
       </c>
     </row>
@@ -4979,10 +4985,10 @@
       <c r="A309" t="s">
         <v>253</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="3">
         <v>17</v>
       </c>
-      <c r="C309">
+      <c r="C309" s="3">
         <v>59.21</v>
       </c>
     </row>
@@ -4990,10 +4996,10 @@
       <c r="A310" t="s">
         <v>253</v>
       </c>
-      <c r="B310">
-        <v>1</v>
-      </c>
-      <c r="C310">
+      <c r="B310" s="3">
+        <v>1</v>
+      </c>
+      <c r="C310" s="3">
         <v>66.3</v>
       </c>
     </row>
@@ -5001,10 +5007,10 @@
       <c r="A311" t="s">
         <v>254</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="3">
         <v>6</v>
       </c>
-      <c r="C311">
+      <c r="C311" s="3">
         <v>233.7</v>
       </c>
     </row>
@@ -5012,10 +5018,10 @@
       <c r="A312" t="s">
         <v>255</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="3">
         <v>14</v>
       </c>
-      <c r="C312">
+      <c r="C312" s="3">
         <v>57.18</v>
       </c>
     </row>
@@ -5023,10 +5029,10 @@
       <c r="A313" t="s">
         <v>256</v>
       </c>
-      <c r="B313">
-        <v>1</v>
-      </c>
-      <c r="C313">
+      <c r="B313" s="3">
+        <v>1</v>
+      </c>
+      <c r="C313" s="3">
         <v>77.760000000000005</v>
       </c>
     </row>
@@ -5034,10 +5040,10 @@
       <c r="A314" t="s">
         <v>257</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="3">
         <v>17</v>
       </c>
-      <c r="C314">
+      <c r="C314" s="3">
         <v>48.86</v>
       </c>
     </row>
@@ -5045,10 +5051,10 @@
       <c r="A315" t="s">
         <v>258</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="3">
         <v>13</v>
       </c>
-      <c r="C315">
+      <c r="C315" s="3">
         <v>46.53</v>
       </c>
     </row>
@@ -5056,10 +5062,10 @@
       <c r="A316" t="s">
         <v>259</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="3">
         <v>6</v>
       </c>
-      <c r="C316">
+      <c r="C316" s="3">
         <v>224.6</v>
       </c>
     </row>
@@ -5067,10 +5073,10 @@
       <c r="A317" t="s">
         <v>260</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="3">
         <v>12</v>
       </c>
-      <c r="C317">
+      <c r="C317" s="3">
         <v>70.430000000000007</v>
       </c>
     </row>
@@ -5078,10 +5084,10 @@
       <c r="A318" t="s">
         <v>261</v>
       </c>
-      <c r="B318">
-        <v>1</v>
-      </c>
-      <c r="C318">
+      <c r="B318" s="3">
+        <v>1</v>
+      </c>
+      <c r="C318" s="3">
         <v>61.47</v>
       </c>
     </row>
@@ -5089,10 +5095,10 @@
       <c r="A319" t="s">
         <v>261</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="3">
         <v>12</v>
       </c>
-      <c r="C319">
+      <c r="C319" s="3">
         <v>83.84</v>
       </c>
     </row>
@@ -5100,10 +5106,10 @@
       <c r="A320" t="s">
         <v>262</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="3">
         <v>3</v>
       </c>
-      <c r="C320">
+      <c r="C320" s="3">
         <v>243.35</v>
       </c>
     </row>
@@ -5111,10 +5117,10 @@
       <c r="A321" t="s">
         <v>263</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="3">
         <v>19</v>
       </c>
-      <c r="C321">
+      <c r="C321" s="3">
         <v>71.209999999999994</v>
       </c>
     </row>
@@ -5122,10 +5128,10 @@
       <c r="A322" t="s">
         <v>264</v>
       </c>
-      <c r="B322">
-        <v>16</v>
-      </c>
-      <c r="C322">
+      <c r="B322" s="3">
+        <v>15</v>
+      </c>
+      <c r="C322" s="3">
         <v>65.209999999999994</v>
       </c>
     </row>
@@ -5133,10 +5139,10 @@
       <c r="A323" t="s">
         <v>264</v>
       </c>
-      <c r="B323">
+      <c r="B323" s="3">
         <v>12</v>
       </c>
-      <c r="C323">
+      <c r="C323" s="3">
         <v>83.84</v>
       </c>
     </row>
@@ -5144,10 +5150,10 @@
       <c r="A324" t="s">
         <v>265</v>
       </c>
-      <c r="B324">
-        <v>8</v>
-      </c>
-      <c r="C324">
+      <c r="B324" s="3">
+        <v>7</v>
+      </c>
+      <c r="C324" s="3">
         <v>253.63</v>
       </c>
     </row>
@@ -5155,10 +5161,10 @@
       <c r="A325" t="s">
         <v>266</v>
       </c>
-      <c r="B325">
+      <c r="B325" s="3">
         <v>12</v>
       </c>
-      <c r="C325">
+      <c r="C325" s="3">
         <v>22.2</v>
       </c>
     </row>
@@ -5166,10 +5172,10 @@
       <c r="A326" t="s">
         <v>267</v>
       </c>
-      <c r="B326">
+      <c r="B326" s="3">
         <v>2</v>
       </c>
-      <c r="C326">
+      <c r="C326" s="3">
         <v>43.07</v>
       </c>
     </row>
@@ -5177,10 +5183,10 @@
       <c r="A327" t="s">
         <v>268</v>
       </c>
-      <c r="B327">
+      <c r="B327" s="3">
         <v>9</v>
       </c>
-      <c r="C327">
+      <c r="C327" s="3">
         <v>46.01</v>
       </c>
     </row>
@@ -5188,10 +5194,10 @@
       <c r="A328" t="s">
         <v>269</v>
       </c>
-      <c r="B328">
+      <c r="B328" s="3">
         <v>5</v>
       </c>
-      <c r="C328">
+      <c r="C328" s="3">
         <v>36.22</v>
       </c>
     </row>
@@ -5199,10 +5205,10 @@
       <c r="A329" t="s">
         <v>270</v>
       </c>
-      <c r="B329">
+      <c r="B329" s="3">
         <v>39</v>
       </c>
-      <c r="C329">
+      <c r="C329" s="3">
         <v>36.229999999999997</v>
       </c>
     </row>
@@ -5210,10 +5216,10 @@
       <c r="A330" t="s">
         <v>271</v>
       </c>
-      <c r="B330">
+      <c r="B330" s="3">
         <v>24</v>
       </c>
-      <c r="C330">
+      <c r="C330" s="3">
         <v>48.32</v>
       </c>
     </row>
@@ -5221,10 +5227,10 @@
       <c r="A331" t="s">
         <v>272</v>
       </c>
-      <c r="B331">
+      <c r="B331" s="3">
         <v>12</v>
       </c>
-      <c r="C331">
+      <c r="C331" s="3">
         <v>58.37</v>
       </c>
     </row>
@@ -5232,10 +5238,10 @@
       <c r="A332" t="s">
         <v>273</v>
       </c>
-      <c r="B332">
+      <c r="B332" s="3">
         <v>10</v>
       </c>
-      <c r="C332">
+      <c r="C332" s="3">
         <v>228.53</v>
       </c>
     </row>
@@ -5243,10 +5249,10 @@
       <c r="A333" t="s">
         <v>274</v>
       </c>
-      <c r="B333">
+      <c r="B333" s="3">
         <v>7</v>
       </c>
-      <c r="C333">
+      <c r="C333" s="3">
         <v>48.31</v>
       </c>
     </row>
@@ -5254,10 +5260,10 @@
       <c r="A334" t="s">
         <v>275</v>
       </c>
-      <c r="B334">
+      <c r="B334" s="3">
         <v>10</v>
       </c>
-      <c r="C334">
+      <c r="C334" s="3">
         <v>78.209999999999994</v>
       </c>
     </row>
@@ -5265,10 +5271,10 @@
       <c r="A335" t="s">
         <v>276</v>
       </c>
-      <c r="B335">
-        <v>200</v>
-      </c>
-      <c r="C335">
+      <c r="B335" s="3">
+        <v>198</v>
+      </c>
+      <c r="C335" s="3">
         <v>44.93</v>
       </c>
     </row>
@@ -5276,10 +5282,10 @@
       <c r="A336" t="s">
         <v>277</v>
       </c>
-      <c r="B336">
-        <v>1</v>
-      </c>
-      <c r="C336">
+      <c r="B336" s="3">
+        <v>1</v>
+      </c>
+      <c r="C336" s="3">
         <v>6578.46</v>
       </c>
     </row>
@@ -5287,10 +5293,10 @@
       <c r="A337" t="s">
         <v>278</v>
       </c>
-      <c r="B337">
-        <v>37</v>
-      </c>
-      <c r="C337">
+      <c r="B337" s="3">
+        <v>36</v>
+      </c>
+      <c r="C337" s="3">
         <v>173.09</v>
       </c>
     </row>
@@ -5298,10 +5304,10 @@
       <c r="A338" t="s">
         <v>279</v>
       </c>
-      <c r="B338">
-        <v>89</v>
-      </c>
-      <c r="C338">
+      <c r="B338" s="3">
+        <v>85</v>
+      </c>
+      <c r="C338" s="3">
         <v>211.23</v>
       </c>
     </row>
@@ -5309,10 +5315,10 @@
       <c r="A339" t="s">
         <v>280</v>
       </c>
-      <c r="B339">
-        <v>1</v>
-      </c>
-      <c r="C339">
+      <c r="B339" s="3">
+        <v>1</v>
+      </c>
+      <c r="C339" s="3">
         <v>2314.8000000000002</v>
       </c>
     </row>
@@ -5320,10 +5326,10 @@
       <c r="A340" t="s">
         <v>281</v>
       </c>
-      <c r="B340">
+      <c r="B340" s="3">
         <v>3</v>
       </c>
-      <c r="C340">
+      <c r="C340" s="3">
         <v>791.3</v>
       </c>
     </row>
@@ -5331,10 +5337,10 @@
       <c r="A341" t="s">
         <v>282</v>
       </c>
-      <c r="B341">
+      <c r="B341" s="3">
         <v>25</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="3">
         <v>28.22</v>
       </c>
     </row>
@@ -5342,10 +5348,10 @@
       <c r="A342" t="s">
         <v>282</v>
       </c>
-      <c r="B342">
-        <v>1</v>
-      </c>
-      <c r="C342">
+      <c r="B342" s="3">
+        <v>1</v>
+      </c>
+      <c r="C342" s="3">
         <v>31.6</v>
       </c>
     </row>
@@ -5353,10 +5359,10 @@
       <c r="A343" t="s">
         <v>283</v>
       </c>
-      <c r="B343">
+      <c r="B343" s="3">
         <v>6</v>
       </c>
-      <c r="C343">
+      <c r="C343" s="3">
         <v>69.010000000000005</v>
       </c>
     </row>
@@ -5364,10 +5370,10 @@
       <c r="A344" t="s">
         <v>283</v>
       </c>
-      <c r="B344">
-        <v>1</v>
-      </c>
-      <c r="C344">
+      <c r="B344" s="3">
+        <v>1</v>
+      </c>
+      <c r="C344" s="3">
         <v>77.28</v>
       </c>
     </row>
@@ -5375,10 +5381,10 @@
       <c r="A345" t="s">
         <v>284</v>
       </c>
-      <c r="B345">
+      <c r="B345" s="3">
         <v>24</v>
       </c>
-      <c r="C345">
+      <c r="C345" s="3">
         <v>39.11</v>
       </c>
     </row>
@@ -5386,10 +5392,10 @@
       <c r="A346" t="s">
         <v>285</v>
       </c>
-      <c r="B346">
+      <c r="B346" s="3">
         <v>7</v>
       </c>
-      <c r="C346">
+      <c r="C346" s="3">
         <v>11.69</v>
       </c>
     </row>
@@ -5397,10 +5403,10 @@
       <c r="A347" t="s">
         <v>286</v>
       </c>
-      <c r="B347">
+      <c r="B347" s="3">
         <v>3</v>
       </c>
-      <c r="C347">
+      <c r="C347" s="3">
         <v>713.06</v>
       </c>
     </row>
@@ -5408,10 +5414,10 @@
       <c r="A348" t="s">
         <v>287</v>
       </c>
-      <c r="B348">
+      <c r="B348" s="3">
         <v>95</v>
       </c>
-      <c r="C348">
+      <c r="C348" s="3">
         <v>20.7</v>
       </c>
     </row>
@@ -5419,10 +5425,10 @@
       <c r="A349" t="s">
         <v>288</v>
       </c>
-      <c r="B349">
+      <c r="B349" s="3">
         <v>64</v>
       </c>
-      <c r="C349">
+      <c r="C349" s="3">
         <v>7.36</v>
       </c>
     </row>
@@ -5430,10 +5436,10 @@
       <c r="A350" t="s">
         <v>289</v>
       </c>
-      <c r="B350">
+      <c r="B350" s="3">
         <v>9</v>
       </c>
-      <c r="C350">
+      <c r="C350" s="3">
         <v>11.5</v>
       </c>
     </row>
@@ -5441,10 +5447,10 @@
       <c r="A351" t="s">
         <v>290</v>
       </c>
-      <c r="B351">
-        <v>1</v>
-      </c>
-      <c r="C351">
+      <c r="B351" s="3">
+        <v>1</v>
+      </c>
+      <c r="C351" s="3">
         <v>26.36</v>
       </c>
     </row>
@@ -5452,10 +5458,10 @@
       <c r="A352" t="s">
         <v>291</v>
       </c>
-      <c r="B352">
+      <c r="B352" s="3">
         <v>9</v>
       </c>
-      <c r="C352">
+      <c r="C352" s="3">
         <v>28.52</v>
       </c>
     </row>
@@ -5463,10 +5469,10 @@
       <c r="A353" t="s">
         <v>292</v>
       </c>
-      <c r="B353">
+      <c r="B353" s="3">
         <v>106</v>
       </c>
-      <c r="C353">
+      <c r="C353" s="3">
         <v>14.49</v>
       </c>
     </row>
@@ -5474,10 +5480,10 @@
       <c r="A354" t="s">
         <v>293</v>
       </c>
-      <c r="B354">
+      <c r="B354" s="3">
         <v>11</v>
       </c>
-      <c r="C354">
+      <c r="C354" s="3">
         <v>19.55</v>
       </c>
     </row>
@@ -5485,10 +5491,10 @@
       <c r="A355" t="s">
         <v>294</v>
       </c>
-      <c r="B355">
+      <c r="B355" s="3">
         <v>12</v>
       </c>
-      <c r="C355">
+      <c r="C355" s="3">
         <v>19.48</v>
       </c>
     </row>
@@ -5496,10 +5502,10 @@
       <c r="A356" t="s">
         <v>295</v>
       </c>
-      <c r="B356">
+      <c r="B356" s="3">
         <v>11</v>
       </c>
-      <c r="C356">
+      <c r="C356" s="3">
         <v>19</v>
       </c>
     </row>
@@ -5507,10 +5513,10 @@
       <c r="A357" t="s">
         <v>296</v>
       </c>
-      <c r="B357">
+      <c r="B357" s="3">
         <v>34</v>
       </c>
-      <c r="C357">
+      <c r="C357" s="3">
         <v>19</v>
       </c>
     </row>
@@ -5518,10 +5524,10 @@
       <c r="A358" t="s">
         <v>297</v>
       </c>
-      <c r="B358">
+      <c r="B358" s="3">
         <v>11</v>
       </c>
-      <c r="C358">
+      <c r="C358" s="3">
         <v>51.75</v>
       </c>
     </row>
@@ -5529,10 +5535,10 @@
       <c r="A359" t="s">
         <v>297</v>
       </c>
-      <c r="B359">
-        <v>1</v>
-      </c>
-      <c r="C359">
+      <c r="B359" s="3">
+        <v>1</v>
+      </c>
+      <c r="C359" s="3">
         <v>57.96</v>
       </c>
     </row>
@@ -5540,10 +5546,10 @@
       <c r="A360" t="s">
         <v>298</v>
       </c>
-      <c r="B360">
-        <v>1</v>
-      </c>
-      <c r="C360">
+      <c r="B360" s="3">
+        <v>1</v>
+      </c>
+      <c r="C360" s="3">
         <v>862.7</v>
       </c>
     </row>
@@ -5551,10 +5557,10 @@
       <c r="A361" t="s">
         <v>299</v>
       </c>
-      <c r="B361">
+      <c r="B361" s="3">
         <v>11</v>
       </c>
-      <c r="C361">
+      <c r="C361" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -5562,10 +5568,10 @@
       <c r="A362" t="s">
         <v>300</v>
       </c>
-      <c r="B362">
+      <c r="B362" s="3">
         <v>2</v>
       </c>
-      <c r="C362">
+      <c r="C362" s="3">
         <v>1265</v>
       </c>
     </row>
@@ -5573,10 +5579,10 @@
       <c r="A363" t="s">
         <v>301</v>
       </c>
-      <c r="B363">
+      <c r="B363" s="3">
         <v>30</v>
       </c>
-      <c r="C363">
+      <c r="C363" s="3">
         <v>56.05</v>
       </c>
     </row>
@@ -5584,10 +5590,10 @@
       <c r="A364" t="s">
         <v>302</v>
       </c>
-      <c r="B364">
+      <c r="B364" s="3">
         <v>6</v>
       </c>
-      <c r="C364">
+      <c r="C364" s="3">
         <v>235.74</v>
       </c>
     </row>
@@ -5595,10 +5601,10 @@
       <c r="A365" t="s">
         <v>303</v>
       </c>
-      <c r="B365">
+      <c r="B365" s="3">
         <v>17</v>
       </c>
-      <c r="C365">
+      <c r="C365" s="3">
         <v>62.6</v>
       </c>
     </row>
@@ -5606,10 +5612,10 @@
       <c r="A366" t="s">
         <v>304</v>
       </c>
-      <c r="B366">
+      <c r="B366" s="3">
         <v>15</v>
       </c>
-      <c r="C366">
+      <c r="C366" s="3">
         <v>264.36</v>
       </c>
     </row>
@@ -5617,10 +5623,10 @@
       <c r="A367" t="s">
         <v>305</v>
       </c>
-      <c r="B367">
+      <c r="B367" s="3">
         <v>10</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="3">
         <v>64.400000000000006</v>
       </c>
     </row>
@@ -5628,10 +5634,10 @@
       <c r="A368" t="s">
         <v>306</v>
       </c>
-      <c r="B368">
+      <c r="B368" s="3">
         <v>44</v>
       </c>
-      <c r="C368">
+      <c r="C368" s="3">
         <v>231.16</v>
       </c>
     </row>
@@ -5639,10 +5645,10 @@
       <c r="A369" t="s">
         <v>307</v>
       </c>
-      <c r="B369">
+      <c r="B369" s="3">
         <v>38</v>
       </c>
-      <c r="C369">
+      <c r="C369" s="3">
         <v>36.799999999999997</v>
       </c>
     </row>
@@ -5650,10 +5656,10 @@
       <c r="A370" t="s">
         <v>308</v>
       </c>
-      <c r="B370">
+      <c r="B370" s="3">
         <v>2</v>
       </c>
-      <c r="C370">
+      <c r="C370" s="3">
         <v>400.55</v>
       </c>
     </row>
@@ -5661,10 +5667,10 @@
       <c r="A371" t="s">
         <v>309</v>
       </c>
-      <c r="B371">
+      <c r="B371" s="3">
         <v>3</v>
       </c>
-      <c r="C371">
+      <c r="C371" s="3">
         <v>400.55</v>
       </c>
     </row>
@@ -5672,10 +5678,10 @@
       <c r="A372" t="s">
         <v>310</v>
       </c>
-      <c r="B372">
+      <c r="B372" s="3">
         <v>4</v>
       </c>
-      <c r="C372">
+      <c r="C372" s="3">
         <v>409.86</v>
       </c>
     </row>
@@ -5683,10 +5689,10 @@
       <c r="A373" t="s">
         <v>311</v>
       </c>
-      <c r="B373">
+      <c r="B373" s="3">
         <v>19</v>
       </c>
-      <c r="C373">
+      <c r="C373" s="3">
         <v>28.97</v>
       </c>
     </row>
@@ -5694,10 +5700,10 @@
       <c r="A374" t="s">
         <v>312</v>
       </c>
-      <c r="B374">
+      <c r="B374" s="3">
         <v>2</v>
       </c>
-      <c r="C374">
+      <c r="C374" s="3">
         <v>87.16</v>
       </c>
     </row>
@@ -5705,10 +5711,10 @@
       <c r="A375" t="s">
         <v>313</v>
       </c>
-      <c r="B375">
+      <c r="B375" s="3">
         <v>23</v>
       </c>
-      <c r="C375">
+      <c r="C375" s="3">
         <v>41.92</v>
       </c>
     </row>
@@ -5716,10 +5722,10 @@
       <c r="A376" t="s">
         <v>314</v>
       </c>
-      <c r="B376">
+      <c r="B376" s="3">
         <v>2</v>
       </c>
-      <c r="C376">
+      <c r="C376" s="3">
         <v>299.11</v>
       </c>
     </row>
@@ -5727,10 +5733,10 @@
       <c r="A377" t="s">
         <v>315</v>
       </c>
-      <c r="B377">
+      <c r="B377" s="3">
         <v>2</v>
       </c>
-      <c r="C377">
+      <c r="C377" s="3">
         <v>2512.7399999999998</v>
       </c>
     </row>
@@ -5738,10 +5744,10 @@
       <c r="A378" t="s">
         <v>316</v>
       </c>
-      <c r="B378">
+      <c r="B378" s="3">
         <v>5</v>
       </c>
-      <c r="C378">
+      <c r="C378" s="3">
         <v>305.32</v>
       </c>
     </row>
@@ -5749,10 +5755,10 @@
       <c r="A379" t="s">
         <v>317</v>
       </c>
-      <c r="B379">
-        <v>1</v>
-      </c>
-      <c r="C379">
+      <c r="B379" s="3">
+        <v>1</v>
+      </c>
+      <c r="C379" s="3">
         <v>103.51</v>
       </c>
     </row>
@@ -5760,10 +5766,10 @@
       <c r="A380" t="s">
         <v>318</v>
       </c>
-      <c r="B380">
-        <v>1</v>
-      </c>
-      <c r="C380">
+      <c r="B380" s="3">
+        <v>1</v>
+      </c>
+      <c r="C380" s="3">
         <v>41.91</v>
       </c>
     </row>
@@ -5771,10 +5777,10 @@
       <c r="A381" t="s">
         <v>318</v>
       </c>
-      <c r="B381">
+      <c r="B381" s="3">
         <v>41</v>
       </c>
-      <c r="C381">
+      <c r="C381" s="3">
         <v>54.2</v>
       </c>
     </row>
@@ -5782,10 +5788,10 @@
       <c r="A382" t="s">
         <v>319</v>
       </c>
-      <c r="B382">
+      <c r="B382" s="3">
         <v>12</v>
       </c>
-      <c r="C382">
+      <c r="C382" s="3">
         <v>28.13</v>
       </c>
     </row>
@@ -5793,10 +5799,10 @@
       <c r="A383" t="s">
         <v>320</v>
       </c>
-      <c r="B383">
+      <c r="B383" s="3">
         <v>4</v>
       </c>
-      <c r="C383">
+      <c r="C383" s="3">
         <v>101.87</v>
       </c>
     </row>
@@ -5804,10 +5810,10 @@
       <c r="A384" t="s">
         <v>321</v>
       </c>
-      <c r="B384">
+      <c r="B384" s="3">
         <v>4</v>
       </c>
-      <c r="C384">
+      <c r="C384" s="3">
         <v>125</v>
       </c>
     </row>
@@ -5815,10 +5821,10 @@
       <c r="A385" t="s">
         <v>322</v>
       </c>
-      <c r="B385">
+      <c r="B385" s="3">
         <v>10</v>
       </c>
-      <c r="C385">
+      <c r="C385" s="3">
         <v>27.39</v>
       </c>
     </row>
@@ -5826,10 +5832,10 @@
       <c r="A386" t="s">
         <v>323</v>
       </c>
-      <c r="B386">
+      <c r="B386" s="3">
         <v>8</v>
       </c>
-      <c r="C386">
+      <c r="C386" s="3">
         <v>96.82</v>
       </c>
     </row>
@@ -5837,10 +5843,10 @@
       <c r="A387" t="s">
         <v>324</v>
       </c>
-      <c r="B387">
+      <c r="B387" s="3">
         <v>2</v>
       </c>
-      <c r="C387">
+      <c r="C387" s="3">
         <v>297.04000000000002</v>
       </c>
     </row>
@@ -5848,10 +5854,10 @@
       <c r="A388" t="s">
         <v>325</v>
       </c>
-      <c r="B388">
+      <c r="B388" s="3">
         <v>8</v>
       </c>
-      <c r="C388">
+      <c r="C388" s="3">
         <v>27.6</v>
       </c>
     </row>
@@ -5859,10 +5865,10 @@
       <c r="A389" t="s">
         <v>326</v>
       </c>
-      <c r="B389">
-        <v>1</v>
-      </c>
-      <c r="C389">
+      <c r="B389" s="3">
+        <v>1</v>
+      </c>
+      <c r="C389" s="3">
         <v>5746.5</v>
       </c>
     </row>
@@ -5870,10 +5876,10 @@
       <c r="A390" t="s">
         <v>327</v>
       </c>
-      <c r="B390">
-        <v>1</v>
-      </c>
-      <c r="C390">
+      <c r="B390" s="3">
+        <v>1</v>
+      </c>
+      <c r="C390" s="3">
         <v>375.7</v>
       </c>
     </row>
@@ -5881,10 +5887,10 @@
       <c r="A391" t="s">
         <v>327</v>
       </c>
-      <c r="B391">
+      <c r="B391" s="3">
         <v>2</v>
       </c>
-      <c r="C391">
+      <c r="C391" s="3">
         <v>516.46</v>
       </c>
     </row>
@@ -5892,10 +5898,10 @@
       <c r="A392" t="s">
         <v>328</v>
       </c>
-      <c r="B392">
+      <c r="B392" s="3">
         <v>4</v>
       </c>
-      <c r="C392">
+      <c r="C392" s="3">
         <v>124.21</v>
       </c>
     </row>
@@ -5903,10 +5909,10 @@
       <c r="A393" t="s">
         <v>329</v>
       </c>
-      <c r="B393">
+      <c r="B393" s="3">
         <v>31</v>
       </c>
-      <c r="C393">
+      <c r="C393" s="3">
         <v>11.5</v>
       </c>
     </row>
@@ -5914,10 +5920,10 @@
       <c r="A394" t="s">
         <v>330</v>
       </c>
-      <c r="B394">
+      <c r="B394" s="3">
         <v>4</v>
       </c>
-      <c r="C394">
+      <c r="C394" s="3">
         <v>569.26</v>
       </c>
     </row>
@@ -5925,10 +5931,10 @@
       <c r="A395" t="s">
         <v>331</v>
       </c>
-      <c r="B395">
+      <c r="B395" s="3">
         <v>4</v>
       </c>
-      <c r="C395">
+      <c r="C395" s="3">
         <v>381.24</v>
       </c>
     </row>
@@ -5936,10 +5942,10 @@
       <c r="A396" t="s">
         <v>332</v>
       </c>
-      <c r="B396">
-        <v>1</v>
-      </c>
-      <c r="C396">
+      <c r="B396" s="3">
+        <v>0</v>
+      </c>
+      <c r="C396" s="3">
         <v>46.8</v>
       </c>
     </row>
@@ -5947,10 +5953,10 @@
       <c r="A397" t="s">
         <v>333</v>
       </c>
-      <c r="B397">
-        <v>1</v>
-      </c>
-      <c r="C397">
+      <c r="B397" s="3">
+        <v>1</v>
+      </c>
+      <c r="C397" s="3">
         <v>461.23</v>
       </c>
     </row>
@@ -5958,10 +5964,10 @@
       <c r="A398" t="s">
         <v>333</v>
       </c>
-      <c r="B398">
-        <v>1</v>
-      </c>
-      <c r="C398">
+      <c r="B398" s="3">
+        <v>1</v>
+      </c>
+      <c r="C398" s="3">
         <v>518.41999999999996</v>
       </c>
     </row>
@@ -5969,10 +5975,10 @@
       <c r="A399" t="s">
         <v>334</v>
       </c>
-      <c r="B399">
-        <v>1</v>
-      </c>
-      <c r="C399">
+      <c r="B399" s="3">
+        <v>1</v>
+      </c>
+      <c r="C399" s="3">
         <v>348.08</v>
       </c>
     </row>
@@ -5980,10 +5986,10 @@
       <c r="A400" t="s">
         <v>335</v>
       </c>
-      <c r="B400">
+      <c r="B400" s="3">
         <v>10</v>
       </c>
-      <c r="C400">
+      <c r="C400" s="3">
         <v>25.99</v>
       </c>
     </row>
@@ -5991,10 +5997,10 @@
       <c r="A401" t="s">
         <v>336</v>
       </c>
-      <c r="B401">
+      <c r="B401" s="3">
         <v>13</v>
       </c>
-      <c r="C401">
+      <c r="C401" s="3">
         <v>27.79</v>
       </c>
     </row>
@@ -6002,10 +6008,10 @@
       <c r="A402" t="s">
         <v>337</v>
       </c>
-      <c r="B402">
+      <c r="B402" s="3">
         <v>3</v>
       </c>
-      <c r="C402">
+      <c r="C402" s="3">
         <v>198.67</v>
       </c>
     </row>
@@ -6013,10 +6019,10 @@
       <c r="A403" t="s">
         <v>338</v>
       </c>
-      <c r="B403">
+      <c r="B403" s="3">
         <v>18</v>
       </c>
-      <c r="C403">
+      <c r="C403" s="3">
         <v>25.79</v>
       </c>
     </row>
@@ -6024,10 +6030,10 @@
       <c r="A404" t="s">
         <v>339</v>
       </c>
-      <c r="B404">
+      <c r="B404" s="3">
         <v>39</v>
       </c>
-      <c r="C404">
+      <c r="C404" s="3">
         <v>17.440000000000001</v>
       </c>
     </row>
@@ -6035,10 +6041,10 @@
       <c r="A405" t="s">
         <v>340</v>
       </c>
-      <c r="B405">
-        <v>1</v>
-      </c>
-      <c r="C405">
+      <c r="B405" s="3">
+        <v>1</v>
+      </c>
+      <c r="C405" s="3">
         <v>361.41</v>
       </c>
     </row>
@@ -6046,10 +6052,10 @@
       <c r="A406" t="s">
         <v>341</v>
       </c>
-      <c r="B406">
+      <c r="B406" s="3">
         <v>63</v>
       </c>
-      <c r="C406">
+      <c r="C406" s="3">
         <v>22.73</v>
       </c>
     </row>
@@ -6057,10 +6063,10 @@
       <c r="A407" t="s">
         <v>341</v>
       </c>
-      <c r="B407">
-        <v>1</v>
-      </c>
-      <c r="C407">
+      <c r="B407" s="3">
+        <v>1</v>
+      </c>
+      <c r="C407" s="3">
         <v>29.26</v>
       </c>
     </row>
@@ -6068,10 +6074,10 @@
       <c r="A408" t="s">
         <v>342</v>
       </c>
-      <c r="B408">
-        <v>1</v>
-      </c>
-      <c r="C408">
+      <c r="B408" s="3">
+        <v>0</v>
+      </c>
+      <c r="C408" s="3">
         <v>7257.28</v>
       </c>
     </row>
@@ -6079,10 +6085,10 @@
       <c r="A409" t="s">
         <v>343</v>
       </c>
-      <c r="B409">
-        <v>1</v>
-      </c>
-      <c r="C409">
+      <c r="B409" s="3">
+        <v>1</v>
+      </c>
+      <c r="C409" s="3">
         <v>304.54000000000002</v>
       </c>
     </row>
@@ -6090,10 +6096,10 @@
       <c r="A410" t="s">
         <v>344</v>
       </c>
-      <c r="B410">
+      <c r="B410" s="3">
         <v>17</v>
       </c>
-      <c r="C410">
+      <c r="C410" s="3">
         <v>18.39</v>
       </c>
     </row>
@@ -6101,10 +6107,10 @@
       <c r="A411" t="s">
         <v>345</v>
       </c>
-      <c r="B411">
+      <c r="B411" s="3">
         <v>11</v>
       </c>
-      <c r="C411">
+      <c r="C411" s="3">
         <v>39.090000000000003</v>
       </c>
     </row>
@@ -6112,10 +6118,10 @@
       <c r="A412" t="s">
         <v>346</v>
       </c>
-      <c r="B412">
+      <c r="B412" s="3">
         <v>12</v>
       </c>
-      <c r="C412">
+      <c r="C412" s="3">
         <v>74.819999999999993</v>
       </c>
     </row>
@@ -6123,10 +6129,10 @@
       <c r="A413" t="s">
         <v>347</v>
       </c>
-      <c r="B413">
+      <c r="B413" s="3">
         <v>42</v>
       </c>
-      <c r="C413">
+      <c r="C413" s="3">
         <v>42.24</v>
       </c>
     </row>
@@ -6134,10 +6140,10 @@
       <c r="A414" t="s">
         <v>347</v>
       </c>
-      <c r="B414">
+      <c r="B414" s="3">
         <v>72</v>
       </c>
-      <c r="C414">
+      <c r="C414" s="3">
         <v>44.31</v>
       </c>
     </row>
@@ -6145,10 +6151,10 @@
       <c r="A415" t="s">
         <v>348</v>
       </c>
-      <c r="B415">
-        <v>1</v>
-      </c>
-      <c r="C415">
+      <c r="B415" s="3">
+        <v>1</v>
+      </c>
+      <c r="C415" s="3">
         <v>7173.59</v>
       </c>
     </row>
@@ -6156,10 +6162,10 @@
       <c r="A416" t="s">
         <v>349</v>
       </c>
-      <c r="B416">
-        <v>1</v>
-      </c>
-      <c r="C416">
+      <c r="B416" s="3">
+        <v>1</v>
+      </c>
+      <c r="C416" s="3">
         <v>781.18</v>
       </c>
     </row>
@@ -6167,10 +6173,10 @@
       <c r="A417" t="s">
         <v>350</v>
       </c>
-      <c r="B417">
-        <v>3</v>
-      </c>
-      <c r="C417">
+      <c r="B417" s="3">
+        <v>2</v>
+      </c>
+      <c r="C417" s="3">
         <v>156.97999999999999</v>
       </c>
     </row>
@@ -6178,10 +6184,10 @@
       <c r="A418" t="s">
         <v>350</v>
       </c>
-      <c r="B418">
+      <c r="B418" s="3">
         <v>40</v>
       </c>
-      <c r="C418">
+      <c r="C418" s="3">
         <v>167.33</v>
       </c>
     </row>
@@ -6189,10 +6195,10 @@
       <c r="A419" t="s">
         <v>351</v>
       </c>
-      <c r="B419">
-        <v>63</v>
-      </c>
-      <c r="C419">
+      <c r="B419" s="3">
+        <v>61</v>
+      </c>
+      <c r="C419" s="3">
         <v>191.01</v>
       </c>
     </row>
@@ -6200,10 +6206,10 @@
       <c r="A420" t="s">
         <v>352</v>
       </c>
-      <c r="B420">
+      <c r="B420" s="3">
         <v>3</v>
       </c>
-      <c r="C420">
+      <c r="C420" s="3">
         <v>1652.02</v>
       </c>
     </row>
@@ -6211,10 +6217,10 @@
       <c r="A421" t="s">
         <v>353</v>
       </c>
-      <c r="B421">
-        <v>15</v>
-      </c>
-      <c r="C421">
+      <c r="B421" s="3">
+        <v>11</v>
+      </c>
+      <c r="C421" s="3">
         <v>55.4</v>
       </c>
     </row>
@@ -6222,10 +6228,10 @@
       <c r="A422" t="s">
         <v>353</v>
       </c>
-      <c r="B422">
+      <c r="B422" s="3">
         <v>72</v>
       </c>
-      <c r="C422">
+      <c r="C422" s="3">
         <v>62.04</v>
       </c>
     </row>
@@ -6233,10 +6239,10 @@
       <c r="A423" t="s">
         <v>354</v>
       </c>
-      <c r="B423">
+      <c r="B423" s="3">
         <v>2</v>
       </c>
-      <c r="C423">
+      <c r="C423" s="3">
         <v>8139.6</v>
       </c>
     </row>
@@ -6244,10 +6250,10 @@
       <c r="A424" t="s">
         <v>355</v>
       </c>
-      <c r="B424">
+      <c r="B424" s="3">
         <v>32</v>
       </c>
-      <c r="C424">
+      <c r="C424" s="3">
         <v>235.53</v>
       </c>
     </row>
@@ -6255,10 +6261,10 @@
       <c r="A425" t="s">
         <v>356</v>
       </c>
-      <c r="B425">
-        <v>28</v>
-      </c>
-      <c r="C425">
+      <c r="B425" s="3">
+        <v>25</v>
+      </c>
+      <c r="C425" s="3">
         <v>231.92</v>
       </c>
     </row>
@@ -6266,10 +6272,10 @@
       <c r="A426" t="s">
         <v>357</v>
       </c>
-      <c r="B426">
-        <v>1</v>
-      </c>
-      <c r="C426">
+      <c r="B426" s="3">
+        <v>1</v>
+      </c>
+      <c r="C426" s="3">
         <v>34.630000000000003</v>
       </c>
     </row>
@@ -6277,10 +6283,10 @@
       <c r="A427" t="s">
         <v>358</v>
       </c>
-      <c r="B427">
+      <c r="B427" s="3">
         <v>4</v>
       </c>
-      <c r="C427">
+      <c r="C427" s="3">
         <v>65.55</v>
       </c>
     </row>
@@ -6288,10 +6294,10 @@
       <c r="A428" t="s">
         <v>359</v>
       </c>
-      <c r="B428">
+      <c r="B428" s="3">
         <v>13</v>
       </c>
-      <c r="C428">
+      <c r="C428" s="3">
         <v>260.89999999999998</v>
       </c>
     </row>
@@ -6299,10 +6305,10 @@
       <c r="A429" t="s">
         <v>360</v>
       </c>
-      <c r="B429">
+      <c r="B429" s="3">
         <v>25</v>
       </c>
-      <c r="C429">
+      <c r="C429" s="3">
         <v>55.89</v>
       </c>
     </row>
@@ -6310,10 +6316,10 @@
       <c r="A430" t="s">
         <v>361</v>
       </c>
-      <c r="B430">
+      <c r="B430" s="3">
         <v>8</v>
       </c>
-      <c r="C430">
+      <c r="C430" s="3">
         <v>279.29000000000002</v>
       </c>
     </row>
@@ -6321,10 +6327,10 @@
       <c r="A431" t="s">
         <v>362</v>
       </c>
-      <c r="B431">
-        <v>16</v>
-      </c>
-      <c r="C431">
+      <c r="B431" s="3">
+        <v>15</v>
+      </c>
+      <c r="C431" s="3">
         <v>52.79</v>
       </c>
     </row>
@@ -6332,10 +6338,10 @@
       <c r="A432" t="s">
         <v>362</v>
       </c>
-      <c r="B432">
+      <c r="B432" s="3">
         <v>21</v>
       </c>
-      <c r="C432">
+      <c r="C432" s="3">
         <v>67.28</v>
       </c>
     </row>
@@ -6343,10 +6349,10 @@
       <c r="A433" t="s">
         <v>363</v>
       </c>
-      <c r="B433">
+      <c r="B433" s="3">
         <v>3</v>
       </c>
-      <c r="C433">
+      <c r="C433" s="3">
         <v>1024.01</v>
       </c>
     </row>
@@ -6354,10 +6360,10 @@
       <c r="A434" t="s">
         <v>363</v>
       </c>
-      <c r="B434">
-        <v>1</v>
-      </c>
-      <c r="C434">
+      <c r="B434" s="3">
+        <v>1</v>
+      </c>
+      <c r="C434" s="3">
         <v>1138.5</v>
       </c>
     </row>
@@ -6365,10 +6371,10 @@
       <c r="A435" t="s">
         <v>364</v>
       </c>
-      <c r="B435">
+      <c r="B435" s="3">
         <v>2</v>
       </c>
-      <c r="C435">
+      <c r="C435" s="3">
         <v>40.32</v>
       </c>
     </row>
@@ -6376,10 +6382,10 @@
       <c r="A436" t="s">
         <v>365</v>
       </c>
-      <c r="B436">
+      <c r="B436" s="3">
         <v>3</v>
       </c>
-      <c r="C436">
+      <c r="C436" s="3">
         <v>216.34</v>
       </c>
     </row>
@@ -6387,10 +6393,10 @@
       <c r="A437" t="s">
         <v>366</v>
       </c>
-      <c r="B437">
+      <c r="B437" s="3">
         <v>5</v>
       </c>
-      <c r="C437">
+      <c r="C437" s="3">
         <v>47.16</v>
       </c>
     </row>
@@ -6398,10 +6404,10 @@
       <c r="A438" t="s">
         <v>366</v>
       </c>
-      <c r="B438">
+      <c r="B438" s="3">
         <v>30</v>
       </c>
-      <c r="C438">
+      <c r="C438" s="3">
         <v>54.1</v>
       </c>
     </row>
@@ -6409,10 +6415,10 @@
       <c r="A439" t="s">
         <v>367</v>
       </c>
-      <c r="B439">
+      <c r="B439" s="3">
         <v>20</v>
       </c>
-      <c r="C439">
+      <c r="C439" s="3">
         <v>255.03</v>
       </c>
     </row>
@@ -6420,10 +6426,10 @@
       <c r="A440" t="s">
         <v>368</v>
       </c>
-      <c r="B440">
+      <c r="B440" s="3">
         <v>18</v>
       </c>
-      <c r="C440">
+      <c r="C440" s="3">
         <v>220.8</v>
       </c>
     </row>
@@ -6431,10 +6437,10 @@
       <c r="A441" t="s">
         <v>369</v>
       </c>
-      <c r="B441">
+      <c r="B441" s="3">
         <v>22</v>
       </c>
-      <c r="C441">
+      <c r="C441" s="3">
         <v>255.03</v>
       </c>
     </row>
@@ -6442,10 +6448,10 @@
       <c r="A442" t="s">
         <v>370</v>
       </c>
-      <c r="B442">
+      <c r="B442" s="3">
         <v>12</v>
       </c>
-      <c r="C442">
+      <c r="C442" s="3">
         <v>61.48</v>
       </c>
     </row>
@@ -6453,10 +6459,10 @@
       <c r="A443" t="s">
         <v>371</v>
       </c>
-      <c r="B443">
+      <c r="B443" s="3">
         <v>4</v>
       </c>
-      <c r="C443">
+      <c r="C443" s="3">
         <v>307.39999999999998</v>
       </c>
     </row>
@@ -6464,10 +6470,10 @@
       <c r="A444" t="s">
         <v>372</v>
       </c>
-      <c r="B444">
+      <c r="B444" s="3">
         <v>10</v>
       </c>
-      <c r="C444">
+      <c r="C444" s="3">
         <v>53.82</v>
       </c>
     </row>
@@ -6475,10 +6481,10 @@
       <c r="A445" t="s">
         <v>373</v>
       </c>
-      <c r="B445">
+      <c r="B445" s="3">
         <v>3</v>
       </c>
-      <c r="C445">
+      <c r="C445" s="3">
         <v>233.75</v>
       </c>
     </row>
@@ -6486,10 +6492,10 @@
       <c r="A446" t="s">
         <v>373</v>
       </c>
-      <c r="B446">
-        <v>1</v>
-      </c>
-      <c r="C446">
+      <c r="B446" s="3">
+        <v>1</v>
+      </c>
+      <c r="C446" s="3">
         <v>261.8</v>
       </c>
     </row>
@@ -6497,10 +6503,10 @@
       <c r="A447" t="s">
         <v>374</v>
       </c>
-      <c r="B447">
-        <v>1</v>
-      </c>
-      <c r="C447">
+      <c r="B447" s="3">
+        <v>1</v>
+      </c>
+      <c r="C447" s="3">
         <v>30.58</v>
       </c>
     </row>
@@ -6508,10 +6514,10 @@
       <c r="A448" t="s">
         <v>375</v>
       </c>
-      <c r="B448">
-        <v>1</v>
-      </c>
-      <c r="C448">
+      <c r="B448" s="3">
+        <v>1</v>
+      </c>
+      <c r="C448" s="3">
         <v>30.58</v>
       </c>
     </row>
@@ -6519,10 +6525,10 @@
       <c r="A449" t="s">
         <v>376</v>
       </c>
-      <c r="B449">
+      <c r="B449" s="3">
         <v>54</v>
       </c>
-      <c r="C449">
+      <c r="C449" s="3">
         <v>14.79</v>
       </c>
     </row>
@@ -6530,10 +6536,10 @@
       <c r="A450" t="s">
         <v>377</v>
       </c>
-      <c r="B450">
+      <c r="B450" s="3">
         <v>60</v>
       </c>
-      <c r="C450">
+      <c r="C450" s="3">
         <v>22.08</v>
       </c>
     </row>
@@ -6541,10 +6547,10 @@
       <c r="A451" t="s">
         <v>378</v>
       </c>
-      <c r="B451">
+      <c r="B451" s="3">
         <v>3</v>
       </c>
-      <c r="C451">
+      <c r="C451" s="3">
         <v>641.49</v>
       </c>
     </row>
@@ -6552,10 +6558,10 @@
       <c r="A452" t="s">
         <v>379</v>
       </c>
-      <c r="B452">
+      <c r="B452" s="3">
         <v>12</v>
       </c>
-      <c r="C452">
+      <c r="C452" s="3">
         <v>35.18</v>
       </c>
     </row>
@@ -6563,10 +6569,10 @@
       <c r="A453" t="s">
         <v>380</v>
       </c>
-      <c r="B453">
+      <c r="B453" s="3">
         <v>36</v>
       </c>
-      <c r="C453">
+      <c r="C453" s="3">
         <v>51.83</v>
       </c>
     </row>
@@ -6574,10 +6580,10 @@
       <c r="A454" t="s">
         <v>381</v>
       </c>
-      <c r="B454">
+      <c r="B454" s="3">
         <v>48</v>
       </c>
-      <c r="C454">
+      <c r="C454" s="3">
         <v>29.94</v>
       </c>
     </row>
@@ -6585,10 +6591,10 @@
       <c r="A455" t="s">
         <v>382</v>
       </c>
-      <c r="B455">
+      <c r="B455" s="3">
         <v>21</v>
       </c>
-      <c r="C455">
+      <c r="C455" s="3">
         <v>132.83000000000001</v>
       </c>
     </row>
@@ -6596,10 +6602,10 @@
       <c r="A456" t="s">
         <v>383</v>
       </c>
-      <c r="B456">
+      <c r="B456" s="3">
         <v>25</v>
       </c>
-      <c r="C456">
+      <c r="C456" s="3">
         <v>127.84</v>
       </c>
     </row>
@@ -6607,10 +6613,10 @@
       <c r="A457" t="s">
         <v>384</v>
       </c>
-      <c r="B457">
+      <c r="B457" s="3">
         <v>25</v>
       </c>
-      <c r="C457">
+      <c r="C457" s="3">
         <v>100.93</v>
       </c>
     </row>
@@ -6618,10 +6624,10 @@
       <c r="A458" t="s">
         <v>385</v>
       </c>
-      <c r="B458">
+      <c r="B458" s="3">
         <v>14</v>
       </c>
-      <c r="C458">
+      <c r="C458" s="3">
         <v>109.5</v>
       </c>
     </row>
@@ -6629,10 +6635,10 @@
       <c r="A459" t="s">
         <v>386</v>
       </c>
-      <c r="B459">
+      <c r="B459" s="3">
         <v>10</v>
       </c>
-      <c r="C459">
+      <c r="C459" s="3">
         <v>23.99</v>
       </c>
     </row>
@@ -6640,10 +6646,10 @@
       <c r="A460" t="s">
         <v>387</v>
       </c>
-      <c r="B460">
+      <c r="B460" s="3">
         <v>94</v>
       </c>
-      <c r="C460">
+      <c r="C460" s="3">
         <v>21.61</v>
       </c>
     </row>
@@ -6651,10 +6657,10 @@
       <c r="A461" t="s">
         <v>388</v>
       </c>
-      <c r="B461">
+      <c r="B461" s="3">
         <v>10</v>
       </c>
-      <c r="C461">
+      <c r="C461" s="3">
         <v>32.85</v>
       </c>
     </row>
@@ -6662,10 +6668,10 @@
       <c r="A462" t="s">
         <v>389</v>
       </c>
-      <c r="B462">
+      <c r="B462" s="3">
         <v>10</v>
       </c>
-      <c r="C462">
+      <c r="C462" s="3">
         <v>157.47999999999999</v>
       </c>
     </row>
@@ -6673,10 +6679,10 @@
       <c r="A463" t="s">
         <v>390</v>
       </c>
-      <c r="B463">
+      <c r="B463" s="3">
         <v>48</v>
       </c>
-      <c r="C463">
+      <c r="C463" s="3">
         <v>23.88</v>
       </c>
     </row>
@@ -6684,10 +6690,10 @@
       <c r="A464" t="s">
         <v>391</v>
       </c>
-      <c r="B464">
+      <c r="B464" s="3">
         <v>50</v>
       </c>
-      <c r="C464">
+      <c r="C464" s="3">
         <v>8.26</v>
       </c>
     </row>
@@ -6695,10 +6701,10 @@
       <c r="A465" t="s">
         <v>392</v>
       </c>
-      <c r="B465">
-        <v>1</v>
-      </c>
-      <c r="C465">
+      <c r="B465" s="3">
+        <v>1</v>
+      </c>
+      <c r="C465" s="3">
         <v>859.21</v>
       </c>
     </row>
@@ -6706,10 +6712,10 @@
       <c r="A466" t="s">
         <v>393</v>
       </c>
-      <c r="B466">
-        <v>1</v>
-      </c>
-      <c r="C466">
+      <c r="B466" s="3">
+        <v>1</v>
+      </c>
+      <c r="C466" s="3">
         <v>242.4</v>
       </c>
     </row>
@@ -6717,10 +6723,10 @@
       <c r="A467" t="s">
         <v>394</v>
       </c>
-      <c r="B467">
+      <c r="B467" s="3">
         <v>3</v>
       </c>
-      <c r="C467">
+      <c r="C467" s="3">
         <v>5000</v>
       </c>
     </row>
@@ -6728,10 +6734,10 @@
       <c r="A468" t="s">
         <v>395</v>
       </c>
-      <c r="B468">
+      <c r="B468" s="3">
         <v>105</v>
       </c>
-      <c r="C468">
+      <c r="C468" s="3">
         <v>18.309999999999999</v>
       </c>
     </row>
@@ -6739,10 +6745,10 @@
       <c r="A469" t="s">
         <v>396</v>
       </c>
-      <c r="B469">
+      <c r="B469" s="3">
         <v>31</v>
       </c>
-      <c r="C469">
+      <c r="C469" s="3">
         <v>97.45</v>
       </c>
     </row>
@@ -6750,10 +6756,10 @@
       <c r="A470" t="s">
         <v>397</v>
       </c>
-      <c r="B470">
+      <c r="B470" s="3">
         <v>3</v>
       </c>
-      <c r="C470">
+      <c r="C470" s="3">
         <v>304.02999999999997</v>
       </c>
     </row>
@@ -6761,10 +6767,10 @@
       <c r="A471" t="s">
         <v>397</v>
       </c>
-      <c r="B471">
+      <c r="B471" s="3">
         <v>11</v>
       </c>
-      <c r="C471">
+      <c r="C471" s="3">
         <v>304.02999999999997</v>
       </c>
     </row>
@@ -6772,10 +6778,10 @@
       <c r="A472" t="s">
         <v>398</v>
       </c>
-      <c r="B472">
+      <c r="B472" s="3">
         <v>6</v>
       </c>
-      <c r="C472">
+      <c r="C472" s="3">
         <v>1694.69</v>
       </c>
     </row>
@@ -6783,10 +6789,10 @@
       <c r="A473" t="s">
         <v>399</v>
       </c>
-      <c r="B473">
+      <c r="B473" s="3">
         <v>6</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="3">
         <v>177</v>
       </c>
     </row>
@@ -6794,10 +6800,10 @@
       <c r="A474" t="s">
         <v>400</v>
       </c>
-      <c r="B474">
+      <c r="B474" s="3">
         <v>10</v>
       </c>
-      <c r="C474">
+      <c r="C474" s="3">
         <v>230.99</v>
       </c>
     </row>
@@ -6805,10 +6811,10 @@
       <c r="A475" t="s">
         <v>401</v>
       </c>
-      <c r="B475">
+      <c r="B475" s="3">
         <v>96</v>
       </c>
-      <c r="C475">
+      <c r="C475" s="3">
         <v>29.55</v>
       </c>
     </row>
@@ -6816,14 +6822,15 @@
       <c r="A476" t="s">
         <v>402</v>
       </c>
-      <c r="B476">
+      <c r="B476" s="3">
         <v>72</v>
       </c>
-      <c r="C476">
+      <c r="C476" s="3">
         <v>20.66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4703,7 +4703,7 @@
         <v>45</v>
       </c>
       <c r="C283" s="3">
-        <v>58.69</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -4714,7 +4714,7 @@
         <v>35</v>
       </c>
       <c r="C284" s="3">
-        <v>58.12</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -4725,7 +4725,7 @@
         <v>5</v>
       </c>
       <c r="C285" s="3">
-        <v>58.51</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -4747,7 +4747,7 @@
         <v>32</v>
       </c>
       <c r="C287" s="3">
-        <v>72.45</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -4758,7 +4758,7 @@
         <v>26</v>
       </c>
       <c r="C288" s="3">
-        <v>29.89</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -4780,7 +4780,7 @@
         <v>6</v>
       </c>
       <c r="C290" s="3">
-        <v>335.8</v>
+        <v>422.09</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -4791,7 +4791,7 @@
         <v>2</v>
       </c>
       <c r="C291" s="3">
-        <v>1007.4</v>
+        <v>1277.7</v>
       </c>
     </row>
     <row r="292" spans="1:3">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1299,10 +1299,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1600,15 +1606,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C483"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" style="3" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1616,10 +1626,10 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>235</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>12.4</v>
       </c>
     </row>
@@ -1627,10 +1637,10 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>139.26</v>
       </c>
     </row>
@@ -1638,10 +1648,10 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>176.78</v>
       </c>
     </row>
@@ -1649,10 +1659,10 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>22</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>239.2</v>
       </c>
     </row>
@@ -1660,21 +1670,21 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>262.6</v>
+      <c r="C6" s="3">
+        <v>262.60000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>20</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>262.61</v>
       </c>
     </row>
@@ -1682,10 +1692,10 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>407.86</v>
       </c>
     </row>
@@ -1693,10 +1703,10 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>9</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>635.11</v>
       </c>
     </row>
@@ -1704,10 +1714,10 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>27</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>309.52</v>
       </c>
     </row>
@@ -1715,10 +1725,10 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>46</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>343.45</v>
       </c>
     </row>
@@ -1726,10 +1736,10 @@
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>467.19</v>
       </c>
     </row>
@@ -1737,10 +1747,10 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>535.12</v>
       </c>
     </row>
@@ -1748,10 +1758,10 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>687.26</v>
       </c>
     </row>
@@ -1759,10 +1769,10 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>6</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>825.42</v>
       </c>
     </row>
@@ -1770,10 +1780,10 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>2</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>825.42</v>
       </c>
     </row>
@@ -1781,10 +1791,10 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>10</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>902.73</v>
       </c>
     </row>
@@ -1792,10 +1802,10 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>4</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>698.39</v>
       </c>
     </row>
@@ -1803,10 +1813,10 @@
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="3">
         <v>909.67</v>
       </c>
     </row>
@@ -1814,10 +1824,10 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>909.67</v>
       </c>
     </row>
@@ -1825,10 +1835,10 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>2</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>934.13</v>
       </c>
     </row>
@@ -1836,10 +1846,10 @@
       <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="3">
         <v>4</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>1132.73</v>
       </c>
     </row>
@@ -1847,10 +1857,10 @@
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>1132.73</v>
       </c>
     </row>
@@ -1858,10 +1868,10 @@
       <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
         <v>2400</v>
       </c>
     </row>
@@ -1869,21 +1879,21 @@
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="3">
         <v>27</v>
       </c>
-      <c r="C25">
-        <v>534.95</v>
+      <c r="C25" s="3">
+        <v>534.95000000000005</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>706.12</v>
       </c>
     </row>
@@ -1891,10 +1901,10 @@
       <c r="A27" t="s">
         <v>24</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="3">
         <v>3</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>241.24</v>
       </c>
     </row>
@@ -1902,10 +1912,10 @@
       <c r="A28" t="s">
         <v>24</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3">
         <v>241.24</v>
       </c>
     </row>
@@ -1913,10 +1923,10 @@
       <c r="A29" t="s">
         <v>25</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="3">
         <v>9</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>278.02</v>
       </c>
     </row>
@@ -1924,10 +1934,10 @@
       <c r="A30" t="s">
         <v>26</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="3">
         <v>4</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>358.39</v>
       </c>
     </row>
@@ -1935,10 +1945,10 @@
       <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="3">
         <v>27</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>376.62</v>
       </c>
     </row>
@@ -1946,10 +1956,10 @@
       <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="3">
         <v>7</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>409.88</v>
       </c>
     </row>
@@ -1957,10 +1967,10 @@
       <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="3">
         <v>21</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>442.81</v>
       </c>
     </row>
@@ -1968,10 +1978,10 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="3">
         <v>3</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>491.37</v>
       </c>
     </row>
@@ -1979,10 +1989,10 @@
       <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3">
         <v>478.19</v>
       </c>
     </row>
@@ -1990,10 +2000,10 @@
       <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="3">
         <v>3</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="3">
         <v>108.16</v>
       </c>
     </row>
@@ -2001,10 +2011,10 @@
       <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="3">
         <v>6</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="3">
         <v>33.28</v>
       </c>
     </row>
@@ -2012,10 +2022,10 @@
       <c r="A38" t="s">
         <v>34</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="3">
         <v>5</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="3">
         <v>20.66</v>
       </c>
     </row>
@@ -2023,10 +2033,10 @@
       <c r="A39" t="s">
         <v>35</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="3">
         <v>120</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="3">
         <v>41.58</v>
       </c>
     </row>
@@ -2034,10 +2044,10 @@
       <c r="A40" t="s">
         <v>36</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="3">
         <v>2</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="3">
         <v>5899.25</v>
       </c>
     </row>
@@ -2045,10 +2055,10 @@
       <c r="A41" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="3">
         <v>4</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="3">
         <v>5899.25</v>
       </c>
     </row>
@@ -2056,10 +2066,10 @@
       <c r="A42" t="s">
         <v>38</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="3">
         <v>20</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="3">
         <v>182.58</v>
       </c>
     </row>
@@ -2067,10 +2077,10 @@
       <c r="A43" t="s">
         <v>39</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="3">
         <v>7</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>41.58</v>
       </c>
     </row>
@@ -2078,43 +2088,43 @@
       <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="3">
         <v>7</v>
       </c>
-      <c r="C44">
-        <v>146.98</v>
+      <c r="C44" s="3">
+        <v>146.97999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>41</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="3">
         <v>42</v>
       </c>
-      <c r="C45">
-        <v>34.62</v>
+      <c r="C45" s="3">
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>42</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="3">
         <v>4</v>
       </c>
-      <c r="C46">
-        <v>34.62</v>
+      <c r="C46" s="3">
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>43</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="3">
         <v>15</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>122.46</v>
       </c>
     </row>
@@ -2122,10 +2132,10 @@
       <c r="A48" t="s">
         <v>44</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="3">
         <v>16</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="3">
         <v>200.92</v>
       </c>
     </row>
@@ -2133,10 +2143,10 @@
       <c r="A49" t="s">
         <v>45</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49">
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3">
         <v>156.07</v>
       </c>
     </row>
@@ -2144,10 +2154,10 @@
       <c r="A50" t="s">
         <v>46</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="3">
         <v>60</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>25.61</v>
       </c>
     </row>
@@ -2155,10 +2165,10 @@
       <c r="A51" t="s">
         <v>47</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="3">
         <v>30</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="3">
         <v>115.42</v>
       </c>
     </row>
@@ -2166,10 +2176,10 @@
       <c r="A52" t="s">
         <v>48</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>64</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="3">
         <v>25.6</v>
       </c>
     </row>
@@ -2177,10 +2187,10 @@
       <c r="A53" t="s">
         <v>49</v>
       </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53">
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3">
         <v>36.4</v>
       </c>
     </row>
@@ -2188,10 +2198,10 @@
       <c r="A54" t="s">
         <v>50</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="3">
         <v>3194</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="3">
         <v>13</v>
       </c>
     </row>
@@ -2199,10 +2209,10 @@
       <c r="A55" t="s">
         <v>51</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="3">
         <v>12</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="3">
         <v>20.99</v>
       </c>
     </row>
@@ -2210,10 +2220,10 @@
       <c r="A56" t="s">
         <v>51</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="3">
         <v>60</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="3">
         <v>23.37</v>
       </c>
     </row>
@@ -2221,10 +2231,10 @@
       <c r="A57" t="s">
         <v>52</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="3">
         <v>4</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="3">
         <v>361.92</v>
       </c>
     </row>
@@ -2232,10 +2242,10 @@
       <c r="A58" t="s">
         <v>53</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="3">
         <v>2</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="3">
         <v>20.69</v>
       </c>
     </row>
@@ -2243,10 +2253,10 @@
       <c r="A59" t="s">
         <v>53</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="3">
         <v>24</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>21</v>
       </c>
     </row>
@@ -2254,10 +2264,10 @@
       <c r="A60" t="s">
         <v>54</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="3">
         <v>2</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="3">
         <v>318.18</v>
       </c>
     </row>
@@ -2265,10 +2275,10 @@
       <c r="A61" t="s">
         <v>54</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="3">
         <v>2</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="3">
         <v>357.53</v>
       </c>
     </row>
@@ -2276,21 +2286,21 @@
       <c r="A62" t="s">
         <v>55</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="3">
         <v>23</v>
       </c>
-      <c r="C62">
-        <v>18.15</v>
+      <c r="C62" s="3">
+        <v>18.149999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>55</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>12</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="3">
         <v>19.3</v>
       </c>
     </row>
@@ -2298,10 +2308,10 @@
       <c r="A64" t="s">
         <v>56</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="3">
         <v>4</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="3">
         <v>337.5</v>
       </c>
     </row>
@@ -2309,10 +2319,10 @@
       <c r="A65" t="s">
         <v>57</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="3">
         <v>36</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="3">
         <v>33.64</v>
       </c>
     </row>
@@ -2320,10 +2330,10 @@
       <c r="A66" t="s">
         <v>57</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="3">
         <v>10</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="3">
         <v>33.64</v>
       </c>
     </row>
@@ -2331,10 +2341,10 @@
       <c r="A67" t="s">
         <v>58</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="3">
         <v>20</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="3">
         <v>298.12</v>
       </c>
     </row>
@@ -2342,10 +2352,10 @@
       <c r="A68" t="s">
         <v>59</v>
       </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68">
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3">
         <v>1982.77</v>
       </c>
     </row>
@@ -2353,10 +2363,10 @@
       <c r="A69" t="s">
         <v>60</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="3">
         <v>20</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="3">
         <v>280.12</v>
       </c>
     </row>
@@ -2364,10 +2374,10 @@
       <c r="A70" t="s">
         <v>61</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="3">
         <v>88</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="3">
         <v>24.51</v>
       </c>
     </row>
@@ -2375,10 +2385,10 @@
       <c r="A71" t="s">
         <v>62</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="3">
         <v>24</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="3">
         <v>26.08</v>
       </c>
     </row>
@@ -2386,10 +2396,10 @@
       <c r="A72" t="s">
         <v>62</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="3">
         <v>36</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="3">
         <v>26.21</v>
       </c>
     </row>
@@ -2397,10 +2407,10 @@
       <c r="A73" t="s">
         <v>63</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="3">
         <v>12</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="3">
         <v>87.56</v>
       </c>
     </row>
@@ -2408,10 +2418,10 @@
       <c r="A74" t="s">
         <v>63</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="3">
         <v>24</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="3">
         <v>101.08</v>
       </c>
     </row>
@@ -2419,10 +2429,10 @@
       <c r="A75" t="s">
         <v>64</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="3">
         <v>60</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="3">
         <v>29.13</v>
       </c>
     </row>
@@ -2430,10 +2440,10 @@
       <c r="A76" t="s">
         <v>65</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="3">
         <v>23</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="3">
         <v>102.31</v>
       </c>
     </row>
@@ -2441,10 +2451,10 @@
       <c r="A77" t="s">
         <v>66</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="3">
         <v>3</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="3">
         <v>126.7</v>
       </c>
     </row>
@@ -2452,10 +2462,10 @@
       <c r="A78" t="s">
         <v>66</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="3">
         <v>4</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="3">
         <v>168.07</v>
       </c>
     </row>
@@ -2463,21 +2473,21 @@
       <c r="A79" t="s">
         <v>67</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="3">
         <v>451</v>
       </c>
-      <c r="C79">
-        <v>16.6</v>
+      <c r="C79" s="3">
+        <v>16.600000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>68</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="3">
         <v>4</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="3">
         <v>60.08</v>
       </c>
     </row>
@@ -2485,10 +2495,10 @@
       <c r="A81" t="s">
         <v>68</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="3">
         <v>70</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="3">
         <v>60.95</v>
       </c>
     </row>
@@ -2496,21 +2506,21 @@
       <c r="A82" t="s">
         <v>69</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="3">
         <v>73</v>
       </c>
-      <c r="C82">
-        <v>76.56999999999999</v>
+      <c r="C82" s="3">
+        <v>76.569999999999993</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>70</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="3">
         <v>59</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="3">
         <v>16.79</v>
       </c>
     </row>
@@ -2518,10 +2528,10 @@
       <c r="A84" t="s">
         <v>70</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="3">
         <v>120</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="3">
         <v>18.96</v>
       </c>
     </row>
@@ -2529,21 +2539,21 @@
       <c r="A85" t="s">
         <v>71</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="3">
         <v>27</v>
       </c>
-      <c r="C85">
-        <v>64.43000000000001</v>
+      <c r="C85" s="3">
+        <v>64.430000000000007</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>71</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="3">
         <v>8</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="3">
         <v>73.13</v>
       </c>
     </row>
@@ -2551,10 +2561,10 @@
       <c r="A87" t="s">
         <v>72</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="3">
         <v>22</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="3">
         <v>79.5</v>
       </c>
     </row>
@@ -2562,10 +2572,10 @@
       <c r="A88" t="s">
         <v>72</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="3">
         <v>60</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="3">
         <v>89.38</v>
       </c>
     </row>
@@ -2573,10 +2583,10 @@
       <c r="A89" t="s">
         <v>73</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="3">
         <v>50</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="3">
         <v>16.98</v>
       </c>
     </row>
@@ -2584,10 +2594,10 @@
       <c r="A90" t="s">
         <v>73</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="3">
         <v>38</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="3">
         <v>18.96</v>
       </c>
     </row>
@@ -2595,21 +2605,21 @@
       <c r="A91" t="s">
         <v>74</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="3">
         <v>19</v>
       </c>
-      <c r="C91">
-        <v>65.59999999999999</v>
+      <c r="C91" s="3">
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>74</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="3">
         <v>40</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="3">
         <v>73.13</v>
       </c>
     </row>
@@ -2617,10 +2627,10 @@
       <c r="A93" t="s">
         <v>75</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="3">
         <v>23</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="3">
         <v>89.39</v>
       </c>
     </row>
@@ -2628,10 +2638,10 @@
       <c r="A94" t="s">
         <v>76</v>
       </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94">
+      <c r="B94" s="3">
+        <v>1</v>
+      </c>
+      <c r="C94" s="3">
         <v>3173.52</v>
       </c>
     </row>
@@ -2639,10 +2649,10 @@
       <c r="A95" t="s">
         <v>77</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="3">
         <v>2</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="3">
         <v>190.08</v>
       </c>
     </row>
@@ -2650,10 +2660,10 @@
       <c r="A96" t="s">
         <v>78</v>
       </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96">
+      <c r="B96" s="3">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3">
         <v>66.12</v>
       </c>
     </row>
@@ -2661,10 +2671,10 @@
       <c r="A97" t="s">
         <v>79</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="3">
         <v>21</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="3">
         <v>25.4</v>
       </c>
     </row>
@@ -2672,10 +2682,10 @@
       <c r="A98" t="s">
         <v>80</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="3">
         <v>15</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="3">
         <v>40.92</v>
       </c>
     </row>
@@ -2683,10 +2693,10 @@
       <c r="A99" t="s">
         <v>81</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="3">
         <v>9</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="3">
         <v>25.4</v>
       </c>
     </row>
@@ -2694,10 +2704,10 @@
       <c r="A100" t="s">
         <v>82</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="3">
         <v>15</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="3">
         <v>28.07</v>
       </c>
     </row>
@@ -2705,10 +2715,10 @@
       <c r="A101" t="s">
         <v>83</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="3">
         <v>4</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="3">
         <v>23.33</v>
       </c>
     </row>
@@ -2716,10 +2726,10 @@
       <c r="A102" t="s">
         <v>84</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="3">
         <v>24</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2727,10 +2737,10 @@
       <c r="A103" t="s">
         <v>85</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="3">
         <v>32</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="3">
         <v>27.95</v>
       </c>
     </row>
@@ -2738,32 +2748,32 @@
       <c r="A104" t="s">
         <v>85</v>
       </c>
-      <c r="B104">
-        <v>1</v>
-      </c>
-      <c r="C104">
-        <v>34.63</v>
+      <c r="B104" s="3">
+        <v>1</v>
+      </c>
+      <c r="C104" s="3">
+        <v>34.630000000000003</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>86</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="3">
         <v>47</v>
       </c>
-      <c r="C105">
-        <v>16.56</v>
+      <c r="C105" s="3">
+        <v>16.559999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>87</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="3">
         <v>30</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="3">
         <v>82.88</v>
       </c>
     </row>
@@ -2771,10 +2781,10 @@
       <c r="A107" t="s">
         <v>88</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="3">
         <v>5</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="3">
         <v>161.01</v>
       </c>
     </row>
@@ -2782,10 +2792,10 @@
       <c r="A108" t="s">
         <v>89</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="3">
         <v>2</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="3">
         <v>44.85</v>
       </c>
     </row>
@@ -2793,10 +2803,10 @@
       <c r="A109" t="s">
         <v>90</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="3">
         <v>9</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="3">
         <v>65.83</v>
       </c>
     </row>
@@ -2804,10 +2814,10 @@
       <c r="A110" t="s">
         <v>91</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="3">
         <v>3</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="3">
         <v>46.76</v>
       </c>
     </row>
@@ -2815,10 +2825,10 @@
       <c r="A111" t="s">
         <v>92</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="3">
         <v>19</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -2826,10 +2836,10 @@
       <c r="A112" t="s">
         <v>93</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="3">
         <v>10</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="3">
         <v>47.61</v>
       </c>
     </row>
@@ -2837,10 +2847,10 @@
       <c r="A113" t="s">
         <v>94</v>
       </c>
-      <c r="B113">
-        <v>1</v>
-      </c>
-      <c r="C113">
+      <c r="B113" s="3">
+        <v>1</v>
+      </c>
+      <c r="C113" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -2848,10 +2858,10 @@
       <c r="A114" t="s">
         <v>95</v>
       </c>
-      <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114">
+      <c r="B114" s="3">
+        <v>1</v>
+      </c>
+      <c r="C114" s="3">
         <v>1159.2</v>
       </c>
     </row>
@@ -2859,10 +2869,10 @@
       <c r="A115" t="s">
         <v>96</v>
       </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
-      <c r="C115">
+      <c r="B115" s="3">
+        <v>1</v>
+      </c>
+      <c r="C115" s="3">
         <v>255</v>
       </c>
     </row>
@@ -2870,10 +2880,10 @@
       <c r="A116" t="s">
         <v>97</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="3">
         <v>5</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="3">
         <v>62.1</v>
       </c>
     </row>
@@ -2881,10 +2891,10 @@
       <c r="A117" t="s">
         <v>97</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="3">
         <v>24</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="3">
         <v>69.55</v>
       </c>
     </row>
@@ -2892,10 +2902,10 @@
       <c r="A118" t="s">
         <v>98</v>
       </c>
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118">
+      <c r="B118" s="3">
+        <v>1</v>
+      </c>
+      <c r="C118" s="3">
         <v>1391.04</v>
       </c>
     </row>
@@ -2903,21 +2913,21 @@
       <c r="A119" t="s">
         <v>99</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="3">
         <v>11</v>
       </c>
-      <c r="C119">
-        <v>87.09999999999999</v>
+      <c r="C119" s="3">
+        <v>87.1</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>100</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="3">
         <v>24</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="3">
         <v>40.54</v>
       </c>
     </row>
@@ -2925,10 +2935,10 @@
       <c r="A121" t="s">
         <v>101</v>
       </c>
-      <c r="B121">
-        <v>1</v>
-      </c>
-      <c r="C121">
+      <c r="B121" s="3">
+        <v>1</v>
+      </c>
+      <c r="C121" s="3">
         <v>460.01</v>
       </c>
     </row>
@@ -2936,10 +2946,10 @@
       <c r="A122" t="s">
         <v>101</v>
       </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122">
+      <c r="B122" s="3">
+        <v>1</v>
+      </c>
+      <c r="C122" s="3">
         <v>639.4</v>
       </c>
     </row>
@@ -2947,10 +2957,10 @@
       <c r="A123" t="s">
         <v>102</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="3">
         <v>7</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="3">
         <v>103.89</v>
       </c>
     </row>
@@ -2958,10 +2968,10 @@
       <c r="A124" t="s">
         <v>103</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="3">
         <v>5</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="3">
         <v>43.99</v>
       </c>
     </row>
@@ -2969,10 +2979,10 @@
       <c r="A125" t="s">
         <v>104</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="3">
         <v>27</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -2980,10 +2990,10 @@
       <c r="A126" t="s">
         <v>104</v>
       </c>
-      <c r="B126">
-        <v>1</v>
-      </c>
-      <c r="C126">
+      <c r="B126" s="3">
+        <v>1</v>
+      </c>
+      <c r="C126" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -2991,10 +3001,10 @@
       <c r="A127" t="s">
         <v>105</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="3">
         <v>3</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="3">
         <v>61.92</v>
       </c>
     </row>
@@ -3002,10 +3012,10 @@
       <c r="A128" t="s">
         <v>106</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="3">
         <v>15</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3013,10 +3023,10 @@
       <c r="A129" t="s">
         <v>107</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="3">
         <v>30</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="3">
         <v>69.56</v>
       </c>
     </row>
@@ -3024,10 +3034,10 @@
       <c r="A130" t="s">
         <v>108</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="3">
         <v>4</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="3">
         <v>59.68</v>
       </c>
     </row>
@@ -3035,10 +3045,10 @@
       <c r="A131" t="s">
         <v>109</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="3">
         <v>32</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3046,10 +3056,10 @@
       <c r="A132" t="s">
         <v>110</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="3">
         <v>5</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3057,10 +3067,10 @@
       <c r="A133" t="s">
         <v>110</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="3">
         <v>4</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="3">
         <v>70.38</v>
       </c>
     </row>
@@ -3068,10 +3078,10 @@
       <c r="A134" t="s">
         <v>111</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="3">
         <v>23</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="3">
         <v>98.95</v>
       </c>
     </row>
@@ -3079,10 +3089,10 @@
       <c r="A135" t="s">
         <v>112</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="3">
         <v>14</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="3">
         <v>92.91</v>
       </c>
     </row>
@@ -3090,10 +3100,10 @@
       <c r="A136" t="s">
         <v>112</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="3">
         <v>3</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="3">
         <v>93.25</v>
       </c>
     </row>
@@ -3101,10 +3111,10 @@
       <c r="A137" t="s">
         <v>113</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="3">
         <v>12</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3112,10 +3122,10 @@
       <c r="A138" t="s">
         <v>113</v>
       </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138">
+      <c r="B138" s="3">
+        <v>1</v>
+      </c>
+      <c r="C138" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3123,10 +3133,10 @@
       <c r="A139" t="s">
         <v>114</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="3">
         <v>17</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -3134,10 +3144,10 @@
       <c r="A140" t="s">
         <v>114</v>
       </c>
-      <c r="B140">
-        <v>1</v>
-      </c>
-      <c r="C140">
+      <c r="B140" s="3">
+        <v>1</v>
+      </c>
+      <c r="C140" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3145,21 +3155,21 @@
       <c r="A141" t="s">
         <v>115</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="3">
         <v>14</v>
       </c>
-      <c r="C141">
-        <v>81.15000000000001</v>
+      <c r="C141" s="3">
+        <v>81.150000000000006</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>116</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="3">
         <v>27</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3167,10 +3177,10 @@
       <c r="A143" t="s">
         <v>117</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="3">
         <v>19</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="3">
         <v>69.87</v>
       </c>
     </row>
@@ -3178,10 +3188,10 @@
       <c r="A144" t="s">
         <v>118</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="3">
         <v>14</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="3">
         <v>63.76</v>
       </c>
     </row>
@@ -3189,10 +3199,10 @@
       <c r="A145" t="s">
         <v>119</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="3">
         <v>30</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="3">
         <v>69.56</v>
       </c>
     </row>
@@ -3200,10 +3210,10 @@
       <c r="A146" t="s">
         <v>120</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="3">
         <v>6</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="3">
         <v>69.56</v>
       </c>
     </row>
@@ -3211,10 +3221,10 @@
       <c r="A147" t="s">
         <v>121</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="3">
         <v>50</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="3">
         <v>52.17</v>
       </c>
     </row>
@@ -3222,10 +3232,10 @@
       <c r="A148" t="s">
         <v>121</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="3">
         <v>2</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="3">
         <v>52.17</v>
       </c>
     </row>
@@ -3233,10 +3243,10 @@
       <c r="A149" t="s">
         <v>122</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="3">
         <v>9</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="3">
         <v>208.66</v>
       </c>
     </row>
@@ -3244,21 +3254,21 @@
       <c r="A150" t="s">
         <v>123</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="3">
         <v>7</v>
       </c>
-      <c r="C150">
-        <v>79.34999999999999</v>
+      <c r="C150" s="3">
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>123</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="3">
         <v>24</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="3">
         <v>88.87</v>
       </c>
     </row>
@@ -3266,10 +3276,10 @@
       <c r="A152" t="s">
         <v>124</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="3">
         <v>72</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="3">
         <v>67.28</v>
       </c>
     </row>
@@ -3277,10 +3287,10 @@
       <c r="A153" t="s">
         <v>125</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="3">
         <v>8</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="3">
         <v>62.11</v>
       </c>
     </row>
@@ -3288,10 +3298,10 @@
       <c r="A154" t="s">
         <v>125</v>
       </c>
-      <c r="B154">
-        <v>1</v>
-      </c>
-      <c r="C154">
+      <c r="B154" s="3">
+        <v>1</v>
+      </c>
+      <c r="C154" s="3">
         <v>69.55</v>
       </c>
     </row>
@@ -3299,10 +3309,10 @@
       <c r="A155" t="s">
         <v>126</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="3">
         <v>10</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="3">
         <v>63.89</v>
       </c>
     </row>
@@ -3310,10 +3320,10 @@
       <c r="A156" t="s">
         <v>127</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="3">
         <v>5</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="3">
         <v>95.05</v>
       </c>
     </row>
@@ -3321,10 +3331,10 @@
       <c r="A157" t="s">
         <v>128</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="3">
         <v>5</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="3">
         <v>38.57</v>
       </c>
     </row>
@@ -3332,10 +3342,10 @@
       <c r="A158" t="s">
         <v>129</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="3">
         <v>7</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="3">
         <v>207.31</v>
       </c>
     </row>
@@ -3343,10 +3353,10 @@
       <c r="A159" t="s">
         <v>130</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="3">
         <v>24</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="3">
         <v>58.24</v>
       </c>
     </row>
@@ -3354,10 +3364,10 @@
       <c r="A160" t="s">
         <v>130</v>
       </c>
-      <c r="B160">
-        <v>1</v>
-      </c>
-      <c r="C160">
+      <c r="B160" s="3">
+        <v>1</v>
+      </c>
+      <c r="C160" s="3">
         <v>65.23</v>
       </c>
     </row>
@@ -3365,10 +3375,10 @@
       <c r="A161" t="s">
         <v>131</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="3">
         <v>11</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="3">
         <v>325.87</v>
       </c>
     </row>
@@ -3376,10 +3386,10 @@
       <c r="A162" t="s">
         <v>132</v>
       </c>
-      <c r="B162">
-        <v>1</v>
-      </c>
-      <c r="C162">
+      <c r="B162" s="3">
+        <v>1</v>
+      </c>
+      <c r="C162" s="3">
         <v>5165.8</v>
       </c>
     </row>
@@ -3387,10 +3397,10 @@
       <c r="A163" t="s">
         <v>133</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="3">
         <v>3</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="3">
         <v>511.75</v>
       </c>
     </row>
@@ -3398,21 +3408,21 @@
       <c r="A164" t="s">
         <v>134</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="3">
         <v>4</v>
       </c>
-      <c r="C164">
-        <v>572.7</v>
+      <c r="C164" s="3">
+        <v>572.70000000000005</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
         <v>135</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="3">
         <v>30</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="3">
         <v>66.98</v>
       </c>
     </row>
@@ -3420,10 +3430,10 @@
       <c r="A166" t="s">
         <v>136</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="3">
         <v>4</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="3">
         <v>367.42</v>
       </c>
     </row>
@@ -3431,10 +3441,10 @@
       <c r="A167" t="s">
         <v>137</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="3">
         <v>12</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="3">
         <v>51.52</v>
       </c>
     </row>
@@ -3442,18 +3452,21 @@
       <c r="A168" t="s">
         <v>138</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="3">
         <v>2</v>
+      </c>
+      <c r="C168" s="3">
+        <v>23.19</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
         <v>139</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="3">
         <v>21</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="3">
         <v>23.19</v>
       </c>
     </row>
@@ -3461,10 +3474,10 @@
       <c r="A170" t="s">
         <v>139</v>
       </c>
-      <c r="B170">
-        <v>1</v>
-      </c>
-      <c r="C170">
+      <c r="B170" s="3">
+        <v>1</v>
+      </c>
+      <c r="C170" s="3">
         <v>23.19</v>
       </c>
     </row>
@@ -3472,10 +3485,10 @@
       <c r="A171" t="s">
         <v>140</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="3">
         <v>28</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="3">
         <v>69.55</v>
       </c>
     </row>
@@ -3483,10 +3496,10 @@
       <c r="A172" t="s">
         <v>141</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="3">
         <v>2</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="3">
         <v>3169.7</v>
       </c>
     </row>
@@ -3494,10 +3507,10 @@
       <c r="A173" t="s">
         <v>142</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="3">
         <v>12</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="3">
         <v>81.14</v>
       </c>
     </row>
@@ -3505,10 +3518,10 @@
       <c r="A174" t="s">
         <v>143</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="3">
         <v>19</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="3">
         <v>81.14</v>
       </c>
     </row>
@@ -3516,10 +3529,10 @@
       <c r="A175" t="s">
         <v>144</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="3">
         <v>60</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="3">
         <v>66.98</v>
       </c>
     </row>
@@ -3527,10 +3540,10 @@
       <c r="A176" t="s">
         <v>145</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="3">
         <v>3</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="3">
         <v>53.83</v>
       </c>
     </row>
@@ -3538,10 +3551,10 @@
       <c r="A177" t="s">
         <v>145</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="3">
         <v>3</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="3">
         <v>60.28</v>
       </c>
     </row>
@@ -3549,10 +3562,10 @@
       <c r="A178" t="s">
         <v>145</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="3">
         <v>40</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="3">
         <v>60.29</v>
       </c>
     </row>
@@ -3560,43 +3573,43 @@
       <c r="A179" t="s">
         <v>146</v>
       </c>
-      <c r="B179">
+      <c r="B179" s="3">
         <v>8</v>
       </c>
-      <c r="C179">
-        <v>82.65000000000001</v>
+      <c r="C179" s="3">
+        <v>82.65</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
         <v>146</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="3">
         <v>24</v>
       </c>
-      <c r="C180">
-        <v>93.34999999999999</v>
+      <c r="C180" s="3">
+        <v>93.35</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
         <v>147</v>
       </c>
-      <c r="B181">
-        <v>1</v>
-      </c>
-      <c r="C181">
-        <v>1217.16</v>
+      <c r="B181" s="3">
+        <v>1</v>
+      </c>
+      <c r="C181" s="3">
+        <v>1217.1600000000001</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
         <v>148</v>
       </c>
-      <c r="B182">
-        <v>1</v>
-      </c>
-      <c r="C182">
+      <c r="B182" s="3">
+        <v>1</v>
+      </c>
+      <c r="C182" s="3">
         <v>3079</v>
       </c>
     </row>
@@ -3604,10 +3617,10 @@
       <c r="A183" t="s">
         <v>149</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="3">
         <v>9</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="3">
         <v>43.7</v>
       </c>
     </row>
@@ -3615,10 +3628,10 @@
       <c r="A184" t="s">
         <v>149</v>
       </c>
-      <c r="B184">
-        <v>1</v>
-      </c>
-      <c r="C184">
+      <c r="B184" s="3">
+        <v>1</v>
+      </c>
+      <c r="C184" s="3">
         <v>48.95</v>
       </c>
     </row>
@@ -3626,10 +3639,10 @@
       <c r="A185" t="s">
         <v>150</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="3">
         <v>8</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="3">
         <v>64.59</v>
       </c>
     </row>
@@ -3637,10 +3650,10 @@
       <c r="A186" t="s">
         <v>150</v>
       </c>
-      <c r="B186">
-        <v>1</v>
-      </c>
-      <c r="C186">
+      <c r="B186" s="3">
+        <v>1</v>
+      </c>
+      <c r="C186" s="3">
         <v>72.33</v>
       </c>
     </row>
@@ -3648,10 +3661,10 @@
       <c r="A187" t="s">
         <v>151</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="3">
         <v>7</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="3">
         <v>284.19</v>
       </c>
     </row>
@@ -3659,43 +3672,43 @@
       <c r="A188" t="s">
         <v>152</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="3">
         <v>10</v>
       </c>
-      <c r="C188">
-        <v>75.26000000000001</v>
+      <c r="C188" s="3">
+        <v>75.260000000000005</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
         <v>153</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="3">
         <v>62</v>
       </c>
-      <c r="C189">
-        <v>32.2</v>
+      <c r="C189" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
         <v>154</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="3">
         <v>5</v>
       </c>
-      <c r="C190">
-        <v>32.2</v>
+      <c r="C190" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
         <v>155</v>
       </c>
-      <c r="B191">
-        <v>1</v>
-      </c>
-      <c r="C191">
+      <c r="B191" s="3">
+        <v>1</v>
+      </c>
+      <c r="C191" s="3">
         <v>37.43</v>
       </c>
     </row>
@@ -3703,21 +3716,21 @@
       <c r="A192" t="s">
         <v>156</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="3">
         <v>46</v>
       </c>
-      <c r="C192">
-        <v>32.2</v>
+      <c r="C192" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
         <v>157</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="3">
         <v>9</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="3">
         <v>115.01</v>
       </c>
     </row>
@@ -3725,10 +3738,10 @@
       <c r="A194" t="s">
         <v>158</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="3">
         <v>16</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="3">
         <v>38.39</v>
       </c>
     </row>
@@ -3736,10 +3749,10 @@
       <c r="A195" t="s">
         <v>158</v>
       </c>
-      <c r="B195">
-        <v>1</v>
-      </c>
-      <c r="C195">
+      <c r="B195" s="3">
+        <v>1</v>
+      </c>
+      <c r="C195" s="3">
         <v>38.39</v>
       </c>
     </row>
@@ -3747,21 +3760,21 @@
       <c r="A196" t="s">
         <v>159</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="3">
         <v>3</v>
       </c>
-      <c r="C196">
-        <v>151.48</v>
+      <c r="C196" s="3">
+        <v>151.47999999999999</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
         <v>160</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="3">
         <v>12</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="3">
         <v>181.68</v>
       </c>
     </row>
@@ -3769,21 +3782,21 @@
       <c r="A198" t="s">
         <v>161</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="3">
         <v>12</v>
       </c>
-      <c r="C198">
-        <v>20.06</v>
+      <c r="C198" s="3">
+        <v>20.059999999999999</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
         <v>162</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="3">
         <v>9</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="3">
         <v>12.88</v>
       </c>
     </row>
@@ -3791,10 +3804,10 @@
       <c r="A200" t="s">
         <v>163</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="3">
         <v>14</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="3">
         <v>26.73</v>
       </c>
     </row>
@@ -3802,10 +3815,10 @@
       <c r="A201" t="s">
         <v>164</v>
       </c>
-      <c r="B201">
+      <c r="B201" s="3">
         <v>12</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="3">
         <v>29.95</v>
       </c>
     </row>
@@ -3813,10 +3826,10 @@
       <c r="A202" t="s">
         <v>165</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="3">
         <v>10</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="3">
         <v>58.68</v>
       </c>
     </row>
@@ -3824,10 +3837,10 @@
       <c r="A203" t="s">
         <v>166</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="3">
         <v>3</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="3">
         <v>79.98</v>
       </c>
     </row>
@@ -3835,32 +3848,32 @@
       <c r="A204" t="s">
         <v>167</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="3">
         <v>31</v>
       </c>
-      <c r="C204">
-        <v>34.62</v>
+      <c r="C204" s="3">
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
         <v>167</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="3">
         <v>12</v>
       </c>
-      <c r="C205">
-        <v>38.77</v>
+      <c r="C205" s="3">
+        <v>38.770000000000003</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
         <v>168</v>
       </c>
-      <c r="B206">
+      <c r="B206" s="3">
         <v>12</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="3">
         <v>107.35</v>
       </c>
     </row>
@@ -3868,10 +3881,10 @@
       <c r="A207" t="s">
         <v>169</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="3">
         <v>19</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="3">
         <v>55.2</v>
       </c>
     </row>
@@ -3879,10 +3892,10 @@
       <c r="A208" t="s">
         <v>169</v>
       </c>
-      <c r="B208">
-        <v>1</v>
-      </c>
-      <c r="C208">
+      <c r="B208" s="3">
+        <v>1</v>
+      </c>
+      <c r="C208" s="3">
         <v>61.83</v>
       </c>
     </row>
@@ -3890,10 +3903,10 @@
       <c r="A209" t="s">
         <v>170</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="3">
         <v>19</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="3">
         <v>243.16</v>
       </c>
     </row>
@@ -3901,21 +3914,21 @@
       <c r="A210" t="s">
         <v>171</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="3">
         <v>60</v>
       </c>
-      <c r="C210">
-        <v>32.2</v>
+      <c r="C210" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
         <v>172</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="3">
         <v>35</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="3">
         <v>63.78</v>
       </c>
     </row>
@@ -3923,43 +3936,43 @@
       <c r="A212" t="s">
         <v>173</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="3">
         <v>16</v>
       </c>
-      <c r="C212">
-        <v>67.84999999999999</v>
+      <c r="C212" s="3">
+        <v>67.849999999999994</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
         <v>173</v>
       </c>
-      <c r="B213">
-        <v>1</v>
-      </c>
-      <c r="C213">
-        <v>75.98999999999999</v>
+      <c r="B213" s="3">
+        <v>1</v>
+      </c>
+      <c r="C213" s="3">
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
         <v>174</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="3">
         <v>3</v>
       </c>
-      <c r="C214">
-        <v>297.65</v>
+      <c r="C214" s="3">
+        <v>297.64999999999998</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
         <v>175</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="3">
         <v>14</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="3">
         <v>77.28</v>
       </c>
     </row>
@@ -3967,21 +3980,21 @@
       <c r="A216" t="s">
         <v>176</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="3">
         <v>15</v>
       </c>
-      <c r="C216">
-        <v>75.98999999999999</v>
+      <c r="C216" s="3">
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
         <v>177</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="3">
         <v>7</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="3">
         <v>342.24</v>
       </c>
     </row>
@@ -3989,10 +4002,10 @@
       <c r="A218" t="s">
         <v>178</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="3">
         <v>2</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="3">
         <v>633.75</v>
       </c>
     </row>
@@ -4000,21 +4013,21 @@
       <c r="A219" t="s">
         <v>179</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="3">
         <v>55</v>
       </c>
-      <c r="C219">
-        <v>36.8</v>
+      <c r="C219" s="3">
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
         <v>179</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="3">
         <v>23</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="3">
         <v>50.51</v>
       </c>
     </row>
@@ -4022,10 +4035,10 @@
       <c r="A221" t="s">
         <v>180</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="3">
         <v>2</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="3">
         <v>768.2</v>
       </c>
     </row>
@@ -4033,10 +4046,10 @@
       <c r="A222" t="s">
         <v>181</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="3">
         <v>2</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="3">
         <v>787.75</v>
       </c>
     </row>
@@ -4044,10 +4057,10 @@
       <c r="A223" t="s">
         <v>182</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="3">
         <v>11</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="3">
         <v>109.26</v>
       </c>
     </row>
@@ -4055,10 +4068,10 @@
       <c r="A224" t="s">
         <v>182</v>
       </c>
-      <c r="B224">
-        <v>1</v>
-      </c>
-      <c r="C224">
+      <c r="B224" s="3">
+        <v>1</v>
+      </c>
+      <c r="C224" s="3">
         <v>122.36</v>
       </c>
     </row>
@@ -4066,10 +4079,10 @@
       <c r="A225" t="s">
         <v>183</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="3">
         <v>2</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="3">
         <v>31.98</v>
       </c>
     </row>
@@ -4077,10 +4090,10 @@
       <c r="A226" t="s">
         <v>183</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="3">
         <v>25</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="3">
         <v>35.81</v>
       </c>
     </row>
@@ -4088,10 +4101,10 @@
       <c r="A227" t="s">
         <v>184</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="3">
         <v>33</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="3">
         <v>59.25</v>
       </c>
     </row>
@@ -4099,10 +4112,10 @@
       <c r="A228" t="s">
         <v>185</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="3">
         <v>12</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="3">
         <v>260</v>
       </c>
     </row>
@@ -4110,10 +4123,10 @@
       <c r="A229" t="s">
         <v>186</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="3">
         <v>8</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="3">
         <v>43.07</v>
       </c>
     </row>
@@ -4121,10 +4134,10 @@
       <c r="A230" t="s">
         <v>187</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="3">
         <v>12</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="3">
         <v>48.23</v>
       </c>
     </row>
@@ -4132,10 +4145,10 @@
       <c r="A231" t="s">
         <v>188</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="3">
         <v>6</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="3">
         <v>221.86</v>
       </c>
     </row>
@@ -4143,10 +4156,10 @@
       <c r="A232" t="s">
         <v>189</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="3">
         <v>4</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="3">
         <v>74.7</v>
       </c>
     </row>
@@ -4154,10 +4167,10 @@
       <c r="A233" t="s">
         <v>190</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="3">
         <v>20</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="3">
         <v>296.3</v>
       </c>
     </row>
@@ -4165,21 +4178,21 @@
       <c r="A234" t="s">
         <v>191</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="3">
         <v>15</v>
       </c>
-      <c r="C234">
-        <v>141.8</v>
+      <c r="C234" s="3">
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
         <v>192</v>
       </c>
-      <c r="B235">
-        <v>1</v>
-      </c>
-      <c r="C235">
+      <c r="B235" s="3">
+        <v>1</v>
+      </c>
+      <c r="C235" s="3">
         <v>29.25</v>
       </c>
     </row>
@@ -4187,10 +4200,10 @@
       <c r="A236" t="s">
         <v>192</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="3">
         <v>25</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="3">
         <v>41.4</v>
       </c>
     </row>
@@ -4198,21 +4211,21 @@
       <c r="A237" t="s">
         <v>193</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="3">
         <v>2</v>
       </c>
-      <c r="C237">
-        <v>141.8</v>
+      <c r="C237" s="3">
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
         <v>194</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="3">
         <v>16</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="3">
         <v>173.3</v>
       </c>
     </row>
@@ -4220,10 +4233,10 @@
       <c r="A239" t="s">
         <v>195</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="3">
         <v>3</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="3">
         <v>2189.02</v>
       </c>
     </row>
@@ -4231,10 +4244,10 @@
       <c r="A240" t="s">
         <v>196</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="3">
         <v>2</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="3">
         <v>453.22</v>
       </c>
     </row>
@@ -4242,10 +4255,10 @@
       <c r="A241" t="s">
         <v>197</v>
       </c>
-      <c r="B241">
-        <v>1</v>
-      </c>
-      <c r="C241">
+      <c r="B241" s="3">
+        <v>1</v>
+      </c>
+      <c r="C241" s="3">
         <v>31.3</v>
       </c>
     </row>
@@ -4253,10 +4266,10 @@
       <c r="A242" t="s">
         <v>198</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="3">
         <v>9</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="3">
         <v>126.63</v>
       </c>
     </row>
@@ -4264,10 +4277,10 @@
       <c r="A243" t="s">
         <v>199</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="3">
         <v>5</v>
       </c>
-      <c r="C243">
+      <c r="C243" s="3">
         <v>69.56</v>
       </c>
     </row>
@@ -4275,10 +4288,10 @@
       <c r="A244" t="s">
         <v>200</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="3">
         <v>11</v>
       </c>
-      <c r="C244">
+      <c r="C244" s="3">
         <v>42.44</v>
       </c>
     </row>
@@ -4286,10 +4299,10 @@
       <c r="A245" t="s">
         <v>201</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="3">
         <v>13</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="3">
         <v>42.43</v>
       </c>
     </row>
@@ -4297,10 +4310,10 @@
       <c r="A246" t="s">
         <v>202</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="3">
         <v>9</v>
       </c>
-      <c r="C246">
+      <c r="C246" s="3">
         <v>145.94</v>
       </c>
     </row>
@@ -4308,10 +4321,10 @@
       <c r="A247" t="s">
         <v>203</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="3">
         <v>36</v>
       </c>
-      <c r="C247">
+      <c r="C247" s="3">
         <v>179</v>
       </c>
     </row>
@@ -4319,21 +4332,21 @@
       <c r="A248" t="s">
         <v>204</v>
       </c>
-      <c r="B248">
-        <v>1</v>
-      </c>
-      <c r="C248">
-        <v>2060.8</v>
+      <c r="B248" s="3">
+        <v>1</v>
+      </c>
+      <c r="C248" s="3">
+        <v>2060.8000000000002</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
         <v>205</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="3">
         <v>8</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="3">
         <v>51</v>
       </c>
     </row>
@@ -4341,10 +4354,10 @@
       <c r="A250" t="s">
         <v>205</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="3">
         <v>11</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="3">
         <v>51</v>
       </c>
     </row>
@@ -4352,10 +4365,10 @@
       <c r="A251" t="s">
         <v>206</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="3">
         <v>11</v>
       </c>
-      <c r="C251">
+      <c r="C251" s="3">
         <v>183.41</v>
       </c>
     </row>
@@ -4363,10 +4376,10 @@
       <c r="A252" t="s">
         <v>207</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="3">
         <v>10</v>
       </c>
-      <c r="C252">
+      <c r="C252" s="3">
         <v>206.33</v>
       </c>
     </row>
@@ -4374,32 +4387,32 @@
       <c r="A253" t="s">
         <v>208</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="3">
         <v>12</v>
       </c>
-      <c r="C253">
-        <v>33.48</v>
+      <c r="C253" s="3">
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
         <v>208</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="3">
         <v>25</v>
       </c>
-      <c r="C254">
-        <v>33.48</v>
+      <c r="C254" s="3">
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
         <v>209</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="3">
         <v>36</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="3">
         <v>46.06</v>
       </c>
     </row>
@@ -4407,10 +4420,10 @@
       <c r="A256" t="s">
         <v>210</v>
       </c>
-      <c r="B256">
-        <v>1</v>
-      </c>
-      <c r="C256">
+      <c r="B256" s="3">
+        <v>1</v>
+      </c>
+      <c r="C256" s="3">
         <v>4667</v>
       </c>
     </row>
@@ -4418,10 +4431,10 @@
       <c r="A257" t="s">
         <v>210</v>
       </c>
-      <c r="B257">
-        <v>1</v>
-      </c>
-      <c r="C257">
+      <c r="B257" s="3">
+        <v>1</v>
+      </c>
+      <c r="C257" s="3">
         <v>5345.33</v>
       </c>
     </row>
@@ -4429,10 +4442,10 @@
       <c r="A258" t="s">
         <v>211</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="3">
         <v>17</v>
       </c>
-      <c r="C258">
+      <c r="C258" s="3">
         <v>170.78</v>
       </c>
     </row>
@@ -4440,10 +4453,10 @@
       <c r="A259" t="s">
         <v>212</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="3">
         <v>2</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="3">
         <v>162.13</v>
       </c>
     </row>
@@ -4451,10 +4464,10 @@
       <c r="A260" t="s">
         <v>212</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="3">
         <v>11</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="3">
         <v>192.51</v>
       </c>
     </row>
@@ -4462,10 +4475,10 @@
       <c r="A261" t="s">
         <v>213</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="3">
         <v>25</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="3">
         <v>59.7</v>
       </c>
     </row>
@@ -4473,10 +4486,10 @@
       <c r="A262" t="s">
         <v>214</v>
       </c>
-      <c r="B262">
-        <v>1</v>
-      </c>
-      <c r="C262">
+      <c r="B262" s="3">
+        <v>1</v>
+      </c>
+      <c r="C262" s="3">
         <v>265.05</v>
       </c>
     </row>
@@ -4484,21 +4497,21 @@
       <c r="A263" t="s">
         <v>215</v>
       </c>
-      <c r="B263">
+      <c r="B263" s="3">
         <v>25</v>
       </c>
-      <c r="C263">
-        <v>36.8</v>
+      <c r="C263" s="3">
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
         <v>216</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="3">
         <v>18</v>
       </c>
-      <c r="C264">
+      <c r="C264" s="3">
         <v>103.04</v>
       </c>
     </row>
@@ -4506,10 +4519,10 @@
       <c r="A265" t="s">
         <v>217</v>
       </c>
-      <c r="B265">
+      <c r="B265" s="3">
         <v>54</v>
       </c>
-      <c r="C265">
+      <c r="C265" s="3">
         <v>36.75</v>
       </c>
     </row>
@@ -4517,10 +4530,10 @@
       <c r="A266" t="s">
         <v>218</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="3">
         <v>11</v>
       </c>
-      <c r="C266">
+      <c r="C266" s="3">
         <v>47.16</v>
       </c>
     </row>
@@ -4528,21 +4541,21 @@
       <c r="A267" t="s">
         <v>219</v>
       </c>
-      <c r="B267">
+      <c r="B267" s="3">
         <v>27</v>
       </c>
-      <c r="C267">
-        <v>16.81</v>
+      <c r="C267" s="3">
+        <v>16.809999999999999</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
         <v>220</v>
       </c>
-      <c r="B268">
+      <c r="B268" s="3">
         <v>4</v>
       </c>
-      <c r="C268">
+      <c r="C268" s="3">
         <v>27.68</v>
       </c>
     </row>
@@ -4550,10 +4563,10 @@
       <c r="A269" t="s">
         <v>220</v>
       </c>
-      <c r="B269">
+      <c r="B269" s="3">
         <v>10</v>
       </c>
-      <c r="C269">
+      <c r="C269" s="3">
         <v>28.69</v>
       </c>
     </row>
@@ -4561,10 +4574,10 @@
       <c r="A270" t="s">
         <v>220</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="3">
         <v>28</v>
       </c>
-      <c r="C270">
+      <c r="C270" s="3">
         <v>37.31</v>
       </c>
     </row>
@@ -4572,21 +4585,21 @@
       <c r="A271" t="s">
         <v>221</v>
       </c>
-      <c r="B271">
-        <v>1</v>
-      </c>
-      <c r="C271">
-        <v>97.48999999999999</v>
+      <c r="B271" s="3">
+        <v>1</v>
+      </c>
+      <c r="C271" s="3">
+        <v>97.49</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
         <v>221</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="3">
         <v>5</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="3">
         <v>103.46</v>
       </c>
     </row>
@@ -4594,10 +4607,10 @@
       <c r="A273" t="s">
         <v>221</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="3">
         <v>20</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="3">
         <v>126.24</v>
       </c>
     </row>
@@ -4605,21 +4618,21 @@
       <c r="A274" t="s">
         <v>222</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="3">
         <v>3</v>
       </c>
-      <c r="C274">
-        <v>144.27</v>
+      <c r="C274" s="3">
+        <v>144.27000000000001</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
         <v>222</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="3">
         <v>16</v>
       </c>
-      <c r="C275">
+      <c r="C275" s="3">
         <v>154.62</v>
       </c>
     </row>
@@ -4627,10 +4640,10 @@
       <c r="A276" t="s">
         <v>223</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="3">
         <v>2</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="3">
         <v>508.2</v>
       </c>
     </row>
@@ -4638,10 +4651,10 @@
       <c r="A277" t="s">
         <v>224</v>
       </c>
-      <c r="B277">
-        <v>1</v>
-      </c>
-      <c r="C277">
+      <c r="B277" s="3">
+        <v>1</v>
+      </c>
+      <c r="C277" s="3">
         <v>5069</v>
       </c>
     </row>
@@ -4649,10 +4662,10 @@
       <c r="A278" t="s">
         <v>225</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="3">
         <v>2</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="3">
         <v>466.78</v>
       </c>
     </row>
@@ -4660,10 +4673,10 @@
       <c r="A279" t="s">
         <v>226</v>
       </c>
-      <c r="B279">
+      <c r="B279" s="3">
         <v>15</v>
       </c>
-      <c r="C279">
+      <c r="C279" s="3">
         <v>57.5</v>
       </c>
     </row>
@@ -4671,10 +4684,10 @@
       <c r="A280" t="s">
         <v>227</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="3">
         <v>8</v>
       </c>
-      <c r="C280">
+      <c r="C280" s="3">
         <v>63.13</v>
       </c>
     </row>
@@ -4682,10 +4695,10 @@
       <c r="A281" t="s">
         <v>228</v>
       </c>
-      <c r="B281">
-        <v>1</v>
-      </c>
-      <c r="C281">
+      <c r="B281" s="3">
+        <v>1</v>
+      </c>
+      <c r="C281" s="3">
         <v>20789.41</v>
       </c>
     </row>
@@ -4693,10 +4706,10 @@
       <c r="A282" t="s">
         <v>228</v>
       </c>
-      <c r="B282">
-        <v>1</v>
-      </c>
-      <c r="C282">
+      <c r="B282" s="3">
+        <v>1</v>
+      </c>
+      <c r="C282" s="3">
         <v>33057.85</v>
       </c>
     </row>
@@ -4704,10 +4717,10 @@
       <c r="A283" t="s">
         <v>229</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="3">
         <v>7</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="3">
         <v>83.5</v>
       </c>
     </row>
@@ -4715,10 +4728,10 @@
       <c r="A284" t="s">
         <v>230</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="3">
         <v>6</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="3">
         <v>45.88</v>
       </c>
     </row>
@@ -4726,10 +4739,10 @@
       <c r="A285" t="s">
         <v>231</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="3">
         <v>16</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="3">
         <v>50.71</v>
       </c>
     </row>
@@ -4737,10 +4750,10 @@
       <c r="A286" t="s">
         <v>231</v>
       </c>
-      <c r="B286">
-        <v>1</v>
-      </c>
-      <c r="C286">
+      <c r="B286" s="3">
+        <v>1</v>
+      </c>
+      <c r="C286" s="3">
         <v>50.71</v>
       </c>
     </row>
@@ -4748,10 +4761,10 @@
       <c r="A287" t="s">
         <v>232</v>
       </c>
-      <c r="B287">
+      <c r="B287" s="3">
         <v>10</v>
       </c>
-      <c r="C287">
+      <c r="C287" s="3">
         <v>51.75</v>
       </c>
     </row>
@@ -4759,10 +4772,10 @@
       <c r="A288" t="s">
         <v>233</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="3">
         <v>13</v>
       </c>
-      <c r="C288">
+      <c r="C288" s="3">
         <v>36.94</v>
       </c>
     </row>
@@ -4770,10 +4783,10 @@
       <c r="A289" t="s">
         <v>234</v>
       </c>
-      <c r="B289">
+      <c r="B289" s="3">
         <v>24</v>
       </c>
-      <c r="C289">
+      <c r="C289" s="3">
         <v>36.94</v>
       </c>
     </row>
@@ -4781,10 +4794,10 @@
       <c r="A290" t="s">
         <v>235</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="3">
         <v>45</v>
       </c>
-      <c r="C290">
+      <c r="C290" s="3">
         <v>67.28</v>
       </c>
     </row>
@@ -4792,21 +4805,21 @@
       <c r="A291" t="s">
         <v>236</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="3">
         <v>35</v>
       </c>
-      <c r="C291">
-        <v>65.09999999999999</v>
+      <c r="C291" s="3">
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
         <v>237</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="3">
         <v>5</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="3">
         <v>65.53</v>
       </c>
     </row>
@@ -4814,10 +4827,10 @@
       <c r="A293" t="s">
         <v>237</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="3">
         <v>42</v>
       </c>
-      <c r="C293">
+      <c r="C293" s="3">
         <v>65.53</v>
       </c>
     </row>
@@ -4825,21 +4838,21 @@
       <c r="A294" t="s">
         <v>238</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="3">
         <v>32</v>
       </c>
-      <c r="C294">
-        <v>90.90000000000001</v>
+      <c r="C294" s="3">
+        <v>90.9</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
         <v>239</v>
       </c>
-      <c r="B295">
-        <v>1</v>
-      </c>
-      <c r="C295">
+      <c r="B295" s="3">
+        <v>1</v>
+      </c>
+      <c r="C295" s="3">
         <v>29.89</v>
       </c>
     </row>
@@ -4847,21 +4860,21 @@
       <c r="A296" t="s">
         <v>239</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="3">
         <v>30</v>
       </c>
-      <c r="C296">
-        <v>33.48</v>
+      <c r="C296" s="3">
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
         <v>240</v>
       </c>
-      <c r="B297">
+      <c r="B297" s="3">
         <v>6</v>
       </c>
-      <c r="C297">
+      <c r="C297" s="3">
         <v>422.09</v>
       </c>
     </row>
@@ -4869,10 +4882,10 @@
       <c r="A298" t="s">
         <v>241</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="3">
         <v>2</v>
       </c>
-      <c r="C298">
+      <c r="C298" s="3">
         <v>1277.7</v>
       </c>
     </row>
@@ -4880,10 +4893,10 @@
       <c r="A299" t="s">
         <v>242</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="3">
         <v>20</v>
       </c>
-      <c r="C299">
+      <c r="C299" s="3">
         <v>6.44</v>
       </c>
     </row>
@@ -4891,10 +4904,10 @@
       <c r="A300" t="s">
         <v>243</v>
       </c>
-      <c r="B300">
+      <c r="B300" s="3">
         <v>9</v>
       </c>
-      <c r="C300">
+      <c r="C300" s="3">
         <v>108.2</v>
       </c>
     </row>
@@ -4902,21 +4915,21 @@
       <c r="A301" t="s">
         <v>244</v>
       </c>
-      <c r="B301">
-        <v>1</v>
-      </c>
-      <c r="C301">
-        <v>4456.48</v>
+      <c r="B301" s="3">
+        <v>1</v>
+      </c>
+      <c r="C301" s="3">
+        <v>4456.4799999999996</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
         <v>244</v>
       </c>
-      <c r="B302">
-        <v>1</v>
-      </c>
-      <c r="C302">
+      <c r="B302" s="3">
+        <v>1</v>
+      </c>
+      <c r="C302" s="3">
         <v>6279</v>
       </c>
     </row>
@@ -4924,10 +4937,10 @@
       <c r="A303" t="s">
         <v>245</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="3">
         <v>2</v>
       </c>
-      <c r="C303">
+      <c r="C303" s="3">
         <v>609.5</v>
       </c>
     </row>
@@ -4935,54 +4948,54 @@
       <c r="A304" t="s">
         <v>246</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="3">
         <v>22</v>
       </c>
-      <c r="C304">
-        <v>32.2</v>
+      <c r="C304" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
         <v>247</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="3">
         <v>13</v>
       </c>
-      <c r="C305">
-        <v>32.2</v>
+      <c r="C305" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
         <v>248</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="3">
         <v>42</v>
       </c>
-      <c r="C306">
-        <v>32.2</v>
+      <c r="C306" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
         <v>249</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="3">
         <v>9</v>
       </c>
-      <c r="C307">
-        <v>32.2</v>
+      <c r="C307" s="3">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
         <v>250</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="3">
         <v>7</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="3">
         <v>40.4</v>
       </c>
     </row>
@@ -4990,10 +5003,10 @@
       <c r="A309" t="s">
         <v>251</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="3">
         <v>78</v>
       </c>
-      <c r="C309">
+      <c r="C309" s="3">
         <v>36.06</v>
       </c>
     </row>
@@ -5001,10 +5014,10 @@
       <c r="A310" t="s">
         <v>252</v>
       </c>
-      <c r="B310">
+      <c r="B310" s="3">
         <v>85</v>
       </c>
-      <c r="C310">
+      <c r="C310" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5012,10 +5025,10 @@
       <c r="A311" t="s">
         <v>253</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="3">
         <v>13</v>
       </c>
-      <c r="C311">
+      <c r="C311" s="3">
         <v>44.5</v>
       </c>
     </row>
@@ -5023,10 +5036,10 @@
       <c r="A312" t="s">
         <v>253</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="3">
         <v>24</v>
       </c>
-      <c r="C312">
+      <c r="C312" s="3">
         <v>56.01</v>
       </c>
     </row>
@@ -5034,10 +5047,10 @@
       <c r="A313" t="s">
         <v>254</v>
       </c>
-      <c r="B313">
+      <c r="B313" s="3">
         <v>17</v>
       </c>
-      <c r="C313">
+      <c r="C313" s="3">
         <v>57.63</v>
       </c>
     </row>
@@ -5045,10 +5058,10 @@
       <c r="A314" t="s">
         <v>255</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="3">
         <v>4</v>
       </c>
-      <c r="C314">
+      <c r="C314" s="3">
         <v>60.78</v>
       </c>
     </row>
@@ -5056,10 +5069,10 @@
       <c r="A315" t="s">
         <v>256</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="3">
         <v>9</v>
       </c>
-      <c r="C315">
+      <c r="C315" s="3">
         <v>42.49</v>
       </c>
     </row>
@@ -5067,10 +5080,10 @@
       <c r="A316" t="s">
         <v>257</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="3">
         <v>2</v>
       </c>
-      <c r="C316">
+      <c r="C316" s="3">
         <v>46.28</v>
       </c>
     </row>
@@ -5078,10 +5091,10 @@
       <c r="A317" t="s">
         <v>258</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="3">
         <v>17</v>
       </c>
-      <c r="C317">
+      <c r="C317" s="3">
         <v>59.21</v>
       </c>
     </row>
@@ -5089,10 +5102,10 @@
       <c r="A318" t="s">
         <v>258</v>
       </c>
-      <c r="B318">
-        <v>1</v>
-      </c>
-      <c r="C318">
+      <c r="B318" s="3">
+        <v>1</v>
+      </c>
+      <c r="C318" s="3">
         <v>66.3</v>
       </c>
     </row>
@@ -5100,10 +5113,10 @@
       <c r="A319" t="s">
         <v>259</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="3">
         <v>6</v>
       </c>
-      <c r="C319">
+      <c r="C319" s="3">
         <v>261.8</v>
       </c>
     </row>
@@ -5111,32 +5124,32 @@
       <c r="A320" t="s">
         <v>260</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="3">
         <v>14</v>
       </c>
-      <c r="C320">
-        <v>71.70999999999999</v>
+      <c r="C320" s="3">
+        <v>71.709999999999994</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
         <v>261</v>
       </c>
-      <c r="B321">
-        <v>1</v>
-      </c>
-      <c r="C321">
-        <v>77.76000000000001</v>
+      <c r="B321" s="3">
+        <v>1</v>
+      </c>
+      <c r="C321" s="3">
+        <v>77.760000000000005</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
         <v>262</v>
       </c>
-      <c r="B322">
+      <c r="B322" s="3">
         <v>17</v>
       </c>
-      <c r="C322">
+      <c r="C322" s="3">
         <v>54.7</v>
       </c>
     </row>
@@ -5144,10 +5157,10 @@
       <c r="A323" t="s">
         <v>263</v>
       </c>
-      <c r="B323">
+      <c r="B323" s="3">
         <v>9</v>
       </c>
-      <c r="C323">
+      <c r="C323" s="3">
         <v>52.1</v>
       </c>
     </row>
@@ -5155,10 +5168,10 @@
       <c r="A324" t="s">
         <v>264</v>
       </c>
-      <c r="B324">
+      <c r="B324" s="3">
         <v>5</v>
       </c>
-      <c r="C324">
+      <c r="C324" s="3">
         <v>251.5</v>
       </c>
     </row>
@@ -5166,10 +5179,10 @@
       <c r="A325" t="s">
         <v>265</v>
       </c>
-      <c r="B325">
+      <c r="B325" s="3">
         <v>12</v>
       </c>
-      <c r="C325">
+      <c r="C325" s="3">
         <v>78.87</v>
       </c>
     </row>
@@ -5177,10 +5190,10 @@
       <c r="A326" t="s">
         <v>266</v>
       </c>
-      <c r="B326">
-        <v>1</v>
-      </c>
-      <c r="C326">
+      <c r="B326" s="3">
+        <v>1</v>
+      </c>
+      <c r="C326" s="3">
         <v>83.84</v>
       </c>
     </row>
@@ -5188,10 +5201,10 @@
       <c r="A327" t="s">
         <v>266</v>
       </c>
-      <c r="B327">
+      <c r="B327" s="3">
         <v>12</v>
       </c>
-      <c r="C327">
+      <c r="C327" s="3">
         <v>83.84</v>
       </c>
     </row>
@@ -5199,10 +5212,10 @@
       <c r="A328" t="s">
         <v>267</v>
       </c>
-      <c r="B328">
+      <c r="B328" s="3">
         <v>2</v>
       </c>
-      <c r="C328">
+      <c r="C328" s="3">
         <v>272.5</v>
       </c>
     </row>
@@ -5210,10 +5223,10 @@
       <c r="A329" t="s">
         <v>268</v>
       </c>
-      <c r="B329">
+      <c r="B329" s="3">
         <v>19</v>
       </c>
-      <c r="C329">
+      <c r="C329" s="3">
         <v>79.75</v>
       </c>
     </row>
@@ -5221,21 +5234,21 @@
       <c r="A330" t="s">
         <v>269</v>
       </c>
-      <c r="B330">
+      <c r="B330" s="3">
         <v>11</v>
       </c>
-      <c r="C330">
-        <v>65.20999999999999</v>
+      <c r="C330" s="3">
+        <v>65.209999999999994</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
         <v>269</v>
       </c>
-      <c r="B331">
+      <c r="B331" s="3">
         <v>12</v>
       </c>
-      <c r="C331">
+      <c r="C331" s="3">
         <v>83.84</v>
       </c>
     </row>
@@ -5243,10 +5256,10 @@
       <c r="A332" t="s">
         <v>270</v>
       </c>
-      <c r="B332">
+      <c r="B332" s="3">
         <v>7</v>
       </c>
-      <c r="C332">
+      <c r="C332" s="3">
         <v>284</v>
       </c>
     </row>
@@ -5254,10 +5267,10 @@
       <c r="A333" t="s">
         <v>271</v>
       </c>
-      <c r="B333">
+      <c r="B333" s="3">
         <v>12</v>
       </c>
-      <c r="C333">
+      <c r="C333" s="3">
         <v>28.15</v>
       </c>
     </row>
@@ -5265,10 +5278,10 @@
       <c r="A334" t="s">
         <v>272</v>
       </c>
-      <c r="B334">
+      <c r="B334" s="3">
         <v>2</v>
       </c>
-      <c r="C334">
+      <c r="C334" s="3">
         <v>45.08</v>
       </c>
     </row>
@@ -5276,10 +5289,10 @@
       <c r="A335" t="s">
         <v>273</v>
       </c>
-      <c r="B335">
+      <c r="B335" s="3">
         <v>9</v>
       </c>
-      <c r="C335">
+      <c r="C335" s="3">
         <v>51.52</v>
       </c>
     </row>
@@ -5287,10 +5300,10 @@
       <c r="A336" t="s">
         <v>274</v>
       </c>
-      <c r="B336">
+      <c r="B336" s="3">
         <v>5</v>
       </c>
-      <c r="C336">
+      <c r="C336" s="3">
         <v>40.57</v>
       </c>
     </row>
@@ -5298,21 +5311,21 @@
       <c r="A337" t="s">
         <v>275</v>
       </c>
-      <c r="B337">
+      <c r="B337" s="3">
         <v>39</v>
       </c>
-      <c r="C337">
-        <v>36.23</v>
+      <c r="C337" s="3">
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
         <v>276</v>
       </c>
-      <c r="B338">
+      <c r="B338" s="3">
         <v>24</v>
       </c>
-      <c r="C338">
+      <c r="C338" s="3">
         <v>54.12</v>
       </c>
     </row>
@@ -5320,10 +5333,10 @@
       <c r="A339" t="s">
         <v>277</v>
       </c>
-      <c r="B339">
+      <c r="B339" s="3">
         <v>12</v>
       </c>
-      <c r="C339">
+      <c r="C339" s="3">
         <v>69.55</v>
       </c>
     </row>
@@ -5331,21 +5344,21 @@
       <c r="A340" t="s">
         <v>278</v>
       </c>
-      <c r="B340">
+      <c r="B340" s="3">
         <v>10</v>
       </c>
-      <c r="C340">
-        <v>295.15</v>
+      <c r="C340" s="3">
+        <v>295.14999999999998</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
         <v>279</v>
       </c>
-      <c r="B341">
+      <c r="B341" s="3">
         <v>6</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="3">
         <v>38.56</v>
       </c>
     </row>
@@ -5353,10 +5366,10 @@
       <c r="A342" t="s">
         <v>280</v>
       </c>
-      <c r="B342">
+      <c r="B342" s="3">
         <v>7</v>
       </c>
-      <c r="C342">
+      <c r="C342" s="3">
         <v>60.95</v>
       </c>
     </row>
@@ -5364,21 +5377,21 @@
       <c r="A343" t="s">
         <v>281</v>
       </c>
-      <c r="B343">
+      <c r="B343" s="3">
         <v>10</v>
       </c>
-      <c r="C343">
-        <v>78.20999999999999</v>
+      <c r="C343" s="3">
+        <v>78.209999999999994</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
         <v>282</v>
       </c>
-      <c r="B344">
+      <c r="B344" s="3">
         <v>181</v>
       </c>
-      <c r="C344">
+      <c r="C344" s="3">
         <v>44.93</v>
       </c>
     </row>
@@ -5386,10 +5399,10 @@
       <c r="A345" t="s">
         <v>283</v>
       </c>
-      <c r="B345">
-        <v>1</v>
-      </c>
-      <c r="C345">
+      <c r="B345" s="3">
+        <v>1</v>
+      </c>
+      <c r="C345" s="3">
         <v>6578.46</v>
       </c>
     </row>
@@ -5397,10 +5410,10 @@
       <c r="A346" t="s">
         <v>284</v>
       </c>
-      <c r="B346">
+      <c r="B346" s="3">
         <v>35</v>
       </c>
-      <c r="C346">
+      <c r="C346" s="3">
         <v>173.09</v>
       </c>
     </row>
@@ -5408,10 +5421,10 @@
       <c r="A347" t="s">
         <v>285</v>
       </c>
-      <c r="B347">
+      <c r="B347" s="3">
         <v>81</v>
       </c>
-      <c r="C347">
+      <c r="C347" s="3">
         <v>211.23</v>
       </c>
     </row>
@@ -5419,21 +5432,21 @@
       <c r="A348" t="s">
         <v>286</v>
       </c>
-      <c r="B348">
-        <v>1</v>
-      </c>
-      <c r="C348">
-        <v>2314.8</v>
+      <c r="B348" s="3">
+        <v>1</v>
+      </c>
+      <c r="C348" s="3">
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
         <v>287</v>
       </c>
-      <c r="B349">
+      <c r="B349" s="3">
         <v>3</v>
       </c>
-      <c r="C349">
+      <c r="C349" s="3">
         <v>791.3</v>
       </c>
     </row>
@@ -5441,10 +5454,10 @@
       <c r="A350" t="s">
         <v>288</v>
       </c>
-      <c r="B350">
+      <c r="B350" s="3">
         <v>25</v>
       </c>
-      <c r="C350">
+      <c r="C350" s="3">
         <v>31.6</v>
       </c>
     </row>
@@ -5452,10 +5465,10 @@
       <c r="A351" t="s">
         <v>288</v>
       </c>
-      <c r="B351">
-        <v>1</v>
-      </c>
-      <c r="C351">
+      <c r="B351" s="3">
+        <v>1</v>
+      </c>
+      <c r="C351" s="3">
         <v>31.6</v>
       </c>
     </row>
@@ -5463,10 +5476,10 @@
       <c r="A352" t="s">
         <v>289</v>
       </c>
-      <c r="B352">
+      <c r="B352" s="3">
         <v>6</v>
       </c>
-      <c r="C352">
+      <c r="C352" s="3">
         <v>77</v>
       </c>
     </row>
@@ -5474,10 +5487,10 @@
       <c r="A353" t="s">
         <v>289</v>
       </c>
-      <c r="B353">
-        <v>1</v>
-      </c>
-      <c r="C353">
+      <c r="B353" s="3">
+        <v>1</v>
+      </c>
+      <c r="C353" s="3">
         <v>281</v>
       </c>
     </row>
@@ -5485,10 +5498,10 @@
       <c r="A354" t="s">
         <v>290</v>
       </c>
-      <c r="B354">
+      <c r="B354" s="3">
         <v>24</v>
       </c>
-      <c r="C354">
+      <c r="C354" s="3">
         <v>43.8</v>
       </c>
     </row>
@@ -5496,10 +5509,10 @@
       <c r="A355" t="s">
         <v>291</v>
       </c>
-      <c r="B355">
+      <c r="B355" s="3">
         <v>7</v>
       </c>
-      <c r="C355">
+      <c r="C355" s="3">
         <v>21.9</v>
       </c>
     </row>
@@ -5507,10 +5520,10 @@
       <c r="A356" t="s">
         <v>292</v>
       </c>
-      <c r="B356">
+      <c r="B356" s="3">
         <v>3</v>
       </c>
-      <c r="C356">
+      <c r="C356" s="3">
         <v>798.6</v>
       </c>
     </row>
@@ -5518,10 +5531,10 @@
       <c r="A357" t="s">
         <v>293</v>
       </c>
-      <c r="B357">
+      <c r="B357" s="3">
         <v>94</v>
       </c>
-      <c r="C357">
+      <c r="C357" s="3">
         <v>23.19</v>
       </c>
     </row>
@@ -5529,10 +5542,10 @@
       <c r="A358" t="s">
         <v>294</v>
       </c>
-      <c r="B358">
+      <c r="B358" s="3">
         <v>63</v>
       </c>
-      <c r="C358">
+      <c r="C358" s="3">
         <v>8.24</v>
       </c>
     </row>
@@ -5540,10 +5553,10 @@
       <c r="A359" t="s">
         <v>295</v>
       </c>
-      <c r="B359">
+      <c r="B359" s="3">
         <v>8</v>
       </c>
-      <c r="C359">
+      <c r="C359" s="3">
         <v>13.72</v>
       </c>
     </row>
@@ -5551,10 +5564,10 @@
       <c r="A360" t="s">
         <v>296</v>
       </c>
-      <c r="B360">
+      <c r="B360" s="3">
         <v>9</v>
       </c>
-      <c r="C360">
+      <c r="C360" s="3">
         <v>31.95</v>
       </c>
     </row>
@@ -5562,10 +5575,10 @@
       <c r="A361" t="s">
         <v>297</v>
       </c>
-      <c r="B361">
+      <c r="B361" s="3">
         <v>105</v>
       </c>
-      <c r="C361">
+      <c r="C361" s="3">
         <v>16.2</v>
       </c>
     </row>
@@ -5573,21 +5586,21 @@
       <c r="A362" t="s">
         <v>298</v>
       </c>
-      <c r="B362">
+      <c r="B362" s="3">
         <v>6</v>
       </c>
-      <c r="C362">
-        <v>36.87</v>
+      <c r="C362" s="3">
+        <v>36.869999999999997</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
         <v>299</v>
       </c>
-      <c r="B363">
+      <c r="B363" s="3">
         <v>24</v>
       </c>
-      <c r="C363">
+      <c r="C363" s="3">
         <v>31.48</v>
       </c>
     </row>
@@ -5595,10 +5608,10 @@
       <c r="A364" t="s">
         <v>300</v>
       </c>
-      <c r="B364">
+      <c r="B364" s="3">
         <v>10</v>
       </c>
-      <c r="C364">
+      <c r="C364" s="3">
         <v>21.9</v>
       </c>
     </row>
@@ -5606,10 +5619,10 @@
       <c r="A365" t="s">
         <v>301</v>
       </c>
-      <c r="B365">
+      <c r="B365" s="3">
         <v>6</v>
       </c>
-      <c r="C365">
+      <c r="C365" s="3">
         <v>23.19</v>
       </c>
     </row>
@@ -5617,10 +5630,10 @@
       <c r="A366" t="s">
         <v>302</v>
       </c>
-      <c r="B366">
+      <c r="B366" s="3">
         <v>12</v>
       </c>
-      <c r="C366">
+      <c r="C366" s="3">
         <v>19.55</v>
       </c>
     </row>
@@ -5628,10 +5641,10 @@
       <c r="A367" t="s">
         <v>303</v>
       </c>
-      <c r="B367">
+      <c r="B367" s="3">
         <v>11</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="3">
         <v>19.07</v>
       </c>
     </row>
@@ -5639,10 +5652,10 @@
       <c r="A368" t="s">
         <v>304</v>
       </c>
-      <c r="B368">
+      <c r="B368" s="3">
         <v>34</v>
       </c>
-      <c r="C368">
+      <c r="C368" s="3">
         <v>21.9</v>
       </c>
     </row>
@@ -5650,10 +5663,10 @@
       <c r="A369" t="s">
         <v>305</v>
       </c>
-      <c r="B369">
+      <c r="B369" s="3">
         <v>11</v>
       </c>
-      <c r="C369">
+      <c r="C369" s="3">
         <v>57.96</v>
       </c>
     </row>
@@ -5661,10 +5674,10 @@
       <c r="A370" t="s">
         <v>306</v>
       </c>
-      <c r="B370">
-        <v>1</v>
-      </c>
-      <c r="C370">
+      <c r="B370" s="3">
+        <v>1</v>
+      </c>
+      <c r="C370" s="3">
         <v>862.7</v>
       </c>
     </row>
@@ -5672,10 +5685,10 @@
       <c r="A371" t="s">
         <v>307</v>
       </c>
-      <c r="B371">
+      <c r="B371" s="3">
         <v>11</v>
       </c>
-      <c r="C371">
+      <c r="C371" s="3">
         <v>56.93</v>
       </c>
     </row>
@@ -5683,10 +5696,10 @@
       <c r="A372" t="s">
         <v>308</v>
       </c>
-      <c r="B372">
+      <c r="B372" s="3">
         <v>2</v>
       </c>
-      <c r="C372">
+      <c r="C372" s="3">
         <v>1265</v>
       </c>
     </row>
@@ -5694,10 +5707,10 @@
       <c r="A373" t="s">
         <v>309</v>
       </c>
-      <c r="B373">
+      <c r="B373" s="3">
         <v>30</v>
       </c>
-      <c r="C373">
+      <c r="C373" s="3">
         <v>76</v>
       </c>
     </row>
@@ -5705,21 +5718,21 @@
       <c r="A374" t="s">
         <v>310</v>
       </c>
-      <c r="B374">
+      <c r="B374" s="3">
         <v>6</v>
       </c>
-      <c r="C374">
-        <v>267.85</v>
+      <c r="C374" s="3">
+        <v>267.85000000000002</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
         <v>311</v>
       </c>
-      <c r="B375">
+      <c r="B375" s="3">
         <v>17</v>
       </c>
-      <c r="C375">
+      <c r="C375" s="3">
         <v>74.7</v>
       </c>
     </row>
@@ -5727,10 +5740,10 @@
       <c r="A376" t="s">
         <v>312</v>
       </c>
-      <c r="B376">
+      <c r="B376" s="3">
         <v>15</v>
       </c>
-      <c r="C376">
+      <c r="C376" s="3">
         <v>327.3</v>
       </c>
     </row>
@@ -5738,10 +5751,10 @@
       <c r="A377" t="s">
         <v>313</v>
       </c>
-      <c r="B377">
+      <c r="B377" s="3">
         <v>10</v>
       </c>
-      <c r="C377">
+      <c r="C377" s="3">
         <v>72.13</v>
       </c>
     </row>
@@ -5749,32 +5762,32 @@
       <c r="A378" t="s">
         <v>314</v>
       </c>
-      <c r="B378">
+      <c r="B378" s="3">
         <v>44</v>
       </c>
-      <c r="C378">
-        <v>302.4</v>
+      <c r="C378" s="3">
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
         <v>315</v>
       </c>
-      <c r="B379">
+      <c r="B379" s="3">
         <v>38</v>
       </c>
-      <c r="C379">
-        <v>36.8</v>
+      <c r="C379" s="3">
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
         <v>316</v>
       </c>
-      <c r="B380">
+      <c r="B380" s="3">
         <v>2</v>
       </c>
-      <c r="C380">
+      <c r="C380" s="3">
         <v>428.5</v>
       </c>
     </row>
@@ -5782,10 +5795,10 @@
       <c r="A381" t="s">
         <v>317</v>
       </c>
-      <c r="B381">
+      <c r="B381" s="3">
         <v>3</v>
       </c>
-      <c r="C381">
+      <c r="C381" s="3">
         <v>450.22</v>
       </c>
     </row>
@@ -5793,10 +5806,10 @@
       <c r="A382" t="s">
         <v>318</v>
       </c>
-      <c r="B382">
+      <c r="B382" s="3">
         <v>4</v>
       </c>
-      <c r="C382">
+      <c r="C382" s="3">
         <v>465.7</v>
       </c>
     </row>
@@ -5804,10 +5817,10 @@
       <c r="A383" t="s">
         <v>319</v>
       </c>
-      <c r="B383">
+      <c r="B383" s="3">
         <v>19</v>
       </c>
-      <c r="C383">
+      <c r="C383" s="3">
         <v>38.25</v>
       </c>
     </row>
@@ -5815,21 +5828,21 @@
       <c r="A384" t="s">
         <v>320</v>
       </c>
-      <c r="B384">
+      <c r="B384" s="3">
         <v>2</v>
       </c>
-      <c r="C384">
-        <v>87.48999999999999</v>
+      <c r="C384" s="3">
+        <v>87.49</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
         <v>321</v>
       </c>
-      <c r="B385">
+      <c r="B385" s="3">
         <v>23</v>
       </c>
-      <c r="C385">
+      <c r="C385" s="3">
         <v>63.13</v>
       </c>
     </row>
@@ -5837,10 +5850,10 @@
       <c r="A386" t="s">
         <v>322</v>
       </c>
-      <c r="B386">
+      <c r="B386" s="3">
         <v>2</v>
       </c>
-      <c r="C386">
+      <c r="C386" s="3">
         <v>377.78</v>
       </c>
     </row>
@@ -5848,10 +5861,10 @@
       <c r="A387" t="s">
         <v>323</v>
       </c>
-      <c r="B387">
+      <c r="B387" s="3">
         <v>2</v>
       </c>
-      <c r="C387">
+      <c r="C387" s="3">
         <v>3333.85</v>
       </c>
     </row>
@@ -5859,10 +5872,10 @@
       <c r="A388" t="s">
         <v>324</v>
       </c>
-      <c r="B388">
+      <c r="B388" s="3">
         <v>4</v>
       </c>
-      <c r="C388">
+      <c r="C388" s="3">
         <v>374.67</v>
       </c>
     </row>
@@ -5870,10 +5883,10 @@
       <c r="A389" t="s">
         <v>325</v>
       </c>
-      <c r="B389">
-        <v>1</v>
-      </c>
-      <c r="C389">
+      <c r="B389" s="3">
+        <v>1</v>
+      </c>
+      <c r="C389" s="3">
         <v>120.06</v>
       </c>
     </row>
@@ -5881,10 +5894,10 @@
       <c r="A390" t="s">
         <v>326</v>
       </c>
-      <c r="B390">
-        <v>1</v>
-      </c>
-      <c r="C390">
+      <c r="B390" s="3">
+        <v>1</v>
+      </c>
+      <c r="C390" s="3">
         <v>54.2</v>
       </c>
     </row>
@@ -5892,10 +5905,10 @@
       <c r="A391" t="s">
         <v>326</v>
       </c>
-      <c r="B391">
+      <c r="B391" s="3">
         <v>41</v>
       </c>
-      <c r="C391">
+      <c r="C391" s="3">
         <v>54.2</v>
       </c>
     </row>
@@ -5903,10 +5916,10 @@
       <c r="A392" t="s">
         <v>327</v>
       </c>
-      <c r="B392">
+      <c r="B392" s="3">
         <v>12</v>
       </c>
-      <c r="C392">
+      <c r="C392" s="3">
         <v>31.5</v>
       </c>
     </row>
@@ -5914,10 +5927,10 @@
       <c r="A393" t="s">
         <v>328</v>
       </c>
-      <c r="B393">
+      <c r="B393" s="3">
         <v>4</v>
       </c>
-      <c r="C393">
+      <c r="C393" s="3">
         <v>114.09</v>
       </c>
     </row>
@@ -5925,10 +5938,10 @@
       <c r="A394" t="s">
         <v>329</v>
       </c>
-      <c r="B394">
+      <c r="B394" s="3">
         <v>4</v>
       </c>
-      <c r="C394">
+      <c r="C394" s="3">
         <v>139.9</v>
       </c>
     </row>
@@ -5936,10 +5949,10 @@
       <c r="A395" t="s">
         <v>330</v>
       </c>
-      <c r="B395">
+      <c r="B395" s="3">
         <v>10</v>
       </c>
-      <c r="C395">
+      <c r="C395" s="3">
         <v>35.94</v>
       </c>
     </row>
@@ -5947,10 +5960,10 @@
       <c r="A396" t="s">
         <v>331</v>
       </c>
-      <c r="B396">
+      <c r="B396" s="3">
         <v>8</v>
       </c>
-      <c r="C396">
+      <c r="C396" s="3">
         <v>140.26</v>
       </c>
     </row>
@@ -5958,10 +5971,10 @@
       <c r="A397" t="s">
         <v>332</v>
       </c>
-      <c r="B397">
-        <v>1</v>
-      </c>
-      <c r="C397">
+      <c r="B397" s="3">
+        <v>1</v>
+      </c>
+      <c r="C397" s="3">
         <v>370.53</v>
       </c>
     </row>
@@ -5969,10 +5982,10 @@
       <c r="A398" t="s">
         <v>333</v>
       </c>
-      <c r="B398">
+      <c r="B398" s="3">
         <v>5</v>
       </c>
-      <c r="C398">
+      <c r="C398" s="3">
         <v>30.9</v>
       </c>
     </row>
@@ -5980,10 +5993,10 @@
       <c r="A399" t="s">
         <v>334</v>
       </c>
-      <c r="B399">
-        <v>1</v>
-      </c>
-      <c r="C399">
+      <c r="B399" s="3">
+        <v>1</v>
+      </c>
+      <c r="C399" s="3">
         <v>4772.5</v>
       </c>
     </row>
@@ -5991,10 +6004,10 @@
       <c r="A400" t="s">
         <v>335</v>
       </c>
-      <c r="B400">
-        <v>1</v>
-      </c>
-      <c r="C400">
+      <c r="B400" s="3">
+        <v>1</v>
+      </c>
+      <c r="C400" s="3">
         <v>375.7</v>
       </c>
     </row>
@@ -6002,10 +6015,10 @@
       <c r="A401" t="s">
         <v>335</v>
       </c>
-      <c r="B401">
+      <c r="B401" s="3">
         <v>2</v>
       </c>
-      <c r="C401">
+      <c r="C401" s="3">
         <v>516.46</v>
       </c>
     </row>
@@ -6013,10 +6026,10 @@
       <c r="A402" t="s">
         <v>336</v>
       </c>
-      <c r="B402">
+      <c r="B402" s="3">
         <v>4</v>
       </c>
-      <c r="C402">
+      <c r="C402" s="3">
         <v>185.15</v>
       </c>
     </row>
@@ -6024,10 +6037,10 @@
       <c r="A403" t="s">
         <v>337</v>
       </c>
-      <c r="B403">
+      <c r="B403" s="3">
         <v>31</v>
       </c>
-      <c r="C403">
+      <c r="C403" s="3">
         <v>11.5</v>
       </c>
     </row>
@@ -6035,10 +6048,10 @@
       <c r="A404" t="s">
         <v>338</v>
       </c>
-      <c r="B404">
+      <c r="B404" s="3">
         <v>4</v>
       </c>
-      <c r="C404">
+      <c r="C404" s="3">
         <v>724.5</v>
       </c>
     </row>
@@ -6046,10 +6059,10 @@
       <c r="A405" t="s">
         <v>339</v>
       </c>
-      <c r="B405">
+      <c r="B405" s="3">
         <v>4</v>
       </c>
-      <c r="C405">
+      <c r="C405" s="3">
         <v>450.22</v>
       </c>
     </row>
@@ -6057,10 +6070,10 @@
       <c r="A406" t="s">
         <v>340</v>
       </c>
-      <c r="B406">
-        <v>1</v>
-      </c>
-      <c r="C406">
+      <c r="B406" s="3">
+        <v>1</v>
+      </c>
+      <c r="C406" s="3">
         <v>461.23</v>
       </c>
     </row>
@@ -6068,21 +6081,21 @@
       <c r="A407" t="s">
         <v>340</v>
       </c>
-      <c r="B407">
-        <v>1</v>
-      </c>
-      <c r="C407">
-        <v>518.42</v>
+      <c r="B407" s="3">
+        <v>1</v>
+      </c>
+      <c r="C407" s="3">
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
         <v>341</v>
       </c>
-      <c r="B408">
-        <v>1</v>
-      </c>
-      <c r="C408">
+      <c r="B408" s="3">
+        <v>1</v>
+      </c>
+      <c r="C408" s="3">
         <v>348.08</v>
       </c>
     </row>
@@ -6090,21 +6103,21 @@
       <c r="A409" t="s">
         <v>342</v>
       </c>
-      <c r="B409">
+      <c r="B409" s="3">
         <v>10</v>
       </c>
-      <c r="C409">
-        <v>33.48</v>
+      <c r="C409" s="3">
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
         <v>343</v>
       </c>
-      <c r="B410">
+      <c r="B410" s="3">
         <v>13</v>
       </c>
-      <c r="C410">
+      <c r="C410" s="3">
         <v>35.79</v>
       </c>
     </row>
@@ -6112,10 +6125,10 @@
       <c r="A411" t="s">
         <v>344</v>
       </c>
-      <c r="B411">
+      <c r="B411" s="3">
         <v>3</v>
       </c>
-      <c r="C411">
+      <c r="C411" s="3">
         <v>377.7</v>
       </c>
     </row>
@@ -6123,10 +6136,10 @@
       <c r="A412" t="s">
         <v>345</v>
       </c>
-      <c r="B412">
+      <c r="B412" s="3">
         <v>18</v>
       </c>
-      <c r="C412">
+      <c r="C412" s="3">
         <v>33.21</v>
       </c>
     </row>
@@ -6134,10 +6147,10 @@
       <c r="A413" t="s">
         <v>346</v>
       </c>
-      <c r="B413">
+      <c r="B413" s="3">
         <v>39</v>
       </c>
-      <c r="C413">
+      <c r="C413" s="3">
         <v>27.16</v>
       </c>
     </row>
@@ -6145,10 +6158,10 @@
       <c r="A414" t="s">
         <v>347</v>
       </c>
-      <c r="B414">
-        <v>1</v>
-      </c>
-      <c r="C414">
+      <c r="B414" s="3">
+        <v>1</v>
+      </c>
+      <c r="C414" s="3">
         <v>361.41</v>
       </c>
     </row>
@@ -6156,10 +6169,10 @@
       <c r="A415" t="s">
         <v>348</v>
       </c>
-      <c r="B415">
+      <c r="B415" s="3">
         <v>63</v>
       </c>
-      <c r="C415">
+      <c r="C415" s="3">
         <v>29.25</v>
       </c>
     </row>
@@ -6167,10 +6180,10 @@
       <c r="A416" t="s">
         <v>348</v>
       </c>
-      <c r="B416">
-        <v>1</v>
-      </c>
-      <c r="C416">
+      <c r="B416" s="3">
+        <v>1</v>
+      </c>
+      <c r="C416" s="3">
         <v>29.26</v>
       </c>
     </row>
@@ -6178,32 +6191,32 @@
       <c r="A417" t="s">
         <v>349</v>
       </c>
-      <c r="B417">
-        <v>1</v>
-      </c>
-      <c r="C417">
-        <v>304.54</v>
+      <c r="B417" s="3">
+        <v>1</v>
+      </c>
+      <c r="C417" s="3">
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
         <v>350</v>
       </c>
-      <c r="B418">
+      <c r="B418" s="3">
         <v>17</v>
       </c>
-      <c r="C418">
-        <v>34.05</v>
+      <c r="C418" s="3">
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
         <v>351</v>
       </c>
-      <c r="B419">
+      <c r="B419" s="3">
         <v>11</v>
       </c>
-      <c r="C419">
+      <c r="C419" s="3">
         <v>57.7</v>
       </c>
     </row>
@@ -6211,21 +6224,21 @@
       <c r="A420" t="s">
         <v>352</v>
       </c>
-      <c r="B420">
+      <c r="B420" s="3">
         <v>12</v>
       </c>
-      <c r="C420">
-        <v>90.90000000000001</v>
+      <c r="C420" s="3">
+        <v>90.9</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
         <v>353</v>
       </c>
-      <c r="B421">
+      <c r="B421" s="3">
         <v>30</v>
       </c>
-      <c r="C421">
+      <c r="C421" s="3">
         <v>44.3</v>
       </c>
     </row>
@@ -6233,10 +6246,10 @@
       <c r="A422" t="s">
         <v>353</v>
       </c>
-      <c r="B422">
+      <c r="B422" s="3">
         <v>72</v>
       </c>
-      <c r="C422">
+      <c r="C422" s="3">
         <v>44.31</v>
       </c>
     </row>
@@ -6244,10 +6257,10 @@
       <c r="A423" t="s">
         <v>354</v>
       </c>
-      <c r="B423">
-        <v>1</v>
-      </c>
-      <c r="C423">
+      <c r="B423" s="3">
+        <v>1</v>
+      </c>
+      <c r="C423" s="3">
         <v>7173.59</v>
       </c>
     </row>
@@ -6255,10 +6268,10 @@
       <c r="A424" t="s">
         <v>355</v>
       </c>
-      <c r="B424">
-        <v>1</v>
-      </c>
-      <c r="C424">
+      <c r="B424" s="3">
+        <v>1</v>
+      </c>
+      <c r="C424" s="3">
         <v>677.79</v>
       </c>
     </row>
@@ -6266,10 +6279,10 @@
       <c r="A425" t="s">
         <v>356</v>
       </c>
-      <c r="B425">
-        <v>1</v>
-      </c>
-      <c r="C425">
+      <c r="B425" s="3">
+        <v>1</v>
+      </c>
+      <c r="C425" s="3">
         <v>167.33</v>
       </c>
     </row>
@@ -6277,10 +6290,10 @@
       <c r="A426" t="s">
         <v>356</v>
       </c>
-      <c r="B426">
+      <c r="B426" s="3">
         <v>40</v>
       </c>
-      <c r="C426">
+      <c r="C426" s="3">
         <v>167.33</v>
       </c>
     </row>
@@ -6288,10 +6301,10 @@
       <c r="A427" t="s">
         <v>357</v>
       </c>
-      <c r="B427">
+      <c r="B427" s="3">
         <v>55</v>
       </c>
-      <c r="C427">
+      <c r="C427" s="3">
         <v>191.01</v>
       </c>
     </row>
@@ -6299,10 +6312,10 @@
       <c r="A428" t="s">
         <v>358</v>
       </c>
-      <c r="B428">
+      <c r="B428" s="3">
         <v>3</v>
       </c>
-      <c r="C428">
+      <c r="C428" s="3">
         <v>2335.67</v>
       </c>
     </row>
@@ -6310,10 +6323,10 @@
       <c r="A429" t="s">
         <v>359</v>
       </c>
-      <c r="B429">
+      <c r="B429" s="3">
         <v>2</v>
       </c>
-      <c r="C429">
+      <c r="C429" s="3">
         <v>62.04</v>
       </c>
     </row>
@@ -6321,10 +6334,10 @@
       <c r="A430" t="s">
         <v>359</v>
       </c>
-      <c r="B430">
+      <c r="B430" s="3">
         <v>72</v>
       </c>
-      <c r="C430">
+      <c r="C430" s="3">
         <v>62.04</v>
       </c>
     </row>
@@ -6332,10 +6345,10 @@
       <c r="A431" t="s">
         <v>360</v>
       </c>
-      <c r="B431">
+      <c r="B431" s="3">
         <v>2</v>
       </c>
-      <c r="C431">
+      <c r="C431" s="3">
         <v>8139.6</v>
       </c>
     </row>
@@ -6343,10 +6356,10 @@
       <c r="A432" t="s">
         <v>361</v>
       </c>
-      <c r="B432">
+      <c r="B432" s="3">
         <v>28</v>
       </c>
-      <c r="C432">
+      <c r="C432" s="3">
         <v>235.53</v>
       </c>
     </row>
@@ -6354,10 +6367,10 @@
       <c r="A433" t="s">
         <v>362</v>
       </c>
-      <c r="B433">
+      <c r="B433" s="3">
         <v>14</v>
       </c>
-      <c r="C433">
+      <c r="C433" s="3">
         <v>259.8</v>
       </c>
     </row>
@@ -6365,10 +6378,10 @@
       <c r="A434" t="s">
         <v>363</v>
       </c>
-      <c r="B434">
-        <v>1</v>
-      </c>
-      <c r="C434">
+      <c r="B434" s="3">
+        <v>1</v>
+      </c>
+      <c r="C434" s="3">
         <v>310.2</v>
       </c>
     </row>
@@ -6376,10 +6389,10 @@
       <c r="A435" t="s">
         <v>364</v>
       </c>
-      <c r="B435">
-        <v>1</v>
-      </c>
-      <c r="C435">
+      <c r="B435" s="3">
+        <v>1</v>
+      </c>
+      <c r="C435" s="3">
         <v>36.43</v>
       </c>
     </row>
@@ -6387,10 +6400,10 @@
       <c r="A436" t="s">
         <v>365</v>
       </c>
-      <c r="B436">
+      <c r="B436" s="3">
         <v>4</v>
       </c>
-      <c r="C436">
+      <c r="C436" s="3">
         <v>73.42</v>
       </c>
     </row>
@@ -6398,21 +6411,21 @@
       <c r="A437" t="s">
         <v>366</v>
       </c>
-      <c r="B437">
+      <c r="B437" s="3">
         <v>12</v>
       </c>
-      <c r="C437">
-        <v>319.6</v>
+      <c r="C437" s="3">
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
         <v>367</v>
       </c>
-      <c r="B438">
+      <c r="B438" s="3">
         <v>25</v>
       </c>
-      <c r="C438">
+      <c r="C438" s="3">
         <v>62.6</v>
       </c>
     </row>
@@ -6420,10 +6433,10 @@
       <c r="A439" t="s">
         <v>368</v>
       </c>
-      <c r="B439">
+      <c r="B439" s="3">
         <v>8</v>
       </c>
-      <c r="C439">
+      <c r="C439" s="3">
         <v>312.8</v>
       </c>
     </row>
@@ -6431,10 +6444,10 @@
       <c r="A440" t="s">
         <v>369</v>
       </c>
-      <c r="B440">
+      <c r="B440" s="3">
         <v>10</v>
       </c>
-      <c r="C440">
+      <c r="C440" s="3">
         <v>67.28</v>
       </c>
     </row>
@@ -6442,10 +6455,10 @@
       <c r="A441" t="s">
         <v>369</v>
       </c>
-      <c r="B441">
+      <c r="B441" s="3">
         <v>21</v>
       </c>
-      <c r="C441">
+      <c r="C441" s="3">
         <v>67.28</v>
       </c>
     </row>
@@ -6453,10 +6466,10 @@
       <c r="A442" t="s">
         <v>370</v>
       </c>
-      <c r="B442">
+      <c r="B442" s="3">
         <v>3</v>
       </c>
-      <c r="C442">
+      <c r="C442" s="3">
         <v>1138.5</v>
       </c>
     </row>
@@ -6464,10 +6477,10 @@
       <c r="A443" t="s">
         <v>370</v>
       </c>
-      <c r="B443">
-        <v>1</v>
-      </c>
-      <c r="C443">
+      <c r="B443" s="3">
+        <v>1</v>
+      </c>
+      <c r="C443" s="3">
         <v>1138.5</v>
       </c>
     </row>
@@ -6475,10 +6488,10 @@
       <c r="A444" t="s">
         <v>371</v>
       </c>
-      <c r="B444">
+      <c r="B444" s="3">
         <v>2</v>
       </c>
-      <c r="C444">
+      <c r="C444" s="3">
         <v>48.76</v>
       </c>
     </row>
@@ -6486,10 +6499,10 @@
       <c r="A445" t="s">
         <v>372</v>
       </c>
-      <c r="B445">
+      <c r="B445" s="3">
         <v>3</v>
       </c>
-      <c r="C445">
+      <c r="C445" s="3">
         <v>242.34</v>
       </c>
     </row>
@@ -6497,10 +6510,10 @@
       <c r="A446" t="s">
         <v>373</v>
       </c>
-      <c r="B446">
+      <c r="B446" s="3">
         <v>4</v>
       </c>
-      <c r="C446">
+      <c r="C446" s="3">
         <v>54.09</v>
       </c>
     </row>
@@ -6508,10 +6521,10 @@
       <c r="A447" t="s">
         <v>373</v>
       </c>
-      <c r="B447">
+      <c r="B447" s="3">
         <v>30</v>
       </c>
-      <c r="C447">
+      <c r="C447" s="3">
         <v>54.1</v>
       </c>
     </row>
@@ -6519,10 +6532,10 @@
       <c r="A448" t="s">
         <v>374</v>
       </c>
-      <c r="B448">
+      <c r="B448" s="3">
         <v>20</v>
       </c>
-      <c r="C448">
+      <c r="C448" s="3">
         <v>255.03</v>
       </c>
     </row>
@@ -6530,10 +6543,10 @@
       <c r="A449" t="s">
         <v>375</v>
       </c>
-      <c r="B449">
+      <c r="B449" s="3">
         <v>18</v>
       </c>
-      <c r="C449">
+      <c r="C449" s="3">
         <v>220.8</v>
       </c>
     </row>
@@ -6541,10 +6554,10 @@
       <c r="A450" t="s">
         <v>376</v>
       </c>
-      <c r="B450">
+      <c r="B450" s="3">
         <v>21</v>
       </c>
-      <c r="C450">
+      <c r="C450" s="3">
         <v>255.03</v>
       </c>
     </row>
@@ -6552,10 +6565,10 @@
       <c r="A451" t="s">
         <v>377</v>
       </c>
-      <c r="B451">
+      <c r="B451" s="3">
         <v>12</v>
       </c>
-      <c r="C451">
+      <c r="C451" s="3">
         <v>68.86</v>
       </c>
     </row>
@@ -6563,10 +6576,10 @@
       <c r="A452" t="s">
         <v>378</v>
       </c>
-      <c r="B452">
+      <c r="B452" s="3">
         <v>4</v>
       </c>
-      <c r="C452">
+      <c r="C452" s="3">
         <v>344.28</v>
       </c>
     </row>
@@ -6574,10 +6587,10 @@
       <c r="A453" t="s">
         <v>379</v>
       </c>
-      <c r="B453">
+      <c r="B453" s="3">
         <v>10</v>
       </c>
-      <c r="C453">
+      <c r="C453" s="3">
         <v>60.29</v>
       </c>
     </row>
@@ -6585,10 +6598,10 @@
       <c r="A454" t="s">
         <v>380</v>
       </c>
-      <c r="B454">
+      <c r="B454" s="3">
         <v>3</v>
       </c>
-      <c r="C454">
+      <c r="C454" s="3">
         <v>261.8</v>
       </c>
     </row>
@@ -6596,10 +6609,10 @@
       <c r="A455" t="s">
         <v>380</v>
       </c>
-      <c r="B455">
-        <v>1</v>
-      </c>
-      <c r="C455">
+      <c r="B455" s="3">
+        <v>1</v>
+      </c>
+      <c r="C455" s="3">
         <v>261.8</v>
       </c>
     </row>
@@ -6607,10 +6620,10 @@
       <c r="A456" t="s">
         <v>381</v>
       </c>
-      <c r="B456">
-        <v>1</v>
-      </c>
-      <c r="C456">
+      <c r="B456" s="3">
+        <v>1</v>
+      </c>
+      <c r="C456" s="3">
         <v>30.58</v>
       </c>
     </row>
@@ -6618,10 +6631,10 @@
       <c r="A457" t="s">
         <v>382</v>
       </c>
-      <c r="B457">
-        <v>1</v>
-      </c>
-      <c r="C457">
+      <c r="B457" s="3">
+        <v>1</v>
+      </c>
+      <c r="C457" s="3">
         <v>30.58</v>
       </c>
     </row>
@@ -6629,10 +6642,10 @@
       <c r="A458" t="s">
         <v>383</v>
       </c>
-      <c r="B458">
+      <c r="B458" s="3">
         <v>54</v>
       </c>
-      <c r="C458">
+      <c r="C458" s="3">
         <v>16.95</v>
       </c>
     </row>
@@ -6640,10 +6653,10 @@
       <c r="A459" t="s">
         <v>384</v>
       </c>
-      <c r="B459">
+      <c r="B459" s="3">
         <v>45</v>
       </c>
-      <c r="C459">
+      <c r="C459" s="3">
         <v>24.95</v>
       </c>
     </row>
@@ -6651,10 +6664,10 @@
       <c r="A460" t="s">
         <v>385</v>
       </c>
-      <c r="B460">
+      <c r="B460" s="3">
         <v>3</v>
       </c>
-      <c r="C460">
+      <c r="C460" s="3">
         <v>641.49</v>
       </c>
     </row>
@@ -6662,10 +6675,10 @@
       <c r="A461" t="s">
         <v>386</v>
       </c>
-      <c r="B461">
+      <c r="B461" s="3">
         <v>12</v>
       </c>
-      <c r="C461">
+      <c r="C461" s="3">
         <v>39.57</v>
       </c>
     </row>
@@ -6673,10 +6686,10 @@
       <c r="A462" t="s">
         <v>387</v>
       </c>
-      <c r="B462">
+      <c r="B462" s="3">
         <v>36</v>
       </c>
-      <c r="C462">
+      <c r="C462" s="3">
         <v>51.83</v>
       </c>
     </row>
@@ -6684,21 +6697,21 @@
       <c r="A463" t="s">
         <v>388</v>
       </c>
-      <c r="B463">
+      <c r="B463" s="3">
         <v>48</v>
       </c>
-      <c r="C463">
-        <v>33.84</v>
+      <c r="C463" s="3">
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
         <v>389</v>
       </c>
-      <c r="B464">
+      <c r="B464" s="3">
         <v>21</v>
       </c>
-      <c r="C464">
+      <c r="C464" s="3">
         <v>150.15</v>
       </c>
     </row>
@@ -6706,10 +6719,10 @@
       <c r="A465" t="s">
         <v>390</v>
       </c>
-      <c r="B465">
+      <c r="B465" s="3">
         <v>25</v>
       </c>
-      <c r="C465">
+      <c r="C465" s="3">
         <v>144.5</v>
       </c>
     </row>
@@ -6717,10 +6730,10 @@
       <c r="A466" t="s">
         <v>391</v>
       </c>
-      <c r="B466">
+      <c r="B466" s="3">
         <v>25</v>
       </c>
-      <c r="C466">
+      <c r="C466" s="3">
         <v>100.93</v>
       </c>
     </row>
@@ -6728,10 +6741,10 @@
       <c r="A467" t="s">
         <v>392</v>
       </c>
-      <c r="B467">
+      <c r="B467" s="3">
         <v>14</v>
       </c>
-      <c r="C467">
+      <c r="C467" s="3">
         <v>124.5</v>
       </c>
     </row>
@@ -6739,10 +6752,10 @@
       <c r="A468" t="s">
         <v>393</v>
       </c>
-      <c r="B468">
+      <c r="B468" s="3">
         <v>10</v>
       </c>
-      <c r="C468">
+      <c r="C468" s="3">
         <v>27.21</v>
       </c>
     </row>
@@ -6750,10 +6763,10 @@
       <c r="A469" t="s">
         <v>394</v>
       </c>
-      <c r="B469">
+      <c r="B469" s="3">
         <v>94</v>
       </c>
-      <c r="C469">
+      <c r="C469" s="3">
         <v>24.79</v>
       </c>
     </row>
@@ -6761,10 +6774,10 @@
       <c r="A470" t="s">
         <v>395</v>
       </c>
-      <c r="B470">
+      <c r="B470" s="3">
         <v>10</v>
       </c>
-      <c r="C470">
+      <c r="C470" s="3">
         <v>37.1</v>
       </c>
     </row>
@@ -6772,10 +6785,10 @@
       <c r="A471" t="s">
         <v>396</v>
       </c>
-      <c r="B471">
+      <c r="B471" s="3">
         <v>10</v>
       </c>
-      <c r="C471">
+      <c r="C471" s="3">
         <v>178.04</v>
       </c>
     </row>
@@ -6783,10 +6796,10 @@
       <c r="A472" t="s">
         <v>397</v>
       </c>
-      <c r="B472">
+      <c r="B472" s="3">
         <v>48</v>
       </c>
-      <c r="C472">
+      <c r="C472" s="3">
         <v>23.88</v>
       </c>
     </row>
@@ -6794,10 +6807,10 @@
       <c r="A473" t="s">
         <v>398</v>
       </c>
-      <c r="B473">
+      <c r="B473" s="3">
         <v>50</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="3">
         <v>8.26</v>
       </c>
     </row>
@@ -6805,10 +6818,10 @@
       <c r="A474" t="s">
         <v>399</v>
       </c>
-      <c r="B474">
-        <v>1</v>
-      </c>
-      <c r="C474">
+      <c r="B474" s="3">
+        <v>1</v>
+      </c>
+      <c r="C474" s="3">
         <v>859.21</v>
       </c>
     </row>
@@ -6816,10 +6829,10 @@
       <c r="A475" t="s">
         <v>400</v>
       </c>
-      <c r="B475">
-        <v>1</v>
-      </c>
-      <c r="C475">
+      <c r="B475" s="3">
+        <v>1</v>
+      </c>
+      <c r="C475" s="3">
         <v>242.4</v>
       </c>
     </row>
@@ -6827,10 +6840,10 @@
       <c r="A476" t="s">
         <v>401</v>
       </c>
-      <c r="B476">
+      <c r="B476" s="3">
         <v>3</v>
       </c>
-      <c r="C476">
+      <c r="C476" s="3">
         <v>5000</v>
       </c>
     </row>
@@ -6838,10 +6851,10 @@
       <c r="A477" t="s">
         <v>402</v>
       </c>
-      <c r="B477">
+      <c r="B477" s="3">
         <v>93</v>
       </c>
-      <c r="C477">
+      <c r="C477" s="3">
         <v>20.68</v>
       </c>
     </row>
@@ -6849,32 +6862,32 @@
       <c r="A478" t="s">
         <v>403</v>
       </c>
-      <c r="B478">
+      <c r="B478" s="3">
         <v>31</v>
       </c>
-      <c r="C478">
-        <v>97.54000000000001</v>
+      <c r="C478" s="3">
+        <v>97.54</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
         <v>404</v>
       </c>
-      <c r="B479">
+      <c r="B479" s="3">
         <v>10</v>
       </c>
-      <c r="C479">
-        <v>304.03</v>
+      <c r="C479" s="3">
+        <v>304.02999999999997</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
         <v>405</v>
       </c>
-      <c r="B480">
+      <c r="B480" s="3">
         <v>6</v>
       </c>
-      <c r="C480">
+      <c r="C480" s="3">
         <v>1934.56</v>
       </c>
     </row>
@@ -6882,10 +6895,10 @@
       <c r="A481" t="s">
         <v>406</v>
       </c>
-      <c r="B481">
+      <c r="B481" s="3">
         <v>6</v>
       </c>
-      <c r="C481">
+      <c r="C481" s="3">
         <v>230.99</v>
       </c>
     </row>
@@ -6893,10 +6906,10 @@
       <c r="A482" t="s">
         <v>407</v>
       </c>
-      <c r="B482">
+      <c r="B482" s="3">
         <v>96</v>
       </c>
-      <c r="C482">
+      <c r="C482" s="3">
         <v>33.39</v>
       </c>
     </row>
@@ -6904,10 +6917,10 @@
       <c r="A483" t="s">
         <v>408</v>
       </c>
-      <c r="B483">
+      <c r="B483" s="3">
         <v>48</v>
       </c>
-      <c r="C483">
+      <c r="C483" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="409">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1604,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C483"/>
+  <dimension ref="A1:C490"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2969,21 +2969,21 @@
         <v>103</v>
       </c>
       <c r="B124" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C124" s="3">
-        <v>43.99</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B125" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C125" s="3">
-        <v>56.93</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2991,73 +2991,73 @@
         <v>104</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C126" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B127" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B128" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C128" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B129" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C129" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B130" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C130" s="3">
-        <v>59.68</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B131" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C131" s="3">
-        <v>56.93</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B132" s="3">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C132" s="3">
         <v>56.93</v>
@@ -3068,73 +3068,73 @@
         <v>110</v>
       </c>
       <c r="B133" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C133" s="3">
-        <v>70.38</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B134" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C134" s="3">
-        <v>98.95</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B135" s="3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C135" s="3">
-        <v>92.91</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B136" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C136" s="3">
-        <v>93.25</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B137" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C137" s="3">
-        <v>56.93</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C138" s="3">
-        <v>63.76</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B139" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C139" s="3">
         <v>56.93</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B140" s="3">
         <v>1</v>
@@ -3153,21 +3153,21 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B141" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C141" s="3">
-        <v>81.150000000000006</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B142" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C142" s="3">
         <v>63.76</v>
@@ -3175,21 +3175,21 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B143" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C143" s="3">
-        <v>69.87</v>
+        <v>81.150000000000006</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B144" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C144" s="3">
         <v>63.76</v>
@@ -3197,3730 +3197,3807 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B145" s="3">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C145" s="3">
-        <v>69.56</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B146" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C146" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B147" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C147" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B148" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C148" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B149" s="3">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C149" s="3">
-        <v>208.66</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B150" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C150" s="3">
-        <v>79.349999999999994</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B151" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C151" s="3">
-        <v>88.87</v>
+        <v>208.66</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B152" s="3">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C152" s="3">
-        <v>67.28</v>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B153" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C153" s="3">
-        <v>62.11</v>
+        <v>88.87</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B154" s="3">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C154" s="3">
-        <v>69.55</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B155" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C155" s="3">
-        <v>63.89</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B156" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C156" s="3">
-        <v>95.05</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B157" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C157" s="3">
-        <v>38.57</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B158" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C158" s="3">
-        <v>207.31</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B159" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C159" s="3">
-        <v>58.24</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C160" s="3">
-        <v>65.23</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B161" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C161" s="3">
-        <v>325.87</v>
+        <v>207.31</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C162" s="3">
-        <v>5165.8</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B163" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C163" s="3">
-        <v>511.75</v>
+        <v>65.23</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B164" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C164" s="3">
-        <v>572.70000000000005</v>
+        <v>325.87</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B165" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C165" s="3">
-        <v>66.98</v>
+        <v>5165.8</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B166" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C166" s="3">
-        <v>367.42</v>
+        <v>511.75</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B167" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C167" s="3">
-        <v>51.52</v>
+        <v>572.70000000000005</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B168" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C168" s="3">
-        <v>23.19</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B169" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C169" s="3">
-        <v>23.19</v>
+        <v>367.42</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C170" s="3">
-        <v>23.19</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B171" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C171" s="3">
-        <v>69.55</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B172" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C172" s="3">
-        <v>3169.7</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B173" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C173" s="3">
-        <v>81.14</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B174" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C174" s="3">
-        <v>81.14</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B175" s="3">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C175" s="3">
-        <v>66.98</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B176" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C176" s="3">
-        <v>53.83</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B177" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C177" s="3">
-        <v>60.28</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B178" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C178" s="3">
-        <v>60.29</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B179" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C179" s="3">
-        <v>82.65</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B180" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C180" s="3">
-        <v>93.35</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C181" s="3">
-        <v>1217.1600000000001</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C182" s="3">
-        <v>3079</v>
+        <v>82.65</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B183" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C183" s="3">
-        <v>43.7</v>
+        <v>93.35</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B184" s="3">
         <v>1</v>
       </c>
       <c r="C184" s="3">
-        <v>48.95</v>
+        <v>1217.1600000000001</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B185" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C185" s="3">
-        <v>64.59</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C186" s="3">
-        <v>72.33</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B187" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C187" s="3">
-        <v>284.19</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B188" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C188" s="3">
-        <v>75.260000000000005</v>
+        <v>64.59</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B189" s="3">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C189" s="3">
-        <v>32.200000000000003</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B190" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C190" s="3">
-        <v>32.200000000000003</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B191" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C191" s="3">
-        <v>37.43</v>
+        <v>132.19999999999999</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B192" s="3">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C192" s="3">
-        <v>32.200000000000003</v>
+        <v>75.260000000000005</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B193" s="3">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C193" s="3">
-        <v>115.01</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B194" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C194" s="3">
-        <v>38.39</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B195" s="3">
         <v>1</v>
       </c>
       <c r="C195" s="3">
-        <v>38.39</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B196" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C196" s="3">
-        <v>151.47999999999999</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B197" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C197" s="3">
-        <v>181.68</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B198" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C198" s="3">
-        <v>20.059999999999999</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B199" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C199" s="3">
-        <v>12.88</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B200" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C200" s="3">
-        <v>26.73</v>
+        <v>151.47999999999999</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B201" s="3">
         <v>12</v>
       </c>
       <c r="C201" s="3">
-        <v>29.95</v>
+        <v>181.68</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B202" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C202" s="3">
-        <v>58.68</v>
+        <v>20.059999999999999</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B203" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C203" s="3">
-        <v>79.98</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B204" s="3">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C204" s="3">
-        <v>34.619999999999997</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B205" s="3">
         <v>12</v>
       </c>
       <c r="C205" s="3">
-        <v>38.770000000000003</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B206" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C206" s="3">
-        <v>107.35</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B207" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C207" s="3">
-        <v>55.2</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B208" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C208" s="3">
-        <v>61.83</v>
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B209" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C209" s="3">
-        <v>243.16</v>
+        <v>38.770000000000003</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B210" s="3">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C210" s="3">
-        <v>32.200000000000003</v>
+        <v>107.35</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B211" s="3">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C211" s="3">
-        <v>63.78</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B212" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C212" s="3">
-        <v>67.849999999999994</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B213" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C213" s="3">
-        <v>75.989999999999995</v>
+        <v>243.16</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B214" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C214" s="3">
-        <v>297.64999999999998</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B215" s="3">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C215" s="3">
-        <v>77.28</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B216" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C216" s="3">
-        <v>75.989999999999995</v>
+        <v>67.849999999999994</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B217" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C217" s="3">
-        <v>342.24</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B218" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C218" s="3">
-        <v>633.75</v>
+        <v>297.64999999999998</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B219" s="3">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C219" s="3">
-        <v>36.799999999999997</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B220" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C220" s="3">
-        <v>50.51</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B221" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C221" s="3">
-        <v>768.2</v>
+        <v>342.24</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B222" s="3">
         <v>2</v>
       </c>
       <c r="C222" s="3">
-        <v>787.75</v>
+        <v>633.75</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B223" s="3">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="C223" s="3">
-        <v>109.26</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B224" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C224" s="3">
-        <v>122.36</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B225" s="3">
         <v>2</v>
       </c>
       <c r="C225" s="3">
-        <v>31.98</v>
+        <v>768.2</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B226" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C226" s="3">
-        <v>35.81</v>
+        <v>787.75</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B227" s="3">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C227" s="3">
-        <v>59.25</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B228" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C228" s="3">
-        <v>260</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B229" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C229" s="3">
-        <v>43.07</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B230" s="3">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C230" s="3">
-        <v>48.23</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B231" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C231" s="3">
-        <v>221.86</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B232" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C232" s="3">
-        <v>74.7</v>
+        <v>260</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B233" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C233" s="3">
-        <v>296.3</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B234" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C234" s="3">
-        <v>141.80000000000001</v>
+        <v>48.23</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B235" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C235" s="3">
-        <v>29.25</v>
+        <v>221.86</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B236" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C236" s="3">
-        <v>41.4</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B237" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C237" s="3">
-        <v>141.80000000000001</v>
+        <v>296.3</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B238" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C238" s="3">
-        <v>173.3</v>
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B239" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C239" s="3">
-        <v>2189.02</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B240" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C240" s="3">
-        <v>453.22</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B241" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C241" s="3">
-        <v>31.3</v>
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B242" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C242" s="3">
-        <v>126.63</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B243" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C243" s="3">
-        <v>69.56</v>
+        <v>2189.02</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B244" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C244" s="3">
-        <v>42.44</v>
+        <v>453.22</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B245" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C245" s="3">
-        <v>42.43</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B246" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C246" s="3">
-        <v>145.94</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B247" s="3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C247" s="3">
-        <v>179</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B248" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C248" s="3">
-        <v>2060.8000000000002</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B249" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C249" s="3">
-        <v>51</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B250" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C250" s="3">
-        <v>51</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B251" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C251" s="3">
-        <v>183.41</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B252" s="3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C252" s="3">
-        <v>206.33</v>
+        <v>179</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B253" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C253" s="3">
-        <v>33.479999999999997</v>
+        <v>2060.8000000000002</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B254" s="3">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C254" s="3">
-        <v>33.479999999999997</v>
+        <v>51</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B255" s="3">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C255" s="3">
-        <v>46.06</v>
+        <v>51</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B256" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C256" s="3">
-        <v>4667</v>
+        <v>183.41</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B257" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C257" s="3">
-        <v>5345.33</v>
+        <v>206.33</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B258" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C258" s="3">
-        <v>170.78</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B259" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C259" s="3">
-        <v>162.13</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B260" s="3">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C260" s="3">
-        <v>192.51</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B261" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C261" s="3">
-        <v>59.7</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B262" s="3">
         <v>1</v>
       </c>
       <c r="C262" s="3">
-        <v>265.05</v>
+        <v>5345.33</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B263" s="3">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C263" s="3">
-        <v>36.799999999999997</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B264" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C264" s="3">
-        <v>103.04</v>
+        <v>162.13</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B265" s="3">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C265" s="3">
-        <v>36.75</v>
+        <v>192.51</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B266" s="3">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C266" s="3">
-        <v>47.16</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B267" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C267" s="3">
-        <v>16.809999999999999</v>
+        <v>265.05</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B268" s="3">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="C268" s="3">
-        <v>27.68</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B269" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C269" s="3">
-        <v>28.69</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B270" s="3">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C270" s="3">
-        <v>37.31</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B271" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C271" s="3">
-        <v>97.49</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B272" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C272" s="3">
-        <v>103.46</v>
+        <v>16.809999999999999</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B273" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C273" s="3">
-        <v>126.24</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B274" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C274" s="3">
-        <v>144.27000000000001</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B275" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C275" s="3">
-        <v>154.62</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B276" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C276" s="3">
-        <v>508.2</v>
+        <v>97.49</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B277" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C277" s="3">
-        <v>5069</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B278" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C278" s="3">
-        <v>466.78</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B279" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C279" s="3">
-        <v>57.5</v>
+        <v>144.27000000000001</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B280" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C280" s="3">
-        <v>63.13</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B281" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C281" s="3">
-        <v>20789.41</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B282" s="3">
         <v>1</v>
       </c>
       <c r="C282" s="3">
-        <v>33057.85</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B283" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C283" s="3">
-        <v>83.5</v>
+        <v>466.78</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B284" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C284" s="3">
-        <v>45.88</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B285" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C285" s="3">
-        <v>50.71</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B286" s="3">
         <v>1</v>
       </c>
       <c r="C286" s="3">
-        <v>50.71</v>
+        <v>20789.41</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B287" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C287" s="3">
-        <v>51.75</v>
+        <v>33057.85</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B288" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C288" s="3">
-        <v>36.94</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B289" s="3">
         <v>24</v>
       </c>
       <c r="C289" s="3">
-        <v>36.94</v>
+        <v>81.650000000000006</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B290" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C290" s="3">
-        <v>67.28</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B291" s="3">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C291" s="3">
-        <v>65.099999999999994</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B292" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C292" s="3">
-        <v>65.53</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C293" s="3">
-        <v>65.53</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B294" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C294" s="3">
-        <v>90.9</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B295" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C295" s="3">
-        <v>29.89</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C296" s="3">
-        <v>33.479999999999997</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B297" s="3">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C297" s="3">
-        <v>422.09</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B298" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C298" s="3">
-        <v>1277.7</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B299" s="3">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C299" s="3">
-        <v>6.44</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B300" s="3">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C300" s="3">
-        <v>108.2</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B301" s="3">
         <v>1</v>
       </c>
       <c r="C301" s="3">
-        <v>4456.4799999999996</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B302" s="3">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="C302" s="3">
-        <v>6279</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B303" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C303" s="3">
-        <v>609.5</v>
+        <v>422.09</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B304" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C304" s="3">
-        <v>32.200000000000003</v>
+        <v>1277.7</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B305" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C305" s="3">
-        <v>32.200000000000003</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B306" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C306" s="3">
-        <v>32.200000000000003</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B307" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C307" s="3">
-        <v>32.200000000000003</v>
+        <v>4456.4799999999996</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B308" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C308" s="3">
-        <v>40.4</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B309" s="3">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="C309" s="3">
-        <v>36.06</v>
+        <v>609.5</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B310" s="3">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="C310" s="3">
-        <v>0</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B311" s="3">
         <v>13</v>
       </c>
       <c r="C311" s="3">
-        <v>44.5</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B312" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C312" s="3">
-        <v>56.01</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B313" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C313" s="3">
-        <v>57.63</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B314" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C314" s="3">
-        <v>60.78</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B315" s="3">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C315" s="3">
-        <v>42.49</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B316" s="3">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="C316" s="3">
-        <v>46.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B317" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C317" s="3">
-        <v>59.21</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B318" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C318" s="3">
-        <v>66.3</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B319" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C319" s="3">
-        <v>261.8</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B320" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C320" s="3">
-        <v>71.709999999999994</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B321" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C321" s="3">
-        <v>77.760000000000005</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B322" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C322" s="3">
-        <v>54.7</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B323" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C323" s="3">
-        <v>52.1</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B324" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C324" s="3">
-        <v>251.5</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B325" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C325" s="3">
-        <v>78.87</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B326" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C326" s="3">
-        <v>83.84</v>
+        <v>71.709999999999994</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B327" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C327" s="3">
-        <v>83.84</v>
+        <v>77.760000000000005</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B328" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C328" s="3">
-        <v>272.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B329" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C329" s="3">
-        <v>79.75</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B330" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C330" s="3">
-        <v>65.209999999999994</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B331" s="3">
         <v>12</v>
       </c>
       <c r="C331" s="3">
-        <v>83.84</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B332" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C332" s="3">
-        <v>284</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B333" s="3">
         <v>12</v>
       </c>
       <c r="C333" s="3">
-        <v>28.15</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B334" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C334" s="3">
-        <v>45.08</v>
+        <v>331.2</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B335" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C335" s="3">
-        <v>51.52</v>
+        <v>272.5</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B336" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C336" s="3">
-        <v>40.57</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B337" s="3">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C337" s="3">
-        <v>36.229999999999997</v>
+        <v>65.209999999999994</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B338" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C338" s="3">
-        <v>54.12</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B339" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C339" s="3">
-        <v>69.55</v>
+        <v>284</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B340" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C340" s="3">
-        <v>295.14999999999998</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B341" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C341" s="3">
-        <v>38.56</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B342" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C342" s="3">
-        <v>60.95</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B343" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C343" s="3">
-        <v>78.209999999999994</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B344" s="3">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="C344" s="3">
-        <v>44.93</v>
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B345" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C345" s="3">
-        <v>6578.46</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B346" s="3">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C346" s="3">
-        <v>173.09</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B347" s="3">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="C347" s="3">
-        <v>211.23</v>
+        <v>295.14999999999998</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B348" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C348" s="3">
-        <v>2314.8000000000002</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B349" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C349" s="3">
-        <v>791.3</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B350" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C350" s="3">
-        <v>31.6</v>
+        <v>78.209999999999994</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B351" s="3">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="C351" s="3">
-        <v>31.6</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B352" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>77</v>
+        <v>6578.46</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B353" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C353" s="3">
-        <v>281</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B354" s="3">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="C354" s="3">
-        <v>43.8</v>
+        <v>211.23</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B355" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C355" s="3">
-        <v>21.9</v>
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B356" s="3">
         <v>3</v>
       </c>
       <c r="C356" s="3">
-        <v>798.6</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B357" s="3">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="C357" s="3">
-        <v>23.19</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B358" s="3">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C358" s="3">
-        <v>8.24</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B359" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C359" s="3">
-        <v>13.72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B360" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C360" s="3">
-        <v>31.95</v>
+        <v>281</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B361" s="3">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="C361" s="3">
-        <v>16.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B362" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C362" s="3">
-        <v>36.869999999999997</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B363" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C363" s="3">
-        <v>31.48</v>
+        <v>798.6</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B364" s="3">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C364" s="3">
-        <v>21.9</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B365" s="3">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C365" s="3">
-        <v>23.19</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B366" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C366" s="3">
-        <v>19.55</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B367" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C367" s="3">
-        <v>19.07</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B368" s="3">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C368" s="3">
-        <v>21.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B369" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C369" s="3">
-        <v>57.96</v>
+        <v>36.869999999999997</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B370" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C370" s="3">
-        <v>862.7</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B371" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C371" s="3">
-        <v>56.93</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B372" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C372" s="3">
-        <v>1265</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B373" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C373" s="3">
-        <v>76</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B374" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C374" s="3">
-        <v>267.85000000000002</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B375" s="3">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C375" s="3">
-        <v>74.7</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B376" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C376" s="3">
-        <v>327.3</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B377" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C377" s="3">
-        <v>72.13</v>
+        <v>862.7</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B378" s="3">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C378" s="3">
-        <v>302.39999999999998</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B379" s="3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C379" s="3">
-        <v>36.799999999999997</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B380" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C380" s="3">
-        <v>428.5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B381" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C381" s="3">
-        <v>450.22</v>
+        <v>267.85000000000002</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B382" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C382" s="3">
-        <v>465.7</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B383" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C383" s="3">
-        <v>38.25</v>
+        <v>327.3</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B384" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C384" s="3">
-        <v>87.49</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B385" s="3">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C385" s="3">
-        <v>63.13</v>
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B386" s="3">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C386" s="3">
-        <v>377.78</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B387" s="3">
         <v>2</v>
       </c>
       <c r="C387" s="3">
-        <v>3333.85</v>
+        <v>428.5</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B388" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C388" s="3">
-        <v>374.67</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B389" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C389" s="3">
-        <v>120.06</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B390" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C390" s="3">
-        <v>54.2</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B391" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="C391" s="3">
-        <v>54.2</v>
+        <v>87.49</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B392" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C392" s="3">
-        <v>31.5</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B393" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C393" s="3">
-        <v>114.09</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B394" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C394" s="3">
-        <v>139.9</v>
+        <v>3333.85</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B395" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C395" s="3">
-        <v>35.94</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B396" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C396" s="3">
-        <v>140.26</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B397" s="3">
         <v>1</v>
       </c>
       <c r="C397" s="3">
-        <v>370.53</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B398" s="3">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C398" s="3">
-        <v>30.9</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B399" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C399" s="3">
-        <v>4772.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B400" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C400" s="3">
-        <v>375.7</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B401" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C401" s="3">
-        <v>516.46</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B402" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C402" s="3">
-        <v>185.15</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B403" s="3">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C403" s="3">
-        <v>11.5</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B404" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C404" s="3">
-        <v>724.5</v>
+        <v>370.53</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B405" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C405" s="3">
-        <v>450.22</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B406" s="3">
         <v>1</v>
       </c>
       <c r="C406" s="3">
-        <v>461.23</v>
+        <v>4772.5</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B407" s="3">
         <v>1</v>
       </c>
       <c r="C407" s="3">
-        <v>518.41999999999996</v>
+        <v>375.7</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B408" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C408" s="3">
-        <v>348.08</v>
+        <v>516.46</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B409" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C409" s="3">
-        <v>33.479999999999997</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B410" s="3">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C410" s="3">
-        <v>35.79</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B411" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C411" s="3">
-        <v>377.7</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B412" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C412" s="3">
-        <v>33.21</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B413" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C413" s="3">
-        <v>27.16</v>
+        <v>461.23</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B414" s="3">
         <v>1</v>
       </c>
       <c r="C414" s="3">
-        <v>361.41</v>
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B415" s="3">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C415" s="3">
-        <v>29.25</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B416" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C416" s="3">
-        <v>29.26</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B417" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C417" s="3">
-        <v>304.54000000000002</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B418" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C418" s="3">
-        <v>34.049999999999997</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B419" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C419" s="3">
-        <v>57.7</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B420" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C420" s="3">
-        <v>90.9</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B421" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C421" s="3">
-        <v>44.3</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B422" s="3">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C422" s="3">
-        <v>44.31</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B423" s="3">
         <v>1</v>
       </c>
       <c r="C423" s="3">
-        <v>7173.59</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B424" s="3">
         <v>1</v>
       </c>
       <c r="C424" s="3">
-        <v>677.79</v>
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B425" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C425" s="3">
-        <v>167.33</v>
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B426" s="3">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C426" s="3">
-        <v>167.33</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B427" s="3">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C427" s="3">
-        <v>191.01</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B428" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C428" s="3">
-        <v>2335.67</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B429" s="3">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="C429" s="3">
-        <v>62.04</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B430" s="3">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="C430" s="3">
-        <v>62.04</v>
+        <v>7173.59</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B431" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C431" s="3">
-        <v>8139.6</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B432" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C432" s="3">
-        <v>235.53</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B433" s="3">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C433" s="3">
-        <v>259.8</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B434" s="3">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C434" s="3">
-        <v>310.2</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B435" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C435" s="3">
-        <v>36.43</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B436" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C436" s="3">
-        <v>73.42</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B437" s="3">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="C437" s="3">
-        <v>319.60000000000002</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B438" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C438" s="3">
-        <v>62.6</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B439" s="3">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C439" s="3">
-        <v>312.8</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B440" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C440" s="3">
-        <v>67.28</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B441" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C441" s="3">
-        <v>67.28</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B442" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C442" s="3">
-        <v>1138.5</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B443" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C443" s="3">
-        <v>1138.5</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B444" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C444" s="3">
-        <v>48.76</v>
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B445" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C445" s="3">
-        <v>242.34</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B446" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C446" s="3">
-        <v>54.09</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B447" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C447" s="3">
-        <v>54.1</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B448" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C448" s="3">
-        <v>255.03</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B449" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C449" s="3">
-        <v>220.8</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B450" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C450" s="3">
-        <v>255.03</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B451" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C451" s="3">
-        <v>68.86</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B452" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C452" s="3">
-        <v>344.28</v>
+        <v>242.34</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B453" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C453" s="3">
-        <v>60.29</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B454" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C454" s="3">
-        <v>261.8</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B455" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C455" s="3">
-        <v>261.8</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B456" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C456" s="3">
-        <v>30.58</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B457" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C457" s="3">
-        <v>30.58</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B458" s="3">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C458" s="3">
-        <v>16.95</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B459" s="3">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C459" s="3">
-        <v>24.95</v>
+        <v>344.28</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B460" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C460" s="3">
-        <v>641.49</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B461" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C461" s="3">
-        <v>39.57</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B462" s="3">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C462" s="3">
-        <v>51.83</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B463" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C463" s="3">
-        <v>33.840000000000003</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B464" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C464" s="3">
-        <v>150.15</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B465" s="3">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C465" s="3">
-        <v>144.5</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B466" s="3">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C466" s="3">
-        <v>100.93</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B467" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C467" s="3">
-        <v>124.5</v>
+        <v>641.49</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B468" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C468" s="3">
-        <v>27.21</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B469" s="3">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="C469" s="3">
-        <v>24.79</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B470" s="3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C470" s="3">
-        <v>37.1</v>
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B471" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C471" s="3">
-        <v>178.04</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B472" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C472" s="3">
-        <v>23.88</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B473" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C473" s="3">
-        <v>8.26</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B474" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C474" s="3">
-        <v>859.21</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B475" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C475" s="3">
-        <v>242.4</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B476" s="3">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C476" s="3">
-        <v>5000</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B477" s="3">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="C477" s="3">
-        <v>20.68</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B478" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C478" s="3">
-        <v>97.54</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B479" s="3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C479" s="3">
-        <v>304.02999999999997</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B480" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C480" s="3">
-        <v>1934.56</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B481" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C481" s="3">
-        <v>230.99</v>
+        <v>859.21</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B482" s="3">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="C482" s="3">
-        <v>33.39</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
+        <v>401</v>
+      </c>
+      <c r="B483" s="3">
+        <v>3</v>
+      </c>
+      <c r="C483" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" t="s">
+        <v>402</v>
+      </c>
+      <c r="B484" s="3">
+        <v>93</v>
+      </c>
+      <c r="C484" s="3">
+        <v>20.68</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" t="s">
+        <v>403</v>
+      </c>
+      <c r="B485" s="3">
+        <v>31</v>
+      </c>
+      <c r="C485" s="3">
+        <v>97.54</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486" t="s">
+        <v>404</v>
+      </c>
+      <c r="B486" s="3">
+        <v>10</v>
+      </c>
+      <c r="C486" s="3">
+        <v>304.02999999999997</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487" t="s">
+        <v>405</v>
+      </c>
+      <c r="B487" s="3">
+        <v>6</v>
+      </c>
+      <c r="C487" s="3">
+        <v>1934.56</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488" t="s">
+        <v>406</v>
+      </c>
+      <c r="B488" s="3">
+        <v>6</v>
+      </c>
+      <c r="C488" s="3">
+        <v>230.99</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489" t="s">
+        <v>407</v>
+      </c>
+      <c r="B489" s="3">
+        <v>96</v>
+      </c>
+      <c r="C489" s="3">
+        <v>33.39</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490" t="s">
         <v>408</v>
       </c>
-      <c r="B483" s="3">
+      <c r="B490" s="3">
         <v>48</v>
       </c>
-      <c r="C483" s="3">
+      <c r="C490" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -5084,7 +5084,7 @@
         <v>85</v>
       </c>
       <c r="C316" s="3">
-        <v>0</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="317" spans="1:3">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="408">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -593,9 +593,6 @@
   </si>
   <si>
     <t>RAV FO SAE 5W30 1L</t>
-  </si>
-  <si>
-    <t>RAV FO SAE 5W30 4L</t>
   </si>
   <si>
     <t>RAV FO SAE 5W30 5L</t>
@@ -1604,10 +1601,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C490"/>
+  <dimension ref="A1:C481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="1" max="1" width="49.85546875" customWidth="1"/>
     <col min="2" max="3" width="15.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1627,7 +1624,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -1660,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3">
         <v>239.2</v>
@@ -1693,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3">
         <v>407.86</v>
@@ -1704,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3">
         <v>635.11</v>
@@ -1715,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3">
         <v>309.52</v>
@@ -1726,7 +1723,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3">
         <v>343.45</v>
@@ -1946,7 +1943,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C31" s="3">
         <v>376.62</v>
@@ -1957,7 +1954,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="3">
         <v>409.88</v>
@@ -2067,7 +2064,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C42" s="3">
         <v>182.58</v>
@@ -2199,7 +2196,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="3">
-        <v>3194</v>
+        <v>3044</v>
       </c>
       <c r="C54" s="3">
         <v>13</v>
@@ -2474,7 +2471,7 @@
         <v>67</v>
       </c>
       <c r="B79" s="3">
-        <v>451</v>
+        <v>385</v>
       </c>
       <c r="C79" s="3">
         <v>16.600000000000001</v>
@@ -2485,7 +2482,7 @@
         <v>68</v>
       </c>
       <c r="B80" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80" s="3">
         <v>60.08</v>
@@ -2507,7 +2504,7 @@
         <v>69</v>
       </c>
       <c r="B82" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C82" s="3">
         <v>76.569999999999993</v>
@@ -2562,7 +2559,7 @@
         <v>72</v>
       </c>
       <c r="B87" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C87" s="3">
         <v>79.5</v>
@@ -2584,7 +2581,7 @@
         <v>73</v>
       </c>
       <c r="B89" s="3">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C89" s="3">
         <v>16.98</v>
@@ -2628,7 +2625,7 @@
         <v>75</v>
       </c>
       <c r="B93" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C93" s="3">
         <v>89.39</v>
@@ -2760,7 +2757,7 @@
         <v>86</v>
       </c>
       <c r="B105" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C105" s="3">
         <v>16.559999999999999</v>
@@ -2771,7 +2768,7 @@
         <v>87</v>
       </c>
       <c r="B106" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C106" s="3">
         <v>82.88</v>
@@ -2977,13 +2974,13 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B125" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C125" s="3">
-        <v>43.99</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2991,73 +2988,73 @@
         <v>104</v>
       </c>
       <c r="B126" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C126" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B127" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B128" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C128" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B129" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C129" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B130" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C130" s="3">
-        <v>69.56</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B131" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C131" s="3">
-        <v>59.68</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B132" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C132" s="3">
         <v>56.93</v>
@@ -3068,10 +3065,10 @@
         <v>110</v>
       </c>
       <c r="B133" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133" s="3">
-        <v>56.93</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3079,32 +3076,32 @@
         <v>110</v>
       </c>
       <c r="B134" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C134" s="3">
-        <v>70.38</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B135" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C135" s="3">
-        <v>80.73</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B136" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C136" s="3">
-        <v>98.95</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -3112,21 +3109,21 @@
         <v>112</v>
       </c>
       <c r="B137" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C137" s="3">
-        <v>92.91</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B138" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C138" s="3">
-        <v>93.25</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3134,21 +3131,21 @@
         <v>113</v>
       </c>
       <c r="B139" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C139" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B140" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C140" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3156,73 +3153,73 @@
         <v>114</v>
       </c>
       <c r="B141" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C141" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C142" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B143" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C143" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B144" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C144" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B145" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C145" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B146" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C146" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B147" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C147" s="3">
         <v>69.56</v>
@@ -3230,13 +3227,13 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B148" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C148" s="3">
-        <v>69.56</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -3244,7 +3241,7 @@
         <v>121</v>
       </c>
       <c r="B149" s="3">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C149" s="3">
         <v>52.17</v>
@@ -3252,24 +3249,24 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B150" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C150" s="3">
-        <v>52.17</v>
+        <v>208.66</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B151" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C151" s="3">
-        <v>208.66</v>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -3277,32 +3274,32 @@
         <v>123</v>
       </c>
       <c r="B152" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C152" s="3">
-        <v>79.349999999999994</v>
+        <v>88.87</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B153" s="3">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C153" s="3">
-        <v>88.87</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B154" s="3">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="C154" s="3">
-        <v>67.28</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -3310,32 +3307,32 @@
         <v>125</v>
       </c>
       <c r="B155" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C155" s="3">
-        <v>62.11</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C156" s="3">
-        <v>69.55</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B157" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C157" s="3">
-        <v>63.89</v>
+        <v>149.91999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -3343,43 +3340,43 @@
         <v>127</v>
       </c>
       <c r="B158" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C158" s="3">
-        <v>149.91999999999999</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B159" s="3">
         <v>5</v>
       </c>
       <c r="C159" s="3">
-        <v>95.05</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B160" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C160" s="3">
-        <v>38.57</v>
+        <v>207.31</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B161" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C161" s="3">
-        <v>207.31</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -3387,106 +3384,106 @@
         <v>130</v>
       </c>
       <c r="B162" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C162" s="3">
-        <v>58.24</v>
+        <v>65.23</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B163" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C163" s="3">
-        <v>65.23</v>
+        <v>325.87</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B164" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C164" s="3">
-        <v>325.87</v>
+        <v>5165.8</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165" s="3">
-        <v>5165.8</v>
+        <v>511.75</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B166" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C166" s="3">
-        <v>511.75</v>
+        <v>572.70000000000005</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B167" s="3">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C167" s="3">
-        <v>572.70000000000005</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B168" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C168" s="3">
-        <v>66.98</v>
+        <v>367.42</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B169" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C169" s="3">
-        <v>367.42</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B170" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C170" s="3">
-        <v>51.52</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B171" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C171" s="3">
         <v>23.19</v>
@@ -3497,7 +3494,7 @@
         <v>139</v>
       </c>
       <c r="B172" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C172" s="3">
         <v>23.19</v>
@@ -3505,43 +3502,43 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C173" s="3">
-        <v>23.19</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B174" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C174" s="3">
-        <v>69.55</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B175" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C175" s="3">
-        <v>3169.7</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B176" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C176" s="3">
         <v>81.14</v>
@@ -3549,24 +3546,24 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B177" s="3">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C177" s="3">
-        <v>81.14</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B178" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C178" s="3">
-        <v>66.98</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3577,7 +3574,7 @@
         <v>3</v>
       </c>
       <c r="C179" s="3">
-        <v>53.83</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3585,21 +3582,21 @@
         <v>145</v>
       </c>
       <c r="B180" s="3">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C180" s="3">
-        <v>60.28</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B181" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C181" s="3">
-        <v>60.29</v>
+        <v>82.65</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3607,43 +3604,43 @@
         <v>146</v>
       </c>
       <c r="B182" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C182" s="3">
-        <v>82.65</v>
+        <v>93.35</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B183" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C183" s="3">
-        <v>93.35</v>
+        <v>1217.1600000000001</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B184" s="3">
         <v>1</v>
       </c>
       <c r="C184" s="3">
-        <v>1217.1600000000001</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C185" s="3">
-        <v>3079</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3651,21 +3648,21 @@
         <v>149</v>
       </c>
       <c r="B186" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C186" s="3">
-        <v>43.7</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C187" s="3">
-        <v>48.95</v>
+        <v>64.59</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3673,32 +3670,32 @@
         <v>150</v>
       </c>
       <c r="B188" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C188" s="3">
-        <v>64.59</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C189" s="3">
-        <v>72.33</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B190" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C190" s="3">
-        <v>284.19</v>
+        <v>132.19999999999999</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3706,29 +3703,29 @@
         <v>152</v>
       </c>
       <c r="B191" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C191" s="3">
-        <v>132.19999999999999</v>
+        <v>75.260000000000005</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B192" s="3">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C192" s="3">
-        <v>75.260000000000005</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B193" s="3">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C193" s="3">
         <v>32.200000000000003</v>
@@ -3736,46 +3733,46 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B194" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C194" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C195" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B196" s="3">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C196" s="3">
-        <v>32.200000000000003</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B197" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C197" s="3">
-        <v>115.01</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -3783,7 +3780,7 @@
         <v>158</v>
       </c>
       <c r="B198" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C198" s="3">
         <v>38.39</v>
@@ -3791,101 +3788,101 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C199" s="3">
-        <v>38.39</v>
+        <v>151.47999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B200" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C200" s="3">
-        <v>151.47999999999999</v>
+        <v>181.68</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B201" s="3">
         <v>12</v>
       </c>
       <c r="C201" s="3">
-        <v>181.68</v>
+        <v>20.059999999999999</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B202" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C202" s="3">
-        <v>20.059999999999999</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B203" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C203" s="3">
-        <v>12.88</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B204" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C204" s="3">
-        <v>26.73</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B205" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C205" s="3">
-        <v>29.95</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B206" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C206" s="3">
-        <v>58.68</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B207" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C207" s="3">
-        <v>79.98</v>
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -3893,32 +3890,32 @@
         <v>167</v>
       </c>
       <c r="B208" s="3">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C208" s="3">
-        <v>34.619999999999997</v>
+        <v>38.770000000000003</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B209" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C209" s="3">
-        <v>38.770000000000003</v>
+        <v>107.35</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B210" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C210" s="3">
-        <v>107.35</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3926,54 +3923,54 @@
         <v>169</v>
       </c>
       <c r="B211" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C211" s="3">
-        <v>55.2</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B212" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C212" s="3">
-        <v>61.83</v>
+        <v>243.16</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B213" s="3">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C213" s="3">
-        <v>243.16</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B214" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C214" s="3">
-        <v>32.200000000000003</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B215" s="3">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C215" s="3">
-        <v>63.78</v>
+        <v>67.849999999999994</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -3981,76 +3978,76 @@
         <v>173</v>
       </c>
       <c r="B216" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C216" s="3">
-        <v>67.849999999999994</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B217" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C217" s="3">
-        <v>75.989999999999995</v>
+        <v>297.64999999999998</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B218" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C218" s="3">
-        <v>297.64999999999998</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B219" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C219" s="3">
-        <v>77.28</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B220" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C220" s="3">
-        <v>75.989999999999995</v>
+        <v>342.24</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B221" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C221" s="3">
-        <v>342.24</v>
+        <v>633.75</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B222" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="C222" s="3">
-        <v>633.75</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -4058,43 +4055,43 @@
         <v>179</v>
       </c>
       <c r="B223" s="3">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C223" s="3">
-        <v>36.799999999999997</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B224" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C224" s="3">
-        <v>50.51</v>
+        <v>768.2</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B225" s="3">
         <v>2</v>
       </c>
       <c r="C225" s="3">
-        <v>768.2</v>
+        <v>787.75</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B226" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C226" s="3">
-        <v>787.75</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -4102,21 +4099,21 @@
         <v>182</v>
       </c>
       <c r="B227" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C227" s="3">
-        <v>109.26</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B228" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C228" s="3">
-        <v>122.36</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -4124,109 +4121,109 @@
         <v>183</v>
       </c>
       <c r="B229" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C229" s="3">
-        <v>31.98</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B230" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C230" s="3">
-        <v>35.81</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B231" s="3">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C231" s="3">
-        <v>59.25</v>
+        <v>260</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B232" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C232" s="3">
-        <v>260</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B233" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C233" s="3">
-        <v>43.07</v>
+        <v>48.23</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B234" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C234" s="3">
-        <v>48.23</v>
+        <v>221.86</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B235" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C235" s="3">
-        <v>221.86</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B236" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C236" s="3">
-        <v>74.7</v>
+        <v>296.3</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B237" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C237" s="3">
-        <v>296.3</v>
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B238" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C238" s="3">
-        <v>141.80000000000001</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -4234,54 +4231,54 @@
         <v>192</v>
       </c>
       <c r="B239" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C239" s="3">
-        <v>29.25</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B240" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C240" s="3">
-        <v>41.4</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B241" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C241" s="3">
-        <v>141.80000000000001</v>
+        <v>2189.02</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B242" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C242" s="3">
-        <v>173.3</v>
+        <v>453.22</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B243" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C243" s="3">
-        <v>2189.02</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -4289,10 +4286,10 @@
         <v>196</v>
       </c>
       <c r="B244" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C244" s="3">
-        <v>453.22</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -4300,87 +4297,87 @@
         <v>197</v>
       </c>
       <c r="B245" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C245" s="3">
-        <v>48.65</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B246" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C246" s="3">
-        <v>31.3</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B247" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C247" s="3">
-        <v>126.63</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B248" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C248" s="3">
-        <v>69.56</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B249" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C249" s="3">
-        <v>42.44</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B250" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C250" s="3">
-        <v>42.43</v>
+        <v>179</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B251" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C251" s="3">
-        <v>145.94</v>
+        <v>2060.8000000000002</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B252" s="3">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C252" s="3">
-        <v>179</v>
+        <v>51</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -4388,10 +4385,10 @@
         <v>204</v>
       </c>
       <c r="B253" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C253" s="3">
-        <v>2060.8000000000002</v>
+        <v>51</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -4399,32 +4396,32 @@
         <v>205</v>
       </c>
       <c r="B254" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C254" s="3">
-        <v>51</v>
+        <v>183.41</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B255" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C255" s="3">
-        <v>51</v>
+        <v>206.33</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B256" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C256" s="3">
-        <v>183.41</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -4432,10 +4429,10 @@
         <v>207</v>
       </c>
       <c r="B257" s="3">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C257" s="3">
-        <v>206.33</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -4443,21 +4440,21 @@
         <v>208</v>
       </c>
       <c r="B258" s="3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C258" s="3">
-        <v>33.479999999999997</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B259" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C259" s="3">
-        <v>33.479999999999997</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -4465,10 +4462,10 @@
         <v>209</v>
       </c>
       <c r="B260" s="3">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C260" s="3">
-        <v>46.06</v>
+        <v>5345.33</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -4476,120 +4473,120 @@
         <v>210</v>
       </c>
       <c r="B261" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C261" s="3">
-        <v>4667</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B262" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C262" s="3">
-        <v>5345.33</v>
+        <v>192.51</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B263" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C263" s="3">
-        <v>170.78</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B264" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C264" s="3">
-        <v>162.13</v>
+        <v>265.05</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B265" s="3">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C265" s="3">
-        <v>192.51</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B266" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C266" s="3">
-        <v>59.7</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B267" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C267" s="3">
-        <v>265.05</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B268" s="3">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="C268" s="3">
-        <v>36.799999999999997</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B269" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C269" s="3">
-        <v>103.04</v>
+        <v>16.809999999999999</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B270" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C270" s="3">
-        <v>36.75</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B271" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C271" s="3">
-        <v>47.16</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -4597,10 +4594,10 @@
         <v>219</v>
       </c>
       <c r="B272" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C272" s="3">
-        <v>16.809999999999999</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -4608,10 +4605,10 @@
         <v>220</v>
       </c>
       <c r="B273" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C273" s="3">
-        <v>27.68</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -4619,645 +4616,645 @@
         <v>220</v>
       </c>
       <c r="B274" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C274" s="3">
-        <v>28.69</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B275" s="3">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C275" s="3">
-        <v>37.31</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B276" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C276" s="3">
-        <v>97.49</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B277" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C277" s="3">
-        <v>103.46</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B278" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C278" s="3">
-        <v>126.24</v>
+        <v>466.78</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B279" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C279" s="3">
-        <v>144.27000000000001</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B280" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C280" s="3">
-        <v>154.62</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B281" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C281" s="3">
-        <v>508.2</v>
+        <v>20789.41</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B282" s="3">
         <v>1</v>
       </c>
       <c r="C282" s="3">
-        <v>5069</v>
+        <v>33057.85</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B283" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C283" s="3">
-        <v>466.78</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B284" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C284" s="3">
-        <v>57.5</v>
+        <v>81.650000000000006</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B285" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C285" s="3">
-        <v>63.13</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B286" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C286" s="3">
-        <v>20789.41</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B287" s="3">
         <v>1</v>
       </c>
       <c r="C287" s="3">
-        <v>33057.85</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B288" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C288" s="3">
-        <v>83.5</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B289" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C289" s="3">
-        <v>81.650000000000006</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B290" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C290" s="3">
-        <v>45.88</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B291" s="3">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C291" s="3">
-        <v>50.71</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B292" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C292" s="3">
-        <v>50.71</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B293" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C293" s="3">
-        <v>51.75</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B294" s="3">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C294" s="3">
-        <v>36.94</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B295" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C295" s="3">
-        <v>36.94</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B296" s="3">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C296" s="3">
-        <v>67.28</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B297" s="3">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C297" s="3">
-        <v>65.099999999999994</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B298" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C298" s="3">
-        <v>65.53</v>
+        <v>422.09</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B299" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C299" s="3">
-        <v>65.53</v>
+        <v>1277.7</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B300" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C300" s="3">
-        <v>90.9</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B301" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C301" s="3">
-        <v>29.89</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B302" s="3">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="C302" s="3">
-        <v>33.479999999999997</v>
+        <v>4456.4799999999996</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B303" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C303" s="3">
-        <v>422.09</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B304" s="3">
         <v>2</v>
       </c>
       <c r="C304" s="3">
-        <v>1277.7</v>
+        <v>609.5</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B305" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C305" s="3">
-        <v>6.44</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B306" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C306" s="3">
-        <v>108.2</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B307" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C307" s="3">
-        <v>4456.4799999999996</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B308" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C308" s="3">
-        <v>6279</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B309" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C309" s="3">
-        <v>609.5</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B310" s="3">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C310" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B311" s="3">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C311" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B312" s="3">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C312" s="3">
-        <v>32.200000000000003</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B313" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C313" s="3">
-        <v>32.200000000000003</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B314" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C314" s="3">
-        <v>40.4</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B315" s="3">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="C315" s="3">
-        <v>36.06</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B316" s="3">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="C316" s="3">
-        <v>36.06</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B317" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C317" s="3">
-        <v>44.5</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B318" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C318" s="3">
-        <v>56.01</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B319" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C319" s="3">
-        <v>57.63</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B320" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C320" s="3">
-        <v>60.78</v>
+        <v>71.709999999999994</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B321" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C321" s="3">
-        <v>42.49</v>
+        <v>77.760000000000005</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B322" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C322" s="3">
-        <v>46.28</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B323" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C323" s="3">
-        <v>59.21</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B324" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C324" s="3">
-        <v>66.3</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B325" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C325" s="3">
-        <v>261.8</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B326" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C326" s="3">
-        <v>71.709999999999994</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B327" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C327" s="3">
-        <v>77.760000000000005</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B328" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C328" s="3">
-        <v>54.7</v>
+        <v>331.2</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B329" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C329" s="3">
-        <v>52.1</v>
+        <v>272.5</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B330" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C330" s="3">
-        <v>251.5</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B331" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C331" s="3">
-        <v>78.87</v>
+        <v>65.209999999999994</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B332" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C332" s="3">
         <v>83.84</v>
@@ -5265,1739 +5262,1640 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B333" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C333" s="3">
-        <v>83.84</v>
+        <v>284</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B334" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C334" s="3">
-        <v>331.2</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B335" s="3">
         <v>2</v>
       </c>
       <c r="C335" s="3">
-        <v>272.5</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B336" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C336" s="3">
-        <v>79.75</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B337" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C337" s="3">
-        <v>65.209999999999994</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B338" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C338" s="3">
-        <v>83.84</v>
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B339" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C339" s="3">
-        <v>284</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B340" s="3">
         <v>12</v>
       </c>
       <c r="C340" s="3">
-        <v>28.15</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B341" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C341" s="3">
-        <v>45.08</v>
+        <v>295.14999999999998</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B342" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C342" s="3">
-        <v>51.52</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B343" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C343" s="3">
-        <v>40.57</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B344" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C344" s="3">
-        <v>36.229999999999997</v>
+        <v>78.209999999999994</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B345" s="3">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="C345" s="3">
-        <v>54.12</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B346" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C346" s="3">
-        <v>69.55</v>
+        <v>6578.46</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B347" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C347" s="3">
-        <v>295.14999999999998</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B348" s="3">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C348" s="3">
-        <v>38.56</v>
+        <v>211.23</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B349" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C349" s="3">
-        <v>60.95</v>
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B350" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C350" s="3">
-        <v>78.209999999999994</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B351" s="3">
-        <v>181</v>
+        <v>25</v>
       </c>
       <c r="C351" s="3">
-        <v>44.93</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B352" s="3">
         <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>6578.46</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B353" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C353" s="3">
-        <v>173.09</v>
+        <v>77</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B354" s="3">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C354" s="3">
-        <v>211.23</v>
+        <v>281</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B355" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C355" s="3">
-        <v>2314.8000000000002</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B356" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C356" s="3">
-        <v>791.3</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B357" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C357" s="3">
-        <v>31.6</v>
+        <v>798.6</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B358" s="3">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="C358" s="3">
-        <v>31.6</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B359" s="3">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C359" s="3">
-        <v>77</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B360" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C360" s="3">
-        <v>281</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B361" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C361" s="3">
-        <v>43.8</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B362" s="3">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C362" s="3">
-        <v>21.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B363" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C363" s="3">
-        <v>798.6</v>
+        <v>36.869999999999997</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B364" s="3">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C364" s="3">
-        <v>23.19</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B365" s="3">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C365" s="3">
-        <v>8.24</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B366" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C366" s="3">
-        <v>13.72</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B367" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C367" s="3">
-        <v>31.95</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B368" s="3">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="C368" s="3">
-        <v>16.2</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B369" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C369" s="3">
-        <v>36.869999999999997</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B370" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C370" s="3">
-        <v>31.48</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B371" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C371" s="3">
-        <v>21.9</v>
+        <v>862.7</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B372" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C372" s="3">
-        <v>23.19</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B373" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C373" s="3">
-        <v>19.55</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B374" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C374" s="3">
-        <v>19.07</v>
+        <v>76</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B375" s="3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C375" s="3">
-        <v>21.9</v>
+        <v>267.85000000000002</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B376" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C376" s="3">
-        <v>57.96</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B377" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C377" s="3">
-        <v>862.7</v>
+        <v>327.3</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B378" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C378" s="3">
-        <v>56.93</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B379" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C379" s="3">
-        <v>1265</v>
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B380" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C380" s="3">
-        <v>76</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B381" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C381" s="3">
-        <v>267.85000000000002</v>
+        <v>428.5</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B382" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C382" s="3">
-        <v>74.7</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B383" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C383" s="3">
-        <v>327.3</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B384" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C384" s="3">
-        <v>72.13</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B385" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C385" s="3">
-        <v>302.39999999999998</v>
+        <v>87.49</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B386" s="3">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C386" s="3">
-        <v>36.799999999999997</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B387" s="3">
         <v>2</v>
       </c>
       <c r="C387" s="3">
-        <v>428.5</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B388" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C388" s="3">
-        <v>450.22</v>
+        <v>3333.85</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B389" s="3">
         <v>4</v>
       </c>
       <c r="C389" s="3">
-        <v>465.7</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B390" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C390" s="3">
-        <v>38.25</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B391" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C391" s="3">
-        <v>87.49</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B392" s="3">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C392" s="3">
-        <v>63.13</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B393" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C393" s="3">
-        <v>377.78</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B394" s="3">
         <v>2</v>
       </c>
       <c r="C394" s="3">
-        <v>3333.85</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B395" s="3">
         <v>4</v>
       </c>
       <c r="C395" s="3">
-        <v>374.67</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B396" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C396" s="3">
-        <v>120.06</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B397" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C397" s="3">
-        <v>54.2</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B398" s="3">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C398" s="3">
-        <v>54.2</v>
+        <v>370.53</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B399" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C399" s="3">
-        <v>31.5</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B400" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C400" s="3">
-        <v>114.09</v>
+        <v>4772.5</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B401" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C401" s="3">
-        <v>139.9</v>
+        <v>375.7</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B402" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C402" s="3">
-        <v>35.94</v>
+        <v>516.46</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B403" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C403" s="3">
-        <v>140.26</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B404" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C404" s="3">
-        <v>370.53</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B405" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C405" s="3">
-        <v>30.9</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B406" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C406" s="3">
-        <v>4772.5</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B407" s="3">
         <v>1</v>
       </c>
       <c r="C407" s="3">
-        <v>375.7</v>
+        <v>461.23</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B408" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C408" s="3">
-        <v>516.46</v>
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B409" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C409" s="3">
-        <v>185.15</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B410" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C410" s="3">
-        <v>11.5</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B411" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C411" s="3">
-        <v>724.5</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B412" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C412" s="3">
-        <v>450.22</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B413" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C413" s="3">
-        <v>461.23</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B414" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C414" s="3">
-        <v>518.41999999999996</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B415" s="3">
         <v>1</v>
       </c>
       <c r="C415" s="3">
-        <v>348.08</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B416" s="3">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C416" s="3">
-        <v>33.479999999999997</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B417" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C417" s="3">
-        <v>35.79</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B418" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C418" s="3">
-        <v>377.7</v>
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B419" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C419" s="3">
-        <v>33.21</v>
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B420" s="3">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C420" s="3">
-        <v>27.16</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B421" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C421" s="3">
-        <v>361.41</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B422" s="3">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C422" s="3">
-        <v>29.25</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B423" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C423" s="3">
-        <v>29.26</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B424" s="3">
         <v>1</v>
       </c>
       <c r="C424" s="3">
-        <v>304.54000000000002</v>
+        <v>7173.59</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B425" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C425" s="3">
-        <v>34.049999999999997</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B426" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C426" s="3">
-        <v>57.7</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B427" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C427" s="3">
-        <v>90.9</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B428" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C428" s="3">
-        <v>44.3</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B429" s="3">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C429" s="3">
-        <v>44.31</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B430" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C430" s="3">
-        <v>7173.59</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B431" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C431" s="3">
-        <v>677.79</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B432" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C432" s="3">
-        <v>167.33</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B433" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C433" s="3">
-        <v>167.33</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B434" s="3">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="C434" s="3">
-        <v>191.01</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B435" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C435" s="3">
-        <v>2335.67</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B436" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C436" s="3">
-        <v>62.04</v>
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B437" s="3">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C437" s="3">
-        <v>62.04</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B438" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C438" s="3">
-        <v>8139.6</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B439" s="3">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C439" s="3">
-        <v>235.53</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B440" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C440" s="3">
-        <v>259.8</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B441" s="3">
         <v>1</v>
       </c>
       <c r="C441" s="3">
-        <v>310.2</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B442" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C442" s="3">
-        <v>36.43</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B443" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C443" s="3">
-        <v>73.42</v>
+        <v>242.34</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B444" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C444" s="3">
-        <v>319.60000000000002</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B445" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C445" s="3">
-        <v>62.6</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B446" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C446" s="3">
-        <v>312.8</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B447" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C447" s="3">
-        <v>67.28</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B448" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C448" s="3">
-        <v>67.28</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B449" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C449" s="3">
-        <v>1138.5</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B450" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C450" s="3">
-        <v>1138.5</v>
+        <v>344.28</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B451" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C451" s="3">
-        <v>48.76</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B452" s="3">
         <v>3</v>
       </c>
       <c r="C452" s="3">
-        <v>242.34</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B453" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C453" s="3">
-        <v>54.09</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B454" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C454" s="3">
-        <v>54.1</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B455" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C455" s="3">
-        <v>255.03</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B456" s="3">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C456" s="3">
-        <v>220.8</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B457" s="3">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C457" s="3">
-        <v>255.03</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B458" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C458" s="3">
-        <v>68.86</v>
+        <v>641.49</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B459" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C459" s="3">
-        <v>344.28</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B460" s="3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C460" s="3">
-        <v>60.29</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B461" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C461" s="3">
-        <v>261.8</v>
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B462" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C462" s="3">
-        <v>261.8</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B463" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C463" s="3">
-        <v>30.58</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B464" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C464" s="3">
-        <v>30.58</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B465" s="3">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C465" s="3">
-        <v>16.95</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B466" s="3">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C466" s="3">
-        <v>24.95</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B467" s="3">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C467" s="3">
-        <v>641.49</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B468" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C468" s="3">
-        <v>39.57</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B469" s="3">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C469" s="3">
-        <v>51.83</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B470" s="3">
         <v>48</v>
       </c>
       <c r="C470" s="3">
-        <v>33.840000000000003</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B471" s="3">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C471" s="3">
-        <v>150.15</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B472" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C472" s="3">
-        <v>144.5</v>
+        <v>859.21</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B473" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C473" s="3">
-        <v>100.93</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B474" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C474" s="3">
-        <v>124.5</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B475" s="3">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="C475" s="3">
-        <v>27.21</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B476" s="3">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="C476" s="3">
-        <v>24.79</v>
+        <v>97.54</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B477" s="3">
         <v>10</v>
       </c>
       <c r="C477" s="3">
-        <v>37.1</v>
+        <v>304.02999999999997</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B478" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C478" s="3">
-        <v>178.04</v>
+        <v>1934.56</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B479" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="C479" s="3">
-        <v>23.88</v>
+        <v>230.99</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B480" s="3">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="C480" s="3">
-        <v>8.26</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B481" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C481" s="3">
-        <v>859.21</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3">
-      <c r="A482" t="s">
-        <v>400</v>
-      </c>
-      <c r="B482" s="3">
-        <v>1</v>
-      </c>
-      <c r="C482" s="3">
-        <v>242.4</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3">
-      <c r="A483" t="s">
-        <v>401</v>
-      </c>
-      <c r="B483" s="3">
-        <v>3</v>
-      </c>
-      <c r="C483" s="3">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3">
-      <c r="A484" t="s">
-        <v>402</v>
-      </c>
-      <c r="B484" s="3">
-        <v>93</v>
-      </c>
-      <c r="C484" s="3">
-        <v>20.68</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3">
-      <c r="A485" t="s">
-        <v>403</v>
-      </c>
-      <c r="B485" s="3">
-        <v>31</v>
-      </c>
-      <c r="C485" s="3">
-        <v>97.54</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3">
-      <c r="A486" t="s">
-        <v>404</v>
-      </c>
-      <c r="B486" s="3">
-        <v>10</v>
-      </c>
-      <c r="C486" s="3">
-        <v>304.02999999999997</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3">
-      <c r="A487" t="s">
-        <v>405</v>
-      </c>
-      <c r="B487" s="3">
-        <v>6</v>
-      </c>
-      <c r="C487" s="3">
-        <v>1934.56</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3">
-      <c r="A488" t="s">
-        <v>406</v>
-      </c>
-      <c r="B488" s="3">
-        <v>6</v>
-      </c>
-      <c r="C488" s="3">
-        <v>230.99</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3">
-      <c r="A489" t="s">
-        <v>407</v>
-      </c>
-      <c r="B489" s="3">
-        <v>96</v>
-      </c>
-      <c r="C489" s="3">
-        <v>33.39</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3">
-      <c r="A490" t="s">
-        <v>408</v>
-      </c>
-      <c r="B490" s="3">
-        <v>48</v>
-      </c>
-      <c r="C490" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="410">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1238,6 +1238,12 @@
   </si>
   <si>
     <t>WURTH curatitor frane 750 ML</t>
+  </si>
+  <si>
+    <t>RAV VSH SAE 0W20 1L</t>
+  </si>
+  <si>
+    <t>RAV VSH SAE 0W20 5L</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C481"/>
+  <dimension ref="A1:C480"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -3054,10 +3060,10 @@
         <v>110</v>
       </c>
       <c r="B132" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132" s="3">
-        <v>56.93</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3065,32 +3071,32 @@
         <v>110</v>
       </c>
       <c r="B133" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C133" s="3">
-        <v>70.38</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B134" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C134" s="3">
-        <v>80.73</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B135" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C135" s="3">
-        <v>98.95</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3098,21 +3104,21 @@
         <v>112</v>
       </c>
       <c r="B136" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C136" s="3">
-        <v>92.91</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B137" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C137" s="3">
-        <v>93.25</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -3120,21 +3126,21 @@
         <v>113</v>
       </c>
       <c r="B138" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C138" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B139" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C139" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3142,73 +3148,73 @@
         <v>114</v>
       </c>
       <c r="B140" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C140" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C141" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B142" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C142" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B143" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C143" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B144" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C144" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B145" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C145" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B146" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C146" s="3">
         <v>69.56</v>
@@ -3216,13 +3222,13 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B147" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C147" s="3">
-        <v>69.56</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -3230,7 +3236,7 @@
         <v>121</v>
       </c>
       <c r="B148" s="3">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C148" s="3">
         <v>52.17</v>
@@ -3238,24 +3244,24 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B149" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C149" s="3">
-        <v>52.17</v>
+        <v>208.66</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B150" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C150" s="3">
-        <v>208.66</v>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -3263,32 +3269,32 @@
         <v>123</v>
       </c>
       <c r="B151" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C151" s="3">
-        <v>79.349999999999994</v>
+        <v>88.87</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B152" s="3">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C152" s="3">
-        <v>88.87</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B153" s="3">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="C153" s="3">
-        <v>67.28</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -3296,32 +3302,32 @@
         <v>125</v>
       </c>
       <c r="B154" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C154" s="3">
-        <v>62.11</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C155" s="3">
-        <v>69.55</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B156" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C156" s="3">
-        <v>63.89</v>
+        <v>149.91</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -3329,43 +3335,43 @@
         <v>127</v>
       </c>
       <c r="B157" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C157" s="3">
-        <v>149.91999999999999</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B158" s="3">
         <v>5</v>
       </c>
       <c r="C158" s="3">
-        <v>95.05</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B159" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C159" s="3">
-        <v>38.57</v>
+        <v>207.31</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B160" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C160" s="3">
-        <v>207.31</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -3373,106 +3379,106 @@
         <v>130</v>
       </c>
       <c r="B161" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C161" s="3">
-        <v>58.24</v>
+        <v>65.23</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C162" s="3">
-        <v>65.23</v>
+        <v>325.87</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B163" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C163" s="3">
-        <v>325.87</v>
+        <v>5165.8</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B164" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C164" s="3">
-        <v>5165.8</v>
+        <v>511.75</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B165" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C165" s="3">
-        <v>511.75</v>
+        <v>572.70000000000005</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B166" s="3">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C166" s="3">
-        <v>572.70000000000005</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B167" s="3">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="C167" s="3">
-        <v>66.98</v>
+        <v>367.42</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B168" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C168" s="3">
-        <v>367.42</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B169" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C169" s="3">
-        <v>51.52</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C170" s="3">
         <v>23.19</v>
@@ -3483,7 +3489,7 @@
         <v>139</v>
       </c>
       <c r="B171" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C171" s="3">
         <v>23.19</v>
@@ -3491,43 +3497,43 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C172" s="3">
-        <v>23.19</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B173" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C173" s="3">
-        <v>69.55</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B174" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C174" s="3">
-        <v>3169.7</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B175" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C175" s="3">
         <v>81.14</v>
@@ -3535,24 +3541,24 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B176" s="3">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C176" s="3">
-        <v>81.14</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B177" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C177" s="3">
-        <v>66.98</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3563,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="C178" s="3">
-        <v>53.83</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3571,21 +3577,21 @@
         <v>145</v>
       </c>
       <c r="B179" s="3">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C179" s="3">
-        <v>60.28</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B180" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C180" s="3">
-        <v>60.29</v>
+        <v>82.65</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -3593,43 +3599,43 @@
         <v>146</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C181" s="3">
-        <v>82.65</v>
+        <v>93.35</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B182" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C182" s="3">
-        <v>93.35</v>
+        <v>1217.1600000000001</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B183" s="3">
         <v>1</v>
       </c>
       <c r="C183" s="3">
-        <v>1217.1600000000001</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B184" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C184" s="3">
-        <v>3079</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3637,21 +3643,21 @@
         <v>149</v>
       </c>
       <c r="B185" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C185" s="3">
-        <v>43.7</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C186" s="3">
-        <v>48.95</v>
+        <v>64.59</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3659,32 +3665,32 @@
         <v>150</v>
       </c>
       <c r="B187" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C187" s="3">
-        <v>64.59</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B188" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C188" s="3">
-        <v>72.33</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B189" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C189" s="3">
-        <v>284.19</v>
+        <v>132.19</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -3692,29 +3698,29 @@
         <v>152</v>
       </c>
       <c r="B190" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C190" s="3">
-        <v>132.19999999999999</v>
+        <v>75.260000000000005</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B191" s="3">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C191" s="3">
-        <v>75.260000000000005</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B192" s="3">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C192" s="3">
         <v>32.200000000000003</v>
@@ -3722,46 +3728,46 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B193" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C193" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C194" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B195" s="3">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C195" s="3">
-        <v>32.200000000000003</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B196" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C196" s="3">
-        <v>115.01</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -3769,7 +3775,7 @@
         <v>158</v>
       </c>
       <c r="B197" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C197" s="3">
         <v>38.39</v>
@@ -3777,101 +3783,101 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B198" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C198" s="3">
-        <v>38.39</v>
+        <v>151.47999999999999</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B199" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C199" s="3">
-        <v>151.47999999999999</v>
+        <v>181.68</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B200" s="3">
         <v>12</v>
       </c>
       <c r="C200" s="3">
-        <v>181.68</v>
+        <v>20.059999999999999</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B201" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C201" s="3">
-        <v>20.059999999999999</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B202" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C202" s="3">
-        <v>12.88</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B203" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C203" s="3">
-        <v>26.73</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B204" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C204" s="3">
-        <v>29.95</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B205" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C205" s="3">
-        <v>58.68</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B206" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C206" s="3">
-        <v>79.98</v>
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -3879,32 +3885,32 @@
         <v>167</v>
       </c>
       <c r="B207" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C207" s="3">
-        <v>34.619999999999997</v>
+        <v>38.770000000000003</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B208" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C208" s="3">
-        <v>38.770000000000003</v>
+        <v>107.35</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B209" s="3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C209" s="3">
-        <v>107.35</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -3912,54 +3918,54 @@
         <v>169</v>
       </c>
       <c r="B210" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C210" s="3">
-        <v>55.2</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B211" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C211" s="3">
-        <v>61.83</v>
+        <v>243.16</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B212" s="3">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C212" s="3">
-        <v>243.16</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B213" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C213" s="3">
-        <v>32.200000000000003</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B214" s="3">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C214" s="3">
-        <v>63.78</v>
+        <v>67.849999999999994</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3967,76 +3973,76 @@
         <v>173</v>
       </c>
       <c r="B215" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C215" s="3">
-        <v>67.849999999999994</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B216" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C216" s="3">
-        <v>75.989999999999995</v>
+        <v>297.64999999999998</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B217" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C217" s="3">
-        <v>297.64999999999998</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B218" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C218" s="3">
-        <v>77.28</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B219" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C219" s="3">
-        <v>75.989999999999995</v>
+        <v>342.24</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B220" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C220" s="3">
-        <v>342.24</v>
+        <v>633.75</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B221" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="C221" s="3">
-        <v>633.75</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -4044,43 +4050,43 @@
         <v>179</v>
       </c>
       <c r="B222" s="3">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C222" s="3">
-        <v>36.799999999999997</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B223" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C223" s="3">
-        <v>50.51</v>
+        <v>768.2</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B224" s="3">
         <v>2</v>
       </c>
       <c r="C224" s="3">
-        <v>768.2</v>
+        <v>787.75</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B225" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C225" s="3">
-        <v>787.75</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -4088,21 +4094,21 @@
         <v>182</v>
       </c>
       <c r="B226" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C226" s="3">
-        <v>109.26</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B227" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C227" s="3">
-        <v>122.36</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -4110,109 +4116,109 @@
         <v>183</v>
       </c>
       <c r="B228" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C228" s="3">
-        <v>31.98</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B229" s="3">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C229" s="3">
-        <v>35.81</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B230" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C230" s="3">
-        <v>59.25</v>
+        <v>260</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B231" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C231" s="3">
-        <v>260</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B232" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C232" s="3">
-        <v>43.07</v>
+        <v>48.23</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B233" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C233" s="3">
-        <v>48.23</v>
+        <v>221.86</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B234" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C234" s="3">
-        <v>221.86</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B235" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C235" s="3">
-        <v>74.7</v>
+        <v>296.3</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B236" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C236" s="3">
-        <v>296.3</v>
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B237" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C237" s="3">
-        <v>141.80000000000001</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -4220,351 +4226,351 @@
         <v>192</v>
       </c>
       <c r="B238" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C238" s="3">
-        <v>29.25</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B239" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C239" s="3">
-        <v>41.4</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B240" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C240" s="3">
-        <v>173.3</v>
+        <v>2189.02</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B241" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C241" s="3">
-        <v>2189.02</v>
+        <v>453.22</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B242" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C242" s="3">
-        <v>453.22</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B243" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C243" s="3">
-        <v>48.65</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B244" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C244" s="3">
-        <v>31.3</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B245" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C245" s="3">
-        <v>126.63</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B246" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C246" s="3">
-        <v>69.56</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B247" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C247" s="3">
-        <v>42.44</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B248" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C248" s="3">
-        <v>42.43</v>
+        <v>179</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B249" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C249" s="3">
-        <v>145.94</v>
+        <v>2060.8000000000002</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B250" s="3">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C250" s="3">
-        <v>179</v>
+        <v>51</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B251" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C251" s="3">
-        <v>2060.8000000000002</v>
+        <v>51</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B252" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C252" s="3">
-        <v>51</v>
+        <v>183.41</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B253" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C253" s="3">
-        <v>51</v>
+        <v>206.33</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B254" s="3">
         <v>9</v>
       </c>
       <c r="C254" s="3">
-        <v>183.41</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B255" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C255" s="3">
-        <v>206.33</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B256" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C256" s="3">
-        <v>29.9</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B257" s="3">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C257" s="3">
-        <v>33.479999999999997</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B258" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C258" s="3">
-        <v>46.06</v>
+        <v>5345.33</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B259" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C259" s="3">
-        <v>4667</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B260" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C260" s="3">
-        <v>5345.33</v>
+        <v>192.51</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B261" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C261" s="3">
-        <v>170.78</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B262" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C262" s="3">
-        <v>192.51</v>
+        <v>265.05</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B263" s="3">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C263" s="3">
-        <v>59.7</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B264" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C264" s="3">
-        <v>265.05</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B265" s="3">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C265" s="3">
-        <v>36.799999999999997</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B266" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C266" s="3">
-        <v>103.04</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B267" s="3">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C267" s="3">
-        <v>36.75</v>
+        <v>16.809999999999999</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B268" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C268" s="3">
-        <v>47.16</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B269" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C269" s="3">
-        <v>16.809999999999999</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -4572,392 +4578,392 @@
         <v>219</v>
       </c>
       <c r="B270" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C270" s="3">
-        <v>27.68</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B271" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C271" s="3">
-        <v>28.69</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B272" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C272" s="3">
-        <v>37.31</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B273" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C273" s="3">
-        <v>103.46</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B274" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C274" s="3">
-        <v>126.24</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B275" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C275" s="3">
-        <v>154.62</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B276" s="3">
         <v>2</v>
       </c>
       <c r="C276" s="3">
-        <v>508.2</v>
+        <v>466.78</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B277" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C277" s="3">
-        <v>5069</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B278" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C278" s="3">
-        <v>466.78</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B279" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C279" s="3">
-        <v>57.5</v>
+        <v>20789.41</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B280" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C280" s="3">
-        <v>63.13</v>
+        <v>33057.85</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B281" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C281" s="3">
-        <v>20789.41</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B282" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C282" s="3">
-        <v>33057.85</v>
+        <v>81.650000000000006</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B283" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C283" s="3">
-        <v>83.5</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B284" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C284" s="3">
-        <v>81.650000000000006</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B285" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C285" s="3">
-        <v>45.88</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B286" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C286" s="3">
-        <v>50.71</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B287" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C287" s="3">
-        <v>50.71</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B288" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C288" s="3">
-        <v>51.75</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B289" s="3">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C289" s="3">
-        <v>36.94</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B290" s="3">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C290" s="3">
-        <v>36.94</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B291" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C291" s="3">
-        <v>67.28</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B292" s="3">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C292" s="3">
-        <v>65.099999999999994</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B293" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C293" s="3">
-        <v>65.53</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B294" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C294" s="3">
-        <v>65.53</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B295" s="3">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="C295" s="3">
-        <v>90.9</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B296" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C296" s="3">
-        <v>29.89</v>
+        <v>422.09</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B297" s="3">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="C297" s="3">
-        <v>33.479999999999997</v>
+        <v>1277.7</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B298" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C298" s="3">
-        <v>422.09</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B299" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C299" s="3">
-        <v>1277.7</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B300" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C300" s="3">
-        <v>6.44</v>
+        <v>4456.4799999999996</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B301" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C301" s="3">
-        <v>108.2</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B302" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C302" s="3">
-        <v>4456.4799999999996</v>
+        <v>609.5</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B303" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C303" s="3">
-        <v>6279</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B304" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C304" s="3">
-        <v>609.5</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B305" s="3">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C305" s="3">
         <v>32.200000000000003</v>
@@ -4965,10 +4971,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B306" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C306" s="3">
         <v>32.200000000000003</v>
@@ -4976,1509 +4982,1509 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B307" s="3">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C307" s="3">
-        <v>32.200000000000003</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B308" s="3">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C308" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B309" s="3">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C309" s="3">
-        <v>40.4</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B310" s="3">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C310" s="3">
-        <v>36.06</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B311" s="3">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C311" s="3">
-        <v>36.06</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B312" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C312" s="3">
-        <v>44.5</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B313" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C313" s="3">
-        <v>56.01</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B314" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C314" s="3">
-        <v>57.63</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B315" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C315" s="3">
-        <v>60.78</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B316" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C316" s="3">
-        <v>42.49</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B317" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C317" s="3">
-        <v>46.28</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B318" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C318" s="3">
-        <v>59.21</v>
+        <v>71.709999999999994</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B319" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C319" s="3">
-        <v>261.8</v>
+        <v>77.760000000000005</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B320" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C320" s="3">
-        <v>71.709999999999994</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B321" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C321" s="3">
-        <v>77.760000000000005</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B322" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C322" s="3">
-        <v>54.7</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B323" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C323" s="3">
-        <v>52.1</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B324" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C324" s="3">
-        <v>251.5</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B325" s="3">
         <v>12</v>
       </c>
       <c r="C325" s="3">
-        <v>78.87</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B326" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C326" s="3">
-        <v>83.84</v>
+        <v>331.2</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B327" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C327" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B328" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C328" s="3">
-        <v>331.2</v>
+        <v>65.209999999999994</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B329" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C329" s="3">
-        <v>272.5</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B330" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C330" s="3">
-        <v>79.75</v>
+        <v>284</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B331" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C331" s="3">
-        <v>65.209999999999994</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B332" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C332" s="3">
-        <v>83.84</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B333" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C333" s="3">
-        <v>284</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B334" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C334" s="3">
-        <v>28.15</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B335" s="3">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C335" s="3">
-        <v>45.08</v>
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B336" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C336" s="3">
-        <v>51.52</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B337" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C337" s="3">
-        <v>40.57</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B338" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C338" s="3">
-        <v>36.229999999999997</v>
+        <v>295.14999999999998</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B339" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C339" s="3">
-        <v>54.12</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B340" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C340" s="3">
-        <v>69.55</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B341" s="3">
         <v>10</v>
       </c>
       <c r="C341" s="3">
-        <v>295.14999999999998</v>
+        <v>78.209999999999994</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B342" s="3">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="C342" s="3">
-        <v>38.56</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B343" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C343" s="3">
-        <v>60.95</v>
+        <v>6578.46</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B344" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C344" s="3">
-        <v>78.209999999999994</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B345" s="3">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="C345" s="3">
-        <v>44.93</v>
+        <v>211.23</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B346" s="3">
         <v>1</v>
       </c>
       <c r="C346" s="3">
-        <v>6578.46</v>
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B347" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C347" s="3">
-        <v>173.09</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B348" s="3">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C348" s="3">
-        <v>211.23</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B349" s="3">
         <v>1</v>
       </c>
       <c r="C349" s="3">
-        <v>2314.8000000000002</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B350" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C350" s="3">
-        <v>791.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B351" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C351" s="3">
-        <v>31.6</v>
+        <v>281</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B352" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C352" s="3">
-        <v>31.6</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B353" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C353" s="3">
-        <v>77</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B354" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C354" s="3">
-        <v>281</v>
+        <v>798.6</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B355" s="3">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="C355" s="3">
-        <v>43.8</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B356" s="3">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C356" s="3">
-        <v>21.9</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B357" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C357" s="3">
-        <v>798.6</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B358" s="3">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="C358" s="3">
-        <v>23.19</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B359" s="3">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C359" s="3">
-        <v>8.24</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B360" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C360" s="3">
-        <v>13.72</v>
+        <v>36.869999999999997</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B361" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C361" s="3">
-        <v>31.95</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B362" s="3">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="C362" s="3">
-        <v>16.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B363" s="3">
         <v>6</v>
       </c>
       <c r="C363" s="3">
-        <v>36.869999999999997</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B364" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C364" s="3">
-        <v>31.48</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B365" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C365" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B366" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C366" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B367" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C367" s="3">
-        <v>19.55</v>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B368" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C368" s="3">
-        <v>19.07</v>
+        <v>862.7</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B369" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C369" s="3">
-        <v>21.9</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B370" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C370" s="3">
-        <v>57.96</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B371" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C371" s="3">
-        <v>862.7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B372" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C372" s="3">
-        <v>56.93</v>
+        <v>267.85000000000002</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B373" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C373" s="3">
-        <v>1265</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B374" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C374" s="3">
-        <v>76</v>
+        <v>327.3</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B375" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C375" s="3">
-        <v>267.85000000000002</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B376" s="3">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C376" s="3">
-        <v>74.7</v>
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B377" s="3">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C377" s="3">
-        <v>327.3</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B378" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C378" s="3">
-        <v>72.13</v>
+        <v>428.5</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B379" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C379" s="3">
-        <v>302.39999999999998</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B380" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C380" s="3">
-        <v>36.799999999999997</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B381" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C381" s="3">
-        <v>428.5</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B382" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C382" s="3">
-        <v>450.22</v>
+        <v>87.49</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B383" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C383" s="3">
-        <v>465.7</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B384" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C384" s="3">
-        <v>38.25</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B385" s="3">
         <v>2</v>
       </c>
       <c r="C385" s="3">
-        <v>87.49</v>
+        <v>3333.85</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B386" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C386" s="3">
-        <v>63.13</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B387" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C387" s="3">
-        <v>377.78</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B388" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C388" s="3">
-        <v>3333.85</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B389" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C389" s="3">
-        <v>374.67</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B390" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C390" s="3">
-        <v>120.06</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B391" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C391" s="3">
-        <v>54.2</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B392" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C392" s="3">
-        <v>54.2</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B393" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C393" s="3">
-        <v>31.5</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B394" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C394" s="3">
-        <v>114.09</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B395" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C395" s="3">
-        <v>139.9</v>
+        <v>370.53</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B396" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C396" s="3">
-        <v>35.94</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B397" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C397" s="3">
-        <v>140.26</v>
+        <v>4772.5</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B398" s="3">
         <v>1</v>
       </c>
       <c r="C398" s="3">
-        <v>370.53</v>
+        <v>375.7</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B399" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C399" s="3">
-        <v>30.9</v>
+        <v>516.46</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B400" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C400" s="3">
-        <v>4772.5</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B401" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C401" s="3">
-        <v>375.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B402" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C402" s="3">
-        <v>516.46</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B403" s="3">
         <v>4</v>
       </c>
       <c r="C403" s="3">
-        <v>185.15</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B404" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C404" s="3">
-        <v>11.5</v>
+        <v>461.23</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B405" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C405" s="3">
-        <v>724.5</v>
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B406" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C406" s="3">
-        <v>450.22</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B407" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C407" s="3">
-        <v>461.23</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B408" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C408" s="3">
-        <v>518.41999999999996</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B409" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C409" s="3">
-        <v>348.08</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B410" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C410" s="3">
-        <v>33.479999999999997</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B411" s="3">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C411" s="3">
-        <v>35.79</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B412" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C412" s="3">
-        <v>377.7</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B413" s="3">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C413" s="3">
-        <v>33.21</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B414" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C414" s="3">
-        <v>27.16</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B415" s="3">
         <v>1</v>
       </c>
       <c r="C415" s="3">
-        <v>361.41</v>
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B416" s="3">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="C416" s="3">
-        <v>29.25</v>
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B417" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C417" s="3">
-        <v>29.26</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B418" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C418" s="3">
-        <v>304.54000000000002</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B419" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C419" s="3">
-        <v>34.049999999999997</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B420" s="3">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="C420" s="3">
-        <v>57.7</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B421" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C421" s="3">
-        <v>90.9</v>
+        <v>7173.59</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B422" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C422" s="3">
-        <v>42.24</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B423" s="3">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C423" s="3">
-        <v>44.31</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B424" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C424" s="3">
-        <v>7173.59</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B425" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C425" s="3">
-        <v>677.79</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B426" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C426" s="3">
-        <v>167.33</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B427" s="3">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C427" s="3">
-        <v>191.01</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B428" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C428" s="3">
-        <v>2335.67</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B429" s="3">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C429" s="3">
-        <v>62.04</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B430" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C430" s="3">
-        <v>8139.6</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B431" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C431" s="3">
-        <v>235.53</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B432" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C432" s="3">
-        <v>259.8</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B433" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C433" s="3">
-        <v>310.2</v>
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B434" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C434" s="3">
-        <v>36.43</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B435" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C435" s="3">
-        <v>73.42</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B436" s="3">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C436" s="3">
-        <v>319.60000000000002</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B437" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C437" s="3">
-        <v>62.6</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B438" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C438" s="3">
-        <v>312.8</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="B439" s="3">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C439" s="3">
-        <v>67.28</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="B440" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C440" s="3">
-        <v>1138.5</v>
+        <v>289.33999999999997</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B441" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C441" s="3">
-        <v>1138.5</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B442" s="3">
         <v>2</v>
       </c>
       <c r="C442" s="3">
-        <v>48.76</v>
+        <v>242.34</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B443" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C443" s="3">
-        <v>242.34</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -6486,87 +6492,87 @@
         <v>372</v>
       </c>
       <c r="B444" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C444" s="3">
-        <v>54.09</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B445" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C445" s="3">
-        <v>54.1</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B446" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C446" s="3">
-        <v>255.03</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B447" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C447" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B448" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C448" s="3">
-        <v>255.03</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B449" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C449" s="3">
-        <v>68.86</v>
+        <v>344.28</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B450" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C450" s="3">
-        <v>344.28</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B451" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C451" s="3">
-        <v>60.29</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -6574,7 +6580,7 @@
         <v>379</v>
       </c>
       <c r="B452" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C452" s="3">
         <v>261.8</v>
@@ -6582,18 +6588,18 @@
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B453" s="3">
         <v>1</v>
       </c>
       <c r="C453" s="3">
-        <v>261.8</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B454" s="3">
         <v>1</v>
@@ -6604,298 +6610,287 @@
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B455" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C455" s="3">
-        <v>30.58</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B456" s="3">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C456" s="3">
-        <v>16.95</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B457" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C457" s="3">
-        <v>24.95</v>
+        <v>641.49</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B458" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C458" s="3">
-        <v>641.49</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B459" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C459" s="3">
-        <v>39.57</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B460" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C460" s="3">
-        <v>51.83</v>
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B461" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C461" s="3">
-        <v>33.840000000000003</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B462" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C462" s="3">
-        <v>150.15</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B463" s="3">
         <v>25</v>
       </c>
       <c r="C463" s="3">
-        <v>144.5</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B464" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C464" s="3">
-        <v>100.93</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B465" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C465" s="3">
-        <v>124.5</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B466" s="3">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C466" s="3">
-        <v>27.21</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B467" s="3">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="C467" s="3">
-        <v>24.79</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B468" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C468" s="3">
-        <v>37.1</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B469" s="3">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C469" s="3">
-        <v>178.04</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B470" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C470" s="3">
-        <v>23.88</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B471" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C471" s="3">
-        <v>8.26</v>
+        <v>859.21</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B472" s="3">
         <v>1</v>
       </c>
       <c r="C472" s="3">
-        <v>859.21</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B473" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C473" s="3">
-        <v>242.4</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B474" s="3">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C474" s="3">
-        <v>5000</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B475" s="3">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="C475" s="3">
-        <v>20.68</v>
+        <v>97.54</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B476" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C476" s="3">
-        <v>97.54</v>
+        <v>304.02999999999997</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B477" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C477" s="3">
-        <v>304.02999999999997</v>
+        <v>1934.56</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B478" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C478" s="3">
-        <v>1934.56</v>
+        <v>230.99</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B479" s="3">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="C479" s="3">
-        <v>230.99</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B480" s="3">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C480" s="3">
-        <v>33.39</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3">
-      <c r="A481" t="s">
-        <v>407</v>
-      </c>
-      <c r="B481" s="3">
-        <v>48</v>
-      </c>
-      <c r="C481" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4435,7 +4435,7 @@
         <v>209</v>
       </c>
       <c r="B257" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C257" s="3">
         <v>4667</v>
@@ -4446,7 +4446,7 @@
         <v>209</v>
       </c>
       <c r="B258" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C258" s="3">
         <v>5345.33</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="410">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1607,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C480"/>
+  <dimension ref="A1:C479"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -5986,65 +5986,65 @@
         <v>334</v>
       </c>
       <c r="B398" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C398" s="3">
-        <v>375.7</v>
+        <v>516.46</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B399" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C399" s="3">
-        <v>516.46</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B400" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C400" s="3">
-        <v>185.15</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B401" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C401" s="3">
-        <v>11.5</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B402" s="3">
         <v>4</v>
       </c>
       <c r="C402" s="3">
-        <v>724.5</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B403" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C403" s="3">
-        <v>450.22</v>
+        <v>461.23</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -6055,95 +6055,95 @@
         <v>1</v>
       </c>
       <c r="C404" s="3">
-        <v>461.23</v>
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B405" s="3">
         <v>1</v>
       </c>
       <c r="C405" s="3">
-        <v>518.41999999999996</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B406" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C406" s="3">
-        <v>348.08</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B407" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C407" s="3">
-        <v>33.479999999999997</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B408" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C408" s="3">
-        <v>35.79</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B409" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C409" s="3">
-        <v>377.7</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B410" s="3">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C410" s="3">
-        <v>33.21</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B411" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C411" s="3">
-        <v>27.16</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B412" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C412" s="3">
-        <v>361.41</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -6151,65 +6151,65 @@
         <v>347</v>
       </c>
       <c r="B413" s="3">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C413" s="3">
-        <v>29.25</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B414" s="3">
         <v>1</v>
       </c>
       <c r="C414" s="3">
-        <v>29.26</v>
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B415" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C415" s="3">
-        <v>304.54000000000002</v>
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B416" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C416" s="3">
-        <v>34.049999999999997</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B417" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C417" s="3">
-        <v>57.7</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B418" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C418" s="3">
-        <v>90.9</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -6217,197 +6217,197 @@
         <v>352</v>
       </c>
       <c r="B419" s="3">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C419" s="3">
-        <v>42.24</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B420" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C420" s="3">
-        <v>44.31</v>
+        <v>7173.59</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B421" s="3">
         <v>1</v>
       </c>
       <c r="C421" s="3">
-        <v>7173.59</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B422" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C422" s="3">
-        <v>677.79</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B423" s="3">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C423" s="3">
-        <v>167.33</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B424" s="3">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C424" s="3">
-        <v>191.01</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B425" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C425" s="3">
-        <v>2335.67</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B426" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C426" s="3">
-        <v>62.04</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B427" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C427" s="3">
-        <v>8139.6</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B428" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C428" s="3">
-        <v>235.53</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B429" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C429" s="3">
-        <v>259.8</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B430" s="3">
         <v>1</v>
       </c>
       <c r="C430" s="3">
-        <v>310.2</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B431" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C431" s="3">
-        <v>36.43</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B432" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C432" s="3">
-        <v>87.22</v>
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B433" s="3">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C433" s="3">
-        <v>319.60000000000002</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B434" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C434" s="3">
-        <v>62.6</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B435" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C435" s="3">
-        <v>312.8</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B436" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C436" s="3">
-        <v>67.28</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -6415,7 +6415,7 @@
         <v>369</v>
       </c>
       <c r="B437" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C437" s="3">
         <v>1138.5</v>
@@ -6423,57 +6423,57 @@
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="B438" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C438" s="3">
-        <v>1138.5</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B439" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C439" s="3">
-        <v>58.69</v>
+        <v>289.33999999999997</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="B440" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C440" s="3">
-        <v>289.33999999999997</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B441" s="3">
         <v>2</v>
       </c>
       <c r="C441" s="3">
-        <v>48.76</v>
+        <v>242.34</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B442" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C442" s="3">
-        <v>242.34</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -6481,87 +6481,87 @@
         <v>372</v>
       </c>
       <c r="B443" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C443" s="3">
-        <v>54.09</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B444" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C444" s="3">
-        <v>54.1</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B445" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C445" s="3">
-        <v>255.03</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B446" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C446" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B447" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C447" s="3">
-        <v>255.03</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B448" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C448" s="3">
-        <v>68.86</v>
+        <v>344.28</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B449" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C449" s="3">
-        <v>344.28</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B450" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C450" s="3">
-        <v>60.29</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -6569,7 +6569,7 @@
         <v>379</v>
       </c>
       <c r="B451" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C451" s="3">
         <v>261.8</v>
@@ -6577,18 +6577,18 @@
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B452" s="3">
         <v>1</v>
       </c>
       <c r="C452" s="3">
-        <v>261.8</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B453" s="3">
         <v>1</v>
@@ -6599,298 +6599,287 @@
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B454" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C454" s="3">
-        <v>30.58</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B455" s="3">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C455" s="3">
-        <v>16.95</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B456" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C456" s="3">
-        <v>24.95</v>
+        <v>641.49</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B457" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C457" s="3">
-        <v>641.49</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B458" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C458" s="3">
-        <v>39.57</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B459" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C459" s="3">
-        <v>51.83</v>
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B460" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C460" s="3">
-        <v>33.840000000000003</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B461" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C461" s="3">
-        <v>150.15</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B462" s="3">
         <v>25</v>
       </c>
       <c r="C462" s="3">
-        <v>144.5</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B463" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C463" s="3">
-        <v>100.93</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B464" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C464" s="3">
-        <v>124.5</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B465" s="3">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C465" s="3">
-        <v>27.21</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B466" s="3">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="C466" s="3">
-        <v>24.79</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B467" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C467" s="3">
-        <v>37.1</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B468" s="3">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C468" s="3">
-        <v>178.04</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B469" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C469" s="3">
-        <v>23.88</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B470" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C470" s="3">
-        <v>8.26</v>
+        <v>859.21</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B471" s="3">
         <v>1</v>
       </c>
       <c r="C471" s="3">
-        <v>859.21</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B472" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C472" s="3">
-        <v>242.4</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B473" s="3">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C473" s="3">
-        <v>5000</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B474" s="3">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="C474" s="3">
-        <v>20.68</v>
+        <v>97.54</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B475" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C475" s="3">
-        <v>97.54</v>
+        <v>304.02999999999997</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B476" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C476" s="3">
-        <v>304.02999999999997</v>
+        <v>1934.56</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B477" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C477" s="3">
-        <v>1934.56</v>
+        <v>230.99</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B478" s="3">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="C478" s="3">
-        <v>230.99</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B479" s="3">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C479" s="3">
-        <v>33.39</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3">
-      <c r="A480" t="s">
-        <v>407</v>
-      </c>
-      <c r="B480" s="3">
-        <v>48</v>
-      </c>
-      <c r="C480" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="410">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1607,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C479"/>
+  <dimension ref="A1:C476"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -4556,392 +4556,392 @@
         <v>219</v>
       </c>
       <c r="B268" s="3">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="C268" s="3">
-        <v>27.68</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B269" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C269" s="3">
-        <v>28.69</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B270" s="3">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C270" s="3">
-        <v>37.31</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B271" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C271" s="3">
-        <v>103.46</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B272" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C272" s="3">
-        <v>126.24</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B273" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C273" s="3">
-        <v>154.62</v>
+        <v>466.78</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B274" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C274" s="3">
-        <v>508.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B275" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C275" s="3">
-        <v>5069</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B276" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C276" s="3">
-        <v>466.78</v>
+        <v>20789.41</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B277" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C277" s="3">
-        <v>57.5</v>
+        <v>33057.85</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B278" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C278" s="3">
-        <v>63.13</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B279" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C279" s="3">
-        <v>20789.41</v>
+        <v>81.650000000000006</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B280" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C280" s="3">
-        <v>33057.85</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B281" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C281" s="3">
-        <v>83.5</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B282" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C282" s="3">
-        <v>81.650000000000006</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B283" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C283" s="3">
-        <v>45.88</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B284" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C284" s="3">
-        <v>50.71</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B285" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C285" s="3">
-        <v>50.71</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B286" s="3">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C286" s="3">
-        <v>51.75</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B287" s="3">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C287" s="3">
-        <v>36.94</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B288" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C288" s="3">
-        <v>36.94</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B289" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C289" s="3">
-        <v>67.28</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B290" s="3">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C290" s="3">
-        <v>65.099999999999994</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B291" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C291" s="3">
-        <v>65.53</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B292" s="3">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="C292" s="3">
-        <v>65.53</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B293" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C293" s="3">
-        <v>109.08</v>
+        <v>422.09</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B294" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C294" s="3">
-        <v>29.89</v>
+        <v>1277.7</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B295" s="3">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="C295" s="3">
-        <v>33.479999999999997</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B296" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C296" s="3">
-        <v>422.09</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B297" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C297" s="3">
-        <v>1277.7</v>
+        <v>4456.4799999999996</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B298" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C298" s="3">
-        <v>6.44</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B299" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C299" s="3">
-        <v>108.2</v>
+        <v>609.5</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B300" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C300" s="3">
-        <v>4456.4799999999996</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B301" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C301" s="3">
-        <v>6279</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B302" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C302" s="3">
-        <v>609.5</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B303" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C303" s="3">
         <v>32.200000000000003</v>
@@ -4949,1937 +4949,1904 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B304" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C304" s="3">
-        <v>32.200000000000003</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B305" s="3">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="C305" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B306" s="3">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C306" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B307" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C307" s="3">
-        <v>40.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B308" s="3">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C308" s="3">
-        <v>36.06</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B309" s="3">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="C309" s="3">
-        <v>36.06</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B310" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C310" s="3">
-        <v>44.5</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B311" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C311" s="3">
-        <v>56.01</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B312" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C312" s="3">
-        <v>57.63</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B313" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C313" s="3">
-        <v>60.78</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B314" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C314" s="3">
-        <v>42.49</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B315" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C315" s="3">
-        <v>46.28</v>
+        <v>71.709999999999994</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B316" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C316" s="3">
-        <v>59.21</v>
+        <v>77.760000000000005</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B317" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C317" s="3">
-        <v>261.8</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B318" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C318" s="3">
-        <v>71.709999999999994</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B319" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C319" s="3">
-        <v>77.760000000000005</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B320" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C320" s="3">
-        <v>54.7</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B321" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C321" s="3">
-        <v>67.28</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B322" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C322" s="3">
-        <v>251.5</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B323" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C323" s="3">
-        <v>78.87</v>
+        <v>331.2</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B324" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C324" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B325" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C325" s="3">
-        <v>83.84</v>
+        <v>65.209999999999994</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B326" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C326" s="3">
-        <v>331.2</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B327" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C327" s="3">
-        <v>79.75</v>
+        <v>284</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B328" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C328" s="3">
-        <v>65.209999999999994</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B329" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C329" s="3">
-        <v>83.84</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B330" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C330" s="3">
-        <v>284</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B331" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C331" s="3">
-        <v>28.15</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B332" s="3">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C332" s="3">
-        <v>45.08</v>
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B333" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C333" s="3">
-        <v>51.52</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B334" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C334" s="3">
-        <v>40.57</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B335" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C335" s="3">
-        <v>36.229999999999997</v>
+        <v>295.14999999999998</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B336" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C336" s="3">
-        <v>54.12</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B337" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C337" s="3">
-        <v>69.55</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B338" s="3">
         <v>10</v>
       </c>
       <c r="C338" s="3">
-        <v>295.14999999999998</v>
+        <v>78.209999999999994</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B339" s="3">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="C339" s="3">
-        <v>38.56</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B340" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C340" s="3">
-        <v>60.95</v>
+        <v>6578.46</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B341" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C341" s="3">
-        <v>78.209999999999994</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B342" s="3">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="C342" s="3">
-        <v>44.93</v>
+        <v>211.23</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B343" s="3">
         <v>1</v>
       </c>
       <c r="C343" s="3">
-        <v>6578.46</v>
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B344" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C344" s="3">
-        <v>173.09</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B345" s="3">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C345" s="3">
-        <v>211.23</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B346" s="3">
         <v>1</v>
       </c>
       <c r="C346" s="3">
-        <v>2314.8000000000002</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B347" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C347" s="3">
-        <v>791.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B348" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C348" s="3">
-        <v>31.6</v>
+        <v>281</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B349" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C349" s="3">
-        <v>31.6</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B350" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C350" s="3">
-        <v>77</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B351" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C351" s="3">
-        <v>281</v>
+        <v>798.6</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B352" s="3">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="C352" s="3">
-        <v>43.8</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B353" s="3">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C353" s="3">
-        <v>21.9</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B354" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C354" s="3">
-        <v>798.6</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B355" s="3">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="C355" s="3">
-        <v>23.19</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B356" s="3">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C356" s="3">
-        <v>8.24</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B357" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C357" s="3">
-        <v>13.72</v>
+        <v>36.869999999999997</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B358" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C358" s="3">
-        <v>31.95</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B359" s="3">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="C359" s="3">
-        <v>16.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B360" s="3">
         <v>6</v>
       </c>
       <c r="C360" s="3">
-        <v>36.869999999999997</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B361" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C361" s="3">
-        <v>31.48</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B362" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C362" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B363" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C363" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B364" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C364" s="3">
-        <v>19.55</v>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B365" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C365" s="3">
-        <v>19.07</v>
+        <v>862.7</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C366" s="3">
-        <v>21.9</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B367" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C367" s="3">
-        <v>79.349999999999994</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B368" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C368" s="3">
-        <v>862.7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B369" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C369" s="3">
-        <v>56.93</v>
+        <v>267.85000000000002</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B370" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C370" s="3">
-        <v>1265</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B371" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C371" s="3">
-        <v>76</v>
+        <v>327.3</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B372" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C372" s="3">
-        <v>267.85000000000002</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B373" s="3">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C373" s="3">
-        <v>74.7</v>
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B374" s="3">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C374" s="3">
-        <v>327.3</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B375" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C375" s="3">
-        <v>72.13</v>
+        <v>428.5</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B376" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C376" s="3">
-        <v>302.39999999999998</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B377" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C377" s="3">
-        <v>36.799999999999997</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B378" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C378" s="3">
-        <v>428.5</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B379" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C379" s="3">
-        <v>450.22</v>
+        <v>87.49</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B380" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C380" s="3">
-        <v>465.7</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B381" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C381" s="3">
-        <v>38.25</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B382" s="3">
         <v>2</v>
       </c>
       <c r="C382" s="3">
-        <v>87.49</v>
+        <v>3333.85</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B383" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C383" s="3">
-        <v>63.13</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B384" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C384" s="3">
-        <v>377.78</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B385" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C385" s="3">
-        <v>3333.85</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B386" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C386" s="3">
-        <v>374.67</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B387" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C387" s="3">
-        <v>120.06</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B388" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C388" s="3">
-        <v>54.2</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B389" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C389" s="3">
-        <v>54.2</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B390" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C390" s="3">
-        <v>31.5</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B391" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C391" s="3">
-        <v>114.09</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B392" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C392" s="3">
-        <v>139.9</v>
+        <v>370.53</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B393" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C393" s="3">
-        <v>35.94</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B394" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C394" s="3">
-        <v>140.26</v>
+        <v>4772.5</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B395" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C395" s="3">
-        <v>370.53</v>
+        <v>516.46</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B396" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C396" s="3">
-        <v>30.9</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B397" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C397" s="3">
-        <v>4772.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B398" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C398" s="3">
-        <v>516.46</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B399" s="3">
         <v>4</v>
       </c>
       <c r="C399" s="3">
-        <v>185.15</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B400" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C400" s="3">
-        <v>11.5</v>
+        <v>461.23</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B401" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C401" s="3">
-        <v>724.5</v>
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B402" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C402" s="3">
-        <v>450.22</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B403" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C403" s="3">
-        <v>461.23</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B404" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C404" s="3">
-        <v>518.41999999999996</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B405" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C405" s="3">
-        <v>348.08</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B406" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C406" s="3">
-        <v>33.479999999999997</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B407" s="3">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C407" s="3">
-        <v>35.79</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B408" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C408" s="3">
-        <v>377.7</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B409" s="3">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C409" s="3">
-        <v>33.21</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B410" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C410" s="3">
-        <v>27.16</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B411" s="3">
         <v>1</v>
       </c>
       <c r="C411" s="3">
-        <v>361.41</v>
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B412" s="3">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="C412" s="3">
-        <v>29.25</v>
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B413" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C413" s="3">
-        <v>29.26</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B414" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C414" s="3">
-        <v>304.54000000000002</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B415" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C415" s="3">
-        <v>34.049999999999997</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B416" s="3">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="C416" s="3">
-        <v>57.7</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B417" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C417" s="3">
-        <v>90.9</v>
+        <v>7173.59</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B418" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C418" s="3">
-        <v>42.24</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B419" s="3">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C419" s="3">
-        <v>44.31</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B420" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C420" s="3">
-        <v>7173.59</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B421" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C421" s="3">
-        <v>677.79</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B422" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C422" s="3">
-        <v>167.33</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B423" s="3">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C423" s="3">
-        <v>191.01</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B424" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C424" s="3">
-        <v>2335.67</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B425" s="3">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C425" s="3">
-        <v>62.04</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B426" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C426" s="3">
-        <v>8139.6</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B427" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C427" s="3">
-        <v>235.53</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B428" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C428" s="3">
-        <v>259.8</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B429" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C429" s="3">
-        <v>310.2</v>
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B430" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C430" s="3">
-        <v>36.43</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B431" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C431" s="3">
-        <v>87.22</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B432" s="3">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C432" s="3">
-        <v>319.60000000000002</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B433" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C433" s="3">
-        <v>62.6</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B434" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C434" s="3">
-        <v>312.8</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="B435" s="3">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C435" s="3">
-        <v>67.28</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="B436" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C436" s="3">
-        <v>1138.5</v>
+        <v>289.33999999999997</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B437" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C437" s="3">
-        <v>1138.5</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="B438" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C438" s="3">
-        <v>58.69</v>
+        <v>242.34</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="B439" s="3">
         <v>4</v>
       </c>
       <c r="C439" s="3">
-        <v>289.33999999999997</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B440" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C440" s="3">
-        <v>48.76</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B441" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C441" s="3">
-        <v>242.34</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B442" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C442" s="3">
-        <v>54.09</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B443" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C443" s="3">
-        <v>54.1</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B444" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C444" s="3">
-        <v>255.03</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B445" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C445" s="3">
-        <v>220.8</v>
+        <v>344.28</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B446" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C446" s="3">
-        <v>255.03</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B447" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C447" s="3">
-        <v>68.86</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B448" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C448" s="3">
-        <v>344.28</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B449" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C449" s="3">
-        <v>60.29</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B450" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C450" s="3">
-        <v>261.8</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B451" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C451" s="3">
-        <v>261.8</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B452" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C452" s="3">
-        <v>30.58</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B453" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C453" s="3">
-        <v>30.58</v>
+        <v>641.49</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B454" s="3">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C454" s="3">
-        <v>16.95</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B455" s="3">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C455" s="3">
-        <v>24.95</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B456" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C456" s="3">
-        <v>641.49</v>
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B457" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C457" s="3">
-        <v>39.57</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B458" s="3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C458" s="3">
-        <v>51.83</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B459" s="3">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C459" s="3">
-        <v>33.840000000000003</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B460" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C460" s="3">
-        <v>150.15</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B461" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C461" s="3">
-        <v>144.5</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B462" s="3">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="C462" s="3">
-        <v>100.93</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B463" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C463" s="3">
-        <v>124.5</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B464" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C464" s="3">
-        <v>27.21</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B465" s="3">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="C465" s="3">
-        <v>24.79</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B466" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C466" s="3">
-        <v>37.1</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B467" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C467" s="3">
-        <v>178.04</v>
+        <v>859.21</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B468" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C468" s="3">
-        <v>23.88</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B469" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C469" s="3">
-        <v>8.26</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B470" s="3">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="C470" s="3">
-        <v>859.21</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B471" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C471" s="3">
-        <v>242.4</v>
+        <v>97.54</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B472" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C472" s="3">
-        <v>5000</v>
+        <v>304.02999999999997</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B473" s="3">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="C473" s="3">
-        <v>20.68</v>
+        <v>1934.56</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B474" s="3">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C474" s="3">
-        <v>97.54</v>
+        <v>230.99</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B475" s="3">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="C475" s="3">
-        <v>304.02999999999997</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B476" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="C476" s="3">
-        <v>1934.56</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3">
-      <c r="A477" t="s">
-        <v>405</v>
-      </c>
-      <c r="B477" s="3">
-        <v>6</v>
-      </c>
-      <c r="C477" s="3">
-        <v>230.99</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3">
-      <c r="A478" t="s">
-        <v>406</v>
-      </c>
-      <c r="B478" s="3">
-        <v>96</v>
-      </c>
-      <c r="C478" s="3">
-        <v>33.39</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3">
-      <c r="A479" t="s">
-        <v>407</v>
-      </c>
-      <c r="B479" s="3">
-        <v>48</v>
-      </c>
-      <c r="C479" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4141,7 +4141,7 @@
         <v>10</v>
       </c>
       <c r="C230" s="3">
-        <v>260</v>
+        <v>201.84</v>
       </c>
     </row>
     <row r="231" spans="1:3">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="403">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -529,9 +529,6 @@
     <t>RAV DXG SAE 5W30 USVO 4+1</t>
   </si>
   <si>
-    <t>RAV Diesel Clean Extreme 0.3L</t>
-  </si>
-  <si>
     <t>RAV E-PSF 1L</t>
   </si>
   <si>
@@ -556,9 +553,6 @@
     <t>RAV EPX SAE 80W90 GL5 1L</t>
   </si>
   <si>
-    <t>RAV EPX SAE 80W90 GL5 20L</t>
-  </si>
-  <si>
     <t>RAV EPX SAE 85W90 GL5 20L</t>
   </si>
   <si>
@@ -574,9 +568,6 @@
     <t>RAV FDS SAE 5W30 USVO 4+1</t>
   </si>
   <si>
-    <t>RAV FEL SAE 5W-30 1 L</t>
-  </si>
-  <si>
     <t>RAV FEL SAE 5W30 1L</t>
   </si>
   <si>
@@ -613,9 +604,6 @@
     <t>RAV GHA-F FLUID 1L</t>
   </si>
   <si>
-    <t>RAV HCS SAE 5W-40 1 L</t>
-  </si>
-  <si>
     <t>RAV HCS SAE 5W40 1L</t>
   </si>
   <si>
@@ -634,9 +622,6 @@
     <t>RAV HDS SAE 5W30 4L</t>
   </si>
   <si>
-    <t>RAV HDS SAW 5W30 5L</t>
-  </si>
-  <si>
     <t>RAV HJC 1.5L</t>
   </si>
   <si>
@@ -769,9 +754,6 @@
     <t>RAV PROFESSIONAL ENGINE CLEANER 0.3L</t>
   </si>
   <si>
-    <t>RAV PROFESSIONAL ENGINE CLEANER 0.3L PRM</t>
-  </si>
-  <si>
     <t>RAV PSA SAE 75W80 1L</t>
   </si>
   <si>
@@ -784,9 +766,6 @@
     <t>RAV QUAD 4T SAE 10W40 1L</t>
   </si>
   <si>
-    <t>RAV RECIPIENT PT ULEI 5L</t>
-  </si>
-  <si>
     <t>RAV REP SAE 5W30 1L</t>
   </si>
   <si>
@@ -1156,9 +1135,6 @@
     <t>RAV WIV II SAE 0W30 5L</t>
   </si>
   <si>
-    <t>RAVENOL SPRAY KETTENOEL OFF ROAD</t>
-  </si>
-  <si>
     <t>RAVENOL Spray Vaselina Off Road 0.4L</t>
   </si>
   <si>
@@ -1244,6 +1220,9 @@
   </si>
   <si>
     <t>RAV VSH SAE 0W20 5L</t>
+  </si>
+  <si>
+    <t>RAV HDS SAE 5W30 5L</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C476"/>
+  <dimension ref="A1:C425"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1663,7 +1642,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3">
         <v>239.2</v>
@@ -1674,98 +1653,98 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3">
-        <v>262.60000000000002</v>
+        <v>262.61</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3">
-        <v>262.61</v>
+        <v>407.86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
-        <v>10</v>
-      </c>
       <c r="C8" s="3">
-        <v>407.86</v>
+        <v>635.11</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3">
-        <v>635.11</v>
+        <v>309.52</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3">
-        <v>309.52</v>
+        <v>343.45</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3">
-        <v>343.45</v>
+        <v>467.19</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3">
-        <v>467.19</v>
+        <v>535.12</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="3">
-        <v>535.12</v>
+        <v>687.26</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3">
-        <v>687.26</v>
+        <v>825.42</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1773,7 +1752,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C15" s="3">
         <v>825.42</v>
@@ -1781,35 +1760,35 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3">
-        <v>825.42</v>
+        <v>902.73</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C17" s="3">
-        <v>902.73</v>
+        <v>698.39</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3">
-        <v>698.39</v>
+        <v>909.67</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1817,7 +1796,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3">
         <v>909.67</v>
@@ -1825,24 +1804,24 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="3">
-        <v>909.67</v>
+        <v>934.13</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" s="3">
-        <v>934.13</v>
+        <v>1132.73</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1858,46 +1837,46 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" s="3">
-        <v>1132.73</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
-        <v>2400</v>
+        <v>534.95000000000005</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>534.95000000000005</v>
+        <v>706.12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3">
         <v>3</v>
       </c>
       <c r="C26" s="3">
-        <v>706.12</v>
+        <v>241.24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1905,7 +1884,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3">
         <v>241.24</v>
@@ -1913,142 +1892,142 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C28" s="3">
-        <v>241.24</v>
+        <v>278.02</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C29" s="3">
-        <v>278.02</v>
+        <v>358.39</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C30" s="3">
-        <v>358.39</v>
+        <v>376.62</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C31" s="3">
-        <v>376.62</v>
+        <v>409.88</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C32" s="3">
-        <v>409.88</v>
+        <v>442.81</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C33" s="3">
-        <v>442.81</v>
+        <v>491.37</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="3">
-        <v>491.37</v>
+        <v>478.19</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3">
-        <v>478.19</v>
+        <v>108.16</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" s="3">
-        <v>108.16</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="3">
-        <v>33.28</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" s="3">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="C38" s="3">
-        <v>20.66</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="3">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="C39" s="3">
-        <v>41.58</v>
+        <v>5899.25</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40" s="3">
         <v>5899.25</v>
@@ -2056,54 +2035,54 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="3">
         <v>4</v>
       </c>
       <c r="C41" s="3">
-        <v>5899.25</v>
+        <v>182.58</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3">
-        <v>182.58</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" s="3">
         <v>7</v>
       </c>
       <c r="C43" s="3">
-        <v>41.58</v>
+        <v>146.97999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="C44" s="3">
-        <v>146.97999999999999</v>
+        <v>34.619999999999997</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="C45" s="3">
         <v>34.619999999999997</v>
@@ -2111,101 +2090,101 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C46" s="3">
-        <v>34.619999999999997</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C47" s="3">
-        <v>122.46</v>
+        <v>200.92</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B48" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C48" s="3">
-        <v>200.92</v>
+        <v>156.07</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" s="3">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C49" s="3">
-        <v>156.07</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="3">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C50" s="3">
-        <v>25.61</v>
+        <v>115.42</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B51" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C51" s="3">
-        <v>115.42</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C52" s="3">
-        <v>25.6</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>2936</v>
       </c>
       <c r="C53" s="3">
-        <v>36.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="3">
-        <v>3044</v>
+        <v>12</v>
       </c>
       <c r="C54" s="3">
-        <v>13</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2213,32 +2192,32 @@
         <v>51</v>
       </c>
       <c r="B55" s="3">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C55" s="3">
-        <v>20.99</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B56" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C56" s="3">
-        <v>23.37</v>
+        <v>361.92</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B57" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C57" s="3">
-        <v>361.92</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2246,21 +2225,21 @@
         <v>53</v>
       </c>
       <c r="B58" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C58" s="3">
-        <v>20.69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B59" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C59" s="3">
-        <v>21</v>
+        <v>318.18</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2271,18 +2250,18 @@
         <v>2</v>
       </c>
       <c r="C60" s="3">
-        <v>318.18</v>
+        <v>357.53</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B61" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C61" s="3">
-        <v>357.53</v>
+        <v>18.149999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2290,32 +2269,32 @@
         <v>55</v>
       </c>
       <c r="B62" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C62" s="3">
-        <v>18.149999999999999</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B63" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C63" s="3">
-        <v>19.3</v>
+        <v>337.5</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B64" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C64" s="3">
-        <v>337.5</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2323,7 +2302,7 @@
         <v>57</v>
       </c>
       <c r="B65" s="3">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C65" s="3">
         <v>33.64</v>
@@ -2331,57 +2310,57 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B66" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C66" s="3">
-        <v>33.64</v>
+        <v>298.12</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B67" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C67" s="3">
-        <v>298.12</v>
+        <v>1982.77</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B68" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C68" s="3">
-        <v>1982.77</v>
+        <v>280.12</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B69" s="3">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="C69" s="3">
-        <v>280.12</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B70" s="3">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="C70" s="3">
-        <v>24.51</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -2389,21 +2368,21 @@
         <v>62</v>
       </c>
       <c r="B71" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C71" s="3">
-        <v>26.08</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B72" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C72" s="3">
-        <v>26.21</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -2411,43 +2390,43 @@
         <v>63</v>
       </c>
       <c r="B73" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C73" s="3">
-        <v>87.56</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B74" s="3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C74" s="3">
-        <v>101.08</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B75" s="3">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="C75" s="3">
-        <v>29.13</v>
+        <v>102.31</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B76" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C76" s="3">
-        <v>102.31</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2455,227 +2434,227 @@
         <v>66</v>
       </c>
       <c r="B77" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C77" s="3">
-        <v>126.7</v>
+        <v>168.07</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B78" s="3">
-        <v>4</v>
+        <v>367</v>
       </c>
       <c r="C78" s="3">
-        <v>168.07</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B79" s="3">
-        <v>385</v>
+        <v>70</v>
       </c>
       <c r="C79" s="3">
-        <v>16.600000000000001</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="3">
         <v>68</v>
       </c>
-      <c r="B80" s="3">
-        <v>3</v>
-      </c>
       <c r="C80" s="3">
-        <v>60.08</v>
+        <v>76.569999999999993</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B81" s="3">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C81" s="3">
-        <v>60.95</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B82" s="3">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C82" s="3">
-        <v>76.569999999999993</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B83" s="3">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C83" s="3">
-        <v>16.79</v>
+        <v>64.430000000000007</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B84" s="3">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="C84" s="3">
-        <v>18.96</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B85" s="3">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C85" s="3">
-        <v>64.430000000000007</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B86" s="3">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C86" s="3">
-        <v>73.13</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B87" s="3">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C87" s="3">
-        <v>79.5</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B88" s="3">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C88" s="3">
-        <v>89.38</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B89" s="3">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C89" s="3">
-        <v>16.98</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B90" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C90" s="3">
-        <v>18.96</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B91" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C91" s="3">
-        <v>65.599999999999994</v>
+        <v>89.39</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B92" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C92" s="3">
-        <v>73.13</v>
+        <v>3173.52</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B93" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C93" s="3">
-        <v>89.39</v>
+        <v>190.08</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B94" s="3">
         <v>1</v>
       </c>
       <c r="C94" s="3">
-        <v>3173.52</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B95" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C95" s="3">
-        <v>190.08</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B96" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C96" s="3">
-        <v>66.12</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B97" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C97" s="3">
         <v>25.4</v>
@@ -2683,1737 +2662,1737 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B98" s="3">
         <v>15</v>
       </c>
       <c r="C98" s="3">
-        <v>40.92</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B99" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C99" s="3">
-        <v>25.4</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B100" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C100" s="3">
-        <v>28.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B101" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C101" s="3">
-        <v>23.33</v>
+        <v>34.630000000000003</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B102" s="3">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C102" s="3">
-        <v>0</v>
+        <v>16.559999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B103" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C103" s="3">
-        <v>27.95</v>
+        <v>82.88</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B104" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C104" s="3">
-        <v>34.630000000000003</v>
+        <v>161.01</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B105" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C105" s="3">
-        <v>16.559999999999999</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B106" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C106" s="3">
-        <v>82.88</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B107" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C107" s="3">
-        <v>161.01</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B108" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C108" s="3">
-        <v>44.85</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B109" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C109" s="3">
-        <v>65.83</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B110" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C110" s="3">
-        <v>46.76</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B111" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C111" s="3">
-        <v>62.11</v>
+        <v>1159.2</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B112" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C112" s="3">
-        <v>47.61</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B113" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C113" s="3">
-        <v>63.76</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B114" s="3">
         <v>1</v>
       </c>
       <c r="C114" s="3">
-        <v>1159.2</v>
+        <v>1391.04</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B115" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C115" s="3">
-        <v>255</v>
+        <v>87.1</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B116" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C116" s="3">
-        <v>62.1</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B117" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C117" s="3">
-        <v>69.55</v>
+        <v>460.01</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B118" s="3">
         <v>1</v>
       </c>
       <c r="C118" s="3">
-        <v>1391.04</v>
+        <v>639.4</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B119" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C119" s="3">
-        <v>87.1</v>
+        <v>103.89</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B120" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C120" s="3">
-        <v>40.54</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B121" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C121" s="3">
-        <v>460.01</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B122" s="3">
         <v>1</v>
       </c>
       <c r="C122" s="3">
-        <v>639.4</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B123" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C123" s="3">
-        <v>103.89</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B124" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C124" s="3">
-        <v>58.48</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B125" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C125" s="3">
-        <v>56.93</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C126" s="3">
-        <v>63.76</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B127" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C127" s="3">
-        <v>61.92</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B128" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C128" s="3">
-        <v>63.76</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B129" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C129" s="3">
-        <v>69.56</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B130" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C130" s="3">
-        <v>59.68</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B131" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C131" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B132" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C132" s="3">
-        <v>70.38</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B133" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C133" s="3">
-        <v>80.73</v>
+        <v>81.150000000000006</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B134" s="3">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C134" s="3">
-        <v>98.95</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B135" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C135" s="3">
-        <v>92.91</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B136" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C136" s="3">
-        <v>93.25</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B137" s="3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C137" s="3">
-        <v>56.93</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C138" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B139" s="3">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="C139" s="3">
-        <v>56.93</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B140" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C140" s="3">
-        <v>63.76</v>
+        <v>208.66</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B141" s="3">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C141" s="3">
-        <v>81.150000000000006</v>
+        <v>88.87</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B142" s="3">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="C142" s="3">
-        <v>63.76</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B143" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C143" s="3">
-        <v>69.87</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B144" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C144" s="3">
-        <v>63.76</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B145" s="3">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C145" s="3">
-        <v>69.56</v>
+        <v>149.91</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B146" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" s="3">
-        <v>69.56</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B147" s="3">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="C147" s="3">
-        <v>52.17</v>
+        <v>207.31</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B148" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C148" s="3">
-        <v>52.17</v>
+        <v>65.23</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B149" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C149" s="3">
-        <v>208.66</v>
+        <v>325.87</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B150" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C150" s="3">
-        <v>79.349999999999994</v>
+        <v>5165.8</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B151" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C151" s="3">
-        <v>88.87</v>
+        <v>511.75</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B152" s="3">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="C152" s="3">
-        <v>67.28</v>
+        <v>572.70000000000005</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B153" s="3">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="C153" s="3">
-        <v>62.11</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B154" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C154" s="3">
-        <v>69.55</v>
+        <v>367.42</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B155" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C155" s="3">
-        <v>63.89</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B156" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C156" s="3">
-        <v>149.91</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B157" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C157" s="3">
-        <v>95.05</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B158" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C158" s="3">
-        <v>38.57</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B159" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C159" s="3">
-        <v>207.31</v>
+        <v>3169.7</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B160" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C160" s="3">
-        <v>58.24</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C161" s="3">
-        <v>65.23</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B162" s="3">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C162" s="3">
-        <v>325.87</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B163" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C163" s="3">
-        <v>5165.8</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B164" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C164" s="3">
-        <v>511.75</v>
+        <v>93.35</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B165" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C165" s="3">
-        <v>572.70000000000005</v>
+        <v>1217.1600000000001</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B166" s="3">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C166" s="3">
-        <v>66.98</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B167" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C167" s="3">
-        <v>367.42</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B168" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C168" s="3">
-        <v>51.52</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C169" s="3">
-        <v>23.19</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B170" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C170" s="3">
-        <v>23.19</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B171" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C171" s="3">
-        <v>23.19</v>
+        <v>132.19</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B172" s="3">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C172" s="3">
-        <v>69.55</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B173" s="3">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C173" s="3">
-        <v>3169.7</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B174" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C174" s="3">
-        <v>81.14</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B175" s="3">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C175" s="3">
-        <v>81.14</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B176" s="3">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C176" s="3">
-        <v>66.98</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B177" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C177" s="3">
-        <v>53.83</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B178" s="3">
         <v>3</v>
       </c>
       <c r="C178" s="3">
-        <v>60.28</v>
+        <v>151.47999999999999</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B179" s="3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C179" s="3">
-        <v>60.29</v>
+        <v>181.68</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C180" s="3">
-        <v>82.65</v>
+        <v>20.059999999999999</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B181" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C181" s="3">
-        <v>93.35</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C182" s="3">
-        <v>1217.1600000000001</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C183" s="3">
-        <v>3079</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B184" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C184" s="3">
-        <v>43.7</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C185" s="3">
-        <v>48.95</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B186" s="3">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C186" s="3">
-        <v>64.59</v>
+        <v>38.770000000000003</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C187" s="3">
-        <v>72.33</v>
+        <v>107.35</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="B188" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C188" s="3">
-        <v>284.19</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B189" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C189" s="3">
-        <v>132.19</v>
+        <v>243.16</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="B190" s="3">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C190" s="3">
-        <v>75.260000000000005</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B191" s="3">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="C191" s="3">
-        <v>32.200000000000003</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B192" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C192" s="3">
-        <v>32.200000000000003</v>
+        <v>297.64999999999998</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B193" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C193" s="3">
-        <v>37.43</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B194" s="3">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C194" s="3">
-        <v>32.200000000000003</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B195" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C195" s="3">
-        <v>115.01</v>
+        <v>342.24</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B196" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C196" s="3">
-        <v>38.39</v>
+        <v>633.75</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B197" s="3">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C197" s="3">
-        <v>38.39</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B198" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198" s="3">
-        <v>151.47999999999999</v>
+        <v>787.75</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B199" s="3">
         <v>12</v>
       </c>
       <c r="C199" s="3">
-        <v>181.68</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B200" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C200" s="3">
-        <v>20.059999999999999</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B201" s="3">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C201" s="3">
-        <v>12.88</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B202" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C202" s="3">
-        <v>26.73</v>
+        <v>201.84</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B203" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C203" s="3">
-        <v>29.95</v>
+        <v>48.23</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B204" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C204" s="3">
-        <v>58.68</v>
+        <v>221.86</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B205" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C205" s="3">
-        <v>79.98</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B206" s="3">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C206" s="3">
-        <v>34.619999999999997</v>
+        <v>296.3</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B207" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C207" s="3">
-        <v>38.770000000000003</v>
+        <v>141.80000000000001</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B208" s="3">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C208" s="3">
-        <v>107.35</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B209" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C209" s="3">
-        <v>55.2</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B210" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C210" s="3">
-        <v>61.83</v>
+        <v>2189.02</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B211" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C211" s="3">
-        <v>243.16</v>
+        <v>453.22</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="B212" s="3">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C212" s="3">
-        <v>32.200000000000003</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="B213" s="3">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C213" s="3">
-        <v>63.78</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B214" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C214" s="3">
-        <v>67.849999999999994</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B215" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C215" s="3">
-        <v>75.989999999999995</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="B216" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C216" s="3">
-        <v>297.64999999999998</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="B217" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C217" s="3">
-        <v>77.28</v>
+        <v>179</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="B218" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C218" s="3">
-        <v>75.989999999999995</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="B219" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C219" s="3">
-        <v>342.24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B220" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C220" s="3">
-        <v>633.75</v>
+        <v>183.41</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>179</v>
+        <v>402</v>
       </c>
       <c r="B221" s="3">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C221" s="3">
-        <v>36.799999999999997</v>
+        <v>206.33</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="B222" s="3">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C222" s="3">
-        <v>50.51</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="B223" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C223" s="3">
-        <v>768.2</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="B224" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C224" s="3">
-        <v>787.75</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="B225" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C225" s="3">
-        <v>109.26</v>
+        <v>5345.33</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="B226" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C226" s="3">
-        <v>122.36</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="B227" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C227" s="3">
-        <v>31.98</v>
+        <v>192.51</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="B228" s="3">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C228" s="3">
-        <v>35.81</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B229" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C229" s="3">
-        <v>59.25</v>
+        <v>265.05</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="B230" s="3">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C230" s="3">
-        <v>201.84</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="B231" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C231" s="3">
-        <v>43.07</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="B232" s="3">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C232" s="3">
-        <v>48.23</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="B233" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C233" s="3">
-        <v>221.86</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="B234" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C234" s="3">
-        <v>74.7</v>
+        <v>16.809999999999999</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="B235" s="3">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C235" s="3">
-        <v>296.3</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="B236" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C236" s="3">
-        <v>141.80000000000001</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="B237" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C237" s="3">
-        <v>29.25</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="B238" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C238" s="3">
-        <v>41.4</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B239" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C239" s="3">
-        <v>173.3</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="B240" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C240" s="3">
-        <v>2189.02</v>
+        <v>466.78</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="B241" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C241" s="3">
-        <v>453.22</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="B242" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C242" s="3">
-        <v>48.64</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="B243" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C243" s="3">
-        <v>126.63</v>
+        <v>20789.41</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="B244" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C244" s="3">
-        <v>69.56</v>
+        <v>33057.85</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="B245" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C245" s="3">
-        <v>42.44</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="B246" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C246" s="3">
-        <v>44.51</v>
+        <v>81.650000000000006</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="B247" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C247" s="3">
-        <v>145.94</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="B248" s="3">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C248" s="3">
-        <v>179</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="B249" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C249" s="3">
-        <v>2060.8000000000002</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="B250" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C250" s="3">
-        <v>51</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="B251" s="3">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C251" s="3">
-        <v>51</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="B252" s="3">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C252" s="3">
-        <v>183.41</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B253" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C253" s="3">
-        <v>206.33</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="B254" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C254" s="3">
-        <v>29.9</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B255" s="3">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="C255" s="3">
         <v>33.479999999999997</v>
@@ -4421,2432 +4400,1871 @@
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B256" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C256" s="3">
-        <v>46.06</v>
+        <v>422.09</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="B257" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C257" s="3">
-        <v>4667</v>
+        <v>1277.7</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="B258" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C258" s="3">
-        <v>5345.33</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B259" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C259" s="3">
-        <v>170.78</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="B260" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C260" s="3">
-        <v>192.51</v>
+        <v>4456.4799999999996</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B261" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C261" s="3">
-        <v>59.7</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="B262" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C262" s="3">
-        <v>265.05</v>
+        <v>609.5</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="B263" s="3">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C263" s="3">
-        <v>36.799999999999997</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B264" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C264" s="3">
-        <v>103.04</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B265" s="3">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C265" s="3">
-        <v>36.75</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="B266" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C266" s="3">
-        <v>47.16</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="B267" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C267" s="3">
-        <v>16.809999999999999</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B268" s="3">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="C268" s="3">
-        <v>37.31</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="B269" s="3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C269" s="3">
-        <v>126.24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="B270" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C270" s="3">
-        <v>154.62</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="B271" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C271" s="3">
-        <v>508.2</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="B272" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C272" s="3">
-        <v>5069</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B273" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C273" s="3">
-        <v>466.78</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="B274" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C274" s="3">
-        <v>57.5</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="B275" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C275" s="3">
-        <v>63.13</v>
+        <v>71.709999999999994</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="B276" s="3">
         <v>1</v>
       </c>
       <c r="C276" s="3">
-        <v>20789.41</v>
+        <v>77.760000000000005</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="B277" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C277" s="3">
-        <v>33057.85</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="B278" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C278" s="3">
-        <v>83.5</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="B279" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C279" s="3">
-        <v>81.650000000000006</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="B280" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C280" s="3">
-        <v>45.88</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="B281" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C281" s="3">
-        <v>50.71</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="B282" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C282" s="3">
-        <v>50.71</v>
+        <v>331.2</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="B283" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C283" s="3">
-        <v>51.75</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="B284" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C284" s="3">
-        <v>36.94</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="B285" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C285" s="3">
-        <v>36.94</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="B286" s="3">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C286" s="3">
-        <v>67.28</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="B287" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C287" s="3">
-        <v>65.099999999999994</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="B288" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C288" s="3">
-        <v>65.53</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="B289" s="3">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="C289" s="3">
-        <v>65.53</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B290" s="3">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C290" s="3">
-        <v>109.08</v>
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="B291" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C291" s="3">
-        <v>29.89</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="B292" s="3">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="C292" s="3">
-        <v>33.479999999999997</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="B293" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C293" s="3">
-        <v>422.09</v>
+        <v>295.14999999999998</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="B294" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C294" s="3">
-        <v>1277.7</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="B295" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C295" s="3">
-        <v>6.44</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="B296" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C296" s="3">
-        <v>108.2</v>
+        <v>78.209999999999994</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="B297" s="3">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C297" s="3">
-        <v>4456.4799999999996</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="B298" s="3">
         <v>1</v>
       </c>
       <c r="C298" s="3">
-        <v>6279</v>
+        <v>6578.46</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B299" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C299" s="3">
-        <v>609.5</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="B300" s="3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C300" s="3">
-        <v>32.200000000000003</v>
+        <v>211.23</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="B301" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C301" s="3">
-        <v>32.200000000000003</v>
+        <v>2314.8000000000002</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="B302" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C302" s="3">
-        <v>32.200000000000003</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B303" s="3">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C303" s="3">
-        <v>32.200000000000003</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B304" s="3">
         <v>7</v>
       </c>
       <c r="C304" s="3">
-        <v>40.4</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="B305" s="3">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C305" s="3">
-        <v>36.06</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="B306" s="3">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="C306" s="3">
-        <v>36.06</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="B307" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C307" s="3">
-        <v>44.5</v>
+        <v>798.6</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="B308" s="3">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="C308" s="3">
-        <v>56.01</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="B309" s="3">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C309" s="3">
-        <v>57.63</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="B310" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C310" s="3">
-        <v>60.78</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="B311" s="3">
         <v>9</v>
       </c>
       <c r="C311" s="3">
-        <v>42.49</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="B312" s="3">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="C312" s="3">
-        <v>46.28</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="B313" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C313" s="3">
-        <v>59.21</v>
+        <v>36.869999999999997</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="B314" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C314" s="3">
-        <v>261.8</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="B315" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C315" s="3">
-        <v>71.709999999999994</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="B316" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C316" s="3">
-        <v>77.760000000000005</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="B317" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C317" s="3">
-        <v>54.7</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="B318" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C318" s="3">
-        <v>67.28</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="B319" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C319" s="3">
-        <v>251.5</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B320" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C320" s="3">
-        <v>78.87</v>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B321" s="3">
         <v>1</v>
       </c>
       <c r="C321" s="3">
-        <v>83.84</v>
+        <v>862.7</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B322" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C322" s="3">
-        <v>83.84</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="B323" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C323" s="3">
-        <v>331.2</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B324" s="3">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C324" s="3">
-        <v>79.75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="B325" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C325" s="3">
-        <v>65.209999999999994</v>
+        <v>267.85000000000002</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B326" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C326" s="3">
-        <v>83.84</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="B327" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C327" s="3">
-        <v>284</v>
+        <v>327.3</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="B328" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C328" s="3">
-        <v>28.15</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="B329" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C329" s="3">
-        <v>45.08</v>
+        <v>302.39999999999998</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="B330" s="3">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C330" s="3">
-        <v>51.52</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="B331" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C331" s="3">
-        <v>40.57</v>
+        <v>428.5</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="B332" s="3">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C332" s="3">
-        <v>36.229999999999997</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="B333" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C333" s="3">
-        <v>54.12</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="B334" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C334" s="3">
-        <v>69.55</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="B335" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C335" s="3">
-        <v>295.14999999999998</v>
+        <v>87.49</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="B336" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C336" s="3">
-        <v>38.56</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="B337" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C337" s="3">
-        <v>60.95</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="B338" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C338" s="3">
-        <v>78.209999999999994</v>
+        <v>3333.85</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="B339" s="3">
-        <v>134</v>
+        <v>4</v>
       </c>
       <c r="C339" s="3">
-        <v>44.93</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="B340" s="3">
         <v>1</v>
       </c>
       <c r="C340" s="3">
-        <v>6578.46</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="B341" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C341" s="3">
-        <v>173.09</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="B342" s="3">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C342" s="3">
-        <v>211.23</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="B343" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C343" s="3">
-        <v>2314.8000000000002</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="B344" s="3">
         <v>3</v>
       </c>
       <c r="C344" s="3">
-        <v>791.3</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="B345" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C345" s="3">
-        <v>31.6</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="B346" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C346" s="3">
-        <v>31.6</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="B347" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C347" s="3">
-        <v>77</v>
+        <v>370.53</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="B348" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C348" s="3">
-        <v>281</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="B349" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C349" s="3">
-        <v>43.8</v>
+        <v>4772.5</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="B350" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C350" s="3">
-        <v>21.9</v>
+        <v>516.46</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="B351" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C351" s="3">
-        <v>798.6</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="B352" s="3">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="C352" s="3">
-        <v>23.19</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="B353" s="3">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C353" s="3">
-        <v>8.24</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="B354" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C354" s="3">
-        <v>13.72</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="B355" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C355" s="3">
-        <v>31.95</v>
+        <v>461.23</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="B356" s="3">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="C356" s="3">
-        <v>16.2</v>
+        <v>518.41999999999996</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="B357" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C357" s="3">
-        <v>36.869999999999997</v>
+        <v>348.08</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="B358" s="3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C358" s="3">
-        <v>31.48</v>
+        <v>33.479999999999997</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="B359" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C359" s="3">
-        <v>21.9</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="B360" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C360" s="3">
-        <v>23.19</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="B361" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C361" s="3">
-        <v>19.55</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="B362" s="3">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C362" s="3">
-        <v>19.07</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="B363" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C363" s="3">
-        <v>21.9</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="B364" s="3">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="C364" s="3">
-        <v>79.349999999999994</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="B365" s="3">
         <v>1</v>
       </c>
       <c r="C365" s="3">
-        <v>862.7</v>
+        <v>304.54000000000002</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B366" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C366" s="3">
-        <v>56.93</v>
+        <v>34.049999999999997</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="B367" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C367" s="3">
-        <v>1265</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="B368" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C368" s="3">
-        <v>76</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="B369" s="3">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C369" s="3">
-        <v>267.85000000000002</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="B370" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C370" s="3">
-        <v>74.7</v>
+        <v>7173.59</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="B371" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C371" s="3">
-        <v>327.3</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="B372" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C372" s="3">
-        <v>72.13</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="B373" s="3">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C373" s="3">
-        <v>302.39999999999998</v>
+        <v>191</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="B374" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C374" s="3">
-        <v>36.799999999999997</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="B375" s="3">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="C375" s="3">
-        <v>428.5</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="B376" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C376" s="3">
-        <v>450.22</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="B377" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C377" s="3">
-        <v>465.7</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="B378" s="3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C378" s="3">
-        <v>38.25</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="B379" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C379" s="3">
-        <v>87.49</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="B380" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C380" s="3">
-        <v>63.13</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="B381" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C381" s="3">
-        <v>377.78</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="B382" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C382" s="3">
-        <v>3333.85</v>
+        <v>319.60000000000002</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="B383" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C383" s="3">
-        <v>374.67</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B384" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C384" s="3">
-        <v>120.06</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="B385" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C385" s="3">
-        <v>54.2</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="B386" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C386" s="3">
-        <v>54.2</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>326</v>
+        <v>400</v>
       </c>
       <c r="B387" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C387" s="3">
-        <v>31.5</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>327</v>
+        <v>401</v>
       </c>
       <c r="B388" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C388" s="3">
-        <v>114.09</v>
+        <v>289.33999999999997</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="B389" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C389" s="3">
-        <v>139.9</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="B390" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C390" s="3">
-        <v>35.94</v>
+        <v>242.34</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="B391" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C391" s="3">
-        <v>140.26</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="B392" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C392" s="3">
-        <v>370.53</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="B393" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C393" s="3">
-        <v>30.9</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="B394" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C394" s="3">
-        <v>4772.5</v>
+        <v>255.02</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="B395" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C395" s="3">
-        <v>516.46</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="B396" s="3">
         <v>4</v>
       </c>
       <c r="C396" s="3">
-        <v>185.15</v>
+        <v>344.28</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="B397" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C397" s="3">
-        <v>11.5</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="B398" s="3">
         <v>4</v>
       </c>
       <c r="C398" s="3">
-        <v>724.5</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="B399" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C399" s="3">
-        <v>450.22</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="B400" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C400" s="3">
-        <v>461.23</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="B401" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C401" s="3">
-        <v>518.41999999999996</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="B402" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C402" s="3">
-        <v>348.08</v>
+        <v>641.49</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="B403" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C403" s="3">
-        <v>33.479999999999997</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="B404" s="3">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C404" s="3">
-        <v>35.79</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="B405" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C405" s="3">
-        <v>377.7</v>
+        <v>33.840000000000003</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="B406" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C406" s="3">
-        <v>33.21</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="B407" s="3">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C407" s="3">
-        <v>27.16</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="B408" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C408" s="3">
-        <v>361.41</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="B409" s="3">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C409" s="3">
-        <v>29.25</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="B410" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C410" s="3">
-        <v>29.26</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="B411" s="3">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="C411" s="3">
-        <v>304.54000000000002</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="B412" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C412" s="3">
-        <v>34.049999999999997</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="B413" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C413" s="3">
-        <v>57.7</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="B414" s="3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C414" s="3">
-        <v>90.9</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="B415" s="3">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C415" s="3">
-        <v>42.24</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="B416" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C416" s="3">
-        <v>44.31</v>
+        <v>859.21</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="B417" s="3">
         <v>1</v>
       </c>
       <c r="C417" s="3">
-        <v>7173.59</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="B418" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C418" s="3">
-        <v>677.79</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="B419" s="3">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="C419" s="3">
-        <v>167.33</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="B420" s="3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C420" s="3">
-        <v>191.01</v>
+        <v>97.54</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="B421" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C421" s="3">
-        <v>2335.67</v>
+        <v>304.02999999999997</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="B422" s="3">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C422" s="3">
-        <v>62.04</v>
+        <v>1934.56</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="B423" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C423" s="3">
-        <v>8139.6</v>
+        <v>230.99</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="B424" s="3">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="C424" s="3">
-        <v>235.53</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B425" s="3">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C425" s="3">
-        <v>259.8</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3">
-      <c r="A426" t="s">
-        <v>362</v>
-      </c>
-      <c r="B426" s="3">
-        <v>1</v>
-      </c>
-      <c r="C426" s="3">
-        <v>310.2</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3">
-      <c r="A427" t="s">
-        <v>363</v>
-      </c>
-      <c r="B427" s="3">
-        <v>1</v>
-      </c>
-      <c r="C427" s="3">
-        <v>36.43</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3">
-      <c r="A428" t="s">
-        <v>364</v>
-      </c>
-      <c r="B428" s="3">
-        <v>15</v>
-      </c>
-      <c r="C428" s="3">
-        <v>87.22</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3">
-      <c r="A429" t="s">
-        <v>365</v>
-      </c>
-      <c r="B429" s="3">
-        <v>11</v>
-      </c>
-      <c r="C429" s="3">
-        <v>319.60000000000002</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3">
-      <c r="A430" t="s">
-        <v>366</v>
-      </c>
-      <c r="B430" s="3">
-        <v>25</v>
-      </c>
-      <c r="C430" s="3">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3">
-      <c r="A431" t="s">
-        <v>367</v>
-      </c>
-      <c r="B431" s="3">
-        <v>7</v>
-      </c>
-      <c r="C431" s="3">
-        <v>312.8</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3">
-      <c r="A432" t="s">
-        <v>368</v>
-      </c>
-      <c r="B432" s="3">
-        <v>45</v>
-      </c>
-      <c r="C432" s="3">
-        <v>67.28</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3">
-      <c r="A433" t="s">
-        <v>369</v>
-      </c>
-      <c r="B433" s="3">
-        <v>3</v>
-      </c>
-      <c r="C433" s="3">
-        <v>1138.5</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3">
-      <c r="A434" t="s">
-        <v>369</v>
-      </c>
-      <c r="B434" s="3">
-        <v>1</v>
-      </c>
-      <c r="C434" s="3">
-        <v>1138.5</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3">
-      <c r="A435" t="s">
-        <v>408</v>
-      </c>
-      <c r="B435" s="3">
-        <v>12</v>
-      </c>
-      <c r="C435" s="3">
-        <v>58.69</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3">
-      <c r="A436" t="s">
-        <v>409</v>
-      </c>
-      <c r="B436" s="3">
-        <v>4</v>
-      </c>
-      <c r="C436" s="3">
-        <v>289.33999999999997</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3">
-      <c r="A437" t="s">
-        <v>370</v>
-      </c>
-      <c r="B437" s="3">
-        <v>2</v>
-      </c>
-      <c r="C437" s="3">
-        <v>48.76</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3">
-      <c r="A438" t="s">
-        <v>371</v>
-      </c>
-      <c r="B438" s="3">
-        <v>2</v>
-      </c>
-      <c r="C438" s="3">
-        <v>242.34</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3">
-      <c r="A439" t="s">
-        <v>372</v>
-      </c>
-      <c r="B439" s="3">
-        <v>4</v>
-      </c>
-      <c r="C439" s="3">
-        <v>54.09</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3">
-      <c r="A440" t="s">
-        <v>372</v>
-      </c>
-      <c r="B440" s="3">
-        <v>30</v>
-      </c>
-      <c r="C440" s="3">
-        <v>54.1</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3">
-      <c r="A441" t="s">
-        <v>373</v>
-      </c>
-      <c r="B441" s="3">
-        <v>20</v>
-      </c>
-      <c r="C441" s="3">
-        <v>255.03</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3">
-      <c r="A442" t="s">
-        <v>374</v>
-      </c>
-      <c r="B442" s="3">
-        <v>18</v>
-      </c>
-      <c r="C442" s="3">
-        <v>220.8</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3">
-      <c r="A443" t="s">
-        <v>375</v>
-      </c>
-      <c r="B443" s="3">
-        <v>20</v>
-      </c>
-      <c r="C443" s="3">
-        <v>255.03</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3">
-      <c r="A444" t="s">
-        <v>376</v>
-      </c>
-      <c r="B444" s="3">
-        <v>12</v>
-      </c>
-      <c r="C444" s="3">
-        <v>68.86</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3">
-      <c r="A445" t="s">
-        <v>377</v>
-      </c>
-      <c r="B445" s="3">
-        <v>4</v>
-      </c>
-      <c r="C445" s="3">
-        <v>344.28</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3">
-      <c r="A446" t="s">
-        <v>378</v>
-      </c>
-      <c r="B446" s="3">
-        <v>10</v>
-      </c>
-      <c r="C446" s="3">
-        <v>60.29</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3">
-      <c r="A447" t="s">
-        <v>379</v>
-      </c>
-      <c r="B447" s="3">
-        <v>3</v>
-      </c>
-      <c r="C447" s="3">
-        <v>261.8</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3">
-      <c r="A448" t="s">
-        <v>379</v>
-      </c>
-      <c r="B448" s="3">
-        <v>1</v>
-      </c>
-      <c r="C448" s="3">
-        <v>261.8</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3">
-      <c r="A449" t="s">
-        <v>380</v>
-      </c>
-      <c r="B449" s="3">
-        <v>1</v>
-      </c>
-      <c r="C449" s="3">
-        <v>30.58</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3">
-      <c r="A450" t="s">
-        <v>381</v>
-      </c>
-      <c r="B450" s="3">
-        <v>1</v>
-      </c>
-      <c r="C450" s="3">
-        <v>30.58</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3">
-      <c r="A451" t="s">
-        <v>382</v>
-      </c>
-      <c r="B451" s="3">
-        <v>54</v>
-      </c>
-      <c r="C451" s="3">
-        <v>16.95</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3">
-      <c r="A452" t="s">
-        <v>383</v>
-      </c>
-      <c r="B452" s="3">
-        <v>45</v>
-      </c>
-      <c r="C452" s="3">
-        <v>24.95</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3">
-      <c r="A453" t="s">
-        <v>384</v>
-      </c>
-      <c r="B453" s="3">
-        <v>3</v>
-      </c>
-      <c r="C453" s="3">
-        <v>641.49</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3">
-      <c r="A454" t="s">
-        <v>385</v>
-      </c>
-      <c r="B454" s="3">
-        <v>12</v>
-      </c>
-      <c r="C454" s="3">
-        <v>39.57</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3">
-      <c r="A455" t="s">
-        <v>386</v>
-      </c>
-      <c r="B455" s="3">
-        <v>36</v>
-      </c>
-      <c r="C455" s="3">
-        <v>51.83</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3">
-      <c r="A456" t="s">
-        <v>387</v>
-      </c>
-      <c r="B456" s="3">
-        <v>44</v>
-      </c>
-      <c r="C456" s="3">
-        <v>33.840000000000003</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3">
-      <c r="A457" t="s">
-        <v>388</v>
-      </c>
-      <c r="B457" s="3">
-        <v>19</v>
-      </c>
-      <c r="C457" s="3">
-        <v>150.15</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3">
-      <c r="A458" t="s">
-        <v>389</v>
-      </c>
-      <c r="B458" s="3">
-        <v>25</v>
-      </c>
-      <c r="C458" s="3">
-        <v>144.5</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3">
-      <c r="A459" t="s">
-        <v>390</v>
-      </c>
-      <c r="B459" s="3">
-        <v>25</v>
-      </c>
-      <c r="C459" s="3">
-        <v>100.93</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3">
-      <c r="A460" t="s">
-        <v>391</v>
-      </c>
-      <c r="B460" s="3">
-        <v>14</v>
-      </c>
-      <c r="C460" s="3">
-        <v>124.5</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3">
-      <c r="A461" t="s">
-        <v>392</v>
-      </c>
-      <c r="B461" s="3">
-        <v>10</v>
-      </c>
-      <c r="C461" s="3">
-        <v>27.21</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3">
-      <c r="A462" t="s">
-        <v>393</v>
-      </c>
-      <c r="B462" s="3">
-        <v>94</v>
-      </c>
-      <c r="C462" s="3">
-        <v>24.79</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3">
-      <c r="A463" t="s">
-        <v>394</v>
-      </c>
-      <c r="B463" s="3">
-        <v>6</v>
-      </c>
-      <c r="C463" s="3">
-        <v>37.1</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3">
-      <c r="A464" t="s">
-        <v>395</v>
-      </c>
-      <c r="B464" s="3">
-        <v>8</v>
-      </c>
-      <c r="C464" s="3">
-        <v>178.04</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3">
-      <c r="A465" t="s">
-        <v>396</v>
-      </c>
-      <c r="B465" s="3">
-        <v>48</v>
-      </c>
-      <c r="C465" s="3">
-        <v>23.88</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3">
-      <c r="A466" t="s">
-        <v>397</v>
-      </c>
-      <c r="B466" s="3">
-        <v>50</v>
-      </c>
-      <c r="C466" s="3">
-        <v>8.26</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3">
-      <c r="A467" t="s">
-        <v>398</v>
-      </c>
-      <c r="B467" s="3">
-        <v>1</v>
-      </c>
-      <c r="C467" s="3">
-        <v>859.21</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3">
-      <c r="A468" t="s">
-        <v>399</v>
-      </c>
-      <c r="B468" s="3">
-        <v>1</v>
-      </c>
-      <c r="C468" s="3">
-        <v>242.4</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3">
-      <c r="A469" t="s">
-        <v>400</v>
-      </c>
-      <c r="B469" s="3">
-        <v>3</v>
-      </c>
-      <c r="C469" s="3">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3">
-      <c r="A470" t="s">
-        <v>401</v>
-      </c>
-      <c r="B470" s="3">
-        <v>93</v>
-      </c>
-      <c r="C470" s="3">
-        <v>20.68</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3">
-      <c r="A471" t="s">
-        <v>402</v>
-      </c>
-      <c r="B471" s="3">
-        <v>31</v>
-      </c>
-      <c r="C471" s="3">
-        <v>97.54</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3">
-      <c r="A472" t="s">
-        <v>403</v>
-      </c>
-      <c r="B472" s="3">
-        <v>10</v>
-      </c>
-      <c r="C472" s="3">
-        <v>304.02999999999997</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3">
-      <c r="A473" t="s">
-        <v>404</v>
-      </c>
-      <c r="B473" s="3">
-        <v>4</v>
-      </c>
-      <c r="C473" s="3">
-        <v>1934.56</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3">
-      <c r="A474" t="s">
-        <v>405</v>
-      </c>
-      <c r="B474" s="3">
-        <v>6</v>
-      </c>
-      <c r="C474" s="3">
-        <v>230.99</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3">
-      <c r="A475" t="s">
-        <v>406</v>
-      </c>
-      <c r="B475" s="3">
-        <v>96</v>
-      </c>
-      <c r="C475" s="3">
-        <v>33.39</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3">
-      <c r="A476" t="s">
-        <v>407</v>
-      </c>
-      <c r="B476" s="3">
-        <v>48</v>
-      </c>
-      <c r="C476" s="3">
         <v>20.66</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="412">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1635,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D411"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1662,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -1914,7 +1914,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2124,7 +2124,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="3">
         <v>146.97999999999999</v>
@@ -2278,10 +2278,10 @@
         <v>47</v>
       </c>
       <c r="B46" s="3">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="C46" s="3">
-        <v>20.99</v>
+        <v>23.37</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>405</v>
@@ -2289,13 +2289,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C47" s="3">
-        <v>23.37</v>
+        <v>361.92</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>405</v>
@@ -2303,13 +2303,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C48" s="3">
-        <v>361.92</v>
+        <v>20.69</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>405</v>
@@ -2320,10 +2320,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C49" s="3">
-        <v>20.69</v>
+        <v>21</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>405</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3">
-        <v>21</v>
+        <v>318.18</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>405</v>
@@ -2351,7 +2351,7 @@
         <v>2</v>
       </c>
       <c r="C51" s="3">
-        <v>318.18</v>
+        <v>357.53</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>405</v>
@@ -2359,13 +2359,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C52" s="3">
-        <v>357.53</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>405</v>
@@ -2376,10 +2376,10 @@
         <v>51</v>
       </c>
       <c r="B53" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C53" s="3">
-        <v>18.149999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>405</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C54" s="3">
-        <v>19.3</v>
+        <v>337.5</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>405</v>
@@ -2401,13 +2401,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C55" s="3">
-        <v>337.5</v>
+        <v>33.64</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>405</v>
@@ -2418,7 +2418,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="3">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C56" s="3">
         <v>33.64</v>
@@ -2429,41 +2429,41 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B57" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C57" s="3">
-        <v>33.64</v>
+        <v>298.12</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B58" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C58" s="3">
-        <v>298.12</v>
+        <v>1982.77</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C59" s="3">
-        <v>1982.77</v>
+        <v>280.12</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>406</v>
@@ -2471,27 +2471,27 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B60" s="3">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="C60" s="3">
-        <v>280.12</v>
+        <v>24.51</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B61" s="3">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="C61" s="3">
-        <v>24.51</v>
+        <v>26.08</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>402</v>
@@ -2502,10 +2502,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C62" s="3">
-        <v>26.08</v>
+        <v>26.21</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>402</v>
@@ -2513,13 +2513,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B63" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C63" s="3">
-        <v>26.21</v>
+        <v>87.56</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>402</v>
@@ -2530,10 +2530,10 @@
         <v>59</v>
       </c>
       <c r="B64" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C64" s="3">
-        <v>87.56</v>
+        <v>101.08</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>402</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B65" s="3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C65" s="3">
-        <v>101.08</v>
+        <v>29.13</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>402</v>
@@ -2555,13 +2555,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B66" s="3">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="C66" s="3">
-        <v>29.13</v>
+        <v>102.31</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>402</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B67" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C67" s="3">
-        <v>102.31</v>
+        <v>126.7</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>402</v>
@@ -2586,10 +2586,10 @@
         <v>62</v>
       </c>
       <c r="B68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68" s="3">
-        <v>126.7</v>
+        <v>168.07</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>402</v>
@@ -2597,13 +2597,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B69" s="3">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="C69" s="3">
-        <v>168.07</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>402</v>
@@ -2611,13 +2611,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B70" s="3">
-        <v>367</v>
+        <v>70</v>
       </c>
       <c r="C70" s="3">
-        <v>16.600000000000001</v>
+        <v>60.95</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>402</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B71" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C71" s="3">
-        <v>60.95</v>
+        <v>76.569999999999993</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>402</v>
@@ -2639,13 +2639,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B72" s="3">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C72" s="3">
-        <v>76.569999999999993</v>
+        <v>16.79</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>402</v>
@@ -2656,10 +2656,10 @@
         <v>66</v>
       </c>
       <c r="B73" s="3">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="C73" s="3">
-        <v>16.79</v>
+        <v>18.96</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>402</v>
@@ -2667,13 +2667,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B74" s="3">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="C74" s="3">
-        <v>18.96</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>402</v>
@@ -2684,10 +2684,10 @@
         <v>67</v>
       </c>
       <c r="B75" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C75" s="3">
-        <v>64.430000000000007</v>
+        <v>73.13</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>402</v>
@@ -2695,13 +2695,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B76" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C76" s="3">
-        <v>73.13</v>
+        <v>79.5</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>402</v>
@@ -2712,10 +2712,10 @@
         <v>68</v>
       </c>
       <c r="B77" s="3">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C77" s="3">
-        <v>79.5</v>
+        <v>89.38</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>402</v>
@@ -2723,13 +2723,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B78" s="3">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C78" s="3">
-        <v>89.38</v>
+        <v>18.96</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>402</v>
@@ -2737,13 +2737,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B79" s="3">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C79" s="3">
-        <v>16.98</v>
+        <v>73.13</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>402</v>
@@ -2751,13 +2751,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B80" s="3">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C80" s="3">
-        <v>18.96</v>
+        <v>89.39</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>402</v>
@@ -2765,13 +2765,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B81" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C81" s="3">
-        <v>65.599999999999994</v>
+        <v>3173.52</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>402</v>
@@ -2779,55 +2779,55 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B82" s="3">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C82" s="3">
-        <v>73.13</v>
+        <v>25.4</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B83" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C83" s="3">
-        <v>89.39</v>
+        <v>40.92</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C84" s="3">
-        <v>3173.52</v>
+        <v>25.4</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B85" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C85" s="3">
-        <v>25.4</v>
+        <v>28.07</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>404</v>
@@ -2835,13 +2835,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B86" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C86" s="3">
-        <v>40.92</v>
+        <v>23.33</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>404</v>
@@ -2849,69 +2849,69 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B87" s="3">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C87" s="3">
-        <v>25.4</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B88" s="3">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C88" s="3">
-        <v>28.07</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B89" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C89" s="3">
-        <v>23.33</v>
+        <v>82.88</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B90" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C90" s="3">
-        <v>34.630000000000003</v>
+        <v>161.01</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B91" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C91" s="3">
-        <v>16.559999999999999</v>
+        <v>44.85</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>407</v>
@@ -2919,83 +2919,83 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B92" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C92" s="3">
-        <v>82.88</v>
+        <v>65.83</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B93" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C93" s="3">
-        <v>161.01</v>
+        <v>46.76</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B94" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C94" s="3">
-        <v>44.85</v>
+        <v>62.11</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B95" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C95" s="3">
-        <v>65.83</v>
+        <v>47.61</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B96" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96" s="3">
-        <v>46.76</v>
+        <v>63.76</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B97" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C97" s="3">
-        <v>62.11</v>
+        <v>1159.2</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>405</v>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B98" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C98" s="3">
-        <v>47.61</v>
+        <v>255</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>405</v>
@@ -3017,13 +3017,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B99" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C99" s="3">
-        <v>63.76</v>
+        <v>69.55</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>405</v>
@@ -3031,13 +3031,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B100" s="3">
         <v>1</v>
       </c>
       <c r="C100" s="3">
-        <v>1159.2</v>
+        <v>1391.04</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>405</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B101" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C101" s="3">
-        <v>255</v>
+        <v>87.1</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>405</v>
@@ -3059,13 +3059,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B102" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C102" s="3">
-        <v>69.55</v>
+        <v>40.54</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>405</v>
@@ -3073,13 +3073,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B103" s="3">
         <v>1</v>
       </c>
       <c r="C103" s="3">
-        <v>1391.04</v>
+        <v>460.01</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>405</v>
@@ -3087,13 +3087,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B104" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C104" s="3">
-        <v>87.1</v>
+        <v>639.4</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>405</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B105" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C105" s="3">
-        <v>40.54</v>
+        <v>103.89</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>405</v>
@@ -3115,13 +3115,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B106" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C106" s="3">
-        <v>460.01</v>
+        <v>58.48</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>405</v>
@@ -3129,13 +3129,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C107" s="3">
-        <v>639.4</v>
+        <v>56.93</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>405</v>
@@ -3143,13 +3143,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B108" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C108" s="3">
-        <v>103.89</v>
+        <v>63.76</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>405</v>
@@ -3157,13 +3157,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B109" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C109" s="3">
-        <v>58.48</v>
+        <v>61.92</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>405</v>
@@ -3171,13 +3171,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B110" s="3">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C110" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>405</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B111" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C111" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>405</v>
@@ -3199,13 +3199,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B112" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C112" s="3">
-        <v>61.92</v>
+        <v>59.68</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>405</v>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B113" s="3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C113" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>405</v>
@@ -3227,13 +3227,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B114" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C114" s="3">
-        <v>69.56</v>
+        <v>80.73</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>405</v>
@@ -3241,13 +3241,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B115" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C115" s="3">
-        <v>59.68</v>
+        <v>98.95</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>405</v>
@@ -3255,13 +3255,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B116" s="3">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C116" s="3">
-        <v>56.93</v>
+        <v>93.25</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>405</v>
@@ -3269,13 +3269,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B117" s="3">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C117" s="3">
-        <v>80.73</v>
+        <v>63.76</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>405</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B118" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C118" s="3">
-        <v>98.95</v>
+        <v>63.76</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>405</v>
@@ -3297,13 +3297,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B119" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C119" s="3">
-        <v>93.25</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>405</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B120" s="3">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C120" s="3">
         <v>63.76</v>
@@ -3325,13 +3325,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B121" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C121" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>405</v>
@@ -3339,13 +3339,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B122" s="3">
         <v>14</v>
       </c>
       <c r="C122" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>405</v>
@@ -3353,13 +3353,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B123" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C123" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>405</v>
@@ -3367,13 +3367,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B124" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C124" s="3">
-        <v>69.87</v>
+        <v>69.56</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>405</v>
@@ -3381,13 +3381,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B125" s="3">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C125" s="3">
-        <v>63.76</v>
+        <v>52.17</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>405</v>
@@ -3395,13 +3395,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B126" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C126" s="3">
-        <v>69.56</v>
+        <v>208.66</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>405</v>
@@ -3409,13 +3409,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B127" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C127" s="3">
-        <v>69.56</v>
+        <v>88.87</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>405</v>
@@ -3423,13 +3423,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B128" s="3">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C128" s="3">
-        <v>52.17</v>
+        <v>67.27</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>405</v>
@@ -3437,13 +3437,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B129" s="3">
         <v>9</v>
       </c>
       <c r="C129" s="3">
-        <v>208.66</v>
+        <v>69.55</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>405</v>
@@ -3451,13 +3451,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B130" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C130" s="3">
-        <v>88.87</v>
+        <v>63.89</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>405</v>
@@ -3465,13 +3465,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B131" s="3">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="C131" s="3">
-        <v>67.27</v>
+        <v>149.91</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>405</v>
@@ -3479,13 +3479,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B132" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C132" s="3">
-        <v>69.55</v>
+        <v>38.57</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>405</v>
@@ -3493,13 +3493,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B133" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C133" s="3">
-        <v>63.89</v>
+        <v>207.31</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>405</v>
@@ -3507,41 +3507,41 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B134" s="3">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C134" s="3">
-        <v>149.91</v>
+        <v>65.23</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B135" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C135" s="3">
-        <v>38.57</v>
+        <v>325.87</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B136" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C136" s="3">
-        <v>207.31</v>
+        <v>5165.8</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>405</v>
@@ -3549,55 +3549,55 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B137" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C137" s="3">
-        <v>65.23</v>
+        <v>511.75</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B138" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C138" s="3">
-        <v>325.87</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B139" s="3">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="C139" s="3">
-        <v>5165.8</v>
+        <v>66.98</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B140" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C140" s="3">
-        <v>511.75</v>
+        <v>367.42</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>405</v>
@@ -3605,97 +3605,97 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B141" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C141" s="3">
-        <v>572.70000000000005</v>
+        <v>51.52</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B142" s="3">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="C142" s="3">
-        <v>66.98</v>
+        <v>23.19</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B143" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C143" s="3">
-        <v>367.42</v>
+        <v>23.19</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B144" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C144" s="3">
-        <v>51.52</v>
+        <v>69.55</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B145" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C145" s="3">
-        <v>23.19</v>
+        <v>3169.7</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B146" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C146" s="3">
-        <v>23.19</v>
+        <v>81.14</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B147" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C147" s="3">
-        <v>69.55</v>
+        <v>81.14</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>405</v>
@@ -3703,27 +3703,27 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B148" s="3">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="C148" s="3">
-        <v>3169.7</v>
+        <v>66.98</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B149" s="3">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C149" s="3">
-        <v>81.14</v>
+        <v>60.28</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>405</v>
@@ -3731,13 +3731,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B150" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C150" s="3">
-        <v>81.14</v>
+        <v>93.35</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>405</v>
@@ -3745,27 +3745,27 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B151" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C151" s="3">
-        <v>66.98</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B152" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C152" s="3">
-        <v>60.28</v>
+        <v>3079</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>405</v>
@@ -3773,122 +3773,122 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B153" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C153" s="3">
-        <v>93.35</v>
+        <v>43.7</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B154" s="3">
         <v>1</v>
       </c>
       <c r="C154" s="3">
-        <v>1217.1600000000001</v>
+        <v>48.95</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C155" s="3">
-        <v>3079</v>
+        <v>72.33</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B156" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C156" s="3">
-        <v>43.7</v>
+        <v>284.19</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C157" s="3">
-        <v>48.95</v>
+        <v>132.19</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B158" s="3">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C158" s="3">
-        <v>72.33</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B159" s="3">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C159" s="3">
-        <v>284.19</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B160" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C160" s="3">
-        <v>132.19</v>
+        <v>37.43</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B161" s="3">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C161" s="3">
         <v>32.200000000000003</v>
@@ -3899,111 +3899,111 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B162" s="3">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="C162" s="3">
-        <v>32.200000000000003</v>
+        <v>115.01</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B163" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C163" s="3">
-        <v>37.43</v>
+        <v>38.39</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B164" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C164" s="3">
-        <v>32.200000000000003</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B165" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C165" s="3">
-        <v>115.01</v>
+        <v>181.68</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B166" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C166" s="3">
-        <v>38.39</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B167" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C167" s="3">
-        <v>151.47999999999999</v>
+        <v>12.88</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B168" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C168" s="3">
-        <v>181.68</v>
+        <v>26.73</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B169" s="3">
         <v>12</v>
       </c>
       <c r="C169" s="3">
-        <v>20.059999999999999</v>
+        <v>29.95</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>392</v>
@@ -4011,13 +4011,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B170" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C170" s="3">
-        <v>12.88</v>
+        <v>58.68</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>392</v>
@@ -4025,13 +4025,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B171" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C171" s="3">
-        <v>26.73</v>
+        <v>79.98</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>392</v>
@@ -4039,69 +4039,69 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B172" s="3">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C172" s="3">
-        <v>29.95</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B173" s="3">
         <v>10</v>
       </c>
       <c r="C173" s="3">
-        <v>58.68</v>
+        <v>107.35</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B174" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C174" s="3">
-        <v>79.98</v>
+        <v>61.83</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B175" s="3">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="C175" s="3">
-        <v>38.770000000000003</v>
+        <v>243.16</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B176" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C176" s="3">
-        <v>107.35</v>
+        <v>63.78</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>405</v>
@@ -4109,13 +4109,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B177" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C177" s="3">
-        <v>61.83</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>402</v>
@@ -4123,13 +4123,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B178" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C178" s="3">
-        <v>243.16</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>402</v>
@@ -4137,24 +4137,24 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B179" s="3">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C179" s="3">
-        <v>63.78</v>
+        <v>77.28</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B180" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C180" s="3">
         <v>75.989999999999995</v>
@@ -4165,13 +4165,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B181" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C181" s="3">
-        <v>297.64999999999998</v>
+        <v>342.24</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>402</v>
@@ -4179,125 +4179,125 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B182" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C182" s="3">
-        <v>77.28</v>
+        <v>633.75</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B183" s="3">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C183" s="3">
-        <v>75.989999999999995</v>
+        <v>50.51</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B184" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C184" s="3">
-        <v>342.24</v>
+        <v>787.75</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B185" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C185" s="3">
-        <v>633.75</v>
+        <v>122.36</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B186" s="3">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C186" s="3">
-        <v>50.51</v>
+        <v>35.81</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B187" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C187" s="3">
-        <v>787.75</v>
+        <v>59.25</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B188" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C188" s="3">
-        <v>122.36</v>
+        <v>201.84</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B189" s="3">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C189" s="3">
-        <v>35.81</v>
+        <v>48.23</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B190" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C190" s="3">
-        <v>59.25</v>
+        <v>221.86</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>402</v>
@@ -4305,13 +4305,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B191" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C191" s="3">
-        <v>201.84</v>
+        <v>74.7</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>402</v>
@@ -4319,13 +4319,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B192" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C192" s="3">
-        <v>48.23</v>
+        <v>296.3</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>402</v>
@@ -4333,13 +4333,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B193" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C193" s="3">
-        <v>221.86</v>
+        <v>141.80000000000001</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>402</v>
@@ -4347,13 +4347,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B194" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C194" s="3">
-        <v>74.7</v>
+        <v>41.4</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>402</v>
@@ -4361,13 +4361,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B195" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C195" s="3">
-        <v>296.3</v>
+        <v>173.3</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>402</v>
@@ -4375,13 +4375,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B196" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C196" s="3">
-        <v>141.80000000000001</v>
+        <v>2189.02</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>402</v>
@@ -4389,13 +4389,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B197" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C197" s="3">
-        <v>41.4</v>
+        <v>453.22</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>402</v>
@@ -4403,13 +4403,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B198" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C198" s="3">
-        <v>173.3</v>
+        <v>48.64</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>402</v>
@@ -4417,13 +4417,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B199" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C199" s="3">
-        <v>2189.02</v>
+        <v>126.63</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>402</v>
@@ -4431,27 +4431,27 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B200" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C200" s="3">
-        <v>453.22</v>
+        <v>69.56</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B201" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C201" s="3">
-        <v>48.64</v>
+        <v>44.51</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>402</v>
@@ -4459,13 +4459,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B202" s="3">
         <v>7</v>
       </c>
       <c r="C202" s="3">
-        <v>126.63</v>
+        <v>145.94</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>402</v>
@@ -4473,27 +4473,27 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B203" s="3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C203" s="3">
-        <v>69.56</v>
+        <v>179</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B204" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C204" s="3">
-        <v>44.51</v>
+        <v>2060</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>402</v>
@@ -4501,13 +4501,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B205" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C205" s="3">
-        <v>145.94</v>
+        <v>51</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>402</v>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B206" s="3">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C206" s="3">
-        <v>179</v>
+        <v>183.41</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>402</v>
@@ -4529,13 +4529,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C207" s="3">
-        <v>2060</v>
+        <v>206.33</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>402</v>
@@ -4543,27 +4543,27 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B208" s="3">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C208" s="3">
-        <v>51</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B209" s="3">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C209" s="3">
-        <v>183.41</v>
+        <v>46.06</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>402</v>
@@ -4571,13 +4571,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>389</v>
+        <v>197</v>
       </c>
       <c r="B210" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C210" s="3">
-        <v>206.33</v>
+        <v>4900</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>402</v>
@@ -4585,27 +4585,27 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B211" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C211" s="3">
-        <v>33.479999999999997</v>
+        <v>5345.33</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B212" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C212" s="3">
-        <v>46.06</v>
+        <v>170.78</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>402</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B213" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C213" s="3">
-        <v>4667</v>
+        <v>192.51</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>402</v>
@@ -4627,13 +4627,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B214" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C214" s="3">
-        <v>5345.33</v>
+        <v>59.7</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>402</v>
@@ -4641,13 +4641,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B215" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C215" s="3">
-        <v>170.78</v>
+        <v>265.05</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>402</v>
@@ -4655,69 +4655,69 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B216" s="3">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C216" s="3">
-        <v>192.51</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B217" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C217" s="3">
-        <v>59.7</v>
+        <v>103.04</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B218" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C218" s="3">
-        <v>265.05</v>
+        <v>36.75</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B219" s="3">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C219" s="3">
-        <v>36.799999999999997</v>
+        <v>47.16</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B220" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C220" s="3">
-        <v>103.04</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>404</v>
@@ -4725,55 +4725,55 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B221" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C221" s="3">
-        <v>36.75</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B222" s="3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C222" s="3">
-        <v>47.16</v>
+        <v>126.24</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B223" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C223" s="3">
-        <v>16.809999999999999</v>
+        <v>154.62</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B224" s="3">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C224" s="3">
-        <v>37.299999999999997</v>
+        <v>508.2</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>402</v>
@@ -4781,13 +4781,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B225" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C225" s="3">
-        <v>126.24</v>
+        <v>5069</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>402</v>
@@ -4795,13 +4795,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B226" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C226" s="3">
-        <v>154.62</v>
+        <v>466.78</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>402</v>
@@ -4809,55 +4809,55 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B227" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C227" s="3">
-        <v>508.2</v>
+        <v>57.5</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B228" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C228" s="3">
-        <v>5069</v>
+        <v>63.13</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B229" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C229" s="3">
-        <v>466.78</v>
+        <v>20789.41</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B230" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C230" s="3">
-        <v>57.5</v>
+        <v>33057.85</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>405</v>
@@ -4865,13 +4865,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B231" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C231" s="3">
-        <v>63.13</v>
+        <v>83.5</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>405</v>
@@ -4879,55 +4879,55 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B232" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C232" s="3">
-        <v>20789.41</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B233" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C233" s="3">
-        <v>33057.85</v>
+        <v>50.71</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B234" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C234" s="3">
-        <v>83.5</v>
+        <v>51.75</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B235" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C235" s="3">
-        <v>81.650000000000006</v>
+        <v>36.94</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>402</v>
@@ -4935,13 +4935,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B236" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C236" s="3">
-        <v>50.71</v>
+        <v>36.94</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>402</v>
@@ -4949,55 +4949,55 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B237" s="3">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C237" s="3">
-        <v>51.75</v>
+        <v>67.28</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B238" s="3">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C238" s="3">
-        <v>36.94</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B239" s="3">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C239" s="3">
-        <v>36.94</v>
+        <v>65.53</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B240" s="3">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C240" s="3">
-        <v>67.28</v>
+        <v>109.08</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>405</v>
@@ -5005,164 +5005,164 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B241" s="3">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="C241" s="3">
-        <v>65.099999999999994</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B242" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C242" s="3">
-        <v>65.53</v>
+        <v>422.09</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B243" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C243" s="3">
-        <v>109.08</v>
+        <v>1277.7</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B244" s="3">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="C244" s="3">
-        <v>33.479999999999997</v>
+        <v>6.44</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B245" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C245" s="3">
-        <v>422.09</v>
+        <v>108.2</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B246" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C246" s="3">
-        <v>1277.7</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B247" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C247" s="3">
-        <v>6.44</v>
+        <v>6279</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B248" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C248" s="3">
-        <v>108.2</v>
+        <v>609.5</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B249" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C249" s="3">
-        <v>4456.4799999999996</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B250" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C250" s="3">
-        <v>6279</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B251" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C251" s="3">
-        <v>609.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B252" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C252" s="3">
         <v>32.200000000000003</v>
@@ -5173,13 +5173,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B253" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C253" s="3">
-        <v>32.200000000000003</v>
+        <v>40.4</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>391</v>
@@ -5187,13 +5187,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B254" s="3">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="C254" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>391</v>
@@ -5201,97 +5201,97 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B255" s="3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C255" s="3">
-        <v>32.200000000000003</v>
+        <v>56</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B256" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C256" s="3">
-        <v>40.4</v>
+        <v>57.63</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B257" s="3">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="C257" s="3">
-        <v>36.06</v>
+        <v>60.78</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B258" s="3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C258" s="3">
-        <v>56</v>
+        <v>42.49</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B259" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C259" s="3">
-        <v>57.63</v>
+        <v>66.3</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B260" s="3">
         <v>4</v>
       </c>
       <c r="C260" s="3">
-        <v>60.78</v>
+        <v>261.8</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B261" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C261" s="3">
-        <v>42.49</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>402</v>
@@ -5299,27 +5299,27 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B262" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C262" s="3">
-        <v>66.3</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B263" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C263" s="3">
-        <v>261.8</v>
+        <v>54.7</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>402</v>
@@ -5327,13 +5327,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B264" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C264" s="3">
-        <v>71.709999999999994</v>
+        <v>67.28</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>402</v>
@@ -5341,27 +5341,27 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B265" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C265" s="3">
-        <v>77.760000000000005</v>
+        <v>251.5</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B266" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C266" s="3">
-        <v>54.7</v>
+        <v>78.87</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>402</v>
@@ -5369,13 +5369,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B267" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C267" s="3">
-        <v>67.28</v>
+        <v>83.84</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>402</v>
@@ -5383,13 +5383,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B268" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C268" s="3">
-        <v>251.5</v>
+        <v>331.2</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>402</v>
@@ -5397,13 +5397,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B269" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C269" s="3">
-        <v>78.87</v>
+        <v>79.75</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>402</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B270" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C270" s="3">
         <v>83.84</v>
@@ -5425,13 +5425,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B271" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C271" s="3">
-        <v>331.2</v>
+        <v>284</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>402</v>
@@ -5439,83 +5439,83 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B272" s="3">
         <v>12</v>
       </c>
       <c r="C272" s="3">
-        <v>79.75</v>
+        <v>28.15</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B273" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C273" s="3">
-        <v>83.84</v>
+        <v>45.08</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B274" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C274" s="3">
-        <v>284</v>
+        <v>51.52</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B275" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C275" s="3">
-        <v>28.15</v>
+        <v>40.57</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B276" s="3">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C276" s="3">
-        <v>45.08</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B277" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C277" s="3">
-        <v>51.52</v>
+        <v>54.12</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>404</v>
@@ -5523,13 +5523,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B278" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C278" s="3">
-        <v>40.57</v>
+        <v>69.55</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>402</v>
@@ -5537,13 +5537,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B279" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C279" s="3">
-        <v>36.229999999999997</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>402</v>
@@ -5551,13 +5551,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B280" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C280" s="3">
-        <v>54.12</v>
+        <v>38.56</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>404</v>
@@ -5565,83 +5565,83 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B281" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C281" s="3">
-        <v>69.55</v>
+        <v>60.95</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B282" s="3">
         <v>10</v>
       </c>
       <c r="C282" s="3">
-        <v>295.14999999999998</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B283" s="3">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="C283" s="3">
-        <v>38.56</v>
+        <v>44.93</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B284" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C284" s="3">
-        <v>60.95</v>
+        <v>6578.46</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B285" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C285" s="3">
-        <v>78.209999999999994</v>
+        <v>173.09</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B286" s="3">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="C286" s="3">
-        <v>44.93</v>
+        <v>211.23</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>402</v>
@@ -5649,13 +5649,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B287" s="3">
         <v>1</v>
       </c>
       <c r="C287" s="3">
-        <v>6578.46</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>402</v>
@@ -5663,13 +5663,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B288" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C288" s="3">
-        <v>173.09</v>
+        <v>791.3</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>402</v>
@@ -5677,55 +5677,55 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B289" s="3">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C289" s="3">
-        <v>211.23</v>
+        <v>31.6</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B290" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C290" s="3">
-        <v>2314.8000000000002</v>
+        <v>77.28</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B291" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C291" s="3">
-        <v>791.3</v>
+        <v>43.8</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B292" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C292" s="3">
-        <v>31.6</v>
+        <v>21.9</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>404</v>
@@ -5733,13 +5733,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B293" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C293" s="3">
-        <v>77.28</v>
+        <v>798.6</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>404</v>
@@ -5747,13 +5747,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B294" s="3">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C294" s="3">
-        <v>43.8</v>
+        <v>23.19</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>404</v>
@@ -5761,13 +5761,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B295" s="3">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C295" s="3">
-        <v>21.9</v>
+        <v>8.24</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>404</v>
@@ -5775,13 +5775,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B296" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C296" s="3">
-        <v>798.6</v>
+        <v>13.72</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>404</v>
@@ -5789,13 +5789,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B297" s="3">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="C297" s="3">
-        <v>23.19</v>
+        <v>31.95</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>404</v>
@@ -5803,13 +5803,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>279</v>
+        <v>408</v>
       </c>
       <c r="B298" s="3">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C298" s="3">
-        <v>8.24</v>
+        <v>16.2</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>404</v>
@@ -5817,13 +5817,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B299" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C299" s="3">
-        <v>13.72</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>404</v>
@@ -5831,13 +5831,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B300" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C300" s="3">
-        <v>31.95</v>
+        <v>31.48</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>404</v>
@@ -5845,13 +5845,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>408</v>
+        <v>284</v>
       </c>
       <c r="B301" s="3">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="C301" s="3">
-        <v>16.2</v>
+        <v>21.9</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>404</v>
@@ -5859,13 +5859,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B302" s="3">
         <v>6</v>
       </c>
       <c r="C302" s="3">
-        <v>36.869999999999997</v>
+        <v>23.19</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>404</v>
@@ -5873,13 +5873,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B303" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C303" s="3">
-        <v>31.48</v>
+        <v>19.55</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>404</v>
@@ -5887,13 +5887,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B304" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C304" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>404</v>
@@ -5901,13 +5901,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B305" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C305" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>404</v>
@@ -5915,55 +5915,55 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B306" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C306" s="3">
-        <v>19.55</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B307" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C307" s="3">
-        <v>19.07</v>
+        <v>862.7</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B308" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C308" s="3">
-        <v>21.9</v>
+        <v>56.93</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B309" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C309" s="3">
-        <v>79.349999999999994</v>
+        <v>1265</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>405</v>
@@ -5971,55 +5971,55 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B310" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C310" s="3">
-        <v>862.7</v>
+        <v>76</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B311" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C311" s="3">
-        <v>56.93</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B312" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C312" s="3">
-        <v>1265</v>
+        <v>74.7</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B313" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C313" s="3">
-        <v>76</v>
+        <v>327.3</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>402</v>
@@ -6027,13 +6027,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B314" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C314" s="3">
-        <v>267.85000000000002</v>
+        <v>72.13</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>402</v>
@@ -6041,13 +6041,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B315" s="3">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C315" s="3">
-        <v>74.7</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>402</v>
@@ -6055,27 +6055,27 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B316" s="3">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C316" s="3">
-        <v>327.3</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B317" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C317" s="3">
-        <v>72.13</v>
+        <v>428.5</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>402</v>
@@ -6083,13 +6083,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B318" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C318" s="3">
-        <v>302.39999999999998</v>
+        <v>450.22</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>402</v>
@@ -6097,27 +6097,27 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B319" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C319" s="3">
-        <v>36.799999999999997</v>
+        <v>465.7</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B320" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C320" s="3">
-        <v>428.5</v>
+        <v>38.25</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>402</v>
@@ -6125,13 +6125,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B321" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C321" s="3">
-        <v>450.22</v>
+        <v>87.49</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>402</v>
@@ -6139,13 +6139,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B322" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C322" s="3">
-        <v>465.7</v>
+        <v>63.13</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>402</v>
@@ -6153,55 +6153,55 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B323" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C323" s="3">
-        <v>38.25</v>
+        <v>377.78</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B324" s="3">
         <v>2</v>
       </c>
       <c r="C324" s="3">
-        <v>87.49</v>
+        <v>3333.85</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B325" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C325" s="3">
-        <v>63.13</v>
+        <v>374.67</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B326" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C326" s="3">
-        <v>377.78</v>
+        <v>120.06</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>406</v>
@@ -6209,69 +6209,69 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B327" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C327" s="3">
-        <v>3333.85</v>
+        <v>54.2</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B328" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C328" s="3">
-        <v>374.67</v>
+        <v>31.5</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B329" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C329" s="3">
-        <v>120.06</v>
+        <v>114.09</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B330" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C330" s="3">
-        <v>54.2</v>
+        <v>139.9</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B331" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C331" s="3">
-        <v>31.5</v>
+        <v>35.94</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>402</v>
@@ -6279,13 +6279,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B332" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C332" s="3">
-        <v>114.09</v>
+        <v>140.26</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>402</v>
@@ -6293,41 +6293,41 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B333" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C333" s="3">
-        <v>139.9</v>
+        <v>370.53</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B334" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C334" s="3">
-        <v>35.94</v>
+        <v>30.9</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B335" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C335" s="3">
-        <v>140.26</v>
+        <v>4772.5</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>402</v>
@@ -6335,55 +6335,55 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B336" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C336" s="3">
-        <v>370.53</v>
+        <v>516.46</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B337" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C337" s="3">
-        <v>30.9</v>
+        <v>185.15</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B338" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C338" s="3">
-        <v>4772.5</v>
+        <v>11.5</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B339" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C339" s="3">
-        <v>516.46</v>
+        <v>724.5</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>402</v>
@@ -6391,69 +6391,69 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B340" s="3">
         <v>4</v>
       </c>
       <c r="C340" s="3">
-        <v>185.15</v>
+        <v>450.22</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B341" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C341" s="3">
-        <v>11.5</v>
+        <v>461.23</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B342" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C342" s="3">
-        <v>724.5</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B343" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C343" s="3">
-        <v>450.22</v>
+        <v>348.08</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B344" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C344" s="3">
-        <v>461.23</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>394</v>
@@ -6461,13 +6461,13 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B345" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C345" s="3">
-        <v>518.41999999999996</v>
+        <v>35.79</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>394</v>
@@ -6475,13 +6475,13 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B346" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C346" s="3">
-        <v>348.08</v>
+        <v>377.7</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>394</v>
@@ -6489,13 +6489,13 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B347" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C347" s="3">
-        <v>33.479999999999997</v>
+        <v>33.21</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>394</v>
@@ -6503,13 +6503,13 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B348" s="3">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C348" s="3">
-        <v>35.79</v>
+        <v>27.16</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>394</v>
@@ -6517,13 +6517,13 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B349" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C349" s="3">
-        <v>377.7</v>
+        <v>361.41</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>394</v>
@@ -6531,13 +6531,13 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B350" s="3">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C350" s="3">
-        <v>33.21</v>
+        <v>29.25</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>394</v>
@@ -6545,13 +6545,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B351" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C351" s="3">
-        <v>27.16</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>394</v>
@@ -6559,13 +6559,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B352" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C352" s="3">
-        <v>361.41</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>394</v>
@@ -6573,55 +6573,55 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B353" s="3">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C353" s="3">
-        <v>29.25</v>
+        <v>57.7</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B354" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C354" s="3">
-        <v>304.54000000000002</v>
+        <v>90.9</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B355" s="3">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="C355" s="3">
-        <v>34.049999999999997</v>
+        <v>44.31</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B356" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C356" s="3">
-        <v>57.7</v>
+        <v>7173.59</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>402</v>
@@ -6629,27 +6629,27 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B357" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C357" s="3">
-        <v>90.9</v>
+        <v>677.79</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B358" s="3">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C358" s="3">
-        <v>44.31</v>
+        <v>167.33</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>402</v>
@@ -6657,13 +6657,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B359" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C359" s="3">
-        <v>7173.59</v>
+        <v>191</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>402</v>
@@ -6671,13 +6671,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B360" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C360" s="3">
-        <v>677.79</v>
+        <v>2335.67</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>402</v>
@@ -6685,13 +6685,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B361" s="3">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C361" s="3">
-        <v>167.33</v>
+        <v>62.04</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>402</v>
@@ -6699,13 +6699,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B362" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C362" s="3">
-        <v>191</v>
+        <v>8139.6</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>402</v>
@@ -6713,13 +6713,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B363" s="3">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="C363" s="3">
-        <v>2335.67</v>
+        <v>235.53</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>402</v>
@@ -6727,13 +6727,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B364" s="3">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C364" s="3">
-        <v>62.04</v>
+        <v>259.8</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>402</v>
@@ -6741,13 +6741,13 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B365" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C365" s="3">
-        <v>8139.6</v>
+        <v>310.2</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>402</v>
@@ -6755,13 +6755,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B366" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C366" s="3">
-        <v>235.53</v>
+        <v>36.43</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>402</v>
@@ -6769,13 +6769,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B367" s="3">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C367" s="3">
-        <v>259.8</v>
+        <v>87.22</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>402</v>
@@ -6783,13 +6783,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B368" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C368" s="3">
-        <v>310.2</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>402</v>
@@ -6797,13 +6797,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B369" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C369" s="3">
-        <v>36.43</v>
+        <v>62.6</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>402</v>
@@ -6811,13 +6811,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B370" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C370" s="3">
-        <v>87.22</v>
+        <v>312.8</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>402</v>
@@ -6825,41 +6825,41 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B371" s="3">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C371" s="3">
-        <v>319.60000000000002</v>
+        <v>67.28</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B372" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C372" s="3">
-        <v>62.6</v>
+        <v>1138.5</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="B373" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C373" s="3">
-        <v>312.8</v>
+        <v>58.69</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>402</v>
@@ -6867,41 +6867,41 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="B374" s="3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C374" s="3">
-        <v>67.28</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B375" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C375" s="3">
-        <v>1138.5</v>
+        <v>48.76</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="B376" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C376" s="3">
-        <v>58.69</v>
+        <v>242.34</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>402</v>
@@ -6909,13 +6909,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="B377" s="3">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C377" s="3">
-        <v>289.33999999999997</v>
+        <v>54.09</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>402</v>
@@ -6923,13 +6923,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B378" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C378" s="3">
-        <v>48.76</v>
+        <v>255.03</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>402</v>
@@ -6937,13 +6937,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B379" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C379" s="3">
-        <v>242.34</v>
+        <v>220.8</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>402</v>
@@ -6951,13 +6951,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B380" s="3">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C380" s="3">
-        <v>54.09</v>
+        <v>255.02</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>402</v>
@@ -6965,13 +6965,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B381" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C381" s="3">
-        <v>255.03</v>
+        <v>68.86</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>402</v>
@@ -6979,13 +6979,13 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B382" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C382" s="3">
-        <v>220.8</v>
+        <v>344.28</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>402</v>
@@ -6993,13 +6993,13 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B383" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C383" s="3">
-        <v>255.02</v>
+        <v>60.29</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>402</v>
@@ -7007,13 +7007,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B384" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C384" s="3">
-        <v>68.86</v>
+        <v>261.8</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>402</v>
@@ -7021,83 +7021,83 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B385" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C385" s="3">
-        <v>344.28</v>
+        <v>30.58</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B386" s="3">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C386" s="3">
-        <v>60.29</v>
+        <v>16.95</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B387" s="3">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C387" s="3">
-        <v>261.8</v>
+        <v>24.95</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B388" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C388" s="3">
-        <v>30.58</v>
+        <v>641.49</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B389" s="3">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C389" s="3">
-        <v>16.95</v>
+        <v>39.57</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B390" s="3">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C390" s="3">
-        <v>24.95</v>
+        <v>51.83</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>405</v>
@@ -7105,55 +7105,55 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B391" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C391" s="3">
-        <v>641.49</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B392" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C392" s="3">
-        <v>39.57</v>
+        <v>150.15</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B393" s="3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C393" s="3">
-        <v>51.83</v>
+        <v>144.5</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B394" s="3">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C394" s="3">
-        <v>33.840000000000003</v>
+        <v>100.93</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>402</v>
@@ -7161,13 +7161,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B395" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C395" s="3">
-        <v>150.15</v>
+        <v>124.5</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>402</v>
@@ -7175,13 +7175,13 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B396" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C396" s="3">
-        <v>144.5</v>
+        <v>27.21</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>402</v>
@@ -7189,27 +7189,27 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B397" s="3">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="C397" s="3">
-        <v>100.93</v>
+        <v>24.79</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B398" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C398" s="3">
-        <v>124.5</v>
+        <v>37.1</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>402</v>
@@ -7217,13 +7217,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B399" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C399" s="3">
-        <v>27.21</v>
+        <v>178.04</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>402</v>
@@ -7231,41 +7231,41 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B400" s="3">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="C400" s="3">
-        <v>24.79</v>
+        <v>23.88</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B401" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C401" s="3">
-        <v>37.1</v>
+        <v>5000</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B402" s="3">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="C402" s="3">
-        <v>178.04</v>
+        <v>20.68</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>402</v>
@@ -7273,69 +7273,69 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="B403" s="3">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C403" s="3">
-        <v>23.88</v>
+        <v>97.54</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="B404" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C404" s="3">
-        <v>5000</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B405" s="3">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="C405" s="3">
-        <v>20.68</v>
+        <v>1934.56</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="B406" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C406" s="3">
-        <v>97.54</v>
+        <v>230.99</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="B407" s="3">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C407" s="3">
-        <v>304.02999999999997</v>
+        <v>33.39</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>402</v>
@@ -7343,57 +7343,15 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B408" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="C408" s="3">
-        <v>1934.56</v>
+        <v>20.66</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4">
-      <c r="A409" t="s">
-        <v>384</v>
-      </c>
-      <c r="B409" s="3">
-        <v>0</v>
-      </c>
-      <c r="C409" s="3">
-        <v>230.99</v>
-      </c>
-      <c r="D409" s="4" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4">
-      <c r="A410" t="s">
-        <v>385</v>
-      </c>
-      <c r="B410" s="3">
-        <v>96</v>
-      </c>
-      <c r="C410" s="3">
-        <v>33.39</v>
-      </c>
-      <c r="D410" s="4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4">
-      <c r="A411" t="s">
-        <v>386</v>
-      </c>
-      <c r="B411" s="3">
-        <v>48</v>
-      </c>
-      <c r="C411" s="3">
-        <v>20.66</v>
-      </c>
-      <c r="D411" s="4" t="s">
         <v>404</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="423">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1250,6 +1250,39 @@
   </si>
   <si>
     <t>VAL ALL FLEET 15W40 20L</t>
+  </si>
+  <si>
+    <t>IPERCOMP</t>
+  </si>
+  <si>
+    <t>IPC KIT SIGURANTA AUTO</t>
+  </si>
+  <si>
+    <t>IPC TRUSA SANITARA AUTO</t>
+  </si>
+  <si>
+    <t>IPC STINGATOR AUTO 1KG</t>
+  </si>
+  <si>
+    <t>IPC TRIUNGHI REFLECTORIZANT</t>
+  </si>
+  <si>
+    <t>IPC VESTA REFLECTORIZANTA</t>
+  </si>
+  <si>
+    <t>CLUE</t>
+  </si>
+  <si>
+    <t>NOXARO</t>
+  </si>
+  <si>
+    <t>IPC SPRAY INSONORIZANT 650 ML</t>
+  </si>
+  <si>
+    <t>IPC SPRAY CURATAT FRANE 750 ML</t>
+  </si>
+  <si>
+    <t>IPC SPRAY ANTI-RUGINA 450 ML</t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D417"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -7355,6 +7388,132 @@
         <v>404</v>
       </c>
     </row>
+    <row r="409" spans="1:4">
+      <c r="A409" t="s">
+        <v>413</v>
+      </c>
+      <c r="B409" s="3">
+        <v>200</v>
+      </c>
+      <c r="C409" s="3">
+        <v>97.5</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" t="s">
+        <v>414</v>
+      </c>
+      <c r="B410" s="3">
+        <v>200</v>
+      </c>
+      <c r="C410" s="3">
+        <v>24.7</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" t="s">
+        <v>415</v>
+      </c>
+      <c r="B411" s="3">
+        <v>200</v>
+      </c>
+      <c r="C411" s="3">
+        <v>35.75</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" t="s">
+        <v>416</v>
+      </c>
+      <c r="B412" s="3">
+        <v>200</v>
+      </c>
+      <c r="C412" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" t="s">
+        <v>417</v>
+      </c>
+      <c r="B413" s="3">
+        <v>200</v>
+      </c>
+      <c r="C413" s="3">
+        <v>5.43</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" t="s">
+        <v>421</v>
+      </c>
+      <c r="B414" s="3">
+        <v>150</v>
+      </c>
+      <c r="C414" s="3">
+        <v>9.75</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" t="s">
+        <v>422</v>
+      </c>
+      <c r="B415" s="3">
+        <v>120</v>
+      </c>
+      <c r="C415" s="3">
+        <v>6.37</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" t="s">
+        <v>421</v>
+      </c>
+      <c r="B416" s="3">
+        <v>150</v>
+      </c>
+      <c r="C416" s="3">
+        <v>11.59</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" t="s">
+        <v>420</v>
+      </c>
+      <c r="B417" s="3">
+        <v>120</v>
+      </c>
+      <c r="C417" s="3">
+        <v>12.09</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -7287,7 +7287,7 @@
         <v>5000</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="402" spans="1:4">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1111,9 +1111,6 @@
     <t>RAV WIV II SAE 0W30 5L</t>
   </si>
   <si>
-    <t>RAVENOL Spray Vaselina Off Road 0.4L</t>
-  </si>
-  <si>
     <t>REP ANTIGEL CONCENTRAT 1L</t>
   </si>
   <si>
@@ -1159,9 +1156,6 @@
     <t>REP NAVIGATOR GL-5 80W90 1L</t>
   </si>
   <si>
-    <t>TRUSA ADAPTOARE MASINA ATF</t>
-  </si>
-  <si>
     <t>VAL ALL CLIMATE 10W40 1L</t>
   </si>
   <si>
@@ -1283,6 +1277,12 @@
   </si>
   <si>
     <t>IPC SPRAY ANTI-RUGINA 450 ML</t>
+  </si>
+  <si>
+    <t>RAV TRUSA ADAPTOARE MASINA ATF</t>
+  </si>
+  <si>
+    <t>RAV Spray Vaselina Off Road 0.4L</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1687,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1701,7 +1701,7 @@
         <v>12.4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1715,7 +1715,7 @@
         <v>139.26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1729,7 +1729,7 @@
         <v>176.78</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1743,7 +1743,7 @@
         <v>239.2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1757,7 +1757,7 @@
         <v>262.61</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1771,7 +1771,7 @@
         <v>407.86</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1785,7 +1785,7 @@
         <v>635.11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1799,7 +1799,7 @@
         <v>309.52</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1813,7 +1813,7 @@
         <v>343.45</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1827,7 +1827,7 @@
         <v>467.19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1841,7 +1841,7 @@
         <v>535.12</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1855,7 +1855,7 @@
         <v>687.26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1869,7 +1869,7 @@
         <v>825.42</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1883,7 +1883,7 @@
         <v>902.73</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1897,7 +1897,7 @@
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1911,7 +1911,7 @@
         <v>909.67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1925,7 +1925,7 @@
         <v>934.13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1939,7 +1939,7 @@
         <v>1132.73</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1953,7 +1953,7 @@
         <v>534.95000000000005</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1967,7 +1967,7 @@
         <v>706.12</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1981,7 +1981,7 @@
         <v>241.24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1995,7 +1995,7 @@
         <v>278.02</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2009,7 +2009,7 @@
         <v>358.39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2023,7 +2023,7 @@
         <v>376.62</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2037,7 +2037,7 @@
         <v>409.88</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2051,7 +2051,7 @@
         <v>442.81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2065,7 +2065,7 @@
         <v>491.37</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2079,7 +2079,7 @@
         <v>478.19</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2093,7 +2093,7 @@
         <v>41.58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2107,7 +2107,7 @@
         <v>5899.25</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2121,7 +2121,7 @@
         <v>5899.25</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2135,7 +2135,7 @@
         <v>182.58</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2149,7 +2149,7 @@
         <v>41.58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2163,7 +2163,7 @@
         <v>146.97999999999999</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2177,7 +2177,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2191,7 +2191,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2205,7 +2205,7 @@
         <v>122.46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2219,7 +2219,7 @@
         <v>200.92</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2233,7 +2233,7 @@
         <v>156.07</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2247,7 +2247,7 @@
         <v>25.61</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2261,7 +2261,7 @@
         <v>115.42</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2275,7 +2275,7 @@
         <v>25.6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2289,7 +2289,7 @@
         <v>36.4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2303,7 +2303,7 @@
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2317,7 +2317,7 @@
         <v>23.37</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2331,7 +2331,7 @@
         <v>361.92</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2345,7 +2345,7 @@
         <v>20.69</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2359,7 +2359,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2373,7 +2373,7 @@
         <v>318.18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2387,7 +2387,7 @@
         <v>357.53</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2401,7 +2401,7 @@
         <v>18.149999999999999</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2415,7 +2415,7 @@
         <v>19.3</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2429,7 +2429,7 @@
         <v>337.5</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2443,7 +2443,7 @@
         <v>33.64</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2457,7 +2457,7 @@
         <v>33.64</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2471,7 +2471,7 @@
         <v>298.12</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2485,7 +2485,7 @@
         <v>1982.77</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2499,7 +2499,7 @@
         <v>280.12</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2513,7 +2513,7 @@
         <v>24.51</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2527,7 +2527,7 @@
         <v>26.08</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2541,7 +2541,7 @@
         <v>26.21</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2555,7 +2555,7 @@
         <v>87.56</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2569,7 +2569,7 @@
         <v>101.08</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2583,7 +2583,7 @@
         <v>29.13</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2597,7 +2597,7 @@
         <v>102.31</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2611,7 +2611,7 @@
         <v>126.7</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2625,7 +2625,7 @@
         <v>168.07</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2639,7 +2639,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2653,7 +2653,7 @@
         <v>60.95</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2667,7 +2667,7 @@
         <v>76.569999999999993</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2681,7 +2681,7 @@
         <v>16.79</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2695,7 +2695,7 @@
         <v>18.96</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2709,7 +2709,7 @@
         <v>64.430000000000007</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2723,7 +2723,7 @@
         <v>73.13</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2737,7 +2737,7 @@
         <v>79.5</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2751,7 +2751,7 @@
         <v>89.38</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2765,7 +2765,7 @@
         <v>18.96</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2779,7 +2779,7 @@
         <v>73.13</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2793,7 +2793,7 @@
         <v>89.39</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2807,7 +2807,7 @@
         <v>3173.52</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2821,7 +2821,7 @@
         <v>25.4</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2835,7 +2835,7 @@
         <v>40.92</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2849,7 +2849,7 @@
         <v>25.4</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2863,7 +2863,7 @@
         <v>28.07</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2877,7 +2877,7 @@
         <v>23.33</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2891,7 +2891,7 @@
         <v>34.630000000000003</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2905,7 +2905,7 @@
         <v>16.559999999999999</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2919,7 +2919,7 @@
         <v>82.88</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2933,7 +2933,7 @@
         <v>161.01</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2947,7 +2947,7 @@
         <v>44.85</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2961,7 +2961,7 @@
         <v>65.83</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2975,7 +2975,7 @@
         <v>46.76</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2989,7 +2989,7 @@
         <v>62.11</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3003,7 +3003,7 @@
         <v>47.61</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3017,7 +3017,7 @@
         <v>63.76</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3031,7 +3031,7 @@
         <v>1159.2</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3045,7 +3045,7 @@
         <v>255</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3059,7 +3059,7 @@
         <v>69.55</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3073,7 +3073,7 @@
         <v>1391.04</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3087,7 +3087,7 @@
         <v>87.1</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3101,7 +3101,7 @@
         <v>40.54</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3115,7 +3115,7 @@
         <v>460.01</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3129,7 +3129,7 @@
         <v>639.4</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3143,7 +3143,7 @@
         <v>103.89</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3157,7 +3157,7 @@
         <v>58.48</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3171,7 +3171,7 @@
         <v>56.93</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3185,7 +3185,7 @@
         <v>63.76</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3199,7 +3199,7 @@
         <v>61.92</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3213,7 +3213,7 @@
         <v>63.76</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3227,7 +3227,7 @@
         <v>69.56</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3241,7 +3241,7 @@
         <v>59.68</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3255,7 +3255,7 @@
         <v>56.93</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3269,7 +3269,7 @@
         <v>80.73</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3283,7 +3283,7 @@
         <v>98.95</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3297,7 +3297,7 @@
         <v>93.25</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3311,7 +3311,7 @@
         <v>63.76</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3325,7 +3325,7 @@
         <v>63.76</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3339,7 +3339,7 @@
         <v>81.150000000000006</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3353,7 +3353,7 @@
         <v>63.76</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3367,7 +3367,7 @@
         <v>69.87</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3381,7 +3381,7 @@
         <v>63.76</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3395,7 +3395,7 @@
         <v>69.56</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3409,7 +3409,7 @@
         <v>69.56</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3423,7 +3423,7 @@
         <v>52.17</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3437,7 +3437,7 @@
         <v>208.66</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3451,7 +3451,7 @@
         <v>88.87</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3465,7 +3465,7 @@
         <v>67.27</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3479,7 +3479,7 @@
         <v>69.55</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3493,7 +3493,7 @@
         <v>63.89</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3507,7 +3507,7 @@
         <v>149.91</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3521,7 +3521,7 @@
         <v>38.57</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3535,7 +3535,7 @@
         <v>207.31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3549,7 +3549,7 @@
         <v>65.23</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3563,7 +3563,7 @@
         <v>325.87</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3577,7 +3577,7 @@
         <v>5165.8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3591,7 +3591,7 @@
         <v>511.75</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3605,7 +3605,7 @@
         <v>572.70000000000005</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3619,7 +3619,7 @@
         <v>66.98</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3633,7 +3633,7 @@
         <v>367.42</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3647,7 +3647,7 @@
         <v>51.52</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3661,7 +3661,7 @@
         <v>23.19</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3675,7 +3675,7 @@
         <v>23.19</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3689,7 +3689,7 @@
         <v>69.55</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3703,7 +3703,7 @@
         <v>3169.7</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3717,7 +3717,7 @@
         <v>81.14</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3731,7 +3731,7 @@
         <v>81.14</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3745,7 +3745,7 @@
         <v>66.98</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3759,7 +3759,7 @@
         <v>60.28</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3773,7 +3773,7 @@
         <v>93.35</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3787,7 +3787,7 @@
         <v>1217.1600000000001</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3801,7 +3801,7 @@
         <v>3079</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3815,7 +3815,7 @@
         <v>43.7</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3829,7 +3829,7 @@
         <v>48.95</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3843,7 +3843,7 @@
         <v>72.33</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3857,7 +3857,7 @@
         <v>284.19</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3871,7 +3871,7 @@
         <v>132.19</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3885,7 +3885,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3899,7 +3899,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3913,7 +3913,7 @@
         <v>37.43</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3927,7 +3927,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3941,7 +3941,7 @@
         <v>115.01</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3955,7 +3955,7 @@
         <v>38.39</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3969,7 +3969,7 @@
         <v>151.47999999999999</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3983,7 +3983,7 @@
         <v>181.68</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3997,7 +3997,7 @@
         <v>20.059999999999999</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4011,7 +4011,7 @@
         <v>12.88</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4025,7 +4025,7 @@
         <v>26.73</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4039,7 +4039,7 @@
         <v>29.95</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4053,7 +4053,7 @@
         <v>58.68</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4067,7 +4067,7 @@
         <v>79.98</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4081,7 +4081,7 @@
         <v>38.770000000000003</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4095,7 +4095,7 @@
         <v>107.35</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4109,7 +4109,7 @@
         <v>61.83</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4123,7 +4123,7 @@
         <v>243.16</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4137,7 +4137,7 @@
         <v>63.78</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4151,7 +4151,7 @@
         <v>75.989999999999995</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4165,7 +4165,7 @@
         <v>297.64999999999998</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4179,7 +4179,7 @@
         <v>77.28</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4193,7 +4193,7 @@
         <v>75.989999999999995</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4207,7 +4207,7 @@
         <v>342.24</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4221,7 +4221,7 @@
         <v>633.75</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4235,7 +4235,7 @@
         <v>50.51</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4249,7 +4249,7 @@
         <v>787.75</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4263,7 +4263,7 @@
         <v>122.36</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4277,7 +4277,7 @@
         <v>35.81</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4291,7 +4291,7 @@
         <v>59.25</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4305,7 +4305,7 @@
         <v>201.84</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4319,7 +4319,7 @@
         <v>48.23</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4333,7 +4333,7 @@
         <v>221.86</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4347,7 +4347,7 @@
         <v>74.7</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4361,7 +4361,7 @@
         <v>296.3</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4375,7 +4375,7 @@
         <v>141.80000000000001</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4389,7 +4389,7 @@
         <v>41.4</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4403,7 +4403,7 @@
         <v>173.3</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4417,7 +4417,7 @@
         <v>2189.02</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4431,7 +4431,7 @@
         <v>453.22</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4445,7 +4445,7 @@
         <v>48.64</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4459,7 +4459,7 @@
         <v>126.63</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4473,7 +4473,7 @@
         <v>69.56</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4487,7 +4487,7 @@
         <v>44.51</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4501,7 +4501,7 @@
         <v>145.94</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4515,7 +4515,7 @@
         <v>179</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4529,7 +4529,7 @@
         <v>2060</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4543,7 +4543,7 @@
         <v>51</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4557,12 +4557,12 @@
         <v>183.41</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B207" s="3">
         <v>7</v>
@@ -4571,7 +4571,7 @@
         <v>206.33</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4585,7 +4585,7 @@
         <v>33.479999999999997</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4599,7 +4599,7 @@
         <v>46.06</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4613,7 +4613,7 @@
         <v>4900</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4627,7 +4627,7 @@
         <v>5345.33</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4641,7 +4641,7 @@
         <v>170.78</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4655,7 +4655,7 @@
         <v>192.51</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4669,7 +4669,7 @@
         <v>59.7</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4683,7 +4683,7 @@
         <v>265.05</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4697,7 +4697,7 @@
         <v>36.799999999999997</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4711,7 +4711,7 @@
         <v>103.04</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4725,7 +4725,7 @@
         <v>36.75</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4739,7 +4739,7 @@
         <v>47.16</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4753,7 +4753,7 @@
         <v>16.809999999999999</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4767,7 +4767,7 @@
         <v>37.299999999999997</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4781,7 +4781,7 @@
         <v>126.24</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4795,7 +4795,7 @@
         <v>154.62</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4809,7 +4809,7 @@
         <v>508.2</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4823,7 +4823,7 @@
         <v>5069</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4837,7 +4837,7 @@
         <v>466.78</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4851,7 +4851,7 @@
         <v>57.5</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4865,7 +4865,7 @@
         <v>63.13</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4879,7 +4879,7 @@
         <v>20789.41</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4893,7 +4893,7 @@
         <v>33057.85</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4907,7 +4907,7 @@
         <v>83.5</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4921,7 +4921,7 @@
         <v>81.650000000000006</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4935,7 +4935,7 @@
         <v>50.71</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4949,7 +4949,7 @@
         <v>51.75</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4963,7 +4963,7 @@
         <v>36.94</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4977,7 +4977,7 @@
         <v>36.94</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4991,7 +4991,7 @@
         <v>67.28</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5005,7 +5005,7 @@
         <v>65.099999999999994</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5019,7 +5019,7 @@
         <v>65.53</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5033,7 +5033,7 @@
         <v>109.08</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5047,7 +5047,7 @@
         <v>33.479999999999997</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5061,7 +5061,7 @@
         <v>422.09</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5075,7 +5075,7 @@
         <v>1277.7</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5089,7 +5089,7 @@
         <v>6.44</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5103,7 +5103,7 @@
         <v>108.2</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5117,7 +5117,7 @@
         <v>4456.4799999999996</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5131,7 +5131,7 @@
         <v>6279</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5145,7 +5145,7 @@
         <v>609.5</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5159,7 +5159,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5173,7 +5173,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5187,7 +5187,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5201,7 +5201,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5215,7 +5215,7 @@
         <v>40.4</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5229,7 +5229,7 @@
         <v>36.06</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5243,7 +5243,7 @@
         <v>56</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5257,7 +5257,7 @@
         <v>57.63</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5271,7 +5271,7 @@
         <v>60.78</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5285,7 +5285,7 @@
         <v>42.49</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5299,7 +5299,7 @@
         <v>66.3</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5313,7 +5313,7 @@
         <v>261.8</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5327,7 +5327,7 @@
         <v>71.709999999999994</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5341,7 +5341,7 @@
         <v>77.760000000000005</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5355,7 +5355,7 @@
         <v>54.7</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5369,7 +5369,7 @@
         <v>67.28</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5383,7 +5383,7 @@
         <v>251.5</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5397,7 +5397,7 @@
         <v>78.87</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5411,7 +5411,7 @@
         <v>83.84</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5425,7 +5425,7 @@
         <v>331.2</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5439,7 +5439,7 @@
         <v>79.75</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5453,7 +5453,7 @@
         <v>83.84</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5467,7 +5467,7 @@
         <v>284</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5481,7 +5481,7 @@
         <v>28.15</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5495,7 +5495,7 @@
         <v>45.08</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5509,7 +5509,7 @@
         <v>51.52</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5523,7 +5523,7 @@
         <v>40.57</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5537,7 +5537,7 @@
         <v>36.229999999999997</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5551,7 +5551,7 @@
         <v>54.12</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5565,7 +5565,7 @@
         <v>69.55</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5579,7 +5579,7 @@
         <v>295.14999999999998</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5593,7 +5593,7 @@
         <v>38.56</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5607,7 +5607,7 @@
         <v>60.95</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5621,7 +5621,7 @@
         <v>78.209999999999994</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5635,7 +5635,7 @@
         <v>44.93</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5649,7 +5649,7 @@
         <v>6578.46</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5663,7 +5663,7 @@
         <v>173.09</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5677,7 +5677,7 @@
         <v>211.23</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5691,7 +5691,7 @@
         <v>2314.8000000000002</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5705,7 +5705,7 @@
         <v>791.3</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5719,7 +5719,7 @@
         <v>31.6</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5733,7 +5733,7 @@
         <v>77.28</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5747,7 +5747,7 @@
         <v>43.8</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5761,7 +5761,7 @@
         <v>21.9</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5775,7 +5775,7 @@
         <v>798.6</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5789,7 +5789,7 @@
         <v>23.19</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5803,7 +5803,7 @@
         <v>8.24</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5817,7 +5817,7 @@
         <v>13.72</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5831,12 +5831,12 @@
         <v>31.95</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B298" s="3">
         <v>105</v>
@@ -5845,7 +5845,7 @@
         <v>16.2</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5859,7 +5859,7 @@
         <v>36.869999999999997</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5873,7 +5873,7 @@
         <v>31.48</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5887,7 +5887,7 @@
         <v>21.9</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5901,7 +5901,7 @@
         <v>23.19</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5915,7 +5915,7 @@
         <v>19.55</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5929,7 +5929,7 @@
         <v>19.07</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5943,7 +5943,7 @@
         <v>21.9</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5957,7 +5957,7 @@
         <v>79.349999999999994</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5971,7 +5971,7 @@
         <v>862.7</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5985,7 +5985,7 @@
         <v>56.93</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5999,7 +5999,7 @@
         <v>1265</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6013,7 +6013,7 @@
         <v>76</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6027,7 +6027,7 @@
         <v>267.85000000000002</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6041,7 +6041,7 @@
         <v>74.7</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6055,7 +6055,7 @@
         <v>327.3</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6069,7 +6069,7 @@
         <v>72.13</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6083,7 +6083,7 @@
         <v>302.39999999999998</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6097,7 +6097,7 @@
         <v>36.799999999999997</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6111,7 +6111,7 @@
         <v>428.5</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6125,7 +6125,7 @@
         <v>450.22</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6139,7 +6139,7 @@
         <v>465.7</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6153,7 +6153,7 @@
         <v>38.25</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6167,7 +6167,7 @@
         <v>87.49</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6181,7 +6181,7 @@
         <v>63.13</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6195,7 +6195,7 @@
         <v>377.78</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6209,7 +6209,7 @@
         <v>3333.85</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6223,7 +6223,7 @@
         <v>374.67</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6237,7 +6237,7 @@
         <v>120.06</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6251,7 +6251,7 @@
         <v>54.2</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6265,7 +6265,7 @@
         <v>31.5</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6279,7 +6279,7 @@
         <v>114.09</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6293,7 +6293,7 @@
         <v>139.9</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6307,7 +6307,7 @@
         <v>35.94</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6321,7 +6321,7 @@
         <v>140.26</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6335,7 +6335,7 @@
         <v>370.53</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6349,7 +6349,7 @@
         <v>30.9</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6363,7 +6363,7 @@
         <v>4772.5</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6377,7 +6377,7 @@
         <v>516.46</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6391,7 +6391,7 @@
         <v>185.15</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6405,7 +6405,7 @@
         <v>11.5</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6419,7 +6419,7 @@
         <v>724.5</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6433,7 +6433,7 @@
         <v>450.22</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6447,7 +6447,7 @@
         <v>461.23</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6461,7 +6461,7 @@
         <v>518.41999999999996</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6475,7 +6475,7 @@
         <v>348.08</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6489,7 +6489,7 @@
         <v>33.479999999999997</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6503,7 +6503,7 @@
         <v>35.79</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6517,7 +6517,7 @@
         <v>377.7</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6531,7 +6531,7 @@
         <v>33.21</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6545,7 +6545,7 @@
         <v>27.16</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6559,7 +6559,7 @@
         <v>361.41</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6573,7 +6573,7 @@
         <v>29.25</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6587,7 +6587,7 @@
         <v>304.54000000000002</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6601,7 +6601,7 @@
         <v>34.049999999999997</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6615,7 +6615,7 @@
         <v>57.7</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6629,7 +6629,7 @@
         <v>90.9</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6643,7 +6643,7 @@
         <v>44.31</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6657,7 +6657,7 @@
         <v>7173.59</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6671,7 +6671,7 @@
         <v>677.79</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6685,7 +6685,7 @@
         <v>167.33</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6699,7 +6699,7 @@
         <v>191</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6713,7 +6713,7 @@
         <v>2335.67</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6727,7 +6727,7 @@
         <v>62.04</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6741,7 +6741,7 @@
         <v>8139.6</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6755,7 +6755,7 @@
         <v>235.53</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6769,7 +6769,7 @@
         <v>259.8</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6783,7 +6783,7 @@
         <v>310.2</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6797,7 +6797,7 @@
         <v>36.43</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6811,7 +6811,7 @@
         <v>87.22</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6825,7 +6825,7 @@
         <v>319.60000000000002</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6839,7 +6839,7 @@
         <v>62.6</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6853,7 +6853,7 @@
         <v>312.8</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6867,7 +6867,7 @@
         <v>67.28</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6881,12 +6881,12 @@
         <v>1138.5</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B373" s="3">
         <v>24</v>
@@ -6895,12 +6895,12 @@
         <v>58.69</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B374" s="3">
         <v>12</v>
@@ -6909,7 +6909,7 @@
         <v>289.33999999999997</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6923,7 +6923,7 @@
         <v>48.76</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6937,7 +6937,7 @@
         <v>242.34</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6951,7 +6951,7 @@
         <v>54.09</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6965,7 +6965,7 @@
         <v>255.03</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6979,7 +6979,7 @@
         <v>220.8</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6993,7 +6993,7 @@
         <v>255.02</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -7007,7 +7007,7 @@
         <v>68.86</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -7021,7 +7021,7 @@
         <v>344.28</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -7035,7 +7035,7 @@
         <v>60.29</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -7049,12 +7049,12 @@
         <v>261.8</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="B385" s="3">
         <v>2</v>
@@ -7063,12 +7063,12 @@
         <v>30.58</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B386" s="3">
         <v>54</v>
@@ -7077,12 +7077,12 @@
         <v>16.95</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B387" s="3">
         <v>45</v>
@@ -7091,12 +7091,12 @@
         <v>24.95</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B388" s="3">
         <v>3</v>
@@ -7105,12 +7105,12 @@
         <v>641.49</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B389" s="3">
         <v>12</v>
@@ -7119,12 +7119,12 @@
         <v>39.57</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B390" s="3">
         <v>36</v>
@@ -7133,12 +7133,12 @@
         <v>51.83</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B391" s="3">
         <v>44</v>
@@ -7147,12 +7147,12 @@
         <v>33.840000000000003</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B392" s="3">
         <v>19</v>
@@ -7161,12 +7161,12 @@
         <v>150.15</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B393" s="3">
         <v>25</v>
@@ -7175,12 +7175,12 @@
         <v>144.5</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B394" s="3">
         <v>25</v>
@@ -7189,12 +7189,12 @@
         <v>100.93</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B395" s="3">
         <v>14</v>
@@ -7203,12 +7203,12 @@
         <v>124.5</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B396" s="3">
         <v>10</v>
@@ -7217,12 +7217,12 @@
         <v>27.21</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B397" s="3">
         <v>94</v>
@@ -7231,12 +7231,12 @@
         <v>24.79</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B398" s="3">
         <v>6</v>
@@ -7245,12 +7245,12 @@
         <v>37.1</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B399" s="3">
         <v>8</v>
@@ -7259,12 +7259,12 @@
         <v>178.04</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B400" s="3">
         <v>48</v>
@@ -7273,12 +7273,12 @@
         <v>23.88</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="B401" s="3">
         <v>3</v>
@@ -7287,12 +7287,12 @@
         <v>5000</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B402" s="3">
         <v>93</v>
@@ -7301,12 +7301,12 @@
         <v>20.68</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B403" s="3">
         <v>31</v>
@@ -7315,12 +7315,12 @@
         <v>97.54</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B404" s="3">
         <v>9</v>
@@ -7329,12 +7329,12 @@
         <v>304.02999999999997</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B405" s="3">
         <v>3</v>
@@ -7343,12 +7343,12 @@
         <v>1934.56</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B406" s="3">
         <v>0</v>
@@ -7357,12 +7357,12 @@
         <v>230.99</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B407" s="3">
         <v>96</v>
@@ -7371,12 +7371,12 @@
         <v>33.39</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B408" s="3">
         <v>48</v>
@@ -7385,12 +7385,12 @@
         <v>20.66</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B409" s="3">
         <v>200</v>
@@ -7399,12 +7399,12 @@
         <v>97.5</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B410" s="3">
         <v>200</v>
@@ -7413,12 +7413,12 @@
         <v>24.7</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B411" s="3">
         <v>200</v>
@@ -7427,12 +7427,12 @@
         <v>35.75</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B412" s="3">
         <v>200</v>
@@ -7441,12 +7441,12 @@
         <v>9.1</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B413" s="3">
         <v>200</v>
@@ -7455,12 +7455,12 @@
         <v>5.43</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B414" s="3">
         <v>150</v>
@@ -7469,12 +7469,12 @@
         <v>9.75</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B415" s="3">
         <v>120</v>
@@ -7483,12 +7483,12 @@
         <v>6.37</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B416" s="3">
         <v>150</v>
@@ -7497,12 +7497,12 @@
         <v>11.59</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B417" s="3">
         <v>120</v>
@@ -7511,7 +7511,7 @@
         <v>12.09</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="422">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1277,9 +1277,6 @@
   </si>
   <si>
     <t>IPC SPRAY ANTI-RUGINA 450 ML</t>
-  </si>
-  <si>
-    <t>RAV TRUSA ADAPTOARE MASINA ATF</t>
   </si>
   <si>
     <t>RAV Spray Vaselina Off Road 0.4L</t>
@@ -1668,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D417"/>
+  <dimension ref="A1:D416"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -7054,7 +7051,7 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B385" s="3">
         <v>2</v>
@@ -7278,27 +7275,27 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>421</v>
+        <v>380</v>
       </c>
       <c r="B401" s="3">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C401" s="3">
-        <v>5000</v>
+        <v>20.68</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="B402" s="3">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="C402" s="3">
-        <v>20.68</v>
+        <v>97.54</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>400</v>
@@ -7306,13 +7303,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B403" s="3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C403" s="3">
-        <v>97.54</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>400</v>
@@ -7320,27 +7317,27 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="B404" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C404" s="3">
-        <v>304.02999999999997</v>
+        <v>1934.56</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B405" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C405" s="3">
-        <v>1934.56</v>
+        <v>230.99</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>404</v>
@@ -7348,55 +7345,55 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B406" s="3">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C406" s="3">
-        <v>230.99</v>
+        <v>33.39</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B407" s="3">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C407" s="3">
-        <v>33.39</v>
+        <v>20.66</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B408" s="3">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="C408" s="3">
-        <v>20.66</v>
+        <v>97.5</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B409" s="3">
         <v>200</v>
       </c>
       <c r="C409" s="3">
-        <v>97.5</v>
+        <v>24.7</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>410</v>
@@ -7404,13 +7401,13 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B410" s="3">
         <v>200</v>
       </c>
       <c r="C410" s="3">
-        <v>24.7</v>
+        <v>35.75</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>410</v>
@@ -7418,13 +7415,13 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B411" s="3">
         <v>200</v>
       </c>
       <c r="C411" s="3">
-        <v>35.75</v>
+        <v>9.1</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>410</v>
@@ -7432,13 +7429,13 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B412" s="3">
         <v>200</v>
       </c>
       <c r="C412" s="3">
-        <v>9.1</v>
+        <v>5.43</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>410</v>
@@ -7446,27 +7443,27 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B413" s="3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C413" s="3">
-        <v>5.43</v>
+        <v>9.75</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B414" s="3">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C414" s="3">
-        <v>9.75</v>
+        <v>6.37</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>416</v>
@@ -7474,43 +7471,29 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B415" s="3">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C415" s="3">
-        <v>6.37</v>
+        <v>11.59</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B416" s="3">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C416" s="3">
-        <v>11.59</v>
+        <v>12.09</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="417" spans="1:4">
-      <c r="A417" t="s">
-        <v>418</v>
-      </c>
-      <c r="B417" s="3">
-        <v>120</v>
-      </c>
-      <c r="C417" s="3">
-        <v>12.09</v>
-      </c>
-      <c r="D417" s="4" t="s">
         <v>417</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="423">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1280,6 +1280,9 @@
   </si>
   <si>
     <t>RAV Spray Vaselina Off Road 0.4L</t>
+  </si>
+  <si>
+    <t>BUFFALO</t>
   </si>
 </sst>
 </file>
@@ -1894,7 +1897,7 @@
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:4">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="423">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -247,9 +247,6 @@
     <t>EUROL SILIKONE MULTISPRAY 400ML</t>
   </si>
   <si>
-    <t>EUROL WHITE REASE 400ML</t>
-  </si>
-  <si>
     <t>RAV 4-TAKT GARDENOIL HD30 1L</t>
   </si>
   <si>
@@ -559,9 +556,6 @@
     <t>RAV FES SAE 0W30 USVO 4+1</t>
   </si>
   <si>
-    <t>RAV FO SAE 5W-30 4 L</t>
-  </si>
-  <si>
     <t>RAV FO SAE 5W30 1L</t>
   </si>
   <si>
@@ -1283,6 +1277,12 @@
   </si>
   <si>
     <t>BUFFALO</t>
+  </si>
+  <si>
+    <t>EUROL WHITE GREASE 400ML</t>
+  </si>
+  <si>
+    <t>RAV FO SAE 5W30 4L</t>
   </si>
 </sst>
 </file>
@@ -1668,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D416"/>
+  <dimension ref="A1:D412"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1687,7 +1687,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1695,13 +1695,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1715,7 +1715,7 @@
         <v>139.26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1729,7 +1729,7 @@
         <v>176.78</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1737,13 +1737,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3">
         <v>239.2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1751,13 +1751,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3">
         <v>262.61</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1771,7 +1771,7 @@
         <v>407.86</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1785,7 +1785,7 @@
         <v>635.11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1799,7 +1799,7 @@
         <v>309.52</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1813,7 +1813,7 @@
         <v>343.45</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1827,7 +1827,7 @@
         <v>467.19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1841,7 +1841,7 @@
         <v>535.12</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1855,7 +1855,7 @@
         <v>687.26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1869,7 +1869,7 @@
         <v>825.42</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1883,7 +1883,7 @@
         <v>902.73</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1891,13 +1891,13 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="3">
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1911,7 +1911,7 @@
         <v>909.67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1925,7 +1925,7 @@
         <v>934.13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1933,13 +1933,13 @@
         <v>20</v>
       </c>
       <c r="B19" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="3">
         <v>1132.73</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1947,13 +1947,13 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1967,7 +1967,7 @@
         <v>706.12</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1981,7 +1981,7 @@
         <v>241.24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1995,7 +1995,7 @@
         <v>278.02</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2009,7 +2009,7 @@
         <v>358.39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2017,13 +2017,13 @@
         <v>26</v>
       </c>
       <c r="B25" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="3">
         <v>376.62</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2037,7 +2037,7 @@
         <v>409.88</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2051,7 +2051,7 @@
         <v>442.81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2065,7 +2065,7 @@
         <v>491.37</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2079,7 +2079,7 @@
         <v>478.19</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2087,13 +2087,13 @@
         <v>31</v>
       </c>
       <c r="B30" s="3">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C30" s="3">
         <v>41.58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2107,7 +2107,7 @@
         <v>5899.25</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2121,7 +2121,7 @@
         <v>5899.25</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2135,7 +2135,7 @@
         <v>182.58</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2143,13 +2143,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C34" s="3">
         <v>41.58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2163,7 +2163,7 @@
         <v>146.97999999999999</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2177,7 +2177,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2191,7 +2191,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2205,7 +2205,7 @@
         <v>122.46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2219,7 +2219,7 @@
         <v>200.92</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2233,7 +2233,7 @@
         <v>156.07</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2247,7 +2247,7 @@
         <v>25.61</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2261,7 +2261,7 @@
         <v>115.42</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2269,13 +2269,13 @@
         <v>44</v>
       </c>
       <c r="B43" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C43" s="3">
         <v>25.6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2289,7 +2289,7 @@
         <v>36.4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2297,13 +2297,13 @@
         <v>46</v>
       </c>
       <c r="B45" s="3">
-        <v>2936</v>
+        <v>2888</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2311,13 +2311,13 @@
         <v>47</v>
       </c>
       <c r="B46" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C46" s="3">
         <v>23.37</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2331,7 +2331,7 @@
         <v>361.92</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2345,7 +2345,7 @@
         <v>20.69</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2359,7 +2359,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2367,402 +2367,402 @@
         <v>50</v>
       </c>
       <c r="B50" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" s="3">
-        <v>318.18</v>
+        <v>357.53</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="3">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C51" s="3">
-        <v>357.53</v>
+        <v>19.3</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C52" s="3">
-        <v>18.149999999999999</v>
+        <v>337.5</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B53" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C53" s="3">
-        <v>19.3</v>
+        <v>33.64</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C54" s="3">
-        <v>337.5</v>
+        <v>33.64</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="3">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C55" s="3">
-        <v>33.64</v>
+        <v>298.12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C56" s="3">
-        <v>33.64</v>
+        <v>1982.77</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C57" s="3">
-        <v>298.12</v>
+        <v>280.12</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C58" s="3">
-        <v>1982.77</v>
+        <v>24.51</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C59" s="3">
-        <v>280.12</v>
+        <v>26.08</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="C60" s="3">
-        <v>24.51</v>
+        <v>26.21</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C61" s="3">
-        <v>26.08</v>
+        <v>87.56</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B62" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C62" s="3">
-        <v>26.21</v>
+        <v>101.08</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B63" s="3">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C63" s="3">
-        <v>87.56</v>
+        <v>29.13</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B64" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" s="3">
-        <v>101.08</v>
+        <v>102.31</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B65" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C65" s="3">
-        <v>29.13</v>
+        <v>126.7</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B66" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C66" s="3">
-        <v>102.31</v>
+        <v>168.07</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B67" s="3">
-        <v>3</v>
+        <v>307</v>
       </c>
       <c r="C67" s="3">
-        <v>126.7</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B68" s="3">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="C68" s="3">
-        <v>168.07</v>
+        <v>60.95</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B69" s="3">
-        <v>355</v>
+        <v>57</v>
       </c>
       <c r="C69" s="3">
-        <v>16.600000000000001</v>
+        <v>76.569999999999993</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B70" s="3">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C70" s="3">
-        <v>60.95</v>
+        <v>16.79</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B71" s="3">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C71" s="3">
-        <v>76.569999999999993</v>
+        <v>18.96</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B72" s="3">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C72" s="3">
-        <v>16.79</v>
+        <v>73.13</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B73" s="3">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="C73" s="3">
-        <v>18.96</v>
+        <v>89.38</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B74" s="3">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="C74" s="3">
-        <v>64.430000000000007</v>
+        <v>18.96</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B75" s="3">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C75" s="3">
         <v>73.13</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B76" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C76" s="3">
-        <v>79.5</v>
+        <v>89.39</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B77" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C77" s="3">
-        <v>89.38</v>
+        <v>3173.52</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B78" s="3">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C78" s="3">
-        <v>18.96</v>
+        <v>25.4</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>400</v>
@@ -2770,13 +2770,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B79" s="3">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="C79" s="3">
-        <v>73.13</v>
+        <v>40.92</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>400</v>
@@ -2784,13 +2784,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B80" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C80" s="3">
-        <v>89.39</v>
+        <v>25.4</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>400</v>
@@ -2798,13 +2798,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B81" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C81" s="3">
-        <v>3173.52</v>
+        <v>28.07</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>400</v>
@@ -2812,1399 +2812,1399 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>421</v>
       </c>
       <c r="B82" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3">
-        <v>25.4</v>
+        <v>23.33</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B83" s="3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C83" s="3">
-        <v>40.92</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B84" s="3">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C84" s="3">
-        <v>25.4</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B85" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C85" s="3">
-        <v>28.07</v>
+        <v>82.88</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B86" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C86" s="3">
-        <v>23.33</v>
+        <v>161.01</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B87" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C87" s="3">
-        <v>34.630000000000003</v>
+        <v>44.85</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B88" s="3">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C88" s="3">
-        <v>16.559999999999999</v>
+        <v>65.83</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B89" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C89" s="3">
-        <v>82.88</v>
+        <v>46.76</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B90" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C90" s="3">
-        <v>161.01</v>
+        <v>62.11</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B91" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C91" s="3">
-        <v>44.85</v>
+        <v>47.61</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B92" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C92" s="3">
-        <v>65.83</v>
+        <v>63.76</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B93" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" s="3">
-        <v>46.76</v>
+        <v>1159.2</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B94" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C94" s="3">
-        <v>62.11</v>
+        <v>255</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B95" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C95" s="3">
-        <v>47.61</v>
+        <v>69.55</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B96" s="3">
         <v>1</v>
       </c>
       <c r="C96" s="3">
-        <v>63.76</v>
+        <v>1391.04</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C97" s="3">
-        <v>1159.2</v>
+        <v>87.1</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B98" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C98" s="3">
-        <v>255</v>
+        <v>40.54</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B99" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C99" s="3">
-        <v>69.55</v>
+        <v>460.01</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B100" s="3">
         <v>1</v>
       </c>
       <c r="C100" s="3">
-        <v>1391.04</v>
+        <v>639.4</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B101" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C101" s="3">
-        <v>87.1</v>
+        <v>103.89</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B102" s="3">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C102" s="3">
-        <v>40.54</v>
+        <v>58.48</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C103" s="3">
-        <v>460.01</v>
+        <v>56.93</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B104" s="3">
         <v>1</v>
       </c>
       <c r="C104" s="3">
-        <v>639.4</v>
+        <v>63.76</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B105" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C105" s="3">
-        <v>103.89</v>
+        <v>61.92</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B106" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C106" s="3">
-        <v>58.48</v>
+        <v>63.76</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B107" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C107" s="3">
-        <v>56.93</v>
+        <v>69.56</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B108" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C108" s="3">
-        <v>63.76</v>
+        <v>59.68</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B109" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C109" s="3">
-        <v>61.92</v>
+        <v>56.93</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B110" s="3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C110" s="3">
-        <v>63.76</v>
+        <v>80.73</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B111" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C111" s="3">
-        <v>69.56</v>
+        <v>98.95</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B112" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C112" s="3">
-        <v>59.68</v>
+        <v>93.25</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B113" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C113" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B114" s="3">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C114" s="3">
-        <v>80.73</v>
+        <v>63.76</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B115" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C115" s="3">
-        <v>98.95</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B116" s="3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C116" s="3">
-        <v>93.25</v>
+        <v>63.76</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B117" s="3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C117" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B118" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C118" s="3">
         <v>63.76</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B119" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C119" s="3">
-        <v>81.150000000000006</v>
+        <v>69.56</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B120" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C120" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B121" s="3">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C121" s="3">
-        <v>69.87</v>
+        <v>52.17</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B122" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C122" s="3">
-        <v>63.76</v>
+        <v>208.66</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B123" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C123" s="3">
-        <v>69.56</v>
+        <v>88.87</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B124" s="3">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="C124" s="3">
-        <v>69.56</v>
+        <v>67.27</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B125" s="3">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C125" s="3">
-        <v>52.17</v>
+        <v>69.55</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B126" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C126" s="3">
-        <v>208.66</v>
+        <v>63.89</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B127" s="3">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C127" s="3">
-        <v>88.87</v>
+        <v>149.91</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B128" s="3">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="C128" s="3">
-        <v>67.27</v>
+        <v>38.57</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B129" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C129" s="3">
-        <v>69.55</v>
+        <v>207.31</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B130" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C130" s="3">
-        <v>63.89</v>
+        <v>65.23</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B131" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C131" s="3">
-        <v>149.91</v>
+        <v>325.87</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B132" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C132" s="3">
-        <v>38.57</v>
+        <v>5165.8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B133" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C133" s="3">
-        <v>207.31</v>
+        <v>511.75</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B134" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C134" s="3">
-        <v>65.23</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B135" s="3">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="C135" s="3">
-        <v>325.87</v>
+        <v>66.98</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C136" s="3">
-        <v>5165.8</v>
+        <v>367.42</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B137" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C137" s="3">
-        <v>511.75</v>
+        <v>51.52</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B138" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C138" s="3">
-        <v>572.70000000000005</v>
+        <v>23.19</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B139" s="3">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="C139" s="3">
-        <v>66.98</v>
+        <v>23.19</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B140" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C140" s="3">
-        <v>367.42</v>
+        <v>69.55</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B141" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C141" s="3">
-        <v>51.52</v>
+        <v>3169.7</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B142" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C142" s="3">
-        <v>23.19</v>
+        <v>81.14</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B143" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C143" s="3">
-        <v>23.19</v>
+        <v>81.14</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B144" s="3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C144" s="3">
-        <v>69.55</v>
+        <v>66.98</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B145" s="3">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C145" s="3">
-        <v>3169.7</v>
+        <v>60.28</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B146" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C146" s="3">
-        <v>81.14</v>
+        <v>93.35</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B147" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C147" s="3">
-        <v>81.14</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B148" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C148" s="3">
-        <v>66.98</v>
+        <v>3079</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B149" s="3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C149" s="3">
-        <v>60.28</v>
+        <v>43.7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B150" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C150" s="3">
-        <v>93.35</v>
+        <v>48.95</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C151" s="3">
-        <v>1217.1600000000001</v>
+        <v>72.33</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B152" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C152" s="3">
-        <v>3079</v>
+        <v>284.19</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B153" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C153" s="3">
-        <v>43.7</v>
+        <v>132.19</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B154" s="3">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C154" s="3">
-        <v>48.95</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B155" s="3">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C155" s="3">
-        <v>72.33</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B156" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C156" s="3">
-        <v>284.19</v>
+        <v>37.43</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B157" s="3">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C157" s="3">
-        <v>132.19</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B158" s="3">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="C158" s="3">
-        <v>32.200000000000003</v>
+        <v>115.01</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B159" s="3">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="C159" s="3">
-        <v>32.200000000000003</v>
+        <v>38.39</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C160" s="3">
-        <v>37.43</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B161" s="3">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C161" s="3">
-        <v>32.200000000000003</v>
+        <v>181.68</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B162" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C162" s="3">
-        <v>115.01</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B163" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C163" s="3">
-        <v>38.39</v>
+        <v>12.88</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B164" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C164" s="3">
-        <v>151.47999999999999</v>
+        <v>26.73</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B165" s="3">
         <v>12</v>
       </c>
       <c r="C165" s="3">
-        <v>181.68</v>
+        <v>29.95</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B166" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C166" s="3">
-        <v>20.059999999999999</v>
+        <v>58.68</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B167" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C167" s="3">
-        <v>12.88</v>
+        <v>79.98</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B168" s="3">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C168" s="3">
-        <v>26.73</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B169" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C169" s="3">
-        <v>29.95</v>
+        <v>107.35</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B170" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C170" s="3">
-        <v>58.68</v>
+        <v>61.83</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B171" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C171" s="3">
-        <v>79.98</v>
+        <v>243.16</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B172" s="3">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C172" s="3">
-        <v>38.770000000000003</v>
+        <v>63.78</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B173" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C173" s="3">
-        <v>107.35</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B174" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C174" s="3">
-        <v>61.83</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B175" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C175" s="3">
-        <v>243.16</v>
+        <v>77.28</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B176" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C176" s="3">
-        <v>63.78</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B177" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C177" s="3">
-        <v>75.989999999999995</v>
+        <v>342.24</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B178" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C178" s="3">
-        <v>297.64999999999998</v>
+        <v>633.75</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B179" s="3">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="C179" s="3">
-        <v>77.28</v>
+        <v>50.51</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B180" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C180" s="3">
-        <v>75.989999999999995</v>
+        <v>787.75</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B181" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C181" s="3">
-        <v>342.24</v>
+        <v>122.36</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>400</v>
@@ -4212,447 +4212,447 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B182" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C182" s="3">
-        <v>633.75</v>
+        <v>35.81</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B183" s="3">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C183" s="3">
-        <v>50.51</v>
+        <v>59.25</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B184" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C184" s="3">
-        <v>787.75</v>
+        <v>201.84</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B185" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C185" s="3">
-        <v>122.36</v>
+        <v>48.23</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B186" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C186" s="3">
-        <v>35.81</v>
+        <v>221.86</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B187" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C187" s="3">
-        <v>59.25</v>
+        <v>74.7</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B188" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C188" s="3">
-        <v>201.84</v>
+        <v>296.3</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>177</v>
+        <v>422</v>
       </c>
       <c r="B189" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C189" s="3">
-        <v>48.23</v>
+        <v>141.80000000000001</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B190" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C190" s="3">
-        <v>221.86</v>
+        <v>41.4</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B191" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C191" s="3">
-        <v>74.7</v>
+        <v>173.3</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B192" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C192" s="3">
-        <v>296.3</v>
+        <v>2189.02</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B193" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C193" s="3">
-        <v>141.80000000000001</v>
+        <v>453.22</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B194" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C194" s="3">
-        <v>41.4</v>
+        <v>48.64</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B195" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C195" s="3">
-        <v>173.3</v>
+        <v>126.63</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B196" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C196" s="3">
-        <v>2189.02</v>
+        <v>69.56</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B197" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C197" s="3">
-        <v>453.22</v>
+        <v>44.51</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B198" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C198" s="3">
-        <v>48.64</v>
+        <v>145.94</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B199" s="3">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C199" s="3">
-        <v>126.63</v>
+        <v>179</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B200" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C200" s="3">
-        <v>69.56</v>
+        <v>2060</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B201" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C201" s="3">
-        <v>44.51</v>
+        <v>51</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B202" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C202" s="3">
-        <v>145.94</v>
+        <v>183.41</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>191</v>
+        <v>385</v>
       </c>
       <c r="B203" s="3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C203" s="3">
-        <v>179</v>
+        <v>206.33</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B204" s="3">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C204" s="3">
-        <v>2060</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B205" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C205" s="3">
-        <v>51</v>
+        <v>46.06</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B206" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C206" s="3">
-        <v>183.41</v>
+        <v>4900</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>387</v>
+        <v>195</v>
       </c>
       <c r="B207" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C207" s="3">
-        <v>206.33</v>
+        <v>5345.33</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B208" s="3">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C208" s="3">
-        <v>33.479999999999997</v>
+        <v>170.78</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B209" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C209" s="3">
-        <v>46.06</v>
+        <v>192.51</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B210" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C210" s="3">
-        <v>4900</v>
+        <v>59.7</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B211" s="3">
         <v>0</v>
       </c>
       <c r="C211" s="3">
-        <v>5345.33</v>
+        <v>265.05</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B212" s="3">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C212" s="3">
-        <v>170.78</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B213" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C213" s="3">
-        <v>192.51</v>
+        <v>103.04</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>400</v>
@@ -4660,769 +4660,769 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B214" s="3">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C214" s="3">
-        <v>59.7</v>
+        <v>36.75</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B215" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C215" s="3">
-        <v>265.05</v>
+        <v>47.16</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B216" s="3">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C216" s="3">
-        <v>36.799999999999997</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B217" s="3">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>103.04</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B218" s="3">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C218" s="3">
-        <v>36.75</v>
+        <v>126.24</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B219" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C219" s="3">
-        <v>47.16</v>
+        <v>154.62</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B220" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C220" s="3">
-        <v>16.809999999999999</v>
+        <v>508.2</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B221" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C221" s="3">
-        <v>37.299999999999997</v>
+        <v>5069</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B222" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C222" s="3">
-        <v>126.24</v>
+        <v>466.78</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B223" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C223" s="3">
-        <v>154.62</v>
+        <v>57.5</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B224" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C224" s="3">
-        <v>508.2</v>
+        <v>63.13</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B225" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225" s="3">
-        <v>5069</v>
+        <v>20789.41</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B226" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C226" s="3">
-        <v>466.78</v>
+        <v>33057.85</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B227" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C227" s="3">
-        <v>57.5</v>
+        <v>83.5</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B228" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C228" s="3">
-        <v>63.13</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B229" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C229" s="3">
-        <v>20789.41</v>
+        <v>50.71</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B230" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C230" s="3">
-        <v>33057.85</v>
+        <v>51.75</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B231" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C231" s="3">
-        <v>83.5</v>
+        <v>36.94</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B232" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C232" s="3">
-        <v>81.650000000000006</v>
+        <v>36.94</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B233" s="3">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C233" s="3">
-        <v>50.71</v>
+        <v>67.28</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B234" s="3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C234" s="3">
-        <v>51.75</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B235" s="3">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C235" s="3">
-        <v>36.94</v>
+        <v>65.53</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B236" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C236" s="3">
-        <v>36.94</v>
+        <v>109.08</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B237" s="3">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="C237" s="3">
-        <v>67.28</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B238" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C238" s="3">
-        <v>65.099999999999994</v>
+        <v>422.09</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B239" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C239" s="3">
-        <v>65.53</v>
+        <v>1277.7</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B240" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C240" s="3">
-        <v>109.08</v>
+        <v>6.44</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B241" s="3">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="C241" s="3">
-        <v>33.479999999999997</v>
+        <v>108.2</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B242" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C242" s="3">
-        <v>422.09</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B243" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C243" s="3">
-        <v>1277.7</v>
+        <v>6279</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B244" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C244" s="3">
-        <v>6.44</v>
+        <v>609.5</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B245" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C245" s="3">
-        <v>108.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B246" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C246" s="3">
-        <v>4456.4799999999996</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B247" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C247" s="3">
-        <v>6279</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B248" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C248" s="3">
-        <v>609.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B249" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C249" s="3">
-        <v>32.200000000000003</v>
+        <v>40.4</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B250" s="3">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="C250" s="3">
-        <v>32.200000000000003</v>
+        <v>36.06</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B251" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C251" s="3">
-        <v>32.200000000000003</v>
+        <v>56</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B252" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C252" s="3">
-        <v>32.200000000000003</v>
+        <v>57.63</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B253" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C253" s="3">
-        <v>40.4</v>
+        <v>60.78</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B254" s="3">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="C254" s="3">
-        <v>36.06</v>
+        <v>42.49</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B255" s="3">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C255" s="3">
-        <v>56</v>
+        <v>66.3</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B256" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C256" s="3">
-        <v>57.63</v>
+        <v>261.8</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B257" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C257" s="3">
-        <v>60.78</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B258" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C258" s="3">
-        <v>42.49</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B259" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C259" s="3">
-        <v>66.3</v>
+        <v>54.7</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B260" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C260" s="3">
-        <v>261.8</v>
+        <v>67.28</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B261" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C261" s="3">
-        <v>71.709999999999994</v>
+        <v>251.5</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B262" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C262" s="3">
-        <v>77.760000000000005</v>
+        <v>78.87</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B263" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C263" s="3">
-        <v>54.7</v>
+        <v>83.84</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B264" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C264" s="3">
-        <v>67.28</v>
+        <v>331.2</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B265" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C265" s="3">
-        <v>251.5</v>
+        <v>79.75</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B266" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C266" s="3">
-        <v>78.87</v>
+        <v>83.84</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B267" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C267" s="3">
-        <v>83.84</v>
+        <v>284</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B268" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C268" s="3">
-        <v>331.2</v>
+        <v>28.15</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>400</v>
@@ -5430,13 +5430,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B269" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C269" s="3">
-        <v>79.75</v>
+        <v>45.08</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>400</v>
@@ -5444,13 +5444,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B270" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C270" s="3">
-        <v>83.84</v>
+        <v>51.52</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>400</v>
@@ -5458,83 +5458,83 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B271" s="3">
         <v>5</v>
       </c>
       <c r="C271" s="3">
-        <v>284</v>
+        <v>40.57</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B272" s="3">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C272" s="3">
-        <v>28.15</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B273" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C273" s="3">
-        <v>45.08</v>
+        <v>54.12</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B274" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C274" s="3">
-        <v>51.52</v>
+        <v>69.55</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B275" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C275" s="3">
-        <v>40.57</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B276" s="3">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C276" s="3">
-        <v>36.229999999999997</v>
+        <v>38.56</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>400</v>
@@ -5542,125 +5542,125 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B277" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C277" s="3">
-        <v>54.12</v>
+        <v>60.95</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B278" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C278" s="3">
-        <v>69.55</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B279" s="3">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="C279" s="3">
-        <v>295.14999999999998</v>
+        <v>44.93</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B280" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C280" s="3">
-        <v>38.56</v>
+        <v>6578.46</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B281" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C281" s="3">
-        <v>60.95</v>
+        <v>173.09</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B282" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C282" s="3">
-        <v>78.209999999999994</v>
+        <v>211.23</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B283" s="3">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C283" s="3">
-        <v>44.93</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B284" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C284" s="3">
-        <v>6578.46</v>
+        <v>791.3</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B285" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C285" s="3">
-        <v>173.09</v>
+        <v>31.6</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>400</v>
@@ -5668,13 +5668,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B286" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C286" s="3">
-        <v>211.23</v>
+        <v>77.28</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>400</v>
@@ -5682,13 +5682,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B287" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C287" s="3">
-        <v>2314.8000000000002</v>
+        <v>43.8</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>400</v>
@@ -5696,13 +5696,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B288" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C288" s="3">
-        <v>791.3</v>
+        <v>21.9</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>400</v>
@@ -5710,1150 +5710,1150 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B289" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C289" s="3">
-        <v>31.6</v>
+        <v>798.6</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B290" s="3">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="C290" s="3">
-        <v>77.28</v>
+        <v>23.19</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B291" s="3">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C291" s="3">
-        <v>43.8</v>
+        <v>8.24</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B292" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C292" s="3">
-        <v>21.9</v>
+        <v>13.72</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B293" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C293" s="3">
-        <v>798.6</v>
+        <v>31.95</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>278</v>
+        <v>404</v>
       </c>
       <c r="B294" s="3">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C294" s="3">
-        <v>23.19</v>
+        <v>16.2</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B295" s="3">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="C295" s="3">
-        <v>8.24</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B296" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C296" s="3">
-        <v>13.72</v>
+        <v>31.48</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B297" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C297" s="3">
-        <v>31.95</v>
+        <v>21.9</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>406</v>
+        <v>283</v>
       </c>
       <c r="B298" s="3">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="C298" s="3">
-        <v>16.2</v>
+        <v>23.19</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B299" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C299" s="3">
-        <v>36.869999999999997</v>
+        <v>19.55</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B300" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C300" s="3">
-        <v>31.48</v>
+        <v>19.07</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B301" s="3">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C301" s="3">
         <v>21.9</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B302" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C302" s="3">
-        <v>23.19</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B303" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C303" s="3">
-        <v>19.55</v>
+        <v>862.7</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B304" s="3">
         <v>11</v>
       </c>
       <c r="C304" s="3">
-        <v>19.07</v>
+        <v>56.93</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B305" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C305" s="3">
-        <v>21.9</v>
+        <v>1265</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B306" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C306" s="3">
-        <v>79.349999999999994</v>
+        <v>76</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B307" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C307" s="3">
-        <v>862.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B308" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C308" s="3">
-        <v>56.93</v>
+        <v>74.7</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B309" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C309" s="3">
-        <v>1265</v>
+        <v>327.3</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B310" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C310" s="3">
-        <v>76</v>
+        <v>72.13</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B311" s="3">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C311" s="3">
-        <v>267.85000000000002</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B312" s="3">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C312" s="3">
-        <v>74.7</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B313" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C313" s="3">
-        <v>327.3</v>
+        <v>428.5</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B314" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C314" s="3">
-        <v>72.13</v>
+        <v>450.22</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B315" s="3">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C315" s="3">
-        <v>302.39999999999998</v>
+        <v>465.7</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B316" s="3">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C316" s="3">
-        <v>36.799999999999997</v>
+        <v>38.25</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B317" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C317" s="3">
-        <v>428.5</v>
+        <v>87.49</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B318" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C318" s="3">
-        <v>450.22</v>
+        <v>63.13</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B319" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C319" s="3">
-        <v>465.7</v>
+        <v>377.78</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B320" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C320" s="3">
-        <v>38.25</v>
+        <v>3333.85</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B321" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C321" s="3">
-        <v>87.49</v>
+        <v>374.67</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B322" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C322" s="3">
-        <v>63.13</v>
+        <v>120.06</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B323" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C323" s="3">
-        <v>377.78</v>
+        <v>54.2</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B324" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C324" s="3">
-        <v>3333.85</v>
+        <v>31.5</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B325" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C325" s="3">
-        <v>374.67</v>
+        <v>114.09</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B326" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C326" s="3">
-        <v>120.06</v>
+        <v>139.9</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B327" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C327" s="3">
-        <v>54.2</v>
+        <v>35.94</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B328" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C328" s="3">
-        <v>31.5</v>
+        <v>140.26</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B329" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C329" s="3">
-        <v>114.09</v>
+        <v>370.53</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B330" s="3">
         <v>3</v>
       </c>
       <c r="C330" s="3">
-        <v>139.9</v>
+        <v>30.9</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B331" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C331" s="3">
-        <v>35.94</v>
+        <v>4772.5</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B332" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C332" s="3">
-        <v>140.26</v>
+        <v>516.46</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B333" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C333" s="3">
-        <v>370.53</v>
+        <v>185.15</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B334" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C334" s="3">
-        <v>30.9</v>
+        <v>11.5</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B335" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C335" s="3">
-        <v>4772.5</v>
+        <v>724.5</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B336" s="3">
         <v>4</v>
       </c>
       <c r="C336" s="3">
-        <v>516.46</v>
+        <v>450.22</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B337" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C337" s="3">
-        <v>185.15</v>
+        <v>461.23</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B338" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C338" s="3">
-        <v>11.5</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B339" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C339" s="3">
-        <v>724.5</v>
+        <v>348.08</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B340" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C340" s="3">
-        <v>450.22</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B341" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C341" s="3">
-        <v>461.23</v>
+        <v>35.79</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B342" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C342" s="3">
-        <v>518.41999999999996</v>
+        <v>377.7</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B343" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C343" s="3">
-        <v>348.08</v>
+        <v>33.21</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B344" s="3">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C344" s="3">
-        <v>33.479999999999997</v>
+        <v>27.16</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B345" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C345" s="3">
-        <v>35.79</v>
+        <v>361.41</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B346" s="3">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C346" s="3">
-        <v>377.7</v>
+        <v>29.25</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B347" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C347" s="3">
-        <v>33.21</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B348" s="3">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C348" s="3">
-        <v>27.16</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B349" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C349" s="3">
-        <v>361.41</v>
+        <v>57.7</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B350" s="3">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C350" s="3">
-        <v>29.25</v>
+        <v>90.9</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B351" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C351" s="3">
-        <v>304.54000000000002</v>
+        <v>44.31</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B352" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>34.049999999999997</v>
+        <v>7173.59</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B353" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C353" s="3">
-        <v>57.7</v>
+        <v>677.79</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B354" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C354" s="3">
-        <v>90.9</v>
+        <v>167.33</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B355" s="3">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C355" s="3">
-        <v>44.31</v>
+        <v>191</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B356" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C356" s="3">
-        <v>7173.59</v>
+        <v>2335.67</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B357" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C357" s="3">
-        <v>677.79</v>
+        <v>62.04</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B358" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C358" s="3">
-        <v>167.33</v>
+        <v>8139.6</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B359" s="3">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C359" s="3">
-        <v>191</v>
+        <v>235.53</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B360" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C360" s="3">
-        <v>2335.67</v>
+        <v>259.8</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B361" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="C361" s="3">
-        <v>62.04</v>
+        <v>310.2</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B362" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C362" s="3">
-        <v>8139.6</v>
+        <v>36.43</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B363" s="3">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="C363" s="3">
-        <v>235.53</v>
+        <v>87.22</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B364" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C364" s="3">
-        <v>259.8</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B365" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C365" s="3">
-        <v>310.2</v>
+        <v>62.6</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B366" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C366" s="3">
-        <v>36.43</v>
+        <v>312.8</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B367" s="3">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C367" s="3">
-        <v>87.22</v>
+        <v>67.28</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B368" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C368" s="3">
-        <v>319.60000000000002</v>
+        <v>1138.5</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="B369" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C369" s="3">
-        <v>62.6</v>
+        <v>58.69</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="B370" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C370" s="3">
-        <v>312.8</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6861,13 +6861,13 @@
         <v>353</v>
       </c>
       <c r="B371" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C371" s="3">
-        <v>67.28</v>
+        <v>48.76</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6875,136 +6875,136 @@
         <v>354</v>
       </c>
       <c r="B372" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C372" s="3">
-        <v>1138.5</v>
+        <v>242.34</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="B373" s="3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C373" s="3">
-        <v>58.69</v>
+        <v>54.09</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="B374" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C374" s="3">
-        <v>289.33999999999997</v>
+        <v>255.03</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B375" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C375" s="3">
-        <v>48.76</v>
+        <v>220.8</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B376" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C376" s="3">
-        <v>242.34</v>
+        <v>255.02</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B377" s="3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C377" s="3">
-        <v>54.09</v>
+        <v>68.86</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B378" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C378" s="3">
-        <v>255.03</v>
+        <v>344.28</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B379" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C379" s="3">
-        <v>220.8</v>
+        <v>60.29</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B380" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C380" s="3">
-        <v>255.02</v>
+        <v>261.8</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="B381" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C381" s="3">
-        <v>68.86</v>
+        <v>30.58</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>400</v>
@@ -7012,254 +7012,254 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B382" s="3">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C382" s="3">
-        <v>344.28</v>
+        <v>16.95</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B383" s="3">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C383" s="3">
-        <v>60.29</v>
+        <v>24.95</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B384" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C384" s="3">
-        <v>261.8</v>
+        <v>641.49</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>421</v>
+        <v>366</v>
       </c>
       <c r="B385" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C385" s="3">
-        <v>30.58</v>
+        <v>39.57</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B386" s="3">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C386" s="3">
-        <v>16.95</v>
+        <v>51.83</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B387" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C387" s="3">
-        <v>24.95</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B388" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C388" s="3">
-        <v>641.49</v>
+        <v>150.15</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B389" s="3">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C389" s="3">
-        <v>39.57</v>
+        <v>144.5</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B390" s="3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C390" s="3">
-        <v>51.83</v>
+        <v>100.93</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B391" s="3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C391" s="3">
-        <v>33.840000000000003</v>
+        <v>124.5</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B392" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C392" s="3">
-        <v>150.15</v>
+        <v>27.21</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B393" s="3">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="C393" s="3">
-        <v>144.5</v>
+        <v>24.79</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B394" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C394" s="3">
-        <v>100.93</v>
+        <v>37.1</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B395" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C395" s="3">
-        <v>124.5</v>
+        <v>178.04</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B396" s="3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C396" s="3">
-        <v>27.21</v>
+        <v>23.88</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B397" s="3">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C397" s="3">
-        <v>24.79</v>
+        <v>20.68</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="B398" s="3">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C398" s="3">
-        <v>37.1</v>
+        <v>97.54</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="B399" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C399" s="3">
-        <v>178.04</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7267,13 +7267,13 @@
         <v>379</v>
       </c>
       <c r="B400" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C400" s="3">
-        <v>23.88</v>
+        <v>1934.56</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7281,38 +7281,38 @@
         <v>380</v>
       </c>
       <c r="B401" s="3">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C401" s="3">
-        <v>20.68</v>
+        <v>230.99</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="B402" s="3">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="C402" s="3">
-        <v>97.54</v>
+        <v>33.39</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="B403" s="3">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C403" s="3">
-        <v>304.02999999999997</v>
+        <v>20.66</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>400</v>
@@ -7320,184 +7320,128 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="B404" s="3">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="C404" s="3">
-        <v>1934.56</v>
+        <v>97.5</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="B405" s="3">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="C405" s="3">
-        <v>230.99</v>
+        <v>24.7</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="B406" s="3">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c r="C406" s="3">
-        <v>33.39</v>
+        <v>35.75</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="B407" s="3">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="C407" s="3">
-        <v>20.66</v>
+        <v>9.1</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B408" s="3">
         <v>200</v>
       </c>
       <c r="C408" s="3">
-        <v>97.5</v>
+        <v>5.43</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B409" s="3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C409" s="3">
-        <v>24.7</v>
+        <v>9.75</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B410" s="3">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="C410" s="3">
-        <v>35.75</v>
+        <v>6.37</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B411" s="3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C411" s="3">
-        <v>9.1</v>
+        <v>11.59</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
+        <v>416</v>
+      </c>
+      <c r="B412" s="3">
+        <v>115</v>
+      </c>
+      <c r="C412" s="3">
+        <v>12.09</v>
+      </c>
+      <c r="D412" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="B412" s="3">
-        <v>200</v>
-      </c>
-      <c r="C412" s="3">
-        <v>5.43</v>
-      </c>
-      <c r="D412" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4">
-      <c r="A413" t="s">
-        <v>419</v>
-      </c>
-      <c r="B413" s="3">
-        <v>150</v>
-      </c>
-      <c r="C413" s="3">
-        <v>9.75</v>
-      </c>
-      <c r="D413" s="4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4">
-      <c r="A414" t="s">
-        <v>420</v>
-      </c>
-      <c r="B414" s="3">
-        <v>120</v>
-      </c>
-      <c r="C414" s="3">
-        <v>6.37</v>
-      </c>
-      <c r="D414" s="4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4">
-      <c r="A415" t="s">
-        <v>419</v>
-      </c>
-      <c r="B415" s="3">
-        <v>150</v>
-      </c>
-      <c r="C415" s="3">
-        <v>11.59</v>
-      </c>
-      <c r="D415" s="4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4">
-      <c r="A416" t="s">
-        <v>418</v>
-      </c>
-      <c r="B416" s="3">
-        <v>120</v>
-      </c>
-      <c r="C416" s="3">
-        <v>12.09</v>
-      </c>
-      <c r="D416" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="424">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1283,6 +1283,9 @@
   </si>
   <si>
     <t>RAV FO SAE 5W30 4L</t>
+  </si>
+  <si>
+    <t>MAGMA X-100</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1676,7 @@
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
     <col min="2" max="3" width="15.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2611,7 +2614,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68" spans="1:4">

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="428">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -34,81 +34,12 @@
     <t>BANNER 51214 BTX14-BS AGM</t>
   </si>
   <si>
-    <t>BANNER 55519</t>
-  </si>
-  <si>
-    <t>BANNER 56219</t>
-  </si>
-  <si>
-    <t>BANNER 56511 EFB</t>
-  </si>
-  <si>
-    <t>BANNER 57001</t>
-  </si>
-  <si>
-    <t>BANNER 57044</t>
-  </si>
-  <si>
-    <t>BANNER 57212</t>
-  </si>
-  <si>
-    <t>BANNER 57511 EFB</t>
-  </si>
-  <si>
-    <t>BANNER 57512 EFB</t>
-  </si>
-  <si>
     <t>BANNER 58001 AGM</t>
   </si>
   <si>
-    <t>BANNER 59501</t>
-  </si>
-  <si>
-    <t>BANNER 60501</t>
-  </si>
-  <si>
-    <t>BANNER 65001</t>
-  </si>
-  <si>
     <t>BANNER 68008 SHD PRO</t>
   </si>
   <si>
-    <t>BANNER 69017</t>
-  </si>
-  <si>
-    <t>BANNER 72503</t>
-  </si>
-  <si>
-    <t>BANNER P10040</t>
-  </si>
-  <si>
-    <t>BANNER P11040</t>
-  </si>
-  <si>
-    <t>BANNER P4409</t>
-  </si>
-  <si>
-    <t>BANNER P5003</t>
-  </si>
-  <si>
-    <t>BANNER P6340</t>
-  </si>
-  <si>
-    <t>BANNER P7412</t>
-  </si>
-  <si>
-    <t>BANNER P7740</t>
-  </si>
-  <si>
-    <t>BANNER P8014</t>
-  </si>
-  <si>
-    <t>BANNER P9504</t>
-  </si>
-  <si>
-    <t>BANNER P9505</t>
-  </si>
-  <si>
     <t>CASTROL EDGE 5W30 LL 1L APR</t>
   </si>
   <si>
@@ -1286,6 +1217,87 @@
   </si>
   <si>
     <t>MAGMA X-100</t>
+  </si>
+  <si>
+    <t>SYN V1</t>
+  </si>
+  <si>
+    <t>SYN TDI</t>
+  </si>
+  <si>
+    <t>PRO V1</t>
+  </si>
+  <si>
+    <t>CAMIOANE</t>
+  </si>
+  <si>
+    <t>BANNER 55519 55Ah</t>
+  </si>
+  <si>
+    <t>BANNER 56219 62 Ah</t>
+  </si>
+  <si>
+    <t>BANNER 56511 EFB 65Ah</t>
+  </si>
+  <si>
+    <t>BANNER 57044 70Ah</t>
+  </si>
+  <si>
+    <t>BANNER 57212 72Ah</t>
+  </si>
+  <si>
+    <t>BANNER P10040 100Ah</t>
+  </si>
+  <si>
+    <t>BANNER P11040 110Ah</t>
+  </si>
+  <si>
+    <t>BANNER P4409 44Ah</t>
+  </si>
+  <si>
+    <t>BANNER P5003 50Ah</t>
+  </si>
+  <si>
+    <t>BANNER P6340 63Ah</t>
+  </si>
+  <si>
+    <t>BANNER P7412 74Ah</t>
+  </si>
+  <si>
+    <t>BANNER P7740 77Ah</t>
+  </si>
+  <si>
+    <t>BANNER P8014 80Ah</t>
+  </si>
+  <si>
+    <t>BANNER P9504 95Ah</t>
+  </si>
+  <si>
+    <t>BANNER P9505 95Ah</t>
+  </si>
+  <si>
+    <t>BANNER 57001 70Ah</t>
+  </si>
+  <si>
+    <t>BANNER 59501 95Ah</t>
+  </si>
+  <si>
+    <t>BANNER 60501 105Ah</t>
+  </si>
+  <si>
+    <t>BANNER 65001 150Ah</t>
+  </si>
+  <si>
+    <t>BANNER 69017 190Ah</t>
+  </si>
+  <si>
+    <t>BANNER 72503 225Ah</t>
+  </si>
+  <si>
+    <t>BANNER 57511 EFB 75Ah</t>
+  </si>
+  <si>
+    <t>BANNER 57512 EFB 75Ah</t>
   </si>
 </sst>
 </file>
@@ -1690,7 +1702,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1704,7 +1716,7 @@
         <v>12.4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1718,7 +1730,7 @@
         <v>139.26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1732,12 +1744,12 @@
         <v>176.78</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>405</v>
       </c>
       <c r="B5" s="3">
         <v>16</v>
@@ -1746,12 +1758,12 @@
         <v>239.2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -1760,12 +1772,12 @@
         <v>262.61</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>407</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -1774,12 +1786,12 @@
         <v>407.86</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -1788,12 +1800,12 @@
         <v>635.11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>408</v>
       </c>
       <c r="B9" s="3">
         <v>24</v>
@@ -1802,12 +1814,12 @@
         <v>309.52</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>409</v>
       </c>
       <c r="B10" s="3">
         <v>45</v>
@@ -1816,12 +1828,12 @@
         <v>343.45</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>426</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
@@ -1830,12 +1842,12 @@
         <v>467.19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>427</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -1844,12 +1856,12 @@
         <v>535.12</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3">
         <v>4</v>
@@ -1858,12 +1870,12 @@
         <v>687.26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>421</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1872,12 +1884,12 @@
         <v>825.42</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>422</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1886,12 +1898,12 @@
         <v>902.73</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>423</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -1900,12 +1912,12 @@
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3">
         <v>14</v>
@@ -1914,12 +1926,12 @@
         <v>909.67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>424</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -1928,12 +1940,12 @@
         <v>934.13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="B19" s="3">
         <v>6</v>
@@ -1942,12 +1954,12 @@
         <v>1132.73</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="B20" s="3">
         <v>24</v>
@@ -1956,12 +1968,12 @@
         <v>534.95000000000005</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>411</v>
       </c>
       <c r="B21" s="3">
         <v>3</v>
@@ -1970,12 +1982,12 @@
         <v>706.12</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>412</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
@@ -1984,12 +1996,12 @@
         <v>241.24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>413</v>
       </c>
       <c r="B23" s="3">
         <v>9</v>
@@ -1998,12 +2010,12 @@
         <v>278.02</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>414</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -2012,12 +2024,12 @@
         <v>358.39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>415</v>
       </c>
       <c r="B25" s="3">
         <v>23</v>
@@ -2026,12 +2038,12 @@
         <v>376.62</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>416</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
@@ -2040,12 +2052,12 @@
         <v>409.88</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>417</v>
       </c>
       <c r="B27" s="3">
         <v>21</v>
@@ -2054,12 +2066,12 @@
         <v>442.81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>418</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -2068,12 +2080,12 @@
         <v>491.37</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2082,12 +2094,12 @@
         <v>478.19</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B30" s="3">
         <v>115</v>
@@ -2096,12 +2108,12 @@
         <v>41.58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B31" s="3">
         <v>2</v>
@@ -2110,12 +2122,12 @@
         <v>5899.25</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B32" s="3">
         <v>4</v>
@@ -2124,12 +2136,12 @@
         <v>5899.25</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B33" s="3">
         <v>4</v>
@@ -2138,12 +2150,12 @@
         <v>182.58</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -2152,12 +2164,12 @@
         <v>41.58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B35" s="3">
         <v>6</v>
@@ -2166,12 +2178,12 @@
         <v>146.97999999999999</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B36" s="3">
         <v>42</v>
@@ -2180,12 +2192,12 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -2194,12 +2206,12 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B38" s="3">
         <v>13</v>
@@ -2208,12 +2220,12 @@
         <v>122.46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B39" s="3">
         <v>16</v>
@@ -2222,12 +2234,12 @@
         <v>200.92</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -2236,12 +2248,12 @@
         <v>156.07</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B41" s="3">
         <v>60</v>
@@ -2250,12 +2262,12 @@
         <v>25.61</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B42" s="3">
         <v>18</v>
@@ -2264,12 +2276,12 @@
         <v>115.42</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B43" s="3">
         <v>52</v>
@@ -2278,12 +2290,12 @@
         <v>25.6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="B44" s="3">
         <v>1</v>
@@ -2292,12 +2304,12 @@
         <v>36.4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B45" s="3">
         <v>2888</v>
@@ -2306,12 +2318,12 @@
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B46" s="3">
         <v>66</v>
@@ -2320,12 +2332,12 @@
         <v>23.37</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B47" s="3">
         <v>4</v>
@@ -2334,12 +2346,12 @@
         <v>361.92</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B48" s="3">
         <v>2</v>
@@ -2348,12 +2360,12 @@
         <v>20.69</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B49" s="3">
         <v>24</v>
@@ -2362,12 +2374,12 @@
         <v>21</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B50" s="3">
         <v>3</v>
@@ -2376,12 +2388,12 @@
         <v>357.53</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="B51" s="3">
         <v>29</v>
@@ -2390,12 +2402,12 @@
         <v>19.3</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B52" s="3">
         <v>4</v>
@@ -2404,12 +2416,12 @@
         <v>337.5</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B53" s="3">
         <v>36</v>
@@ -2418,12 +2430,12 @@
         <v>33.64</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B54" s="3">
         <v>8</v>
@@ -2432,12 +2444,12 @@
         <v>33.64</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B55" s="3">
         <v>20</v>
@@ -2446,12 +2458,12 @@
         <v>298.12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
@@ -2460,12 +2472,12 @@
         <v>1982.77</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="B57" s="3">
         <v>18</v>
@@ -2474,12 +2486,12 @@
         <v>280.12</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B58" s="3">
         <v>76</v>
@@ -2488,12 +2500,12 @@
         <v>24.51</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B59" s="3">
         <v>24</v>
@@ -2502,12 +2514,12 @@
         <v>26.08</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B60" s="3">
         <v>36</v>
@@ -2516,12 +2528,12 @@
         <v>26.21</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B61" s="3">
         <v>12</v>
@@ -2530,12 +2542,12 @@
         <v>87.56</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B62" s="3">
         <v>24</v>
@@ -2544,12 +2556,12 @@
         <v>101.08</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B63" s="3">
         <v>60</v>
@@ -2558,12 +2570,12 @@
         <v>29.13</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B64" s="3">
         <v>23</v>
@@ -2572,12 +2584,12 @@
         <v>102.31</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B65" s="3">
         <v>0</v>
@@ -2586,12 +2598,12 @@
         <v>126.7</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B66" s="3">
         <v>0</v>
@@ -2600,12 +2612,12 @@
         <v>168.07</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B67" s="3">
         <v>307</v>
@@ -2614,12 +2626,12 @@
         <v>16.600000000000001</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B68" s="3">
         <v>70</v>
@@ -2628,12 +2640,12 @@
         <v>60.95</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B69" s="3">
         <v>57</v>
@@ -2642,12 +2654,12 @@
         <v>76.569999999999993</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B70" s="3">
         <v>35</v>
@@ -2656,12 +2668,12 @@
         <v>16.79</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B71" s="3">
         <v>120</v>
@@ -2670,12 +2682,12 @@
         <v>18.96</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B72" s="3">
         <v>33</v>
@@ -2684,12 +2696,12 @@
         <v>73.13</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B73" s="3">
         <v>75</v>
@@ -2698,12 +2710,12 @@
         <v>89.38</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B74" s="3">
         <v>77</v>
@@ -2712,12 +2724,12 @@
         <v>18.96</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B75" s="3">
         <v>56</v>
@@ -2726,12 +2738,12 @@
         <v>73.13</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B76" s="3">
         <v>15</v>
@@ -2740,12 +2752,12 @@
         <v>89.39</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="B77" s="3">
         <v>0</v>
@@ -2754,12 +2766,12 @@
         <v>3173.52</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="B78" s="3">
         <v>21</v>
@@ -2768,12 +2780,12 @@
         <v>25.4</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B79" s="3">
         <v>15</v>
@@ -2782,12 +2794,12 @@
         <v>40.92</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B80" s="3">
         <v>9</v>
@@ -2796,12 +2808,12 @@
         <v>25.4</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B81" s="3">
         <v>15</v>
@@ -2810,12 +2822,12 @@
         <v>28.07</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="B82" s="3">
         <v>4</v>
@@ -2824,12 +2836,12 @@
         <v>23.33</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B83" s="3">
         <v>32</v>
@@ -2838,12 +2850,12 @@
         <v>34.630000000000003</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B84" s="3">
         <v>40</v>
@@ -2852,12 +2864,12 @@
         <v>16.559999999999999</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B85" s="3">
         <v>20</v>
@@ -2866,12 +2878,12 @@
         <v>82.88</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B86" s="3">
         <v>5</v>
@@ -2880,12 +2892,12 @@
         <v>161.01</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B87" s="3">
         <v>2</v>
@@ -2894,12 +2906,12 @@
         <v>44.85</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B88" s="3">
         <v>9</v>
@@ -2908,12 +2920,12 @@
         <v>65.83</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B89" s="3">
         <v>3</v>
@@ -2922,12 +2934,12 @@
         <v>46.76</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B90" s="3">
         <v>19</v>
@@ -2936,12 +2948,12 @@
         <v>62.11</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B91" s="3">
         <v>10</v>
@@ -2950,12 +2962,12 @@
         <v>47.61</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B92" s="3">
         <v>1</v>
@@ -2964,12 +2976,12 @@
         <v>63.76</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B93" s="3">
         <v>1</v>
@@ -2978,12 +2990,12 @@
         <v>1159.2</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B94" s="3">
         <v>1</v>
@@ -2992,12 +3004,12 @@
         <v>255</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B95" s="3">
         <v>22</v>
@@ -3006,12 +3018,12 @@
         <v>69.55</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B96" s="3">
         <v>1</v>
@@ -3020,12 +3032,12 @@
         <v>1391.04</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="B97" s="3">
         <v>11</v>
@@ -3034,12 +3046,12 @@
         <v>87.1</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B98" s="3">
         <v>24</v>
@@ -3048,12 +3060,12 @@
         <v>40.54</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B99" s="3">
         <v>1</v>
@@ -3062,12 +3074,12 @@
         <v>460.01</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B100" s="3">
         <v>1</v>
@@ -3076,12 +3088,12 @@
         <v>639.4</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B101" s="3">
         <v>7</v>
@@ -3090,12 +3102,12 @@
         <v>103.89</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B102" s="3">
         <v>11</v>
@@ -3104,12 +3116,12 @@
         <v>58.48</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B103" s="3">
         <v>27</v>
@@ -3118,12 +3130,12 @@
         <v>56.93</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B104" s="3">
         <v>1</v>
@@ -3132,12 +3144,12 @@
         <v>63.76</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B105" s="3">
         <v>3</v>
@@ -3146,12 +3158,12 @@
         <v>61.92</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B106" s="3">
         <v>15</v>
@@ -3160,12 +3172,12 @@
         <v>63.76</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B107" s="3">
         <v>30</v>
@@ -3174,12 +3186,12 @@
         <v>69.56</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="B108" s="3">
         <v>4</v>
@@ -3188,12 +3200,12 @@
         <v>59.68</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B109" s="3">
         <v>32</v>
@@ -3202,12 +3214,12 @@
         <v>56.93</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B110" s="3">
         <v>32</v>
@@ -3216,12 +3228,12 @@
         <v>80.73</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="B111" s="3">
         <v>12</v>
@@ -3230,12 +3242,12 @@
         <v>98.95</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B112" s="3">
         <v>9</v>
@@ -3244,12 +3256,12 @@
         <v>93.25</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B113" s="3">
         <v>13</v>
@@ -3258,12 +3270,12 @@
         <v>63.76</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B114" s="3">
         <v>18</v>
@@ -3272,12 +3284,12 @@
         <v>63.76</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="B115" s="3">
         <v>14</v>
@@ -3286,12 +3298,12 @@
         <v>81.150000000000006</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B116" s="3">
         <v>27</v>
@@ -3300,12 +3312,12 @@
         <v>63.76</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B117" s="3">
         <v>19</v>
@@ -3314,12 +3326,12 @@
         <v>69.87</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B118" s="3">
         <v>14</v>
@@ -3328,12 +3340,12 @@
         <v>63.76</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B119" s="3">
         <v>30</v>
@@ -3342,12 +3354,12 @@
         <v>69.56</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B120" s="3">
         <v>6</v>
@@ -3356,12 +3368,12 @@
         <v>69.56</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B121" s="3">
         <v>52</v>
@@ -3370,12 +3382,12 @@
         <v>52.17</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B122" s="3">
         <v>9</v>
@@ -3384,12 +3396,12 @@
         <v>208.66</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B123" s="3">
         <v>20</v>
@@ -3398,12 +3410,12 @@
         <v>88.87</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B124" s="3">
         <v>72</v>
@@ -3412,12 +3424,12 @@
         <v>67.27</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="B125" s="3">
         <v>9</v>
@@ -3426,12 +3438,12 @@
         <v>69.55</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B126" s="3">
         <v>10</v>
@@ -3440,12 +3452,12 @@
         <v>63.89</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B127" s="3">
         <v>10</v>
@@ -3454,12 +3466,12 @@
         <v>149.91</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="B128" s="3">
         <v>5</v>
@@ -3468,12 +3480,12 @@
         <v>38.57</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B129" s="3">
         <v>7</v>
@@ -3482,12 +3494,12 @@
         <v>207.31</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B130" s="3">
         <v>25</v>
@@ -3496,12 +3508,12 @@
         <v>65.23</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="B131" s="3">
         <v>11</v>
@@ -3510,12 +3522,12 @@
         <v>325.87</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B132" s="3">
         <v>1</v>
@@ -3524,12 +3536,12 @@
         <v>5165.8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B133" s="3">
         <v>3</v>
@@ -3538,12 +3550,12 @@
         <v>511.75</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B134" s="3">
         <v>4</v>
@@ -3552,12 +3564,12 @@
         <v>572.70000000000005</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B135" s="3">
         <v>127</v>
@@ -3566,12 +3578,12 @@
         <v>66.98</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B136" s="3">
         <v>4</v>
@@ -3580,12 +3592,12 @@
         <v>367.42</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B137" s="3">
         <v>12</v>
@@ -3594,12 +3606,12 @@
         <v>51.52</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B138" s="3">
         <v>0</v>
@@ -3608,12 +3620,12 @@
         <v>23.19</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B139" s="3">
         <v>22</v>
@@ -3622,12 +3634,12 @@
         <v>23.19</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B140" s="3">
         <v>24</v>
@@ -3636,12 +3648,12 @@
         <v>69.55</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B141" s="3">
         <v>1</v>
@@ -3650,12 +3662,12 @@
         <v>3169.7</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="B142" s="3">
         <v>12</v>
@@ -3664,12 +3676,12 @@
         <v>81.14</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B143" s="3">
         <v>19</v>
@@ -3678,12 +3690,12 @@
         <v>81.14</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="B144" s="3">
         <v>60</v>
@@ -3692,12 +3704,12 @@
         <v>66.98</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="B145" s="3">
         <v>31</v>
@@ -3706,12 +3718,12 @@
         <v>60.28</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B146" s="3">
         <v>6</v>
@@ -3720,12 +3732,12 @@
         <v>93.35</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="B147" s="3">
         <v>1</v>
@@ -3734,12 +3746,12 @@
         <v>1217.1600000000001</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B148" s="3">
         <v>1</v>
@@ -3748,12 +3760,12 @@
         <v>3079</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B149" s="3">
         <v>9</v>
@@ -3762,12 +3774,12 @@
         <v>43.7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B150" s="3">
         <v>1</v>
@@ -3776,12 +3788,12 @@
         <v>48.95</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B151" s="3">
         <v>9</v>
@@ -3790,12 +3802,12 @@
         <v>72.33</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B152" s="3">
         <v>6</v>
@@ -3804,12 +3816,12 @@
         <v>284.19</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="B153" s="3">
         <v>19</v>
@@ -3818,12 +3830,12 @@
         <v>132.19</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B154" s="3">
         <v>62</v>
@@ -3832,12 +3844,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B155" s="3">
         <v>62</v>
@@ -3846,12 +3858,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B156" s="3">
         <v>1</v>
@@ -3860,12 +3872,12 @@
         <v>37.43</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="B157" s="3">
         <v>45</v>
@@ -3874,12 +3886,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B158" s="3">
         <v>9</v>
@@ -3888,12 +3900,12 @@
         <v>115.01</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B159" s="3">
         <v>17</v>
@@ -3902,12 +3914,12 @@
         <v>38.39</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B160" s="3">
         <v>3</v>
@@ -3916,12 +3928,12 @@
         <v>151.47999999999999</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="B161" s="3">
         <v>12</v>
@@ -3930,12 +3942,12 @@
         <v>181.68</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B162" s="3">
         <v>12</v>
@@ -3944,12 +3956,12 @@
         <v>20.059999999999999</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="B163" s="3">
         <v>9</v>
@@ -3958,12 +3970,12 @@
         <v>12.88</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B164" s="3">
         <v>14</v>
@@ -3972,12 +3984,12 @@
         <v>26.73</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B165" s="3">
         <v>12</v>
@@ -3986,12 +3998,12 @@
         <v>29.95</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B166" s="3">
         <v>10</v>
@@ -4000,12 +4012,12 @@
         <v>58.68</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="B167" s="3">
         <v>3</v>
@@ -4014,12 +4026,12 @@
         <v>79.98</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="B168" s="3">
         <v>42</v>
@@ -4028,12 +4040,12 @@
         <v>38.770000000000003</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="B169" s="3">
         <v>10</v>
@@ -4042,12 +4054,12 @@
         <v>107.35</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="B170" s="3">
         <v>20</v>
@@ -4056,12 +4068,12 @@
         <v>61.83</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="B171" s="3">
         <v>17</v>
@@ -4070,12 +4082,12 @@
         <v>243.16</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B172" s="3">
         <v>35</v>
@@ -4084,12 +4096,12 @@
         <v>63.78</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B173" s="3">
         <v>17</v>
@@ -4098,12 +4110,12 @@
         <v>75.989999999999995</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="B174" s="3">
         <v>3</v>
@@ -4112,12 +4124,12 @@
         <v>297.64999999999998</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B175" s="3">
         <v>14</v>
@@ -4126,12 +4138,12 @@
         <v>77.28</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B176" s="3">
         <v>15</v>
@@ -4140,12 +4152,12 @@
         <v>75.989999999999995</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="B177" s="3">
         <v>6</v>
@@ -4154,12 +4166,12 @@
         <v>342.24</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="B178" s="3">
         <v>2</v>
@@ -4168,12 +4180,12 @@
         <v>633.75</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="B179" s="3">
         <v>72</v>
@@ -4182,12 +4194,12 @@
         <v>50.51</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="B180" s="3">
         <v>4</v>
@@ -4196,12 +4208,12 @@
         <v>787.75</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B181" s="3">
         <v>12</v>
@@ -4210,12 +4222,12 @@
         <v>122.36</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="B182" s="3">
         <v>20</v>
@@ -4224,12 +4236,12 @@
         <v>35.81</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="B183" s="3">
         <v>25</v>
@@ -4238,12 +4250,12 @@
         <v>59.25</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="B184" s="3">
         <v>6</v>
@@ -4252,12 +4264,12 @@
         <v>201.84</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B185" s="3">
         <v>15</v>
@@ -4266,12 +4278,12 @@
         <v>48.23</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B186" s="3">
         <v>5</v>
@@ -4280,12 +4292,12 @@
         <v>221.86</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B187" s="3">
         <v>4</v>
@@ -4294,12 +4306,12 @@
         <v>74.7</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="B188" s="3">
         <v>16</v>
@@ -4308,12 +4320,12 @@
         <v>296.3</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="B189" s="3">
         <v>14</v>
@@ -4322,12 +4334,12 @@
         <v>141.80000000000001</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B190" s="3">
         <v>18</v>
@@ -4336,12 +4348,12 @@
         <v>41.4</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B191" s="3">
         <v>13</v>
@@ -4350,12 +4362,12 @@
         <v>173.3</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B192" s="3">
         <v>3</v>
@@ -4364,12 +4376,12 @@
         <v>2189.02</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -4378,12 +4390,12 @@
         <v>453.22</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B194" s="3">
         <v>25</v>
@@ -4392,12 +4404,12 @@
         <v>48.64</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="B195" s="3">
         <v>7</v>
@@ -4406,12 +4418,12 @@
         <v>126.63</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="B196" s="3">
         <v>5</v>
@@ -4420,12 +4432,12 @@
         <v>69.56</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="B197" s="3">
         <v>26</v>
@@ -4434,12 +4446,12 @@
         <v>44.51</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B198" s="3">
         <v>7</v>
@@ -4448,12 +4460,12 @@
         <v>145.94</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="B199" s="3">
         <v>31</v>
@@ -4462,12 +4474,12 @@
         <v>179</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B200" s="3">
         <v>1</v>
@@ -4476,12 +4488,12 @@
         <v>2060</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="B201" s="3">
         <v>17</v>
@@ -4490,12 +4502,12 @@
         <v>51</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="B202" s="3">
         <v>9</v>
@@ -4504,12 +4516,12 @@
         <v>183.41</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="B203" s="3">
         <v>5</v>
@@ -4518,12 +4530,12 @@
         <v>206.33</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B204" s="3">
         <v>55</v>
@@ -4532,12 +4544,12 @@
         <v>33.479999999999997</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B205" s="3">
         <v>23</v>
@@ -4546,12 +4558,12 @@
         <v>46.06</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B206" s="3">
         <v>3</v>
@@ -4560,12 +4572,12 @@
         <v>4900</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B207" s="3">
         <v>0</v>
@@ -4574,12 +4586,12 @@
         <v>5345.33</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="B208" s="3">
         <v>15</v>
@@ -4588,12 +4600,12 @@
         <v>170.78</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="B209" s="3">
         <v>10</v>
@@ -4602,12 +4614,12 @@
         <v>192.51</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="B210" s="3">
         <v>25</v>
@@ -4616,12 +4628,12 @@
         <v>59.7</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="B211" s="3">
         <v>0</v>
@@ -4630,12 +4642,12 @@
         <v>265.05</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B212" s="3">
         <v>65</v>
@@ -4644,12 +4656,12 @@
         <v>36.799999999999997</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="B213" s="3">
         <v>18</v>
@@ -4658,12 +4670,12 @@
         <v>103.04</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="B214" s="3">
         <v>54</v>
@@ -4672,12 +4684,12 @@
         <v>36.75</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="B215" s="3">
         <v>11</v>
@@ -4686,12 +4698,12 @@
         <v>47.16</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="B216" s="3">
         <v>27</v>
@@ -4700,12 +4712,12 @@
         <v>16.809999999999999</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="B217" s="3">
         <v>53</v>
@@ -4714,12 +4726,12 @@
         <v>37.299999999999997</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="B218" s="3">
         <v>18</v>
@@ -4728,12 +4740,12 @@
         <v>126.24</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B219" s="3">
         <v>17</v>
@@ -4742,12 +4754,12 @@
         <v>154.62</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="B220" s="3">
         <v>2</v>
@@ -4756,12 +4768,12 @@
         <v>508.2</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B221" s="3">
         <v>0</v>
@@ -4770,12 +4782,12 @@
         <v>5069</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B222" s="3">
         <v>2</v>
@@ -4784,12 +4796,12 @@
         <v>466.78</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="B223" s="3">
         <v>15</v>
@@ -4798,12 +4810,12 @@
         <v>57.5</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B224" s="3">
         <v>8</v>
@@ -4812,12 +4824,12 @@
         <v>63.13</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="B225" s="3">
         <v>1</v>
@@ -4826,12 +4838,12 @@
         <v>20789.41</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="B226" s="3">
         <v>1</v>
@@ -4840,12 +4852,12 @@
         <v>33057.85</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="B227" s="3">
         <v>7</v>
@@ -4854,12 +4866,12 @@
         <v>83.5</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="B228" s="3">
         <v>30</v>
@@ -4868,12 +4880,12 @@
         <v>81.650000000000006</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="B229" s="3">
         <v>17</v>
@@ -4882,12 +4894,12 @@
         <v>50.71</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="B230" s="3">
         <v>10</v>
@@ -4896,12 +4908,12 @@
         <v>51.75</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="B231" s="3">
         <v>13</v>
@@ -4910,12 +4922,12 @@
         <v>36.94</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B232" s="3">
         <v>24</v>
@@ -4924,12 +4936,12 @@
         <v>36.94</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="B233" s="3">
         <v>45</v>
@@ -4938,12 +4950,12 @@
         <v>67.28</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="B234" s="3">
         <v>31</v>
@@ -4952,12 +4964,12 @@
         <v>65.099999999999994</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B235" s="3">
         <v>45</v>
@@ -4966,12 +4978,12 @@
         <v>65.53</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="B236" s="3">
         <v>26</v>
@@ -4980,12 +4992,12 @@
         <v>109.08</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="B237" s="3">
         <v>129</v>
@@ -4994,12 +5006,12 @@
         <v>33.479999999999997</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B238" s="3">
         <v>6</v>
@@ -5008,12 +5020,12 @@
         <v>422.09</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="B239" s="3">
         <v>2</v>
@@ -5022,12 +5034,12 @@
         <v>1277.7</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="B240" s="3">
         <v>20</v>
@@ -5036,12 +5048,12 @@
         <v>6.44</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="B241" s="3">
         <v>9</v>
@@ -5050,12 +5062,12 @@
         <v>108.2</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="B242" s="3">
         <v>1</v>
@@ -5064,12 +5076,12 @@
         <v>4456.4799999999996</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="B243" s="3">
         <v>1</v>
@@ -5078,12 +5090,12 @@
         <v>6279</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="B244" s="3">
         <v>2</v>
@@ -5092,12 +5104,12 @@
         <v>609.5</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="B245" s="3">
         <v>21</v>
@@ -5106,12 +5118,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="B246" s="3">
         <v>13</v>
@@ -5120,12 +5132,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="B247" s="3">
         <v>42</v>
@@ -5134,12 +5146,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B248" s="3">
         <v>9</v>
@@ -5148,12 +5160,12 @@
         <v>32.200000000000003</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="B249" s="3">
         <v>7</v>
@@ -5162,12 +5174,12 @@
         <v>40.4</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B250" s="3">
         <v>156</v>
@@ -5176,12 +5188,12 @@
         <v>36.06</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B251" s="3">
         <v>37</v>
@@ -5190,12 +5202,12 @@
         <v>56</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="B252" s="3">
         <v>17</v>
@@ -5204,12 +5216,12 @@
         <v>57.63</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B253" s="3">
         <v>4</v>
@@ -5218,12 +5230,12 @@
         <v>60.78</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B254" s="3">
         <v>9</v>
@@ -5232,12 +5244,12 @@
         <v>42.49</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B255" s="3">
         <v>12</v>
@@ -5246,12 +5258,12 @@
         <v>66.3</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="B256" s="3">
         <v>3</v>
@@ -5260,12 +5272,12 @@
         <v>261.8</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B257" s="3">
         <v>14</v>
@@ -5274,12 +5286,12 @@
         <v>71.709999999999994</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="B258" s="3">
         <v>1</v>
@@ -5288,12 +5300,12 @@
         <v>77.760000000000005</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="B259" s="3">
         <v>17</v>
@@ -5302,12 +5314,12 @@
         <v>54.7</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="B260" s="3">
         <v>15</v>
@@ -5316,12 +5328,12 @@
         <v>67.28</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="B261" s="3">
         <v>5</v>
@@ -5330,12 +5342,12 @@
         <v>251.5</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="B262" s="3">
         <v>12</v>
@@ -5344,12 +5356,12 @@
         <v>78.87</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="B263" s="3">
         <v>13</v>
@@ -5358,12 +5370,12 @@
         <v>83.84</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="B264" s="3">
         <v>6</v>
@@ -5372,12 +5384,12 @@
         <v>331.2</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="B265" s="3">
         <v>19</v>
@@ -5386,12 +5398,12 @@
         <v>79.75</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="B266" s="3">
         <v>22</v>
@@ -5400,12 +5412,12 @@
         <v>83.84</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="B267" s="3">
         <v>5</v>
@@ -5414,12 +5426,12 @@
         <v>284</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="B268" s="3">
         <v>12</v>
@@ -5428,12 +5440,12 @@
         <v>28.15</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="B269" s="3">
         <v>2</v>
@@ -5442,12 +5454,12 @@
         <v>45.08</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="B270" s="3">
         <v>9</v>
@@ -5456,12 +5468,12 @@
         <v>51.52</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B271" s="3">
         <v>5</v>
@@ -5470,12 +5482,12 @@
         <v>40.57</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="B272" s="3">
         <v>27</v>
@@ -5484,12 +5496,12 @@
         <v>36.229999999999997</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="B273" s="3">
         <v>24</v>
@@ -5498,12 +5510,12 @@
         <v>54.12</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="B274" s="3">
         <v>12</v>
@@ -5512,12 +5524,12 @@
         <v>69.55</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="B275" s="3">
         <v>10</v>
@@ -5526,12 +5538,12 @@
         <v>295.14999999999998</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B276" s="3">
         <v>6</v>
@@ -5540,12 +5552,12 @@
         <v>38.56</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="B277" s="3">
         <v>7</v>
@@ -5554,12 +5566,12 @@
         <v>60.95</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="B278" s="3">
         <v>10</v>
@@ -5568,12 +5580,12 @@
         <v>78.209999999999994</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="B279" s="3">
         <v>88</v>
@@ -5582,12 +5594,12 @@
         <v>44.93</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="B280" s="3">
         <v>1</v>
@@ -5596,12 +5608,12 @@
         <v>6578.46</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B281" s="3">
         <v>20</v>
@@ -5610,12 +5622,12 @@
         <v>173.09</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="B282" s="3">
         <v>9</v>
@@ -5624,12 +5636,12 @@
         <v>211.23</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="B283" s="3">
         <v>0</v>
@@ -5638,12 +5650,12 @@
         <v>2314.8000000000002</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="B284" s="3">
         <v>3</v>
@@ -5652,12 +5664,12 @@
         <v>791.3</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B285" s="3">
         <v>26</v>
@@ -5666,12 +5678,12 @@
         <v>31.6</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="B286" s="3">
         <v>7</v>
@@ -5680,12 +5692,12 @@
         <v>77.28</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="B287" s="3">
         <v>24</v>
@@ -5694,12 +5706,12 @@
         <v>43.8</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="B288" s="3">
         <v>7</v>
@@ -5708,12 +5720,12 @@
         <v>21.9</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B289" s="3">
         <v>3</v>
@@ -5722,12 +5734,12 @@
         <v>798.6</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B290" s="3">
         <v>93</v>
@@ -5736,12 +5748,12 @@
         <v>23.19</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B291" s="3">
         <v>63</v>
@@ -5750,12 +5762,12 @@
         <v>8.24</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="B292" s="3">
         <v>8</v>
@@ -5764,12 +5776,12 @@
         <v>13.72</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B293" s="3">
         <v>9</v>
@@ -5778,12 +5790,12 @@
         <v>31.95</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="B294" s="3">
         <v>105</v>
@@ -5792,12 +5804,12 @@
         <v>16.2</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="B295" s="3">
         <v>6</v>
@@ -5806,12 +5818,12 @@
         <v>36.869999999999997</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="B296" s="3">
         <v>21</v>
@@ -5820,12 +5832,12 @@
         <v>31.48</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B297" s="3">
         <v>7</v>
@@ -5834,12 +5846,12 @@
         <v>21.9</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="B298" s="3">
         <v>6</v>
@@ -5848,12 +5860,12 @@
         <v>23.19</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="B299" s="3">
         <v>12</v>
@@ -5862,12 +5874,12 @@
         <v>19.55</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="B300" s="3">
         <v>11</v>
@@ -5876,12 +5888,12 @@
         <v>19.07</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="B301" s="3">
         <v>34</v>
@@ -5890,12 +5902,12 @@
         <v>21.9</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="B302" s="3">
         <v>20</v>
@@ -5904,12 +5916,12 @@
         <v>79.349999999999994</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="B303" s="3">
         <v>1</v>
@@ -5918,12 +5930,12 @@
         <v>862.7</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="B304" s="3">
         <v>11</v>
@@ -5932,12 +5944,12 @@
         <v>56.93</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="B305" s="3">
         <v>0</v>
@@ -5946,12 +5958,12 @@
         <v>1265</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="B306" s="3">
         <v>30</v>
@@ -5960,12 +5972,12 @@
         <v>76</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="B307" s="3">
         <v>6</v>
@@ -5974,12 +5986,12 @@
         <v>267.85000000000002</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="B308" s="3">
         <v>17</v>
@@ -5988,12 +6000,12 @@
         <v>74.7</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B309" s="3">
         <v>15</v>
@@ -6002,12 +6014,12 @@
         <v>327.3</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="B310" s="3">
         <v>10</v>
@@ -6016,12 +6028,12 @@
         <v>72.13</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="B311" s="3">
         <v>43</v>
@@ -6030,12 +6042,12 @@
         <v>302.39999999999998</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="B312" s="3">
         <v>35</v>
@@ -6044,12 +6056,12 @@
         <v>36.799999999999997</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="B313" s="3">
         <v>0</v>
@@ -6058,12 +6070,12 @@
         <v>428.5</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="B314" s="3">
         <v>3</v>
@@ -6072,12 +6084,12 @@
         <v>450.22</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B315" s="3">
         <v>4</v>
@@ -6086,12 +6098,12 @@
         <v>465.7</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="B316" s="3">
         <v>19</v>
@@ -6100,12 +6112,12 @@
         <v>38.25</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="B317" s="3">
         <v>2</v>
@@ -6114,12 +6126,12 @@
         <v>87.49</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="B318" s="3">
         <v>23</v>
@@ -6128,12 +6140,12 @@
         <v>63.13</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="B319" s="3">
         <v>2</v>
@@ -6142,12 +6154,12 @@
         <v>377.78</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="B320" s="3">
         <v>2</v>
@@ -6156,12 +6168,12 @@
         <v>3333.85</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="B321" s="3">
         <v>7</v>
@@ -6170,12 +6182,12 @@
         <v>374.67</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="B322" s="3">
         <v>1</v>
@@ -6184,12 +6196,12 @@
         <v>120.06</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="B323" s="3">
         <v>24</v>
@@ -6198,12 +6210,12 @@
         <v>54.2</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="B324" s="3">
         <v>12</v>
@@ -6212,12 +6224,12 @@
         <v>31.5</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="B325" s="3">
         <v>2</v>
@@ -6226,12 +6238,12 @@
         <v>114.09</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="B326" s="3">
         <v>3</v>
@@ -6240,12 +6252,12 @@
         <v>139.9</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B327" s="3">
         <v>4</v>
@@ -6254,12 +6266,12 @@
         <v>35.94</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="B328" s="3">
         <v>8</v>
@@ -6268,12 +6280,12 @@
         <v>140.26</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="B329" s="3">
         <v>1</v>
@@ -6282,12 +6294,12 @@
         <v>370.53</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B330" s="3">
         <v>3</v>
@@ -6296,12 +6308,12 @@
         <v>30.9</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="B331" s="3">
         <v>1</v>
@@ -6310,12 +6322,12 @@
         <v>4772.5</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="B332" s="3">
         <v>4</v>
@@ -6324,12 +6336,12 @@
         <v>516.46</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="B333" s="3">
         <v>4</v>
@@ -6338,12 +6350,12 @@
         <v>185.15</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="B334" s="3">
         <v>31</v>
@@ -6352,12 +6364,12 @@
         <v>11.5</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="B335" s="3">
         <v>4</v>
@@ -6366,12 +6378,12 @@
         <v>724.5</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="B336" s="3">
         <v>4</v>
@@ -6380,12 +6392,12 @@
         <v>450.22</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="B337" s="3">
         <v>1</v>
@@ -6394,12 +6406,12 @@
         <v>461.23</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="B338" s="3">
         <v>1</v>
@@ -6408,12 +6420,12 @@
         <v>518.41999999999996</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="B339" s="3">
         <v>1</v>
@@ -6422,12 +6434,12 @@
         <v>348.08</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="B340" s="3">
         <v>10</v>
@@ -6436,12 +6448,12 @@
         <v>33.479999999999997</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="B341" s="3">
         <v>13</v>
@@ -6450,12 +6462,12 @@
         <v>35.79</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="B342" s="3">
         <v>3</v>
@@ -6464,12 +6476,12 @@
         <v>377.7</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="B343" s="3">
         <v>18</v>
@@ -6478,12 +6490,12 @@
         <v>33.21</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B344" s="3">
         <v>39</v>
@@ -6492,12 +6504,12 @@
         <v>27.16</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="B345" s="3">
         <v>1</v>
@@ -6506,12 +6518,12 @@
         <v>361.41</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="B346" s="3">
         <v>64</v>
@@ -6520,12 +6532,12 @@
         <v>29.25</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="B347" s="3">
         <v>1</v>
@@ -6534,12 +6546,12 @@
         <v>304.54000000000002</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="B348" s="3">
         <v>17</v>
@@ -6548,12 +6560,12 @@
         <v>34.049999999999997</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="B349" s="3">
         <v>7</v>
@@ -6562,12 +6574,12 @@
         <v>57.7</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="B350" s="3">
         <v>10</v>
@@ -6576,12 +6588,12 @@
         <v>90.9</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="B351" s="3">
         <v>48</v>
@@ -6590,12 +6602,12 @@
         <v>44.31</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="B352" s="3">
         <v>1</v>
@@ -6604,12 +6616,12 @@
         <v>7173.59</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="B353" s="3">
         <v>1</v>
@@ -6618,12 +6630,12 @@
         <v>677.79</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="B354" s="3">
         <v>23</v>
@@ -6632,12 +6644,12 @@
         <v>167.33</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="B355" s="3">
         <v>19</v>
@@ -6646,12 +6658,12 @@
         <v>191</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="B356" s="3">
         <v>3</v>
@@ -6660,12 +6672,12 @@
         <v>2335.67</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B357" s="3">
         <v>64</v>
@@ -6674,12 +6686,12 @@
         <v>62.04</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="B358" s="3">
         <v>2</v>
@@ -6688,12 +6700,12 @@
         <v>8139.6</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="B359" s="3">
         <v>126</v>
@@ -6702,12 +6714,12 @@
         <v>235.53</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="B360" s="3">
         <v>19</v>
@@ -6716,12 +6728,12 @@
         <v>259.8</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="B361" s="3">
         <v>1</v>
@@ -6730,12 +6742,12 @@
         <v>310.2</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="B362" s="3">
         <v>1</v>
@@ -6744,12 +6756,12 @@
         <v>36.43</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="B363" s="3">
         <v>15</v>
@@ -6758,12 +6770,12 @@
         <v>87.22</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="B364" s="3">
         <v>9</v>
@@ -6772,12 +6784,12 @@
         <v>319.60000000000002</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="B365" s="3">
         <v>24</v>
@@ -6786,12 +6798,12 @@
         <v>62.6</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="B366" s="3">
         <v>6</v>
@@ -6800,12 +6812,12 @@
         <v>312.8</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="B367" s="3">
         <v>48</v>
@@ -6814,12 +6826,12 @@
         <v>67.28</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="B368" s="3">
         <v>4</v>
@@ -6828,12 +6840,12 @@
         <v>1138.5</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="B369" s="3">
         <v>24</v>
@@ -6842,12 +6854,12 @@
         <v>58.69</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="B370" s="3">
         <v>12</v>
@@ -6856,12 +6868,12 @@
         <v>289.33999999999997</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="B371" s="3">
         <v>2</v>
@@ -6870,12 +6882,12 @@
         <v>48.76</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="B372" s="3">
         <v>2</v>
@@ -6884,12 +6896,12 @@
         <v>242.34</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="B373" s="3">
         <v>31</v>
@@ -6898,12 +6910,12 @@
         <v>54.09</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="B374" s="3">
         <v>20</v>
@@ -6912,12 +6924,12 @@
         <v>255.03</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="B375" s="3">
         <v>18</v>
@@ -6926,12 +6938,12 @@
         <v>220.8</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="B376" s="3">
         <v>17</v>
@@ -6940,12 +6952,12 @@
         <v>255.02</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B377" s="3">
         <v>6</v>
@@ -6954,12 +6966,12 @@
         <v>68.86</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="B378" s="3">
         <v>3</v>
@@ -6968,12 +6980,12 @@
         <v>344.28</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="B379" s="3">
         <v>10</v>
@@ -6982,12 +6994,12 @@
         <v>60.29</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="B380" s="3">
         <v>4</v>
@@ -6996,12 +7008,12 @@
         <v>261.8</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="B381" s="3">
         <v>2</v>
@@ -7010,12 +7022,12 @@
         <v>30.58</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="B382" s="3">
         <v>54</v>
@@ -7024,12 +7036,12 @@
         <v>16.95</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="B383" s="3">
         <v>45</v>
@@ -7038,12 +7050,12 @@
         <v>24.95</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="B384" s="3">
         <v>3</v>
@@ -7052,12 +7064,12 @@
         <v>641.49</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="B385" s="3">
         <v>12</v>
@@ -7066,12 +7078,12 @@
         <v>39.57</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="B386" s="3">
         <v>36</v>
@@ -7080,12 +7092,12 @@
         <v>51.83</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="B387" s="3">
         <v>44</v>
@@ -7094,12 +7106,12 @@
         <v>33.840000000000003</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="B388" s="3">
         <v>19</v>
@@ -7108,12 +7120,12 @@
         <v>150.15</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="B389" s="3">
         <v>25</v>
@@ -7122,12 +7134,12 @@
         <v>144.5</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="B390" s="3">
         <v>25</v>
@@ -7136,12 +7148,12 @@
         <v>100.93</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="B391" s="3">
         <v>14</v>
@@ -7150,12 +7162,12 @@
         <v>124.5</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="B392" s="3">
         <v>10</v>
@@ -7164,12 +7176,12 @@
         <v>27.21</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="B393" s="3">
         <v>94</v>
@@ -7178,12 +7190,12 @@
         <v>24.79</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>405</v>
+        <v>382</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="B394" s="3">
         <v>6</v>
@@ -7192,12 +7204,12 @@
         <v>37.1</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="B395" s="3">
         <v>8</v>
@@ -7206,12 +7218,12 @@
         <v>178.04</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="B396" s="3">
         <v>48</v>
@@ -7220,12 +7232,12 @@
         <v>23.88</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="B397" s="3">
         <v>93</v>
@@ -7234,12 +7246,12 @@
         <v>20.68</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="B398" s="3">
         <v>31</v>
@@ -7248,12 +7260,12 @@
         <v>97.54</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="B399" s="3">
         <v>9</v>
@@ -7262,12 +7274,12 @@
         <v>304.02999999999997</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="B400" s="3">
         <v>3</v>
@@ -7276,12 +7288,12 @@
         <v>1934.56</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="B401" s="3">
         <v>0</v>
@@ -7290,12 +7302,12 @@
         <v>230.99</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="B402" s="3">
         <v>96</v>
@@ -7304,12 +7316,12 @@
         <v>33.39</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="B403" s="3">
         <v>48</v>
@@ -7318,12 +7330,12 @@
         <v>20.66</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="B404" s="3">
         <v>197</v>
@@ -7332,12 +7344,12 @@
         <v>97.5</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="B405" s="3">
         <v>195</v>
@@ -7346,12 +7358,12 @@
         <v>24.7</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="B406" s="3">
         <v>195</v>
@@ -7360,12 +7372,12 @@
         <v>35.75</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="B407" s="3">
         <v>200</v>
@@ -7374,12 +7386,12 @@
         <v>9.1</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B408" s="3">
         <v>200</v>
@@ -7388,12 +7400,12 @@
         <v>5.43</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="B409" s="3">
         <v>150</v>
@@ -7402,12 +7414,12 @@
         <v>9.75</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="B410" s="3">
         <v>108</v>
@@ -7416,12 +7428,12 @@
         <v>6.37</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="B411" s="3">
         <v>150</v>
@@ -7430,12 +7442,12 @@
         <v>11.59</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="B412" s="3">
         <v>115</v>
@@ -7444,7 +7456,7 @@
         <v>12.09</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1710,7 +1710,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -1780,7 +1780,7 @@
         <v>407</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3">
         <v>407.86</v>
@@ -2312,7 +2312,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2888</v>
+        <v>2852</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
@@ -2620,7 +2620,7 @@
         <v>40</v>
       </c>
       <c r="B67" s="3">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C67" s="3">
         <v>16.600000000000001</v>
@@ -2634,7 +2634,7 @@
         <v>41</v>
       </c>
       <c r="B68" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C68" s="3">
         <v>60.95</v>
@@ -2844,7 +2844,7 @@
         <v>54</v>
       </c>
       <c r="B83" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C83" s="3">
         <v>34.630000000000003</v>
@@ -2872,7 +2872,7 @@
         <v>56</v>
       </c>
       <c r="B85" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C85" s="3">
         <v>82.88</v>
@@ -3572,7 +3572,7 @@
         <v>104</v>
       </c>
       <c r="B135" s="3">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C135" s="3">
         <v>66.98</v>
@@ -3628,7 +3628,7 @@
         <v>108</v>
       </c>
       <c r="B139" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C139" s="3">
         <v>23.19</v>
@@ -4034,7 +4034,7 @@
         <v>136</v>
       </c>
       <c r="B168" s="3">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C168" s="3">
         <v>38.770000000000003</v>
@@ -4188,7 +4188,7 @@
         <v>147</v>
       </c>
       <c r="B179" s="3">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C179" s="3">
         <v>50.51</v>
@@ -4230,7 +4230,7 @@
         <v>150</v>
       </c>
       <c r="B182" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C182" s="3">
         <v>35.81</v>
@@ -4720,7 +4720,7 @@
         <v>182</v>
       </c>
       <c r="B217" s="3">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C217" s="3">
         <v>37.299999999999997</v>
@@ -5000,7 +5000,7 @@
         <v>201</v>
       </c>
       <c r="B237" s="3">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C237" s="3">
         <v>33.479999999999997</v>
@@ -5182,7 +5182,7 @@
         <v>213</v>
       </c>
       <c r="B250" s="3">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C250" s="3">
         <v>36.06</v>
@@ -5252,7 +5252,7 @@
         <v>218</v>
       </c>
       <c r="B255" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C255" s="3">
         <v>66.3</v>
@@ -5266,7 +5266,7 @@
         <v>219</v>
       </c>
       <c r="B256" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C256" s="3">
         <v>261.8</v>
@@ -5630,7 +5630,7 @@
         <v>245</v>
       </c>
       <c r="B282" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C282" s="3">
         <v>211.23</v>
@@ -5644,7 +5644,7 @@
         <v>246</v>
       </c>
       <c r="B283" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C283" s="3">
         <v>2314.8000000000002</v>
@@ -5658,7 +5658,7 @@
         <v>247</v>
       </c>
       <c r="B284" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C284" s="3">
         <v>791.3</v>
@@ -5742,7 +5742,7 @@
         <v>253</v>
       </c>
       <c r="B290" s="3">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C290" s="3">
         <v>23.19</v>
@@ -6638,7 +6638,7 @@
         <v>315</v>
       </c>
       <c r="B354" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C354" s="3">
         <v>167.33</v>
@@ -6652,7 +6652,7 @@
         <v>316</v>
       </c>
       <c r="B355" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C355" s="3">
         <v>191</v>
@@ -6666,7 +6666,7 @@
         <v>317</v>
       </c>
       <c r="B356" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C356" s="3">
         <v>2335.67</v>
@@ -6680,7 +6680,7 @@
         <v>318</v>
       </c>
       <c r="B357" s="3">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C357" s="3">
         <v>62.04</v>
@@ -6722,7 +6722,7 @@
         <v>321</v>
       </c>
       <c r="B360" s="3">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="C360" s="3">
         <v>259.8</v>
@@ -6778,7 +6778,7 @@
         <v>325</v>
       </c>
       <c r="B364" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C364" s="3">
         <v>319.60000000000002</v>
@@ -6820,7 +6820,7 @@
         <v>328</v>
       </c>
       <c r="B367" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C367" s="3">
         <v>67.28</v>
@@ -7044,7 +7044,7 @@
         <v>341</v>
       </c>
       <c r="B383" s="3">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C383" s="3">
         <v>24.95</v>
@@ -7338,7 +7338,7 @@
         <v>386</v>
       </c>
       <c r="B404" s="3">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C404" s="3">
         <v>97.5</v>
@@ -7352,7 +7352,7 @@
         <v>387</v>
       </c>
       <c r="B405" s="3">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C405" s="3">
         <v>24.7</v>
@@ -7422,7 +7422,7 @@
         <v>395</v>
       </c>
       <c r="B410" s="3">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C410" s="3">
         <v>6.37</v>
@@ -7450,7 +7450,7 @@
         <v>393</v>
       </c>
       <c r="B412" s="3">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C412" s="3">
         <v>12.09</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="429">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1195,15 +1195,6 @@
     <t>NOXARO</t>
   </si>
   <si>
-    <t>IPC SPRAY INSONORIZANT 650 ML</t>
-  </si>
-  <si>
-    <t>IPC SPRAY CURATAT FRANE 750 ML</t>
-  </si>
-  <si>
-    <t>IPC SPRAY ANTI-RUGINA 450 ML</t>
-  </si>
-  <si>
     <t>RAV Spray Vaselina Off Road 0.4L</t>
   </si>
   <si>
@@ -1298,6 +1289,18 @@
   </si>
   <si>
     <t>BANNER 57512 EFB 75Ah</t>
+  </si>
+  <si>
+    <t>IPC SPRAY CURATAT FRANE 750 ML CLUE</t>
+  </si>
+  <si>
+    <t>IPC SPRAY ANTI-RUGINA 450 ML CLUE</t>
+  </si>
+  <si>
+    <t>IPC SPRAY CURATAT FRANE 750 ML NOXARO</t>
+  </si>
+  <si>
+    <t>IPC SPRAY INSONORIZANT 650 ML NOXARO</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1752,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B5" s="3">
         <v>16</v>
@@ -1763,7 +1766,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -1777,7 +1780,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -1791,7 +1794,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -1805,7 +1808,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B9" s="3">
         <v>24</v>
@@ -1819,7 +1822,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B10" s="3">
         <v>45</v>
@@ -1833,7 +1836,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
@@ -1847,7 +1850,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -1875,7 +1878,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1889,7 +1892,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1903,7 +1906,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -1912,7 +1915,7 @@
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1931,7 +1934,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -1945,7 +1948,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B19" s="3">
         <v>6</v>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B20" s="3">
         <v>24</v>
@@ -1973,7 +1976,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B21" s="3">
         <v>3</v>
@@ -1987,7 +1990,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
@@ -2001,7 +2004,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B23" s="3">
         <v>9</v>
@@ -2015,7 +2018,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -2029,7 +2032,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B25" s="3">
         <v>23</v>
@@ -2043,7 +2046,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
@@ -2057,7 +2060,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B27" s="3">
         <v>21</v>
@@ -2071,7 +2074,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -2085,7 +2088,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2458,7 +2461,7 @@
         <v>298.12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2500,7 +2503,7 @@
         <v>24.51</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2514,7 +2517,7 @@
         <v>26.08</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2528,7 +2531,7 @@
         <v>26.21</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2542,7 +2545,7 @@
         <v>87.56</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2556,7 +2559,7 @@
         <v>101.08</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2570,7 +2573,7 @@
         <v>29.13</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2584,7 +2587,7 @@
         <v>102.31</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2598,7 +2601,7 @@
         <v>126.7</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2612,7 +2615,7 @@
         <v>168.07</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2626,7 +2629,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2640,7 +2643,7 @@
         <v>60.95</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2654,7 +2657,7 @@
         <v>76.569999999999993</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2668,7 +2671,7 @@
         <v>16.79</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2682,7 +2685,7 @@
         <v>18.96</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2696,7 +2699,7 @@
         <v>73.13</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2710,7 +2713,7 @@
         <v>89.38</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2724,7 +2727,7 @@
         <v>18.96</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2738,7 +2741,7 @@
         <v>73.13</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2752,7 +2755,7 @@
         <v>89.39</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2766,7 +2769,7 @@
         <v>3173.52</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2827,7 +2830,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B82" s="3">
         <v>4</v>
@@ -4325,7 +4328,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B189" s="3">
         <v>14</v>
@@ -7013,7 +7016,7 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B381" s="3">
         <v>2</v>
@@ -7405,7 +7408,7 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="B409" s="3">
         <v>150</v>
@@ -7419,7 +7422,7 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="B410" s="3">
         <v>104</v>
@@ -7433,7 +7436,7 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="B411" s="3">
         <v>150</v>
@@ -7447,7 +7450,7 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="B412" s="3">
         <v>111</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -6714,7 +6714,7 @@
         <v>126</v>
       </c>
       <c r="C359" s="3">
-        <v>235.53</v>
+        <v>259.81</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>375</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1755,7 +1755,7 @@
         <v>402</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>239.2</v>
@@ -1769,7 +1769,7 @@
         <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3">
         <v>262.61</v>
@@ -2315,7 +2315,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2852</v>
+        <v>2804</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
@@ -2623,7 +2623,7 @@
         <v>40</v>
       </c>
       <c r="B67" s="3">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C67" s="3">
         <v>16.600000000000001</v>
@@ -2637,7 +2637,7 @@
         <v>41</v>
       </c>
       <c r="B68" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C68" s="3">
         <v>60.95</v>
@@ -2693,7 +2693,7 @@
         <v>44</v>
       </c>
       <c r="B72" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C72" s="3">
         <v>73.13</v>
@@ -2707,7 +2707,7 @@
         <v>45</v>
       </c>
       <c r="B73" s="3">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C73" s="3">
         <v>89.38</v>
@@ -2735,7 +2735,7 @@
         <v>47</v>
       </c>
       <c r="B75" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C75" s="3">
         <v>73.13</v>
@@ -2875,7 +2875,7 @@
         <v>56</v>
       </c>
       <c r="B85" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C85" s="3">
         <v>82.88</v>
@@ -3463,7 +3463,7 @@
         <v>96</v>
       </c>
       <c r="B127" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C127" s="3">
         <v>149.91</v>
@@ -3575,7 +3575,7 @@
         <v>104</v>
       </c>
       <c r="B135" s="3">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C135" s="3">
         <v>66.98</v>
@@ -3911,7 +3911,7 @@
         <v>127</v>
       </c>
       <c r="B159" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C159" s="3">
         <v>38.39</v>
@@ -4079,7 +4079,7 @@
         <v>139</v>
       </c>
       <c r="B171" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C171" s="3">
         <v>243.16</v>
@@ -4275,7 +4275,7 @@
         <v>153</v>
       </c>
       <c r="B185" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C185" s="3">
         <v>48.23</v>
@@ -4611,7 +4611,7 @@
         <v>174</v>
       </c>
       <c r="B209" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C209" s="3">
         <v>192.51</v>
@@ -5003,7 +5003,7 @@
         <v>201</v>
       </c>
       <c r="B237" s="3">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C237" s="3">
         <v>33.479999999999997</v>
@@ -5199,7 +5199,7 @@
         <v>214</v>
       </c>
       <c r="B251" s="3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C251" s="3">
         <v>56</v>
@@ -5325,7 +5325,7 @@
         <v>223</v>
       </c>
       <c r="B260" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C260" s="3">
         <v>67.28</v>
@@ -5619,7 +5619,7 @@
         <v>244</v>
       </c>
       <c r="B281" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C281" s="3">
         <v>173.09</v>
@@ -6683,7 +6683,7 @@
         <v>318</v>
       </c>
       <c r="B357" s="3">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C357" s="3">
         <v>62.04</v>
@@ -6711,7 +6711,7 @@
         <v>320</v>
       </c>
       <c r="B359" s="3">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C359" s="3">
         <v>259.81</v>
@@ -6725,7 +6725,7 @@
         <v>321</v>
       </c>
       <c r="B360" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C360" s="3">
         <v>259.8</v>
@@ -6949,7 +6949,7 @@
         <v>335</v>
       </c>
       <c r="B376" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C376" s="3">
         <v>255.02</v>
@@ -7341,7 +7341,7 @@
         <v>386</v>
       </c>
       <c r="B404" s="3">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C404" s="3">
         <v>97.5</v>
@@ -7355,7 +7355,7 @@
         <v>387</v>
       </c>
       <c r="B405" s="3">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C405" s="3">
         <v>24.7</v>
@@ -7369,7 +7369,7 @@
         <v>388</v>
       </c>
       <c r="B406" s="3">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C406" s="3">
         <v>35.75</v>
@@ -7383,7 +7383,7 @@
         <v>389</v>
       </c>
       <c r="B407" s="3">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C407" s="3">
         <v>9.1</v>
@@ -7397,7 +7397,7 @@
         <v>390</v>
       </c>
       <c r="B408" s="3">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C408" s="3">
         <v>5.43</v>
@@ -7411,7 +7411,7 @@
         <v>425</v>
       </c>
       <c r="B409" s="3">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C409" s="3">
         <v>9.75</v>
@@ -7425,7 +7425,7 @@
         <v>426</v>
       </c>
       <c r="B410" s="3">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C410" s="3">
         <v>6.37</v>
@@ -7453,7 +7453,7 @@
         <v>428</v>
       </c>
       <c r="B412" s="3">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="C412" s="3">
         <v>12.09</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="429">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1686,7 +1686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D412"/>
+  <dimension ref="A1:D406"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2357,10 +2357,10 @@
         <v>26</v>
       </c>
       <c r="B48" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C48" s="3">
-        <v>20.69</v>
+        <v>21</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>378</v>
@@ -2368,13 +2368,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C49" s="3">
-        <v>21</v>
+        <v>357.53</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>378</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C50" s="3">
-        <v>357.53</v>
+        <v>19.3</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>378</v>
@@ -2396,13 +2396,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51" s="3">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C51" s="3">
-        <v>19.3</v>
+        <v>337.5</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>378</v>
@@ -2410,13 +2410,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52" s="3">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C52" s="3">
-        <v>337.5</v>
+        <v>33.64</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>378</v>
@@ -2424,209 +2424,209 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" s="3">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C53" s="3">
-        <v>33.64</v>
+        <v>298.12</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B54" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C54" s="3">
-        <v>33.64</v>
+        <v>1982.77</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B55" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C55" s="3">
-        <v>298.12</v>
+        <v>280.12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B56" s="3">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C56" s="3">
-        <v>1982.77</v>
+        <v>24.51</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B57" s="3">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C57" s="3">
-        <v>280.12</v>
+        <v>26.21</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B58" s="3">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C58" s="3">
-        <v>24.51</v>
+        <v>101.08</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B59" s="3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C59" s="3">
-        <v>26.08</v>
+        <v>29.13</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B60" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C60" s="3">
-        <v>26.21</v>
+        <v>102.31</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B61" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C61" s="3">
-        <v>87.56</v>
+        <v>168.07</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B62" s="3">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="C62" s="3">
-        <v>101.08</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B63" s="3">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C63" s="3">
-        <v>29.13</v>
+        <v>60.95</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B64" s="3">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C64" s="3">
-        <v>102.31</v>
+        <v>76.569999999999993</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B65" s="3">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C65" s="3">
-        <v>126.7</v>
+        <v>18.96</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B66" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C66" s="3">
-        <v>168.07</v>
+        <v>73.13</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B67" s="3">
-        <v>289</v>
+        <v>73</v>
       </c>
       <c r="C67" s="3">
-        <v>16.600000000000001</v>
+        <v>89.38</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>397</v>
@@ -2634,13 +2634,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B68" s="3">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C68" s="3">
-        <v>60.95</v>
+        <v>18.96</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>397</v>
@@ -2648,13 +2648,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B69" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C69" s="3">
-        <v>76.569999999999993</v>
+        <v>73.13</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>397</v>
@@ -2662,13 +2662,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B70" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C70" s="3">
-        <v>16.79</v>
+        <v>89.39</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>397</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B71" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="C71" s="3">
-        <v>18.96</v>
+        <v>3173.52</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>397</v>
@@ -2690,265 +2690,265 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B72" s="3">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C72" s="3">
-        <v>73.13</v>
+        <v>25.4</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B73" s="3">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C73" s="3">
-        <v>89.38</v>
+        <v>40.92</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B74" s="3">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="C74" s="3">
-        <v>18.96</v>
+        <v>25.4</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B75" s="3">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C75" s="3">
-        <v>73.13</v>
+        <v>28.07</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>395</v>
       </c>
       <c r="B76" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C76" s="3">
-        <v>89.39</v>
+        <v>23.33</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B77" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C77" s="3">
-        <v>3173.52</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B78" s="3">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C78" s="3">
-        <v>25.4</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B79" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C79" s="3">
-        <v>40.92</v>
+        <v>82.88</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B80" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C80" s="3">
-        <v>25.4</v>
+        <v>161.01</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B81" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C81" s="3">
-        <v>28.07</v>
+        <v>44.85</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>395</v>
+        <v>59</v>
       </c>
       <c r="B82" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C82" s="3">
-        <v>23.33</v>
+        <v>65.83</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B83" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C83" s="3">
-        <v>34.630000000000003</v>
+        <v>46.76</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B84" s="3">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C84" s="3">
-        <v>16.559999999999999</v>
+        <v>62.11</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B85" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C85" s="3">
-        <v>82.88</v>
+        <v>47.61</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B86" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C86" s="3">
-        <v>161.01</v>
+        <v>63.76</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B87" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" s="3">
-        <v>44.85</v>
+        <v>1159.2</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B88" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C88" s="3">
-        <v>65.83</v>
+        <v>255</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B89" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C89" s="3">
-        <v>46.76</v>
+        <v>69.55</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B90" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C90" s="3">
-        <v>62.11</v>
+        <v>1391.04</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>378</v>
@@ -2956,13 +2956,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B91" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3">
-        <v>47.61</v>
+        <v>87.1</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>378</v>
@@ -2970,13 +2970,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C92" s="3">
-        <v>63.76</v>
+        <v>40.54</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>378</v>
@@ -2984,13 +2984,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B93" s="3">
         <v>1</v>
       </c>
       <c r="C93" s="3">
-        <v>1159.2</v>
+        <v>460.01</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>378</v>
@@ -2998,13 +2998,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B94" s="3">
         <v>1</v>
       </c>
       <c r="C94" s="3">
-        <v>255</v>
+        <v>639.4</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>378</v>
@@ -3012,13 +3012,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B95" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C95" s="3">
-        <v>69.55</v>
+        <v>103.89</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>378</v>
@@ -3026,13 +3026,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B96" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C96" s="3">
-        <v>1391.04</v>
+        <v>58.48</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>378</v>
@@ -3040,13 +3040,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B97" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C97" s="3">
-        <v>87.1</v>
+        <v>56.93</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>378</v>
@@ -3054,13 +3054,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B98" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C98" s="3">
-        <v>40.54</v>
+        <v>63.76</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>378</v>
@@ -3068,13 +3068,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B99" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99" s="3">
-        <v>460.01</v>
+        <v>61.92</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>378</v>
@@ -3082,13 +3082,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C100" s="3">
-        <v>639.4</v>
+        <v>63.76</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>378</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B101" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C101" s="3">
-        <v>103.89</v>
+        <v>69.56</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>378</v>
@@ -3110,13 +3110,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B102" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C102" s="3">
-        <v>58.48</v>
+        <v>59.68</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>378</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B103" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C103" s="3">
         <v>56.93</v>
@@ -3138,13 +3138,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B104" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C104" s="3">
-        <v>63.76</v>
+        <v>80.73</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>378</v>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B105" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C105" s="3">
-        <v>61.92</v>
+        <v>98.95</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>378</v>
@@ -3166,13 +3166,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B106" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C106" s="3">
-        <v>63.76</v>
+        <v>93.25</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>378</v>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B107" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C107" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>378</v>
@@ -3194,13 +3194,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B108" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C108" s="3">
-        <v>59.68</v>
+        <v>63.76</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>378</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B109" s="3">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C109" s="3">
-        <v>56.93</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>378</v>
@@ -3222,13 +3222,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B110" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C110" s="3">
-        <v>80.73</v>
+        <v>63.76</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>378</v>
@@ -3236,13 +3236,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B111" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C111" s="3">
-        <v>98.95</v>
+        <v>69.87</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>378</v>
@@ -3250,13 +3250,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B112" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C112" s="3">
-        <v>93.25</v>
+        <v>63.76</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>378</v>
@@ -3264,13 +3264,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B113" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C113" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>378</v>
@@ -3278,13 +3278,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B114" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C114" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>378</v>
@@ -3292,13 +3292,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B115" s="3">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C115" s="3">
-        <v>81.150000000000006</v>
+        <v>52.17</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>378</v>
@@ -3306,13 +3306,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B116" s="3">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C116" s="3">
-        <v>63.76</v>
+        <v>208.66</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>378</v>
@@ -3320,13 +3320,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B117" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C117" s="3">
-        <v>69.87</v>
+        <v>88.87</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>378</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B118" s="3">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="C118" s="3">
-        <v>63.76</v>
+        <v>67.27</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>378</v>
@@ -3348,13 +3348,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B119" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C119" s="3">
-        <v>69.56</v>
+        <v>69.55</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>378</v>
@@ -3362,13 +3362,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B120" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C120" s="3">
-        <v>69.56</v>
+        <v>63.89</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>378</v>
@@ -3376,13 +3376,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B121" s="3">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C121" s="3">
-        <v>52.17</v>
+        <v>149.91</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>378</v>
@@ -3390,13 +3390,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B122" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C122" s="3">
-        <v>208.66</v>
+        <v>38.57</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>378</v>
@@ -3404,13 +3404,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B123" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C123" s="3">
-        <v>88.87</v>
+        <v>207.31</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>378</v>
@@ -3418,41 +3418,41 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B124" s="3">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C124" s="3">
-        <v>67.27</v>
+        <v>65.23</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B125" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C125" s="3">
-        <v>69.55</v>
+        <v>325.87</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B126" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C126" s="3">
-        <v>63.89</v>
+        <v>5165.8</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>378</v>
@@ -3460,13 +3460,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B127" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C127" s="3">
-        <v>149.91</v>
+        <v>511.75</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>378</v>
@@ -3474,13 +3474,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B128" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128" s="3">
-        <v>38.57</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>378</v>
@@ -3488,83 +3488,83 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B129" s="3">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C129" s="3">
-        <v>207.31</v>
+        <v>66.98</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B130" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C130" s="3">
-        <v>65.23</v>
+        <v>367.42</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B131" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C131" s="3">
-        <v>325.87</v>
+        <v>51.52</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B132" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" s="3">
-        <v>5165.8</v>
+        <v>23.19</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B133" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C133" s="3">
-        <v>511.75</v>
+        <v>23.19</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B134" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C134" s="3">
-        <v>572.70000000000005</v>
+        <v>69.55</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>378</v>
@@ -3572,27 +3572,27 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B135" s="3">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="C135" s="3">
-        <v>66.98</v>
+        <v>3169.7</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B136" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C136" s="3">
-        <v>367.42</v>
+        <v>81.14</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>378</v>
@@ -3600,55 +3600,55 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B137" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C137" s="3">
-        <v>51.52</v>
+        <v>81.14</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B138" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C138" s="3">
-        <v>23.19</v>
+        <v>66.98</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B139" s="3">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C139" s="3">
-        <v>23.19</v>
+        <v>60.28</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B140" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C140" s="3">
-        <v>69.55</v>
+        <v>93.35</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>378</v>
@@ -3656,13 +3656,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B141" s="3">
         <v>1</v>
       </c>
       <c r="C141" s="3">
-        <v>3169.7</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>378</v>
@@ -3670,13 +3670,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B142" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C142" s="3">
-        <v>81.14</v>
+        <v>3079</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>378</v>
@@ -3684,69 +3684,69 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B143" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C143" s="3">
-        <v>81.14</v>
+        <v>43.7</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B144" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C144" s="3">
-        <v>66.98</v>
+        <v>48.95</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B145" s="3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C145" s="3">
-        <v>60.28</v>
+        <v>72.33</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B146" s="3">
         <v>6</v>
       </c>
       <c r="C146" s="3">
-        <v>93.35</v>
+        <v>284.19</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C147" s="3">
-        <v>1217.1600000000001</v>
+        <v>132.19</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>378</v>
@@ -3754,321 +3754,321 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C148" s="3">
-        <v>3079</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B149" s="3">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C149" s="3">
-        <v>43.7</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B150" s="3">
         <v>1</v>
       </c>
       <c r="C150" s="3">
-        <v>48.95</v>
+        <v>37.43</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B151" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C151" s="3">
-        <v>72.33</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B152" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C152" s="3">
-        <v>284.19</v>
+        <v>115.01</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B153" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C153" s="3">
-        <v>132.19</v>
+        <v>38.39</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B154" s="3">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C154" s="3">
-        <v>32.200000000000003</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B155" s="3">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="C155" s="3">
-        <v>32.200000000000003</v>
+        <v>181.68</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C156" s="3">
-        <v>37.43</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B157" s="3">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C157" s="3">
-        <v>32.200000000000003</v>
+        <v>12.88</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B158" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C158" s="3">
-        <v>115.01</v>
+        <v>26.73</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B159" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C159" s="3">
-        <v>38.39</v>
+        <v>29.95</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B160" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C160" s="3">
-        <v>151.47999999999999</v>
+        <v>58.68</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B161" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C161" s="3">
-        <v>181.68</v>
+        <v>79.98</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B162" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C162" s="3">
-        <v>20.059999999999999</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B163" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C163" s="3">
-        <v>12.88</v>
+        <v>107.35</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B164" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C164" s="3">
-        <v>26.73</v>
+        <v>61.83</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B165" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C165" s="3">
-        <v>29.95</v>
+        <v>243.16</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B166" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C166" s="3">
-        <v>58.68</v>
+        <v>63.78</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B167" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C167" s="3">
-        <v>79.98</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B168" s="3">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C168" s="3">
-        <v>38.770000000000003</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B169" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C169" s="3">
-        <v>107.35</v>
+        <v>77.28</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B170" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C170" s="3">
-        <v>61.83</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>375</v>
@@ -4076,13 +4076,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B171" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C171" s="3">
-        <v>243.16</v>
+        <v>342.24</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>375</v>
@@ -4090,13 +4090,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B172" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C172" s="3">
-        <v>63.78</v>
+        <v>633.75</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>378</v>
@@ -4104,69 +4104,69 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B173" s="3">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C173" s="3">
-        <v>75.989999999999995</v>
+        <v>50.51</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B174" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C174" s="3">
-        <v>297.64999999999998</v>
+        <v>787.75</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B175" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C175" s="3">
-        <v>77.28</v>
+        <v>122.36</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B176" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C176" s="3">
-        <v>75.989999999999995</v>
+        <v>35.81</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B177" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C177" s="3">
-        <v>342.24</v>
+        <v>59.25</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>375</v>
@@ -4174,83 +4174,83 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B178" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C178" s="3">
-        <v>633.75</v>
+        <v>201.84</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B179" s="3">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C179" s="3">
-        <v>50.51</v>
+        <v>48.23</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B180" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C180" s="3">
-        <v>787.75</v>
+        <v>221.86</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B181" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C181" s="3">
-        <v>122.36</v>
+        <v>74.7</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B182" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C182" s="3">
-        <v>35.81</v>
+        <v>296.3</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>151</v>
+        <v>396</v>
       </c>
       <c r="B183" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C183" s="3">
-        <v>59.25</v>
+        <v>141.80000000000001</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>375</v>
@@ -4258,13 +4258,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B184" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C184" s="3">
-        <v>201.84</v>
+        <v>41.4</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>375</v>
@@ -4272,13 +4272,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B185" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C185" s="3">
-        <v>48.23</v>
+        <v>173.3</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>375</v>
@@ -4286,13 +4286,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B186" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C186" s="3">
-        <v>221.86</v>
+        <v>2189.02</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>375</v>
@@ -4300,13 +4300,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B187" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C187" s="3">
-        <v>74.7</v>
+        <v>453.22</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>375</v>
@@ -4314,13 +4314,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B188" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C188" s="3">
-        <v>296.3</v>
+        <v>48.64</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>375</v>
@@ -4328,13 +4328,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>396</v>
+        <v>162</v>
       </c>
       <c r="B189" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C189" s="3">
-        <v>141.80000000000001</v>
+        <v>126.63</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>375</v>
@@ -4342,27 +4342,27 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B190" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C190" s="3">
-        <v>41.4</v>
+        <v>69.56</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B191" s="3">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C191" s="3">
-        <v>173.3</v>
+        <v>44.51</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>375</v>
@@ -4370,13 +4370,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B192" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C192" s="3">
-        <v>2189.02</v>
+        <v>145.94</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>375</v>
@@ -4384,13 +4384,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B193" s="3">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C193" s="3">
-        <v>453.22</v>
+        <v>179</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>375</v>
@@ -4398,13 +4398,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B194" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C194" s="3">
-        <v>48.64</v>
+        <v>2060</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>375</v>
@@ -4412,13 +4412,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B195" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C195" s="3">
-        <v>126.63</v>
+        <v>51</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>375</v>
@@ -4426,27 +4426,27 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B196" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C196" s="3">
-        <v>69.56</v>
+        <v>183.41</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>164</v>
+        <v>362</v>
       </c>
       <c r="B197" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C197" s="3">
-        <v>44.51</v>
+        <v>206.33</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>375</v>
@@ -4454,27 +4454,27 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B198" s="3">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C198" s="3">
-        <v>145.94</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B199" s="3">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C199" s="3">
-        <v>179</v>
+        <v>46.06</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>375</v>
@@ -4482,13 +4482,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C200" s="3">
-        <v>2060</v>
+        <v>4900</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>375</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B201" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C201" s="3">
-        <v>51</v>
+        <v>5345.33</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>375</v>
@@ -4510,13 +4510,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B202" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C202" s="3">
-        <v>183.41</v>
+        <v>170.78</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>375</v>
@@ -4524,13 +4524,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>362</v>
+        <v>174</v>
       </c>
       <c r="B203" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C203" s="3">
-        <v>206.33</v>
+        <v>192.51</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>375</v>
@@ -4538,27 +4538,27 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B204" s="3">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C204" s="3">
-        <v>33.479999999999997</v>
+        <v>59.7</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B205" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C205" s="3">
-        <v>46.06</v>
+        <v>265.05</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>375</v>
@@ -4566,83 +4566,83 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B206" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C206" s="3">
-        <v>4900</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B207" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C207" s="3">
-        <v>5345.33</v>
+        <v>103.04</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B208" s="3">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C208" s="3">
-        <v>170.78</v>
+        <v>36.75</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B209" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C209" s="3">
-        <v>192.51</v>
+        <v>47.16</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B210" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C210" s="3">
-        <v>59.7</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B211" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C211" s="3">
-        <v>265.05</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>375</v>
@@ -4650,153 +4650,153 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B212" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C212" s="3">
-        <v>36.799999999999997</v>
+        <v>126.24</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B213" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C213" s="3">
-        <v>103.04</v>
+        <v>154.62</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B214" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C214" s="3">
-        <v>36.75</v>
+        <v>508.2</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B215" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C215" s="3">
-        <v>47.16</v>
+        <v>5069</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B216" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C216" s="3">
-        <v>16.809999999999999</v>
+        <v>466.78</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B217" s="3">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C217" s="3">
-        <v>37.299999999999997</v>
+        <v>57.5</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B218" s="3">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C218" s="3">
-        <v>126.24</v>
+        <v>63.13</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B219" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C219" s="3">
-        <v>154.62</v>
+        <v>20789.41</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B220" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C220" s="3">
-        <v>508.2</v>
+        <v>33057.85</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B221" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C221" s="3">
-        <v>5069</v>
+        <v>83.5</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B222" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C222" s="3">
-        <v>466.78</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>375</v>
@@ -4804,69 +4804,69 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B223" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C223" s="3">
-        <v>57.5</v>
+        <v>50.71</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B224" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C224" s="3">
-        <v>63.13</v>
+        <v>51.75</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B225" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C225" s="3">
-        <v>20789.41</v>
+        <v>36.94</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B226" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C226" s="3">
-        <v>33057.85</v>
+        <v>36.94</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B227" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C227" s="3">
-        <v>83.5</v>
+        <v>67.28</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>378</v>
@@ -4874,349 +4874,349 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B228" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C228" s="3">
-        <v>81.650000000000006</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B229" s="3">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C229" s="3">
-        <v>50.71</v>
+        <v>65.53</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B230" s="3">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C230" s="3">
-        <v>51.75</v>
+        <v>109.08</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B231" s="3">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="C231" s="3">
-        <v>36.94</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B232" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C232" s="3">
-        <v>36.94</v>
+        <v>422.09</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B233" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C233" s="3">
-        <v>67.28</v>
+        <v>1277.7</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B234" s="3">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C234" s="3">
-        <v>65.099999999999994</v>
+        <v>6.44</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B235" s="3">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C235" s="3">
-        <v>65.53</v>
+        <v>108.2</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B236" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C236" s="3">
-        <v>109.08</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B237" s="3">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="C237" s="3">
-        <v>33.479999999999997</v>
+        <v>6279</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B238" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C238" s="3">
-        <v>422.09</v>
+        <v>609.5</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B239" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C239" s="3">
-        <v>1277.7</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B240" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C240" s="3">
-        <v>6.44</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B241" s="3">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C241" s="3">
-        <v>108.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B242" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C242" s="3">
-        <v>4456.4799999999996</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B243" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C243" s="3">
-        <v>6279</v>
+        <v>40.4</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B244" s="3">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="C244" s="3">
-        <v>609.5</v>
+        <v>36.06</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B245" s="3">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C245" s="3">
-        <v>32.200000000000003</v>
+        <v>56</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B246" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C246" s="3">
-        <v>32.200000000000003</v>
+        <v>57.63</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B247" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="C247" s="3">
-        <v>32.200000000000003</v>
+        <v>60.78</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B248" s="3">
         <v>9</v>
       </c>
       <c r="C248" s="3">
-        <v>32.200000000000003</v>
+        <v>42.49</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B249" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C249" s="3">
-        <v>40.4</v>
+        <v>66.3</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B250" s="3">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="C250" s="3">
-        <v>36.06</v>
+        <v>261.8</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B251" s="3">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C251" s="3">
-        <v>56</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B252" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C252" s="3">
-        <v>57.63</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>378</v>
@@ -5224,27 +5224,27 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B253" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C253" s="3">
-        <v>60.78</v>
+        <v>54.7</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B254" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C254" s="3">
-        <v>42.49</v>
+        <v>67.28</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>375</v>
@@ -5252,13 +5252,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B255" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C255" s="3">
-        <v>66.3</v>
+        <v>251.5</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>375</v>
@@ -5266,13 +5266,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B256" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C256" s="3">
-        <v>261.8</v>
+        <v>78.87</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>375</v>
@@ -5280,13 +5280,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B257" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C257" s="3">
-        <v>71.709999999999994</v>
+        <v>83.84</v>
       </c>
       <c r="D257" s="4" t="s">
         <v>375</v>
@@ -5294,27 +5294,27 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B258" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C258" s="3">
-        <v>77.760000000000005</v>
+        <v>331.2</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B259" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C259" s="3">
-        <v>54.7</v>
+        <v>79.75</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>375</v>
@@ -5322,13 +5322,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B260" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C260" s="3">
-        <v>67.28</v>
+        <v>83.84</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>375</v>
@@ -5336,13 +5336,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B261" s="3">
         <v>5</v>
       </c>
       <c r="C261" s="3">
-        <v>251.5</v>
+        <v>284</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>375</v>
@@ -5350,55 +5350,55 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B262" s="3">
         <v>12</v>
       </c>
       <c r="C262" s="3">
-        <v>78.87</v>
+        <v>28.15</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B263" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C263" s="3">
-        <v>83.84</v>
+        <v>45.08</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B264" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C264" s="3">
-        <v>331.2</v>
+        <v>51.52</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B265" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C265" s="3">
-        <v>79.75</v>
+        <v>40.57</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>375</v>
@@ -5406,13 +5406,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B266" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C266" s="3">
-        <v>83.84</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>375</v>
@@ -5420,55 +5420,55 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B267" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C267" s="3">
-        <v>284</v>
+        <v>54.12</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B268" s="3">
         <v>12</v>
       </c>
       <c r="C268" s="3">
-        <v>28.15</v>
+        <v>69.55</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B269" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C269" s="3">
-        <v>45.08</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B270" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C270" s="3">
-        <v>51.52</v>
+        <v>38.56</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>377</v>
@@ -5476,55 +5476,55 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B271" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C271" s="3">
-        <v>40.57</v>
+        <v>60.95</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B272" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C272" s="3">
-        <v>36.229999999999997</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B273" s="3">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="C273" s="3">
-        <v>54.12</v>
+        <v>44.93</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B274" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C274" s="3">
-        <v>69.55</v>
+        <v>6578.46</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>375</v>
@@ -5532,13 +5532,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B275" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C275" s="3">
-        <v>295.14999999999998</v>
+        <v>173.09</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>375</v>
@@ -5546,139 +5546,139 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B276" s="3">
         <v>6</v>
       </c>
       <c r="C276" s="3">
-        <v>38.56</v>
+        <v>211.23</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B277" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C277" s="3">
-        <v>60.95</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B278" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C278" s="3">
-        <v>78.209999999999994</v>
+        <v>791.3</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B279" s="3">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="C279" s="3">
-        <v>44.93</v>
+        <v>31.6</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B280" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C280" s="3">
-        <v>6578.46</v>
+        <v>77.28</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B281" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C281" s="3">
-        <v>173.09</v>
+        <v>43.8</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B282" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C282" s="3">
-        <v>211.23</v>
+        <v>21.9</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B283" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C283" s="3">
-        <v>2314.8000000000002</v>
+        <v>798.6</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B284" s="3">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C284" s="3">
-        <v>791.3</v>
+        <v>23.19</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B285" s="3">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="C285" s="3">
-        <v>31.6</v>
+        <v>8.24</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>377</v>
@@ -5686,13 +5686,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B286" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C286" s="3">
-        <v>77.28</v>
+        <v>13.72</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>377</v>
@@ -5700,13 +5700,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B287" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C287" s="3">
-        <v>43.8</v>
+        <v>31.95</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>377</v>
@@ -5714,13 +5714,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>251</v>
+        <v>381</v>
       </c>
       <c r="B288" s="3">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C288" s="3">
-        <v>21.9</v>
+        <v>16.2</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>377</v>
@@ -5728,13 +5728,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B289" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C289" s="3">
-        <v>798.6</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>377</v>
@@ -5742,13 +5742,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B290" s="3">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C290" s="3">
-        <v>23.19</v>
+        <v>31.48</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>377</v>
@@ -5756,13 +5756,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B291" s="3">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C291" s="3">
-        <v>8.24</v>
+        <v>21.9</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>377</v>
@@ -5770,13 +5770,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B292" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C292" s="3">
-        <v>13.72</v>
+        <v>23.19</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>377</v>
@@ -5784,13 +5784,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B293" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C293" s="3">
-        <v>31.95</v>
+        <v>19.55</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>377</v>
@@ -5798,13 +5798,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>381</v>
+        <v>262</v>
       </c>
       <c r="B294" s="3">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="C294" s="3">
-        <v>16.2</v>
+        <v>19.07</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>377</v>
@@ -5812,13 +5812,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B295" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C295" s="3">
-        <v>36.869999999999997</v>
+        <v>21.9</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>377</v>
@@ -5826,167 +5826,167 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B296" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C296" s="3">
-        <v>31.48</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B297" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C297" s="3">
-        <v>21.9</v>
+        <v>862.7</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B298" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C298" s="3">
-        <v>23.19</v>
+        <v>56.93</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B299" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C299" s="3">
-        <v>19.55</v>
+        <v>1265</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B300" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C300" s="3">
-        <v>19.07</v>
+        <v>76</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B301" s="3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C301" s="3">
-        <v>21.9</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B302" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C302" s="3">
-        <v>79.349999999999994</v>
+        <v>74.7</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B303" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C303" s="3">
-        <v>862.7</v>
+        <v>327.3</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B304" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C304" s="3">
-        <v>56.93</v>
+        <v>72.13</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B305" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C305" s="3">
-        <v>1265</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B306" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C306" s="3">
-        <v>76</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B307" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C307" s="3">
-        <v>267.85000000000002</v>
+        <v>428.5</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>375</v>
@@ -5994,13 +5994,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B308" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C308" s="3">
-        <v>74.7</v>
+        <v>450.22</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>375</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B309" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C309" s="3">
-        <v>327.3</v>
+        <v>465.7</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>375</v>
@@ -6022,13 +6022,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B310" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C310" s="3">
-        <v>72.13</v>
+        <v>38.25</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>375</v>
@@ -6036,13 +6036,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B311" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C311" s="3">
-        <v>302.39999999999998</v>
+        <v>87.49</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>375</v>
@@ -6050,97 +6050,97 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B312" s="3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C312" s="3">
-        <v>36.799999999999997</v>
+        <v>63.13</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B313" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C313" s="3">
-        <v>428.5</v>
+        <v>377.78</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B314" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C314" s="3">
-        <v>450.22</v>
+        <v>3333.85</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B315" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C315" s="3">
-        <v>465.7</v>
+        <v>374.67</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B316" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C316" s="3">
-        <v>38.25</v>
+        <v>120.06</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B317" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C317" s="3">
-        <v>87.49</v>
+        <v>54.2</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B318" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C318" s="3">
-        <v>63.13</v>
+        <v>31.5</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>375</v>
@@ -6148,97 +6148,97 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B319" s="3">
         <v>2</v>
       </c>
       <c r="C319" s="3">
-        <v>377.78</v>
+        <v>114.09</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B320" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C320" s="3">
-        <v>3333.85</v>
+        <v>139.9</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B321" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C321" s="3">
-        <v>374.67</v>
+        <v>35.94</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B322" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C322" s="3">
-        <v>120.06</v>
+        <v>140.26</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B323" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C323" s="3">
-        <v>54.2</v>
+        <v>370.53</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B324" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C324" s="3">
-        <v>31.5</v>
+        <v>30.9</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B325" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C325" s="3">
-        <v>114.09</v>
+        <v>4772.5</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>375</v>
@@ -6246,13 +6246,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B326" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C326" s="3">
-        <v>139.9</v>
+        <v>516.46</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>375</v>
@@ -6260,13 +6260,13 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B327" s="3">
         <v>4</v>
       </c>
       <c r="C327" s="3">
-        <v>35.94</v>
+        <v>185.15</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>375</v>
@@ -6274,139 +6274,139 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B328" s="3">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C328" s="3">
-        <v>140.26</v>
+        <v>11.5</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B329" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C329" s="3">
-        <v>370.53</v>
+        <v>724.5</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B330" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C330" s="3">
-        <v>30.9</v>
+        <v>450.22</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B331" s="3">
         <v>1</v>
       </c>
       <c r="C331" s="3">
-        <v>4772.5</v>
+        <v>461.23</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B332" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C332" s="3">
-        <v>516.46</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B333" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C333" s="3">
-        <v>185.15</v>
+        <v>348.08</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B334" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C334" s="3">
-        <v>11.5</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B335" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C335" s="3">
-        <v>724.5</v>
+        <v>35.79</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B336" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C336" s="3">
-        <v>450.22</v>
+        <v>377.7</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B337" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C337" s="3">
-        <v>461.23</v>
+        <v>33.21</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>367</v>
@@ -6414,13 +6414,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B338" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C338" s="3">
-        <v>518.41999999999996</v>
+        <v>27.16</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>367</v>
@@ -6428,13 +6428,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B339" s="3">
         <v>1</v>
       </c>
       <c r="C339" s="3">
-        <v>348.08</v>
+        <v>361.41</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>367</v>
@@ -6442,13 +6442,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B340" s="3">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C340" s="3">
-        <v>33.479999999999997</v>
+        <v>29.25</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>367</v>
@@ -6456,13 +6456,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B341" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C341" s="3">
-        <v>35.79</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>367</v>
@@ -6470,13 +6470,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B342" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C342" s="3">
-        <v>377.7</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>367</v>
@@ -6484,97 +6484,97 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B343" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C343" s="3">
-        <v>33.21</v>
+        <v>57.7</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B344" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C344" s="3">
-        <v>27.16</v>
+        <v>90.9</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B345" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C345" s="3">
-        <v>361.41</v>
+        <v>44.31</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B346" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C346" s="3">
-        <v>29.25</v>
+        <v>7173.59</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B347" s="3">
         <v>1</v>
       </c>
       <c r="C347" s="3">
-        <v>304.54000000000002</v>
+        <v>677.79</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B348" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C348" s="3">
-        <v>34.049999999999997</v>
+        <v>167.33</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B349" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C349" s="3">
-        <v>57.7</v>
+        <v>191</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>375</v>
@@ -6582,27 +6582,27 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B350" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C350" s="3">
-        <v>90.9</v>
+        <v>2335.67</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B351" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C351" s="3">
-        <v>44.31</v>
+        <v>62.04</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>375</v>
@@ -6610,13 +6610,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B352" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C352" s="3">
-        <v>7173.59</v>
+        <v>8139.6</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>375</v>
@@ -6624,13 +6624,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B353" s="3">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="C353" s="3">
-        <v>677.79</v>
+        <v>259.81</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>375</v>
@@ -6638,13 +6638,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B354" s="3">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C354" s="3">
-        <v>167.33</v>
+        <v>259.8</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>375</v>
@@ -6652,13 +6652,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B355" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C355" s="3">
-        <v>191</v>
+        <v>310.2</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>375</v>
@@ -6666,13 +6666,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B356" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C356" s="3">
-        <v>2335.67</v>
+        <v>36.43</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>375</v>
@@ -6680,13 +6680,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B357" s="3">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="C357" s="3">
-        <v>62.04</v>
+        <v>87.22</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>375</v>
@@ -6694,13 +6694,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B358" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C358" s="3">
-        <v>8139.6</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>375</v>
@@ -6708,13 +6708,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B359" s="3">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="C359" s="3">
-        <v>259.81</v>
+        <v>62.6</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>375</v>
@@ -6722,13 +6722,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B360" s="3">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C360" s="3">
-        <v>259.8</v>
+        <v>312.8</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>375</v>
@@ -6736,41 +6736,41 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B361" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C361" s="3">
-        <v>310.2</v>
+        <v>67.28</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B362" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C362" s="3">
-        <v>36.43</v>
+        <v>1138.5</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B363" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C363" s="3">
-        <v>87.22</v>
+        <v>58.69</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>375</v>
@@ -6778,13 +6778,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="B364" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C364" s="3">
-        <v>319.60000000000002</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>375</v>
@@ -6792,13 +6792,13 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B365" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C365" s="3">
-        <v>62.6</v>
+        <v>48.76</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>375</v>
@@ -6806,13 +6806,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B366" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C366" s="3">
-        <v>312.8</v>
+        <v>242.34</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>375</v>
@@ -6820,41 +6820,41 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B367" s="3">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C367" s="3">
-        <v>67.28</v>
+        <v>54.09</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B368" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C368" s="3">
-        <v>1138.5</v>
+        <v>255.03</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="B369" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C369" s="3">
-        <v>58.69</v>
+        <v>220.8</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>375</v>
@@ -6862,13 +6862,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="B370" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C370" s="3">
-        <v>289.33999999999997</v>
+        <v>255.02</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>375</v>
@@ -6876,13 +6876,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B371" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C371" s="3">
-        <v>48.76</v>
+        <v>68.86</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>375</v>
@@ -6890,13 +6890,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B372" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C372" s="3">
-        <v>242.34</v>
+        <v>344.28</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>375</v>
@@ -6904,13 +6904,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B373" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C373" s="3">
-        <v>54.09</v>
+        <v>60.29</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>375</v>
@@ -6918,13 +6918,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B374" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C374" s="3">
-        <v>255.03</v>
+        <v>261.8</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>375</v>
@@ -6932,195 +6932,195 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="B375" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C375" s="3">
-        <v>220.8</v>
+        <v>30.58</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B376" s="3">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C376" s="3">
-        <v>255.02</v>
+        <v>16.95</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B377" s="3">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="C377" s="3">
-        <v>68.86</v>
+        <v>24.95</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B378" s="3">
         <v>3</v>
       </c>
       <c r="C378" s="3">
-        <v>344.28</v>
+        <v>641.49</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B379" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C379" s="3">
-        <v>60.29</v>
+        <v>39.57</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B380" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C380" s="3">
-        <v>261.8</v>
+        <v>51.83</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>393</v>
+        <v>345</v>
       </c>
       <c r="B381" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C381" s="3">
-        <v>30.58</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B382" s="3">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C382" s="3">
-        <v>16.95</v>
+        <v>150.15</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B383" s="3">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C383" s="3">
-        <v>24.95</v>
+        <v>144.5</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B384" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C384" s="3">
-        <v>641.49</v>
+        <v>100.93</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B385" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C385" s="3">
-        <v>39.57</v>
+        <v>124.5</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B386" s="3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C386" s="3">
-        <v>51.83</v>
+        <v>27.21</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B387" s="3">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="C387" s="3">
-        <v>33.840000000000003</v>
+        <v>24.79</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B388" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C388" s="3">
-        <v>150.15</v>
+        <v>37.1</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>375</v>
@@ -7128,13 +7128,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B389" s="3">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C389" s="3">
-        <v>144.5</v>
+        <v>178.04</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>375</v>
@@ -7142,27 +7142,27 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B390" s="3">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C390" s="3">
-        <v>100.93</v>
+        <v>23.88</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B391" s="3">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="C391" s="3">
-        <v>124.5</v>
+        <v>20.68</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>375</v>
@@ -7170,13 +7170,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="B392" s="3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C392" s="3">
-        <v>27.21</v>
+        <v>97.54</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>375</v>
@@ -7184,281 +7184,197 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="B393" s="3">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="C393" s="3">
-        <v>24.79</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B394" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C394" s="3">
-        <v>37.1</v>
+        <v>1934.56</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B395" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C395" s="3">
-        <v>178.04</v>
+        <v>230.99</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B396" s="3">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="C396" s="3">
-        <v>23.88</v>
+        <v>33.39</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B397" s="3">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C397" s="3">
-        <v>20.68</v>
+        <v>20.66</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B398" s="3">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="C398" s="3">
-        <v>97.54</v>
+        <v>97.5</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B399" s="3">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="C399" s="3">
-        <v>304.02999999999997</v>
+        <v>24.7</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="B400" s="3">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="C400" s="3">
-        <v>1934.56</v>
+        <v>35.75</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="B401" s="3">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="C401" s="3">
-        <v>230.99</v>
+        <v>9.1</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B402" s="3">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="C402" s="3">
-        <v>33.39</v>
+        <v>5.43</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="B403" s="3">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="C403" s="3">
-        <v>20.66</v>
+        <v>9.75</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="B404" s="3">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="C404" s="3">
-        <v>97.5</v>
+        <v>6.37</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
       <c r="B405" s="3">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C405" s="3">
-        <v>24.7</v>
+        <v>11.59</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>388</v>
+        <v>428</v>
       </c>
       <c r="B406" s="3">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="C406" s="3">
-        <v>35.75</v>
+        <v>12.09</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4">
-      <c r="A407" t="s">
-        <v>389</v>
-      </c>
-      <c r="B407" s="3">
-        <v>196</v>
-      </c>
-      <c r="C407" s="3">
-        <v>9.1</v>
-      </c>
-      <c r="D407" s="4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4">
-      <c r="A408" t="s">
-        <v>390</v>
-      </c>
-      <c r="B408" s="3">
-        <v>196</v>
-      </c>
-      <c r="C408" s="3">
-        <v>5.43</v>
-      </c>
-      <c r="D408" s="4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4">
-      <c r="A409" t="s">
-        <v>425</v>
-      </c>
-      <c r="B409" s="3">
-        <v>120</v>
-      </c>
-      <c r="C409" s="3">
-        <v>9.75</v>
-      </c>
-      <c r="D409" s="4" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4">
-      <c r="A410" t="s">
-        <v>426</v>
-      </c>
-      <c r="B410" s="3">
-        <v>94</v>
-      </c>
-      <c r="C410" s="3">
-        <v>6.37</v>
-      </c>
-      <c r="D410" s="4" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4">
-      <c r="A411" t="s">
-        <v>427</v>
-      </c>
-      <c r="B411" s="3">
-        <v>150</v>
-      </c>
-      <c r="C411" s="3">
-        <v>11.59</v>
-      </c>
-      <c r="D411" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4">
-      <c r="A412" t="s">
-        <v>428</v>
-      </c>
-      <c r="B412" s="3">
-        <v>83</v>
-      </c>
-      <c r="C412" s="3">
-        <v>12.09</v>
-      </c>
-      <c r="D412" s="4" t="s">
         <v>392</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1965,7 +1965,7 @@
         <v>407</v>
       </c>
       <c r="B20" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2315,7 +2315,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2804</v>
+        <v>2768</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
@@ -2343,7 +2343,7 @@
         <v>25</v>
       </c>
       <c r="B47" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="3">
         <v>361.92</v>
@@ -2399,7 +2399,7 @@
         <v>29</v>
       </c>
       <c r="B51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" s="3">
         <v>337.5</v>
@@ -2553,7 +2553,7 @@
         <v>40</v>
       </c>
       <c r="B62" s="3">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C62" s="3">
         <v>16.600000000000001</v>
@@ -2567,7 +2567,7 @@
         <v>41</v>
       </c>
       <c r="B63" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C63" s="3">
         <v>60.95</v>
@@ -2581,7 +2581,7 @@
         <v>42</v>
       </c>
       <c r="B64" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C64" s="3">
         <v>76.569999999999993</v>
@@ -2595,7 +2595,7 @@
         <v>43</v>
       </c>
       <c r="B65" s="3">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C65" s="3">
         <v>18.96</v>
@@ -2609,7 +2609,7 @@
         <v>44</v>
       </c>
       <c r="B66" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C66" s="3">
         <v>73.13</v>
@@ -2623,7 +2623,7 @@
         <v>45</v>
       </c>
       <c r="B67" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C67" s="3">
         <v>89.38</v>
@@ -2637,7 +2637,7 @@
         <v>46</v>
       </c>
       <c r="B68" s="3">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C68" s="3">
         <v>18.96</v>
@@ -2651,7 +2651,7 @@
         <v>47</v>
       </c>
       <c r="B69" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="3">
         <v>73.13</v>
@@ -2665,7 +2665,7 @@
         <v>48</v>
       </c>
       <c r="B70" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C70" s="3">
         <v>89.39</v>
@@ -3855,7 +3855,7 @@
         <v>129</v>
       </c>
       <c r="B155" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C155" s="3">
         <v>181.68</v>
@@ -4177,7 +4177,7 @@
         <v>152</v>
       </c>
       <c r="B178" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C178" s="3">
         <v>201.84</v>
@@ -4191,7 +4191,7 @@
         <v>153</v>
       </c>
       <c r="B179" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C179" s="3">
         <v>48.23</v>
@@ -4205,7 +4205,7 @@
         <v>154</v>
       </c>
       <c r="B180" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C180" s="3">
         <v>221.86</v>
@@ -4443,7 +4443,7 @@
         <v>362</v>
       </c>
       <c r="B197" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C197" s="3">
         <v>206.33</v>
@@ -4485,7 +4485,7 @@
         <v>172</v>
       </c>
       <c r="B200" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C200" s="3">
         <v>4900</v>
@@ -4667,7 +4667,7 @@
         <v>184</v>
       </c>
       <c r="B213" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C213" s="3">
         <v>154.62</v>
@@ -5507,7 +5507,7 @@
         <v>242</v>
       </c>
       <c r="B273" s="3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C273" s="3">
         <v>44.93</v>
@@ -5535,7 +5535,7 @@
         <v>244</v>
       </c>
       <c r="B275" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C275" s="3">
         <v>173.09</v>
@@ -6557,7 +6557,7 @@
         <v>315</v>
       </c>
       <c r="B348" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C348" s="3">
         <v>167.33</v>
@@ -6641,7 +6641,7 @@
         <v>321</v>
       </c>
       <c r="B354" s="3">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C354" s="3">
         <v>259.8</v>
@@ -6683,7 +6683,7 @@
         <v>324</v>
       </c>
       <c r="B357" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C357" s="3">
         <v>87.22</v>
@@ -6697,7 +6697,7 @@
         <v>325</v>
       </c>
       <c r="B358" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C358" s="3">
         <v>319.60000000000002</v>
@@ -7257,7 +7257,7 @@
         <v>386</v>
       </c>
       <c r="B398" s="3">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C398" s="3">
         <v>97.5</v>
@@ -7327,7 +7327,7 @@
         <v>425</v>
       </c>
       <c r="B403" s="3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C403" s="3">
         <v>9.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2780,7 +2780,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="3">
-        <v>16.559999999999999</v>
+        <v>18.37</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>380</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1839,7 +1839,7 @@
         <v>423</v>
       </c>
       <c r="B11" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3">
         <v>467.19</v>
@@ -2343,7 +2343,7 @@
         <v>25</v>
       </c>
       <c r="B47" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" s="3">
         <v>361.92</v>
@@ -2427,7 +2427,7 @@
         <v>31</v>
       </c>
       <c r="B53" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C53" s="3">
         <v>298.12</v>
@@ -2455,7 +2455,7 @@
         <v>33</v>
       </c>
       <c r="B55" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3">
         <v>280.12</v>
@@ -2665,7 +2665,7 @@
         <v>48</v>
       </c>
       <c r="B70" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C70" s="3">
         <v>89.39</v>
@@ -2777,7 +2777,7 @@
         <v>55</v>
       </c>
       <c r="B78" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C78" s="3">
         <v>18.37</v>
@@ -2805,7 +2805,7 @@
         <v>57</v>
       </c>
       <c r="B80" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C80" s="3">
         <v>161.01</v>
@@ -3771,7 +3771,7 @@
         <v>123</v>
       </c>
       <c r="B149" s="3">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C149" s="3">
         <v>32.200000000000003</v>
@@ -4191,7 +4191,7 @@
         <v>153</v>
       </c>
       <c r="B179" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C179" s="3">
         <v>48.23</v>
@@ -4205,7 +4205,7 @@
         <v>154</v>
       </c>
       <c r="B180" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C180" s="3">
         <v>221.86</v>
@@ -4443,7 +4443,7 @@
         <v>362</v>
       </c>
       <c r="B197" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197" s="3">
         <v>206.33</v>
@@ -4667,7 +4667,7 @@
         <v>184</v>
       </c>
       <c r="B213" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C213" s="3">
         <v>154.62</v>
@@ -4891,7 +4891,7 @@
         <v>199</v>
       </c>
       <c r="B229" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C229" s="3">
         <v>65.53</v>
@@ -5101,7 +5101,7 @@
         <v>213</v>
       </c>
       <c r="B244" s="3">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C244" s="3">
         <v>36.06</v>
@@ -5255,7 +5255,7 @@
         <v>224</v>
       </c>
       <c r="B255" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C255" s="3">
         <v>251.5</v>
@@ -5451,7 +5451,7 @@
         <v>238</v>
       </c>
       <c r="B269" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C269" s="3">
         <v>295.14999999999998</v>
@@ -5507,7 +5507,7 @@
         <v>242</v>
       </c>
       <c r="B273" s="3">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C273" s="3">
         <v>44.93</v>
@@ -5549,7 +5549,7 @@
         <v>245</v>
       </c>
       <c r="B276" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C276" s="3">
         <v>211.23</v>
@@ -6515,7 +6515,7 @@
         <v>312</v>
       </c>
       <c r="B345" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C345" s="3">
         <v>44.31</v>
@@ -6571,7 +6571,7 @@
         <v>316</v>
       </c>
       <c r="B349" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C349" s="3">
         <v>191</v>
@@ -6599,7 +6599,7 @@
         <v>318</v>
       </c>
       <c r="B351" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C351" s="3">
         <v>62.04</v>
@@ -6627,7 +6627,7 @@
         <v>320</v>
       </c>
       <c r="B353" s="3">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C353" s="3">
         <v>259.81</v>
@@ -6641,7 +6641,7 @@
         <v>321</v>
       </c>
       <c r="B354" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C354" s="3">
         <v>259.8</v>
@@ -7257,7 +7257,7 @@
         <v>386</v>
       </c>
       <c r="B398" s="3">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C398" s="3">
         <v>97.5</v>
@@ -7271,7 +7271,7 @@
         <v>387</v>
       </c>
       <c r="B399" s="3">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C399" s="3">
         <v>24.7</v>
@@ -7285,7 +7285,7 @@
         <v>388</v>
       </c>
       <c r="B400" s="3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C400" s="3">
         <v>35.75</v>
@@ -7327,7 +7327,7 @@
         <v>425</v>
       </c>
       <c r="B403" s="3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="C403" s="3">
         <v>9.75</v>
@@ -7341,7 +7341,7 @@
         <v>426</v>
       </c>
       <c r="B404" s="3">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C404" s="3">
         <v>6.37</v>
@@ -7369,7 +7369,7 @@
         <v>428</v>
       </c>
       <c r="B406" s="3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C406" s="3">
         <v>12.09</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4488,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="C200" s="3">
-        <v>4900</v>
+        <v>5400</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>375</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="431">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1301,6 +1301,12 @@
   </si>
   <si>
     <t>IPC SPRAY INSONORIZANT 650 ML NOXARO</t>
+  </si>
+  <si>
+    <t>CYC HIDROPREMIUM 46 PAIL 10L</t>
+  </si>
+  <si>
+    <t>CYC MAGMA X-100 10W40 DRUM 60L</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2452,13 +2458,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>429</v>
       </c>
       <c r="B55" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C55" s="3">
-        <v>280.12</v>
+        <v>144.34</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>379</v>
@@ -2466,41 +2472,41 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B56" s="3">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="C56" s="3">
-        <v>24.51</v>
+        <v>280.12</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B57" s="3">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C57" s="3">
-        <v>26.21</v>
+        <v>24.51</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C58" s="3">
-        <v>101.08</v>
+        <v>26.21</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>399</v>
@@ -2508,27 +2514,27 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B59" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C59" s="3">
-        <v>29.13</v>
+        <v>101.08</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B60" s="3">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C60" s="3">
-        <v>102.31</v>
+        <v>29.13</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>398</v>
@@ -2536,13 +2542,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C61" s="3">
-        <v>168.07</v>
+        <v>102.31</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>398</v>
@@ -2550,27 +2556,27 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B62" s="3">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="C62" s="3">
-        <v>16.600000000000001</v>
+        <v>168.07</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" s="3">
-        <v>65</v>
+        <v>283</v>
       </c>
       <c r="C63" s="3">
-        <v>60.95</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>397</v>
@@ -2578,13 +2584,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C64" s="3">
-        <v>76.569999999999993</v>
+        <v>60.95</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>397</v>
@@ -2592,13 +2598,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B65" s="3">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="C65" s="3">
-        <v>18.96</v>
+        <v>76.569999999999993</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>397</v>
@@ -2606,13 +2612,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>430</v>
       </c>
       <c r="B66" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C66" s="3">
-        <v>73.13</v>
+        <v>1041.71</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>397</v>
@@ -2620,13 +2626,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B67" s="3">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="C67" s="3">
-        <v>89.38</v>
+        <v>18.96</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>397</v>
@@ -2634,13 +2640,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B68" s="3">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C68" s="3">
-        <v>18.96</v>
+        <v>73.13</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>397</v>
@@ -2648,13 +2654,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B69" s="3">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C69" s="3">
-        <v>73.13</v>
+        <v>89.38</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>397</v>
@@ -2662,13 +2668,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B70" s="3">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C70" s="3">
-        <v>89.39</v>
+        <v>18.96</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>397</v>
@@ -2676,13 +2682,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B71" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="C71" s="3">
-        <v>3173.52</v>
+        <v>73.13</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>397</v>
@@ -2690,38 +2696,38 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B72" s="3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C72" s="3">
-        <v>25.4</v>
+        <v>89.39</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B73" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C73" s="3">
-        <v>40.92</v>
+        <v>3173.52</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B74" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C74" s="3">
         <v>25.4</v>
@@ -2732,13 +2738,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B75" s="3">
         <v>15</v>
       </c>
       <c r="C75" s="3">
-        <v>28.07</v>
+        <v>40.92</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>377</v>
@@ -2746,13 +2752,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>395</v>
+        <v>52</v>
       </c>
       <c r="B76" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C76" s="3">
-        <v>23.33</v>
+        <v>25.4</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>377</v>
@@ -2760,55 +2766,55 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B77" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C77" s="3">
-        <v>34.630000000000003</v>
+        <v>28.07</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>395</v>
       </c>
       <c r="B78" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C78" s="3">
-        <v>18.37</v>
+        <v>23.33</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B79" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C79" s="3">
-        <v>82.88</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B80" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C80" s="3">
-        <v>161.01</v>
+        <v>18.37</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>380</v>
@@ -2816,13 +2822,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B81" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C81" s="3">
-        <v>44.85</v>
+        <v>82.88</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>380</v>
@@ -2830,69 +2836,69 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B82" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C82" s="3">
-        <v>65.83</v>
+        <v>161.01</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B83" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" s="3">
-        <v>46.76</v>
+        <v>44.85</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B84" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C84" s="3">
-        <v>62.11</v>
+        <v>65.83</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B85" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C85" s="3">
-        <v>47.61</v>
+        <v>46.76</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B86" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C86" s="3">
-        <v>63.76</v>
+        <v>62.11</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>378</v>
@@ -2900,13 +2906,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B87" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C87" s="3">
-        <v>1159.2</v>
+        <v>47.61</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>378</v>
@@ -2914,13 +2920,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B88" s="3">
         <v>1</v>
       </c>
       <c r="C88" s="3">
-        <v>255</v>
+        <v>63.76</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>378</v>
@@ -2928,13 +2934,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B89" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C89" s="3">
-        <v>69.55</v>
+        <v>1159.2</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>378</v>
@@ -2942,13 +2948,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B90" s="3">
         <v>1</v>
       </c>
       <c r="C90" s="3">
-        <v>1391.04</v>
+        <v>255</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>378</v>
@@ -2956,13 +2962,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B91" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C91" s="3">
-        <v>87.1</v>
+        <v>69.55</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>378</v>
@@ -2970,13 +2976,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B92" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C92" s="3">
-        <v>40.54</v>
+        <v>1391.04</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>378</v>
@@ -2984,13 +2990,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B93" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C93" s="3">
-        <v>460.01</v>
+        <v>87.1</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>378</v>
@@ -2998,13 +3004,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B94" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C94" s="3">
-        <v>639.4</v>
+        <v>40.54</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>378</v>
@@ -3012,13 +3018,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B95" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C95" s="3">
-        <v>103.89</v>
+        <v>460.01</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>378</v>
@@ -3026,13 +3032,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B96" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C96" s="3">
-        <v>58.48</v>
+        <v>639.4</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>378</v>
@@ -3040,13 +3046,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B97" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C97" s="3">
-        <v>56.93</v>
+        <v>103.89</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>378</v>
@@ -3054,13 +3060,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B98" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C98" s="3">
-        <v>63.76</v>
+        <v>58.48</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>378</v>
@@ -3068,13 +3074,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B99" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C99" s="3">
-        <v>61.92</v>
+        <v>56.93</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>378</v>
@@ -3082,10 +3088,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B100" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C100" s="3">
         <v>63.76</v>
@@ -3096,13 +3102,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B101" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C101" s="3">
-        <v>69.56</v>
+        <v>61.92</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>378</v>
@@ -3110,13 +3116,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B102" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C102" s="3">
-        <v>59.68</v>
+        <v>63.76</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>378</v>
@@ -3124,13 +3130,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B103" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C103" s="3">
-        <v>56.93</v>
+        <v>69.56</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>378</v>
@@ -3138,13 +3144,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B104" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C104" s="3">
-        <v>80.73</v>
+        <v>59.68</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>378</v>
@@ -3152,13 +3158,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B105" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C105" s="3">
-        <v>98.95</v>
+        <v>56.93</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>378</v>
@@ -3166,13 +3172,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B106" s="3">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C106" s="3">
-        <v>93.25</v>
+        <v>80.73</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>378</v>
@@ -3180,13 +3186,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B107" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107" s="3">
-        <v>63.76</v>
+        <v>98.95</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>378</v>
@@ -3194,13 +3200,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B108" s="3">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C108" s="3">
-        <v>63.76</v>
+        <v>93.25</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>378</v>
@@ -3208,13 +3214,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B109" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C109" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>378</v>
@@ -3222,10 +3228,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B110" s="3">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C110" s="3">
         <v>63.76</v>
@@ -3236,13 +3242,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B111" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C111" s="3">
-        <v>69.87</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>378</v>
@@ -3250,10 +3256,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B112" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C112" s="3">
         <v>63.76</v>
@@ -3264,13 +3270,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B113" s="3">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C113" s="3">
-        <v>69.56</v>
+        <v>69.87</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>378</v>
@@ -3278,13 +3284,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B114" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C114" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>378</v>
@@ -3292,13 +3298,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B115" s="3">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C115" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>378</v>
@@ -3306,13 +3312,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B116" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C116" s="3">
-        <v>208.66</v>
+        <v>69.56</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>378</v>
@@ -3320,13 +3326,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B117" s="3">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C117" s="3">
-        <v>88.87</v>
+        <v>52.17</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>378</v>
@@ -3334,13 +3340,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B118" s="3">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C118" s="3">
-        <v>67.27</v>
+        <v>208.66</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>378</v>
@@ -3348,13 +3354,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B119" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C119" s="3">
-        <v>69.55</v>
+        <v>88.87</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>378</v>
@@ -3362,13 +3368,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B120" s="3">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C120" s="3">
-        <v>63.89</v>
+        <v>67.27</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>378</v>
@@ -3376,13 +3382,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B121" s="3">
         <v>9</v>
       </c>
       <c r="C121" s="3">
-        <v>149.91</v>
+        <v>69.55</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>378</v>
@@ -3390,13 +3396,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B122" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C122" s="3">
-        <v>38.57</v>
+        <v>63.89</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>378</v>
@@ -3404,13 +3410,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B123" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C123" s="3">
-        <v>207.31</v>
+        <v>149.91</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>378</v>
@@ -3418,69 +3424,69 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B124" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C124" s="3">
-        <v>65.23</v>
+        <v>38.57</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B125" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C125" s="3">
-        <v>325.87</v>
+        <v>207.31</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C126" s="3">
-        <v>5165.8</v>
+        <v>65.23</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B127" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C127" s="3">
-        <v>511.75</v>
+        <v>325.87</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B128" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C128" s="3">
-        <v>572.70000000000005</v>
+        <v>5165.8</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>378</v>
@@ -3488,27 +3494,27 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B129" s="3">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="C129" s="3">
-        <v>66.98</v>
+        <v>511.75</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B130" s="3">
         <v>4</v>
       </c>
       <c r="C130" s="3">
-        <v>367.42</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>378</v>
@@ -3516,41 +3522,41 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B131" s="3">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="C131" s="3">
-        <v>51.52</v>
+        <v>66.98</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B132" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C132" s="3">
-        <v>23.19</v>
+        <v>367.42</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B133" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C133" s="3">
-        <v>23.19</v>
+        <v>51.52</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>377</v>
@@ -3558,41 +3564,41 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B134" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C134" s="3">
-        <v>69.55</v>
+        <v>23.19</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B135" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C135" s="3">
-        <v>3169.7</v>
+        <v>23.19</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B136" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C136" s="3">
-        <v>81.14</v>
+        <v>69.55</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>378</v>
@@ -3600,13 +3606,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B137" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C137" s="3">
-        <v>81.14</v>
+        <v>3169.7</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>378</v>
@@ -3614,27 +3620,27 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B138" s="3">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C138" s="3">
-        <v>66.98</v>
+        <v>81.14</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B139" s="3">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C139" s="3">
-        <v>60.28</v>
+        <v>81.14</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>378</v>
@@ -3642,27 +3648,27 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B140" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C140" s="3">
-        <v>93.35</v>
+        <v>66.98</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C141" s="3">
-        <v>1217.1600000000001</v>
+        <v>60.28</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>378</v>
@@ -3670,13 +3676,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C142" s="3">
-        <v>3079</v>
+        <v>93.35</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>378</v>
@@ -3684,111 +3690,111 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B143" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C143" s="3">
-        <v>43.7</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B144" s="3">
         <v>1</v>
       </c>
       <c r="C144" s="3">
-        <v>48.95</v>
+        <v>3079</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B145" s="3">
         <v>9</v>
       </c>
       <c r="C145" s="3">
-        <v>72.33</v>
+        <v>43.7</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B146" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C146" s="3">
-        <v>284.19</v>
+        <v>48.95</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B147" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C147" s="3">
-        <v>132.19</v>
+        <v>72.33</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B148" s="3">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="C148" s="3">
-        <v>32.200000000000003</v>
+        <v>284.19</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B149" s="3">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="C149" s="3">
-        <v>32.200000000000003</v>
+        <v>132.19</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B150" s="3">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C150" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>364</v>
@@ -3796,10 +3802,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B151" s="3">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C151" s="3">
         <v>32.200000000000003</v>
@@ -3810,55 +3816,55 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B152" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C152" s="3">
-        <v>115.01</v>
+        <v>37.43</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B153" s="3">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C153" s="3">
-        <v>38.39</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B154" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C154" s="3">
-        <v>151.47999999999999</v>
+        <v>115.01</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B155" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C155" s="3">
-        <v>181.68</v>
+        <v>38.39</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>375</v>
@@ -3866,41 +3872,41 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B156" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C156" s="3">
-        <v>20.059999999999999</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B157" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C157" s="3">
-        <v>12.88</v>
+        <v>181.68</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B158" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C158" s="3">
-        <v>26.73</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>365</v>
@@ -3908,13 +3914,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B159" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C159" s="3">
-        <v>29.95</v>
+        <v>12.88</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>365</v>
@@ -3922,13 +3928,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B160" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C160" s="3">
-        <v>58.68</v>
+        <v>26.73</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>365</v>
@@ -3936,13 +3942,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B161" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C161" s="3">
-        <v>79.98</v>
+        <v>29.95</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>365</v>
@@ -3950,83 +3956,83 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B162" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C162" s="3">
-        <v>38.770000000000003</v>
+        <v>58.68</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B163" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C163" s="3">
-        <v>107.35</v>
+        <v>79.98</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B164" s="3">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C164" s="3">
-        <v>61.83</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B165" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C165" s="3">
-        <v>243.16</v>
+        <v>107.35</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B166" s="3">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C166" s="3">
-        <v>63.78</v>
+        <v>61.83</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B167" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C167" s="3">
-        <v>75.989999999999995</v>
+        <v>243.16</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>375</v>
@@ -4034,27 +4040,27 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B168" s="3">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C168" s="3">
-        <v>297.64999999999998</v>
+        <v>63.78</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B169" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C169" s="3">
-        <v>77.28</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>375</v>
@@ -4062,13 +4068,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B170" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C170" s="3">
-        <v>75.989999999999995</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>375</v>
@@ -4076,13 +4082,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B171" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C171" s="3">
-        <v>342.24</v>
+        <v>77.28</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>375</v>
@@ -4090,41 +4096,41 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B172" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C172" s="3">
-        <v>633.75</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B173" s="3">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C173" s="3">
-        <v>50.51</v>
+        <v>342.24</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B174" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C174" s="3">
-        <v>787.75</v>
+        <v>633.75</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>378</v>
@@ -4132,69 +4138,69 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B175" s="3">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C175" s="3">
-        <v>122.36</v>
+        <v>50.51</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B176" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C176" s="3">
-        <v>35.81</v>
+        <v>787.75</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B177" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C177" s="3">
-        <v>59.25</v>
+        <v>122.36</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B178" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C178" s="3">
-        <v>201.84</v>
+        <v>35.81</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B179" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C179" s="3">
-        <v>48.23</v>
+        <v>59.25</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>375</v>
@@ -4202,13 +4208,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B180" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C180" s="3">
-        <v>221.86</v>
+        <v>201.84</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>375</v>
@@ -4216,13 +4222,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B181" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C181" s="3">
-        <v>74.7</v>
+        <v>48.23</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>375</v>
@@ -4230,13 +4236,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B182" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C182" s="3">
-        <v>296.3</v>
+        <v>221.86</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>375</v>
@@ -4244,13 +4250,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>396</v>
+        <v>155</v>
       </c>
       <c r="B183" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C183" s="3">
-        <v>141.80000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>375</v>
@@ -4258,13 +4264,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B184" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C184" s="3">
-        <v>41.4</v>
+        <v>296.3</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>375</v>
@@ -4272,13 +4278,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>158</v>
+        <v>396</v>
       </c>
       <c r="B185" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C185" s="3">
-        <v>173.3</v>
+        <v>141.80000000000001</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>375</v>
@@ -4286,13 +4292,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B186" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C186" s="3">
-        <v>2189.02</v>
+        <v>41.4</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>375</v>
@@ -4300,13 +4306,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B187" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C187" s="3">
-        <v>453.22</v>
+        <v>173.3</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>375</v>
@@ -4314,13 +4320,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B188" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C188" s="3">
-        <v>48.64</v>
+        <v>2189.02</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>375</v>
@@ -4328,13 +4334,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B189" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C189" s="3">
-        <v>126.63</v>
+        <v>453.22</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>375</v>
@@ -4342,27 +4348,27 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B190" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C190" s="3">
-        <v>69.56</v>
+        <v>48.64</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B191" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C191" s="3">
-        <v>44.51</v>
+        <v>126.63</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>375</v>
@@ -4370,27 +4376,27 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B192" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C192" s="3">
-        <v>145.94</v>
+        <v>69.56</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B193" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C193" s="3">
-        <v>179</v>
+        <v>44.51</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>375</v>
@@ -4398,13 +4404,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C194" s="3">
-        <v>2060</v>
+        <v>145.94</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>375</v>
@@ -4412,13 +4418,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B195" s="3">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C195" s="3">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>375</v>
@@ -4426,13 +4432,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B196" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C196" s="3">
-        <v>183.41</v>
+        <v>2060</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>375</v>
@@ -4440,13 +4446,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>362</v>
+        <v>168</v>
       </c>
       <c r="B197" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C197" s="3">
-        <v>206.33</v>
+        <v>51</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>375</v>
@@ -4454,27 +4460,27 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B198" s="3">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C198" s="3">
-        <v>33.479999999999997</v>
+        <v>183.41</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>171</v>
+        <v>362</v>
       </c>
       <c r="B199" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C199" s="3">
-        <v>46.06</v>
+        <v>206.33</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>375</v>
@@ -4482,27 +4488,27 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B200" s="3">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="C200" s="3">
-        <v>5400</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B201" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C201" s="3">
-        <v>5345.33</v>
+        <v>46.06</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>375</v>
@@ -4510,13 +4516,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B202" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C202" s="3">
-        <v>170.78</v>
+        <v>5400</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>375</v>
@@ -4524,13 +4530,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B203" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C203" s="3">
-        <v>192.51</v>
+        <v>5345.33</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>375</v>
@@ -4538,13 +4544,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B204" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C204" s="3">
-        <v>59.7</v>
+        <v>170.78</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>375</v>
@@ -4552,13 +4558,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B205" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C205" s="3">
-        <v>265.05</v>
+        <v>192.51</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>375</v>
@@ -4566,41 +4572,41 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B206" s="3">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C206" s="3">
-        <v>36.799999999999997</v>
+        <v>59.7</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B207" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C207" s="3">
-        <v>103.04</v>
+        <v>265.05</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B208" s="3">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C208" s="3">
-        <v>36.75</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>366</v>
@@ -4608,69 +4614,69 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B209" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C209" s="3">
-        <v>47.16</v>
+        <v>103.04</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B210" s="3">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C210" s="3">
-        <v>16.809999999999999</v>
+        <v>36.75</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B211" s="3">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C211" s="3">
-        <v>37.299999999999997</v>
+        <v>47.16</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B212" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C212" s="3">
-        <v>126.24</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B213" s="3">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C213" s="3">
-        <v>154.62</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>375</v>
@@ -4678,13 +4684,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B214" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C214" s="3">
-        <v>508.2</v>
+        <v>126.24</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>375</v>
@@ -4692,13 +4698,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B215" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C215" s="3">
-        <v>5069</v>
+        <v>154.62</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>375</v>
@@ -4706,13 +4712,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B216" s="3">
         <v>2</v>
       </c>
       <c r="C216" s="3">
-        <v>466.78</v>
+        <v>508.2</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>375</v>
@@ -4720,41 +4726,41 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B217" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C217" s="3">
-        <v>57.5</v>
+        <v>5069</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B218" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C218" s="3">
-        <v>63.13</v>
+        <v>466.78</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B219" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C219" s="3">
-        <v>20789.41</v>
+        <v>57.5</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>378</v>
@@ -4762,13 +4768,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B220" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C220" s="3">
-        <v>33057.85</v>
+        <v>63.13</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>378</v>
@@ -4776,13 +4782,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B221" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C221" s="3">
-        <v>83.5</v>
+        <v>20789.41</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>378</v>
@@ -4790,41 +4796,41 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B222" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C222" s="3">
-        <v>81.650000000000006</v>
+        <v>33057.85</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B223" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C223" s="3">
-        <v>50.71</v>
+        <v>83.5</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B224" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C224" s="3">
-        <v>51.75</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>375</v>
@@ -4832,13 +4838,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B225" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C225" s="3">
-        <v>36.94</v>
+        <v>50.71</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>375</v>
@@ -4846,13 +4852,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B226" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C226" s="3">
-        <v>36.94</v>
+        <v>51.75</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>375</v>
@@ -4860,41 +4866,41 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B227" s="3">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C227" s="3">
-        <v>67.28</v>
+        <v>36.94</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B228" s="3">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C228" s="3">
-        <v>65.099999999999994</v>
+        <v>36.94</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B229" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C229" s="3">
-        <v>65.53</v>
+        <v>67.28</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>378</v>
@@ -4902,13 +4908,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B230" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C230" s="3">
-        <v>109.08</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>378</v>
@@ -4916,41 +4922,41 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B231" s="3">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="C231" s="3">
-        <v>33.479999999999997</v>
+        <v>65.53</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B232" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C232" s="3">
-        <v>422.09</v>
+        <v>109.08</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B233" s="3">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="C233" s="3">
-        <v>1277.7</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>366</v>
@@ -4958,69 +4964,69 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B234" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C234" s="3">
-        <v>6.44</v>
+        <v>422.09</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B235" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C235" s="3">
-        <v>108.2</v>
+        <v>1277.7</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B236" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C236" s="3">
-        <v>4456.4799999999996</v>
+        <v>6.44</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B237" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C237" s="3">
-        <v>6279</v>
+        <v>108.2</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B238" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C238" s="3">
-        <v>609.5</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>375</v>
@@ -5028,38 +5034,38 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B239" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C239" s="3">
-        <v>32.200000000000003</v>
+        <v>6279</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B240" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C240" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B241" s="3">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C241" s="3">
         <v>32.200000000000003</v>
@@ -5070,10 +5076,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B242" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C242" s="3">
         <v>32.200000000000003</v>
@@ -5084,13 +5090,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B243" s="3">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="C243" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>364</v>
@@ -5098,13 +5104,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B244" s="3">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="C244" s="3">
-        <v>36.06</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>364</v>
@@ -5112,41 +5118,41 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B245" s="3">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C245" s="3">
-        <v>56</v>
+        <v>40.4</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B246" s="3">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C246" s="3">
-        <v>57.63</v>
+        <v>36.06</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B247" s="3">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C247" s="3">
-        <v>60.78</v>
+        <v>56</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>378</v>
@@ -5154,41 +5160,41 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B248" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C248" s="3">
-        <v>42.49</v>
+        <v>57.63</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B249" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C249" s="3">
-        <v>66.3</v>
+        <v>60.78</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B250" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C250" s="3">
-        <v>261.8</v>
+        <v>42.49</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>375</v>
@@ -5196,13 +5202,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B251" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C251" s="3">
-        <v>71.709999999999994</v>
+        <v>66.3</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>375</v>
@@ -5210,27 +5216,27 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B252" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C252" s="3">
-        <v>77.760000000000005</v>
+        <v>261.8</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B253" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C253" s="3">
-        <v>54.7</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>375</v>
@@ -5238,27 +5244,27 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B254" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C254" s="3">
-        <v>67.28</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B255" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C255" s="3">
-        <v>251.5</v>
+        <v>54.7</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>375</v>
@@ -5266,13 +5272,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B256" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C256" s="3">
-        <v>78.87</v>
+        <v>67.28</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>375</v>
@@ -5280,13 +5286,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B257" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C257" s="3">
-        <v>83.84</v>
+        <v>251.5</v>
       </c>
       <c r="D257" s="4" t="s">
         <v>375</v>
@@ -5294,13 +5300,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B258" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C258" s="3">
-        <v>331.2</v>
+        <v>78.87</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>375</v>
@@ -5308,13 +5314,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B259" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C259" s="3">
-        <v>79.75</v>
+        <v>83.84</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>375</v>
@@ -5322,13 +5328,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B260" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C260" s="3">
-        <v>83.84</v>
+        <v>331.2</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>375</v>
@@ -5336,13 +5342,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B261" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C261" s="3">
-        <v>284</v>
+        <v>79.75</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>375</v>
@@ -5350,41 +5356,41 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B262" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C262" s="3">
-        <v>28.15</v>
+        <v>83.84</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B263" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C263" s="3">
-        <v>45.08</v>
+        <v>284</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B264" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C264" s="3">
-        <v>51.52</v>
+        <v>28.15</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>377</v>
@@ -5392,55 +5398,55 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B265" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C265" s="3">
-        <v>40.57</v>
+        <v>45.08</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B266" s="3">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C266" s="3">
-        <v>36.229999999999997</v>
+        <v>51.52</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B267" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C267" s="3">
-        <v>54.12</v>
+        <v>40.57</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B268" s="3">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C268" s="3">
-        <v>69.55</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>375</v>
@@ -5448,97 +5454,97 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B269" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C269" s="3">
-        <v>295.14999999999998</v>
+        <v>54.12</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B270" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C270" s="3">
-        <v>38.56</v>
+        <v>69.55</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B271" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C271" s="3">
-        <v>60.95</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B272" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C272" s="3">
-        <v>78.209999999999994</v>
+        <v>38.56</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B273" s="3">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="C273" s="3">
-        <v>44.93</v>
+        <v>60.95</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B274" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C274" s="3">
-        <v>6578.46</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B275" s="3">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="C275" s="3">
-        <v>173.09</v>
+        <v>44.93</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>375</v>
@@ -5546,13 +5552,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B276" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C276" s="3">
-        <v>211.23</v>
+        <v>6578.46</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>375</v>
@@ -5560,13 +5566,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B277" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C277" s="3">
-        <v>2314.8000000000002</v>
+        <v>173.09</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>375</v>
@@ -5574,13 +5580,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B278" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C278" s="3">
-        <v>791.3</v>
+        <v>211.23</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>375</v>
@@ -5588,41 +5594,41 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B279" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C279" s="3">
-        <v>31.6</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B280" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C280" s="3">
-        <v>77.28</v>
+        <v>791.3</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B281" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C281" s="3">
-        <v>43.8</v>
+        <v>31.6</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>377</v>
@@ -5630,13 +5636,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B282" s="3">
         <v>7</v>
       </c>
       <c r="C282" s="3">
-        <v>21.9</v>
+        <v>77.28</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>377</v>
@@ -5644,13 +5650,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B283" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C283" s="3">
-        <v>798.6</v>
+        <v>43.8</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>377</v>
@@ -5658,13 +5664,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B284" s="3">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C284" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>377</v>
@@ -5672,13 +5678,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B285" s="3">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C285" s="3">
-        <v>8.24</v>
+        <v>798.6</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>377</v>
@@ -5686,13 +5692,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B286" s="3">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="C286" s="3">
-        <v>13.72</v>
+        <v>23.19</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>377</v>
@@ -5700,13 +5706,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B287" s="3">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C287" s="3">
-        <v>31.95</v>
+        <v>8.24</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>377</v>
@@ -5714,13 +5720,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>381</v>
+        <v>255</v>
       </c>
       <c r="B288" s="3">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="C288" s="3">
-        <v>16.2</v>
+        <v>13.72</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>377</v>
@@ -5728,13 +5734,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B289" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C289" s="3">
-        <v>36.869999999999997</v>
+        <v>31.95</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>377</v>
@@ -5742,13 +5748,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="B290" s="3">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="C290" s="3">
-        <v>31.48</v>
+        <v>16.2</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>377</v>
@@ -5756,13 +5762,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B291" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C291" s="3">
-        <v>21.9</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>377</v>
@@ -5770,13 +5776,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B292" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C292" s="3">
-        <v>23.19</v>
+        <v>31.48</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>377</v>
@@ -5784,13 +5790,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B293" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C293" s="3">
-        <v>19.55</v>
+        <v>21.9</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>377</v>
@@ -5798,13 +5804,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B294" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C294" s="3">
-        <v>19.07</v>
+        <v>23.19</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>377</v>
@@ -5812,13 +5818,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B295" s="3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C295" s="3">
-        <v>21.9</v>
+        <v>19.55</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>377</v>
@@ -5826,41 +5832,41 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B296" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C296" s="3">
-        <v>79.349999999999994</v>
+        <v>19.07</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B297" s="3">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C297" s="3">
-        <v>862.7</v>
+        <v>21.9</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B298" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C298" s="3">
-        <v>56.93</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>378</v>
@@ -5868,13 +5874,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B299" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299" s="3">
-        <v>1265</v>
+        <v>862.7</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>378</v>
@@ -5882,41 +5888,41 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B300" s="3">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C300" s="3">
-        <v>76</v>
+        <v>56.93</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B301" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C301" s="3">
-        <v>267.85000000000002</v>
+        <v>1265</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B302" s="3">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C302" s="3">
-        <v>74.7</v>
+        <v>76</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>375</v>
@@ -5924,13 +5930,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B303" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C303" s="3">
-        <v>327.3</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>375</v>
@@ -5938,13 +5944,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B304" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C304" s="3">
-        <v>72.13</v>
+        <v>74.7</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>375</v>
@@ -5952,13 +5958,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B305" s="3">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C305" s="3">
-        <v>302.39999999999998</v>
+        <v>327.3</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>375</v>
@@ -5966,27 +5972,27 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B306" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C306" s="3">
-        <v>36.799999999999997</v>
+        <v>72.13</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B307" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C307" s="3">
-        <v>428.5</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>375</v>
@@ -5994,27 +6000,27 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B308" s="3">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C308" s="3">
-        <v>450.22</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B309" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C309" s="3">
-        <v>465.7</v>
+        <v>428.5</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>375</v>
@@ -6022,13 +6028,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B310" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C310" s="3">
-        <v>38.25</v>
+        <v>450.22</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>375</v>
@@ -6036,13 +6042,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B311" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C311" s="3">
-        <v>87.49</v>
+        <v>465.7</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>375</v>
@@ -6050,13 +6056,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B312" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C312" s="3">
-        <v>63.13</v>
+        <v>38.25</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>375</v>
@@ -6064,41 +6070,41 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B313" s="3">
         <v>2</v>
       </c>
       <c r="C313" s="3">
-        <v>377.78</v>
+        <v>87.49</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B314" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C314" s="3">
-        <v>3333.85</v>
+        <v>63.13</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B315" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C315" s="3">
-        <v>374.67</v>
+        <v>377.78</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>379</v>
@@ -6106,13 +6112,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B316" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316" s="3">
-        <v>120.06</v>
+        <v>3333.85</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>379</v>
@@ -6120,55 +6126,55 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B317" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C317" s="3">
-        <v>54.2</v>
+        <v>374.67</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B318" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C318" s="3">
-        <v>31.5</v>
+        <v>120.06</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B319" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C319" s="3">
-        <v>114.09</v>
+        <v>54.2</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B320" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C320" s="3">
-        <v>139.9</v>
+        <v>31.5</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>375</v>
@@ -6176,13 +6182,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B321" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C321" s="3">
-        <v>35.94</v>
+        <v>114.09</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>375</v>
@@ -6190,13 +6196,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B322" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C322" s="3">
-        <v>140.26</v>
+        <v>139.9</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>375</v>
@@ -6204,69 +6210,69 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B323" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C323" s="3">
-        <v>370.53</v>
+        <v>35.94</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B324" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C324" s="3">
-        <v>30.9</v>
+        <v>140.26</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B325" s="3">
         <v>1</v>
       </c>
       <c r="C325" s="3">
-        <v>4772.5</v>
+        <v>370.53</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B326" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C326" s="3">
-        <v>516.46</v>
+        <v>30.9</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B327" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C327" s="3">
-        <v>185.15</v>
+        <v>4772.5</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>375</v>
@@ -6274,27 +6280,27 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B328" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C328" s="3">
-        <v>11.5</v>
+        <v>516.46</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B329" s="3">
         <v>4</v>
       </c>
       <c r="C329" s="3">
-        <v>724.5</v>
+        <v>185.15</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>375</v>
@@ -6302,13 +6308,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B330" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C330" s="3">
-        <v>450.22</v>
+        <v>11.5</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>378</v>
@@ -6316,41 +6322,41 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B331" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C331" s="3">
-        <v>461.23</v>
+        <v>724.5</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B332" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C332" s="3">
-        <v>518.41999999999996</v>
+        <v>450.22</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B333" s="3">
         <v>1</v>
       </c>
       <c r="C333" s="3">
-        <v>348.08</v>
+        <v>461.23</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>367</v>
@@ -6358,13 +6364,13 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B334" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C334" s="3">
-        <v>33.479999999999997</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>367</v>
@@ -6372,13 +6378,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B335" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C335" s="3">
-        <v>35.79</v>
+        <v>348.08</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>367</v>
@@ -6386,13 +6392,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B336" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C336" s="3">
-        <v>377.7</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>367</v>
@@ -6400,13 +6406,13 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B337" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C337" s="3">
-        <v>33.21</v>
+        <v>35.79</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>367</v>
@@ -6414,13 +6420,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B338" s="3">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C338" s="3">
-        <v>27.16</v>
+        <v>377.7</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>367</v>
@@ -6428,13 +6434,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B339" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C339" s="3">
-        <v>361.41</v>
+        <v>33.21</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>367</v>
@@ -6442,13 +6448,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B340" s="3">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C340" s="3">
-        <v>29.25</v>
+        <v>27.16</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>367</v>
@@ -6456,13 +6462,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B341" s="3">
         <v>1</v>
       </c>
       <c r="C341" s="3">
-        <v>304.54000000000002</v>
+        <v>361.41</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>367</v>
@@ -6470,13 +6476,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B342" s="3">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C342" s="3">
-        <v>34.049999999999997</v>
+        <v>29.25</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>367</v>
@@ -6484,41 +6490,41 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B343" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C343" s="3">
-        <v>57.7</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B344" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C344" s="3">
-        <v>90.9</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B345" s="3">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C345" s="3">
-        <v>44.31</v>
+        <v>57.7</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>375</v>
@@ -6526,27 +6532,27 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B346" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C346" s="3">
-        <v>7173.59</v>
+        <v>90.9</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B347" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C347" s="3">
-        <v>677.79</v>
+        <v>44.31</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>375</v>
@@ -6554,13 +6560,13 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B348" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C348" s="3">
-        <v>167.33</v>
+        <v>7173.59</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>375</v>
@@ -6568,13 +6574,13 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B349" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C349" s="3">
-        <v>191</v>
+        <v>677.79</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>375</v>
@@ -6582,13 +6588,13 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B350" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C350" s="3">
-        <v>2335.67</v>
+        <v>167.33</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>375</v>
@@ -6596,13 +6602,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B351" s="3">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C351" s="3">
-        <v>62.04</v>
+        <v>191</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>375</v>
@@ -6610,13 +6616,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B352" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C352" s="3">
-        <v>8139.6</v>
+        <v>2335.67</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>375</v>
@@ -6624,13 +6630,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B353" s="3">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="C353" s="3">
-        <v>259.81</v>
+        <v>62.04</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>375</v>
@@ -6638,13 +6644,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B354" s="3">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="C354" s="3">
-        <v>259.8</v>
+        <v>8139.6</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>375</v>
@@ -6652,13 +6658,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B355" s="3">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C355" s="3">
-        <v>310.2</v>
+        <v>259.81</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>375</v>
@@ -6666,13 +6672,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B356" s="3">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C356" s="3">
-        <v>36.43</v>
+        <v>259.8</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>375</v>
@@ -6680,13 +6686,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B357" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C357" s="3">
-        <v>87.22</v>
+        <v>310.2</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>375</v>
@@ -6694,13 +6700,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B358" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C358" s="3">
-        <v>319.60000000000002</v>
+        <v>36.43</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>375</v>
@@ -6708,13 +6714,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B359" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C359" s="3">
-        <v>62.6</v>
+        <v>87.22</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>375</v>
@@ -6722,13 +6728,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B360" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C360" s="3">
-        <v>312.8</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>375</v>
@@ -6736,69 +6742,69 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B361" s="3">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C361" s="3">
-        <v>67.28</v>
+        <v>62.6</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B362" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C362" s="3">
-        <v>1138.5</v>
+        <v>312.8</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="B363" s="3">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C363" s="3">
-        <v>58.69</v>
+        <v>67.28</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="B364" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C364" s="3">
-        <v>289.33999999999997</v>
+        <v>1138.5</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B365" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C365" s="3">
-        <v>48.76</v>
+        <v>58.69</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>375</v>
@@ -6806,13 +6812,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B366" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C366" s="3">
-        <v>242.34</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>375</v>
@@ -6820,13 +6826,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B367" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C367" s="3">
-        <v>54.09</v>
+        <v>48.76</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>375</v>
@@ -6834,13 +6840,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B368" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C368" s="3">
-        <v>255.03</v>
+        <v>242.34</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>375</v>
@@ -6848,13 +6854,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B369" s="3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C369" s="3">
-        <v>220.8</v>
+        <v>54.09</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>375</v>
@@ -6862,13 +6868,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B370" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C370" s="3">
-        <v>255.02</v>
+        <v>255.03</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>375</v>
@@ -6876,13 +6882,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B371" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C371" s="3">
-        <v>68.86</v>
+        <v>220.8</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>375</v>
@@ -6890,13 +6896,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B372" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C372" s="3">
-        <v>344.28</v>
+        <v>255.02</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>375</v>
@@ -6904,13 +6910,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B373" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C373" s="3">
-        <v>60.29</v>
+        <v>68.86</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>375</v>
@@ -6918,13 +6924,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B374" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C374" s="3">
-        <v>261.8</v>
+        <v>344.28</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>375</v>
@@ -6932,69 +6938,69 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>393</v>
+        <v>338</v>
       </c>
       <c r="B375" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C375" s="3">
-        <v>30.58</v>
+        <v>60.29</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B376" s="3">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C376" s="3">
-        <v>16.95</v>
+        <v>261.8</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="B377" s="3">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C377" s="3">
-        <v>24.95</v>
+        <v>30.58</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B378" s="3">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C378" s="3">
-        <v>641.49</v>
+        <v>16.95</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B379" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C379" s="3">
-        <v>39.57</v>
+        <v>24.95</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>378</v>
@@ -7002,13 +7008,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B380" s="3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C380" s="3">
-        <v>51.83</v>
+        <v>641.49</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>378</v>
@@ -7016,41 +7022,41 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B381" s="3">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C381" s="3">
-        <v>33.840000000000003</v>
+        <v>39.57</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B382" s="3">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C382" s="3">
-        <v>150.15</v>
+        <v>51.83</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B383" s="3">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C383" s="3">
-        <v>144.5</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>375</v>
@@ -7058,13 +7064,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B384" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C384" s="3">
-        <v>100.93</v>
+        <v>150.15</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>375</v>
@@ -7072,13 +7078,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B385" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C385" s="3">
-        <v>124.5</v>
+        <v>144.5</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>375</v>
@@ -7086,13 +7092,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B386" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C386" s="3">
-        <v>27.21</v>
+        <v>100.93</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>375</v>
@@ -7100,27 +7106,27 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B387" s="3">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C387" s="3">
-        <v>24.79</v>
+        <v>124.5</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B388" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C388" s="3">
-        <v>37.1</v>
+        <v>27.21</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>375</v>
@@ -7128,41 +7134,41 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B389" s="3">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="C389" s="3">
-        <v>178.04</v>
+        <v>24.79</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B390" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="C390" s="3">
-        <v>23.88</v>
+        <v>37.1</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B391" s="3">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C391" s="3">
-        <v>20.68</v>
+        <v>178.04</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>375</v>
@@ -7170,27 +7176,27 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="B392" s="3">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C392" s="3">
-        <v>97.54</v>
+        <v>23.88</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="B393" s="3">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="C393" s="3">
-        <v>304.02999999999997</v>
+        <v>20.68</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>375</v>
@@ -7198,97 +7204,97 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="B394" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C394" s="3">
-        <v>1934.56</v>
+        <v>97.54</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="B395" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C395" s="3">
-        <v>230.99</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B396" s="3">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="C396" s="3">
-        <v>33.39</v>
+        <v>1934.56</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B397" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C397" s="3">
-        <v>20.66</v>
+        <v>230.99</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="B398" s="3">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="C398" s="3">
-        <v>97.5</v>
+        <v>33.39</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B399" s="3">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="C399" s="3">
-        <v>24.7</v>
+        <v>20.66</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B400" s="3">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C400" s="3">
-        <v>35.75</v>
+        <v>97.5</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>385</v>
@@ -7296,13 +7302,13 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B401" s="3">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="C401" s="3">
-        <v>9.1</v>
+        <v>24.7</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>385</v>
@@ -7310,13 +7316,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B402" s="3">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C402" s="3">
-        <v>5.43</v>
+        <v>35.75</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>385</v>
@@ -7324,57 +7330,85 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="B403" s="3">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="C403" s="3">
-        <v>9.75</v>
+        <v>9.1</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="B404" s="3">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="C404" s="3">
-        <v>6.37</v>
+        <v>5.43</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B405" s="3">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="C405" s="3">
-        <v>11.59</v>
+        <v>9.75</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
+        <v>426</v>
+      </c>
+      <c r="B406" s="3">
+        <v>82</v>
+      </c>
+      <c r="C406" s="3">
+        <v>6.37</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" t="s">
+        <v>427</v>
+      </c>
+      <c r="B407" s="3">
+        <v>150</v>
+      </c>
+      <c r="C407" s="3">
+        <v>11.59</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" t="s">
         <v>428</v>
       </c>
-      <c r="B406" s="3">
+      <c r="B408" s="3">
         <v>81</v>
       </c>
-      <c r="C406" s="3">
+      <c r="C408" s="3">
         <v>12.09</v>
       </c>
-      <c r="D406" s="4" t="s">
+      <c r="D408" s="4" t="s">
         <v>392</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1313,7 +1313,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1329,6 +1329,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1338,7 +1344,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1374,11 +1380,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1397,6 +1431,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3667,8 +3707,8 @@
       <c r="B141" s="3">
         <v>31</v>
       </c>
-      <c r="C141" s="3">
-        <v>60.28</v>
+      <c r="C141" s="8">
+        <v>74.989999999999995</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>378</v>
@@ -4227,8 +4267,8 @@
       <c r="B181" s="3">
         <v>8</v>
       </c>
-      <c r="C181" s="3">
-        <v>48.23</v>
+      <c r="C181" s="7">
+        <v>57.59</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>375</v>
@@ -4479,8 +4519,8 @@
       <c r="B199" s="3">
         <v>3</v>
       </c>
-      <c r="C199" s="3">
-        <v>206.33</v>
+      <c r="C199" s="8">
+        <v>248.99</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>375</v>
@@ -5207,8 +5247,8 @@
       <c r="B251" s="3">
         <v>6</v>
       </c>
-      <c r="C251" s="3">
-        <v>66.3</v>
+      <c r="C251" s="8">
+        <v>84</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>375</v>
@@ -5219,10 +5259,10 @@
         <v>219</v>
       </c>
       <c r="B252" s="3">
-        <v>0</v>
-      </c>
-      <c r="C252" s="3">
-        <v>261.8</v>
+        <v>4</v>
+      </c>
+      <c r="C252" s="8">
+        <v>301.99</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>375</v>
@@ -5586,7 +5626,7 @@
         <v>3</v>
       </c>
       <c r="C278" s="3">
-        <v>211.23</v>
+        <v>215.08</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>375</v>
@@ -6608,7 +6648,7 @@
         <v>7</v>
       </c>
       <c r="C351" s="3">
-        <v>191</v>
+        <v>205.53</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>375</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="431">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1732,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D407"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2613,7 +2613,7 @@
         <v>40</v>
       </c>
       <c r="B63" s="3">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3">
         <v>16.600000000000001</v>
@@ -2627,10 +2627,10 @@
         <v>41</v>
       </c>
       <c r="B64" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C64" s="3">
-        <v>60.95</v>
+        <v>70.47</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>397</v>
@@ -2641,10 +2641,10 @@
         <v>42</v>
       </c>
       <c r="B65" s="3">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C65" s="3">
-        <v>76.569999999999993</v>
+        <v>86.8</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>397</v>
@@ -2879,7 +2879,7 @@
         <v>57</v>
       </c>
       <c r="B82" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C82" s="3">
         <v>161.01</v>
@@ -3243,7 +3243,7 @@
         <v>81</v>
       </c>
       <c r="B108" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C108" s="3">
         <v>93.25</v>
@@ -3705,7 +3705,7 @@
         <v>114</v>
       </c>
       <c r="B141" s="3">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C141" s="8">
         <v>74.989999999999995</v>
@@ -3719,7 +3719,7 @@
         <v>115</v>
       </c>
       <c r="B142" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C142" s="3">
         <v>93.35</v>
@@ -4223,7 +4223,7 @@
         <v>150</v>
       </c>
       <c r="B178" s="3">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C178" s="3">
         <v>35.81</v>
@@ -4265,7 +4265,7 @@
         <v>153</v>
       </c>
       <c r="B181" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C181" s="7">
         <v>57.59</v>
@@ -4279,7 +4279,7 @@
         <v>154</v>
       </c>
       <c r="B182" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C182" s="3">
         <v>221.86</v>
@@ -4363,7 +4363,7 @@
         <v>159</v>
       </c>
       <c r="B188" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C188" s="3">
         <v>2189.02</v>
@@ -4503,7 +4503,7 @@
         <v>169</v>
       </c>
       <c r="B198" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C198" s="3">
         <v>183.41</v>
@@ -4517,7 +4517,7 @@
         <v>362</v>
       </c>
       <c r="B199" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C199" s="8">
         <v>248.99</v>
@@ -4531,7 +4531,7 @@
         <v>170</v>
       </c>
       <c r="B200" s="3">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C200" s="3">
         <v>33.479999999999997</v>
@@ -4559,7 +4559,7 @@
         <v>172</v>
       </c>
       <c r="B202" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C202" s="3">
         <v>5400</v>
@@ -4570,13 +4570,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B203" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C203" s="3">
-        <v>5345.33</v>
+        <v>170.78</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>375</v>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B204" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C204" s="3">
-        <v>170.78</v>
+        <v>192.51</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>375</v>
@@ -4598,13 +4598,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B205" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C205" s="3">
-        <v>192.51</v>
+        <v>59.7</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>375</v>
@@ -4612,13 +4612,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B206" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C206" s="3">
-        <v>59.7</v>
+        <v>265.05</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>375</v>
@@ -4626,97 +4626,97 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B207" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C207" s="3">
-        <v>265.05</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B208" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C208" s="3">
-        <v>36.799999999999997</v>
+        <v>103.04</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B209" s="3">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C209" s="3">
-        <v>103.04</v>
+        <v>36.75</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B210" s="3">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C210" s="3">
-        <v>36.75</v>
+        <v>47.16</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B211" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C211" s="3">
-        <v>47.16</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B212" s="3">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C212" s="3">
-        <v>16.809999999999999</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B213" s="3">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C213" s="3">
-        <v>37.299999999999997</v>
+        <v>126.24</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>375</v>
@@ -4724,13 +4724,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B214" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C214" s="3">
-        <v>126.24</v>
+        <v>154.62</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>375</v>
@@ -4738,13 +4738,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B215" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C215" s="3">
-        <v>154.62</v>
+        <v>508.2</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>375</v>
@@ -4752,13 +4752,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B216" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C216" s="3">
-        <v>508.2</v>
+        <v>5069</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>375</v>
@@ -4766,13 +4766,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B217" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C217" s="3">
-        <v>5069</v>
+        <v>466.78</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>375</v>
@@ -4780,27 +4780,27 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B218" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C218" s="3">
-        <v>466.78</v>
+        <v>57.5</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B219" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C219" s="3">
-        <v>57.5</v>
+        <v>63.13</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>378</v>
@@ -4808,13 +4808,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B220" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C220" s="3">
-        <v>63.13</v>
+        <v>20789.41</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>378</v>
@@ -4828,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="C221" s="3">
-        <v>20789.41</v>
+        <v>33057.85</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>378</v>
@@ -4836,13 +4836,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B222" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C222" s="3">
-        <v>33057.85</v>
+        <v>83.5</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>378</v>
@@ -4850,27 +4850,27 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B223" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C223" s="3">
-        <v>83.5</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B224" s="3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C224" s="3">
-        <v>81.650000000000006</v>
+        <v>50.71</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>375</v>
@@ -4878,13 +4878,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B225" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C225" s="3">
-        <v>50.71</v>
+        <v>51.75</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>375</v>
@@ -4892,13 +4892,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B226" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C226" s="3">
-        <v>51.75</v>
+        <v>36.94</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>375</v>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B227" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C227" s="3">
         <v>36.94</v>
@@ -4920,27 +4920,27 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B228" s="3">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C228" s="3">
-        <v>36.94</v>
+        <v>67.28</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B229" s="3">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C229" s="3">
-        <v>67.28</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>378</v>
@@ -4948,13 +4948,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B230" s="3">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C230" s="3">
-        <v>65.099999999999994</v>
+        <v>65.53</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>378</v>
@@ -4962,13 +4962,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B231" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C231" s="3">
-        <v>65.53</v>
+        <v>109.08</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>378</v>
@@ -4976,27 +4976,27 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B232" s="3">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C232" s="3">
-        <v>109.08</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B233" s="3">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="C233" s="3">
-        <v>33.479999999999997</v>
+        <v>422.09</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>366</v>
@@ -5004,13 +5004,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B234" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C234" s="3">
-        <v>422.09</v>
+        <v>1277.7</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>366</v>
@@ -5018,27 +5018,27 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B235" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C235" s="3">
-        <v>1277.7</v>
+        <v>6.44</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B236" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C236" s="3">
-        <v>6.44</v>
+        <v>108.2</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>377</v>
@@ -5046,16 +5046,16 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B237" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C237" s="3">
-        <v>108.2</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5066,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="C238" s="3">
-        <v>4456.4799999999996</v>
+        <v>6279</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>375</v>
@@ -5074,13 +5074,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B239" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C239" s="3">
-        <v>6279</v>
+        <v>609.5</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>375</v>
@@ -5088,24 +5088,24 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B240" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C240" s="3">
-        <v>609.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B241" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C241" s="3">
         <v>32.200000000000003</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B242" s="3">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C242" s="3">
         <v>32.200000000000003</v>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B243" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C243" s="3">
         <v>32.200000000000003</v>
@@ -5144,13 +5144,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B244" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C244" s="3">
-        <v>32.200000000000003</v>
+        <v>40.4</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>364</v>
@@ -5158,13 +5158,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B245" s="3">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="C245" s="3">
-        <v>40.4</v>
+        <v>36.06</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>364</v>
@@ -5172,27 +5172,27 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B246" s="3">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="C246" s="3">
-        <v>36.06</v>
+        <v>56</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B247" s="3">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C247" s="3">
-        <v>56</v>
+        <v>57.63</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>378</v>
@@ -5200,13 +5200,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B248" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C248" s="3">
-        <v>57.63</v>
+        <v>60.78</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>378</v>
@@ -5214,27 +5214,27 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B249" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C249" s="3">
-        <v>60.78</v>
+        <v>42.49</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B250" s="3">
-        <v>9</v>
-      </c>
-      <c r="C250" s="3">
-        <v>42.49</v>
+        <v>18</v>
+      </c>
+      <c r="C250" s="8">
+        <v>84</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>375</v>
@@ -5242,13 +5242,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B251" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C251" s="8">
-        <v>84</v>
+        <v>301.99</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>375</v>
@@ -5256,13 +5256,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B252" s="3">
-        <v>4</v>
-      </c>
-      <c r="C252" s="8">
-        <v>301.99</v>
+        <v>14</v>
+      </c>
+      <c r="C252" s="3">
+        <v>71.709999999999994</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>375</v>
@@ -5270,41 +5270,41 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B253" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C253" s="3">
-        <v>71.709999999999994</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B254" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C254" s="3">
-        <v>77.760000000000005</v>
+        <v>54.7</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B255" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C255" s="3">
-        <v>54.7</v>
+        <v>67.28</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>375</v>
@@ -5312,13 +5312,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B256" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C256" s="3">
-        <v>67.28</v>
+        <v>251.5</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>375</v>
@@ -5326,13 +5326,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B257" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C257" s="3">
-        <v>251.5</v>
+        <v>78.87</v>
       </c>
       <c r="D257" s="4" t="s">
         <v>375</v>
@@ -5340,13 +5340,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B258" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C258" s="3">
-        <v>78.87</v>
+        <v>83.84</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>375</v>
@@ -5354,13 +5354,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B259" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C259" s="3">
-        <v>83.84</v>
+        <v>331.2</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>375</v>
@@ -5368,13 +5368,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B260" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C260" s="3">
-        <v>331.2</v>
+        <v>79.75</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>375</v>
@@ -5382,13 +5382,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B261" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C261" s="3">
-        <v>79.75</v>
+        <v>83.84</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>375</v>
@@ -5396,13 +5396,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B262" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C262" s="3">
-        <v>83.84</v>
+        <v>284</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>375</v>
@@ -5410,27 +5410,27 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B263" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C263" s="3">
-        <v>284</v>
+        <v>28.15</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B264" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C264" s="3">
-        <v>28.15</v>
+        <v>45.08</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>377</v>
@@ -5438,13 +5438,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B265" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C265" s="3">
-        <v>45.08</v>
+        <v>51.52</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>377</v>
@@ -5452,27 +5452,27 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B266" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C266" s="3">
-        <v>51.52</v>
+        <v>40.57</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B267" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C267" s="3">
-        <v>40.57</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>375</v>
@@ -5480,41 +5480,41 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B268" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C268" s="3">
-        <v>36.229999999999997</v>
+        <v>54.12</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B269" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C269" s="3">
-        <v>54.12</v>
+        <v>69.55</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B270" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C270" s="3">
-        <v>69.55</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>375</v>
@@ -5522,41 +5522,41 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B271" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C271" s="3">
-        <v>295.14999999999998</v>
+        <v>38.56</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B272" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C272" s="3">
-        <v>38.56</v>
+        <v>60.95</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B273" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C273" s="3">
-        <v>60.95</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>378</v>
@@ -5564,27 +5564,27 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B274" s="3">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="C274" s="3">
-        <v>78.209999999999994</v>
+        <v>44.93</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B275" s="3">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="C275" s="3">
-        <v>44.93</v>
+        <v>6578.46</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>375</v>
@@ -5592,13 +5592,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B276" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C276" s="3">
-        <v>6578.46</v>
+        <v>173.09</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>375</v>
@@ -5606,13 +5606,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B277" s="3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C277" s="3">
-        <v>173.09</v>
+        <v>215.08</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>375</v>
@@ -5620,13 +5620,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B278" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C278" s="3">
-        <v>215.08</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>375</v>
@@ -5634,13 +5634,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B279" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C279" s="3">
-        <v>2314.8000000000002</v>
+        <v>791.3</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>375</v>
@@ -5648,27 +5648,27 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B280" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C280" s="3">
-        <v>791.3</v>
+        <v>31.6</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B281" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C281" s="3">
-        <v>31.6</v>
+        <v>77.28</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>377</v>
@@ -5676,13 +5676,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B282" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C282" s="3">
-        <v>77.28</v>
+        <v>43.8</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>377</v>
@@ -5690,13 +5690,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B283" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C283" s="3">
-        <v>43.8</v>
+        <v>21.9</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>377</v>
@@ -5704,13 +5704,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B284" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C284" s="3">
-        <v>21.9</v>
+        <v>798.6</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>377</v>
@@ -5718,13 +5718,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B285" s="3">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C285" s="3">
-        <v>798.6</v>
+        <v>23.19</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>377</v>
@@ -5732,13 +5732,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B286" s="3">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="C286" s="3">
-        <v>23.19</v>
+        <v>8.24</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>377</v>
@@ -5746,13 +5746,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B287" s="3">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C287" s="3">
-        <v>8.24</v>
+        <v>13.72</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>377</v>
@@ -5760,13 +5760,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B288" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C288" s="3">
-        <v>13.72</v>
+        <v>31.95</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>377</v>
@@ -5774,13 +5774,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="B289" s="3">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="C289" s="3">
-        <v>31.95</v>
+        <v>16.2</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>377</v>
@@ -5788,13 +5788,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>381</v>
+        <v>257</v>
       </c>
       <c r="B290" s="3">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="C290" s="3">
-        <v>16.2</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>377</v>
@@ -5802,13 +5802,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B291" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C291" s="3">
-        <v>36.869999999999997</v>
+        <v>31.48</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>377</v>
@@ -5816,13 +5816,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B292" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C292" s="3">
-        <v>31.48</v>
+        <v>21.9</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>377</v>
@@ -5830,13 +5830,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B293" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C293" s="3">
-        <v>21.9</v>
+        <v>23.19</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>377</v>
@@ -5844,13 +5844,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B294" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C294" s="3">
-        <v>23.19</v>
+        <v>19.55</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>377</v>
@@ -5858,13 +5858,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B295" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C295" s="3">
-        <v>19.55</v>
+        <v>19.07</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>377</v>
@@ -5872,13 +5872,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B296" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C296" s="3">
-        <v>19.07</v>
+        <v>21.9</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>377</v>
@@ -5886,27 +5886,27 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B297" s="3">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C297" s="3">
-        <v>21.9</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B298" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C298" s="3">
-        <v>79.349999999999994</v>
+        <v>862.7</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>378</v>
@@ -5914,13 +5914,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B299" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C299" s="3">
-        <v>862.7</v>
+        <v>56.93</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>378</v>
@@ -5928,13 +5928,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B300" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C300" s="3">
-        <v>56.93</v>
+        <v>1265</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>378</v>
@@ -5942,27 +5942,27 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B301" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C301" s="3">
-        <v>1265</v>
+        <v>76</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B302" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C302" s="3">
-        <v>76</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>375</v>
@@ -5970,13 +5970,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B303" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C303" s="3">
-        <v>267.85000000000002</v>
+        <v>74.7</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>375</v>
@@ -5984,13 +5984,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B304" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C304" s="3">
-        <v>74.7</v>
+        <v>327.3</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>375</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B305" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C305" s="3">
-        <v>327.3</v>
+        <v>72.13</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>375</v>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B306" s="3">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C306" s="3">
-        <v>72.13</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>375</v>
@@ -6026,41 +6026,41 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B307" s="3">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C307" s="3">
-        <v>302.39999999999998</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B308" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C308" s="3">
-        <v>36.799999999999997</v>
+        <v>428.5</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B309" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C309" s="3">
-        <v>428.5</v>
+        <v>450.22</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>375</v>
@@ -6068,13 +6068,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B310" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C310" s="3">
-        <v>450.22</v>
+        <v>465.7</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>375</v>
@@ -6082,13 +6082,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B311" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C311" s="3">
-        <v>465.7</v>
+        <v>38.25</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>375</v>
@@ -6096,13 +6096,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B312" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C312" s="3">
-        <v>38.25</v>
+        <v>87.49</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>375</v>
@@ -6110,13 +6110,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B313" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C313" s="3">
-        <v>87.49</v>
+        <v>63.13</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>375</v>
@@ -6124,27 +6124,27 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B314" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C314" s="3">
-        <v>63.13</v>
+        <v>377.78</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B315" s="3">
         <v>2</v>
       </c>
       <c r="C315" s="3">
-        <v>377.78</v>
+        <v>3333.85</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>379</v>
@@ -6152,13 +6152,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B316" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C316" s="3">
-        <v>3333.85</v>
+        <v>374.67</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>379</v>
@@ -6166,13 +6166,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B317" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C317" s="3">
-        <v>374.67</v>
+        <v>120.06</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>379</v>
@@ -6180,41 +6180,41 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B318" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C318" s="3">
-        <v>120.06</v>
+        <v>54.2</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B319" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C319" s="3">
-        <v>54.2</v>
+        <v>31.5</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B320" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C320" s="3">
-        <v>31.5</v>
+        <v>114.09</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>375</v>
@@ -6222,13 +6222,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B321" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C321" s="3">
-        <v>114.09</v>
+        <v>139.9</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>375</v>
@@ -6236,13 +6236,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B322" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C322" s="3">
-        <v>139.9</v>
+        <v>35.94</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>375</v>
@@ -6250,13 +6250,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B323" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C323" s="3">
-        <v>35.94</v>
+        <v>140.26</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>375</v>
@@ -6264,55 +6264,55 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B324" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C324" s="3">
-        <v>140.26</v>
+        <v>370.53</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B325" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C325" s="3">
-        <v>370.53</v>
+        <v>30.9</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B326" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C326" s="3">
-        <v>30.9</v>
+        <v>4772.5</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B327" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C327" s="3">
-        <v>4772.5</v>
+        <v>516.46</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>375</v>
@@ -6320,13 +6320,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B328" s="3">
         <v>4</v>
       </c>
       <c r="C328" s="3">
-        <v>516.46</v>
+        <v>185.15</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>375</v>
@@ -6334,58 +6334,58 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B329" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C329" s="3">
-        <v>185.15</v>
+        <v>11.5</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B330" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C330" s="3">
-        <v>11.5</v>
+        <v>724.5</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B331" s="3">
         <v>4</v>
       </c>
       <c r="C331" s="3">
-        <v>724.5</v>
+        <v>450.22</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B332" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C332" s="3">
-        <v>450.22</v>
+        <v>461.23</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6396,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="C333" s="3">
-        <v>461.23</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>367</v>
@@ -6404,13 +6404,13 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B334" s="3">
         <v>1</v>
       </c>
       <c r="C334" s="3">
-        <v>518.41999999999996</v>
+        <v>348.08</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>367</v>
@@ -6418,13 +6418,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B335" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C335" s="3">
-        <v>348.08</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>367</v>
@@ -6432,13 +6432,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B336" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C336" s="3">
-        <v>33.479999999999997</v>
+        <v>35.79</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>367</v>
@@ -6446,13 +6446,13 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B337" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C337" s="3">
-        <v>35.79</v>
+        <v>377.7</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>367</v>
@@ -6460,13 +6460,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B338" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C338" s="3">
-        <v>377.7</v>
+        <v>33.21</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>367</v>
@@ -6474,13 +6474,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B339" s="3">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C339" s="3">
-        <v>33.21</v>
+        <v>27.16</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>367</v>
@@ -6488,13 +6488,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B340" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C340" s="3">
-        <v>27.16</v>
+        <v>361.41</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>367</v>
@@ -6502,13 +6502,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B341" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C341" s="3">
-        <v>361.41</v>
+        <v>29.25</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>367</v>
@@ -6516,13 +6516,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B342" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C342" s="3">
-        <v>29.25</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>367</v>
@@ -6530,13 +6530,13 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B343" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C343" s="3">
-        <v>304.54000000000002</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>367</v>
@@ -6544,55 +6544,55 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B344" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C344" s="3">
-        <v>34.049999999999997</v>
+        <v>57.7</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B345" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C345" s="3">
-        <v>57.7</v>
+        <v>90.9</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B346" s="3">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C346" s="3">
-        <v>90.9</v>
+        <v>44.31</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B347" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C347" s="3">
-        <v>44.31</v>
+        <v>7173.59</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>375</v>
@@ -6600,13 +6600,13 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B348" s="3">
         <v>1</v>
       </c>
       <c r="C348" s="3">
-        <v>7173.59</v>
+        <v>677.79</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>375</v>
@@ -6614,13 +6614,13 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B349" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C349" s="3">
-        <v>677.79</v>
+        <v>167.33</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>375</v>
@@ -6628,13 +6628,13 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B350" s="3">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C350" s="3">
-        <v>167.33</v>
+        <v>205.53</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>375</v>
@@ -6642,13 +6642,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B351" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C351" s="3">
-        <v>205.53</v>
+        <v>2335.67</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>375</v>
@@ -6656,13 +6656,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B352" s="3">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C352" s="3">
-        <v>2335.67</v>
+        <v>62.04</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>375</v>
@@ -6670,13 +6670,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B353" s="3">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C353" s="3">
-        <v>62.04</v>
+        <v>8139.6</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>375</v>
@@ -6684,13 +6684,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B354" s="3">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="C354" s="3">
-        <v>8139.6</v>
+        <v>259.81</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>375</v>
@@ -6698,13 +6698,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B355" s="3">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="C355" s="3">
-        <v>259.81</v>
+        <v>259.8</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>375</v>
@@ -6712,13 +6712,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B356" s="3">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C356" s="3">
-        <v>259.8</v>
+        <v>310.2</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>375</v>
@@ -6726,13 +6726,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B357" s="3">
         <v>1</v>
       </c>
       <c r="C357" s="3">
-        <v>310.2</v>
+        <v>36.43</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>375</v>
@@ -6740,13 +6740,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B358" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C358" s="3">
-        <v>36.43</v>
+        <v>87.22</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>375</v>
@@ -6754,13 +6754,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B359" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C359" s="3">
-        <v>87.22</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>375</v>
@@ -6768,13 +6768,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B360" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C360" s="3">
-        <v>319.60000000000002</v>
+        <v>62.6</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>375</v>
@@ -6782,13 +6782,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B361" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C361" s="3">
-        <v>62.6</v>
+        <v>312.8</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>375</v>
@@ -6796,27 +6796,27 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B362" s="3">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="C362" s="3">
-        <v>312.8</v>
+        <v>67.28</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B363" s="3">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="C363" s="3">
-        <v>67.28</v>
+        <v>1138.5</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>378</v>
@@ -6824,27 +6824,27 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="B364" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C364" s="3">
-        <v>1138.5</v>
+        <v>58.69</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B365" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C365" s="3">
-        <v>58.69</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>375</v>
@@ -6852,13 +6852,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="B366" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C366" s="3">
-        <v>289.33999999999997</v>
+        <v>48.76</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>375</v>
@@ -6866,13 +6866,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B367" s="3">
         <v>2</v>
       </c>
       <c r="C367" s="3">
-        <v>48.76</v>
+        <v>242.34</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>375</v>
@@ -6880,13 +6880,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B368" s="3">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C368" s="3">
-        <v>242.34</v>
+        <v>54.09</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>375</v>
@@ -6894,13 +6894,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B369" s="3">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C369" s="3">
-        <v>54.09</v>
+        <v>255.03</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>375</v>
@@ -6908,13 +6908,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B370" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C370" s="3">
-        <v>255.03</v>
+        <v>220.8</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>375</v>
@@ -6922,13 +6922,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B371" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C371" s="3">
-        <v>220.8</v>
+        <v>255.02</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>375</v>
@@ -6936,13 +6936,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B372" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C372" s="3">
-        <v>255.02</v>
+        <v>68.86</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>375</v>
@@ -6950,13 +6950,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B373" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C373" s="3">
-        <v>68.86</v>
+        <v>344.28</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>375</v>
@@ -6964,13 +6964,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B374" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C374" s="3">
-        <v>344.28</v>
+        <v>60.29</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>375</v>
@@ -6978,13 +6978,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B375" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C375" s="3">
-        <v>60.29</v>
+        <v>261.8</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>375</v>
@@ -6992,55 +6992,55 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="B376" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C376" s="3">
-        <v>261.8</v>
+        <v>30.58</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="B377" s="3">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C377" s="3">
-        <v>30.58</v>
+        <v>16.95</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B378" s="3">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C378" s="3">
-        <v>16.95</v>
+        <v>24.95</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B379" s="3">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C379" s="3">
-        <v>24.95</v>
+        <v>641.49</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>378</v>
@@ -7048,13 +7048,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B380" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C380" s="3">
-        <v>641.49</v>
+        <v>39.57</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>378</v>
@@ -7062,13 +7062,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B381" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C381" s="3">
-        <v>39.57</v>
+        <v>51.83</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>378</v>
@@ -7076,27 +7076,27 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B382" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C382" s="3">
-        <v>51.83</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B383" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C383" s="3">
-        <v>33.840000000000003</v>
+        <v>150.15</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>375</v>
@@ -7104,13 +7104,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B384" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C384" s="3">
-        <v>150.15</v>
+        <v>144.5</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>375</v>
@@ -7118,13 +7118,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B385" s="3">
         <v>25</v>
       </c>
       <c r="C385" s="3">
-        <v>144.5</v>
+        <v>100.93</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>375</v>
@@ -7132,13 +7132,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B386" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C386" s="3">
-        <v>100.93</v>
+        <v>124.5</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>375</v>
@@ -7146,13 +7146,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B387" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C387" s="3">
-        <v>124.5</v>
+        <v>27.21</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>375</v>
@@ -7160,41 +7160,41 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B388" s="3">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C388" s="3">
-        <v>27.21</v>
+        <v>24.79</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B389" s="3">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="C389" s="3">
-        <v>24.79</v>
+        <v>37.1</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B390" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C390" s="3">
-        <v>37.1</v>
+        <v>178.04</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>375</v>
@@ -7202,41 +7202,41 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B391" s="3">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C391" s="3">
-        <v>178.04</v>
+        <v>23.88</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B392" s="3">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C392" s="3">
-        <v>23.88</v>
+        <v>20.68</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="B393" s="3">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="C393" s="3">
-        <v>20.68</v>
+        <v>97.54</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>375</v>
@@ -7244,13 +7244,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B394" s="3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C394" s="3">
-        <v>97.54</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>375</v>
@@ -7258,27 +7258,27 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="B395" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C395" s="3">
-        <v>304.02999999999997</v>
+        <v>1934.56</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B396" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C396" s="3">
-        <v>1934.56</v>
+        <v>230.99</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>379</v>
@@ -7286,55 +7286,55 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B397" s="3">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C397" s="3">
-        <v>230.99</v>
+        <v>33.39</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B398" s="3">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C398" s="3">
-        <v>33.39</v>
+        <v>20.66</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B399" s="3">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="C399" s="3">
-        <v>20.66</v>
+        <v>97.5</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B400" s="3">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C400" s="3">
-        <v>97.5</v>
+        <v>24.7</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>385</v>
@@ -7342,13 +7342,13 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B401" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C401" s="3">
-        <v>24.7</v>
+        <v>35.75</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>385</v>
@@ -7356,13 +7356,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B402" s="3">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C402" s="3">
-        <v>35.75</v>
+        <v>9.1</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>385</v>
@@ -7370,13 +7370,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B403" s="3">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C403" s="3">
-        <v>9.1</v>
+        <v>5.43</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>385</v>
@@ -7384,27 +7384,27 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="B404" s="3">
-        <v>196</v>
+        <v>60</v>
       </c>
       <c r="C404" s="3">
-        <v>5.43</v>
+        <v>9.75</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B405" s="3">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C405" s="3">
-        <v>9.75</v>
+        <v>6.37</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>391</v>
@@ -7412,43 +7412,29 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B406" s="3">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="C406" s="3">
-        <v>6.37</v>
+        <v>11.59</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B407" s="3">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="C407" s="3">
-        <v>11.59</v>
+        <v>12.09</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4">
-      <c r="A408" t="s">
-        <v>428</v>
-      </c>
-      <c r="B408" s="3">
-        <v>81</v>
-      </c>
-      <c r="C408" s="3">
-        <v>12.09</v>
-      </c>
-      <c r="D408" s="4" t="s">
         <v>392</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1801,7 +1801,7 @@
         <v>402</v>
       </c>
       <c r="B5" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3">
         <v>239.2</v>
@@ -1815,7 +1815,7 @@
         <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
         <v>262.61</v>
@@ -1871,7 +1871,7 @@
         <v>406</v>
       </c>
       <c r="B10" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3">
         <v>343.45</v>
@@ -2011,7 +2011,7 @@
         <v>407</v>
       </c>
       <c r="B20" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2109,7 +2109,7 @@
         <v>414</v>
       </c>
       <c r="B27" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27" s="3">
         <v>442.81</v>
@@ -2277,7 +2277,7 @@
         <v>17</v>
       </c>
       <c r="B39" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C39" s="3">
         <v>200.92</v>
@@ -2361,7 +2361,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2768</v>
+        <v>2732</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
@@ -2627,7 +2627,7 @@
         <v>41</v>
       </c>
       <c r="B64" s="3">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C64" s="3">
         <v>70.47</v>
@@ -2669,7 +2669,7 @@
         <v>43</v>
       </c>
       <c r="B67" s="3">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C67" s="3">
         <v>18.96</v>
@@ -2711,7 +2711,7 @@
         <v>46</v>
       </c>
       <c r="B70" s="3">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C70" s="3">
         <v>18.96</v>
@@ -2837,7 +2837,7 @@
         <v>54</v>
       </c>
       <c r="B79" s="3">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C79" s="3">
         <v>34.630000000000003</v>
@@ -3565,7 +3565,7 @@
         <v>104</v>
       </c>
       <c r="B131" s="3">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C131" s="3">
         <v>66.98</v>
@@ -4139,7 +4139,7 @@
         <v>144</v>
       </c>
       <c r="B172" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C172" s="3">
         <v>75.989999999999995</v>
@@ -4391,7 +4391,7 @@
         <v>161</v>
       </c>
       <c r="B190" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C190" s="3">
         <v>48.64</v>
@@ -4405,7 +4405,7 @@
         <v>162</v>
       </c>
       <c r="B191" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C191" s="3">
         <v>126.63</v>
@@ -4461,7 +4461,7 @@
         <v>166</v>
       </c>
       <c r="B195" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C195" s="3">
         <v>179</v>
@@ -4489,7 +4489,7 @@
         <v>168</v>
       </c>
       <c r="B197" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C197" s="3">
         <v>51</v>
@@ -4699,7 +4699,7 @@
         <v>182</v>
       </c>
       <c r="B212" s="3">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C212" s="3">
         <v>37.299999999999997</v>
@@ -5371,7 +5371,7 @@
         <v>228</v>
       </c>
       <c r="B260" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C260" s="3">
         <v>79.75</v>
@@ -5567,7 +5567,7 @@
         <v>242</v>
       </c>
       <c r="B274" s="3">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C274" s="3">
         <v>44.93</v>
@@ -5595,7 +5595,7 @@
         <v>244</v>
       </c>
       <c r="B276" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C276" s="3">
         <v>173.09</v>
@@ -5609,7 +5609,7 @@
         <v>245</v>
       </c>
       <c r="B277" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C277" s="3">
         <v>215.08</v>
@@ -6631,7 +6631,7 @@
         <v>316</v>
       </c>
       <c r="B350" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C350" s="3">
         <v>205.53</v>
@@ -6687,7 +6687,7 @@
         <v>320</v>
       </c>
       <c r="B354" s="3">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C354" s="3">
         <v>259.81</v>
@@ -6785,7 +6785,7 @@
         <v>327</v>
       </c>
       <c r="B361" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C361" s="3">
         <v>312.8</v>
@@ -7317,7 +7317,7 @@
         <v>386</v>
       </c>
       <c r="B399" s="3">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C399" s="3">
         <v>97.5</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="432">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1307,6 +1307,9 @@
   </si>
   <si>
     <t>CYC MAGMA X-100 10W40 DRUM 60L</t>
+  </si>
+  <si>
+    <t>ULEI MOTO</t>
   </si>
 </sst>
 </file>
@@ -1815,7 +1818,7 @@
         <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>262.61</v>
@@ -1857,7 +1860,7 @@
         <v>405</v>
       </c>
       <c r="B9" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3">
         <v>309.52</v>
@@ -1969,7 +1972,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3">
         <v>909.67</v>
@@ -2081,7 +2084,7 @@
         <v>412</v>
       </c>
       <c r="B25" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3">
         <v>376.62</v>
@@ -2361,7 +2364,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2732</v>
+        <v>2696</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
@@ -2613,7 +2616,7 @@
         <v>40</v>
       </c>
       <c r="B63" s="3">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C63" s="3">
         <v>16.600000000000001</v>
@@ -2641,7 +2644,7 @@
         <v>42</v>
       </c>
       <c r="B65" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C65" s="3">
         <v>86.8</v>
@@ -2669,7 +2672,7 @@
         <v>43</v>
       </c>
       <c r="B67" s="3">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C67" s="3">
         <v>18.96</v>
@@ -2683,7 +2686,7 @@
         <v>44</v>
       </c>
       <c r="B68" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C68" s="3">
         <v>73.13</v>
@@ -2851,7 +2854,7 @@
         <v>55</v>
       </c>
       <c r="B80" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C80" s="3">
         <v>18.37</v>
@@ -2865,7 +2868,7 @@
         <v>56</v>
       </c>
       <c r="B81" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C81" s="3">
         <v>82.88</v>
@@ -3411,7 +3414,7 @@
         <v>93</v>
       </c>
       <c r="B120" s="3">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C120" s="3">
         <v>67.27</v>
@@ -3845,7 +3848,7 @@
         <v>123</v>
       </c>
       <c r="B151" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C151" s="3">
         <v>32.200000000000003</v>
@@ -3901,7 +3904,7 @@
         <v>127</v>
       </c>
       <c r="B155" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C155" s="3">
         <v>38.39</v>
@@ -4349,7 +4352,7 @@
         <v>158</v>
       </c>
       <c r="B187" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C187" s="3">
         <v>173.3</v>
@@ -4531,7 +4534,7 @@
         <v>170</v>
       </c>
       <c r="B200" s="3">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C200" s="3">
         <v>33.479999999999997</v>
@@ -4545,7 +4548,7 @@
         <v>171</v>
       </c>
       <c r="B201" s="3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C201" s="3">
         <v>46.06</v>
@@ -4559,7 +4562,7 @@
         <v>172</v>
       </c>
       <c r="B202" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C202" s="3">
         <v>5400</v>
@@ -4587,7 +4590,7 @@
         <v>174</v>
       </c>
       <c r="B204" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C204" s="3">
         <v>192.51</v>
@@ -4699,7 +4702,7 @@
         <v>182</v>
       </c>
       <c r="B212" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C212" s="3">
         <v>37.299999999999997</v>
@@ -4713,7 +4716,7 @@
         <v>183</v>
       </c>
       <c r="B213" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C213" s="3">
         <v>126.24</v>
@@ -4769,7 +4772,7 @@
         <v>187</v>
       </c>
       <c r="B217" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C217" s="3">
         <v>466.78</v>
@@ -4859,7 +4862,7 @@
         <v>81.650000000000006</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4873,7 +4876,7 @@
         <v>50.71</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4887,7 +4890,7 @@
         <v>51.75</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4901,7 +4904,7 @@
         <v>36.94</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4915,7 +4918,7 @@
         <v>36.94</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4923,7 +4926,7 @@
         <v>197</v>
       </c>
       <c r="B228" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C228" s="3">
         <v>67.28</v>
@@ -5223,7 +5226,7 @@
         <v>42.49</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5231,7 +5234,7 @@
         <v>218</v>
       </c>
       <c r="B250" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C250" s="8">
         <v>84</v>
@@ -5461,7 +5464,7 @@
         <v>40.57</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5475,7 +5478,7 @@
         <v>36.229999999999997</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5567,7 +5570,7 @@
         <v>242</v>
       </c>
       <c r="B274" s="3">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C274" s="3">
         <v>44.93</v>
@@ -5595,7 +5598,7 @@
         <v>244</v>
       </c>
       <c r="B276" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C276" s="3">
         <v>173.09</v>
@@ -5609,7 +5612,7 @@
         <v>245</v>
       </c>
       <c r="B277" s="3">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C277" s="3">
         <v>215.08</v>
@@ -6575,7 +6578,7 @@
         <v>312</v>
       </c>
       <c r="B346" s="3">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C346" s="3">
         <v>44.31</v>
@@ -6617,7 +6620,7 @@
         <v>315</v>
       </c>
       <c r="B349" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C349" s="3">
         <v>167.33</v>
@@ -6631,7 +6634,7 @@
         <v>316</v>
       </c>
       <c r="B350" s="3">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C350" s="3">
         <v>205.53</v>
@@ -6659,7 +6662,7 @@
         <v>318</v>
       </c>
       <c r="B352" s="3">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C352" s="3">
         <v>62.04</v>
@@ -6687,7 +6690,7 @@
         <v>320</v>
       </c>
       <c r="B354" s="3">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C354" s="3">
         <v>259.81</v>
@@ -6715,7 +6718,7 @@
         <v>322</v>
       </c>
       <c r="B356" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C356" s="3">
         <v>310.2</v>
@@ -7317,7 +7320,7 @@
         <v>386</v>
       </c>
       <c r="B399" s="3">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C399" s="3">
         <v>97.5</v>
@@ -7331,7 +7334,7 @@
         <v>387</v>
       </c>
       <c r="B400" s="3">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C400" s="3">
         <v>24.7</v>
@@ -7345,7 +7348,7 @@
         <v>388</v>
       </c>
       <c r="B401" s="3">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C401" s="3">
         <v>35.75</v>
@@ -7401,7 +7404,7 @@
         <v>426</v>
       </c>
       <c r="B405" s="3">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C405" s="3">
         <v>6.37</v>
@@ -7429,7 +7432,7 @@
         <v>428</v>
       </c>
       <c r="B407" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C407" s="3">
         <v>12.09</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2504,7 +2504,7 @@
         <v>429</v>
       </c>
       <c r="B55" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C55" s="3">
         <v>144.34</v>
@@ -2616,7 +2616,7 @@
         <v>40</v>
       </c>
       <c r="B63" s="3">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C63" s="3">
         <v>16.600000000000001</v>
@@ -4072,7 +4072,7 @@
         <v>139</v>
       </c>
       <c r="B167" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C167" s="3">
         <v>243.16</v>
@@ -5598,7 +5598,7 @@
         <v>244</v>
       </c>
       <c r="B276" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C276" s="3">
         <v>173.09</v>
@@ -6634,7 +6634,7 @@
         <v>316</v>
       </c>
       <c r="B350" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C350" s="3">
         <v>205.53</v>
@@ -6662,7 +6662,7 @@
         <v>318</v>
       </c>
       <c r="B352" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C352" s="3">
         <v>62.04</v>
@@ -6718,7 +6718,7 @@
         <v>322</v>
       </c>
       <c r="B356" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C356" s="3">
         <v>310.2</v>
@@ -7334,7 +7334,7 @@
         <v>387</v>
       </c>
       <c r="B400" s="3">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C400" s="3">
         <v>24.7</v>
@@ -7362,7 +7362,7 @@
         <v>389</v>
       </c>
       <c r="B402" s="3">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C402" s="3">
         <v>9.1</v>
@@ -7376,7 +7376,7 @@
         <v>390</v>
       </c>
       <c r="B403" s="3">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C403" s="3">
         <v>5.43</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="431">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1127,9 +1127,6 @@
   </si>
   <si>
     <t>EFB</t>
-  </si>
-  <si>
-    <t>RUNNING BULL</t>
   </si>
   <si>
     <t>AGM</t>
@@ -1801,7 +1798,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -1815,7 +1812,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="3">
         <v>11</v>
@@ -1829,7 +1826,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -1843,7 +1840,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -1857,7 +1854,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B9" s="3">
         <v>23</v>
@@ -1871,7 +1868,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" s="3">
         <v>43</v>
@@ -1885,7 +1882,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B11" s="3">
         <v>5</v>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -1922,12 +1919,12 @@
         <v>687.26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1936,12 +1933,12 @@
         <v>825.42</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1950,12 +1947,12 @@
         <v>902.73</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -1964,7 +1961,7 @@
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1978,12 +1975,12 @@
         <v>909.67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -1997,7 +1994,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B19" s="3">
         <v>6</v>
@@ -2006,12 +2003,12 @@
         <v>1132.73</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B20" s="3">
         <v>19</v>
@@ -2020,12 +2017,12 @@
         <v>534.95000000000005</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B21" s="3">
         <v>3</v>
@@ -2034,12 +2031,12 @@
         <v>706.12</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
@@ -2048,12 +2045,12 @@
         <v>241.24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B23" s="3">
         <v>9</v>
@@ -2062,12 +2059,12 @@
         <v>278.02</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -2076,12 +2073,12 @@
         <v>358.39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B25" s="3">
         <v>22</v>
@@ -2090,12 +2087,12 @@
         <v>376.62</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
@@ -2104,12 +2101,12 @@
         <v>409.88</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B27" s="3">
         <v>19</v>
@@ -2118,12 +2115,12 @@
         <v>442.81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -2132,12 +2129,12 @@
         <v>491.37</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2146,7 +2143,7 @@
         <v>478.19</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2160,7 +2157,7 @@
         <v>41.58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2174,7 +2171,7 @@
         <v>5899.25</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2188,7 +2185,7 @@
         <v>5899.25</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2202,7 +2199,7 @@
         <v>182.58</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2216,7 +2213,7 @@
         <v>41.58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2230,7 +2227,7 @@
         <v>146.97999999999999</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2244,7 +2241,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2258,7 +2255,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2272,7 +2269,7 @@
         <v>122.46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2286,7 +2283,7 @@
         <v>200.92</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2300,7 +2297,7 @@
         <v>156.07</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2314,7 +2311,7 @@
         <v>25.61</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2328,7 +2325,7 @@
         <v>115.42</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2342,7 +2339,7 @@
         <v>25.6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2356,7 +2353,7 @@
         <v>36.4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2370,7 +2367,7 @@
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2384,7 +2381,7 @@
         <v>23.37</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2398,7 +2395,7 @@
         <v>361.92</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2412,7 +2409,7 @@
         <v>21</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2426,7 +2423,7 @@
         <v>357.53</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2440,7 +2437,7 @@
         <v>19.3</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2454,7 +2451,7 @@
         <v>337.5</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2468,7 +2465,7 @@
         <v>33.64</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2482,7 +2479,7 @@
         <v>298.12</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2496,12 +2493,12 @@
         <v>1982.77</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B55" s="3">
         <v>18</v>
@@ -2510,7 +2507,7 @@
         <v>144.34</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2524,7 +2521,7 @@
         <v>280.12</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2538,7 +2535,7 @@
         <v>24.51</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2552,7 +2549,7 @@
         <v>26.21</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2566,7 +2563,7 @@
         <v>101.08</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2580,7 +2577,7 @@
         <v>29.13</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2594,7 +2591,7 @@
         <v>102.31</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2608,7 +2605,7 @@
         <v>168.07</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2622,7 +2619,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2636,7 +2633,7 @@
         <v>70.47</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2650,12 +2647,12 @@
         <v>86.8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
@@ -2664,7 +2661,7 @@
         <v>1041.71</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2678,7 +2675,7 @@
         <v>18.96</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2692,7 +2689,7 @@
         <v>73.13</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2706,7 +2703,7 @@
         <v>89.38</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2720,7 +2717,7 @@
         <v>18.96</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2734,7 +2731,7 @@
         <v>73.13</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2748,7 +2745,7 @@
         <v>89.39</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2762,7 +2759,7 @@
         <v>3173.52</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2776,7 +2773,7 @@
         <v>25.4</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2790,7 +2787,7 @@
         <v>40.92</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2804,7 +2801,7 @@
         <v>25.4</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2818,12 +2815,12 @@
         <v>28.07</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B78" s="3">
         <v>4</v>
@@ -2832,7 +2829,7 @@
         <v>23.33</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2846,7 +2843,7 @@
         <v>34.630000000000003</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2860,7 +2857,7 @@
         <v>18.37</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2874,7 +2871,7 @@
         <v>82.88</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2888,7 +2885,7 @@
         <v>161.01</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2902,7 +2899,7 @@
         <v>44.85</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2916,7 +2913,7 @@
         <v>65.83</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2944,7 +2941,7 @@
         <v>62.11</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2958,7 +2955,7 @@
         <v>47.61</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2972,7 +2969,7 @@
         <v>63.76</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2986,7 +2983,7 @@
         <v>1159.2</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3000,7 +2997,7 @@
         <v>255</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3014,7 +3011,7 @@
         <v>69.55</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3028,7 +3025,7 @@
         <v>1391.04</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3042,7 +3039,7 @@
         <v>87.1</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3056,7 +3053,7 @@
         <v>40.54</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3070,7 +3067,7 @@
         <v>460.01</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3084,7 +3081,7 @@
         <v>639.4</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3098,7 +3095,7 @@
         <v>103.89</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3112,7 +3109,7 @@
         <v>58.48</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3126,7 +3123,7 @@
         <v>56.93</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3140,7 +3137,7 @@
         <v>63.76</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3154,7 +3151,7 @@
         <v>61.92</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3168,7 +3165,7 @@
         <v>63.76</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3182,7 +3179,7 @@
         <v>69.56</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3196,7 +3193,7 @@
         <v>59.68</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3210,7 +3207,7 @@
         <v>56.93</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3224,7 +3221,7 @@
         <v>80.73</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3238,7 +3235,7 @@
         <v>98.95</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3252,7 +3249,7 @@
         <v>93.25</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3266,7 +3263,7 @@
         <v>63.76</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3280,7 +3277,7 @@
         <v>63.76</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3294,7 +3291,7 @@
         <v>81.150000000000006</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3308,7 +3305,7 @@
         <v>63.76</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3322,7 +3319,7 @@
         <v>69.87</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3336,7 +3333,7 @@
         <v>63.76</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3350,7 +3347,7 @@
         <v>69.56</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3364,7 +3361,7 @@
         <v>69.56</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3378,7 +3375,7 @@
         <v>52.17</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3392,7 +3389,7 @@
         <v>208.66</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3406,7 +3403,7 @@
         <v>88.87</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3420,7 +3417,7 @@
         <v>67.27</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3434,7 +3431,7 @@
         <v>69.55</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3448,7 +3445,7 @@
         <v>63.89</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3462,7 +3459,7 @@
         <v>149.91</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3476,7 +3473,7 @@
         <v>38.57</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3490,7 +3487,7 @@
         <v>207.31</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3504,7 +3501,7 @@
         <v>65.23</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3518,7 +3515,7 @@
         <v>325.87</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3532,7 +3529,7 @@
         <v>5165.8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3546,7 +3543,7 @@
         <v>511.75</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3560,7 +3557,7 @@
         <v>572.70000000000005</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3588,7 +3585,7 @@
         <v>367.42</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3602,7 +3599,7 @@
         <v>51.52</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3616,7 +3613,7 @@
         <v>23.19</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3630,7 +3627,7 @@
         <v>23.19</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3644,7 +3641,7 @@
         <v>69.55</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3658,7 +3655,7 @@
         <v>3169.7</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3672,7 +3669,7 @@
         <v>81.14</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3686,7 +3683,7 @@
         <v>81.14</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3714,7 +3711,7 @@
         <v>74.989999999999995</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3728,7 +3725,7 @@
         <v>93.35</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3742,7 +3739,7 @@
         <v>1217.1600000000001</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3756,7 +3753,7 @@
         <v>3079</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3770,7 +3767,7 @@
         <v>43.7</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3784,7 +3781,7 @@
         <v>48.95</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3798,7 +3795,7 @@
         <v>72.33</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3812,7 +3809,7 @@
         <v>284.19</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3826,7 +3823,7 @@
         <v>132.19</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3896,7 +3893,7 @@
         <v>115.01</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3910,7 +3907,7 @@
         <v>38.39</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3924,7 +3921,7 @@
         <v>151.47999999999999</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3938,7 +3935,7 @@
         <v>181.68</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4047,7 @@
         <v>107.35</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4064,7 +4061,7 @@
         <v>61.83</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4078,7 +4075,7 @@
         <v>243.16</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4092,7 +4089,7 @@
         <v>63.78</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4106,7 +4103,7 @@
         <v>75.989999999999995</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4120,7 +4117,7 @@
         <v>297.64999999999998</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4134,7 +4131,7 @@
         <v>77.28</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4148,7 +4145,7 @@
         <v>75.989999999999995</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4162,7 +4159,7 @@
         <v>342.24</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4176,7 +4173,7 @@
         <v>633.75</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4190,7 +4187,7 @@
         <v>50.51</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4204,7 +4201,7 @@
         <v>787.75</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4218,7 +4215,7 @@
         <v>122.36</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4246,7 +4243,7 @@
         <v>59.25</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4260,7 +4257,7 @@
         <v>201.84</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4274,7 +4271,7 @@
         <v>57.59</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4288,7 +4285,7 @@
         <v>221.86</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4302,7 +4299,7 @@
         <v>74.7</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4316,12 +4313,12 @@
         <v>296.3</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B185" s="3">
         <v>14</v>
@@ -4330,7 +4327,7 @@
         <v>141.80000000000001</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4344,7 +4341,7 @@
         <v>41.4</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4358,7 +4355,7 @@
         <v>173.3</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4372,7 +4369,7 @@
         <v>2189.02</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4386,7 +4383,7 @@
         <v>453.22</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4400,7 +4397,7 @@
         <v>48.64</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4414,7 +4411,7 @@
         <v>126.63</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4428,7 +4425,7 @@
         <v>69.56</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4442,7 +4439,7 @@
         <v>44.51</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4456,7 +4453,7 @@
         <v>145.94</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4470,7 +4467,7 @@
         <v>179</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4484,7 +4481,7 @@
         <v>2060</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4498,7 +4495,7 @@
         <v>51</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4512,7 +4509,7 @@
         <v>183.41</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4526,7 +4523,7 @@
         <v>248.99</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4554,7 +4551,7 @@
         <v>46.06</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4568,7 +4565,7 @@
         <v>5400</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4582,7 +4579,7 @@
         <v>170.78</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4596,7 +4593,7 @@
         <v>192.51</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4610,7 +4607,7 @@
         <v>59.7</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4624,7 +4621,7 @@
         <v>265.05</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4652,7 +4649,7 @@
         <v>103.04</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4680,7 +4677,7 @@
         <v>47.16</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4694,7 +4691,7 @@
         <v>16.809999999999999</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4708,7 +4705,7 @@
         <v>37.299999999999997</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4722,7 +4719,7 @@
         <v>126.24</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4736,7 +4733,7 @@
         <v>154.62</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4750,7 +4747,7 @@
         <v>508.2</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4764,7 +4761,7 @@
         <v>5069</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4778,7 +4775,7 @@
         <v>466.78</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4792,7 +4789,7 @@
         <v>57.5</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4806,7 +4803,7 @@
         <v>63.13</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4820,7 +4817,7 @@
         <v>20789.41</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4834,7 +4831,7 @@
         <v>33057.85</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4848,7 +4845,7 @@
         <v>83.5</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4862,7 +4859,7 @@
         <v>81.650000000000006</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4876,7 +4873,7 @@
         <v>50.71</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4890,7 +4887,7 @@
         <v>51.75</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4904,7 +4901,7 @@
         <v>36.94</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4918,7 +4915,7 @@
         <v>36.94</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4932,7 +4929,7 @@
         <v>67.28</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4946,7 +4943,7 @@
         <v>65.099999999999994</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4960,7 +4957,7 @@
         <v>65.53</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4974,7 +4971,7 @@
         <v>109.08</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5030,7 +5027,7 @@
         <v>6.44</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5044,7 +5041,7 @@
         <v>108.2</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5058,7 +5055,7 @@
         <v>4456.4799999999996</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5072,7 +5069,7 @@
         <v>6279</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5086,7 +5083,7 @@
         <v>609.5</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5184,7 +5181,7 @@
         <v>56</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5198,7 +5195,7 @@
         <v>57.63</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5212,7 +5209,7 @@
         <v>60.78</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5226,7 +5223,7 @@
         <v>42.49</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5240,7 +5237,7 @@
         <v>84</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5254,7 +5251,7 @@
         <v>301.99</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5268,7 +5265,7 @@
         <v>71.709999999999994</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5282,7 +5279,7 @@
         <v>77.760000000000005</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5296,7 +5293,7 @@
         <v>54.7</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5310,7 +5307,7 @@
         <v>67.28</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5324,7 +5321,7 @@
         <v>251.5</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5338,7 +5335,7 @@
         <v>78.87</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5352,7 +5349,7 @@
         <v>83.84</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5366,7 +5363,7 @@
         <v>331.2</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5380,7 +5377,7 @@
         <v>79.75</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5394,7 +5391,7 @@
         <v>83.84</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5408,7 +5405,7 @@
         <v>284</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5422,7 +5419,7 @@
         <v>28.15</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5436,7 +5433,7 @@
         <v>45.08</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5450,7 +5447,7 @@
         <v>51.52</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5464,7 +5461,7 @@
         <v>40.57</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5478,7 +5475,7 @@
         <v>36.229999999999997</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5492,7 +5489,7 @@
         <v>54.12</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5506,7 +5503,7 @@
         <v>69.55</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5520,7 +5517,7 @@
         <v>295.14999999999998</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5534,7 +5531,7 @@
         <v>38.56</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5548,7 +5545,7 @@
         <v>60.95</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5562,7 +5559,7 @@
         <v>78.209999999999994</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5576,7 +5573,7 @@
         <v>44.93</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5590,7 +5587,7 @@
         <v>6578.46</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5604,7 +5601,7 @@
         <v>173.09</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5618,7 +5615,7 @@
         <v>215.08</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5632,7 +5629,7 @@
         <v>2314.8000000000002</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5646,7 +5643,7 @@
         <v>791.3</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5660,7 +5657,7 @@
         <v>31.6</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5674,7 +5671,7 @@
         <v>77.28</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5688,7 +5685,7 @@
         <v>43.8</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5702,7 +5699,7 @@
         <v>21.9</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5716,7 +5713,7 @@
         <v>798.6</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5730,7 +5727,7 @@
         <v>23.19</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5744,7 +5741,7 @@
         <v>8.24</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5758,7 +5755,7 @@
         <v>13.72</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5772,12 +5769,12 @@
         <v>31.95</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B289" s="3">
         <v>105</v>
@@ -5786,7 +5783,7 @@
         <v>16.2</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5800,7 +5797,7 @@
         <v>36.869999999999997</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5814,7 +5811,7 @@
         <v>31.48</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5828,7 +5825,7 @@
         <v>21.9</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5842,7 +5839,7 @@
         <v>23.19</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5856,7 +5853,7 @@
         <v>19.55</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5870,7 +5867,7 @@
         <v>19.07</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5884,7 +5881,7 @@
         <v>21.9</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5898,7 +5895,7 @@
         <v>79.349999999999994</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5912,7 +5909,7 @@
         <v>862.7</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5926,7 +5923,7 @@
         <v>56.93</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5940,7 +5937,7 @@
         <v>1265</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5954,7 +5951,7 @@
         <v>76</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5968,7 +5965,7 @@
         <v>267.85000000000002</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5982,7 +5979,7 @@
         <v>74.7</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5996,7 +5993,7 @@
         <v>327.3</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -6010,7 +6007,7 @@
         <v>72.13</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -6024,7 +6021,7 @@
         <v>302.39999999999998</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -6052,7 +6049,7 @@
         <v>428.5</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -6066,7 +6063,7 @@
         <v>450.22</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6080,7 +6077,7 @@
         <v>465.7</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6094,7 +6091,7 @@
         <v>38.25</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6108,7 +6105,7 @@
         <v>87.49</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6122,7 +6119,7 @@
         <v>63.13</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6136,7 +6133,7 @@
         <v>377.78</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6150,7 +6147,7 @@
         <v>3333.85</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6164,7 +6161,7 @@
         <v>374.67</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6178,7 +6175,7 @@
         <v>120.06</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6192,7 +6189,7 @@
         <v>54.2</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6206,7 +6203,7 @@
         <v>31.5</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6220,7 +6217,7 @@
         <v>114.09</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6234,7 +6231,7 @@
         <v>139.9</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6248,7 +6245,7 @@
         <v>35.94</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6262,7 +6259,7 @@
         <v>140.26</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6276,7 +6273,7 @@
         <v>370.53</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6304,7 +6301,7 @@
         <v>4772.5</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6318,7 +6315,7 @@
         <v>516.46</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6332,7 +6329,7 @@
         <v>185.15</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6346,7 +6343,7 @@
         <v>11.5</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6360,7 +6357,7 @@
         <v>724.5</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6374,7 +6371,7 @@
         <v>450.22</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6556,7 +6553,7 @@
         <v>57.7</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6570,7 +6567,7 @@
         <v>90.9</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6584,7 +6581,7 @@
         <v>44.31</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6598,7 +6595,7 @@
         <v>7173.59</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6612,7 +6609,7 @@
         <v>677.79</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6626,7 +6623,7 @@
         <v>167.33</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6640,7 +6637,7 @@
         <v>205.53</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6654,7 +6651,7 @@
         <v>2335.67</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6668,7 +6665,7 @@
         <v>62.04</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6682,7 +6679,7 @@
         <v>8139.6</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6696,7 +6693,7 @@
         <v>259.81</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6710,7 +6707,7 @@
         <v>259.8</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6724,7 +6721,7 @@
         <v>310.2</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6738,7 +6735,7 @@
         <v>36.43</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6752,7 +6749,7 @@
         <v>87.22</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6766,7 +6763,7 @@
         <v>319.60000000000002</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6780,7 +6777,7 @@
         <v>62.6</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6794,7 +6791,7 @@
         <v>312.8</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6808,7 +6805,7 @@
         <v>67.28</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6822,7 +6819,7 @@
         <v>1138.5</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6836,7 +6833,7 @@
         <v>58.69</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6850,7 +6847,7 @@
         <v>289.33999999999997</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6864,7 +6861,7 @@
         <v>48.76</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6878,7 +6875,7 @@
         <v>242.34</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6892,7 +6889,7 @@
         <v>54.09</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6906,7 +6903,7 @@
         <v>255.03</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6920,7 +6917,7 @@
         <v>220.8</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6934,7 +6931,7 @@
         <v>255.02</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6948,7 +6945,7 @@
         <v>68.86</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6962,7 +6959,7 @@
         <v>344.28</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6976,7 +6973,7 @@
         <v>60.29</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6990,12 +6987,12 @@
         <v>261.8</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B376" s="3">
         <v>2</v>
@@ -7004,7 +7001,7 @@
         <v>30.58</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -7032,7 +7029,7 @@
         <v>24.95</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -7046,7 +7043,7 @@
         <v>641.49</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -7060,7 +7057,7 @@
         <v>39.57</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -7074,7 +7071,7 @@
         <v>51.83</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -7088,7 +7085,7 @@
         <v>33.840000000000003</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -7102,7 +7099,7 @@
         <v>150.15</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -7116,7 +7113,7 @@
         <v>144.5</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -7130,7 +7127,7 @@
         <v>100.93</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7144,7 +7141,7 @@
         <v>124.5</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7158,7 +7155,7 @@
         <v>27.21</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7172,7 +7169,7 @@
         <v>24.79</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7186,7 +7183,7 @@
         <v>37.1</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7200,7 +7197,7 @@
         <v>178.04</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7214,7 +7211,7 @@
         <v>23.88</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7228,12 +7225,12 @@
         <v>20.68</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B393" s="3">
         <v>31</v>
@@ -7242,12 +7239,12 @@
         <v>97.54</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B394" s="3">
         <v>9</v>
@@ -7256,7 +7253,7 @@
         <v>304.02999999999997</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7270,7 +7267,7 @@
         <v>1934.56</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7284,7 +7281,7 @@
         <v>230.99</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7298,7 +7295,7 @@
         <v>33.39</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7312,12 +7309,12 @@
         <v>20.66</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B399" s="3">
         <v>160</v>
@@ -7326,12 +7323,12 @@
         <v>97.5</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B400" s="3">
         <v>129</v>
@@ -7340,12 +7337,12 @@
         <v>24.7</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B401" s="3">
         <v>171</v>
@@ -7354,12 +7351,12 @@
         <v>35.75</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B402" s="3">
         <v>180</v>
@@ -7368,12 +7365,12 @@
         <v>9.1</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B403" s="3">
         <v>176</v>
@@ -7382,12 +7379,12 @@
         <v>5.43</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B404" s="3">
         <v>60</v>
@@ -7396,12 +7393,12 @@
         <v>9.75</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B405" s="3">
         <v>58</v>
@@ -7410,12 +7407,12 @@
         <v>6.37</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B406" s="3">
         <v>150</v>
@@ -7424,12 +7421,12 @@
         <v>11.59</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B407" s="3">
         <v>37</v>
@@ -7438,7 +7435,7 @@
         <v>12.09</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2151,7 +2151,7 @@
         <v>8</v>
       </c>
       <c r="B30" s="3">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C30" s="3">
         <v>41.58</v>
@@ -2235,7 +2235,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="3">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C36" s="3">
         <v>34.619999999999997</v>
@@ -2333,7 +2333,7 @@
         <v>21</v>
       </c>
       <c r="B43" s="3">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C43" s="3">
         <v>25.6</v>
@@ -2347,7 +2347,7 @@
         <v>22</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="3">
         <v>36.4</v>
@@ -2361,7 +2361,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2696</v>
+        <v>2648</v>
       </c>
       <c r="C45" s="3">
         <v>13</v>
@@ -2613,7 +2613,7 @@
         <v>40</v>
       </c>
       <c r="B63" s="3">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C63" s="3">
         <v>16.600000000000001</v>
@@ -2627,7 +2627,7 @@
         <v>41</v>
       </c>
       <c r="B64" s="3">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C64" s="3">
         <v>70.47</v>
@@ -2711,7 +2711,7 @@
         <v>46</v>
       </c>
       <c r="B70" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70" s="3">
         <v>18.96</v>
@@ -3705,7 +3705,7 @@
         <v>114</v>
       </c>
       <c r="B141" s="3">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C141" s="8">
         <v>74.989999999999995</v>
@@ -3719,7 +3719,7 @@
         <v>115</v>
       </c>
       <c r="B142" s="3">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C142" s="3">
         <v>93.35</v>
@@ -4069,7 +4069,7 @@
         <v>139</v>
       </c>
       <c r="B167" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C167" s="3">
         <v>243.16</v>
@@ -4321,7 +4321,7 @@
         <v>395</v>
       </c>
       <c r="B185" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C185" s="3">
         <v>141.80000000000001</v>
@@ -4349,7 +4349,7 @@
         <v>158</v>
       </c>
       <c r="B187" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C187" s="3">
         <v>173.3</v>
@@ -4517,7 +4517,7 @@
         <v>362</v>
       </c>
       <c r="B199" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C199" s="8">
         <v>248.99</v>
@@ -4601,7 +4601,7 @@
         <v>175</v>
       </c>
       <c r="B205" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C205" s="3">
         <v>59.7</v>
@@ -4615,7 +4615,7 @@
         <v>176</v>
       </c>
       <c r="B206" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C206" s="3">
         <v>265.05</v>
@@ -4727,7 +4727,7 @@
         <v>184</v>
       </c>
       <c r="B214" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C214" s="3">
         <v>154.62</v>
@@ -4769,7 +4769,7 @@
         <v>187</v>
       </c>
       <c r="B217" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217" s="3">
         <v>466.78</v>
@@ -4937,7 +4937,7 @@
         <v>198</v>
       </c>
       <c r="B229" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C229" s="3">
         <v>65.099999999999994</v>
@@ -4951,7 +4951,7 @@
         <v>199</v>
       </c>
       <c r="B230" s="3">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C230" s="3">
         <v>65.53</v>
@@ -5567,7 +5567,7 @@
         <v>242</v>
       </c>
       <c r="B274" s="3">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C274" s="3">
         <v>44.93</v>
@@ -5581,7 +5581,7 @@
         <v>243</v>
       </c>
       <c r="B275" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C275" s="3">
         <v>6578.46</v>
@@ -5595,7 +5595,7 @@
         <v>244</v>
       </c>
       <c r="B276" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C276" s="3">
         <v>173.09</v>
@@ -5609,7 +5609,7 @@
         <v>245</v>
       </c>
       <c r="B277" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C277" s="3">
         <v>215.08</v>
@@ -5637,7 +5637,7 @@
         <v>247</v>
       </c>
       <c r="B279" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C279" s="3">
         <v>791.3</v>
@@ -6239,7 +6239,7 @@
         <v>289</v>
       </c>
       <c r="B322" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C322" s="3">
         <v>35.94</v>
@@ -6631,7 +6631,7 @@
         <v>316</v>
       </c>
       <c r="B350" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C350" s="3">
         <v>205.53</v>
@@ -6687,7 +6687,7 @@
         <v>320</v>
       </c>
       <c r="B354" s="3">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C354" s="3">
         <v>259.81</v>
@@ -6701,7 +6701,7 @@
         <v>321</v>
       </c>
       <c r="B355" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C355" s="3">
         <v>259.8</v>
@@ -6715,7 +6715,7 @@
         <v>322</v>
       </c>
       <c r="B356" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C356" s="3">
         <v>310.2</v>
@@ -6771,7 +6771,7 @@
         <v>326</v>
       </c>
       <c r="B360" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C360" s="3">
         <v>62.6</v>
@@ -6799,7 +6799,7 @@
         <v>328</v>
       </c>
       <c r="B362" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C362" s="3">
         <v>67.28</v>
@@ -6981,7 +6981,7 @@
         <v>339</v>
       </c>
       <c r="B375" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C375" s="3">
         <v>261.8</v>
@@ -7303,7 +7303,7 @@
         <v>359</v>
       </c>
       <c r="B398" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C398" s="3">
         <v>20.66</v>
@@ -7317,7 +7317,7 @@
         <v>385</v>
       </c>
       <c r="B399" s="3">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C399" s="3">
         <v>97.5</v>
@@ -7331,7 +7331,7 @@
         <v>386</v>
       </c>
       <c r="B400" s="3">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C400" s="3">
         <v>24.7</v>
@@ -7359,7 +7359,7 @@
         <v>388</v>
       </c>
       <c r="B402" s="3">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C402" s="3">
         <v>9.1</v>
@@ -7373,7 +7373,7 @@
         <v>389</v>
       </c>
       <c r="B403" s="3">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C403" s="3">
         <v>5.43</v>
@@ -7387,7 +7387,7 @@
         <v>424</v>
       </c>
       <c r="B404" s="3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C404" s="3">
         <v>9.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -70,9 +70,6 @@
     <t>CASTROL EDGE 5W40 TD 5L</t>
   </si>
   <si>
-    <t>CASTROL EDGE 5W40 TD 5L APR</t>
-  </si>
-  <si>
     <t>CASTROL MAGNATEC 10W40 A/B 1L APR</t>
   </si>
   <si>
@@ -1307,6 +1304,9 @@
   </si>
   <si>
     <t>ULEI MOTO</t>
+  </si>
+  <si>
+    <t>RAV Outboardoel 4T SAE 10W40 1L</t>
   </si>
 </sst>
 </file>
@@ -1751,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1765,7 +1765,7 @@
         <v>12.4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1779,7 +1779,7 @@
         <v>139.26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1793,40 +1793,40 @@
         <v>176.78</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3">
         <v>239.2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3">
         <v>262.61</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -1835,12 +1835,12 @@
         <v>407.86</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -1849,40 +1849,40 @@
         <v>635.11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B9" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3">
         <v>309.52</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B10" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3">
         <v>343.45</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B11" s="3">
         <v>5</v>
@@ -1891,12 +1891,12 @@
         <v>467.19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -1905,7 +1905,7 @@
         <v>535.12</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1919,12 +1919,12 @@
         <v>687.26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1933,12 +1933,12 @@
         <v>825.42</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1947,12 +1947,12 @@
         <v>902.73</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -1961,7 +1961,7 @@
         <v>698.39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1975,12 +1975,12 @@
         <v>909.67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -1989,12 +1989,12 @@
         <v>934.13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B19" s="3">
         <v>6</v>
@@ -2003,12 +2003,12 @@
         <v>1132.73</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B20" s="3">
         <v>19</v>
@@ -2017,12 +2017,12 @@
         <v>534.95000000000005</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B21" s="3">
         <v>3</v>
@@ -2031,12 +2031,12 @@
         <v>706.12</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
@@ -2045,12 +2045,12 @@
         <v>241.24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B23" s="3">
         <v>9</v>
@@ -2059,12 +2059,12 @@
         <v>278.02</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -2073,40 +2073,40 @@
         <v>358.39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B25" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3">
         <v>376.62</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
         <v>409.88</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B27" s="3">
         <v>19</v>
@@ -2115,12 +2115,12 @@
         <v>442.81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -2129,12 +2129,12 @@
         <v>491.37</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2143,7 +2143,7 @@
         <v>478.19</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2157,7 +2157,7 @@
         <v>41.58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2171,7 +2171,7 @@
         <v>5899.25</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2185,7 +2185,7 @@
         <v>5899.25</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2199,7 +2199,7 @@
         <v>182.58</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2213,7 +2213,7 @@
         <v>41.58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2227,7 +2227,7 @@
         <v>146.97999999999999</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2241,7 +2241,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2255,7 +2255,7 @@
         <v>34.619999999999997</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>122.46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2277,13 +2277,13 @@
         <v>17</v>
       </c>
       <c r="B39" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" s="3">
         <v>200.92</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2291,13 +2291,13 @@
         <v>18</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C40" s="3">
-        <v>156.07</v>
+        <v>25.61</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2305,13 +2305,13 @@
         <v>19</v>
       </c>
       <c r="B41" s="3">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C41" s="3">
-        <v>25.61</v>
+        <v>115.42</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2319,13 +2319,13 @@
         <v>20</v>
       </c>
       <c r="B42" s="3">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C42" s="3">
-        <v>115.42</v>
+        <v>25.6</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2333,10 +2333,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C43" s="3">
-        <v>25.6</v>
+        <v>36.4</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>374</v>
@@ -2347,10 +2347,10 @@
         <v>22</v>
       </c>
       <c r="B44" s="3">
-        <v>0</v>
+        <v>2624</v>
       </c>
       <c r="C44" s="3">
-        <v>36.4</v>
+        <v>13</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>375</v>
@@ -2361,10 +2361,10 @@
         <v>23</v>
       </c>
       <c r="B45" s="3">
-        <v>2648</v>
+        <v>66</v>
       </c>
       <c r="C45" s="3">
-        <v>13</v>
+        <v>23.37</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>376</v>
@@ -2375,13 +2375,13 @@
         <v>24</v>
       </c>
       <c r="B46" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C46" s="3">
-        <v>23.37</v>
+        <v>361.92</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2389,13 +2389,13 @@
         <v>25</v>
       </c>
       <c r="B47" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C47" s="3">
-        <v>361.92</v>
+        <v>21</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2403,13 +2403,13 @@
         <v>26</v>
       </c>
       <c r="B48" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C48" s="3">
-        <v>21</v>
+        <v>357.53</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2417,13 +2417,13 @@
         <v>27</v>
       </c>
       <c r="B49" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C49" s="3">
-        <v>357.53</v>
+        <v>19.3</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2431,13 +2431,13 @@
         <v>28</v>
       </c>
       <c r="B50" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C50" s="3">
-        <v>19.3</v>
+        <v>337.5</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2445,13 +2445,13 @@
         <v>29</v>
       </c>
       <c r="B51" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C51" s="3">
-        <v>337.5</v>
+        <v>33.64</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2459,13 +2459,13 @@
         <v>30</v>
       </c>
       <c r="B52" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C52" s="3">
-        <v>33.64</v>
+        <v>298.12</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2473,41 +2473,41 @@
         <v>31</v>
       </c>
       <c r="B53" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C53" s="3">
-        <v>298.12</v>
+        <v>1982.77</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>427</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C54" s="3">
-        <v>1982.77</v>
+        <v>144.34</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>428</v>
+        <v>32</v>
       </c>
       <c r="B55" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C55" s="3">
-        <v>144.34</v>
+        <v>280.12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2515,13 +2515,13 @@
         <v>33</v>
       </c>
       <c r="B56" s="3">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="C56" s="3">
-        <v>280.12</v>
+        <v>24.51</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2529,13 +2529,13 @@
         <v>34</v>
       </c>
       <c r="B57" s="3">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C57" s="3">
-        <v>24.51</v>
+        <v>26.21</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2543,13 +2543,13 @@
         <v>35</v>
       </c>
       <c r="B58" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C58" s="3">
-        <v>26.21</v>
+        <v>101.08</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2557,13 +2557,13 @@
         <v>36</v>
       </c>
       <c r="B59" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C59" s="3">
-        <v>101.08</v>
+        <v>29.13</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2571,13 +2571,13 @@
         <v>37</v>
       </c>
       <c r="B60" s="3">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="C60" s="3">
-        <v>29.13</v>
+        <v>102.31</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2585,13 +2585,13 @@
         <v>38</v>
       </c>
       <c r="B61" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C61" s="3">
-        <v>102.31</v>
+        <v>168.07</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2599,13 +2599,13 @@
         <v>39</v>
       </c>
       <c r="B62" s="3">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="C62" s="3">
-        <v>168.07</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2613,13 +2613,13 @@
         <v>40</v>
       </c>
       <c r="B63" s="3">
-        <v>234</v>
+        <v>69</v>
       </c>
       <c r="C63" s="3">
-        <v>16.600000000000001</v>
+        <v>70.47</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2627,41 +2627,41 @@
         <v>41</v>
       </c>
       <c r="B64" s="3">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C64" s="3">
-        <v>70.47</v>
+        <v>86.8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>428</v>
       </c>
       <c r="B65" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C65" s="3">
-        <v>86.8</v>
+        <v>1041.71</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>429</v>
+        <v>42</v>
       </c>
       <c r="B66" s="3">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="C66" s="3">
-        <v>1041.71</v>
+        <v>18.96</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2669,13 +2669,13 @@
         <v>43</v>
       </c>
       <c r="B67" s="3">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="C67" s="3">
-        <v>18.96</v>
+        <v>73.13</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2683,13 +2683,13 @@
         <v>44</v>
       </c>
       <c r="B68" s="3">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="C68" s="3">
-        <v>73.13</v>
+        <v>89.38</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2697,13 +2697,13 @@
         <v>45</v>
       </c>
       <c r="B69" s="3">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C69" s="3">
-        <v>89.38</v>
+        <v>18.96</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2711,13 +2711,13 @@
         <v>46</v>
       </c>
       <c r="B70" s="3">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C70" s="3">
-        <v>18.96</v>
+        <v>73.13</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2725,13 +2725,13 @@
         <v>47</v>
       </c>
       <c r="B71" s="3">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C71" s="3">
-        <v>73.13</v>
+        <v>89.39</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2739,13 +2739,13 @@
         <v>48</v>
       </c>
       <c r="B72" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C72" s="3">
-        <v>89.39</v>
+        <v>3173.52</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2753,13 +2753,13 @@
         <v>49</v>
       </c>
       <c r="B73" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C73" s="3">
-        <v>3173.52</v>
+        <v>25.4</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2767,13 +2767,13 @@
         <v>50</v>
       </c>
       <c r="B74" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C74" s="3">
-        <v>25.4</v>
+        <v>40.92</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2781,13 +2781,13 @@
         <v>51</v>
       </c>
       <c r="B75" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C75" s="3">
-        <v>40.92</v>
+        <v>25.4</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2795,41 +2795,41 @@
         <v>52</v>
       </c>
       <c r="B76" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C76" s="3">
-        <v>25.4</v>
+        <v>28.07</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>393</v>
       </c>
       <c r="B77" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C77" s="3">
-        <v>28.07</v>
+        <v>23.33</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>394</v>
+        <v>53</v>
       </c>
       <c r="B78" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C78" s="3">
-        <v>23.33</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2837,13 +2837,13 @@
         <v>54</v>
       </c>
       <c r="B79" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C79" s="3">
-        <v>34.630000000000003</v>
+        <v>18.37</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2851,13 +2851,13 @@
         <v>55</v>
       </c>
       <c r="B80" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C80" s="3">
-        <v>18.37</v>
+        <v>82.88</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2865,13 +2865,13 @@
         <v>56</v>
       </c>
       <c r="B81" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C81" s="3">
-        <v>82.88</v>
+        <v>161.01</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2879,13 +2879,13 @@
         <v>57</v>
       </c>
       <c r="B82" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C82" s="3">
-        <v>161.01</v>
+        <v>44.85</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2893,13 +2893,13 @@
         <v>58</v>
       </c>
       <c r="B83" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C83" s="3">
-        <v>44.85</v>
+        <v>65.83</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2907,13 +2907,13 @@
         <v>59</v>
       </c>
       <c r="B84" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C84" s="3">
-        <v>65.83</v>
+        <v>46.76</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2921,13 +2921,13 @@
         <v>60</v>
       </c>
       <c r="B85" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C85" s="3">
-        <v>46.76</v>
+        <v>62.11</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2935,13 +2935,13 @@
         <v>61</v>
       </c>
       <c r="B86" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C86" s="3">
-        <v>62.11</v>
+        <v>47.61</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2949,13 +2949,13 @@
         <v>62</v>
       </c>
       <c r="B87" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C87" s="3">
-        <v>47.61</v>
+        <v>63.76</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2966,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="C88" s="3">
-        <v>63.76</v>
+        <v>1159.2</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2980,10 +2980,10 @@
         <v>1</v>
       </c>
       <c r="C89" s="3">
-        <v>1159.2</v>
+        <v>255</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2991,13 +2991,13 @@
         <v>65</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C90" s="3">
-        <v>255</v>
+        <v>69.55</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3005,13 +3005,13 @@
         <v>66</v>
       </c>
       <c r="B91" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C91" s="3">
-        <v>69.55</v>
+        <v>1391.04</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3019,13 +3019,13 @@
         <v>67</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C92" s="3">
-        <v>1391.04</v>
+        <v>87.1</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3033,13 +3033,13 @@
         <v>68</v>
       </c>
       <c r="B93" s="3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C93" s="3">
-        <v>87.1</v>
+        <v>40.54</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3047,27 +3047,27 @@
         <v>69</v>
       </c>
       <c r="B94" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C94" s="3">
-        <v>40.54</v>
+        <v>460.01</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B95" s="3">
         <v>1</v>
       </c>
       <c r="C95" s="3">
-        <v>460.01</v>
+        <v>639.4</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3075,13 +3075,13 @@
         <v>70</v>
       </c>
       <c r="B96" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C96" s="3">
-        <v>639.4</v>
+        <v>103.89</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3089,13 +3089,13 @@
         <v>71</v>
       </c>
       <c r="B97" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C97" s="3">
-        <v>103.89</v>
+        <v>58.48</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3103,27 +3103,27 @@
         <v>72</v>
       </c>
       <c r="B98" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C98" s="3">
-        <v>58.48</v>
+        <v>56.93</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B99" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C99" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3131,13 +3131,13 @@
         <v>73</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C100" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3145,13 +3145,13 @@
         <v>74</v>
       </c>
       <c r="B101" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C101" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3159,13 +3159,13 @@
         <v>75</v>
       </c>
       <c r="B102" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C102" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3173,13 +3173,13 @@
         <v>76</v>
       </c>
       <c r="B103" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C103" s="3">
-        <v>69.56</v>
+        <v>59.68</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3187,13 +3187,13 @@
         <v>77</v>
       </c>
       <c r="B104" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C104" s="3">
-        <v>59.68</v>
+        <v>56.93</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3204,10 +3204,10 @@
         <v>32</v>
       </c>
       <c r="C105" s="3">
-        <v>56.93</v>
+        <v>80.73</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3215,13 +3215,13 @@
         <v>79</v>
       </c>
       <c r="B106" s="3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C106" s="3">
-        <v>80.73</v>
+        <v>98.95</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3229,13 +3229,13 @@
         <v>80</v>
       </c>
       <c r="B107" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C107" s="3">
-        <v>98.95</v>
+        <v>93.25</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3243,13 +3243,13 @@
         <v>81</v>
       </c>
       <c r="B108" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C108" s="3">
-        <v>93.25</v>
+        <v>63.76</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3257,13 +3257,13 @@
         <v>82</v>
       </c>
       <c r="B109" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C109" s="3">
         <v>63.76</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3271,13 +3271,13 @@
         <v>83</v>
       </c>
       <c r="B110" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C110" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3285,13 +3285,13 @@
         <v>84</v>
       </c>
       <c r="B111" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C111" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3299,13 +3299,13 @@
         <v>85</v>
       </c>
       <c r="B112" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C112" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3313,13 +3313,13 @@
         <v>86</v>
       </c>
       <c r="B113" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C113" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3327,13 +3327,13 @@
         <v>87</v>
       </c>
       <c r="B114" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C114" s="3">
-        <v>63.76</v>
+        <v>69.56</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3341,13 +3341,13 @@
         <v>88</v>
       </c>
       <c r="B115" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C115" s="3">
         <v>69.56</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3355,13 +3355,13 @@
         <v>89</v>
       </c>
       <c r="B116" s="3">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C116" s="3">
-        <v>69.56</v>
+        <v>52.17</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3369,13 +3369,13 @@
         <v>90</v>
       </c>
       <c r="B117" s="3">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C117" s="3">
-        <v>52.17</v>
+        <v>208.66</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3383,13 +3383,13 @@
         <v>91</v>
       </c>
       <c r="B118" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C118" s="3">
-        <v>208.66</v>
+        <v>88.87</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3397,13 +3397,13 @@
         <v>92</v>
       </c>
       <c r="B119" s="3">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C119" s="3">
-        <v>88.87</v>
+        <v>67.27</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3411,13 +3411,13 @@
         <v>93</v>
       </c>
       <c r="B120" s="3">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C120" s="3">
-        <v>67.27</v>
+        <v>69.55</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3425,13 +3425,13 @@
         <v>94</v>
       </c>
       <c r="B121" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C121" s="3">
-        <v>69.55</v>
+        <v>63.89</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3439,13 +3439,13 @@
         <v>95</v>
       </c>
       <c r="B122" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C122" s="3">
-        <v>63.89</v>
+        <v>149.91</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3453,13 +3453,13 @@
         <v>96</v>
       </c>
       <c r="B123" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C123" s="3">
-        <v>149.91</v>
+        <v>38.57</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3467,13 +3467,13 @@
         <v>97</v>
       </c>
       <c r="B124" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C124" s="3">
-        <v>38.57</v>
+        <v>207.31</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3481,13 +3481,13 @@
         <v>98</v>
       </c>
       <c r="B125" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C125" s="3">
-        <v>207.31</v>
+        <v>65.23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3495,13 +3495,13 @@
         <v>99</v>
       </c>
       <c r="B126" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C126" s="3">
-        <v>65.23</v>
+        <v>325.87</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3509,13 +3509,13 @@
         <v>100</v>
       </c>
       <c r="B127" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C127" s="3">
-        <v>325.87</v>
+        <v>5165.8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3523,13 +3523,13 @@
         <v>101</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128" s="3">
-        <v>5165.8</v>
+        <v>511.75</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3537,13 +3537,13 @@
         <v>102</v>
       </c>
       <c r="B129" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C129" s="3">
-        <v>511.75</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3551,13 +3551,13 @@
         <v>103</v>
       </c>
       <c r="B130" s="3">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="C130" s="3">
-        <v>572.70000000000005</v>
+        <v>66.98</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3565,13 +3565,13 @@
         <v>104</v>
       </c>
       <c r="B131" s="3">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="C131" s="3">
-        <v>66.98</v>
+        <v>367.42</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3579,13 +3579,13 @@
         <v>105</v>
       </c>
       <c r="B132" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C132" s="3">
-        <v>367.42</v>
+        <v>51.52</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3593,13 +3593,13 @@
         <v>106</v>
       </c>
       <c r="B133" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C133" s="3">
-        <v>51.52</v>
+        <v>23.19</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3607,13 +3607,13 @@
         <v>107</v>
       </c>
       <c r="B134" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C134" s="3">
         <v>23.19</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3621,10 +3621,10 @@
         <v>108</v>
       </c>
       <c r="B135" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C135" s="3">
-        <v>23.19</v>
+        <v>69.55</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>376</v>
@@ -3635,13 +3635,13 @@
         <v>109</v>
       </c>
       <c r="B136" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C136" s="3">
-        <v>69.55</v>
+        <v>3169.7</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3649,13 +3649,13 @@
         <v>110</v>
       </c>
       <c r="B137" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C137" s="3">
-        <v>3169.7</v>
+        <v>81.14</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3663,13 +3663,13 @@
         <v>111</v>
       </c>
       <c r="B138" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C138" s="3">
         <v>81.14</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3677,13 +3677,13 @@
         <v>112</v>
       </c>
       <c r="B139" s="3">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C139" s="3">
-        <v>81.14</v>
+        <v>66.98</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3691,13 +3691,13 @@
         <v>113</v>
       </c>
       <c r="B140" s="3">
-        <v>60</v>
-      </c>
-      <c r="C140" s="3">
-        <v>66.98</v>
+        <v>34</v>
+      </c>
+      <c r="C140" s="8">
+        <v>74.989999999999995</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3705,13 +3705,13 @@
         <v>114</v>
       </c>
       <c r="B141" s="3">
-        <v>34</v>
-      </c>
-      <c r="C141" s="8">
-        <v>74.989999999999995</v>
+        <v>21</v>
+      </c>
+      <c r="C141" s="3">
+        <v>93.35</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3719,13 +3719,13 @@
         <v>115</v>
       </c>
       <c r="B142" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C142" s="3">
-        <v>93.35</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3736,10 +3736,10 @@
         <v>1</v>
       </c>
       <c r="C143" s="3">
-        <v>1217.1600000000001</v>
+        <v>3079</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3747,27 +3747,27 @@
         <v>117</v>
       </c>
       <c r="B144" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C144" s="3">
-        <v>3079</v>
+        <v>43.7</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B145" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C145" s="3">
-        <v>43.7</v>
+        <v>48.95</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3775,13 +3775,13 @@
         <v>118</v>
       </c>
       <c r="B146" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C146" s="3">
-        <v>48.95</v>
+        <v>72.33</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3789,13 +3789,13 @@
         <v>119</v>
       </c>
       <c r="B147" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C147" s="3">
-        <v>72.33</v>
+        <v>284.19</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3803,13 +3803,13 @@
         <v>120</v>
       </c>
       <c r="B148" s="3">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C148" s="3">
-        <v>284.19</v>
+        <v>132.19</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3817,13 +3817,13 @@
         <v>121</v>
       </c>
       <c r="B149" s="3">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C149" s="3">
-        <v>132.19</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3831,13 +3831,13 @@
         <v>122</v>
       </c>
       <c r="B150" s="3">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C150" s="3">
         <v>32.200000000000003</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3845,13 +3845,13 @@
         <v>123</v>
       </c>
       <c r="B151" s="3">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C151" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3859,13 +3859,13 @@
         <v>124</v>
       </c>
       <c r="B152" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C152" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3873,13 +3873,13 @@
         <v>125</v>
       </c>
       <c r="B153" s="3">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C153" s="3">
-        <v>32.200000000000003</v>
+        <v>115.01</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3887,13 +3887,13 @@
         <v>126</v>
       </c>
       <c r="B154" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C154" s="3">
-        <v>115.01</v>
+        <v>38.39</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3901,13 +3901,13 @@
         <v>127</v>
       </c>
       <c r="B155" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C155" s="3">
-        <v>38.39</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3915,13 +3915,13 @@
         <v>128</v>
       </c>
       <c r="B156" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C156" s="3">
-        <v>151.47999999999999</v>
+        <v>181.68</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3929,13 +3929,13 @@
         <v>129</v>
       </c>
       <c r="B157" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C157" s="3">
-        <v>181.68</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3943,13 +3943,13 @@
         <v>130</v>
       </c>
       <c r="B158" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C158" s="3">
-        <v>20.059999999999999</v>
+        <v>12.88</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3957,13 +3957,13 @@
         <v>131</v>
       </c>
       <c r="B159" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C159" s="3">
-        <v>12.88</v>
+        <v>26.73</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3971,13 +3971,13 @@
         <v>132</v>
       </c>
       <c r="B160" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C160" s="3">
-        <v>26.73</v>
+        <v>29.95</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3985,13 +3985,13 @@
         <v>133</v>
       </c>
       <c r="B161" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C161" s="3">
-        <v>29.95</v>
+        <v>58.68</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3999,13 +3999,13 @@
         <v>134</v>
       </c>
       <c r="B162" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C162" s="3">
-        <v>58.68</v>
+        <v>79.98</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4013,13 +4013,13 @@
         <v>135</v>
       </c>
       <c r="B163" s="3">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C163" s="3">
-        <v>79.98</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4027,13 +4027,13 @@
         <v>136</v>
       </c>
       <c r="B164" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C164" s="3">
-        <v>38.770000000000003</v>
+        <v>107.35</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4041,13 +4041,13 @@
         <v>137</v>
       </c>
       <c r="B165" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C165" s="3">
-        <v>107.35</v>
+        <v>61.83</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4055,13 +4055,13 @@
         <v>138</v>
       </c>
       <c r="B166" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C166" s="3">
-        <v>61.83</v>
+        <v>243.16</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4069,13 +4069,13 @@
         <v>139</v>
       </c>
       <c r="B167" s="3">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C167" s="3">
-        <v>243.16</v>
+        <v>63.78</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4083,13 +4083,13 @@
         <v>140</v>
       </c>
       <c r="B168" s="3">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C168" s="3">
-        <v>63.78</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4097,13 +4097,13 @@
         <v>141</v>
       </c>
       <c r="B169" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C169" s="3">
-        <v>75.989999999999995</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4111,13 +4111,13 @@
         <v>142</v>
       </c>
       <c r="B170" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C170" s="3">
-        <v>297.64999999999998</v>
+        <v>77.28</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4128,10 +4128,10 @@
         <v>14</v>
       </c>
       <c r="C171" s="3">
-        <v>77.28</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4139,13 +4139,13 @@
         <v>144</v>
       </c>
       <c r="B172" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C172" s="3">
-        <v>75.989999999999995</v>
+        <v>342.24</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4153,13 +4153,13 @@
         <v>145</v>
       </c>
       <c r="B173" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C173" s="3">
-        <v>342.24</v>
+        <v>633.75</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4167,13 +4167,13 @@
         <v>146</v>
       </c>
       <c r="B174" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="C174" s="3">
-        <v>633.75</v>
+        <v>50.51</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4181,13 +4181,13 @@
         <v>147</v>
       </c>
       <c r="B175" s="3">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C175" s="3">
-        <v>50.51</v>
+        <v>787.75</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4195,13 +4195,13 @@
         <v>148</v>
       </c>
       <c r="B176" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C176" s="3">
-        <v>787.75</v>
+        <v>122.36</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4209,13 +4209,13 @@
         <v>149</v>
       </c>
       <c r="B177" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C177" s="3">
-        <v>122.36</v>
+        <v>35.81</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4223,13 +4223,13 @@
         <v>150</v>
       </c>
       <c r="B178" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C178" s="3">
-        <v>35.81</v>
+        <v>59.25</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4237,13 +4237,13 @@
         <v>151</v>
       </c>
       <c r="B179" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C179" s="3">
-        <v>59.25</v>
+        <v>201.84</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4251,13 +4251,13 @@
         <v>152</v>
       </c>
       <c r="B180" s="3">
-        <v>5</v>
-      </c>
-      <c r="C180" s="3">
-        <v>201.84</v>
+        <v>20</v>
+      </c>
+      <c r="C180" s="7">
+        <v>57.59</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4265,13 +4265,13 @@
         <v>153</v>
       </c>
       <c r="B181" s="3">
-        <v>20</v>
-      </c>
-      <c r="C181" s="7">
-        <v>57.59</v>
+        <v>9</v>
+      </c>
+      <c r="C181" s="3">
+        <v>248.77</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4279,13 +4279,13 @@
         <v>154</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C182" s="3">
-        <v>221.86</v>
+        <v>74.7</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4293,41 +4293,41 @@
         <v>155</v>
       </c>
       <c r="B183" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C183" s="3">
-        <v>74.7</v>
+        <v>296.3</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>156</v>
+        <v>394</v>
       </c>
       <c r="B184" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C184" s="3">
-        <v>296.3</v>
+        <v>141.80000000000001</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>395</v>
+        <v>156</v>
       </c>
       <c r="B185" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C185" s="3">
-        <v>141.80000000000001</v>
+        <v>41.4</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4335,13 +4335,13 @@
         <v>157</v>
       </c>
       <c r="B186" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C186" s="3">
-        <v>41.4</v>
+        <v>173.3</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4349,13 +4349,13 @@
         <v>158</v>
       </c>
       <c r="B187" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C187" s="3">
-        <v>173.3</v>
+        <v>2189.02</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4366,10 +4366,10 @@
         <v>2</v>
       </c>
       <c r="C188" s="3">
-        <v>2189.02</v>
+        <v>453.22</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4377,13 +4377,13 @@
         <v>160</v>
       </c>
       <c r="B189" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C189" s="3">
-        <v>453.22</v>
+        <v>48.64</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4391,13 +4391,13 @@
         <v>161</v>
       </c>
       <c r="B190" s="3">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C190" s="3">
-        <v>48.64</v>
+        <v>126.63</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4408,10 +4408,10 @@
         <v>5</v>
       </c>
       <c r="C191" s="3">
-        <v>126.63</v>
+        <v>69.56</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4419,13 +4419,13 @@
         <v>163</v>
       </c>
       <c r="B192" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C192" s="3">
-        <v>69.56</v>
+        <v>44.51</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4433,13 +4433,13 @@
         <v>164</v>
       </c>
       <c r="B193" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C193" s="3">
-        <v>44.51</v>
+        <v>145.94</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4447,13 +4447,13 @@
         <v>165</v>
       </c>
       <c r="B194" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C194" s="3">
-        <v>145.94</v>
+        <v>179</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4461,13 +4461,13 @@
         <v>166</v>
       </c>
       <c r="B195" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C195" s="3">
-        <v>179</v>
+        <v>2060</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4475,13 +4475,13 @@
         <v>167</v>
       </c>
       <c r="B196" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C196" s="3">
-        <v>2060</v>
+        <v>51</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4489,41 +4489,41 @@
         <v>168</v>
       </c>
       <c r="B197" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C197" s="3">
-        <v>51</v>
+        <v>183.41</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>169</v>
+        <v>361</v>
       </c>
       <c r="B198" s="3">
-        <v>7</v>
-      </c>
-      <c r="C198" s="3">
-        <v>183.41</v>
+        <v>8</v>
+      </c>
+      <c r="C198" s="8">
+        <v>248.99</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>362</v>
+        <v>169</v>
       </c>
       <c r="B199" s="3">
-        <v>9</v>
-      </c>
-      <c r="C199" s="8">
-        <v>248.99</v>
+        <v>51</v>
+      </c>
+      <c r="C199" s="3">
+        <v>33.479999999999997</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4531,13 +4531,13 @@
         <v>170</v>
       </c>
       <c r="B200" s="3">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C200" s="3">
-        <v>33.479999999999997</v>
+        <v>48.13</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4545,13 +4545,13 @@
         <v>171</v>
       </c>
       <c r="B201" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C201" s="3">
-        <v>46.06</v>
+        <v>5400</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4559,13 +4559,13 @@
         <v>172</v>
       </c>
       <c r="B202" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C202" s="3">
-        <v>5400</v>
+        <v>170.78</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4573,13 +4573,13 @@
         <v>173</v>
       </c>
       <c r="B203" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C203" s="3">
-        <v>170.78</v>
+        <v>216.3</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4587,13 +4587,13 @@
         <v>174</v>
       </c>
       <c r="B204" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C204" s="3">
-        <v>192.51</v>
+        <v>59.7</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4601,13 +4601,13 @@
         <v>175</v>
       </c>
       <c r="B205" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C205" s="3">
-        <v>59.7</v>
+        <v>265.05</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4615,13 +4615,13 @@
         <v>176</v>
       </c>
       <c r="B206" s="3">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C206" s="3">
-        <v>265.05</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4629,13 +4629,13 @@
         <v>177</v>
       </c>
       <c r="B207" s="3">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C207" s="3">
-        <v>36.799999999999997</v>
+        <v>103.04</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4643,13 +4643,13 @@
         <v>178</v>
       </c>
       <c r="B208" s="3">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C208" s="3">
-        <v>103.04</v>
+        <v>36.75</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4657,13 +4657,13 @@
         <v>179</v>
       </c>
       <c r="B209" s="3">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C209" s="3">
-        <v>36.75</v>
+        <v>47.16</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4671,13 +4671,13 @@
         <v>180</v>
       </c>
       <c r="B210" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C210" s="3">
-        <v>47.16</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4685,13 +4685,13 @@
         <v>181</v>
       </c>
       <c r="B211" s="3">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C211" s="3">
-        <v>16.809999999999999</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4699,13 +4699,13 @@
         <v>182</v>
       </c>
       <c r="B212" s="3">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C212" s="3">
-        <v>37.299999999999997</v>
+        <v>126.24</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4713,13 +4713,13 @@
         <v>183</v>
       </c>
       <c r="B213" s="3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C213" s="3">
-        <v>126.24</v>
+        <v>154.62</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4727,13 +4727,13 @@
         <v>184</v>
       </c>
       <c r="B214" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C214" s="3">
-        <v>154.62</v>
+        <v>508.2</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4741,13 +4741,13 @@
         <v>185</v>
       </c>
       <c r="B215" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C215" s="3">
-        <v>508.2</v>
+        <v>5069</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4755,13 +4755,13 @@
         <v>186</v>
       </c>
       <c r="B216" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C216" s="3">
-        <v>5069</v>
+        <v>466.78</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4769,13 +4769,13 @@
         <v>187</v>
       </c>
       <c r="B217" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C217" s="3">
-        <v>466.78</v>
+        <v>57.5</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4783,13 +4783,13 @@
         <v>188</v>
       </c>
       <c r="B218" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C218" s="3">
-        <v>57.5</v>
+        <v>63.13</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4797,27 +4797,27 @@
         <v>189</v>
       </c>
       <c r="B219" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C219" s="3">
-        <v>63.13</v>
+        <v>20789.41</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B220" s="3">
         <v>1</v>
       </c>
       <c r="C220" s="3">
-        <v>20789.41</v>
+        <v>33057.85</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4825,13 +4825,13 @@
         <v>190</v>
       </c>
       <c r="B221" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C221" s="3">
-        <v>33057.85</v>
+        <v>83.5</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4839,13 +4839,13 @@
         <v>191</v>
       </c>
       <c r="B222" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C222" s="3">
-        <v>83.5</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4853,13 +4853,13 @@
         <v>192</v>
       </c>
       <c r="B223" s="3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C223" s="3">
-        <v>81.650000000000006</v>
+        <v>50.71</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4867,13 +4867,13 @@
         <v>193</v>
       </c>
       <c r="B224" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C224" s="3">
-        <v>50.71</v>
+        <v>51.75</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4881,13 +4881,13 @@
         <v>194</v>
       </c>
       <c r="B225" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C225" s="3">
-        <v>51.75</v>
+        <v>36.94</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4895,13 +4895,13 @@
         <v>195</v>
       </c>
       <c r="B226" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C226" s="3">
         <v>36.94</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4909,13 +4909,13 @@
         <v>196</v>
       </c>
       <c r="B227" s="3">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C227" s="3">
-        <v>36.94</v>
+        <v>67.28</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>430</v>
+        <v>376</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4923,13 +4923,13 @@
         <v>197</v>
       </c>
       <c r="B228" s="3">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C228" s="3">
-        <v>67.28</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4937,13 +4937,13 @@
         <v>198</v>
       </c>
       <c r="B229" s="3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C229" s="3">
-        <v>65.099999999999994</v>
+        <v>65.53</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4951,13 +4951,13 @@
         <v>199</v>
       </c>
       <c r="B230" s="3">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C230" s="3">
-        <v>65.53</v>
+        <v>109.08</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4965,13 +4965,13 @@
         <v>200</v>
       </c>
       <c r="B231" s="3">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C231" s="3">
-        <v>109.08</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4979,13 +4979,13 @@
         <v>201</v>
       </c>
       <c r="B232" s="3">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="C232" s="3">
-        <v>33.479999999999997</v>
+        <v>422.09</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4993,13 +4993,13 @@
         <v>202</v>
       </c>
       <c r="B233" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C233" s="3">
-        <v>422.09</v>
+        <v>1277.7</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5007,13 +5007,13 @@
         <v>203</v>
       </c>
       <c r="B234" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C234" s="3">
-        <v>1277.7</v>
+        <v>6.44</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5021,13 +5021,13 @@
         <v>204</v>
       </c>
       <c r="B235" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C235" s="3">
-        <v>6.44</v>
+        <v>108.2</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5035,27 +5035,27 @@
         <v>205</v>
       </c>
       <c r="B236" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C236" s="3">
-        <v>108.2</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B237" s="3">
         <v>1</v>
       </c>
       <c r="C237" s="3">
-        <v>4456.4799999999996</v>
+        <v>6279</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5063,13 +5063,13 @@
         <v>206</v>
       </c>
       <c r="B238" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C238" s="3">
-        <v>6279</v>
+        <v>609.5</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5077,13 +5077,13 @@
         <v>207</v>
       </c>
       <c r="B239" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C239" s="3">
-        <v>609.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5091,13 +5091,13 @@
         <v>208</v>
       </c>
       <c r="B240" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C240" s="3">
         <v>32.200000000000003</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5105,13 +5105,13 @@
         <v>209</v>
       </c>
       <c r="B241" s="3">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C241" s="3">
         <v>32.200000000000003</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5119,13 +5119,13 @@
         <v>210</v>
       </c>
       <c r="B242" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C242" s="3">
         <v>32.200000000000003</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5133,13 +5133,13 @@
         <v>211</v>
       </c>
       <c r="B243" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C243" s="3">
-        <v>32.200000000000003</v>
+        <v>40.4</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5147,13 +5147,13 @@
         <v>212</v>
       </c>
       <c r="B244" s="3">
-        <v>7</v>
+        <v>187</v>
       </c>
       <c r="C244" s="3">
-        <v>40.4</v>
+        <v>36.06</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5161,13 +5161,13 @@
         <v>213</v>
       </c>
       <c r="B245" s="3">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="C245" s="3">
-        <v>36.06</v>
+        <v>56</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5175,13 +5175,13 @@
         <v>214</v>
       </c>
       <c r="B246" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C246" s="3">
-        <v>56</v>
+        <v>57.63</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5189,32 +5189,32 @@
         <v>215</v>
       </c>
       <c r="B247" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C247" s="3">
-        <v>57.63</v>
+        <v>60.78</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>216</v>
+        <v>430</v>
       </c>
       <c r="B248" s="3">
         <v>4</v>
       </c>
       <c r="C248" s="3">
-        <v>60.78</v>
+        <v>65</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B249" s="3">
         <v>9</v>
@@ -5223,26 +5223,26 @@
         <v>42.49</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>218</v>
-      </c>
-      <c r="B250" s="3">
-        <v>16</v>
+        <v>217</v>
+      </c>
+      <c r="B250" s="4">
+        <v>11</v>
       </c>
       <c r="C250" s="8">
         <v>84</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B251" s="3">
         <v>4</v>
@@ -5251,12 +5251,12 @@
         <v>301.99</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B252" s="3">
         <v>14</v>
@@ -5265,12 +5265,12 @@
         <v>71.709999999999994</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B253" s="3">
         <v>1</v>
@@ -5279,12 +5279,12 @@
         <v>77.760000000000005</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B254" s="3">
         <v>17</v>
@@ -5293,12 +5293,12 @@
         <v>54.7</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B255" s="3">
         <v>10</v>
@@ -5307,26 +5307,26 @@
         <v>67.28</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B256" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C256" s="3">
         <v>251.5</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B257" s="3">
         <v>12</v>
@@ -5335,12 +5335,12 @@
         <v>78.87</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B258" s="3">
         <v>13</v>
@@ -5349,12 +5349,12 @@
         <v>83.84</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B259" s="3">
         <v>4</v>
@@ -5363,12 +5363,12 @@
         <v>331.2</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B260" s="3">
         <v>15</v>
@@ -5377,12 +5377,12 @@
         <v>79.75</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B261" s="3">
         <v>22</v>
@@ -5391,12 +5391,12 @@
         <v>83.84</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B262" s="3">
         <v>5</v>
@@ -5405,12 +5405,12 @@
         <v>284</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B263" s="3">
         <v>12</v>
@@ -5419,12 +5419,12 @@
         <v>28.15</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -5433,12 +5433,12 @@
         <v>45.08</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B265" s="3">
         <v>9</v>
@@ -5447,12 +5447,12 @@
         <v>51.52</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B266" s="3">
         <v>5</v>
@@ -5461,12 +5461,12 @@
         <v>40.57</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B267" s="3">
         <v>27</v>
@@ -5475,12 +5475,12 @@
         <v>36.229999999999997</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B268" s="3">
         <v>24</v>
@@ -5489,12 +5489,12 @@
         <v>54.12</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B269" s="3">
         <v>12</v>
@@ -5503,12 +5503,12 @@
         <v>69.55</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B270" s="3">
         <v>9</v>
@@ -5517,12 +5517,12 @@
         <v>295.14999999999998</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B271" s="3">
         <v>6</v>
@@ -5531,12 +5531,12 @@
         <v>38.56</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B272" s="3">
         <v>7</v>
@@ -5545,12 +5545,12 @@
         <v>60.95</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B273" s="3">
         <v>10</v>
@@ -5559,26 +5559,26 @@
         <v>78.209999999999994</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B274" s="3">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C274" s="3">
         <v>44.93</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B275" s="3">
         <v>1</v>
@@ -5587,40 +5587,40 @@
         <v>6578.46</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B276" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C276" s="3">
         <v>173.09</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B277" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C277" s="3">
         <v>215.08</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B278" s="3">
         <v>4</v>
@@ -5629,12 +5629,12 @@
         <v>2314.8000000000002</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B279" s="3">
         <v>0</v>
@@ -5643,12 +5643,12 @@
         <v>791.3</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B280" s="3">
         <v>26</v>
@@ -5657,12 +5657,12 @@
         <v>31.6</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B281" s="3">
         <v>7</v>
@@ -5671,12 +5671,12 @@
         <v>77.28</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B282" s="3">
         <v>24</v>
@@ -5685,12 +5685,12 @@
         <v>43.8</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B283" s="3">
         <v>7</v>
@@ -5699,12 +5699,12 @@
         <v>21.9</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B284" s="3">
         <v>3</v>
@@ -5713,12 +5713,12 @@
         <v>798.6</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B285" s="3">
         <v>88</v>
@@ -5727,12 +5727,12 @@
         <v>23.19</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B286" s="3">
         <v>63</v>
@@ -5741,12 +5741,12 @@
         <v>8.24</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B287" s="3">
         <v>8</v>
@@ -5755,12 +5755,12 @@
         <v>13.72</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B288" s="3">
         <v>9</v>
@@ -5769,12 +5769,12 @@
         <v>31.95</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B289" s="3">
         <v>105</v>
@@ -5783,12 +5783,12 @@
         <v>16.2</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B290" s="3">
         <v>6</v>
@@ -5797,12 +5797,12 @@
         <v>36.869999999999997</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B291" s="3">
         <v>21</v>
@@ -5811,12 +5811,12 @@
         <v>31.48</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B292" s="3">
         <v>7</v>
@@ -5825,12 +5825,12 @@
         <v>21.9</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B293" s="3">
         <v>6</v>
@@ -5839,12 +5839,12 @@
         <v>23.19</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B294" s="3">
         <v>12</v>
@@ -5853,12 +5853,12 @@
         <v>19.55</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B295" s="3">
         <v>11</v>
@@ -5867,12 +5867,12 @@
         <v>19.07</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B296" s="3">
         <v>34</v>
@@ -5881,12 +5881,12 @@
         <v>21.9</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B297" s="3">
         <v>20</v>
@@ -5895,12 +5895,12 @@
         <v>79.349999999999994</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B298" s="3">
         <v>1</v>
@@ -5909,12 +5909,12 @@
         <v>862.7</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B299" s="3">
         <v>11</v>
@@ -5923,12 +5923,12 @@
         <v>56.93</v>
       </c>
   